--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F325"/>
+  <dimension ref="A1:F320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,235 +463,235 @@
         <v>21.84</v>
       </c>
       <c r="D2" t="n">
-        <v>23.34</v>
+        <v>23.07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.87</v>
+        <v>5.63</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.27475</v>
+        <v>-0.19239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38.22</v>
+        <v>11.65</v>
       </c>
       <c r="D3" t="n">
-        <v>42.13</v>
+        <v>12.3</v>
       </c>
       <c r="E3" t="n">
-        <v>10.23</v>
+        <v>5.54</v>
       </c>
       <c r="F3" t="n">
-        <v>0.37088</v>
+        <v>-0.14275</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.87</v>
+        <v>54.33</v>
       </c>
       <c r="D4" t="n">
-        <v>21.15</v>
+        <v>57.31</v>
       </c>
       <c r="E4" t="n">
-        <v>18.35</v>
+        <v>5.48</v>
       </c>
       <c r="F4" t="n">
-        <v>0.44142</v>
+        <v>-0.3375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.03</v>
+        <v>38.22</v>
       </c>
       <c r="D5" t="n">
-        <v>14.34</v>
+        <v>41.87</v>
       </c>
       <c r="E5" t="n">
-        <v>10.05</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1198</v>
+        <v>0.19936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.67</v>
+        <v>17.87</v>
       </c>
       <c r="D6" t="n">
-        <v>6.94</v>
+        <v>21.65</v>
       </c>
       <c r="E6" t="n">
-        <v>22.4</v>
+        <v>21.15</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1411</v>
+        <v>0.6622400000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.36</v>
+        <v>102.63</v>
       </c>
       <c r="D7" t="n">
-        <v>61.53</v>
+        <v>109.35</v>
       </c>
       <c r="E7" t="n">
-        <v>11.15</v>
+        <v>6.54</v>
       </c>
       <c r="F7" t="n">
-        <v>0.65096</v>
+        <v>-0.19827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>298.59</v>
+        <v>13.03</v>
       </c>
       <c r="D8" t="n">
-        <v>323.96</v>
+        <v>14.74</v>
       </c>
       <c r="E8" t="n">
-        <v>8.5</v>
+        <v>13.16</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.06779</v>
+        <v>-0.03934</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>141.63</v>
+        <v>298.59</v>
       </c>
       <c r="D9" t="n">
-        <v>152.78</v>
+        <v>335.36</v>
       </c>
       <c r="E9" t="n">
-        <v>7.87</v>
+        <v>12.31</v>
       </c>
       <c r="F9" t="n">
-        <v>0.47217</v>
+        <v>-1.45657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.17</v>
+        <v>5.67</v>
       </c>
       <c r="D10" t="n">
-        <v>8.33</v>
+        <v>7.07</v>
       </c>
       <c r="E10" t="n">
-        <v>16.18</v>
+        <v>24.6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.15793</v>
+        <v>0.16814</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.98</v>
+        <v>141.63</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>157.01</v>
       </c>
       <c r="E11" t="n">
-        <v>20.81</v>
+        <v>10.86</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0764</v>
+        <v>1.08529</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.23</v>
+        <v>4.46</v>
       </c>
       <c r="D12" t="n">
-        <v>11.85</v>
+        <v>5.21</v>
       </c>
       <c r="E12" t="n">
-        <v>5.52</v>
+        <v>16.82</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02603</v>
+        <v>0.08419</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.46</v>
+        <v>12.43</v>
       </c>
       <c r="D13" t="n">
-        <v>5.29</v>
+        <v>18.51</v>
       </c>
       <c r="E13" t="n">
-        <v>18.61</v>
+        <v>48.95</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09936</v>
+        <v>0.98721</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,70 +748,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.43</v>
+        <v>7.17</v>
       </c>
       <c r="D14" t="n">
-        <v>17.55</v>
+        <v>8.19</v>
       </c>
       <c r="E14" t="n">
-        <v>41.19</v>
+        <v>14.3</v>
       </c>
       <c r="F14" t="n">
-        <v>0.96113</v>
+        <v>0.13194</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KEP</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.18</v>
+        <v>11.23</v>
       </c>
       <c r="D15" t="n">
-        <v>12.21</v>
+        <v>11.81</v>
       </c>
       <c r="E15" t="n">
-        <v>9.210000000000001</v>
+        <v>5.12</v>
       </c>
       <c r="F15" t="n">
-        <v>0.13627</v>
+        <v>0.02403</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STLA</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.05</v>
+        <v>2.98</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4</v>
+        <v>3.53</v>
       </c>
       <c r="E16" t="n">
-        <v>6.93</v>
+        <v>18.29</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.02486</v>
+        <v>0.06673999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.28</v>
+        <v>98.45</v>
       </c>
       <c r="D17" t="n">
-        <v>18.89</v>
+        <v>123.05</v>
       </c>
       <c r="E17" t="n">
-        <v>9.32</v>
+        <v>24.99</v>
       </c>
       <c r="F17" t="n">
-        <v>0.20552</v>
+        <v>2.3585</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -844,184 +844,184 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>98.45</v>
+        <v>17.28</v>
       </c>
       <c r="D18" t="n">
-        <v>121.1</v>
+        <v>19.02</v>
       </c>
       <c r="E18" t="n">
-        <v>23.01</v>
+        <v>10.07</v>
       </c>
       <c r="F18" t="n">
-        <v>3.05519</v>
+        <v>0.21357</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VALE</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13.63</v>
+        <v>35.54</v>
       </c>
       <c r="D19" t="n">
-        <v>15.23</v>
+        <v>50.87</v>
       </c>
       <c r="E19" t="n">
-        <v>11.74</v>
+        <v>43.13</v>
       </c>
       <c r="F19" t="n">
-        <v>0.14495</v>
+        <v>1.94244</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>PPC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>52.62</v>
+        <v>26.51</v>
       </c>
       <c r="D20" t="n">
-        <v>57.39</v>
+        <v>30.48</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>14.98</v>
       </c>
       <c r="F20" t="n">
-        <v>0.73467</v>
+        <v>-0.01849</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.54</v>
+        <v>123.39</v>
       </c>
       <c r="D21" t="n">
-        <v>45.5</v>
+        <v>137.67</v>
       </c>
       <c r="E21" t="n">
-        <v>28.02</v>
+        <v>11.57</v>
       </c>
       <c r="F21" t="n">
-        <v>1.51007</v>
+        <v>1.3686</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>123.39</v>
+        <v>63.54</v>
       </c>
       <c r="D22" t="n">
-        <v>136.61</v>
+        <v>69.95</v>
       </c>
       <c r="E22" t="n">
-        <v>10.71</v>
+        <v>10.09</v>
       </c>
       <c r="F22" t="n">
-        <v>1.27266</v>
+        <v>-0.01106</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>60.35</v>
+        <v>155.62</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59999999999999</v>
+        <v>164.02</v>
       </c>
       <c r="E23" t="n">
-        <v>50.12</v>
+        <v>5.4</v>
       </c>
       <c r="F23" t="n">
-        <v>2.03637</v>
+        <v>-0.98034</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.83</v>
+        <v>60.35</v>
       </c>
       <c r="D24" t="n">
-        <v>35.92</v>
+        <v>96.83</v>
       </c>
       <c r="E24" t="n">
-        <v>29.07</v>
+        <v>60.45</v>
       </c>
       <c r="F24" t="n">
-        <v>0.21349</v>
+        <v>1.90433</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>FIGR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.81</v>
+        <v>24.91</v>
       </c>
       <c r="D25" t="n">
-        <v>10.6</v>
+        <v>36.38</v>
       </c>
       <c r="E25" t="n">
-        <v>35.72</v>
+        <v>46.05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04089</v>
+        <v>0.43295</v>
       </c>
     </row>
     <row r="26">
@@ -1039,43 +1039,43 @@
         <v>205.48</v>
       </c>
       <c r="D26" t="n">
-        <v>248.68</v>
+        <v>248.66</v>
       </c>
       <c r="E26" t="n">
-        <v>21.02</v>
+        <v>21.01</v>
       </c>
       <c r="F26" t="n">
-        <v>2.43479</v>
+        <v>1.11338</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>48.68</v>
+        <v>7.81</v>
       </c>
       <c r="D27" t="n">
-        <v>62.94</v>
+        <v>10.99</v>
       </c>
       <c r="E27" t="n">
-        <v>29.29</v>
+        <v>40.78</v>
       </c>
       <c r="F27" t="n">
-        <v>0.93229</v>
+        <v>0.05557</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1084,22 +1084,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13.93</v>
+        <v>29.31</v>
       </c>
       <c r="D28" t="n">
-        <v>20.26</v>
+        <v>43.86</v>
       </c>
       <c r="E28" t="n">
-        <v>45.44</v>
+        <v>49.64</v>
       </c>
       <c r="F28" t="n">
-        <v>0.19565</v>
+        <v>0.98749</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>602.35</v>
+        <v>41.55</v>
       </c>
       <c r="D29" t="n">
-        <v>927.03</v>
+        <v>62.37</v>
       </c>
       <c r="E29" t="n">
-        <v>53.9</v>
+        <v>50.11</v>
       </c>
       <c r="F29" t="n">
-        <v>27.68843</v>
+        <v>-0.3825</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1132,22 +1132,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>107.01</v>
+        <v>13.93</v>
       </c>
       <c r="D30" t="n">
-        <v>140.37</v>
+        <v>19.92</v>
       </c>
       <c r="E30" t="n">
-        <v>31.17</v>
+        <v>42.96</v>
       </c>
       <c r="F30" t="n">
-        <v>0.26141</v>
+        <v>0.15845</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1156,742 +1156,742 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>672.48</v>
+        <v>298.32</v>
       </c>
       <c r="D31" t="n">
-        <v>780.66</v>
+        <v>362.45</v>
       </c>
       <c r="E31" t="n">
-        <v>16.09</v>
+        <v>21.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.09502</v>
+        <v>3.71261</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>124.05</v>
+        <v>25.28</v>
       </c>
       <c r="D32" t="n">
-        <v>166.4</v>
+        <v>28.13</v>
       </c>
       <c r="E32" t="n">
-        <v>34.14</v>
+        <v>11.27</v>
       </c>
       <c r="F32" t="n">
-        <v>4.52517</v>
+        <v>-0.00865</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>252.49</v>
+        <v>11.03</v>
       </c>
       <c r="D33" t="n">
-        <v>287.25</v>
+        <v>12.74</v>
       </c>
       <c r="E33" t="n">
-        <v>13.77</v>
+        <v>15.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.70983</v>
+        <v>-0.08918</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29.31</v>
+        <v>27.14</v>
       </c>
       <c r="D34" t="n">
-        <v>43.83</v>
+        <v>31.49</v>
       </c>
       <c r="E34" t="n">
-        <v>49.54</v>
+        <v>16.03</v>
       </c>
       <c r="F34" t="n">
-        <v>1.41459</v>
+        <v>-0.36035</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>31.19</v>
+        <v>146.38</v>
       </c>
       <c r="D35" t="n">
-        <v>35.84</v>
+        <v>218.02</v>
       </c>
       <c r="E35" t="n">
-        <v>14.91</v>
+        <v>48.94</v>
       </c>
       <c r="F35" t="n">
-        <v>0.31383</v>
+        <v>-0.01827</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>298.32</v>
+        <v>179.43</v>
       </c>
       <c r="D36" t="n">
-        <v>365.44</v>
+        <v>196.03</v>
       </c>
       <c r="E36" t="n">
-        <v>22.5</v>
+        <v>9.25</v>
       </c>
       <c r="F36" t="n">
-        <v>4.70499</v>
+        <v>0.79955</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>114.99</v>
+        <v>332.02</v>
       </c>
       <c r="D37" t="n">
-        <v>150.28</v>
+        <v>376.45</v>
       </c>
       <c r="E37" t="n">
-        <v>30.69</v>
+        <v>13.38</v>
       </c>
       <c r="F37" t="n">
-        <v>2.96523</v>
+        <v>-2.36011</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>179.43</v>
+        <v>205.77</v>
       </c>
       <c r="D38" t="n">
-        <v>190.31</v>
+        <v>250.88</v>
       </c>
       <c r="E38" t="n">
-        <v>6.06</v>
+        <v>21.92</v>
       </c>
       <c r="F38" t="n">
-        <v>0.80898</v>
+        <v>2.89335</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9.31</v>
+        <v>25.99</v>
       </c>
       <c r="D39" t="n">
-        <v>10.31</v>
+        <v>38.47</v>
       </c>
       <c r="E39" t="n">
-        <v>10.74</v>
+        <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00165</v>
+        <v>0.52133</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>205.77</v>
+        <v>440.76</v>
       </c>
       <c r="D40" t="n">
-        <v>243.29</v>
+        <v>641.51</v>
       </c>
       <c r="E40" t="n">
-        <v>18.23</v>
+        <v>45.55</v>
       </c>
       <c r="F40" t="n">
-        <v>1.22002</v>
+        <v>1.84381</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.99</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>36.24</v>
+        <v>80.75</v>
       </c>
       <c r="E41" t="n">
-        <v>39.44</v>
+        <v>19.45</v>
       </c>
       <c r="F41" t="n">
-        <v>0.29568</v>
+        <v>-0.41731</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>440.76</v>
+        <v>103.45</v>
       </c>
       <c r="D42" t="n">
-        <v>621.17</v>
+        <v>150.51</v>
       </c>
       <c r="E42" t="n">
-        <v>40.93</v>
+        <v>45.49</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3329</v>
+        <v>1.97428</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EGO</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.73</v>
+        <v>198.14</v>
       </c>
       <c r="D43" t="n">
-        <v>43.75</v>
+        <v>262.93</v>
       </c>
       <c r="E43" t="n">
-        <v>57.77</v>
+        <v>32.7</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4759</v>
+        <v>2.76814</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>136.34</v>
+        <v>41.44</v>
       </c>
       <c r="D44" t="n">
-        <v>200.36</v>
+        <v>45.24</v>
       </c>
       <c r="E44" t="n">
-        <v>46.96</v>
+        <v>9.16</v>
       </c>
       <c r="F44" t="n">
-        <v>1.09963</v>
+        <v>0.51388</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>187.36</v>
+        <v>35.49</v>
       </c>
       <c r="D45" t="n">
-        <v>252.28</v>
+        <v>41.4</v>
       </c>
       <c r="E45" t="n">
-        <v>34.65</v>
+        <v>16.64</v>
       </c>
       <c r="F45" t="n">
-        <v>2.43143</v>
+        <v>0.13101</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>89.2</v>
+        <v>510.39</v>
       </c>
       <c r="D46" t="n">
-        <v>126.81</v>
+        <v>662.61</v>
       </c>
       <c r="E46" t="n">
-        <v>42.16</v>
+        <v>29.82</v>
       </c>
       <c r="F46" t="n">
-        <v>1.41665</v>
+        <v>5.45803</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>103.45</v>
+        <v>5.04</v>
       </c>
       <c r="D47" t="n">
-        <v>154.12</v>
+        <v>5.92</v>
       </c>
       <c r="E47" t="n">
-        <v>48.98</v>
+        <v>17.46</v>
       </c>
       <c r="F47" t="n">
-        <v>2.66631</v>
+        <v>0.04961</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14.16</v>
+        <v>176.25</v>
       </c>
       <c r="D48" t="n">
-        <v>20.58</v>
+        <v>250.78</v>
       </c>
       <c r="E48" t="n">
-        <v>45.34</v>
+        <v>42.29</v>
       </c>
       <c r="F48" t="n">
-        <v>0.16176</v>
+        <v>1.06991</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GFI</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>31.25</v>
+        <v>31.45</v>
       </c>
       <c r="D49" t="n">
-        <v>45.1</v>
+        <v>36.81</v>
       </c>
       <c r="E49" t="n">
-        <v>44.32</v>
+        <v>17.03</v>
       </c>
       <c r="F49" t="n">
-        <v>0.62857</v>
+        <v>0.00077</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SBSW</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>162.11</v>
       </c>
       <c r="D50" t="n">
-        <v>12.54</v>
+        <v>177.23</v>
       </c>
       <c r="E50" t="n">
-        <v>56.75</v>
+        <v>9.33</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3557</v>
+        <v>0.38538</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>28.05</v>
+        <v>20.87</v>
       </c>
       <c r="D51" t="n">
-        <v>36.03</v>
+        <v>23.47</v>
       </c>
       <c r="E51" t="n">
-        <v>28.45</v>
+        <v>12.43</v>
       </c>
       <c r="F51" t="n">
-        <v>0.23283</v>
+        <v>0.00143</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>198.14</v>
+        <v>24.36</v>
       </c>
       <c r="D52" t="n">
-        <v>266</v>
+        <v>33.49</v>
       </c>
       <c r="E52" t="n">
-        <v>34.25</v>
+        <v>37.5</v>
       </c>
       <c r="F52" t="n">
-        <v>3.20426</v>
+        <v>0.53464</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>41.44</v>
+        <v>40.48</v>
       </c>
       <c r="D53" t="n">
-        <v>44.85</v>
+        <v>45.24</v>
       </c>
       <c r="E53" t="n">
-        <v>8.23</v>
+        <v>11.76</v>
       </c>
       <c r="F53" t="n">
-        <v>0.46218</v>
+        <v>0.25484</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>510.39</v>
+        <v>17.93</v>
       </c>
       <c r="D54" t="n">
-        <v>650.5700000000001</v>
+        <v>24.06</v>
       </c>
       <c r="E54" t="n">
-        <v>27.47</v>
+        <v>34.16</v>
       </c>
       <c r="F54" t="n">
-        <v>4.1894</v>
+        <v>0.31676</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5.04</v>
+        <v>41.99</v>
       </c>
       <c r="D55" t="n">
-        <v>6.02</v>
+        <v>51.27</v>
       </c>
       <c r="E55" t="n">
-        <v>19.44</v>
+        <v>22.1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.05799</v>
+        <v>0.37872</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GAP</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18.35</v>
+        <v>20.48</v>
       </c>
       <c r="D56" t="n">
-        <v>21.51</v>
+        <v>26.41</v>
       </c>
       <c r="E56" t="n">
-        <v>17.22</v>
+        <v>28.96</v>
       </c>
       <c r="F56" t="n">
-        <v>0.07675</v>
+        <v>0.18272</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>176.25</v>
+        <v>38.92</v>
       </c>
       <c r="D57" t="n">
-        <v>244.6</v>
+        <v>50.64</v>
       </c>
       <c r="E57" t="n">
-        <v>38.78</v>
+        <v>30.11</v>
       </c>
       <c r="F57" t="n">
-        <v>1.52885</v>
+        <v>0.34657</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>40.48</v>
+        <v>53.57</v>
       </c>
       <c r="D58" t="n">
-        <v>44.71</v>
+        <v>69.69</v>
       </c>
       <c r="E58" t="n">
-        <v>10.45</v>
+        <v>30.09</v>
       </c>
       <c r="F58" t="n">
-        <v>0.24483</v>
+        <v>0.84191</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>24.36</v>
+        <v>31.87</v>
       </c>
       <c r="D59" t="n">
-        <v>33.11</v>
+        <v>45.52</v>
       </c>
       <c r="E59" t="n">
-        <v>35.92</v>
+        <v>42.83</v>
       </c>
       <c r="F59" t="n">
-        <v>0.55881</v>
+        <v>0.9454</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>162.11</v>
+        <v>45.57</v>
       </c>
       <c r="D60" t="n">
-        <v>177.85</v>
+        <v>55.31</v>
       </c>
       <c r="E60" t="n">
-        <v>9.710000000000001</v>
+        <v>21.37</v>
       </c>
       <c r="F60" t="n">
-        <v>0.26806</v>
+        <v>0.47701</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>20.87</v>
+        <v>74.8</v>
       </c>
       <c r="D61" t="n">
-        <v>23.39</v>
+        <v>91.83</v>
       </c>
       <c r="E61" t="n">
-        <v>12.07</v>
+        <v>22.77</v>
       </c>
       <c r="F61" t="n">
-        <v>0.02106</v>
+        <v>1.09417</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>53.57</v>
+        <v>104.89</v>
       </c>
       <c r="D62" t="n">
-        <v>68.83</v>
+        <v>121.95</v>
       </c>
       <c r="E62" t="n">
-        <v>28.49</v>
+        <v>16.26</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7410600000000001</v>
+        <v>2.17558</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>171.96</v>
+        <v>14.49</v>
       </c>
       <c r="D63" t="n">
-        <v>204.97</v>
+        <v>19.02</v>
       </c>
       <c r="E63" t="n">
-        <v>19.2</v>
+        <v>31.3</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6839499999999999</v>
+        <v>0.57961</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>17.93</v>
+        <v>15.99</v>
       </c>
       <c r="D64" t="n">
-        <v>23.78</v>
+        <v>21.11</v>
       </c>
       <c r="E64" t="n">
-        <v>32.63</v>
+        <v>32.05</v>
       </c>
       <c r="F64" t="n">
-        <v>0.30747</v>
+        <v>0.63241</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>47.94</v>
+        <v>51.98</v>
       </c>
       <c r="D65" t="n">
-        <v>61.46</v>
+        <v>65.34</v>
       </c>
       <c r="E65" t="n">
-        <v>28.2</v>
+        <v>25.7</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6323800000000001</v>
+        <v>-0.02418</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>45.09</v>
+        <v>13.01</v>
       </c>
       <c r="D66" t="n">
-        <v>56.06</v>
+        <v>17.58</v>
       </c>
       <c r="E66" t="n">
-        <v>24.33</v>
+        <v>35.09</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4946</v>
+        <v>0.38348</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,22 +2020,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38.92</v>
+        <v>36.15</v>
       </c>
       <c r="D67" t="n">
-        <v>50.07</v>
+        <v>46.08</v>
       </c>
       <c r="E67" t="n">
-        <v>28.65</v>
+        <v>27.48</v>
       </c>
       <c r="F67" t="n">
-        <v>0.41042</v>
+        <v>0.85736</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2044,22 +2044,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>13.01</v>
+        <v>103.22</v>
       </c>
       <c r="D68" t="n">
-        <v>17.4</v>
+        <v>137.76</v>
       </c>
       <c r="E68" t="n">
-        <v>33.74</v>
+        <v>33.46</v>
       </c>
       <c r="F68" t="n">
-        <v>0.39595</v>
+        <v>2.13368</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>17.26</v>
+        <v>110.99</v>
       </c>
       <c r="D69" t="n">
-        <v>19.9</v>
+        <v>133.22</v>
       </c>
       <c r="E69" t="n">
-        <v>15.3</v>
+        <v>20.03</v>
       </c>
       <c r="F69" t="n">
-        <v>0.16707</v>
+        <v>-0.04946</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>45.57</v>
+        <v>165.69</v>
       </c>
       <c r="D70" t="n">
-        <v>56.05</v>
+        <v>213.66</v>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>28.95</v>
       </c>
       <c r="F70" t="n">
-        <v>0.48828</v>
+        <v>3.28253</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2116,22 +2116,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>14.49</v>
+        <v>171.96</v>
       </c>
       <c r="D71" t="n">
-        <v>19.11</v>
+        <v>207.44</v>
       </c>
       <c r="E71" t="n">
-        <v>31.88</v>
+        <v>20.63</v>
       </c>
       <c r="F71" t="n">
-        <v>0.62325</v>
+        <v>1.36072</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>41.99</v>
+        <v>17.26</v>
       </c>
       <c r="D72" t="n">
-        <v>50.61</v>
+        <v>20.03</v>
       </c>
       <c r="E72" t="n">
-        <v>20.53</v>
+        <v>16.08</v>
       </c>
       <c r="F72" t="n">
-        <v>0.32806</v>
+        <v>0.17544</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>20.48</v>
+        <v>47.94</v>
       </c>
       <c r="D73" t="n">
-        <v>26.06</v>
+        <v>62.06</v>
       </c>
       <c r="E73" t="n">
-        <v>27.25</v>
+        <v>29.44</v>
       </c>
       <c r="F73" t="n">
-        <v>0.11669</v>
+        <v>0.70597</v>
       </c>
     </row>
     <row r="74">
@@ -2191,403 +2191,403 @@
         <v>40.25</v>
       </c>
       <c r="D74" t="n">
-        <v>50.23</v>
+        <v>50.08</v>
       </c>
       <c r="E74" t="n">
-        <v>24.8</v>
+        <v>24.43</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7184199999999999</v>
+        <v>0.81048</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>236.5</v>
+        <v>167.73</v>
       </c>
       <c r="D75" t="n">
-        <v>284.75</v>
+        <v>183.91</v>
       </c>
       <c r="E75" t="n">
-        <v>20.4</v>
+        <v>9.65</v>
       </c>
       <c r="F75" t="n">
-        <v>3.75135</v>
+        <v>-0.48382</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>31.87</v>
+        <v>124.44</v>
       </c>
       <c r="D76" t="n">
-        <v>44.73</v>
+        <v>193.77</v>
       </c>
       <c r="E76" t="n">
-        <v>40.35</v>
+        <v>55.71</v>
       </c>
       <c r="F76" t="n">
-        <v>0.83755</v>
+        <v>0.61244</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>74.8</v>
+        <v>55.53</v>
       </c>
       <c r="D77" t="n">
-        <v>91.89</v>
+        <v>60.83</v>
       </c>
       <c r="E77" t="n">
-        <v>22.85</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>1.02724</v>
+        <v>0.21319</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36.15</v>
+        <v>38.73</v>
       </c>
       <c r="D78" t="n">
-        <v>46.1</v>
+        <v>63.96</v>
       </c>
       <c r="E78" t="n">
-        <v>27.52</v>
+        <v>65.14</v>
       </c>
       <c r="F78" t="n">
-        <v>0.82077</v>
+        <v>-0.12199</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>103.22</v>
+        <v>62.05</v>
       </c>
       <c r="D79" t="n">
-        <v>137.35</v>
+        <v>81.13</v>
       </c>
       <c r="E79" t="n">
-        <v>33.07</v>
+        <v>30.75</v>
       </c>
       <c r="F79" t="n">
-        <v>2.07196</v>
+        <v>-0.50947</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>165.69</v>
+        <v>13.43</v>
       </c>
       <c r="D80" t="n">
-        <v>214.06</v>
+        <v>15.27</v>
       </c>
       <c r="E80" t="n">
-        <v>29.19</v>
+        <v>13.66</v>
       </c>
       <c r="F80" t="n">
-        <v>3.22174</v>
+        <v>0.08887</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>15.99</v>
+        <v>13.31</v>
       </c>
       <c r="D81" t="n">
-        <v>21.2</v>
+        <v>25.84</v>
       </c>
       <c r="E81" t="n">
-        <v>32.58</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>0.66898</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>104.89</v>
+        <v>7.67</v>
       </c>
       <c r="D82" t="n">
-        <v>122.41</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>16.7</v>
+        <v>20.14</v>
       </c>
       <c r="F82" t="n">
-        <v>2.6088</v>
+        <v>0.17852</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>55.53</v>
+        <v>135.44</v>
       </c>
       <c r="D83" t="n">
-        <v>58.49</v>
+        <v>174.78</v>
       </c>
       <c r="E83" t="n">
-        <v>5.33</v>
+        <v>29.04</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.14595</v>
+        <v>-1.58976</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>13.43</v>
+        <v>218.58</v>
       </c>
       <c r="D84" t="n">
-        <v>14.94</v>
+        <v>279.8</v>
       </c>
       <c r="E84" t="n">
-        <v>11.24</v>
+        <v>28.01</v>
       </c>
       <c r="F84" t="n">
-        <v>0.07875</v>
+        <v>0.16684</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>167.73</v>
+        <v>136.06</v>
       </c>
       <c r="D85" t="n">
-        <v>182.33</v>
+        <v>165.7</v>
       </c>
       <c r="E85" t="n">
-        <v>8.699999999999999</v>
+        <v>21.79</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.7684299999999999</v>
+        <v>1.71684</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>13.31</v>
+        <v>18.94</v>
       </c>
       <c r="D86" t="n">
-        <v>25.03</v>
+        <v>23.66</v>
       </c>
       <c r="E86" t="n">
-        <v>88.05</v>
+        <v>24.92</v>
       </c>
       <c r="F86" t="n">
-        <v>0.68264</v>
+        <v>0.18847</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>124.44</v>
+        <v>76.53</v>
       </c>
       <c r="D87" t="n">
-        <v>183.9</v>
+        <v>96.61</v>
       </c>
       <c r="E87" t="n">
-        <v>47.78</v>
+        <v>26.24</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.87468</v>
+        <v>1.46769</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>136.06</v>
+        <v>31.03</v>
       </c>
       <c r="D88" t="n">
-        <v>165.99</v>
+        <v>44.7</v>
       </c>
       <c r="E88" t="n">
-        <v>22</v>
+        <v>44.05</v>
       </c>
       <c r="F88" t="n">
-        <v>1.36664</v>
+        <v>1.00159</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>218.58</v>
+        <v>56.4</v>
       </c>
       <c r="D89" t="n">
-        <v>275.54</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="E89" t="n">
-        <v>26.06</v>
+        <v>44.24</v>
       </c>
       <c r="F89" t="n">
-        <v>0.01914</v>
+        <v>1.72103</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7.67</v>
+        <v>39.54</v>
       </c>
       <c r="D90" t="n">
-        <v>9.359999999999999</v>
+        <v>51.29</v>
       </c>
       <c r="E90" t="n">
-        <v>22.03</v>
+        <v>29.72</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1989</v>
+        <v>0.10106</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2596,118 +2596,118 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>18.94</v>
+        <v>82.31</v>
       </c>
       <c r="D91" t="n">
-        <v>23.69</v>
+        <v>136.75</v>
       </c>
       <c r="E91" t="n">
-        <v>25.08</v>
+        <v>66.14</v>
       </c>
       <c r="F91" t="n">
-        <v>0.18936</v>
+        <v>3.43709</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>EDU</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>56.4</v>
+        <v>44.44</v>
       </c>
       <c r="D92" t="n">
-        <v>78.87</v>
+        <v>57</v>
       </c>
       <c r="E92" t="n">
-        <v>39.84</v>
+        <v>28.26</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3485</v>
+        <v>-0.36429</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>76.53</v>
+        <v>59.71</v>
       </c>
       <c r="D93" t="n">
-        <v>96.77</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="E93" t="n">
-        <v>26.45</v>
+        <v>32.84</v>
       </c>
       <c r="F93" t="n">
-        <v>1.4864</v>
+        <v>0.61687</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>82.31</v>
+        <v>166.5</v>
       </c>
       <c r="D94" t="n">
-        <v>130.97</v>
+        <v>197.05</v>
       </c>
       <c r="E94" t="n">
-        <v>59.12</v>
+        <v>18.35</v>
       </c>
       <c r="F94" t="n">
-        <v>3.77468</v>
+        <v>0.62078</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>31.03</v>
+        <v>352.83</v>
       </c>
       <c r="D95" t="n">
-        <v>44.8</v>
+        <v>509.32</v>
       </c>
       <c r="E95" t="n">
-        <v>44.38</v>
+        <v>44.35</v>
       </c>
       <c r="F95" t="n">
-        <v>0.96912</v>
+        <v>2.46973</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2716,22 +2716,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>142.52</v>
+        <v>19.32</v>
       </c>
       <c r="D96" t="n">
-        <v>175.26</v>
+        <v>24.62</v>
       </c>
       <c r="E96" t="n">
-        <v>22.97</v>
+        <v>27.46</v>
       </c>
       <c r="F96" t="n">
-        <v>0.26584</v>
+        <v>-0.01943</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2740,22 +2740,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>166.5</v>
+        <v>255.07</v>
       </c>
       <c r="D97" t="n">
-        <v>198.2</v>
+        <v>338.24</v>
       </c>
       <c r="E97" t="n">
-        <v>19.04</v>
+        <v>32.61</v>
       </c>
       <c r="F97" t="n">
-        <v>0.09665</v>
+        <v>-6.08852</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2764,22 +2764,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>19.32</v>
+        <v>107.27</v>
       </c>
       <c r="D98" t="n">
-        <v>23.9</v>
+        <v>173.37</v>
       </c>
       <c r="E98" t="n">
-        <v>23.71</v>
+        <v>61.62</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.13674</v>
+        <v>-1.05229</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2788,22 +2788,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>59.71</v>
+        <v>142.52</v>
       </c>
       <c r="D99" t="n">
-        <v>75.90000000000001</v>
+        <v>190.97</v>
       </c>
       <c r="E99" t="n">
-        <v>27.11</v>
+        <v>34</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.07714</v>
+        <v>1.38624</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2812,22 +2812,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>49.87</v>
+        <v>170.28</v>
       </c>
       <c r="D100" t="n">
-        <v>61.42</v>
+        <v>249.48</v>
       </c>
       <c r="E100" t="n">
-        <v>23.16</v>
+        <v>46.51</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.11501</v>
+        <v>-2.86537</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2836,22 +2836,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>42.46</v>
+        <v>44.39</v>
       </c>
       <c r="D101" t="n">
-        <v>65.65000000000001</v>
+        <v>60.69</v>
       </c>
       <c r="E101" t="n">
-        <v>54.62</v>
+        <v>36.72</v>
       </c>
       <c r="F101" t="n">
-        <v>0.94333</v>
+        <v>-0.10213</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2860,88 +2860,88 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>352.83</v>
+        <v>49.87</v>
       </c>
       <c r="D102" t="n">
-        <v>495.63</v>
+        <v>63.99</v>
       </c>
       <c r="E102" t="n">
-        <v>40.47</v>
+        <v>28.3</v>
       </c>
       <c r="F102" t="n">
-        <v>1.11181</v>
+        <v>0.27833</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>60.37</v>
+        <v>42.46</v>
       </c>
       <c r="D103" t="n">
-        <v>78.45</v>
+        <v>69.61</v>
       </c>
       <c r="E103" t="n">
-        <v>29.95</v>
+        <v>63.94</v>
       </c>
       <c r="F103" t="n">
-        <v>1.83733</v>
+        <v>1.28494</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.51</v>
+        <v>100</v>
       </c>
       <c r="D104" t="n">
-        <v>15.8</v>
+        <v>133.4</v>
       </c>
       <c r="E104" t="n">
-        <v>50.33</v>
+        <v>33.4</v>
       </c>
       <c r="F104" t="n">
-        <v>0.39025</v>
+        <v>-1.54672</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>62.12</v>
+        <v>136.68</v>
       </c>
       <c r="D105" t="n">
-        <v>77.67</v>
+        <v>155.53</v>
       </c>
       <c r="E105" t="n">
-        <v>25.03</v>
+        <v>13.79</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6581</v>
+        <v>-2.3076</v>
       </c>
     </row>
     <row r="106">
@@ -2959,2995 +2959,2995 @@
         <v>36.09</v>
       </c>
       <c r="D106" t="n">
-        <v>38.9</v>
+        <v>38.96</v>
       </c>
       <c r="E106" t="n">
-        <v>7.79</v>
+        <v>7.95</v>
       </c>
       <c r="F106" t="n">
-        <v>0.13144</v>
+        <v>0.1313</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>48.79</v>
+        <v>60.37</v>
       </c>
       <c r="D107" t="n">
-        <v>65.94</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>35.15</v>
+        <v>27.8</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.36491</v>
+        <v>1.32615</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>102.17</v>
+        <v>10.51</v>
       </c>
       <c r="D108" t="n">
-        <v>133.07</v>
+        <v>15.58</v>
       </c>
       <c r="E108" t="n">
-        <v>30.24</v>
+        <v>48.24</v>
       </c>
       <c r="F108" t="n">
-        <v>2.38111</v>
+        <v>0.43404</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>150.12</v>
+        <v>62.12</v>
       </c>
       <c r="D109" t="n">
-        <v>247.72</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="E109" t="n">
-        <v>65.01000000000001</v>
+        <v>26.79</v>
       </c>
       <c r="F109" t="n">
-        <v>6.07809</v>
+        <v>0.77066</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>74.98999999999999</v>
+        <v>102.17</v>
       </c>
       <c r="D110" t="n">
-        <v>98.06999999999999</v>
+        <v>132.16</v>
       </c>
       <c r="E110" t="n">
-        <v>30.78</v>
+        <v>29.35</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.77002</v>
+        <v>1.94768</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>76.04000000000001</v>
+        <v>48.79</v>
       </c>
       <c r="D111" t="n">
-        <v>117.91</v>
+        <v>68.23</v>
       </c>
       <c r="E111" t="n">
-        <v>55.06</v>
+        <v>39.84</v>
       </c>
       <c r="F111" t="n">
-        <v>1.7938</v>
+        <v>-0.04445</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>141.17</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D112" t="n">
-        <v>174.83</v>
+        <v>125.37</v>
       </c>
       <c r="E112" t="n">
-        <v>23.84</v>
+        <v>64.87</v>
       </c>
       <c r="F112" t="n">
-        <v>1.12639</v>
+        <v>2.58105</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>33.22</v>
+        <v>150.12</v>
       </c>
       <c r="D113" t="n">
-        <v>38.43</v>
+        <v>258.91</v>
       </c>
       <c r="E113" t="n">
-        <v>15.68</v>
+        <v>72.47</v>
       </c>
       <c r="F113" t="n">
-        <v>0.28995</v>
+        <v>6.43159</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>32.47</v>
+        <v>275.27</v>
       </c>
       <c r="D114" t="n">
-        <v>38.04</v>
+        <v>360.62</v>
       </c>
       <c r="E114" t="n">
-        <v>17.15</v>
+        <v>31.01</v>
       </c>
       <c r="F114" t="n">
-        <v>0.14645</v>
+        <v>-2.64547</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>450.75</v>
+        <v>47.18</v>
       </c>
       <c r="D115" t="n">
-        <v>546.78</v>
+        <v>52.18</v>
       </c>
       <c r="E115" t="n">
-        <v>21.3</v>
+        <v>10.6</v>
       </c>
       <c r="F115" t="n">
-        <v>2.73475</v>
+        <v>-0.64834</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>14.05</v>
+        <v>30.83</v>
       </c>
       <c r="D116" t="n">
-        <v>19.78</v>
+        <v>35.71</v>
       </c>
       <c r="E116" t="n">
-        <v>40.78</v>
+        <v>15.83</v>
       </c>
       <c r="F116" t="n">
-        <v>0.23666</v>
+        <v>-0.35337</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>14.94</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D117" t="n">
-        <v>19.86</v>
+        <v>104.46</v>
       </c>
       <c r="E117" t="n">
-        <v>32.93</v>
+        <v>39.3</v>
       </c>
       <c r="F117" t="n">
-        <v>0.61757</v>
+        <v>0.40617</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>16.44</v>
+        <v>76.55</v>
       </c>
       <c r="D118" t="n">
-        <v>33</v>
+        <v>105.91</v>
       </c>
       <c r="E118" t="n">
-        <v>100.73</v>
+        <v>38.35</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4888</v>
+        <v>-1.57489</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>91.88</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>129.41</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="E119" t="n">
-        <v>40.85</v>
+        <v>13.09</v>
       </c>
       <c r="F119" t="n">
-        <v>1.61547</v>
+        <v>-0.47985</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>19.82</v>
+        <v>123.42</v>
       </c>
       <c r="D120" t="n">
-        <v>25.19</v>
+        <v>167.53</v>
       </c>
       <c r="E120" t="n">
-        <v>27.09</v>
+        <v>35.74</v>
       </c>
       <c r="F120" t="n">
-        <v>0.59848</v>
+        <v>-0.37504</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2.86</v>
+        <v>125.73</v>
       </c>
       <c r="D121" t="n">
-        <v>3.2</v>
+        <v>194.2</v>
       </c>
       <c r="E121" t="n">
-        <v>11.89</v>
+        <v>54.46</v>
       </c>
       <c r="F121" t="n">
-        <v>0.02074</v>
+        <v>-2.07654</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>53.82</v>
+        <v>33.22</v>
       </c>
       <c r="D122" t="n">
-        <v>75.48999999999999</v>
+        <v>38.56</v>
       </c>
       <c r="E122" t="n">
-        <v>40.26</v>
+        <v>16.06</v>
       </c>
       <c r="F122" t="n">
-        <v>0.47907</v>
+        <v>0.21234</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>205.81</v>
+        <v>61.28</v>
       </c>
       <c r="D123" t="n">
-        <v>263.52</v>
+        <v>73.11</v>
       </c>
       <c r="E123" t="n">
-        <v>28.04</v>
+        <v>19.3</v>
       </c>
       <c r="F123" t="n">
-        <v>2.01368</v>
+        <v>-0.96306</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>361.32</v>
+        <v>450.75</v>
       </c>
       <c r="D124" t="n">
-        <v>426.94</v>
+        <v>550.99</v>
       </c>
       <c r="E124" t="n">
-        <v>18.16</v>
+        <v>22.24</v>
       </c>
       <c r="F124" t="n">
-        <v>2.42172</v>
+        <v>2.6424</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>43.67</v>
+        <v>48.87</v>
       </c>
       <c r="D125" t="n">
-        <v>46.99</v>
+        <v>58.86</v>
       </c>
       <c r="E125" t="n">
-        <v>7.6</v>
+        <v>20.44</v>
       </c>
       <c r="F125" t="n">
-        <v>0.02819</v>
+        <v>-0.39604</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>161.37</v>
+        <v>32.47</v>
       </c>
       <c r="D126" t="n">
-        <v>263.69</v>
+        <v>38.12</v>
       </c>
       <c r="E126" t="n">
-        <v>63.41</v>
+        <v>17.39</v>
       </c>
       <c r="F126" t="n">
-        <v>0.33828</v>
+        <v>0.19798</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>ENSG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>68.77</v>
+        <v>147.13</v>
       </c>
       <c r="D127" t="n">
-        <v>82.20999999999999</v>
+        <v>174.75</v>
       </c>
       <c r="E127" t="n">
-        <v>19.54</v>
+        <v>18.77</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.70053</v>
+        <v>-0.6170600000000001</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>195.11</v>
+        <v>121.48</v>
       </c>
       <c r="D128" t="n">
-        <v>248.72</v>
+        <v>145.79</v>
       </c>
       <c r="E128" t="n">
-        <v>27.48</v>
+        <v>20.01</v>
       </c>
       <c r="F128" t="n">
-        <v>0.26006</v>
+        <v>-0.01089</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>15.03</v>
+        <v>2.86</v>
       </c>
       <c r="D129" t="n">
-        <v>18.26</v>
+        <v>3.15</v>
       </c>
       <c r="E129" t="n">
-        <v>21.49</v>
+        <v>10.31</v>
       </c>
       <c r="F129" t="n">
-        <v>0.06938</v>
+        <v>0.02305</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>140.19</v>
+        <v>16.44</v>
       </c>
       <c r="D130" t="n">
-        <v>145.27</v>
+        <v>34.26</v>
       </c>
       <c r="E130" t="n">
-        <v>3.62</v>
+        <v>108.39</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.49238</v>
+        <v>0.62796</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>275.99</v>
+        <v>14.94</v>
       </c>
       <c r="D131" t="n">
-        <v>322.82</v>
+        <v>19.49</v>
       </c>
       <c r="E131" t="n">
-        <v>16.97</v>
+        <v>30.42</v>
       </c>
       <c r="F131" t="n">
-        <v>1.51503</v>
+        <v>0.51066</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ABVX</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>72.5</v>
+        <v>53.82</v>
       </c>
       <c r="D132" t="n">
-        <v>118.64</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E132" t="n">
-        <v>63.64</v>
+        <v>39.17</v>
       </c>
       <c r="F132" t="n">
-        <v>0.29802</v>
+        <v>0.52773</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>9.85</v>
+        <v>19.82</v>
       </c>
       <c r="D133" t="n">
-        <v>13.58</v>
+        <v>24.59</v>
       </c>
       <c r="E133" t="n">
-        <v>37.87</v>
+        <v>24.07</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5505</v>
+        <v>0.35672</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>190.4</v>
+        <v>91.88</v>
       </c>
       <c r="D134" t="n">
-        <v>217.62</v>
+        <v>126.09</v>
       </c>
       <c r="E134" t="n">
-        <v>14.3</v>
+        <v>37.23</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.59803</v>
+        <v>1.5759</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>63.54</v>
+        <v>361.32</v>
       </c>
       <c r="D135" t="n">
-        <v>69.90000000000001</v>
+        <v>421.09</v>
       </c>
       <c r="E135" t="n">
-        <v>10.01</v>
+        <v>16.54</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1817</v>
+        <v>4.00728</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>33.54</v>
+        <v>205.81</v>
       </c>
       <c r="D136" t="n">
-        <v>42.85</v>
+        <v>262.04</v>
       </c>
       <c r="E136" t="n">
-        <v>27.76</v>
+        <v>27.32</v>
       </c>
       <c r="F136" t="n">
-        <v>0.17598</v>
+        <v>1.05524</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>250.75</v>
+        <v>55.05</v>
       </c>
       <c r="D137" t="n">
-        <v>350.13</v>
+        <v>63.71</v>
       </c>
       <c r="E137" t="n">
-        <v>39.63</v>
+        <v>15.73</v>
       </c>
       <c r="F137" t="n">
-        <v>4.34655</v>
+        <v>-0.46026</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>529.12</v>
+        <v>43.67</v>
       </c>
       <c r="D138" t="n">
-        <v>675.74</v>
+        <v>47.34</v>
       </c>
       <c r="E138" t="n">
-        <v>27.71</v>
+        <v>8.4</v>
       </c>
       <c r="F138" t="n">
-        <v>10.73877</v>
+        <v>0.05503</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>108.01</v>
+        <v>28.18</v>
       </c>
       <c r="D139" t="n">
-        <v>126.94</v>
+        <v>36.99</v>
       </c>
       <c r="E139" t="n">
-        <v>17.53</v>
+        <v>31.28</v>
       </c>
       <c r="F139" t="n">
-        <v>0.60472</v>
+        <v>-0.01441</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SGI</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>61.49</v>
+        <v>140.19</v>
       </c>
       <c r="D140" t="n">
-        <v>66.76000000000001</v>
+        <v>146.2</v>
       </c>
       <c r="E140" t="n">
-        <v>8.57</v>
+        <v>4.29</v>
       </c>
       <c r="F140" t="n">
-        <v>0.42927</v>
+        <v>-0.38644</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>134.71</v>
+        <v>195.11</v>
       </c>
       <c r="D141" t="n">
-        <v>148.38</v>
+        <v>248.52</v>
       </c>
       <c r="E141" t="n">
-        <v>10.15</v>
+        <v>27.38</v>
       </c>
       <c r="F141" t="n">
-        <v>2.1441</v>
+        <v>0.3672</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>196.07</v>
+        <v>207.24</v>
       </c>
       <c r="D142" t="n">
-        <v>211.96</v>
+        <v>253.58</v>
       </c>
       <c r="E142" t="n">
-        <v>8.1</v>
+        <v>22.36</v>
       </c>
       <c r="F142" t="n">
-        <v>0.04079</v>
+        <v>-2.70426</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BMRN</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>49.67</v>
+        <v>15.03</v>
       </c>
       <c r="D143" t="n">
-        <v>65.68000000000001</v>
+        <v>18.67</v>
       </c>
       <c r="E143" t="n">
-        <v>32.23</v>
+        <v>24.22</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.14491</v>
+        <v>0.09611</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>92.38</v>
+        <v>275.99</v>
       </c>
       <c r="D144" t="n">
-        <v>100.56</v>
+        <v>321.69</v>
       </c>
       <c r="E144" t="n">
-        <v>8.85</v>
+        <v>16.56</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.08179</v>
+        <v>1.80502</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>438.34</v>
+        <v>277.69</v>
       </c>
       <c r="D145" t="n">
-        <v>609.8200000000001</v>
+        <v>329.22</v>
       </c>
       <c r="E145" t="n">
-        <v>39.12</v>
+        <v>18.56</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.56321</v>
+        <v>-0.27732</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>26.18</v>
+        <v>73.75</v>
       </c>
       <c r="D146" t="n">
-        <v>36.49</v>
+        <v>93.33</v>
       </c>
       <c r="E146" t="n">
-        <v>39.38</v>
+        <v>26.56</v>
       </c>
       <c r="F146" t="n">
-        <v>0.03658</v>
+        <v>0.27025</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>73.42</v>
+        <v>9.85</v>
       </c>
       <c r="D147" t="n">
-        <v>90.29000000000001</v>
+        <v>13.84</v>
       </c>
       <c r="E147" t="n">
-        <v>22.98</v>
+        <v>40.51</v>
       </c>
       <c r="F147" t="n">
-        <v>0.77528</v>
+        <v>0.52093</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>63.16</v>
+        <v>132.79</v>
       </c>
       <c r="D148" t="n">
-        <v>102.04</v>
+        <v>163.34</v>
       </c>
       <c r="E148" t="n">
-        <v>61.56</v>
+        <v>23.01</v>
       </c>
       <c r="F148" t="n">
-        <v>1.24569</v>
+        <v>-0.13175</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>225.75</v>
+        <v>36.25</v>
       </c>
       <c r="D149" t="n">
-        <v>282.67</v>
+        <v>41.2</v>
       </c>
       <c r="E149" t="n">
-        <v>25.21</v>
+        <v>13.66</v>
       </c>
       <c r="F149" t="n">
-        <v>-3.23344</v>
+        <v>0.18651</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>163.43</v>
+        <v>33.54</v>
       </c>
       <c r="D150" t="n">
-        <v>192.61</v>
+        <v>42.76</v>
       </c>
       <c r="E150" t="n">
-        <v>17.85</v>
+        <v>27.47</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.61748</v>
+        <v>0.14827</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>163.55</v>
+        <v>63.54</v>
       </c>
       <c r="D151" t="n">
-        <v>201.5</v>
+        <v>70.17</v>
       </c>
       <c r="E151" t="n">
-        <v>23.2</v>
+        <v>10.43</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.56516</v>
+        <v>0.20202</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MKC-V</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>45.59</v>
+        <v>190.4</v>
       </c>
       <c r="D152" t="n">
-        <v>56.53</v>
+        <v>219.99</v>
       </c>
       <c r="E152" t="n">
-        <v>24</v>
+        <v>15.54</v>
       </c>
       <c r="F152" t="n">
-        <v>0.71097</v>
+        <v>-0.05678</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>IDCC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>55.52</v>
+        <v>250.75</v>
       </c>
       <c r="D153" t="n">
-        <v>90.8</v>
+        <v>344.15</v>
       </c>
       <c r="E153" t="n">
-        <v>63.54</v>
+        <v>37.25</v>
       </c>
       <c r="F153" t="n">
-        <v>1.21071</v>
+        <v>4.2383</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>99.3</v>
+        <v>529.12</v>
       </c>
       <c r="D154" t="n">
-        <v>153.79</v>
+        <v>681.36</v>
       </c>
       <c r="E154" t="n">
-        <v>54.87</v>
+        <v>28.77</v>
       </c>
       <c r="F154" t="n">
-        <v>0.5426299999999999</v>
+        <v>9.77603</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>197.73</v>
+        <v>57.4</v>
       </c>
       <c r="D155" t="n">
-        <v>222.74</v>
+        <v>104.27</v>
       </c>
       <c r="E155" t="n">
-        <v>12.65</v>
+        <v>81.66</v>
       </c>
       <c r="F155" t="n">
-        <v>0.63872</v>
+        <v>0.16331</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BSAC</t>
+          <t>SGI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>29.79</v>
+        <v>61.49</v>
       </c>
       <c r="D156" t="n">
-        <v>35.19</v>
+        <v>68.25</v>
       </c>
       <c r="E156" t="n">
-        <v>18.13</v>
+        <v>10.99</v>
       </c>
       <c r="F156" t="n">
-        <v>0.065</v>
+        <v>0.26315</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>BMRN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>255.54</v>
+        <v>49.67</v>
       </c>
       <c r="D157" t="n">
-        <v>365.08</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E157" t="n">
-        <v>42.87</v>
+        <v>34.19</v>
       </c>
       <c r="F157" t="n">
-        <v>3.6115</v>
+        <v>0.06127</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>12.64</v>
+        <v>438.34</v>
       </c>
       <c r="D158" t="n">
-        <v>17.75</v>
+        <v>611.7</v>
       </c>
       <c r="E158" t="n">
-        <v>40.43</v>
+        <v>39.55</v>
       </c>
       <c r="F158" t="n">
-        <v>0.27258</v>
+        <v>0.31709</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MPLX</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>54</v>
+        <v>26.18</v>
       </c>
       <c r="D159" t="n">
-        <v>59.84</v>
+        <v>36.84</v>
       </c>
       <c r="E159" t="n">
-        <v>10.81</v>
+        <v>40.72</v>
       </c>
       <c r="F159" t="n">
-        <v>0.28289</v>
+        <v>0.14738</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>32.32</v>
+        <v>63.16</v>
       </c>
       <c r="D160" t="n">
-        <v>37.99</v>
+        <v>101.5</v>
       </c>
       <c r="E160" t="n">
-        <v>17.54</v>
+        <v>60.71</v>
       </c>
       <c r="F160" t="n">
-        <v>0.23389</v>
+        <v>1.39896</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>699965</v>
+        <v>43.3</v>
       </c>
       <c r="D161" t="n">
-        <v>766000</v>
+        <v>72.22</v>
       </c>
       <c r="E161" t="n">
-        <v>9.43</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>1317.486</v>
+        <v>-0.00476</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>139.71</v>
+        <v>163.43</v>
       </c>
       <c r="D162" t="n">
-        <v>192.6</v>
+        <v>200.51</v>
       </c>
       <c r="E162" t="n">
-        <v>37.86</v>
+        <v>22.69</v>
       </c>
       <c r="F162" t="n">
-        <v>1.1005</v>
+        <v>0.60609</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>45.37</v>
+        <v>156.84</v>
       </c>
       <c r="D163" t="n">
-        <v>143.97</v>
+        <v>186.77</v>
       </c>
       <c r="E163" t="n">
-        <v>217.32</v>
+        <v>19.08</v>
       </c>
       <c r="F163" t="n">
-        <v>5.1164</v>
+        <v>-2.70975</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>156.66</v>
+        <v>101.75</v>
       </c>
       <c r="D164" t="n">
-        <v>261.77</v>
+        <v>128.85</v>
       </c>
       <c r="E164" t="n">
-        <v>67.09</v>
+        <v>26.63</v>
       </c>
       <c r="F164" t="n">
-        <v>1.57783</v>
+        <v>-0.2813</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>82.26000000000001</v>
+        <v>55.52</v>
       </c>
       <c r="D165" t="n">
-        <v>124.31</v>
+        <v>93.83</v>
       </c>
       <c r="E165" t="n">
-        <v>51.12</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.05317</v>
+        <v>1.52445</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>13.06</v>
+        <v>99.3</v>
       </c>
       <c r="D166" t="n">
-        <v>19.65</v>
+        <v>151.73</v>
       </c>
       <c r="E166" t="n">
-        <v>50.46</v>
+        <v>52.8</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.07116</v>
+        <v>1.18143</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>197.38</v>
+        <v>197.73</v>
       </c>
       <c r="D167" t="n">
-        <v>257.12</v>
+        <v>226.2</v>
       </c>
       <c r="E167" t="n">
-        <v>30.27</v>
+        <v>14.4</v>
       </c>
       <c r="F167" t="n">
-        <v>-1.42463</v>
+        <v>1.01313</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>465.4</v>
+        <v>725.17</v>
       </c>
       <c r="D168" t="n">
-        <v>510.37</v>
+        <v>903.28</v>
       </c>
       <c r="E168" t="n">
-        <v>9.66</v>
+        <v>24.56</v>
       </c>
       <c r="F168" t="n">
-        <v>0.88445</v>
+        <v>1.18094</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>56.06</v>
+        <v>255.54</v>
       </c>
       <c r="D169" t="n">
-        <v>62.44</v>
+        <v>365.08</v>
       </c>
       <c r="E169" t="n">
-        <v>11.38</v>
+        <v>42.87</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.03757</v>
+        <v>3.6115</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>153.25</v>
+        <v>417.83</v>
       </c>
       <c r="D170" t="n">
-        <v>191.06</v>
+        <v>559.47</v>
       </c>
       <c r="E170" t="n">
-        <v>24.67</v>
+        <v>33.9</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.11953</v>
+        <v>0.73966</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>20.96</v>
+        <v>383.99</v>
       </c>
       <c r="D171" t="n">
-        <v>26.1</v>
+        <v>477.9</v>
       </c>
       <c r="E171" t="n">
-        <v>24.52</v>
+        <v>24.46</v>
       </c>
       <c r="F171" t="n">
-        <v>0.32599</v>
+        <v>-1.17179</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>155.75</v>
+        <v>12.64</v>
       </c>
       <c r="D172" t="n">
-        <v>259.47</v>
+        <v>17.68</v>
       </c>
       <c r="E172" t="n">
-        <v>66.59</v>
+        <v>39.91</v>
       </c>
       <c r="F172" t="n">
-        <v>6.56374</v>
+        <v>0.23758</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>231.51</v>
+        <v>252.74</v>
       </c>
       <c r="D173" t="n">
-        <v>290.25</v>
+        <v>325.73</v>
       </c>
       <c r="E173" t="n">
-        <v>25.37</v>
+        <v>28.88</v>
       </c>
       <c r="F173" t="n">
-        <v>1.4568</v>
+        <v>-0.26739</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>128.43</v>
+        <v>699965</v>
       </c>
       <c r="D174" t="n">
-        <v>147.36</v>
+        <v>769460.0600000001</v>
       </c>
       <c r="E174" t="n">
-        <v>14.74</v>
+        <v>9.93</v>
       </c>
       <c r="F174" t="n">
-        <v>0.39775</v>
+        <v>2303.35043</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>83.51000000000001</v>
+        <v>139.71</v>
       </c>
       <c r="D175" t="n">
-        <v>96.62</v>
+        <v>192.72</v>
       </c>
       <c r="E175" t="n">
-        <v>15.7</v>
+        <v>37.94</v>
       </c>
       <c r="F175" t="n">
-        <v>0.7579900000000001</v>
+        <v>1.6395</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>213.69</v>
+        <v>45.37</v>
       </c>
       <c r="D176" t="n">
-        <v>395.93</v>
+        <v>146.49</v>
       </c>
       <c r="E176" t="n">
-        <v>85.28</v>
+        <v>222.88</v>
       </c>
       <c r="F176" t="n">
-        <v>11.53328</v>
+        <v>5.21579</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>223.65</v>
+        <v>112.47</v>
       </c>
       <c r="D177" t="n">
-        <v>390.42</v>
+        <v>140.42</v>
       </c>
       <c r="E177" t="n">
-        <v>74.56999999999999</v>
+        <v>24.85</v>
       </c>
       <c r="F177" t="n">
-        <v>13.30066</v>
+        <v>0.49292</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>40.59</v>
+        <v>156.66</v>
       </c>
       <c r="D178" t="n">
-        <v>55.55</v>
+        <v>266.54</v>
       </c>
       <c r="E178" t="n">
-        <v>36.86</v>
+        <v>70.14</v>
       </c>
       <c r="F178" t="n">
-        <v>1.21178</v>
+        <v>2.12518</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>18.71</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D179" t="n">
-        <v>21.55</v>
+        <v>125.8</v>
       </c>
       <c r="E179" t="n">
-        <v>15.18</v>
+        <v>52.93</v>
       </c>
       <c r="F179" t="n">
-        <v>0.15383</v>
+        <v>-0.17001</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>66.95</v>
+        <v>13.06</v>
       </c>
       <c r="D180" t="n">
-        <v>86.72</v>
+        <v>19.91</v>
       </c>
       <c r="E180" t="n">
-        <v>29.53</v>
+        <v>52.45</v>
       </c>
       <c r="F180" t="n">
-        <v>1.46018</v>
+        <v>-0.009140000000000001</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>WES</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>40.41</v>
       </c>
       <c r="D181" t="n">
-        <v>49.03</v>
+        <v>52.64</v>
       </c>
       <c r="E181" t="n">
-        <v>21.33</v>
+        <v>30.26</v>
       </c>
       <c r="F181" t="n">
-        <v>0.19255</v>
+        <v>-0.13413</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>18.26</v>
+        <v>197.38</v>
       </c>
       <c r="D182" t="n">
-        <v>35.48</v>
+        <v>261.46</v>
       </c>
       <c r="E182" t="n">
-        <v>94.3</v>
+        <v>32.47</v>
       </c>
       <c r="F182" t="n">
-        <v>0.97924</v>
+        <v>-0.08086</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>166.99</v>
+        <v>393.42</v>
       </c>
       <c r="D183" t="n">
-        <v>306.53</v>
+        <v>593.45</v>
       </c>
       <c r="E183" t="n">
-        <v>83.56</v>
+        <v>50.84</v>
       </c>
       <c r="F183" t="n">
-        <v>5.16986</v>
+        <v>-2.23548</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>83</v>
+        <v>465.4</v>
       </c>
       <c r="D184" t="n">
-        <v>132.53</v>
+        <v>514.15</v>
       </c>
       <c r="E184" t="n">
-        <v>59.67</v>
+        <v>10.47</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.01342</v>
+        <v>1.5926</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>151.43</v>
+        <v>74.63</v>
       </c>
       <c r="D185" t="n">
-        <v>262.4</v>
+        <v>89.14</v>
       </c>
       <c r="E185" t="n">
-        <v>73.28</v>
+        <v>19.45</v>
       </c>
       <c r="F185" t="n">
-        <v>1.63232</v>
+        <v>-0.07488</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>57.15</v>
+        <v>56.06</v>
       </c>
       <c r="D186" t="n">
-        <v>179.7</v>
+        <v>62.37</v>
       </c>
       <c r="E186" t="n">
-        <v>214.44</v>
+        <v>11.25</v>
       </c>
       <c r="F186" t="n">
-        <v>2.90762</v>
+        <v>0.03601</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>121.11</v>
+        <v>153.25</v>
       </c>
       <c r="D187" t="n">
-        <v>328.99</v>
+        <v>193.88</v>
       </c>
       <c r="E187" t="n">
-        <v>171.65</v>
+        <v>26.51</v>
       </c>
       <c r="F187" t="n">
-        <v>2.63639</v>
+        <v>0.76328</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>32.36</v>
+        <v>20.96</v>
       </c>
       <c r="D188" t="n">
-        <v>51.07</v>
+        <v>25.85</v>
       </c>
       <c r="E188" t="n">
-        <v>57.82</v>
+        <v>23.33</v>
       </c>
       <c r="F188" t="n">
-        <v>0.08409</v>
+        <v>0.28351</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>17.89</v>
+        <v>155.75</v>
       </c>
       <c r="D189" t="n">
-        <v>30.26</v>
+        <v>255.24</v>
       </c>
       <c r="E189" t="n">
-        <v>69.14</v>
+        <v>63.88</v>
       </c>
       <c r="F189" t="n">
-        <v>0.14219</v>
+        <v>5.56767</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>62.93</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="D190" t="n">
-        <v>166.5</v>
+        <v>97.02</v>
       </c>
       <c r="E190" t="n">
-        <v>164.58</v>
+        <v>16.18</v>
       </c>
       <c r="F190" t="n">
-        <v>4.92156</v>
+        <v>0.63913</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>95.67</v>
+        <v>40.59</v>
       </c>
       <c r="D191" t="n">
-        <v>199.28</v>
+        <v>56.31</v>
       </c>
       <c r="E191" t="n">
-        <v>108.3</v>
+        <v>38.72</v>
       </c>
       <c r="F191" t="n">
-        <v>0.61832</v>
+        <v>1.40256</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>56.43</v>
+        <v>213.69</v>
       </c>
       <c r="D192" t="n">
-        <v>107.84</v>
+        <v>391.61</v>
       </c>
       <c r="E192" t="n">
-        <v>91.09999999999999</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="F192" t="n">
-        <v>3.47715</v>
+        <v>9.848380000000001</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>52.39</v>
+        <v>223.65</v>
       </c>
       <c r="D193" t="n">
-        <v>66.65000000000001</v>
+        <v>380.15</v>
       </c>
       <c r="E193" t="n">
-        <v>27.22</v>
+        <v>69.98</v>
       </c>
       <c r="F193" t="n">
-        <v>0.09493</v>
+        <v>11.77726</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>22.77</v>
+        <v>128.43</v>
       </c>
       <c r="D194" t="n">
-        <v>32.28</v>
+        <v>149.61</v>
       </c>
       <c r="E194" t="n">
-        <v>41.77</v>
+        <v>16.49</v>
       </c>
       <c r="F194" t="n">
-        <v>0.00061</v>
+        <v>0.76463</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>23.49</v>
+        <v>66.95</v>
       </c>
       <c r="D195" t="n">
-        <v>32.52</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="E195" t="n">
-        <v>38.44</v>
+        <v>29.72</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.04284</v>
+        <v>1.54492</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STRL</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>382.22</v>
+        <v>18.71</v>
       </c>
       <c r="D196" t="n">
-        <v>511.04</v>
+        <v>21.43</v>
       </c>
       <c r="E196" t="n">
-        <v>33.7</v>
+        <v>14.56</v>
       </c>
       <c r="F196" t="n">
-        <v>-4.01339</v>
+        <v>0.13204</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>124.07</v>
+        <v>126.32</v>
       </c>
       <c r="D197" t="n">
-        <v>181.97</v>
+        <v>157.96</v>
       </c>
       <c r="E197" t="n">
-        <v>46.67</v>
+        <v>25.05</v>
       </c>
       <c r="F197" t="n">
-        <v>3.9716</v>
+        <v>-0.25056</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>23.63</v>
+        <v>57.15</v>
       </c>
       <c r="D198" t="n">
-        <v>25.44</v>
+        <v>191.84</v>
       </c>
       <c r="E198" t="n">
-        <v>7.68</v>
+        <v>235.68</v>
       </c>
       <c r="F198" t="n">
-        <v>0.058</v>
+        <v>4.09928</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>172.34</v>
+        <v>62.93</v>
       </c>
       <c r="D199" t="n">
-        <v>217.15</v>
+        <v>187.93</v>
       </c>
       <c r="E199" t="n">
-        <v>26</v>
+        <v>198.64</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.72394</v>
+        <v>6.38998</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>430.4</v>
+        <v>112.5</v>
       </c>
       <c r="D200" t="n">
-        <v>557.61</v>
+        <v>195.62</v>
       </c>
       <c r="E200" t="n">
-        <v>29.56</v>
+        <v>73.89</v>
       </c>
       <c r="F200" t="n">
-        <v>0.09331</v>
+        <v>-0.91844</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BAC-PL</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1180</v>
+        <v>43.81</v>
       </c>
       <c r="D201" t="n">
-        <v>1297.24</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="E201" t="n">
-        <v>9.94</v>
+        <v>126.72</v>
       </c>
       <c r="F201" t="n">
-        <v>0.77758</v>
+        <v>-0.5039</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>96.73</v>
+        <v>17.89</v>
       </c>
       <c r="D202" t="n">
-        <v>121.71</v>
+        <v>31.4</v>
       </c>
       <c r="E202" t="n">
-        <v>25.82</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="F202" t="n">
-        <v>0.25986</v>
+        <v>0.2796</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>164.13</v>
+        <v>76.7</v>
       </c>
       <c r="D203" t="n">
-        <v>567.29</v>
+        <v>169.85</v>
       </c>
       <c r="E203" t="n">
-        <v>245.63</v>
+        <v>121.45</v>
       </c>
       <c r="F203" t="n">
-        <v>23.53755</v>
+        <v>0.64472</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>RF-PC</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>23.5</v>
+        <v>166.99</v>
       </c>
       <c r="D204" t="n">
-        <v>24.64</v>
+        <v>330.67</v>
       </c>
       <c r="E204" t="n">
-        <v>4.85</v>
+        <v>98.02</v>
       </c>
       <c r="F204" t="n">
-        <v>0.07706</v>
+        <v>9.093680000000001</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>73.13</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D205" t="n">
-        <v>96.68000000000001</v>
+        <v>164.01</v>
       </c>
       <c r="E205" t="n">
-        <v>32.2</v>
+        <v>108.66</v>
       </c>
       <c r="F205" t="n">
-        <v>0.53833</v>
+        <v>-0.47787</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ONTO</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>189.27</v>
+        <v>34.41</v>
       </c>
       <c r="D206" t="n">
-        <v>281.26</v>
+        <v>67.83</v>
       </c>
       <c r="E206" t="n">
-        <v>48.6</v>
+        <v>97.14</v>
       </c>
       <c r="F206" t="n">
-        <v>-1.39091</v>
+        <v>0.15408</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>124.03</v>
+        <v>105.37</v>
       </c>
       <c r="D207" t="n">
-        <v>216</v>
+        <v>232.9</v>
       </c>
       <c r="E207" t="n">
-        <v>74.15000000000001</v>
+        <v>121.04</v>
       </c>
       <c r="F207" t="n">
-        <v>3.76432</v>
+        <v>-1.6304</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>26.41</v>
+        <v>25.85</v>
       </c>
       <c r="D208" t="n">
-        <v>40.82</v>
+        <v>42.28</v>
       </c>
       <c r="E208" t="n">
-        <v>54.56</v>
+        <v>63.54</v>
       </c>
       <c r="F208" t="n">
-        <v>1.9156</v>
+        <v>0.06751</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>279.73</v>
+        <v>120.88</v>
       </c>
       <c r="D209" t="n">
-        <v>411.71</v>
+        <v>211.73</v>
       </c>
       <c r="E209" t="n">
-        <v>47.18</v>
+        <v>75.16</v>
       </c>
       <c r="F209" t="n">
-        <v>1.83095</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SITM</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>311.23</v>
+        <v>151.43</v>
       </c>
       <c r="D210" t="n">
-        <v>635.66</v>
+        <v>265.49</v>
       </c>
       <c r="E210" t="n">
-        <v>104.24</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="F210" t="n">
-        <v>2.45158</v>
+        <v>1.53877</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3.88</v>
+        <v>83</v>
       </c>
       <c r="D211" t="n">
-        <v>6.43</v>
+        <v>143</v>
       </c>
       <c r="E211" t="n">
-        <v>65.72</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="F211" t="n">
-        <v>0.10428</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>181.03</v>
+        <v>121.11</v>
       </c>
       <c r="D212" t="n">
-        <v>204.14</v>
+        <v>334.15</v>
       </c>
       <c r="E212" t="n">
-        <v>12.77</v>
+        <v>175.91</v>
       </c>
       <c r="F212" t="n">
-        <v>-1.65921</v>
+        <v>2.25721</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>131.47</v>
+        <v>118.05</v>
       </c>
       <c r="D213" t="n">
-        <v>204.23</v>
+        <v>190.99</v>
       </c>
       <c r="E213" t="n">
-        <v>55.34</v>
+        <v>61.79</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.85663</v>
+        <v>-0.47069</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>VMI</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>384.03</v>
+        <v>32.36</v>
       </c>
       <c r="D214" t="n">
-        <v>483.44</v>
+        <v>52.72</v>
       </c>
       <c r="E214" t="n">
-        <v>25.89</v>
+        <v>62.93</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.2071</v>
+        <v>0.30799</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TTMI</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>88.29000000000001</v>
+        <v>18.26</v>
       </c>
       <c r="D215" t="n">
-        <v>126.44</v>
+        <v>34.08</v>
       </c>
       <c r="E215" t="n">
-        <v>43.21</v>
+        <v>86.64</v>
       </c>
       <c r="F215" t="n">
-        <v>1.06978</v>
+        <v>1.16312</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>257.14</v>
+        <v>10.49</v>
       </c>
       <c r="D216" t="n">
-        <v>356.32</v>
+        <v>20.08</v>
       </c>
       <c r="E216" t="n">
-        <v>38.57</v>
+        <v>91.42</v>
       </c>
       <c r="F216" t="n">
-        <v>2.95633</v>
+        <v>-0.13477</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>316.5</v>
+        <v>188.79</v>
       </c>
       <c r="D217" t="n">
-        <v>433.24</v>
+        <v>275.84</v>
       </c>
       <c r="E217" t="n">
-        <v>36.88</v>
+        <v>46.11</v>
       </c>
       <c r="F217" t="n">
-        <v>5.00493</v>
+        <v>-2.36122</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>90.01000000000001</v>
+        <v>117.65</v>
       </c>
       <c r="D218" t="n">
-        <v>102.7</v>
+        <v>231.77</v>
       </c>
       <c r="E218" t="n">
-        <v>14.1</v>
+        <v>97</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.07063999999999999</v>
+        <v>0.39634</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>85.31999999999999</v>
+        <v>95.67</v>
       </c>
       <c r="D219" t="n">
-        <v>119.76</v>
+        <v>190.83</v>
       </c>
       <c r="E219" t="n">
-        <v>40.37</v>
+        <v>99.47</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.8095</v>
+        <v>0.72133</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>52.5</v>
+        <v>56.43</v>
       </c>
       <c r="D220" t="n">
-        <v>88.34999999999999</v>
+        <v>106.64</v>
       </c>
       <c r="E220" t="n">
-        <v>68.29000000000001</v>
+        <v>88.98</v>
       </c>
       <c r="F220" t="n">
-        <v>4.42311</v>
+        <v>2.98695</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>28.61</v>
+        <v>124.07</v>
       </c>
       <c r="D221" t="n">
-        <v>37.87</v>
+        <v>179.15</v>
       </c>
       <c r="E221" t="n">
-        <v>32.37</v>
+        <v>44.39</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.008959999999999999</v>
+        <v>4.07526</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>220.86</v>
+        <v>23.63</v>
       </c>
       <c r="D222" t="n">
-        <v>345.71</v>
+        <v>25.42</v>
       </c>
       <c r="E222" t="n">
-        <v>56.53</v>
+        <v>7.58</v>
       </c>
       <c r="F222" t="n">
-        <v>1.06733</v>
+        <v>0.06106</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GLXY</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>17.15</v>
+        <v>62.49</v>
       </c>
       <c r="D223" t="n">
-        <v>24.4</v>
+        <v>89.25</v>
       </c>
       <c r="E223" t="n">
-        <v>42.27</v>
+        <v>42.83</v>
       </c>
       <c r="F223" t="n">
-        <v>0.44284</v>
+        <v>-0.29014</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>41.25</v>
+        <v>190.63</v>
       </c>
       <c r="D224" t="n">
-        <v>51.73</v>
+        <v>216.88</v>
       </c>
       <c r="E224" t="n">
-        <v>25.41</v>
+        <v>13.77</v>
       </c>
       <c r="F224" t="n">
-        <v>0.04002</v>
+        <v>-1.68018</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>817.35</v>
+        <v>23.49</v>
       </c>
       <c r="D225" t="n">
-        <v>957.27</v>
+        <v>32.52</v>
       </c>
       <c r="E225" t="n">
-        <v>17.12</v>
+        <v>38.44</v>
       </c>
       <c r="F225" t="n">
-        <v>-2.74535</v>
+        <v>0.10028</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>276.35</v>
+        <v>172.34</v>
       </c>
       <c r="D226" t="n">
-        <v>379.72</v>
+        <v>217.81</v>
       </c>
       <c r="E226" t="n">
-        <v>37.41</v>
+        <v>26.38</v>
       </c>
       <c r="F226" t="n">
-        <v>3.99115</v>
+        <v>-0.14928</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>209.49</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="D227" t="n">
-        <v>274.9</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="E227" t="n">
-        <v>31.22</v>
+        <v>18.81</v>
       </c>
       <c r="F227" t="n">
-        <v>1.16397</v>
+        <v>-0.20036</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>208.37</v>
+        <v>96.73</v>
       </c>
       <c r="D228" t="n">
-        <v>241.87</v>
+        <v>122.64</v>
       </c>
       <c r="E228" t="n">
-        <v>16.08</v>
+        <v>26.79</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.99486</v>
+        <v>0.44226</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>RF-PC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>20.89</v>
+        <v>23.5</v>
       </c>
       <c r="D229" t="n">
-        <v>39.47</v>
+        <v>24.59</v>
       </c>
       <c r="E229" t="n">
-        <v>88.94</v>
+        <v>4.66</v>
       </c>
       <c r="F229" t="n">
-        <v>0.8488599999999999</v>
+        <v>0.05496</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>41.19</v>
+        <v>164.13</v>
       </c>
       <c r="D230" t="n">
-        <v>102.94</v>
+        <v>542.84</v>
       </c>
       <c r="E230" t="n">
-        <v>149.92</v>
+        <v>230.73</v>
       </c>
       <c r="F230" t="n">
-        <v>3.32896</v>
+        <v>22.14874</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1273.18</v>
+        <v>73.13</v>
       </c>
       <c r="D231" t="n">
-        <v>1690.82</v>
+        <v>95.2</v>
       </c>
       <c r="E231" t="n">
-        <v>32.8</v>
+        <v>30.18</v>
       </c>
       <c r="F231" t="n">
-        <v>2.09023</v>
+        <v>0.41372</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5980,22 +5980,22 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>7.96</v>
+        <v>186.42</v>
       </c>
       <c r="D232" t="n">
-        <v>11.13</v>
+        <v>264.71</v>
       </c>
       <c r="E232" t="n">
-        <v>39.82</v>
+        <v>42</v>
       </c>
       <c r="F232" t="n">
-        <v>0.2286</v>
+        <v>-0.25716</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6004,22 +6004,22 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>28.35</v>
+        <v>31.8</v>
       </c>
       <c r="D233" t="n">
-        <v>37.09</v>
+        <v>69.3</v>
       </c>
       <c r="E233" t="n">
-        <v>30.83</v>
+        <v>117.92</v>
       </c>
       <c r="F233" t="n">
-        <v>0.11815</v>
+        <v>0.30504</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6028,22 +6028,22 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>269.41</v>
+        <v>20.33</v>
       </c>
       <c r="D234" t="n">
-        <v>338.64</v>
+        <v>29.06</v>
       </c>
       <c r="E234" t="n">
-        <v>25.7</v>
+        <v>42.92</v>
       </c>
       <c r="F234" t="n">
-        <v>2.12017</v>
+        <v>0.12196</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6052,22 +6052,22 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>8.609999999999999</v>
+        <v>204.77</v>
       </c>
       <c r="D235" t="n">
-        <v>22.64</v>
+        <v>274.32</v>
       </c>
       <c r="E235" t="n">
-        <v>162.95</v>
+        <v>33.96</v>
       </c>
       <c r="F235" t="n">
-        <v>0.88566</v>
+        <v>0.48652</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6076,22 +6076,22 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>69.3</v>
+        <v>257.27</v>
       </c>
       <c r="D236" t="n">
-        <v>83.20999999999999</v>
+        <v>320.37</v>
       </c>
       <c r="E236" t="n">
-        <v>20.07</v>
+        <v>24.53</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.161</v>
+        <v>6.33832</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6100,22 +6100,22 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>257.27</v>
+        <v>97.52</v>
       </c>
       <c r="D237" t="n">
-        <v>346.55</v>
+        <v>132.44</v>
       </c>
       <c r="E237" t="n">
-        <v>34.7</v>
+        <v>35.81</v>
       </c>
       <c r="F237" t="n">
-        <v>8.016030000000001</v>
+        <v>2.13395</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6124,22 +6124,22 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>97.52</v>
+        <v>19.02</v>
       </c>
       <c r="D238" t="n">
-        <v>132.01</v>
+        <v>27.16</v>
       </c>
       <c r="E238" t="n">
-        <v>35.37</v>
+        <v>42.8</v>
       </c>
       <c r="F238" t="n">
-        <v>2.04384</v>
+        <v>0.27103</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>29.16</v>
+        <v>131.47</v>
       </c>
       <c r="D239" t="n">
-        <v>40.11</v>
+        <v>213.11</v>
       </c>
       <c r="E239" t="n">
-        <v>37.55</v>
+        <v>62.1</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.06358</v>
+        <v>0.82591</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>119.51</v>
+        <v>28.35</v>
       </c>
       <c r="D240" t="n">
-        <v>275.75</v>
+        <v>39</v>
       </c>
       <c r="E240" t="n">
-        <v>130.73</v>
+        <v>37.57</v>
       </c>
       <c r="F240" t="n">
-        <v>16.30736</v>
+        <v>0.32023</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>166</v>
+        <v>21.06</v>
       </c>
       <c r="D241" t="n">
-        <v>409.8</v>
+        <v>37.67</v>
       </c>
       <c r="E241" t="n">
-        <v>146.87</v>
+        <v>78.87</v>
       </c>
       <c r="F241" t="n">
-        <v>4.61449</v>
+        <v>0.5991</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,16 +6220,16 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>187.39</v>
+        <v>69.3</v>
       </c>
       <c r="D242" t="n">
-        <v>236.62</v>
+        <v>84.25</v>
       </c>
       <c r="E242" t="n">
-        <v>26.27</v>
+        <v>21.58</v>
       </c>
       <c r="F242" t="n">
-        <v>-0.63052</v>
+        <v>0.27481</v>
       </c>
     </row>
     <row r="243">
@@ -6247,19 +6247,19 @@
         <v>16.32</v>
       </c>
       <c r="D243" t="n">
-        <v>23.89</v>
+        <v>23.86</v>
       </c>
       <c r="E243" t="n">
-        <v>46.38</v>
+        <v>46.2</v>
       </c>
       <c r="F243" t="n">
-        <v>0.22921</v>
+        <v>0.23214</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>572.5</v>
+        <v>67.39</v>
       </c>
       <c r="D244" t="n">
-        <v>1633.35</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="E244" t="n">
-        <v>185.3</v>
+        <v>38.27</v>
       </c>
       <c r="F244" t="n">
-        <v>55.17344</v>
+        <v>0.53301</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>533.78</v>
+        <v>41.19</v>
       </c>
       <c r="D245" t="n">
-        <v>650.58</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="E245" t="n">
-        <v>21.88</v>
+        <v>138.55</v>
       </c>
       <c r="F245" t="n">
-        <v>-0.02439</v>
+        <v>2.42033</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,22 +6316,22 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>126.58</v>
+        <v>29.16</v>
       </c>
       <c r="D246" t="n">
-        <v>146.01</v>
+        <v>39.93</v>
       </c>
       <c r="E246" t="n">
-        <v>15.35</v>
+        <v>36.93</v>
       </c>
       <c r="F246" t="n">
-        <v>0.38161</v>
+        <v>0.01104</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>87.81</v>
+        <v>119.51</v>
       </c>
       <c r="D247" t="n">
-        <v>236.1</v>
+        <v>260.1</v>
       </c>
       <c r="E247" t="n">
-        <v>168.88</v>
+        <v>117.64</v>
       </c>
       <c r="F247" t="n">
-        <v>3.38837</v>
+        <v>13.1238</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>258.08</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="D248" t="n">
-        <v>280.76</v>
+        <v>111.47</v>
       </c>
       <c r="E248" t="n">
-        <v>8.789999999999999</v>
+        <v>44.69</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.53063</v>
+        <v>-0.43007</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>24.77</v>
+        <v>273.14</v>
       </c>
       <c r="D249" t="n">
-        <v>37.27</v>
+        <v>345.73</v>
       </c>
       <c r="E249" t="n">
-        <v>50.46</v>
+        <v>26.58</v>
       </c>
       <c r="F249" t="n">
-        <v>0.47609</v>
+        <v>-1.4371</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>284.79</v>
+        <v>196.04</v>
       </c>
       <c r="D250" t="n">
-        <v>418.72</v>
+        <v>493.84</v>
       </c>
       <c r="E250" t="n">
-        <v>47.03</v>
+        <v>151.91</v>
       </c>
       <c r="F250" t="n">
-        <v>3.19445</v>
+        <v>9.88194</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>59.58</v>
+        <v>52.5</v>
       </c>
       <c r="D251" t="n">
-        <v>83.92</v>
+        <v>80.59</v>
       </c>
       <c r="E251" t="n">
-        <v>40.86</v>
+        <v>53.5</v>
       </c>
       <c r="F251" t="n">
-        <v>0.38935</v>
+        <v>4.49805</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>67.39</v>
+        <v>59.66</v>
       </c>
       <c r="D252" t="n">
-        <v>93.45</v>
+        <v>84.02</v>
       </c>
       <c r="E252" t="n">
-        <v>38.67</v>
+        <v>40.83</v>
       </c>
       <c r="F252" t="n">
-        <v>0.55333</v>
+        <v>1.57919</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>65.16</v>
+        <v>22.61</v>
       </c>
       <c r="D253" t="n">
-        <v>112.57</v>
+        <v>56.88</v>
       </c>
       <c r="E253" t="n">
-        <v>72.76000000000001</v>
+        <v>151.59</v>
       </c>
       <c r="F253" t="n">
-        <v>2.79859</v>
+        <v>1.67485</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>343.53</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D254" t="n">
-        <v>425.37</v>
+        <v>22.17</v>
       </c>
       <c r="E254" t="n">
-        <v>23.82</v>
+        <v>157.55</v>
       </c>
       <c r="F254" t="n">
-        <v>1.55336</v>
+        <v>0.83512</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>19.02</v>
+        <v>246.63</v>
       </c>
       <c r="D255" t="n">
-        <v>27.29</v>
+        <v>334.52</v>
       </c>
       <c r="E255" t="n">
-        <v>43.48</v>
+        <v>35.64</v>
       </c>
       <c r="F255" t="n">
-        <v>0.26062</v>
+        <v>3.66481</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>20.33</v>
+        <v>3.88</v>
       </c>
       <c r="D256" t="n">
-        <v>29.55</v>
+        <v>6.36</v>
       </c>
       <c r="E256" t="n">
-        <v>45.35</v>
+        <v>64.05</v>
       </c>
       <c r="F256" t="n">
-        <v>0.15953</v>
+        <v>0.08054</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>303.1</v>
+        <v>166</v>
       </c>
       <c r="D257" t="n">
-        <v>378.78</v>
+        <v>414.12</v>
       </c>
       <c r="E257" t="n">
-        <v>24.97</v>
+        <v>149.47</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.37386</v>
+        <v>5.22597</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>186.42</v>
+        <v>65.16</v>
       </c>
       <c r="D258" t="n">
-        <v>268.7</v>
+        <v>114.46</v>
       </c>
       <c r="E258" t="n">
-        <v>44.14</v>
+        <v>75.66</v>
       </c>
       <c r="F258" t="n">
-        <v>-0.8937</v>
+        <v>2.25778</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>219.65</v>
+        <v>273.5</v>
       </c>
       <c r="D259" t="n">
-        <v>305.37</v>
+        <v>349.13</v>
       </c>
       <c r="E259" t="n">
-        <v>39.03</v>
+        <v>27.65</v>
       </c>
       <c r="F259" t="n">
-        <v>3.42654</v>
+        <v>-1.45481</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>246.63</v>
+        <v>199.3</v>
       </c>
       <c r="D260" t="n">
-        <v>332.27</v>
+        <v>351.66</v>
       </c>
       <c r="E260" t="n">
-        <v>34.72</v>
+        <v>76.45</v>
       </c>
       <c r="F260" t="n">
-        <v>2.12426</v>
+        <v>-1.45619</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>55.66</v>
+        <v>279.73</v>
       </c>
       <c r="D261" t="n">
-        <v>76.14</v>
+        <v>412.51</v>
       </c>
       <c r="E261" t="n">
-        <v>36.79</v>
+        <v>47.47</v>
       </c>
       <c r="F261" t="n">
-        <v>-1.33547</v>
+        <v>3.83657</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>GLXY</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>92.26000000000001</v>
+        <v>17.15</v>
       </c>
       <c r="D262" t="n">
-        <v>224.55</v>
+        <v>24.21</v>
       </c>
       <c r="E262" t="n">
-        <v>143.39</v>
+        <v>41.17</v>
       </c>
       <c r="F262" t="n">
-        <v>5.71318</v>
+        <v>0.13019</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>116.13</v>
+        <v>258.08</v>
       </c>
       <c r="D263" t="n">
-        <v>199.59</v>
+        <v>288.61</v>
       </c>
       <c r="E263" t="n">
-        <v>71.87</v>
+        <v>11.83</v>
       </c>
       <c r="F263" t="n">
-        <v>0.93349</v>
+        <v>0.73753</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>60.57</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D264" t="n">
-        <v>115.78</v>
+        <v>100.83</v>
       </c>
       <c r="E264" t="n">
-        <v>91.15000000000001</v>
+        <v>12.03</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.17589</v>
+        <v>0.15752</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>31.8</v>
+        <v>26.41</v>
       </c>
       <c r="D265" t="n">
-        <v>66.42</v>
+        <v>41.35</v>
       </c>
       <c r="E265" t="n">
-        <v>108.87</v>
+        <v>56.57</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.1597</v>
+        <v>1.72078</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>77.04000000000001</v>
+        <v>24.77</v>
       </c>
       <c r="D266" t="n">
-        <v>112.13</v>
+        <v>36.81</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>48.61</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.71745</v>
+        <v>0.39741</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>247.48</v>
+        <v>284.79</v>
       </c>
       <c r="D267" t="n">
-        <v>318.08</v>
+        <v>424.15</v>
       </c>
       <c r="E267" t="n">
-        <v>28.53</v>
+        <v>48.93</v>
       </c>
       <c r="F267" t="n">
-        <v>-1.78538</v>
+        <v>5.00546</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,190 +6844,190 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>321.8</v>
+        <v>12.96</v>
       </c>
       <c r="D268" t="n">
-        <v>975.26</v>
+        <v>16.72</v>
       </c>
       <c r="E268" t="n">
-        <v>203.06</v>
+        <v>28.97</v>
       </c>
       <c r="F268" t="n">
-        <v>16.22983</v>
+        <v>-0.04627</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>107.27</v>
+        <v>52.49</v>
       </c>
       <c r="D269" t="n">
-        <v>138.82</v>
+        <v>55.78</v>
       </c>
       <c r="E269" t="n">
-        <v>29.41</v>
+        <v>6.27</v>
       </c>
       <c r="F269" t="n">
-        <v>1.16703</v>
+        <v>-0.04614</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>196.04</v>
+        <v>182.65</v>
       </c>
       <c r="D270" t="n">
-        <v>516.13</v>
+        <v>336.38</v>
       </c>
       <c r="E270" t="n">
-        <v>163.28</v>
+        <v>84.17</v>
       </c>
       <c r="F270" t="n">
-        <v>12.17477</v>
+        <v>3.88875</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>21.06</v>
+        <v>317.93</v>
       </c>
       <c r="D271" t="n">
-        <v>40.1</v>
+        <v>377.91</v>
       </c>
       <c r="E271" t="n">
-        <v>90.41</v>
+        <v>18.87</v>
       </c>
       <c r="F271" t="n">
-        <v>0.93479</v>
+        <v>-0.86572</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>112.75</v>
+        <v>284.93</v>
       </c>
       <c r="D272" t="n">
-        <v>162.38</v>
+        <v>412.13</v>
       </c>
       <c r="E272" t="n">
-        <v>44.02</v>
+        <v>44.64</v>
       </c>
       <c r="F272" t="n">
-        <v>1.48447</v>
+        <v>0.63228</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>AXSM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>57.45</v>
+        <v>156.35</v>
       </c>
       <c r="D273" t="n">
-        <v>70.48</v>
+        <v>221.49</v>
       </c>
       <c r="E273" t="n">
-        <v>22.68</v>
+        <v>41.66</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.27768</v>
+        <v>2.23334</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>QSR</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>59.66</v>
+        <v>71.42</v>
       </c>
       <c r="D274" t="n">
-        <v>84.06</v>
+        <v>78.64</v>
       </c>
       <c r="E274" t="n">
-        <v>40.9</v>
+        <v>10.11</v>
       </c>
       <c r="F274" t="n">
-        <v>1.6949</v>
+        <v>-0.26445</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>107.11</v>
+        <v>87.98</v>
       </c>
       <c r="D275" t="n">
-        <v>126.4</v>
+        <v>110.28</v>
       </c>
       <c r="E275" t="n">
-        <v>18.01</v>
+        <v>25.34</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.54744</v>
+        <v>0.48448</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>525.72</v>
+        <v>92.42</v>
       </c>
       <c r="D276" t="n">
-        <v>648.03</v>
+        <v>109.11</v>
       </c>
       <c r="E276" t="n">
-        <v>23.27</v>
+        <v>18.06</v>
       </c>
       <c r="F276" t="n">
-        <v>18.95295</v>
+        <v>0.23722</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,22 +7060,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>79.19</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D277" t="n">
-        <v>105.3</v>
+        <v>157.2</v>
       </c>
       <c r="E277" t="n">
-        <v>32.97</v>
+        <v>80.38</v>
       </c>
       <c r="F277" t="n">
-        <v>0.32431</v>
+        <v>-0.11238</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7084,22 +7084,22 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>33.63</v>
+        <v>7.58</v>
       </c>
       <c r="D278" t="n">
-        <v>43.49</v>
+        <v>10.75</v>
       </c>
       <c r="E278" t="n">
-        <v>29.32</v>
+        <v>41.82</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.02051</v>
+        <v>0.1819</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7108,22 +7108,22 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>22.3</v>
+        <v>121.84</v>
       </c>
       <c r="D279" t="n">
-        <v>34.67</v>
+        <v>165.15</v>
       </c>
       <c r="E279" t="n">
-        <v>55.47</v>
+        <v>35.54</v>
       </c>
       <c r="F279" t="n">
-        <v>0.3951</v>
+        <v>0.3143</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7132,22 +7132,22 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>285.27</v>
+        <v>35.34</v>
       </c>
       <c r="D280" t="n">
-        <v>375.2</v>
+        <v>53.39</v>
       </c>
       <c r="E280" t="n">
-        <v>31.52</v>
+        <v>51.08</v>
       </c>
       <c r="F280" t="n">
-        <v>0.13349</v>
+        <v>0.71484</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7156,22 +7156,22 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>20.72</v>
+        <v>295.52</v>
       </c>
       <c r="D281" t="n">
-        <v>24.74</v>
+        <v>376.22</v>
       </c>
       <c r="E281" t="n">
-        <v>19.4</v>
+        <v>27.31</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.18065</v>
+        <v>-0.65359</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7180,22 +7180,22 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>14.27</v>
+        <v>285.27</v>
       </c>
       <c r="D282" t="n">
-        <v>18.89</v>
+        <v>376.05</v>
       </c>
       <c r="E282" t="n">
-        <v>32.38</v>
+        <v>31.82</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.00158</v>
+        <v>1.1103</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7204,22 +7204,22 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>28.37</v>
+        <v>22.3</v>
       </c>
       <c r="D283" t="n">
-        <v>40.48</v>
+        <v>34.63</v>
       </c>
       <c r="E283" t="n">
-        <v>42.69</v>
+        <v>55.29</v>
       </c>
       <c r="F283" t="n">
-        <v>0.44352</v>
+        <v>0.44128</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7228,22 +7228,22 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>92.42</v>
+        <v>525.72</v>
       </c>
       <c r="D284" t="n">
-        <v>106.55</v>
+        <v>664.37</v>
       </c>
       <c r="E284" t="n">
-        <v>15.29</v>
+        <v>26.37</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.16412</v>
+        <v>21.99458</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7252,22 +7252,22 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>50.85</v>
+        <v>55.4</v>
       </c>
       <c r="D285" t="n">
-        <v>62.84</v>
+        <v>69.02</v>
       </c>
       <c r="E285" t="n">
-        <v>23.58</v>
+        <v>24.58</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.14971</v>
+        <v>-0.05427</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7276,22 +7276,22 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>156.35</v>
+        <v>20.72</v>
       </c>
       <c r="D286" t="n">
-        <v>220.75</v>
+        <v>24.44</v>
       </c>
       <c r="E286" t="n">
-        <v>41.19</v>
+        <v>17.95</v>
       </c>
       <c r="F286" t="n">
-        <v>1.02948</v>
+        <v>-0.10916</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>LYG</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7300,22 +7300,22 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>4.83</v>
+        <v>3.42</v>
       </c>
       <c r="D287" t="n">
-        <v>6.01</v>
+        <v>4.93</v>
       </c>
       <c r="E287" t="n">
-        <v>24.43</v>
+        <v>44.3</v>
       </c>
       <c r="F287" t="n">
-        <v>-0.02334</v>
+        <v>0.09897</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7324,22 +7324,22 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>317.4</v>
+        <v>67.7</v>
       </c>
       <c r="D288" t="n">
-        <v>413.78</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="E288" t="n">
-        <v>30.37</v>
+        <v>43.34</v>
       </c>
       <c r="F288" t="n">
-        <v>-1.68102</v>
+        <v>0.19021</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7348,16 +7348,16 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>284.93</v>
+        <v>10.65</v>
       </c>
       <c r="D289" t="n">
-        <v>408.22</v>
+        <v>14.7</v>
       </c>
       <c r="E289" t="n">
-        <v>43.27</v>
+        <v>38.03</v>
       </c>
       <c r="F289" t="n">
-        <v>0.1641</v>
+        <v>0.04629</v>
       </c>
     </row>
     <row r="290">
@@ -7375,19 +7375,19 @@
         <v>39.84</v>
       </c>
       <c r="D290" t="n">
-        <v>58.55</v>
+        <v>58.24</v>
       </c>
       <c r="E290" t="n">
-        <v>46.96</v>
+        <v>46.18</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.18999</v>
+        <v>-0.10904</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7396,22 +7396,22 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>91.37</v>
+        <v>243.35</v>
       </c>
       <c r="D291" t="n">
-        <v>120.97</v>
+        <v>355.6</v>
       </c>
       <c r="E291" t="n">
-        <v>32.4</v>
+        <v>46.13</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.15904</v>
+        <v>0.59458</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7420,22 +7420,22 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>134.99</v>
+        <v>41.53</v>
       </c>
       <c r="D292" t="n">
-        <v>189.19</v>
+        <v>56.49</v>
       </c>
       <c r="E292" t="n">
-        <v>40.15</v>
+        <v>36.01</v>
       </c>
       <c r="F292" t="n">
-        <v>0.28198</v>
+        <v>0.3765</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7444,22 +7444,22 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>282.84</v>
+        <v>147.02</v>
       </c>
       <c r="D293" t="n">
-        <v>356.23</v>
+        <v>376.69</v>
       </c>
       <c r="E293" t="n">
-        <v>25.95</v>
+        <v>156.22</v>
       </c>
       <c r="F293" t="n">
-        <v>-0.63374</v>
+        <v>-1.82275</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7468,22 +7468,22 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>7.58</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D294" t="n">
-        <v>10.86</v>
+        <v>80</v>
       </c>
       <c r="E294" t="n">
-        <v>43.27</v>
+        <v>18.4</v>
       </c>
       <c r="F294" t="n">
-        <v>0.18842</v>
+        <v>-0.42092</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7492,22 +7492,22 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>3.93</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D295" t="n">
-        <v>5.68</v>
+        <v>115.66</v>
       </c>
       <c r="E295" t="n">
-        <v>44.53</v>
+        <v>32.93</v>
       </c>
       <c r="F295" t="n">
-        <v>0.03783</v>
+        <v>0.73512</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7516,22 +7516,22 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>182.65</v>
+        <v>67.23</v>
       </c>
       <c r="D296" t="n">
-        <v>328.93</v>
+        <v>98.89</v>
       </c>
       <c r="E296" t="n">
-        <v>80.09</v>
+        <v>47.09</v>
       </c>
       <c r="F296" t="n">
-        <v>3.00967</v>
+        <v>-0.07883999999999999</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7540,22 +7540,22 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>72.90000000000001</v>
+        <v>125.78</v>
       </c>
       <c r="D297" t="n">
-        <v>94.42</v>
+        <v>143.73</v>
       </c>
       <c r="E297" t="n">
-        <v>29.52</v>
+        <v>14.27</v>
       </c>
       <c r="F297" t="n">
-        <v>0.73445</v>
+        <v>-0.3938</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7564,22 +7564,22 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>122.52</v>
+        <v>35.72</v>
       </c>
       <c r="D298" t="n">
-        <v>193.4</v>
+        <v>49.63</v>
       </c>
       <c r="E298" t="n">
-        <v>57.85</v>
+        <v>38.94</v>
       </c>
       <c r="F298" t="n">
-        <v>0.72575</v>
+        <v>-0.53366</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7588,22 +7588,22 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>67.7</v>
+        <v>157.12</v>
       </c>
       <c r="D299" t="n">
-        <v>97.14</v>
+        <v>260.63</v>
       </c>
       <c r="E299" t="n">
-        <v>43.49</v>
+        <v>65.88</v>
       </c>
       <c r="F299" t="n">
-        <v>0.04813</v>
+        <v>1.83577</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7612,22 +7612,22 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>46.97</v>
+        <v>92.39</v>
       </c>
       <c r="D300" t="n">
-        <v>62.69</v>
+        <v>238.64</v>
       </c>
       <c r="E300" t="n">
-        <v>33.47</v>
+        <v>158.28</v>
       </c>
       <c r="F300" t="n">
-        <v>0.03608</v>
+        <v>2.67952</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7636,22 +7636,22 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>289.16</v>
+        <v>213.28</v>
       </c>
       <c r="D301" t="n">
-        <v>408.34</v>
+        <v>283.36</v>
       </c>
       <c r="E301" t="n">
-        <v>41.22</v>
+        <v>32.86</v>
       </c>
       <c r="F301" t="n">
-        <v>-1.16894</v>
+        <v>-0.55426</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7660,22 +7660,22 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>121.84</v>
+        <v>7.63</v>
       </c>
       <c r="D302" t="n">
-        <v>157.77</v>
+        <v>11.3</v>
       </c>
       <c r="E302" t="n">
-        <v>29.49</v>
+        <v>48.1</v>
       </c>
       <c r="F302" t="n">
-        <v>-1.31209</v>
+        <v>0.15799</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7684,22 +7684,22 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>10.65</v>
+        <v>61.37</v>
       </c>
       <c r="D303" t="n">
-        <v>14.96</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="E303" t="n">
-        <v>40.47</v>
+        <v>30.06</v>
       </c>
       <c r="F303" t="n">
-        <v>0.068</v>
+        <v>-0.1355</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7708,22 +7708,22 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>35.34</v>
+        <v>14</v>
       </c>
       <c r="D304" t="n">
-        <v>53.34</v>
+        <v>14.82</v>
       </c>
       <c r="E304" t="n">
-        <v>50.93</v>
+        <v>5.89</v>
       </c>
       <c r="F304" t="n">
-        <v>0.64798</v>
+        <v>0.01538</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7732,22 +7732,22 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>14</v>
+        <v>3.93</v>
       </c>
       <c r="D305" t="n">
-        <v>14.79</v>
+        <v>5.93</v>
       </c>
       <c r="E305" t="n">
-        <v>5.64</v>
+        <v>50.76</v>
       </c>
       <c r="F305" t="n">
-        <v>0.01762</v>
+        <v>0.08137</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7756,142 +7756,142 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>87.98</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D306" t="n">
-        <v>107.75</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="E306" t="n">
-        <v>22.47</v>
+        <v>29.08</v>
       </c>
       <c r="F306" t="n">
-        <v>-0.06295000000000001</v>
+        <v>0.66736</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>36.41</v>
+        <v>17.13</v>
       </c>
       <c r="D307" t="n">
-        <v>54.58</v>
+        <v>43.57</v>
       </c>
       <c r="E307" t="n">
-        <v>49.9</v>
+        <v>154.35</v>
       </c>
       <c r="F307" t="n">
-        <v>0.12294</v>
+        <v>0.30141</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>7.63</v>
+        <v>63.78</v>
       </c>
       <c r="D308" t="n">
-        <v>11.45</v>
+        <v>70.59</v>
       </c>
       <c r="E308" t="n">
-        <v>50.07</v>
+        <v>10.68</v>
       </c>
       <c r="F308" t="n">
-        <v>0.15777</v>
+        <v>0.28062</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>17.13</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D309" t="n">
-        <v>43.96</v>
+        <v>172.41</v>
       </c>
       <c r="E309" t="n">
-        <v>156.63</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="F309" t="n">
-        <v>0.24682</v>
+        <v>0.53291</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>MDGL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>99.98999999999999</v>
+        <v>445.04</v>
       </c>
       <c r="D310" t="n">
-        <v>169.31</v>
+        <v>538.77</v>
       </c>
       <c r="E310" t="n">
-        <v>69.33</v>
+        <v>21.06</v>
       </c>
       <c r="F310" t="n">
-        <v>-0.89257</v>
+        <v>2.07857</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>FMX</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>63.78</v>
+        <v>105.8</v>
       </c>
       <c r="D311" t="n">
-        <v>68.98</v>
+        <v>121.22</v>
       </c>
       <c r="E311" t="n">
-        <v>8.15</v>
+        <v>14.58</v>
       </c>
       <c r="F311" t="n">
-        <v>0.05541</v>
+        <v>-0.81049</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7900,22 +7900,22 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>134.96</v>
+        <v>27.17</v>
       </c>
       <c r="D312" t="n">
-        <v>264.79</v>
+        <v>34.04</v>
       </c>
       <c r="E312" t="n">
-        <v>96.2</v>
+        <v>25.29</v>
       </c>
       <c r="F312" t="n">
-        <v>3.15965</v>
+        <v>-0.22965</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7924,22 +7924,22 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>23.65</v>
+        <v>23.97</v>
       </c>
       <c r="D313" t="n">
-        <v>28.33</v>
+        <v>30.69</v>
       </c>
       <c r="E313" t="n">
-        <v>19.79</v>
+        <v>28.06</v>
       </c>
       <c r="F313" t="n">
-        <v>0.11786</v>
+        <v>-0.06813</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>HMY</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7948,22 +7948,22 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>13.86</v>
+        <v>146.17</v>
       </c>
       <c r="D314" t="n">
-        <v>20.64</v>
+        <v>217.26</v>
       </c>
       <c r="E314" t="n">
-        <v>48.92</v>
+        <v>48.63</v>
       </c>
       <c r="F314" t="n">
-        <v>0.12952</v>
+        <v>0.02127</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ABEV</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7972,22 +7972,22 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2.78</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D315" t="n">
-        <v>3.02</v>
+        <v>111.31</v>
       </c>
       <c r="E315" t="n">
-        <v>8.630000000000001</v>
+        <v>18.11</v>
       </c>
       <c r="F315" t="n">
-        <v>0.03112</v>
+        <v>-0.26258</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MDGL</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7996,232 +7996,112 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>445.04</v>
+        <v>241.14</v>
       </c>
       <c r="D316" t="n">
-        <v>534.49</v>
+        <v>300.65</v>
       </c>
       <c r="E316" t="n">
-        <v>20.1</v>
+        <v>24.68</v>
       </c>
       <c r="F316" t="n">
-        <v>1.8121</v>
+        <v>1.83751</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>202.78</v>
+        <v>23.65</v>
       </c>
       <c r="D317" t="n">
-        <v>270.45</v>
+        <v>29.58</v>
       </c>
       <c r="E317" t="n">
-        <v>33.37</v>
+        <v>25.07</v>
       </c>
       <c r="F317" t="n">
-        <v>0.5861499999999999</v>
+        <v>0.25425</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>86.55</v>
+        <v>115.92</v>
       </c>
       <c r="D318" t="n">
-        <v>116.17</v>
+        <v>159.86</v>
       </c>
       <c r="E318" t="n">
-        <v>34.22</v>
+        <v>37.91</v>
       </c>
       <c r="F318" t="n">
-        <v>0.7472299999999999</v>
+        <v>-0.77523</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>241.4</v>
+        <v>2.78</v>
       </c>
       <c r="D319" t="n">
-        <v>346.23</v>
+        <v>3.03</v>
       </c>
       <c r="E319" t="n">
-        <v>43.43</v>
+        <v>8.99</v>
       </c>
       <c r="F319" t="n">
-        <v>-1.22178</v>
+        <v>0.02721</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>ARGX</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>55.05</v>
+        <v>677.5</v>
       </c>
       <c r="D320" t="n">
-        <v>68.75</v>
+        <v>1001.41</v>
       </c>
       <c r="E320" t="n">
-        <v>24.89</v>
+        <v>47.81</v>
       </c>
       <c r="F320" t="n">
-        <v>-0.12841</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>SNX</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>156.37</v>
-      </c>
-      <c r="D321" t="n">
-        <v>269.21</v>
-      </c>
-      <c r="E321" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="F321" t="n">
-        <v>1.81533</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>NUE</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>160.62</v>
-      </c>
-      <c r="D322" t="n">
-        <v>259.43</v>
-      </c>
-      <c r="E322" t="n">
-        <v>61.52</v>
-      </c>
-      <c r="F322" t="n">
-        <v>0.38868</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>GGB</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="D323" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E323" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="F323" t="n">
-        <v>0.12255</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>VRSN</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>240.92</v>
-      </c>
-      <c r="D324" t="n">
-        <v>292.71</v>
-      </c>
-      <c r="E324" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F324" t="n">
-        <v>0.08883000000000001</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="D325" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="E325" t="n">
-        <v>178.18</v>
-      </c>
-      <c r="F325" t="n">
-        <v>1.76115</v>
+        <v>-1.79368</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F320"/>
+  <dimension ref="A1:F325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,175 +451,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.84</v>
+        <v>2876.75</v>
       </c>
       <c r="D2" t="n">
-        <v>23.07</v>
+        <v>2965.52</v>
       </c>
       <c r="E2" t="n">
-        <v>5.63</v>
+        <v>3.09</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.19239</v>
+        <v>-26.725</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.65</v>
+        <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>12.3</v>
+        <v>57.29</v>
       </c>
       <c r="E3" t="n">
-        <v>5.54</v>
+        <v>5.45</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.14275</v>
+        <v>-0.33941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54.33</v>
+        <v>38.22</v>
       </c>
       <c r="D4" t="n">
-        <v>57.31</v>
+        <v>41.6</v>
       </c>
       <c r="E4" t="n">
-        <v>5.48</v>
+        <v>8.84</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3375</v>
+        <v>0.17365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.22</v>
+        <v>17.87</v>
       </c>
       <c r="D5" t="n">
-        <v>41.87</v>
+        <v>21.62</v>
       </c>
       <c r="E5" t="n">
-        <v>9.550000000000001</v>
+        <v>20.98</v>
       </c>
       <c r="F5" t="n">
-        <v>0.19936</v>
+        <v>0.65938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.87</v>
+        <v>102.63</v>
       </c>
       <c r="D6" t="n">
-        <v>21.65</v>
+        <v>109.08</v>
       </c>
       <c r="E6" t="n">
-        <v>21.15</v>
+        <v>6.28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6622400000000001</v>
+        <v>-0.22351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>102.63</v>
+        <v>13.03</v>
       </c>
       <c r="D7" t="n">
-        <v>109.35</v>
+        <v>14.97</v>
       </c>
       <c r="E7" t="n">
-        <v>6.54</v>
+        <v>14.89</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.19827</v>
+        <v>-0.01791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.03</v>
+        <v>298.59</v>
       </c>
       <c r="D8" t="n">
-        <v>14.74</v>
+        <v>334.24</v>
       </c>
       <c r="E8" t="n">
-        <v>13.16</v>
+        <v>11.94</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03934</v>
+        <v>-1.56324</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -628,70 +628,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>298.59</v>
+        <v>5.67</v>
       </c>
       <c r="D9" t="n">
-        <v>335.36</v>
+        <v>7.03</v>
       </c>
       <c r="E9" t="n">
-        <v>12.31</v>
+        <v>23.99</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.45657</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.67</v>
+        <v>141.63</v>
       </c>
       <c r="D10" t="n">
-        <v>7.07</v>
+        <v>157.31</v>
       </c>
       <c r="E10" t="n">
-        <v>24.6</v>
+        <v>11.07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.16814</v>
+        <v>1.11386</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>141.63</v>
+        <v>12.43</v>
       </c>
       <c r="D11" t="n">
-        <v>157.01</v>
+        <v>18.42</v>
       </c>
       <c r="E11" t="n">
-        <v>10.86</v>
+        <v>48.19</v>
       </c>
       <c r="F11" t="n">
-        <v>1.08529</v>
+        <v>0.97816</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.46</v>
+        <v>11.23</v>
       </c>
       <c r="D12" t="n">
-        <v>5.21</v>
+        <v>11.89</v>
       </c>
       <c r="E12" t="n">
-        <v>16.82</v>
+        <v>5.88</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08419</v>
+        <v>0.03212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12.43</v>
+        <v>7.17</v>
       </c>
       <c r="D13" t="n">
-        <v>18.51</v>
+        <v>8.23</v>
       </c>
       <c r="E13" t="n">
-        <v>48.95</v>
+        <v>14.78</v>
       </c>
       <c r="F13" t="n">
-        <v>0.98721</v>
+        <v>0.13527</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.17</v>
+        <v>4.46</v>
       </c>
       <c r="D14" t="n">
-        <v>8.19</v>
+        <v>5.22</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3</v>
+        <v>17.04</v>
       </c>
       <c r="F14" t="n">
-        <v>0.13194</v>
+        <v>0.08513999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.23</v>
+        <v>2.98</v>
       </c>
       <c r="D15" t="n">
-        <v>11.81</v>
+        <v>3.54</v>
       </c>
       <c r="E15" t="n">
-        <v>5.12</v>
+        <v>18.79</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02403</v>
+        <v>0.06816999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.98</v>
+        <v>17.28</v>
       </c>
       <c r="D16" t="n">
-        <v>3.53</v>
+        <v>19.12</v>
       </c>
       <c r="E16" t="n">
-        <v>18.29</v>
+        <v>10.65</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06673999999999999</v>
+        <v>0.22309</v>
       </c>
     </row>
     <row r="17">
@@ -823,259 +823,259 @@
         <v>98.45</v>
       </c>
       <c r="D17" t="n">
-        <v>123.05</v>
+        <v>122.3</v>
       </c>
       <c r="E17" t="n">
-        <v>24.99</v>
+        <v>24.23</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3585</v>
+        <v>2.28707</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.28</v>
+        <v>35.54</v>
       </c>
       <c r="D18" t="n">
-        <v>19.02</v>
+        <v>51.29</v>
       </c>
       <c r="E18" t="n">
-        <v>10.07</v>
+        <v>44.32</v>
       </c>
       <c r="F18" t="n">
-        <v>0.21357</v>
+        <v>1.98244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>35.54</v>
+        <v>123.39</v>
       </c>
       <c r="D19" t="n">
-        <v>50.87</v>
+        <v>137.82</v>
       </c>
       <c r="E19" t="n">
-        <v>43.13</v>
+        <v>11.69</v>
       </c>
       <c r="F19" t="n">
-        <v>1.94244</v>
+        <v>1.38289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PPC</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26.51</v>
+        <v>63.54</v>
       </c>
       <c r="D20" t="n">
-        <v>30.48</v>
+        <v>70.34</v>
       </c>
       <c r="E20" t="n">
-        <v>14.98</v>
+        <v>10.7</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.01849</v>
+        <v>0.02608</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>123.39</v>
+        <v>155.62</v>
       </c>
       <c r="D21" t="n">
-        <v>137.67</v>
+        <v>163.78</v>
       </c>
       <c r="E21" t="n">
-        <v>11.57</v>
+        <v>5.24</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3686</v>
+        <v>-1.00319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>63.54</v>
+        <v>60.35</v>
       </c>
       <c r="D22" t="n">
-        <v>69.95</v>
+        <v>97.42</v>
       </c>
       <c r="E22" t="n">
-        <v>10.09</v>
+        <v>61.43</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.01106</v>
+        <v>1.96052</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>FIGR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>155.62</v>
+        <v>24.91</v>
       </c>
       <c r="D23" t="n">
-        <v>164.02</v>
+        <v>35.65</v>
       </c>
       <c r="E23" t="n">
-        <v>5.4</v>
+        <v>43.12</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.98034</v>
+        <v>0.36343</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>60.35</v>
+        <v>205.48</v>
       </c>
       <c r="D24" t="n">
-        <v>96.83</v>
+        <v>249.99</v>
       </c>
       <c r="E24" t="n">
-        <v>60.45</v>
+        <v>21.66</v>
       </c>
       <c r="F24" t="n">
-        <v>1.90433</v>
+        <v>1.24005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FIGR</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.91</v>
+        <v>7.81</v>
       </c>
       <c r="D25" t="n">
-        <v>36.38</v>
+        <v>10.87</v>
       </c>
       <c r="E25" t="n">
-        <v>46.05</v>
+        <v>39.18</v>
       </c>
       <c r="F25" t="n">
-        <v>0.43295</v>
+        <v>0.04366</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>205.48</v>
+        <v>298.32</v>
       </c>
       <c r="D26" t="n">
-        <v>248.66</v>
+        <v>358.97</v>
       </c>
       <c r="E26" t="n">
-        <v>21.01</v>
+        <v>20.33</v>
       </c>
       <c r="F26" t="n">
-        <v>1.11338</v>
+        <v>3.38165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.81</v>
+        <v>29.31</v>
       </c>
       <c r="D27" t="n">
-        <v>10.99</v>
+        <v>43.17</v>
       </c>
       <c r="E27" t="n">
-        <v>40.78</v>
+        <v>47.29</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05557</v>
+        <v>0.92178</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1084,142 +1084,142 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29.31</v>
+        <v>41.55</v>
       </c>
       <c r="D28" t="n">
-        <v>43.86</v>
+        <v>62.21</v>
       </c>
       <c r="E28" t="n">
-        <v>49.64</v>
+        <v>49.72</v>
       </c>
       <c r="F28" t="n">
-        <v>0.98749</v>
+        <v>-0.39774</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>41.55</v>
+        <v>25.28</v>
       </c>
       <c r="D29" t="n">
-        <v>62.37</v>
+        <v>28.1</v>
       </c>
       <c r="E29" t="n">
-        <v>50.11</v>
+        <v>11.16</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3825</v>
+        <v>-0.01151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13.93</v>
+        <v>11.03</v>
       </c>
       <c r="D30" t="n">
-        <v>19.92</v>
+        <v>12.72</v>
       </c>
       <c r="E30" t="n">
-        <v>42.96</v>
+        <v>15.32</v>
       </c>
       <c r="F30" t="n">
-        <v>0.15845</v>
+        <v>-0.09100999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>298.32</v>
+        <v>332.02</v>
       </c>
       <c r="D31" t="n">
-        <v>362.45</v>
+        <v>377.94</v>
       </c>
       <c r="E31" t="n">
-        <v>21.5</v>
+        <v>13.83</v>
       </c>
       <c r="F31" t="n">
-        <v>3.71261</v>
+        <v>-2.21821</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25.28</v>
+        <v>179.43</v>
       </c>
       <c r="D32" t="n">
-        <v>28.13</v>
+        <v>193.72</v>
       </c>
       <c r="E32" t="n">
-        <v>11.27</v>
+        <v>7.96</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.00865</v>
+        <v>0.57955</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11.03</v>
+        <v>27.14</v>
       </c>
       <c r="D33" t="n">
-        <v>12.74</v>
+        <v>31.52</v>
       </c>
       <c r="E33" t="n">
-        <v>15.5</v>
+        <v>16.14</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.08918</v>
+        <v>-0.35749</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1228,358 +1228,358 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.14</v>
+        <v>146.38</v>
       </c>
       <c r="D34" t="n">
-        <v>31.49</v>
+        <v>218.28</v>
       </c>
       <c r="E34" t="n">
-        <v>16.03</v>
+        <v>49.12</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.36035</v>
+        <v>0.00649</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>146.38</v>
+        <v>25.99</v>
       </c>
       <c r="D35" t="n">
-        <v>218.02</v>
+        <v>38.71</v>
       </c>
       <c r="E35" t="n">
         <v>48.94</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.01827</v>
+        <v>0.54466</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>179.43</v>
+        <v>205.77</v>
       </c>
       <c r="D36" t="n">
-        <v>196.03</v>
+        <v>249.09</v>
       </c>
       <c r="E36" t="n">
-        <v>9.25</v>
+        <v>21.05</v>
       </c>
       <c r="F36" t="n">
-        <v>0.79955</v>
+        <v>2.72288</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>332.02</v>
+        <v>440.76</v>
       </c>
       <c r="D37" t="n">
-        <v>376.45</v>
+        <v>637.16</v>
       </c>
       <c r="E37" t="n">
-        <v>13.38</v>
+        <v>44.56</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.36011</v>
+        <v>1.42976</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>205.77</v>
+        <v>103.45</v>
       </c>
       <c r="D38" t="n">
-        <v>250.88</v>
+        <v>149.67</v>
       </c>
       <c r="E38" t="n">
-        <v>21.92</v>
+        <v>44.68</v>
       </c>
       <c r="F38" t="n">
-        <v>2.89335</v>
+        <v>1.89428</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>25.99</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>38.47</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>48</v>
+        <v>18.82</v>
       </c>
       <c r="F39" t="n">
-        <v>0.52133</v>
+        <v>-0.45827</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>440.76</v>
+        <v>198.14</v>
       </c>
       <c r="D40" t="n">
-        <v>641.51</v>
+        <v>261.67</v>
       </c>
       <c r="E40" t="n">
-        <v>45.55</v>
+        <v>32.06</v>
       </c>
       <c r="F40" t="n">
-        <v>1.84381</v>
+        <v>2.64766</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>67.59999999999999</v>
+        <v>41.44</v>
       </c>
       <c r="D41" t="n">
-        <v>80.75</v>
+        <v>45.25</v>
       </c>
       <c r="E41" t="n">
-        <v>19.45</v>
+        <v>9.19</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.41731</v>
+        <v>0.51531</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>103.45</v>
+        <v>510.39</v>
       </c>
       <c r="D42" t="n">
-        <v>150.51</v>
+        <v>652.39</v>
       </c>
       <c r="E42" t="n">
-        <v>45.49</v>
+        <v>27.82</v>
       </c>
       <c r="F42" t="n">
-        <v>1.97428</v>
+        <v>4.4847</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>198.14</v>
+        <v>5.04</v>
       </c>
       <c r="D43" t="n">
-        <v>262.93</v>
+        <v>5.95</v>
       </c>
       <c r="E43" t="n">
-        <v>32.7</v>
+        <v>18.06</v>
       </c>
       <c r="F43" t="n">
-        <v>2.76814</v>
+        <v>0.05247</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>41.44</v>
+        <v>176.25</v>
       </c>
       <c r="D44" t="n">
-        <v>45.24</v>
+        <v>249.59</v>
       </c>
       <c r="E44" t="n">
-        <v>9.16</v>
+        <v>41.61</v>
       </c>
       <c r="F44" t="n">
-        <v>0.51388</v>
+        <v>0.95658</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RRC</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35.49</v>
+        <v>20.87</v>
       </c>
       <c r="D45" t="n">
-        <v>41.4</v>
+        <v>23.47</v>
       </c>
       <c r="E45" t="n">
-        <v>16.64</v>
+        <v>12.46</v>
       </c>
       <c r="F45" t="n">
-        <v>0.13101</v>
+        <v>0.00191</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>510.39</v>
+        <v>40.48</v>
       </c>
       <c r="D46" t="n">
-        <v>662.61</v>
+        <v>44.64</v>
       </c>
       <c r="E46" t="n">
-        <v>29.82</v>
+        <v>10.28</v>
       </c>
       <c r="F46" t="n">
-        <v>5.45803</v>
+        <v>0.1977</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5.04</v>
+        <v>24.36</v>
       </c>
       <c r="D47" t="n">
-        <v>5.92</v>
+        <v>33.27</v>
       </c>
       <c r="E47" t="n">
-        <v>17.46</v>
+        <v>36.58</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04961</v>
+        <v>0.5132100000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>176.25</v>
+        <v>31.45</v>
       </c>
       <c r="D48" t="n">
-        <v>250.78</v>
+        <v>36.65</v>
       </c>
       <c r="E48" t="n">
-        <v>42.29</v>
+        <v>16.53</v>
       </c>
       <c r="F48" t="n">
-        <v>1.06991</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1588,118 +1588,118 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>31.45</v>
+        <v>162.11</v>
       </c>
       <c r="D49" t="n">
-        <v>36.81</v>
+        <v>176.94</v>
       </c>
       <c r="E49" t="n">
-        <v>17.03</v>
+        <v>9.15</v>
       </c>
       <c r="F49" t="n">
-        <v>0.00077</v>
+        <v>0.35777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>162.11</v>
+        <v>15.99</v>
       </c>
       <c r="D50" t="n">
-        <v>177.23</v>
+        <v>21.15</v>
       </c>
       <c r="E50" t="n">
-        <v>9.33</v>
+        <v>32.27</v>
       </c>
       <c r="F50" t="n">
-        <v>0.38538</v>
+        <v>0.63574</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20.87</v>
+        <v>14.49</v>
       </c>
       <c r="D51" t="n">
-        <v>23.47</v>
+        <v>19.07</v>
       </c>
       <c r="E51" t="n">
-        <v>12.43</v>
+        <v>31.61</v>
       </c>
       <c r="F51" t="n">
-        <v>0.00143</v>
+        <v>0.58389</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>24.36</v>
+        <v>38.92</v>
       </c>
       <c r="D52" t="n">
-        <v>33.49</v>
+        <v>50.32</v>
       </c>
       <c r="E52" t="n">
-        <v>37.5</v>
+        <v>29.29</v>
       </c>
       <c r="F52" t="n">
-        <v>0.53464</v>
+        <v>0.31609</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>40.48</v>
+        <v>104.89</v>
       </c>
       <c r="D53" t="n">
-        <v>45.24</v>
+        <v>121.23</v>
       </c>
       <c r="E53" t="n">
-        <v>11.76</v>
+        <v>15.58</v>
       </c>
       <c r="F53" t="n">
-        <v>0.25484</v>
+        <v>2.10701</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17.93</v>
+        <v>40.25</v>
       </c>
       <c r="D54" t="n">
-        <v>24.06</v>
+        <v>49.73</v>
       </c>
       <c r="E54" t="n">
-        <v>34.16</v>
+        <v>23.55</v>
       </c>
       <c r="F54" t="n">
-        <v>0.31676</v>
+        <v>0.77667</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>41.99</v>
+        <v>51.98</v>
       </c>
       <c r="D55" t="n">
-        <v>51.27</v>
+        <v>65.36</v>
       </c>
       <c r="E55" t="n">
-        <v>22.1</v>
+        <v>25.74</v>
       </c>
       <c r="F55" t="n">
-        <v>0.37872</v>
+        <v>-0.02228</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>20.48</v>
+        <v>17.26</v>
       </c>
       <c r="D56" t="n">
-        <v>26.41</v>
+        <v>19.97</v>
       </c>
       <c r="E56" t="n">
-        <v>28.96</v>
+        <v>15.7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.18272</v>
+        <v>0.16925</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38.92</v>
+        <v>53.57</v>
       </c>
       <c r="D57" t="n">
-        <v>50.64</v>
+        <v>68.72</v>
       </c>
       <c r="E57" t="n">
-        <v>30.11</v>
+        <v>28.28</v>
       </c>
       <c r="F57" t="n">
-        <v>0.34657</v>
+        <v>0.74953</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>53.57</v>
+        <v>45.57</v>
       </c>
       <c r="D58" t="n">
-        <v>69.69</v>
+        <v>55.4</v>
       </c>
       <c r="E58" t="n">
-        <v>30.09</v>
+        <v>21.57</v>
       </c>
       <c r="F58" t="n">
-        <v>0.84191</v>
+        <v>0.48559</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>31.87</v>
+        <v>13.01</v>
       </c>
       <c r="D59" t="n">
-        <v>45.52</v>
+        <v>17.53</v>
       </c>
       <c r="E59" t="n">
-        <v>42.83</v>
+        <v>34.74</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9454</v>
+        <v>0.37919</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1852,22 +1852,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>45.57</v>
+        <v>110.99</v>
       </c>
       <c r="D60" t="n">
-        <v>55.31</v>
+        <v>131.83</v>
       </c>
       <c r="E60" t="n">
-        <v>21.37</v>
+        <v>18.78</v>
       </c>
       <c r="F60" t="n">
-        <v>0.47701</v>
+        <v>-0.18184</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>74.8</v>
+        <v>17.93</v>
       </c>
       <c r="D61" t="n">
-        <v>91.83</v>
+        <v>23.76</v>
       </c>
       <c r="E61" t="n">
-        <v>22.77</v>
+        <v>32.52</v>
       </c>
       <c r="F61" t="n">
-        <v>1.09417</v>
+        <v>0.28866</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>104.89</v>
+        <v>171.96</v>
       </c>
       <c r="D62" t="n">
-        <v>121.95</v>
+        <v>205.72</v>
       </c>
       <c r="E62" t="n">
-        <v>16.26</v>
+        <v>19.63</v>
       </c>
       <c r="F62" t="n">
-        <v>2.17558</v>
+        <v>1.19691</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>14.49</v>
+        <v>36.15</v>
       </c>
       <c r="D63" t="n">
-        <v>19.02</v>
+        <v>45.93</v>
       </c>
       <c r="E63" t="n">
-        <v>31.3</v>
+        <v>27.05</v>
       </c>
       <c r="F63" t="n">
-        <v>0.57961</v>
+        <v>0.8426</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>15.99</v>
+        <v>47.94</v>
       </c>
       <c r="D64" t="n">
-        <v>21.11</v>
+        <v>61.78</v>
       </c>
       <c r="E64" t="n">
-        <v>32.05</v>
+        <v>28.87</v>
       </c>
       <c r="F64" t="n">
-        <v>0.63241</v>
+        <v>0.67977</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51.98</v>
+        <v>74.8</v>
       </c>
       <c r="D65" t="n">
-        <v>65.34</v>
+        <v>91.14</v>
       </c>
       <c r="E65" t="n">
-        <v>25.7</v>
+        <v>21.84</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.02418</v>
+        <v>1.02845</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>13.01</v>
+        <v>165.69</v>
       </c>
       <c r="D66" t="n">
-        <v>17.58</v>
+        <v>212.17</v>
       </c>
       <c r="E66" t="n">
-        <v>35.09</v>
+        <v>28.05</v>
       </c>
       <c r="F66" t="n">
-        <v>0.38348</v>
+        <v>3.14062</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,22 +2020,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>36.15</v>
+        <v>103.22</v>
       </c>
       <c r="D67" t="n">
-        <v>46.08</v>
+        <v>136.67</v>
       </c>
       <c r="E67" t="n">
-        <v>27.48</v>
+        <v>32.41</v>
       </c>
       <c r="F67" t="n">
-        <v>0.85736</v>
+        <v>2.02987</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2044,22 +2044,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>103.22</v>
+        <v>41.99</v>
       </c>
       <c r="D68" t="n">
-        <v>137.76</v>
+        <v>51.29</v>
       </c>
       <c r="E68" t="n">
-        <v>33.46</v>
+        <v>22.15</v>
       </c>
       <c r="F68" t="n">
-        <v>2.13368</v>
+        <v>0.38063</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>110.99</v>
+        <v>20.48</v>
       </c>
       <c r="D69" t="n">
-        <v>133.22</v>
+        <v>26.51</v>
       </c>
       <c r="E69" t="n">
-        <v>20.03</v>
+        <v>29.44</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.04946</v>
+        <v>0.19225</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2092,118 +2092,118 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>165.69</v>
+        <v>31.87</v>
       </c>
       <c r="D70" t="n">
-        <v>213.66</v>
+        <v>45.03</v>
       </c>
       <c r="E70" t="n">
-        <v>28.95</v>
+        <v>41.29</v>
       </c>
       <c r="F70" t="n">
-        <v>3.28253</v>
+        <v>0.89874</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>171.96</v>
+        <v>124.44</v>
       </c>
       <c r="D71" t="n">
-        <v>207.44</v>
+        <v>195</v>
       </c>
       <c r="E71" t="n">
-        <v>20.63</v>
+        <v>56.7</v>
       </c>
       <c r="F71" t="n">
-        <v>1.36072</v>
+        <v>0.72958</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17.26</v>
+        <v>55.53</v>
       </c>
       <c r="D72" t="n">
-        <v>20.03</v>
+        <v>60.91</v>
       </c>
       <c r="E72" t="n">
-        <v>16.08</v>
+        <v>9.69</v>
       </c>
       <c r="F72" t="n">
-        <v>0.17544</v>
+        <v>0.22128</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>47.94</v>
+        <v>62.05</v>
       </c>
       <c r="D73" t="n">
-        <v>62.06</v>
+        <v>81.22</v>
       </c>
       <c r="E73" t="n">
-        <v>29.44</v>
+        <v>30.89</v>
       </c>
       <c r="F73" t="n">
-        <v>0.70597</v>
+        <v>-0.5008899999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>40.25</v>
+        <v>13.31</v>
       </c>
       <c r="D74" t="n">
-        <v>50.08</v>
+        <v>25.76</v>
       </c>
       <c r="E74" t="n">
-        <v>24.43</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>0.81048</v>
+        <v>0.71191</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2212,22 +2212,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>167.73</v>
+        <v>13.43</v>
       </c>
       <c r="D75" t="n">
-        <v>183.91</v>
+        <v>15.26</v>
       </c>
       <c r="E75" t="n">
-        <v>9.65</v>
+        <v>13.63</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.48382</v>
+        <v>0.08839</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2236,22 +2236,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>124.44</v>
+        <v>38.73</v>
       </c>
       <c r="D76" t="n">
-        <v>193.77</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>55.71</v>
+        <v>65.5</v>
       </c>
       <c r="F76" t="n">
-        <v>0.61244</v>
+        <v>-0.10866</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2260,118 +2260,118 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>55.53</v>
+        <v>167.73</v>
       </c>
       <c r="D77" t="n">
-        <v>60.83</v>
+        <v>182.9</v>
       </c>
       <c r="E77" t="n">
-        <v>9.539999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>0.21319</v>
+        <v>-0.58001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>38.73</v>
+        <v>218.58</v>
       </c>
       <c r="D78" t="n">
-        <v>63.96</v>
+        <v>280.46</v>
       </c>
       <c r="E78" t="n">
-        <v>65.14</v>
+        <v>28.31</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.12199</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>62.05</v>
+        <v>122.91</v>
       </c>
       <c r="D79" t="n">
-        <v>81.13</v>
+        <v>157.75</v>
       </c>
       <c r="E79" t="n">
-        <v>30.75</v>
+        <v>28.35</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.50947</v>
+        <v>-0.37771</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>13.43</v>
+        <v>7.67</v>
       </c>
       <c r="D80" t="n">
-        <v>15.27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>13.66</v>
+        <v>19.95</v>
       </c>
       <c r="F80" t="n">
-        <v>0.08887</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13.31</v>
+        <v>135.44</v>
       </c>
       <c r="D81" t="n">
-        <v>25.84</v>
+        <v>174.39</v>
       </c>
       <c r="E81" t="n">
-        <v>94.18000000000001</v>
+        <v>28.76</v>
       </c>
       <c r="F81" t="n">
-        <v>0.72</v>
+        <v>-1.62645</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2380,94 +2380,94 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7.67</v>
+        <v>136.06</v>
       </c>
       <c r="D82" t="n">
-        <v>9.220000000000001</v>
+        <v>165.08</v>
       </c>
       <c r="E82" t="n">
-        <v>20.14</v>
+        <v>21.33</v>
       </c>
       <c r="F82" t="n">
-        <v>0.17852</v>
+        <v>1.65744</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>135.44</v>
+        <v>18.94</v>
       </c>
       <c r="D83" t="n">
-        <v>174.78</v>
+        <v>23.74</v>
       </c>
       <c r="E83" t="n">
-        <v>29.04</v>
+        <v>25.34</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.58976</v>
+        <v>0.19609</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>218.58</v>
+        <v>31.03</v>
       </c>
       <c r="D84" t="n">
-        <v>279.8</v>
+        <v>44.54</v>
       </c>
       <c r="E84" t="n">
-        <v>28.01</v>
+        <v>43.54</v>
       </c>
       <c r="F84" t="n">
-        <v>0.16684</v>
+        <v>0.9863499999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>136.06</v>
+        <v>56.4</v>
       </c>
       <c r="D85" t="n">
-        <v>165.7</v>
+        <v>80.81</v>
       </c>
       <c r="E85" t="n">
-        <v>21.79</v>
+        <v>43.28</v>
       </c>
       <c r="F85" t="n">
-        <v>1.71684</v>
+        <v>1.6696</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2476,22 +2476,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>18.94</v>
+        <v>82.31</v>
       </c>
       <c r="D86" t="n">
-        <v>23.66</v>
+        <v>136.94</v>
       </c>
       <c r="E86" t="n">
-        <v>24.92</v>
+        <v>66.37</v>
       </c>
       <c r="F86" t="n">
-        <v>0.18847</v>
+        <v>3.45518</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2500,22 +2500,22 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>76.53</v>
+        <v>39.54</v>
       </c>
       <c r="D87" t="n">
-        <v>96.61</v>
+        <v>51.41</v>
       </c>
       <c r="E87" t="n">
-        <v>26.24</v>
+        <v>30.02</v>
       </c>
       <c r="F87" t="n">
-        <v>1.46769</v>
+        <v>0.11249</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2524,94 +2524,94 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>31.03</v>
+        <v>76.53</v>
       </c>
       <c r="D88" t="n">
-        <v>44.7</v>
+        <v>96.45</v>
       </c>
       <c r="E88" t="n">
-        <v>44.05</v>
+        <v>26.03</v>
       </c>
       <c r="F88" t="n">
-        <v>1.00159</v>
+        <v>1.45245</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>56.4</v>
+        <v>107.27</v>
       </c>
       <c r="D89" t="n">
-        <v>81.34999999999999</v>
+        <v>173.31</v>
       </c>
       <c r="E89" t="n">
-        <v>44.24</v>
+        <v>61.56</v>
       </c>
       <c r="F89" t="n">
-        <v>1.72103</v>
+        <v>-1.05801</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>39.54</v>
+        <v>59.71</v>
       </c>
       <c r="D90" t="n">
-        <v>51.29</v>
+        <v>79.11</v>
       </c>
       <c r="E90" t="n">
-        <v>29.72</v>
+        <v>32.49</v>
       </c>
       <c r="F90" t="n">
-        <v>0.10106</v>
+        <v>0.59687</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>EDU</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>82.31</v>
+        <v>44.44</v>
       </c>
       <c r="D91" t="n">
-        <v>136.75</v>
+        <v>56.82</v>
       </c>
       <c r="E91" t="n">
-        <v>66.14</v>
+        <v>27.86</v>
       </c>
       <c r="F91" t="n">
-        <v>3.43709</v>
+        <v>-0.38143</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EDU</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2620,22 +2620,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>44.44</v>
+        <v>255.07</v>
       </c>
       <c r="D92" t="n">
-        <v>57</v>
+        <v>339.15</v>
       </c>
       <c r="E92" t="n">
-        <v>28.26</v>
+        <v>32.96</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.36429</v>
+        <v>-6.00233</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2644,16 +2644,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>59.71</v>
+        <v>19.32</v>
       </c>
       <c r="D93" t="n">
-        <v>79.31999999999999</v>
+        <v>24.47</v>
       </c>
       <c r="E93" t="n">
-        <v>32.84</v>
+        <v>26.66</v>
       </c>
       <c r="F93" t="n">
-        <v>0.61687</v>
+        <v>-0.0342</v>
       </c>
     </row>
     <row r="94">
@@ -2671,19 +2671,19 @@
         <v>166.5</v>
       </c>
       <c r="D94" t="n">
-        <v>197.05</v>
+        <v>197.56</v>
       </c>
       <c r="E94" t="n">
-        <v>18.35</v>
+        <v>18.65</v>
       </c>
       <c r="F94" t="n">
-        <v>0.62078</v>
+        <v>0.66935</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2692,22 +2692,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>352.83</v>
+        <v>42.46</v>
       </c>
       <c r="D95" t="n">
-        <v>509.32</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>44.35</v>
+        <v>64.3</v>
       </c>
       <c r="F95" t="n">
-        <v>2.46973</v>
+        <v>1.2992</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2716,22 +2716,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>19.32</v>
+        <v>170.28</v>
       </c>
       <c r="D96" t="n">
-        <v>24.62</v>
+        <v>250.61</v>
       </c>
       <c r="E96" t="n">
-        <v>27.46</v>
+        <v>47.18</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.01943</v>
+        <v>-2.75775</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2740,22 +2740,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>255.07</v>
+        <v>142.52</v>
       </c>
       <c r="D97" t="n">
-        <v>338.24</v>
+        <v>191.45</v>
       </c>
       <c r="E97" t="n">
-        <v>32.61</v>
+        <v>34.33</v>
       </c>
       <c r="F97" t="n">
-        <v>-6.08852</v>
+        <v>1.43195</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2764,22 +2764,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>107.27</v>
+        <v>352.83</v>
       </c>
       <c r="D98" t="n">
-        <v>173.37</v>
+        <v>505.41</v>
       </c>
       <c r="E98" t="n">
-        <v>61.62</v>
+        <v>43.24</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.05229</v>
+        <v>2.09735</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2788,22 +2788,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>142.52</v>
+        <v>136.68</v>
       </c>
       <c r="D99" t="n">
-        <v>190.97</v>
+        <v>153.4</v>
       </c>
       <c r="E99" t="n">
-        <v>34</v>
+        <v>12.23</v>
       </c>
       <c r="F99" t="n">
-        <v>1.38624</v>
+        <v>-2.51046</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2812,16 +2812,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>170.28</v>
+        <v>49.87</v>
       </c>
       <c r="D100" t="n">
-        <v>249.48</v>
+        <v>63.17</v>
       </c>
       <c r="E100" t="n">
-        <v>46.51</v>
+        <v>26.67</v>
       </c>
       <c r="F100" t="n">
-        <v>-2.86537</v>
+        <v>0.2007</v>
       </c>
     </row>
     <row r="101">
@@ -2839,259 +2839,259 @@
         <v>44.39</v>
       </c>
       <c r="D101" t="n">
-        <v>60.69</v>
+        <v>61.14</v>
       </c>
       <c r="E101" t="n">
-        <v>36.72</v>
+        <v>37.73</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.10213</v>
+        <v>-0.05927</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>49.87</v>
+        <v>10.51</v>
       </c>
       <c r="D102" t="n">
-        <v>63.99</v>
+        <v>15.27</v>
       </c>
       <c r="E102" t="n">
-        <v>28.3</v>
+        <v>45.29</v>
       </c>
       <c r="F102" t="n">
-        <v>0.27833</v>
+        <v>0.40451</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>42.46</v>
+        <v>62.12</v>
       </c>
       <c r="D103" t="n">
-        <v>69.61</v>
+        <v>79.13</v>
       </c>
       <c r="E103" t="n">
-        <v>63.94</v>
+        <v>27.38</v>
       </c>
       <c r="F103" t="n">
-        <v>1.28494</v>
+        <v>0.8058999999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>100</v>
+        <v>60.37</v>
       </c>
       <c r="D104" t="n">
-        <v>133.4</v>
+        <v>77</v>
       </c>
       <c r="E104" t="n">
-        <v>33.4</v>
+        <v>27.55</v>
       </c>
       <c r="F104" t="n">
-        <v>-1.54672</v>
+        <v>1.31187</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>136.68</v>
+        <v>102.17</v>
       </c>
       <c r="D105" t="n">
-        <v>155.53</v>
+        <v>131.24</v>
       </c>
       <c r="E105" t="n">
-        <v>13.79</v>
+        <v>28.45</v>
       </c>
       <c r="F105" t="n">
-        <v>-2.3076</v>
+        <v>1.86006</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>36.09</v>
+        <v>48.79</v>
       </c>
       <c r="D106" t="n">
-        <v>38.96</v>
+        <v>68.53</v>
       </c>
       <c r="E106" t="n">
-        <v>7.95</v>
+        <v>40.46</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1313</v>
+        <v>-0.01588</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>60.37</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D107" t="n">
-        <v>77.15000000000001</v>
+        <v>123.61</v>
       </c>
       <c r="E107" t="n">
-        <v>27.8</v>
+        <v>62.56</v>
       </c>
       <c r="F107" t="n">
-        <v>1.32615</v>
+        <v>2.41344</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10.51</v>
+        <v>30.83</v>
       </c>
       <c r="D108" t="n">
-        <v>15.58</v>
+        <v>35.72</v>
       </c>
       <c r="E108" t="n">
-        <v>48.24</v>
+        <v>15.86</v>
       </c>
       <c r="F108" t="n">
-        <v>0.43404</v>
+        <v>-0.35242</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>62.12</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D109" t="n">
-        <v>78.76000000000001</v>
+        <v>95.31</v>
       </c>
       <c r="E109" t="n">
-        <v>26.79</v>
+        <v>13.71</v>
       </c>
       <c r="F109" t="n">
-        <v>0.77066</v>
+        <v>-0.43033</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>102.17</v>
+        <v>275.27</v>
       </c>
       <c r="D110" t="n">
-        <v>132.16</v>
+        <v>359.54</v>
       </c>
       <c r="E110" t="n">
-        <v>29.35</v>
+        <v>30.61</v>
       </c>
       <c r="F110" t="n">
-        <v>1.94768</v>
+        <v>-2.74832</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>48.79</v>
+        <v>125.73</v>
       </c>
       <c r="D111" t="n">
-        <v>68.23</v>
+        <v>197.07</v>
       </c>
       <c r="E111" t="n">
-        <v>39.84</v>
+        <v>56.74</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.04445</v>
+        <v>-1.80321</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3100,22 +3100,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>76.04000000000001</v>
+        <v>150.12</v>
       </c>
       <c r="D112" t="n">
-        <v>125.37</v>
+        <v>259.43</v>
       </c>
       <c r="E112" t="n">
-        <v>64.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="F112" t="n">
-        <v>2.58105</v>
+        <v>6.48113</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3124,22 +3124,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>150.12</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D113" t="n">
-        <v>258.91</v>
+        <v>104.47</v>
       </c>
       <c r="E113" t="n">
-        <v>72.47</v>
+        <v>39.31</v>
       </c>
       <c r="F113" t="n">
-        <v>6.43159</v>
+        <v>0.40712</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3148,22 +3148,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>275.27</v>
+        <v>140.71</v>
       </c>
       <c r="D114" t="n">
-        <v>360.62</v>
+        <v>182.91</v>
       </c>
       <c r="E114" t="n">
-        <v>31.01</v>
+        <v>29.99</v>
       </c>
       <c r="F114" t="n">
-        <v>-2.64547</v>
+        <v>-1.36471</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3172,22 +3172,22 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>47.18</v>
+        <v>76.55</v>
       </c>
       <c r="D115" t="n">
-        <v>52.18</v>
+        <v>105.82</v>
       </c>
       <c r="E115" t="n">
-        <v>10.6</v>
+        <v>38.23</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.64834</v>
+        <v>-1.58394</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3196,286 +3196,286 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>30.83</v>
+        <v>123.42</v>
       </c>
       <c r="D116" t="n">
-        <v>35.71</v>
+        <v>164.55</v>
       </c>
       <c r="E116" t="n">
-        <v>15.83</v>
+        <v>33.33</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.35337</v>
+        <v>-0.65884</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>74.98999999999999</v>
+        <v>141.17</v>
       </c>
       <c r="D117" t="n">
-        <v>104.46</v>
+        <v>173.25</v>
       </c>
       <c r="E117" t="n">
-        <v>39.3</v>
+        <v>22.72</v>
       </c>
       <c r="F117" t="n">
-        <v>0.40617</v>
+        <v>1.14864</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>76.55</v>
+        <v>61.28</v>
       </c>
       <c r="D118" t="n">
-        <v>105.91</v>
+        <v>72.91</v>
       </c>
       <c r="E118" t="n">
-        <v>38.35</v>
+        <v>18.98</v>
       </c>
       <c r="F118" t="n">
-        <v>-1.57489</v>
+        <v>-0.98211</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>83.81999999999999</v>
+        <v>48.87</v>
       </c>
       <c r="D119" t="n">
-        <v>94.79000000000001</v>
+        <v>58.74</v>
       </c>
       <c r="E119" t="n">
-        <v>13.09</v>
+        <v>20.2</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.47985</v>
+        <v>-0.40747</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>123.42</v>
+        <v>450.75</v>
       </c>
       <c r="D120" t="n">
-        <v>167.53</v>
+        <v>548.65</v>
       </c>
       <c r="E120" t="n">
-        <v>35.74</v>
+        <v>21.72</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.37504</v>
+        <v>2.41907</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>125.73</v>
+        <v>32.47</v>
       </c>
       <c r="D121" t="n">
-        <v>194.2</v>
+        <v>38.43</v>
       </c>
       <c r="E121" t="n">
-        <v>54.46</v>
+        <v>18.36</v>
       </c>
       <c r="F121" t="n">
-        <v>-2.07654</v>
+        <v>0.22774</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ENSG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>33.22</v>
+        <v>147.13</v>
       </c>
       <c r="D122" t="n">
-        <v>38.56</v>
+        <v>174.93</v>
       </c>
       <c r="E122" t="n">
-        <v>16.06</v>
+        <v>18.89</v>
       </c>
       <c r="F122" t="n">
-        <v>0.21234</v>
+        <v>-0.59992</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>61.28</v>
+        <v>62.47</v>
       </c>
       <c r="D123" t="n">
-        <v>73.11</v>
+        <v>90.19</v>
       </c>
       <c r="E123" t="n">
-        <v>19.3</v>
+        <v>44.37</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.96306</v>
+        <v>-0.65359</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>450.75</v>
+        <v>53.82</v>
       </c>
       <c r="D124" t="n">
-        <v>550.99</v>
+        <v>75</v>
       </c>
       <c r="E124" t="n">
-        <v>22.24</v>
+        <v>39.35</v>
       </c>
       <c r="F124" t="n">
-        <v>2.6424</v>
+        <v>0.53725</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>48.87</v>
+        <v>121.48</v>
       </c>
       <c r="D125" t="n">
-        <v>58.86</v>
+        <v>146.41</v>
       </c>
       <c r="E125" t="n">
-        <v>20.44</v>
+        <v>20.52</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.39604</v>
+        <v>0.04863</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>32.47</v>
+        <v>2.86</v>
       </c>
       <c r="D126" t="n">
-        <v>38.12</v>
+        <v>3.18</v>
       </c>
       <c r="E126" t="n">
-        <v>17.39</v>
+        <v>11.19</v>
       </c>
       <c r="F126" t="n">
-        <v>0.19798</v>
+        <v>0.02543</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>147.13</v>
+        <v>19.82</v>
       </c>
       <c r="D127" t="n">
-        <v>174.75</v>
+        <v>25.05</v>
       </c>
       <c r="E127" t="n">
-        <v>18.77</v>
+        <v>26.39</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.6170600000000001</v>
+        <v>0.40053</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3484,22 +3484,22 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>121.48</v>
+        <v>14.94</v>
       </c>
       <c r="D128" t="n">
-        <v>145.79</v>
+        <v>19.59</v>
       </c>
       <c r="E128" t="n">
-        <v>20.01</v>
+        <v>31.16</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.01089</v>
+        <v>0.52114</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3508,22 +3508,22 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2.86</v>
+        <v>16.44</v>
       </c>
       <c r="D129" t="n">
-        <v>3.15</v>
+        <v>33.97</v>
       </c>
       <c r="E129" t="n">
-        <v>10.31</v>
+        <v>106.63</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02305</v>
+        <v>0.60034</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3532,232 +3532,232 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>16.44</v>
+        <v>91.88</v>
       </c>
       <c r="D130" t="n">
-        <v>34.26</v>
+        <v>125.3</v>
       </c>
       <c r="E130" t="n">
-        <v>108.39</v>
+        <v>36.37</v>
       </c>
       <c r="F130" t="n">
-        <v>0.62796</v>
+        <v>1.50067</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>14.94</v>
+        <v>361.32</v>
       </c>
       <c r="D131" t="n">
-        <v>19.49</v>
+        <v>425.49</v>
       </c>
       <c r="E131" t="n">
-        <v>30.42</v>
+        <v>17.76</v>
       </c>
       <c r="F131" t="n">
-        <v>0.51066</v>
+        <v>4.42632</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>53.82</v>
+        <v>205.81</v>
       </c>
       <c r="D132" t="n">
-        <v>74.90000000000001</v>
+        <v>264.92</v>
       </c>
       <c r="E132" t="n">
-        <v>39.17</v>
+        <v>28.72</v>
       </c>
       <c r="F132" t="n">
-        <v>0.52773</v>
+        <v>1.32952</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>19.82</v>
+        <v>28.18</v>
       </c>
       <c r="D133" t="n">
-        <v>24.59</v>
+        <v>37.03</v>
       </c>
       <c r="E133" t="n">
-        <v>24.07</v>
+        <v>31.41</v>
       </c>
       <c r="F133" t="n">
-        <v>0.35672</v>
+        <v>-0.01107</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>91.88</v>
+        <v>43.67</v>
       </c>
       <c r="D134" t="n">
-        <v>126.09</v>
+        <v>47.34</v>
       </c>
       <c r="E134" t="n">
-        <v>37.23</v>
+        <v>8.4</v>
       </c>
       <c r="F134" t="n">
-        <v>1.5759</v>
+        <v>0.05503</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>361.32</v>
+        <v>161.37</v>
       </c>
       <c r="D135" t="n">
-        <v>421.09</v>
+        <v>264.51</v>
       </c>
       <c r="E135" t="n">
-        <v>16.54</v>
+        <v>63.92</v>
       </c>
       <c r="F135" t="n">
-        <v>4.00728</v>
+        <v>0.82511</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>205.81</v>
+        <v>55.05</v>
       </c>
       <c r="D136" t="n">
-        <v>262.04</v>
+        <v>63.57</v>
       </c>
       <c r="E136" t="n">
-        <v>27.32</v>
+        <v>15.48</v>
       </c>
       <c r="F136" t="n">
-        <v>1.05524</v>
+        <v>-0.4736</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>55.05</v>
+        <v>72.55</v>
       </c>
       <c r="D137" t="n">
-        <v>63.71</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>15.73</v>
+        <v>5.16</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.46026</v>
+        <v>-0.36496</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>43.67</v>
+        <v>195.11</v>
       </c>
       <c r="D138" t="n">
-        <v>47.34</v>
+        <v>249.05</v>
       </c>
       <c r="E138" t="n">
-        <v>8.4</v>
+        <v>27.65</v>
       </c>
       <c r="F138" t="n">
-        <v>0.05503</v>
+        <v>0.4172</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>28.18</v>
+        <v>15.03</v>
       </c>
       <c r="D139" t="n">
-        <v>36.99</v>
+        <v>18.6</v>
       </c>
       <c r="E139" t="n">
-        <v>31.28</v>
+        <v>23.75</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.01441</v>
+        <v>0.08944000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -3775,19 +3775,19 @@
         <v>140.19</v>
       </c>
       <c r="D140" t="n">
-        <v>146.2</v>
+        <v>146.13</v>
       </c>
       <c r="E140" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.38644</v>
+        <v>-0.3931</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3796,70 +3796,70 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>195.11</v>
+        <v>207.24</v>
       </c>
       <c r="D141" t="n">
-        <v>248.52</v>
+        <v>253.88</v>
       </c>
       <c r="E141" t="n">
-        <v>27.38</v>
+        <v>22.51</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3672</v>
+        <v>-2.67569</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>207.24</v>
+        <v>277.69</v>
       </c>
       <c r="D142" t="n">
-        <v>253.58</v>
+        <v>330.62</v>
       </c>
       <c r="E142" t="n">
-        <v>22.36</v>
+        <v>19.06</v>
       </c>
       <c r="F142" t="n">
-        <v>-2.70426</v>
+        <v>-0.14398</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>15.03</v>
+        <v>275.99</v>
       </c>
       <c r="D143" t="n">
-        <v>18.67</v>
+        <v>322.99</v>
       </c>
       <c r="E143" t="n">
-        <v>24.22</v>
+        <v>17.03</v>
       </c>
       <c r="F143" t="n">
-        <v>0.09611</v>
+        <v>1.92883</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3868,64 +3868,64 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>275.99</v>
+        <v>73.75</v>
       </c>
       <c r="D144" t="n">
-        <v>321.69</v>
+        <v>93.8</v>
       </c>
       <c r="E144" t="n">
-        <v>16.56</v>
+        <v>27.19</v>
       </c>
       <c r="F144" t="n">
-        <v>1.80502</v>
+        <v>0.31456</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>277.69</v>
+        <v>36.25</v>
       </c>
       <c r="D145" t="n">
-        <v>329.22</v>
+        <v>41.61</v>
       </c>
       <c r="E145" t="n">
-        <v>18.56</v>
+        <v>14.79</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.27732</v>
+        <v>0.22556</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>73.75</v>
+        <v>121.13</v>
       </c>
       <c r="D146" t="n">
-        <v>93.33</v>
+        <v>138.92</v>
       </c>
       <c r="E146" t="n">
-        <v>26.56</v>
+        <v>14.69</v>
       </c>
       <c r="F146" t="n">
-        <v>0.27025</v>
+        <v>0.41111</v>
       </c>
     </row>
     <row r="147">
@@ -3943,19 +3943,19 @@
         <v>9.85</v>
       </c>
       <c r="D147" t="n">
-        <v>13.84</v>
+        <v>13.75</v>
       </c>
       <c r="E147" t="n">
-        <v>40.51</v>
+        <v>39.59</v>
       </c>
       <c r="F147" t="n">
-        <v>0.52093</v>
+        <v>0.51236</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3964,22 +3964,22 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>132.79</v>
+        <v>309.78</v>
       </c>
       <c r="D148" t="n">
-        <v>163.34</v>
+        <v>341.85</v>
       </c>
       <c r="E148" t="n">
-        <v>23.01</v>
+        <v>10.35</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.13175</v>
+        <v>-1.13236</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3988,16 +3988,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>36.25</v>
+        <v>132.79</v>
       </c>
       <c r="D149" t="n">
-        <v>41.2</v>
+        <v>163.39</v>
       </c>
       <c r="E149" t="n">
-        <v>13.66</v>
+        <v>23.04</v>
       </c>
       <c r="F149" t="n">
-        <v>0.18651</v>
+        <v>-0.12699</v>
       </c>
     </row>
     <row r="150">
@@ -4015,13 +4015,13 @@
         <v>33.54</v>
       </c>
       <c r="D150" t="n">
-        <v>42.76</v>
+        <v>42.61</v>
       </c>
       <c r="E150" t="n">
-        <v>27.47</v>
+        <v>27.04</v>
       </c>
       <c r="F150" t="n">
-        <v>0.14827</v>
+        <v>0.13446</v>
       </c>
     </row>
     <row r="151">
@@ -4039,13 +4039,13 @@
         <v>63.54</v>
       </c>
       <c r="D151" t="n">
-        <v>70.17</v>
+        <v>70.87</v>
       </c>
       <c r="E151" t="n">
-        <v>10.43</v>
+        <v>11.54</v>
       </c>
       <c r="F151" t="n">
-        <v>0.20202</v>
+        <v>0.26916</v>
       </c>
     </row>
     <row r="152">
@@ -4063,13 +4063,13 @@
         <v>190.4</v>
       </c>
       <c r="D152" t="n">
-        <v>219.99</v>
+        <v>221.02</v>
       </c>
       <c r="E152" t="n">
-        <v>15.54</v>
+        <v>16.08</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.05678</v>
+        <v>0.04179</v>
       </c>
     </row>
     <row r="153">
@@ -4087,13 +4087,13 @@
         <v>250.75</v>
       </c>
       <c r="D153" t="n">
-        <v>344.15</v>
+        <v>340.38</v>
       </c>
       <c r="E153" t="n">
-        <v>37.25</v>
+        <v>35.74</v>
       </c>
       <c r="F153" t="n">
-        <v>4.2383</v>
+        <v>3.87926</v>
       </c>
     </row>
     <row r="154">
@@ -4111,19 +4111,19 @@
         <v>529.12</v>
       </c>
       <c r="D154" t="n">
-        <v>681.36</v>
+        <v>681.46</v>
       </c>
       <c r="E154" t="n">
-        <v>28.77</v>
+        <v>28.79</v>
       </c>
       <c r="F154" t="n">
-        <v>9.77603</v>
+        <v>9.785550000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>SGI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4132,22 +4132,22 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>57.4</v>
+        <v>61.49</v>
       </c>
       <c r="D155" t="n">
-        <v>104.27</v>
+        <v>68.12</v>
       </c>
       <c r="E155" t="n">
-        <v>81.66</v>
+        <v>10.78</v>
       </c>
       <c r="F155" t="n">
-        <v>0.16331</v>
+        <v>0.25125</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SGI</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>61.49</v>
+        <v>57.4</v>
       </c>
       <c r="D156" t="n">
-        <v>68.25</v>
+        <v>104.79</v>
       </c>
       <c r="E156" t="n">
-        <v>10.99</v>
+        <v>82.56</v>
       </c>
       <c r="F156" t="n">
-        <v>0.26315</v>
+        <v>0.21284</v>
       </c>
     </row>
     <row r="157">
@@ -4183,19 +4183,19 @@
         <v>49.67</v>
       </c>
       <c r="D157" t="n">
-        <v>66.65000000000001</v>
+        <v>66.41</v>
       </c>
       <c r="E157" t="n">
-        <v>34.19</v>
+        <v>33.7</v>
       </c>
       <c r="F157" t="n">
-        <v>0.06127</v>
+        <v>0.03841</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4204,22 +4204,22 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>438.34</v>
+        <v>186.61</v>
       </c>
       <c r="D158" t="n">
-        <v>611.7</v>
+        <v>237.89</v>
       </c>
       <c r="E158" t="n">
-        <v>39.55</v>
+        <v>27.48</v>
       </c>
       <c r="F158" t="n">
-        <v>0.31709</v>
+        <v>-1.00997</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4228,22 +4228,22 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>26.18</v>
+        <v>63.16</v>
       </c>
       <c r="D159" t="n">
-        <v>36.84</v>
+        <v>101.84</v>
       </c>
       <c r="E159" t="n">
-        <v>40.72</v>
+        <v>61.24</v>
       </c>
       <c r="F159" t="n">
-        <v>0.14738</v>
+        <v>1.43086</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4252,16 +4252,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>63.16</v>
+        <v>5563.62</v>
       </c>
       <c r="D160" t="n">
-        <v>101.5</v>
+        <v>6299.56</v>
       </c>
       <c r="E160" t="n">
-        <v>60.71</v>
+        <v>13.23</v>
       </c>
       <c r="F160" t="n">
-        <v>1.39896</v>
+        <v>-44.26965</v>
       </c>
     </row>
     <row r="161">
@@ -4279,1027 +4279,1027 @@
         <v>43.3</v>
       </c>
       <c r="D161" t="n">
-        <v>72.22</v>
+        <v>72.27</v>
       </c>
       <c r="E161" t="n">
-        <v>66.79000000000001</v>
+        <v>66.91</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.00476</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>163.43</v>
+        <v>73.42</v>
       </c>
       <c r="D162" t="n">
-        <v>200.51</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E162" t="n">
-        <v>22.69</v>
+        <v>20.83</v>
       </c>
       <c r="F162" t="n">
-        <v>0.60609</v>
+        <v>0.7728699999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>156.84</v>
+        <v>92.38</v>
       </c>
       <c r="D163" t="n">
-        <v>186.77</v>
+        <v>100.65</v>
       </c>
       <c r="E163" t="n">
-        <v>19.08</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F163" t="n">
-        <v>-2.70975</v>
+        <v>-0.07876</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>101.75</v>
+        <v>438.34</v>
       </c>
       <c r="D164" t="n">
-        <v>128.85</v>
+        <v>613.62</v>
       </c>
       <c r="E164" t="n">
-        <v>26.63</v>
+        <v>39.99</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.2813</v>
+        <v>0.49995</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>55.52</v>
+        <v>26.18</v>
       </c>
       <c r="D165" t="n">
-        <v>93.83</v>
+        <v>36.71</v>
       </c>
       <c r="E165" t="n">
-        <v>69.01000000000001</v>
+        <v>40.22</v>
       </c>
       <c r="F165" t="n">
-        <v>1.52445</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>99.3</v>
+        <v>163.43</v>
       </c>
       <c r="D166" t="n">
-        <v>151.73</v>
+        <v>200.67</v>
       </c>
       <c r="E166" t="n">
-        <v>52.8</v>
+        <v>22.79</v>
       </c>
       <c r="F166" t="n">
-        <v>1.18143</v>
+        <v>0.62133</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>197.73</v>
+        <v>156.84</v>
       </c>
       <c r="D167" t="n">
-        <v>226.2</v>
+        <v>187.03</v>
       </c>
       <c r="E167" t="n">
-        <v>14.4</v>
+        <v>19.25</v>
       </c>
       <c r="F167" t="n">
-        <v>1.01313</v>
+        <v>-2.68499</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>725.17</v>
+        <v>101.75</v>
       </c>
       <c r="D168" t="n">
-        <v>903.28</v>
+        <v>129.17</v>
       </c>
       <c r="E168" t="n">
-        <v>24.56</v>
+        <v>26.95</v>
       </c>
       <c r="F168" t="n">
-        <v>1.18094</v>
+        <v>-0.25082</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>255.54</v>
+        <v>55.52</v>
       </c>
       <c r="D169" t="n">
-        <v>365.08</v>
+        <v>94.83</v>
       </c>
       <c r="E169" t="n">
-        <v>42.87</v>
+        <v>70.8</v>
       </c>
       <c r="F169" t="n">
-        <v>3.6115</v>
+        <v>1.61921</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>417.83</v>
+        <v>99.3</v>
       </c>
       <c r="D170" t="n">
-        <v>559.47</v>
+        <v>151.7</v>
       </c>
       <c r="E170" t="n">
-        <v>33.9</v>
+        <v>52.77</v>
       </c>
       <c r="F170" t="n">
-        <v>0.73966</v>
+        <v>1.17857</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>383.99</v>
+        <v>725.17</v>
       </c>
       <c r="D171" t="n">
-        <v>477.9</v>
+        <v>910.95</v>
       </c>
       <c r="E171" t="n">
-        <v>24.46</v>
+        <v>25.62</v>
       </c>
       <c r="F171" t="n">
-        <v>-1.17179</v>
+        <v>1.91142</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>12.64</v>
+        <v>197.73</v>
       </c>
       <c r="D172" t="n">
-        <v>17.68</v>
+        <v>225.85</v>
       </c>
       <c r="E172" t="n">
-        <v>39.91</v>
+        <v>14.22</v>
       </c>
       <c r="F172" t="n">
-        <v>0.23758</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>252.74</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D173" t="n">
-        <v>325.73</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E173" t="n">
-        <v>28.88</v>
+        <v>28.9</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.26739</v>
+        <v>-0.34243</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>699965</v>
+        <v>255.54</v>
       </c>
       <c r="D174" t="n">
-        <v>769460.0600000001</v>
+        <v>365.08</v>
       </c>
       <c r="E174" t="n">
-        <v>9.93</v>
+        <v>42.87</v>
       </c>
       <c r="F174" t="n">
-        <v>2303.35043</v>
+        <v>3.6115</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>139.71</v>
+        <v>383.99</v>
       </c>
       <c r="D175" t="n">
-        <v>192.72</v>
+        <v>474.13</v>
       </c>
       <c r="E175" t="n">
-        <v>37.94</v>
+        <v>23.47</v>
       </c>
       <c r="F175" t="n">
-        <v>1.6395</v>
+        <v>-1.53084</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>45.37</v>
+        <v>12.64</v>
       </c>
       <c r="D176" t="n">
-        <v>146.49</v>
+        <v>17.74</v>
       </c>
       <c r="E176" t="n">
-        <v>222.88</v>
+        <v>40.35</v>
       </c>
       <c r="F176" t="n">
-        <v>5.21579</v>
+        <v>0.24281</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>112.47</v>
+        <v>417.83</v>
       </c>
       <c r="D177" t="n">
-        <v>140.42</v>
+        <v>556.3099999999999</v>
       </c>
       <c r="E177" t="n">
-        <v>24.85</v>
+        <v>33.14</v>
       </c>
       <c r="F177" t="n">
-        <v>0.49292</v>
+        <v>0.43871</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>156.66</v>
+        <v>32.32</v>
       </c>
       <c r="D178" t="n">
-        <v>266.54</v>
+        <v>37.72</v>
       </c>
       <c r="E178" t="n">
-        <v>70.14</v>
+        <v>16.71</v>
       </c>
       <c r="F178" t="n">
-        <v>2.12518</v>
+        <v>0.15923</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>82.26000000000001</v>
+        <v>252.74</v>
       </c>
       <c r="D179" t="n">
-        <v>125.8</v>
+        <v>326.23</v>
       </c>
       <c r="E179" t="n">
-        <v>52.93</v>
+        <v>29.08</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.17001</v>
+        <v>-0.21978</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>13.06</v>
+        <v>699965</v>
       </c>
       <c r="D180" t="n">
-        <v>19.91</v>
+        <v>771770</v>
       </c>
       <c r="E180" t="n">
-        <v>52.45</v>
+        <v>10.26</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.009140000000000001</v>
+        <v>2523.34448</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>40.41</v>
+        <v>139.71</v>
       </c>
       <c r="D181" t="n">
-        <v>52.64</v>
+        <v>193.61</v>
       </c>
       <c r="E181" t="n">
-        <v>30.26</v>
+        <v>38.58</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.13413</v>
+        <v>1.72426</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>197.38</v>
+        <v>45.37</v>
       </c>
       <c r="D182" t="n">
-        <v>261.46</v>
+        <v>146.69</v>
       </c>
       <c r="E182" t="n">
-        <v>32.47</v>
+        <v>223.32</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.08086</v>
+        <v>5.23484</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>393.42</v>
+        <v>112.47</v>
       </c>
       <c r="D183" t="n">
-        <v>593.45</v>
+        <v>138.49</v>
       </c>
       <c r="E183" t="n">
-        <v>50.84</v>
+        <v>23.14</v>
       </c>
       <c r="F183" t="n">
-        <v>-2.23548</v>
+        <v>0.30959</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>465.4</v>
+        <v>13.06</v>
       </c>
       <c r="D184" t="n">
-        <v>514.15</v>
+        <v>19.91</v>
       </c>
       <c r="E184" t="n">
-        <v>10.47</v>
+        <v>52.45</v>
       </c>
       <c r="F184" t="n">
-        <v>1.5926</v>
+        <v>-0.009140000000000001</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>74.63</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D185" t="n">
-        <v>89.14</v>
+        <v>128.49</v>
       </c>
       <c r="E185" t="n">
-        <v>19.45</v>
+        <v>56.2</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.07488</v>
+        <v>0.08618000000000001</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>56.06</v>
+        <v>156.66</v>
       </c>
       <c r="D186" t="n">
-        <v>62.37</v>
+        <v>265.67</v>
       </c>
       <c r="E186" t="n">
-        <v>11.25</v>
+        <v>69.58</v>
       </c>
       <c r="F186" t="n">
-        <v>0.03601</v>
+        <v>2.0428</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>153.25</v>
+        <v>40.41</v>
       </c>
       <c r="D187" t="n">
-        <v>193.88</v>
+        <v>51.96</v>
       </c>
       <c r="E187" t="n">
-        <v>26.51</v>
+        <v>28.58</v>
       </c>
       <c r="F187" t="n">
-        <v>0.76328</v>
+        <v>-0.19889</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>20.96</v>
+        <v>197.38</v>
       </c>
       <c r="D188" t="n">
-        <v>25.85</v>
+        <v>261.77</v>
       </c>
       <c r="E188" t="n">
-        <v>23.33</v>
+        <v>32.62</v>
       </c>
       <c r="F188" t="n">
-        <v>0.28351</v>
+        <v>-0.05181</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>155.75</v>
+        <v>393.42</v>
       </c>
       <c r="D189" t="n">
-        <v>255.24</v>
+        <v>595.41</v>
       </c>
       <c r="E189" t="n">
-        <v>63.88</v>
+        <v>51.34</v>
       </c>
       <c r="F189" t="n">
-        <v>5.56767</v>
+        <v>-2.04834</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>83.51000000000001</v>
+        <v>74.63</v>
       </c>
       <c r="D190" t="n">
-        <v>97.02</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E190" t="n">
-        <v>16.18</v>
+        <v>19.72</v>
       </c>
       <c r="F190" t="n">
-        <v>0.63913</v>
+        <v>-0.05535</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>40.59</v>
+        <v>465.4</v>
       </c>
       <c r="D191" t="n">
-        <v>56.31</v>
+        <v>514.95</v>
       </c>
       <c r="E191" t="n">
-        <v>38.72</v>
+        <v>10.65</v>
       </c>
       <c r="F191" t="n">
-        <v>1.40256</v>
+        <v>1.66879</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>213.69</v>
+        <v>56.06</v>
       </c>
       <c r="D192" t="n">
-        <v>391.61</v>
+        <v>62.39</v>
       </c>
       <c r="E192" t="n">
-        <v>83.26000000000001</v>
+        <v>11.29</v>
       </c>
       <c r="F192" t="n">
-        <v>9.848380000000001</v>
+        <v>0.03839</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>223.65</v>
+        <v>153.25</v>
       </c>
       <c r="D193" t="n">
-        <v>380.15</v>
+        <v>194.86</v>
       </c>
       <c r="E193" t="n">
-        <v>69.98</v>
+        <v>27.15</v>
       </c>
       <c r="F193" t="n">
-        <v>11.77726</v>
+        <v>0.85662</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>128.43</v>
+        <v>155.75</v>
       </c>
       <c r="D194" t="n">
-        <v>149.61</v>
+        <v>257.06</v>
       </c>
       <c r="E194" t="n">
-        <v>16.49</v>
+        <v>65.05</v>
       </c>
       <c r="F194" t="n">
-        <v>0.76463</v>
+        <v>5.74053</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>66.95</v>
+        <v>20.96</v>
       </c>
       <c r="D195" t="n">
-        <v>86.84999999999999</v>
+        <v>25.85</v>
       </c>
       <c r="E195" t="n">
-        <v>29.72</v>
+        <v>23.33</v>
       </c>
       <c r="F195" t="n">
-        <v>1.54492</v>
+        <v>0.28351</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>18.71</v>
+        <v>40.59</v>
       </c>
       <c r="D196" t="n">
-        <v>21.43</v>
+        <v>56.33</v>
       </c>
       <c r="E196" t="n">
-        <v>14.56</v>
+        <v>38.78</v>
       </c>
       <c r="F196" t="n">
-        <v>0.13204</v>
+        <v>1.40494</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>126.32</v>
+        <v>213.69</v>
       </c>
       <c r="D197" t="n">
-        <v>157.96</v>
+        <v>396.45</v>
       </c>
       <c r="E197" t="n">
-        <v>25.05</v>
+        <v>85.53</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.25056</v>
+        <v>10.30916</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>57.15</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="D198" t="n">
-        <v>191.84</v>
+        <v>96.97</v>
       </c>
       <c r="E198" t="n">
-        <v>235.68</v>
+        <v>16.12</v>
       </c>
       <c r="F198" t="n">
-        <v>4.09928</v>
+        <v>0.63437</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>62.93</v>
+        <v>223.65</v>
       </c>
       <c r="D199" t="n">
-        <v>187.93</v>
+        <v>382.95</v>
       </c>
       <c r="E199" t="n">
-        <v>198.64</v>
+        <v>71.23</v>
       </c>
       <c r="F199" t="n">
-        <v>6.38998</v>
+        <v>12.04345</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>112.5</v>
+        <v>128.43</v>
       </c>
       <c r="D200" t="n">
-        <v>195.62</v>
+        <v>148.54</v>
       </c>
       <c r="E200" t="n">
-        <v>73.89</v>
+        <v>15.66</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.91844</v>
+        <v>0.66273</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>43.81</v>
+        <v>18.71</v>
       </c>
       <c r="D201" t="n">
-        <v>99.31999999999999</v>
+        <v>21.49</v>
       </c>
       <c r="E201" t="n">
-        <v>126.72</v>
+        <v>14.86</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.5039</v>
+        <v>0.13728</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>17.89</v>
+        <v>66.95</v>
       </c>
       <c r="D202" t="n">
-        <v>31.4</v>
+        <v>86.44</v>
       </c>
       <c r="E202" t="n">
-        <v>75.48999999999999</v>
+        <v>29.11</v>
       </c>
       <c r="F202" t="n">
-        <v>0.2796</v>
+        <v>1.50588</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>76.7</v>
+        <v>126.32</v>
       </c>
       <c r="D203" t="n">
-        <v>169.85</v>
+        <v>157.22</v>
       </c>
       <c r="E203" t="n">
-        <v>121.45</v>
+        <v>24.46</v>
       </c>
       <c r="F203" t="n">
-        <v>0.64472</v>
+        <v>-0.32127</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5308,22 +5308,22 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>166.99</v>
+        <v>118.05</v>
       </c>
       <c r="D204" t="n">
-        <v>330.67</v>
+        <v>191.73</v>
       </c>
       <c r="E204" t="n">
-        <v>98.02</v>
+        <v>62.41</v>
       </c>
       <c r="F204" t="n">
-        <v>9.093680000000001</v>
+        <v>-0.40022</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5332,22 +5332,22 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>78.59999999999999</v>
+        <v>17.89</v>
       </c>
       <c r="D205" t="n">
-        <v>164.01</v>
+        <v>31.41</v>
       </c>
       <c r="E205" t="n">
-        <v>108.66</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F205" t="n">
-        <v>-0.47787</v>
+        <v>0.28103</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5356,22 +5356,22 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>34.41</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D206" t="n">
-        <v>67.83</v>
+        <v>167.84</v>
       </c>
       <c r="E206" t="n">
-        <v>97.14</v>
+        <v>113.54</v>
       </c>
       <c r="F206" t="n">
-        <v>0.15408</v>
+        <v>-0.11311</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5380,22 +5380,22 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>105.37</v>
+        <v>57.15</v>
       </c>
       <c r="D207" t="n">
-        <v>232.9</v>
+        <v>192.77</v>
       </c>
       <c r="E207" t="n">
-        <v>121.04</v>
+        <v>237.31</v>
       </c>
       <c r="F207" t="n">
-        <v>-1.6304</v>
+        <v>4.18785</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5404,22 +5404,22 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>25.85</v>
+        <v>151.43</v>
       </c>
       <c r="D208" t="n">
-        <v>42.28</v>
+        <v>265.67</v>
       </c>
       <c r="E208" t="n">
-        <v>63.54</v>
+        <v>75.44</v>
       </c>
       <c r="F208" t="n">
-        <v>0.06751</v>
+        <v>1.55591</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5428,22 +5428,22 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>120.88</v>
+        <v>34.41</v>
       </c>
       <c r="D209" t="n">
-        <v>211.73</v>
+        <v>67.69</v>
       </c>
       <c r="E209" t="n">
-        <v>75.16</v>
+        <v>96.72</v>
       </c>
       <c r="F209" t="n">
-        <v>-0.797</v>
+        <v>0.14027</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>151.43</v>
+        <v>62.93</v>
       </c>
       <c r="D210" t="n">
-        <v>265.49</v>
+        <v>186.45</v>
       </c>
       <c r="E210" t="n">
-        <v>75.31999999999999</v>
+        <v>196.28</v>
       </c>
       <c r="F210" t="n">
-        <v>1.53877</v>
+        <v>6.24855</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5476,22 +5476,22 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>83</v>
+        <v>43.81</v>
       </c>
       <c r="D211" t="n">
-        <v>143</v>
+        <v>100.2</v>
       </c>
       <c r="E211" t="n">
-        <v>72.29000000000001</v>
+        <v>128.71</v>
       </c>
       <c r="F211" t="n">
-        <v>0.825</v>
+        <v>-0.42056</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>121.11</v>
+        <v>166.99</v>
       </c>
       <c r="D212" t="n">
-        <v>334.15</v>
+        <v>330.36</v>
       </c>
       <c r="E212" t="n">
-        <v>175.91</v>
+        <v>97.83</v>
       </c>
       <c r="F212" t="n">
-        <v>2.25721</v>
+        <v>9.064159999999999</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5524,16 +5524,16 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>118.05</v>
+        <v>120.88</v>
       </c>
       <c r="D213" t="n">
-        <v>190.99</v>
+        <v>211.54</v>
       </c>
       <c r="E213" t="n">
-        <v>61.79</v>
+        <v>75</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.47069</v>
+        <v>-0.8151</v>
       </c>
     </row>
     <row r="214">
@@ -5551,19 +5551,19 @@
         <v>32.36</v>
       </c>
       <c r="D214" t="n">
-        <v>52.72</v>
+        <v>53.34</v>
       </c>
       <c r="E214" t="n">
-        <v>62.93</v>
+        <v>64.83</v>
       </c>
       <c r="F214" t="n">
-        <v>0.30799</v>
+        <v>0.36656</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5572,22 +5572,22 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>18.26</v>
+        <v>112.5</v>
       </c>
       <c r="D215" t="n">
-        <v>34.08</v>
+        <v>194.21</v>
       </c>
       <c r="E215" t="n">
-        <v>86.64</v>
+        <v>72.63</v>
       </c>
       <c r="F215" t="n">
-        <v>1.16312</v>
+        <v>-1.0532</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5596,22 +5596,22 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>10.49</v>
+        <v>121.11</v>
       </c>
       <c r="D216" t="n">
-        <v>20.08</v>
+        <v>332.35</v>
       </c>
       <c r="E216" t="n">
-        <v>91.42</v>
+        <v>174.42</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.13477</v>
+        <v>2.08531</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5620,22 +5620,22 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>188.79</v>
+        <v>83</v>
       </c>
       <c r="D217" t="n">
-        <v>275.84</v>
+        <v>142.35</v>
       </c>
       <c r="E217" t="n">
-        <v>46.11</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F217" t="n">
-        <v>-2.36122</v>
+        <v>0.76309</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5644,430 +5644,430 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>117.65</v>
+        <v>76.7</v>
       </c>
       <c r="D218" t="n">
-        <v>231.77</v>
+        <v>170.18</v>
       </c>
       <c r="E218" t="n">
-        <v>97</v>
+        <v>121.88</v>
       </c>
       <c r="F218" t="n">
-        <v>0.39634</v>
+        <v>0.67575</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>95.67</v>
+        <v>105.37</v>
       </c>
       <c r="D219" t="n">
-        <v>190.83</v>
+        <v>230.05</v>
       </c>
       <c r="E219" t="n">
-        <v>99.47</v>
+        <v>118.33</v>
       </c>
       <c r="F219" t="n">
-        <v>0.72133</v>
+        <v>-1.90231</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>56.43</v>
+        <v>188.79</v>
       </c>
       <c r="D220" t="n">
-        <v>106.64</v>
+        <v>276.63</v>
       </c>
       <c r="E220" t="n">
-        <v>88.98</v>
+        <v>46.53</v>
       </c>
       <c r="F220" t="n">
-        <v>2.98695</v>
+        <v>-2.28574</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>124.07</v>
+        <v>18.26</v>
       </c>
       <c r="D221" t="n">
-        <v>179.15</v>
+        <v>34.02</v>
       </c>
       <c r="E221" t="n">
-        <v>44.39</v>
+        <v>86.31</v>
       </c>
       <c r="F221" t="n">
-        <v>4.07526</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>23.63</v>
+        <v>25.85</v>
       </c>
       <c r="D222" t="n">
-        <v>25.42</v>
+        <v>42.91</v>
       </c>
       <c r="E222" t="n">
-        <v>7.58</v>
+        <v>66</v>
       </c>
       <c r="F222" t="n">
-        <v>0.06106</v>
+        <v>0.12798</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>62.49</v>
+        <v>117.65</v>
       </c>
       <c r="D223" t="n">
-        <v>89.25</v>
+        <v>231.88</v>
       </c>
       <c r="E223" t="n">
-        <v>42.83</v>
+        <v>97.09</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.29014</v>
+        <v>0.40682</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>190.63</v>
+        <v>10.49</v>
       </c>
       <c r="D224" t="n">
-        <v>216.88</v>
+        <v>19.88</v>
       </c>
       <c r="E224" t="n">
-        <v>13.77</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="F224" t="n">
-        <v>-1.68018</v>
+        <v>-0.15382</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>23.49</v>
+        <v>56.43</v>
       </c>
       <c r="D225" t="n">
-        <v>32.52</v>
+        <v>106.91</v>
       </c>
       <c r="E225" t="n">
-        <v>38.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="F225" t="n">
-        <v>0.10028</v>
+        <v>3.01266</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>172.34</v>
+        <v>23.63</v>
       </c>
       <c r="D226" t="n">
-        <v>217.81</v>
+        <v>25.41</v>
       </c>
       <c r="E226" t="n">
-        <v>26.38</v>
+        <v>7.53</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.14928</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>72.54000000000001</v>
+        <v>190.63</v>
       </c>
       <c r="D227" t="n">
-        <v>86.18000000000001</v>
+        <v>218.57</v>
       </c>
       <c r="E227" t="n">
-        <v>18.81</v>
+        <v>14.66</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.20036</v>
+        <v>-1.51875</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>96.73</v>
+        <v>124.07</v>
       </c>
       <c r="D228" t="n">
-        <v>122.64</v>
+        <v>180.15</v>
       </c>
       <c r="E228" t="n">
-        <v>26.79</v>
+        <v>45.2</v>
       </c>
       <c r="F228" t="n">
-        <v>0.44226</v>
+        <v>4.1705</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RF-PC</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>23.5</v>
+        <v>23.49</v>
       </c>
       <c r="D229" t="n">
-        <v>24.59</v>
+        <v>32.49</v>
       </c>
       <c r="E229" t="n">
-        <v>4.66</v>
+        <v>38.31</v>
       </c>
       <c r="F229" t="n">
-        <v>0.05496</v>
+        <v>0.09743</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>164.13</v>
+        <v>62.49</v>
       </c>
       <c r="D230" t="n">
-        <v>542.84</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="E230" t="n">
-        <v>230.73</v>
+        <v>43.73</v>
       </c>
       <c r="F230" t="n">
-        <v>22.14874</v>
+        <v>-0.23607</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>73.13</v>
+        <v>172.34</v>
       </c>
       <c r="D231" t="n">
-        <v>95.2</v>
+        <v>217.36</v>
       </c>
       <c r="E231" t="n">
-        <v>30.18</v>
+        <v>26.12</v>
       </c>
       <c r="F231" t="n">
-        <v>0.41372</v>
+        <v>-0.19213</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>186.42</v>
+        <v>430.4</v>
       </c>
       <c r="D232" t="n">
-        <v>264.71</v>
+        <v>558.54</v>
       </c>
       <c r="E232" t="n">
-        <v>42</v>
+        <v>29.77</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.25716</v>
+        <v>0.26252</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>31.8</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="D233" t="n">
-        <v>69.3</v>
+        <v>87.16</v>
       </c>
       <c r="E233" t="n">
-        <v>117.92</v>
+        <v>20.15</v>
       </c>
       <c r="F233" t="n">
-        <v>0.30504</v>
+        <v>-0.10751</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>20.33</v>
+        <v>164.13</v>
       </c>
       <c r="D234" t="n">
-        <v>29.06</v>
+        <v>534.28</v>
       </c>
       <c r="E234" t="n">
-        <v>42.92</v>
+        <v>225.52</v>
       </c>
       <c r="F234" t="n">
-        <v>0.12196</v>
+        <v>21.33398</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>204.77</v>
+        <v>96.73</v>
       </c>
       <c r="D235" t="n">
-        <v>274.32</v>
+        <v>122.53</v>
       </c>
       <c r="E235" t="n">
-        <v>33.96</v>
+        <v>26.67</v>
       </c>
       <c r="F235" t="n">
-        <v>0.48652</v>
+        <v>0.4313</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6076,22 +6076,22 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>257.27</v>
+        <v>73.13</v>
       </c>
       <c r="D236" t="n">
-        <v>320.37</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E236" t="n">
-        <v>24.53</v>
+        <v>30.49</v>
       </c>
       <c r="F236" t="n">
-        <v>6.33832</v>
+        <v>0.43563</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6100,22 +6100,22 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>97.52</v>
+        <v>199.3</v>
       </c>
       <c r="D237" t="n">
-        <v>132.44</v>
+        <v>351.81</v>
       </c>
       <c r="E237" t="n">
-        <v>35.81</v>
+        <v>76.52</v>
       </c>
       <c r="F237" t="n">
-        <v>2.13395</v>
+        <v>-1.44191</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6124,22 +6124,22 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>19.02</v>
+        <v>3.88</v>
       </c>
       <c r="D238" t="n">
-        <v>27.16</v>
+        <v>6.46</v>
       </c>
       <c r="E238" t="n">
-        <v>42.8</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F238" t="n">
-        <v>0.27103</v>
+        <v>0.08959</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>131.47</v>
+        <v>52.5</v>
       </c>
       <c r="D239" t="n">
-        <v>213.11</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="E239" t="n">
-        <v>62.1</v>
+        <v>50.97</v>
       </c>
       <c r="F239" t="n">
-        <v>0.82591</v>
+        <v>4.37139</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>28.35</v>
+        <v>131.47</v>
       </c>
       <c r="D240" t="n">
-        <v>39</v>
+        <v>214.07</v>
       </c>
       <c r="E240" t="n">
-        <v>37.57</v>
+        <v>62.83</v>
       </c>
       <c r="F240" t="n">
-        <v>0.32023</v>
+        <v>0.91734</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>21.06</v>
+        <v>273.5</v>
       </c>
       <c r="D241" t="n">
-        <v>37.67</v>
+        <v>349.39</v>
       </c>
       <c r="E241" t="n">
-        <v>78.87</v>
+        <v>27.75</v>
       </c>
       <c r="F241" t="n">
-        <v>0.5991</v>
+        <v>-1.43004</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,22 +6220,22 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>69.3</v>
+        <v>28.35</v>
       </c>
       <c r="D242" t="n">
-        <v>84.25</v>
+        <v>38.72</v>
       </c>
       <c r="E242" t="n">
-        <v>21.58</v>
+        <v>36.58</v>
       </c>
       <c r="F242" t="n">
-        <v>0.27481</v>
+        <v>0.29357</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6244,22 +6244,22 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>16.32</v>
+        <v>273.14</v>
       </c>
       <c r="D243" t="n">
-        <v>23.86</v>
+        <v>345.71</v>
       </c>
       <c r="E243" t="n">
-        <v>46.2</v>
+        <v>26.57</v>
       </c>
       <c r="F243" t="n">
-        <v>0.23214</v>
+        <v>-1.43948</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>67.39</v>
+        <v>22.61</v>
       </c>
       <c r="D244" t="n">
-        <v>93.18000000000001</v>
+        <v>55.41</v>
       </c>
       <c r="E244" t="n">
-        <v>38.27</v>
+        <v>145.07</v>
       </c>
       <c r="F244" t="n">
-        <v>0.53301</v>
+        <v>1.53437</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>41.19</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D245" t="n">
-        <v>98.26000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="E245" t="n">
-        <v>138.55</v>
+        <v>154.36</v>
       </c>
       <c r="F245" t="n">
-        <v>2.42033</v>
+        <v>0.80893</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,16 +6316,16 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>29.16</v>
+        <v>166</v>
       </c>
       <c r="D246" t="n">
-        <v>39.93</v>
+        <v>407.02</v>
       </c>
       <c r="E246" t="n">
-        <v>36.93</v>
+        <v>145.19</v>
       </c>
       <c r="F246" t="n">
-        <v>0.01104</v>
+        <v>4.5493</v>
       </c>
     </row>
     <row r="247">
@@ -6343,19 +6343,19 @@
         <v>119.51</v>
       </c>
       <c r="D247" t="n">
-        <v>260.1</v>
+        <v>257.05</v>
       </c>
       <c r="E247" t="n">
-        <v>117.64</v>
+        <v>115.09</v>
       </c>
       <c r="F247" t="n">
-        <v>13.1238</v>
+        <v>12.83332</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>77.04000000000001</v>
+        <v>29.16</v>
       </c>
       <c r="D248" t="n">
-        <v>111.47</v>
+        <v>39.94</v>
       </c>
       <c r="E248" t="n">
-        <v>44.69</v>
+        <v>36.97</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.43007</v>
+        <v>0.01199</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>273.14</v>
+        <v>97.52</v>
       </c>
       <c r="D249" t="n">
-        <v>345.73</v>
+        <v>132.88</v>
       </c>
       <c r="E249" t="n">
-        <v>26.58</v>
+        <v>36.26</v>
       </c>
       <c r="F249" t="n">
-        <v>-1.4371</v>
+        <v>2.17585</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>196.04</v>
+        <v>69.3</v>
       </c>
       <c r="D250" t="n">
-        <v>493.84</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E250" t="n">
-        <v>151.91</v>
+        <v>20.55</v>
       </c>
       <c r="F250" t="n">
-        <v>9.88194</v>
+        <v>0.20672</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>52.5</v>
+        <v>258.08</v>
       </c>
       <c r="D251" t="n">
-        <v>80.59</v>
+        <v>290.05</v>
       </c>
       <c r="E251" t="n">
-        <v>53.5</v>
+        <v>12.39</v>
       </c>
       <c r="F251" t="n">
-        <v>4.49805</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>59.66</v>
+        <v>24.77</v>
       </c>
       <c r="D252" t="n">
-        <v>84.02</v>
+        <v>36.96</v>
       </c>
       <c r="E252" t="n">
-        <v>40.83</v>
+        <v>49.21</v>
       </c>
       <c r="F252" t="n">
-        <v>1.57919</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>22.61</v>
+        <v>284.79</v>
       </c>
       <c r="D253" t="n">
-        <v>56.88</v>
+        <v>424.24</v>
       </c>
       <c r="E253" t="n">
-        <v>151.59</v>
+        <v>48.97</v>
       </c>
       <c r="F253" t="n">
-        <v>1.67485</v>
+        <v>5.01403</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>8.609999999999999</v>
+        <v>67.39</v>
       </c>
       <c r="D254" t="n">
-        <v>22.17</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E254" t="n">
-        <v>157.55</v>
+        <v>38.64</v>
       </c>
       <c r="F254" t="n">
-        <v>0.83512</v>
+        <v>0.55682</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>246.63</v>
+        <v>65.16</v>
       </c>
       <c r="D255" t="n">
-        <v>334.52</v>
+        <v>114.33</v>
       </c>
       <c r="E255" t="n">
-        <v>35.64</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="F255" t="n">
-        <v>3.66481</v>
+        <v>2.2454</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3.88</v>
+        <v>19.02</v>
       </c>
       <c r="D256" t="n">
-        <v>6.36</v>
+        <v>27.24</v>
       </c>
       <c r="E256" t="n">
-        <v>64.05</v>
+        <v>43.22</v>
       </c>
       <c r="F256" t="n">
-        <v>0.08054</v>
+        <v>0.27865</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>166</v>
+        <v>20.33</v>
       </c>
       <c r="D257" t="n">
-        <v>414.12</v>
+        <v>29.1</v>
       </c>
       <c r="E257" t="n">
-        <v>149.47</v>
+        <v>43.14</v>
       </c>
       <c r="F257" t="n">
-        <v>5.22597</v>
+        <v>0.12624</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>65.16</v>
+        <v>16.32</v>
       </c>
       <c r="D258" t="n">
-        <v>114.46</v>
+        <v>23.89</v>
       </c>
       <c r="E258" t="n">
-        <v>75.66</v>
+        <v>46.38</v>
       </c>
       <c r="F258" t="n">
-        <v>2.25778</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>273.5</v>
+        <v>41.19</v>
       </c>
       <c r="D259" t="n">
-        <v>349.13</v>
+        <v>97.19</v>
       </c>
       <c r="E259" t="n">
-        <v>27.65</v>
+        <v>135.96</v>
       </c>
       <c r="F259" t="n">
-        <v>-1.45481</v>
+        <v>2.31858</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>199.3</v>
+        <v>107.27</v>
       </c>
       <c r="D260" t="n">
-        <v>351.66</v>
+        <v>136.18</v>
       </c>
       <c r="E260" t="n">
-        <v>76.45</v>
+        <v>26.95</v>
       </c>
       <c r="F260" t="n">
-        <v>-1.45619</v>
+        <v>1.00255</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>279.73</v>
+        <v>196.04</v>
       </c>
       <c r="D261" t="n">
-        <v>412.51</v>
+        <v>493.41</v>
       </c>
       <c r="E261" t="n">
-        <v>47.47</v>
+        <v>151.69</v>
       </c>
       <c r="F261" t="n">
-        <v>3.83657</v>
+        <v>9.84099</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GLXY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>17.15</v>
+        <v>246.63</v>
       </c>
       <c r="D262" t="n">
-        <v>24.21</v>
+        <v>333.08</v>
       </c>
       <c r="E262" t="n">
-        <v>41.17</v>
+        <v>35.05</v>
       </c>
       <c r="F262" t="n">
-        <v>0.13019</v>
+        <v>3.52767</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>258.08</v>
+        <v>59.66</v>
       </c>
       <c r="D263" t="n">
-        <v>288.61</v>
+        <v>84.11</v>
       </c>
       <c r="E263" t="n">
-        <v>11.83</v>
+        <v>40.98</v>
       </c>
       <c r="F263" t="n">
-        <v>0.73753</v>
+        <v>1.58777</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>90.01000000000001</v>
+        <v>57.45</v>
       </c>
       <c r="D264" t="n">
-        <v>100.83</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E264" t="n">
-        <v>12.03</v>
+        <v>22.79</v>
       </c>
       <c r="F264" t="n">
-        <v>0.15752</v>
+        <v>-0.19886</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>26.41</v>
+        <v>279.73</v>
       </c>
       <c r="D265" t="n">
-        <v>41.35</v>
+        <v>411.49</v>
       </c>
       <c r="E265" t="n">
-        <v>56.57</v>
+        <v>47.1</v>
       </c>
       <c r="F265" t="n">
-        <v>1.72078</v>
+        <v>3.73943</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>24.77</v>
+        <v>26.41</v>
       </c>
       <c r="D266" t="n">
-        <v>36.81</v>
+        <v>41.02</v>
       </c>
       <c r="E266" t="n">
-        <v>48.61</v>
+        <v>55.32</v>
       </c>
       <c r="F266" t="n">
-        <v>0.39741</v>
+        <v>1.68935</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>284.79</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D267" t="n">
-        <v>424.15</v>
+        <v>100.36</v>
       </c>
       <c r="E267" t="n">
-        <v>48.93</v>
+        <v>11.5</v>
       </c>
       <c r="F267" t="n">
-        <v>5.00546</v>
+        <v>0.11228</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,70 +6844,70 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>12.96</v>
+        <v>31.8</v>
       </c>
       <c r="D268" t="n">
-        <v>16.72</v>
+        <v>69.41</v>
       </c>
       <c r="E268" t="n">
-        <v>28.97</v>
+        <v>118.27</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.04627</v>
+        <v>0.31551</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SPG-PJ</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>52.49</v>
+        <v>204.77</v>
       </c>
       <c r="D269" t="n">
-        <v>55.78</v>
+        <v>274.99</v>
       </c>
       <c r="E269" t="n">
-        <v>6.27</v>
+        <v>34.29</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.04614</v>
+        <v>0.55032</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>182.65</v>
+        <v>12.96</v>
       </c>
       <c r="D270" t="n">
-        <v>336.38</v>
+        <v>16.66</v>
       </c>
       <c r="E270" t="n">
-        <v>84.17</v>
+        <v>28.55</v>
       </c>
       <c r="F270" t="n">
-        <v>3.88875</v>
+        <v>-0.0515</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6916,22 +6916,22 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>317.93</v>
+        <v>147.02</v>
       </c>
       <c r="D271" t="n">
-        <v>377.91</v>
+        <v>373.94</v>
       </c>
       <c r="E271" t="n">
-        <v>18.87</v>
+        <v>154.35</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.86572</v>
+        <v>-2.08465</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>AXSM</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>284.93</v>
+        <v>156.35</v>
       </c>
       <c r="D272" t="n">
-        <v>412.13</v>
+        <v>216.58</v>
       </c>
       <c r="E272" t="n">
-        <v>44.64</v>
+        <v>38.52</v>
       </c>
       <c r="F272" t="n">
-        <v>0.63228</v>
+        <v>1.76572</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,22 +6964,22 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>156.35</v>
+        <v>92.39</v>
       </c>
       <c r="D273" t="n">
-        <v>221.49</v>
+        <v>235.38</v>
       </c>
       <c r="E273" t="n">
-        <v>41.66</v>
+        <v>154.75</v>
       </c>
       <c r="F273" t="n">
-        <v>2.23334</v>
+        <v>2.36905</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>71.42</v>
+        <v>7.63</v>
       </c>
       <c r="D274" t="n">
-        <v>78.64</v>
+        <v>11.33</v>
       </c>
       <c r="E274" t="n">
-        <v>10.11</v>
+        <v>48.49</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.26445</v>
+        <v>0.16084</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>87.98</v>
+        <v>284.93</v>
       </c>
       <c r="D275" t="n">
-        <v>110.28</v>
+        <v>412.56</v>
       </c>
       <c r="E275" t="n">
-        <v>25.34</v>
+        <v>44.79</v>
       </c>
       <c r="F275" t="n">
-        <v>0.48448</v>
+        <v>0.67323</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>92.42</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D276" t="n">
-        <v>109.11</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="E276" t="n">
-        <v>18.06</v>
+        <v>18.13</v>
       </c>
       <c r="F276" t="n">
-        <v>0.23722</v>
+        <v>-0.43807</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,22 +7060,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>87.15000000000001</v>
+        <v>285.27</v>
       </c>
       <c r="D277" t="n">
-        <v>157.2</v>
+        <v>378.05</v>
       </c>
       <c r="E277" t="n">
-        <v>80.38</v>
+        <v>32.52</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.11238</v>
+        <v>1.30077</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7084,22 +7084,22 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>7.58</v>
+        <v>33.63</v>
       </c>
       <c r="D278" t="n">
-        <v>10.75</v>
+        <v>43.55</v>
       </c>
       <c r="E278" t="n">
-        <v>41.82</v>
+        <v>29.5</v>
       </c>
       <c r="F278" t="n">
-        <v>0.1819</v>
+        <v>-0.00236</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7108,22 +7108,22 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>121.84</v>
+        <v>202.71</v>
       </c>
       <c r="D279" t="n">
-        <v>165.15</v>
+        <v>258.48</v>
       </c>
       <c r="E279" t="n">
-        <v>35.54</v>
+        <v>27.51</v>
       </c>
       <c r="F279" t="n">
-        <v>0.3143</v>
+        <v>-1.41316</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7132,22 +7132,22 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>35.34</v>
+        <v>67.7</v>
       </c>
       <c r="D280" t="n">
-        <v>53.39</v>
+        <v>97.75</v>
       </c>
       <c r="E280" t="n">
-        <v>51.08</v>
+        <v>44.39</v>
       </c>
       <c r="F280" t="n">
-        <v>0.71484</v>
+        <v>0.25783</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7156,22 +7156,22 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>295.52</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D281" t="n">
-        <v>376.22</v>
+        <v>157.45</v>
       </c>
       <c r="E281" t="n">
-        <v>27.31</v>
+        <v>80.67</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.65359</v>
+        <v>-0.08858000000000001</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7180,16 +7180,16 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>285.27</v>
+        <v>91.37</v>
       </c>
       <c r="D282" t="n">
-        <v>376.05</v>
+        <v>120.93</v>
       </c>
       <c r="E282" t="n">
-        <v>31.82</v>
+        <v>32.35</v>
       </c>
       <c r="F282" t="n">
-        <v>1.1103</v>
+        <v>-0.10485</v>
       </c>
     </row>
     <row r="283">
@@ -7207,19 +7207,19 @@
         <v>22.3</v>
       </c>
       <c r="D283" t="n">
-        <v>34.63</v>
+        <v>34.8</v>
       </c>
       <c r="E283" t="n">
-        <v>55.29</v>
+        <v>56.05</v>
       </c>
       <c r="F283" t="n">
-        <v>0.44128</v>
+        <v>0.45747</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7228,22 +7228,22 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>525.72</v>
+        <v>52.49</v>
       </c>
       <c r="D284" t="n">
-        <v>664.37</v>
+        <v>55.78</v>
       </c>
       <c r="E284" t="n">
-        <v>26.37</v>
+        <v>6.27</v>
       </c>
       <c r="F284" t="n">
-        <v>21.99458</v>
+        <v>-0.04614</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7252,22 +7252,22 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>55.4</v>
+        <v>10.65</v>
       </c>
       <c r="D285" t="n">
-        <v>69.02</v>
+        <v>14.74</v>
       </c>
       <c r="E285" t="n">
-        <v>24.58</v>
+        <v>38.4</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.05427</v>
+        <v>0.05009</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7276,22 +7276,22 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>20.72</v>
+        <v>92.42</v>
       </c>
       <c r="D286" t="n">
-        <v>24.44</v>
+        <v>108.59</v>
       </c>
       <c r="E286" t="n">
-        <v>17.95</v>
+        <v>17.5</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.10916</v>
+        <v>0.1877</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7300,22 +7300,22 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>3.42</v>
+        <v>20.72</v>
       </c>
       <c r="D287" t="n">
-        <v>4.93</v>
+        <v>24.85</v>
       </c>
       <c r="E287" t="n">
-        <v>44.3</v>
+        <v>19.93</v>
       </c>
       <c r="F287" t="n">
-        <v>0.09897</v>
+        <v>-0.07012</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7324,22 +7324,22 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>67.7</v>
+        <v>17.45</v>
       </c>
       <c r="D288" t="n">
-        <v>97.04000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="E288" t="n">
-        <v>43.34</v>
+        <v>13.47</v>
       </c>
       <c r="F288" t="n">
-        <v>0.19021</v>
+        <v>-0.03105</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7348,22 +7348,22 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>10.65</v>
+        <v>55.4</v>
       </c>
       <c r="D289" t="n">
-        <v>14.7</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E289" t="n">
-        <v>38.03</v>
+        <v>24.87</v>
       </c>
       <c r="F289" t="n">
-        <v>0.04629</v>
+        <v>-0.03903</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7372,22 +7372,22 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>39.84</v>
+        <v>295.52</v>
       </c>
       <c r="D290" t="n">
-        <v>58.24</v>
+        <v>375.28</v>
       </c>
       <c r="E290" t="n">
-        <v>46.18</v>
+        <v>26.99</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.10904</v>
+        <v>-0.74265</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7396,22 +7396,22 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>243.35</v>
+        <v>3.42</v>
       </c>
       <c r="D291" t="n">
-        <v>355.6</v>
+        <v>4.89</v>
       </c>
       <c r="E291" t="n">
-        <v>46.13</v>
+        <v>42.98</v>
       </c>
       <c r="F291" t="n">
-        <v>0.59458</v>
+        <v>0.09469</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7420,22 +7420,22 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>41.53</v>
+        <v>525.72</v>
       </c>
       <c r="D292" t="n">
-        <v>56.49</v>
+        <v>665.6</v>
       </c>
       <c r="E292" t="n">
-        <v>36.01</v>
+        <v>26.61</v>
       </c>
       <c r="F292" t="n">
-        <v>0.3765</v>
+        <v>22.11172</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7444,22 +7444,22 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>147.02</v>
+        <v>289.16</v>
       </c>
       <c r="D293" t="n">
-        <v>376.69</v>
+        <v>410.01</v>
       </c>
       <c r="E293" t="n">
-        <v>156.22</v>
+        <v>41.79</v>
       </c>
       <c r="F293" t="n">
-        <v>-1.82275</v>
+        <v>-0.38142</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7468,22 +7468,22 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>67.56999999999999</v>
+        <v>39.84</v>
       </c>
       <c r="D294" t="n">
-        <v>80</v>
+        <v>58.53</v>
       </c>
       <c r="E294" t="n">
-        <v>18.4</v>
+        <v>46.91</v>
       </c>
       <c r="F294" t="n">
-        <v>-0.42092</v>
+        <v>-0.08142000000000001</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7492,22 +7492,22 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>87.01000000000001</v>
+        <v>61.37</v>
       </c>
       <c r="D295" t="n">
-        <v>115.66</v>
+        <v>80.23</v>
       </c>
       <c r="E295" t="n">
-        <v>32.93</v>
+        <v>30.73</v>
       </c>
       <c r="F295" t="n">
-        <v>0.73512</v>
+        <v>-0.09644999999999999</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7516,22 +7516,22 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>67.23</v>
+        <v>317.93</v>
       </c>
       <c r="D296" t="n">
-        <v>98.89</v>
+        <v>379.54</v>
       </c>
       <c r="E296" t="n">
-        <v>47.09</v>
+        <v>19.38</v>
       </c>
       <c r="F296" t="n">
-        <v>-0.07883999999999999</v>
+        <v>-0.71048</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7540,22 +7540,22 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>125.78</v>
+        <v>153.68</v>
       </c>
       <c r="D297" t="n">
-        <v>143.73</v>
+        <v>172.02</v>
       </c>
       <c r="E297" t="n">
-        <v>14.27</v>
+        <v>11.93</v>
       </c>
       <c r="F297" t="n">
-        <v>-0.3938</v>
+        <v>-0.63445</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7564,22 +7564,22 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>35.72</v>
+        <v>7.58</v>
       </c>
       <c r="D298" t="n">
-        <v>49.63</v>
+        <v>10.73</v>
       </c>
       <c r="E298" t="n">
-        <v>38.94</v>
+        <v>41.56</v>
       </c>
       <c r="F298" t="n">
-        <v>-0.53366</v>
+        <v>0.17999</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7588,22 +7588,22 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>157.12</v>
+        <v>213.28</v>
       </c>
       <c r="D299" t="n">
-        <v>260.63</v>
+        <v>283.27</v>
       </c>
       <c r="E299" t="n">
-        <v>65.88</v>
+        <v>32.82</v>
       </c>
       <c r="F299" t="n">
-        <v>1.83577</v>
+        <v>-0.5633</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7612,22 +7612,22 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>92.39</v>
+        <v>157.12</v>
       </c>
       <c r="D300" t="n">
-        <v>238.64</v>
+        <v>261.12</v>
       </c>
       <c r="E300" t="n">
-        <v>158.28</v>
+        <v>66.19</v>
       </c>
       <c r="F300" t="n">
-        <v>2.67952</v>
+        <v>1.88244</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7636,22 +7636,22 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>213.28</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D301" t="n">
-        <v>283.36</v>
+        <v>116.9</v>
       </c>
       <c r="E301" t="n">
-        <v>32.86</v>
+        <v>34.35</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.55426</v>
+        <v>0.85321</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>QSR</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7660,22 +7660,22 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>7.63</v>
+        <v>71.42</v>
       </c>
       <c r="D302" t="n">
-        <v>11.3</v>
+        <v>78.89</v>
       </c>
       <c r="E302" t="n">
-        <v>48.1</v>
+        <v>10.46</v>
       </c>
       <c r="F302" t="n">
-        <v>0.15799</v>
+        <v>-0.24064</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7684,22 +7684,22 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>61.37</v>
+        <v>243.35</v>
       </c>
       <c r="D303" t="n">
-        <v>79.81999999999999</v>
+        <v>355.2</v>
       </c>
       <c r="E303" t="n">
-        <v>30.06</v>
+        <v>45.96</v>
       </c>
       <c r="F303" t="n">
-        <v>-0.1355</v>
+        <v>0.55648</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7708,16 +7708,16 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>14</v>
+        <v>182.65</v>
       </c>
       <c r="D304" t="n">
-        <v>14.82</v>
+        <v>341.79</v>
       </c>
       <c r="E304" t="n">
-        <v>5.89</v>
+        <v>87.13</v>
       </c>
       <c r="F304" t="n">
-        <v>0.01538</v>
+        <v>4.40399</v>
       </c>
     </row>
     <row r="305">
@@ -7735,19 +7735,19 @@
         <v>3.93</v>
       </c>
       <c r="D305" t="n">
-        <v>5.93</v>
+        <v>5.84</v>
       </c>
       <c r="E305" t="n">
-        <v>50.76</v>
+        <v>48.6</v>
       </c>
       <c r="F305" t="n">
-        <v>0.08137</v>
+        <v>0.07327</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7756,262 +7756,262 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>72.90000000000001</v>
+        <v>87.98</v>
       </c>
       <c r="D306" t="n">
-        <v>94.09999999999999</v>
+        <v>108.99</v>
       </c>
       <c r="E306" t="n">
-        <v>29.08</v>
+        <v>23.88</v>
       </c>
       <c r="F306" t="n">
-        <v>0.66736</v>
+        <v>0.3621</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>17.13</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D307" t="n">
-        <v>43.57</v>
+        <v>94.92</v>
       </c>
       <c r="E307" t="n">
-        <v>154.35</v>
+        <v>30.21</v>
       </c>
       <c r="F307" t="n">
-        <v>0.30141</v>
+        <v>0.7454499999999999</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>63.78</v>
+        <v>35.34</v>
       </c>
       <c r="D308" t="n">
-        <v>70.59</v>
+        <v>53.67</v>
       </c>
       <c r="E308" t="n">
-        <v>10.68</v>
+        <v>51.87</v>
       </c>
       <c r="F308" t="n">
-        <v>0.28062</v>
+        <v>0.74151</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>99.98999999999999</v>
+        <v>125.78</v>
       </c>
       <c r="D309" t="n">
-        <v>172.41</v>
+        <v>143.7</v>
       </c>
       <c r="E309" t="n">
-        <v>72.43000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="F309" t="n">
-        <v>0.53291</v>
+        <v>-0.39666</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MDGL</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>445.04</v>
+        <v>35.72</v>
       </c>
       <c r="D310" t="n">
-        <v>538.77</v>
+        <v>49.48</v>
       </c>
       <c r="E310" t="n">
-        <v>21.06</v>
+        <v>38.52</v>
       </c>
       <c r="F310" t="n">
-        <v>2.07857</v>
+        <v>-0.54794</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>FMX</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>105.8</v>
+        <v>67.23</v>
       </c>
       <c r="D311" t="n">
-        <v>121.22</v>
+        <v>98.22</v>
       </c>
       <c r="E311" t="n">
-        <v>14.58</v>
+        <v>46.1</v>
       </c>
       <c r="F311" t="n">
-        <v>-0.81049</v>
+        <v>-0.14265</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>27.17</v>
+        <v>14</v>
       </c>
       <c r="D312" t="n">
-        <v>34.04</v>
+        <v>14.8</v>
       </c>
       <c r="E312" t="n">
-        <v>25.29</v>
+        <v>5.71</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.22965</v>
+        <v>0.01308</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>23.97</v>
+        <v>121.84</v>
       </c>
       <c r="D313" t="n">
-        <v>30.69</v>
+        <v>162.38</v>
       </c>
       <c r="E313" t="n">
-        <v>28.06</v>
+        <v>33.27</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.06813</v>
+        <v>0.05096</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>146.17</v>
+        <v>17.13</v>
       </c>
       <c r="D314" t="n">
-        <v>217.26</v>
+        <v>43.45</v>
       </c>
       <c r="E314" t="n">
-        <v>48.63</v>
+        <v>153.65</v>
       </c>
       <c r="F314" t="n">
-        <v>0.02127</v>
+        <v>0.28998</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>94.23999999999999</v>
+        <v>63.78</v>
       </c>
       <c r="D315" t="n">
-        <v>111.31</v>
+        <v>70.61</v>
       </c>
       <c r="E315" t="n">
-        <v>18.11</v>
+        <v>10.71</v>
       </c>
       <c r="F315" t="n">
-        <v>-0.26258</v>
+        <v>0.28252</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>241.14</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D316" t="n">
-        <v>300.65</v>
+        <v>168.93</v>
       </c>
       <c r="E316" t="n">
-        <v>24.68</v>
+        <v>68.95</v>
       </c>
       <c r="F316" t="n">
-        <v>1.83751</v>
+        <v>0.20101</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8020,22 +8020,22 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>23.65</v>
+        <v>27.17</v>
       </c>
       <c r="D317" t="n">
-        <v>29.58</v>
+        <v>33.86</v>
       </c>
       <c r="E317" t="n">
-        <v>25.07</v>
+        <v>24.62</v>
       </c>
       <c r="F317" t="n">
-        <v>0.25425</v>
+        <v>-0.24679</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -8044,22 +8044,22 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>115.92</v>
+        <v>241.14</v>
       </c>
       <c r="D318" t="n">
-        <v>159.86</v>
+        <v>298.6</v>
       </c>
       <c r="E318" t="n">
-        <v>37.91</v>
+        <v>23.83</v>
       </c>
       <c r="F318" t="n">
-        <v>-0.77523</v>
+        <v>1.64228</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ABEV</t>
+          <t>MDGL</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -8068,22 +8068,22 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2.78</v>
+        <v>445.04</v>
       </c>
       <c r="D319" t="n">
-        <v>3.03</v>
+        <v>540.0599999999999</v>
       </c>
       <c r="E319" t="n">
-        <v>8.99</v>
+        <v>21.35</v>
       </c>
       <c r="F319" t="n">
-        <v>0.02721</v>
+        <v>2.20142</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ARGX</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -8092,16 +8092,136 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>677.5</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D320" t="n">
-        <v>1001.41</v>
+        <v>112.01</v>
       </c>
       <c r="E320" t="n">
-        <v>47.81</v>
+        <v>18.86</v>
       </c>
       <c r="F320" t="n">
-        <v>-1.79368</v>
+        <v>-0.19592</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="D321" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E321" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="F321" t="n">
+        <v>0.22235</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>FMX</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="D322" t="n">
+        <v>121.26</v>
+      </c>
+      <c r="E322" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="F322" t="n">
+        <v>-0.80715</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>PAG</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>146.17</v>
+      </c>
+      <c r="D323" t="n">
+        <v>217.15</v>
+      </c>
+      <c r="E323" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="F323" t="n">
+        <v>0.01127</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="D324" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="E324" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="F324" t="n">
+        <v>-0.08098</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ABEV</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D325" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E325" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0.02721</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F325"/>
+  <dimension ref="A1:F324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,151 +451,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2876.75</v>
+        <v>21.84</v>
       </c>
       <c r="D2" t="n">
-        <v>2965.52</v>
+        <v>23.34</v>
       </c>
       <c r="E2" t="n">
-        <v>3.09</v>
+        <v>6.87</v>
       </c>
       <c r="F2" t="n">
-        <v>-26.725</v>
+        <v>-0.27475</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.33</v>
+        <v>38.22</v>
       </c>
       <c r="D3" t="n">
-        <v>57.29</v>
+        <v>42.13</v>
       </c>
       <c r="E3" t="n">
-        <v>5.45</v>
+        <v>10.23</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.33941</v>
+        <v>0.37088</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.22</v>
+        <v>17.87</v>
       </c>
       <c r="D4" t="n">
-        <v>41.6</v>
+        <v>21.15</v>
       </c>
       <c r="E4" t="n">
-        <v>8.84</v>
+        <v>18.35</v>
       </c>
       <c r="F4" t="n">
-        <v>0.17365</v>
+        <v>0.44142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.87</v>
+        <v>13.03</v>
       </c>
       <c r="D5" t="n">
-        <v>21.62</v>
+        <v>14.34</v>
       </c>
       <c r="E5" t="n">
-        <v>20.98</v>
+        <v>10.05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.65938</v>
+        <v>-0.1198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>102.63</v>
+        <v>5.67</v>
       </c>
       <c r="D6" t="n">
-        <v>109.08</v>
+        <v>6.94</v>
       </c>
       <c r="E6" t="n">
-        <v>6.28</v>
+        <v>22.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22351</v>
+        <v>0.1411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13.03</v>
+        <v>298.59</v>
       </c>
       <c r="D7" t="n">
-        <v>14.97</v>
+        <v>323.96</v>
       </c>
       <c r="E7" t="n">
-        <v>14.89</v>
+        <v>8.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01791</v>
+        <v>-4.06779</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -604,64 +604,64 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>298.59</v>
+        <v>55.36</v>
       </c>
       <c r="D8" t="n">
-        <v>334.24</v>
+        <v>61.53</v>
       </c>
       <c r="E8" t="n">
-        <v>11.94</v>
+        <v>11.15</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.56324</v>
+        <v>0.65096</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.67</v>
+        <v>141.63</v>
       </c>
       <c r="D9" t="n">
-        <v>7.03</v>
+        <v>152.78</v>
       </c>
       <c r="E9" t="n">
-        <v>23.99</v>
+        <v>7.87</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1648</v>
+        <v>0.47217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>141.63</v>
+        <v>11.23</v>
       </c>
       <c r="D10" t="n">
-        <v>157.31</v>
+        <v>11.85</v>
       </c>
       <c r="E10" t="n">
-        <v>11.07</v>
+        <v>5.52</v>
       </c>
       <c r="F10" t="n">
-        <v>1.11386</v>
+        <v>0.02603</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +679,19 @@
         <v>12.43</v>
       </c>
       <c r="D11" t="n">
-        <v>18.42</v>
+        <v>17.55</v>
       </c>
       <c r="E11" t="n">
-        <v>48.19</v>
+        <v>41.19</v>
       </c>
       <c r="F11" t="n">
-        <v>0.97816</v>
+        <v>0.96113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.23</v>
+        <v>2.98</v>
       </c>
       <c r="D12" t="n">
-        <v>11.89</v>
+        <v>3.6</v>
       </c>
       <c r="E12" t="n">
-        <v>5.88</v>
+        <v>20.81</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03212</v>
+        <v>0.0764</v>
       </c>
     </row>
     <row r="13">
@@ -727,13 +727,13 @@
         <v>7.17</v>
       </c>
       <c r="D13" t="n">
-        <v>8.23</v>
+        <v>8.33</v>
       </c>
       <c r="E13" t="n">
-        <v>14.78</v>
+        <v>16.18</v>
       </c>
       <c r="F13" t="n">
-        <v>0.13527</v>
+        <v>0.15793</v>
       </c>
     </row>
     <row r="14">
@@ -751,43 +751,43 @@
         <v>4.46</v>
       </c>
       <c r="D14" t="n">
-        <v>5.22</v>
+        <v>5.29</v>
       </c>
       <c r="E14" t="n">
-        <v>17.04</v>
+        <v>18.61</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08513999999999999</v>
+        <v>0.09936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>KEP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.98</v>
+        <v>11.18</v>
       </c>
       <c r="D15" t="n">
-        <v>3.54</v>
+        <v>12.21</v>
       </c>
       <c r="E15" t="n">
-        <v>18.79</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06816999999999999</v>
+        <v>0.13627</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>STLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.28</v>
+        <v>5.05</v>
       </c>
       <c r="D16" t="n">
-        <v>19.12</v>
+        <v>5.4</v>
       </c>
       <c r="E16" t="n">
-        <v>10.65</v>
+        <v>6.93</v>
       </c>
       <c r="F16" t="n">
-        <v>0.22309</v>
+        <v>-0.02486</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,190 +820,190 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>98.45</v>
+        <v>17.28</v>
       </c>
       <c r="D17" t="n">
-        <v>122.3</v>
+        <v>18.89</v>
       </c>
       <c r="E17" t="n">
-        <v>24.23</v>
+        <v>9.32</v>
       </c>
       <c r="F17" t="n">
-        <v>2.28707</v>
+        <v>0.20552</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35.54</v>
+        <v>98.45</v>
       </c>
       <c r="D18" t="n">
-        <v>51.29</v>
+        <v>121.1</v>
       </c>
       <c r="E18" t="n">
-        <v>44.32</v>
+        <v>23.01</v>
       </c>
       <c r="F18" t="n">
-        <v>1.98244</v>
+        <v>3.05519</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>VALE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>123.39</v>
+        <v>13.63</v>
       </c>
       <c r="D19" t="n">
-        <v>137.82</v>
+        <v>15.23</v>
       </c>
       <c r="E19" t="n">
-        <v>11.69</v>
+        <v>11.74</v>
       </c>
       <c r="F19" t="n">
-        <v>1.38289</v>
+        <v>0.14495</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63.54</v>
+        <v>52.62</v>
       </c>
       <c r="D20" t="n">
-        <v>70.34</v>
+        <v>57.39</v>
       </c>
       <c r="E20" t="n">
-        <v>10.7</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02608</v>
+        <v>0.73467</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>155.62</v>
+        <v>35.54</v>
       </c>
       <c r="D21" t="n">
-        <v>163.78</v>
+        <v>45.5</v>
       </c>
       <c r="E21" t="n">
-        <v>5.24</v>
+        <v>28.02</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.00319</v>
+        <v>1.51007</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60.35</v>
+        <v>123.39</v>
       </c>
       <c r="D22" t="n">
-        <v>97.42</v>
+        <v>136.61</v>
       </c>
       <c r="E22" t="n">
-        <v>61.43</v>
+        <v>10.71</v>
       </c>
       <c r="F22" t="n">
-        <v>1.96052</v>
+        <v>1.27266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FIGR</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.91</v>
+        <v>60.35</v>
       </c>
       <c r="D23" t="n">
-        <v>35.65</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>43.12</v>
+        <v>50.12</v>
       </c>
       <c r="F23" t="n">
-        <v>0.36343</v>
+        <v>2.03637</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>205.48</v>
+        <v>27.83</v>
       </c>
       <c r="D24" t="n">
-        <v>249.99</v>
+        <v>35.92</v>
       </c>
       <c r="E24" t="n">
-        <v>21.66</v>
+        <v>29.07</v>
       </c>
       <c r="F24" t="n">
-        <v>1.24005</v>
+        <v>0.21349</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1012,46 +1012,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.81</v>
+        <v>205.48</v>
       </c>
       <c r="D25" t="n">
-        <v>10.87</v>
+        <v>248.68</v>
       </c>
       <c r="E25" t="n">
-        <v>39.18</v>
+        <v>21.02</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04366</v>
+        <v>2.43479</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>298.32</v>
+        <v>7.81</v>
       </c>
       <c r="D26" t="n">
-        <v>358.97</v>
+        <v>10.6</v>
       </c>
       <c r="E26" t="n">
-        <v>20.33</v>
+        <v>35.72</v>
       </c>
       <c r="F26" t="n">
-        <v>3.38165</v>
+        <v>0.04089</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>29.31</v>
+        <v>124.05</v>
       </c>
       <c r="D27" t="n">
-        <v>43.17</v>
+        <v>166.4</v>
       </c>
       <c r="E27" t="n">
-        <v>47.29</v>
+        <v>34.14</v>
       </c>
       <c r="F27" t="n">
-        <v>0.92178</v>
+        <v>4.52517</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>AEIS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1084,814 +1084,814 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41.55</v>
+        <v>252.49</v>
       </c>
       <c r="D28" t="n">
-        <v>62.21</v>
+        <v>287.25</v>
       </c>
       <c r="E28" t="n">
-        <v>49.72</v>
+        <v>13.77</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.39774</v>
+        <v>-1.70983</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.28</v>
+        <v>29.31</v>
       </c>
       <c r="D29" t="n">
-        <v>28.1</v>
+        <v>43.83</v>
       </c>
       <c r="E29" t="n">
-        <v>11.16</v>
+        <v>49.54</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01151</v>
+        <v>1.41459</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.03</v>
+        <v>107.01</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72</v>
+        <v>140.37</v>
       </c>
       <c r="E30" t="n">
-        <v>15.32</v>
+        <v>31.17</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.09100999999999999</v>
+        <v>0.26141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>332.02</v>
+        <v>298.32</v>
       </c>
       <c r="D31" t="n">
-        <v>377.94</v>
+        <v>365.44</v>
       </c>
       <c r="E31" t="n">
-        <v>13.83</v>
+        <v>22.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.21821</v>
+        <v>4.70499</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>179.43</v>
+        <v>602.35</v>
       </c>
       <c r="D32" t="n">
-        <v>193.72</v>
+        <v>927.03</v>
       </c>
       <c r="E32" t="n">
-        <v>7.96</v>
+        <v>53.9</v>
       </c>
       <c r="F32" t="n">
-        <v>0.57955</v>
+        <v>27.68843</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.14</v>
+        <v>13.93</v>
       </c>
       <c r="D33" t="n">
-        <v>31.52</v>
+        <v>20.26</v>
       </c>
       <c r="E33" t="n">
-        <v>16.14</v>
+        <v>45.44</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.35749</v>
+        <v>0.19565</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>146.38</v>
+        <v>672.48</v>
       </c>
       <c r="D34" t="n">
-        <v>218.28</v>
+        <v>780.66</v>
       </c>
       <c r="E34" t="n">
-        <v>49.12</v>
+        <v>16.09</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00649</v>
+        <v>-1.09502</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>25.99</v>
+        <v>48.68</v>
       </c>
       <c r="D35" t="n">
-        <v>38.71</v>
+        <v>62.94</v>
       </c>
       <c r="E35" t="n">
-        <v>48.94</v>
+        <v>29.29</v>
       </c>
       <c r="F35" t="n">
-        <v>0.54466</v>
+        <v>0.93229</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>205.77</v>
+        <v>31.19</v>
       </c>
       <c r="D36" t="n">
-        <v>249.09</v>
+        <v>35.84</v>
       </c>
       <c r="E36" t="n">
-        <v>21.05</v>
+        <v>14.91</v>
       </c>
       <c r="F36" t="n">
-        <v>2.72288</v>
+        <v>0.31383</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>440.76</v>
+        <v>114.99</v>
       </c>
       <c r="D37" t="n">
-        <v>637.16</v>
+        <v>150.28</v>
       </c>
       <c r="E37" t="n">
-        <v>44.56</v>
+        <v>30.69</v>
       </c>
       <c r="F37" t="n">
-        <v>1.42976</v>
+        <v>2.96523</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>103.45</v>
+        <v>9.31</v>
       </c>
       <c r="D38" t="n">
-        <v>149.67</v>
+        <v>10.31</v>
       </c>
       <c r="E38" t="n">
-        <v>44.68</v>
+        <v>10.74</v>
       </c>
       <c r="F38" t="n">
-        <v>1.89428</v>
+        <v>0.00165</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>67.59999999999999</v>
+        <v>179.43</v>
       </c>
       <c r="D39" t="n">
-        <v>80.31999999999999</v>
+        <v>190.31</v>
       </c>
       <c r="E39" t="n">
-        <v>18.82</v>
+        <v>6.06</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.45827</v>
+        <v>0.80898</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>198.14</v>
+        <v>205.77</v>
       </c>
       <c r="D40" t="n">
-        <v>261.67</v>
+        <v>243.29</v>
       </c>
       <c r="E40" t="n">
-        <v>32.06</v>
+        <v>18.23</v>
       </c>
       <c r="F40" t="n">
-        <v>2.64766</v>
+        <v>1.22002</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>41.44</v>
+        <v>25.99</v>
       </c>
       <c r="D41" t="n">
-        <v>45.25</v>
+        <v>36.24</v>
       </c>
       <c r="E41" t="n">
-        <v>9.19</v>
+        <v>39.44</v>
       </c>
       <c r="F41" t="n">
-        <v>0.51531</v>
+        <v>0.29568</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>510.39</v>
+        <v>440.76</v>
       </c>
       <c r="D42" t="n">
-        <v>652.39</v>
+        <v>621.17</v>
       </c>
       <c r="E42" t="n">
-        <v>27.82</v>
+        <v>40.93</v>
       </c>
       <c r="F42" t="n">
-        <v>4.4847</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5.04</v>
+        <v>103.45</v>
       </c>
       <c r="D43" t="n">
-        <v>5.95</v>
+        <v>154.12</v>
       </c>
       <c r="E43" t="n">
-        <v>18.06</v>
+        <v>48.98</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05247</v>
+        <v>2.66631</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>GFI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>176.25</v>
+        <v>31.25</v>
       </c>
       <c r="D44" t="n">
-        <v>249.59</v>
+        <v>45.1</v>
       </c>
       <c r="E44" t="n">
-        <v>41.61</v>
+        <v>44.32</v>
       </c>
       <c r="F44" t="n">
-        <v>0.95658</v>
+        <v>0.62857</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>20.87</v>
+        <v>187.36</v>
       </c>
       <c r="D45" t="n">
-        <v>23.47</v>
+        <v>252.28</v>
       </c>
       <c r="E45" t="n">
-        <v>12.46</v>
+        <v>34.65</v>
       </c>
       <c r="F45" t="n">
-        <v>0.00191</v>
+        <v>2.43143</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>40.48</v>
+        <v>14.16</v>
       </c>
       <c r="D46" t="n">
-        <v>44.64</v>
+        <v>20.58</v>
       </c>
       <c r="E46" t="n">
-        <v>10.28</v>
+        <v>45.34</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1977</v>
+        <v>0.16176</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.36</v>
+        <v>89.2</v>
       </c>
       <c r="D47" t="n">
-        <v>33.27</v>
+        <v>126.81</v>
       </c>
       <c r="E47" t="n">
-        <v>36.58</v>
+        <v>42.16</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5132100000000001</v>
+        <v>1.41665</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>31.45</v>
+        <v>136.34</v>
       </c>
       <c r="D48" t="n">
-        <v>36.65</v>
+        <v>200.36</v>
       </c>
       <c r="E48" t="n">
-        <v>16.53</v>
+        <v>46.96</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.014</v>
+        <v>1.09963</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>EGO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>162.11</v>
+        <v>27.73</v>
       </c>
       <c r="D49" t="n">
-        <v>176.94</v>
+        <v>43.75</v>
       </c>
       <c r="E49" t="n">
-        <v>9.15</v>
+        <v>57.77</v>
       </c>
       <c r="F49" t="n">
-        <v>0.35777</v>
+        <v>0.4759</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>SBSW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15.99</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>21.15</v>
+        <v>12.54</v>
       </c>
       <c r="E50" t="n">
-        <v>32.27</v>
+        <v>56.75</v>
       </c>
       <c r="F50" t="n">
-        <v>0.63574</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>14.49</v>
+        <v>28.05</v>
       </c>
       <c r="D51" t="n">
-        <v>19.07</v>
+        <v>36.03</v>
       </c>
       <c r="E51" t="n">
-        <v>31.61</v>
+        <v>28.45</v>
       </c>
       <c r="F51" t="n">
-        <v>0.58389</v>
+        <v>0.23283</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38.92</v>
+        <v>198.14</v>
       </c>
       <c r="D52" t="n">
-        <v>50.32</v>
+        <v>266</v>
       </c>
       <c r="E52" t="n">
-        <v>29.29</v>
+        <v>34.25</v>
       </c>
       <c r="F52" t="n">
-        <v>0.31609</v>
+        <v>3.20426</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>104.89</v>
+        <v>41.44</v>
       </c>
       <c r="D53" t="n">
-        <v>121.23</v>
+        <v>44.85</v>
       </c>
       <c r="E53" t="n">
-        <v>15.58</v>
+        <v>8.23</v>
       </c>
       <c r="F53" t="n">
-        <v>2.10701</v>
+        <v>0.46218</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>40.25</v>
+        <v>510.39</v>
       </c>
       <c r="D54" t="n">
-        <v>49.73</v>
+        <v>650.5700000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>23.55</v>
+        <v>27.47</v>
       </c>
       <c r="F54" t="n">
-        <v>0.77667</v>
+        <v>4.1894</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>GAP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>51.98</v>
+        <v>18.35</v>
       </c>
       <c r="D55" t="n">
-        <v>65.36</v>
+        <v>21.51</v>
       </c>
       <c r="E55" t="n">
-        <v>25.74</v>
+        <v>17.22</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.02228</v>
+        <v>0.07675</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.26</v>
+        <v>5.04</v>
       </c>
       <c r="D56" t="n">
-        <v>19.97</v>
+        <v>6.02</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7</v>
+        <v>19.44</v>
       </c>
       <c r="F56" t="n">
-        <v>0.16925</v>
+        <v>0.05799</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>53.57</v>
+        <v>176.25</v>
       </c>
       <c r="D57" t="n">
-        <v>68.72</v>
+        <v>244.6</v>
       </c>
       <c r="E57" t="n">
-        <v>28.28</v>
+        <v>38.78</v>
       </c>
       <c r="F57" t="n">
-        <v>0.74953</v>
+        <v>1.52885</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>45.57</v>
+        <v>20.87</v>
       </c>
       <c r="D58" t="n">
-        <v>55.4</v>
+        <v>23.39</v>
       </c>
       <c r="E58" t="n">
-        <v>21.57</v>
+        <v>12.07</v>
       </c>
       <c r="F58" t="n">
-        <v>0.48559</v>
+        <v>0.02106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13.01</v>
+        <v>40.48</v>
       </c>
       <c r="D59" t="n">
-        <v>17.53</v>
+        <v>44.71</v>
       </c>
       <c r="E59" t="n">
-        <v>34.74</v>
+        <v>10.45</v>
       </c>
       <c r="F59" t="n">
-        <v>0.37919</v>
+        <v>0.24483</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>110.99</v>
+        <v>24.36</v>
       </c>
       <c r="D60" t="n">
-        <v>131.83</v>
+        <v>33.11</v>
       </c>
       <c r="E60" t="n">
-        <v>18.78</v>
+        <v>35.92</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.18184</v>
+        <v>0.55881</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>17.93</v>
+        <v>162.11</v>
       </c>
       <c r="D61" t="n">
-        <v>23.76</v>
+        <v>177.85</v>
       </c>
       <c r="E61" t="n">
-        <v>32.52</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.28866</v>
+        <v>0.26806</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>171.96</v>
+        <v>13.01</v>
       </c>
       <c r="D62" t="n">
-        <v>205.72</v>
+        <v>17.4</v>
       </c>
       <c r="E62" t="n">
-        <v>19.63</v>
+        <v>33.74</v>
       </c>
       <c r="F62" t="n">
-        <v>1.19691</v>
+        <v>0.39595</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>36.15</v>
+        <v>53.57</v>
       </c>
       <c r="D63" t="n">
-        <v>45.93</v>
+        <v>68.83</v>
       </c>
       <c r="E63" t="n">
-        <v>27.05</v>
+        <v>28.49</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8426</v>
+        <v>0.7410600000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>47.94</v>
+        <v>165.69</v>
       </c>
       <c r="D64" t="n">
-        <v>61.78</v>
+        <v>214.06</v>
       </c>
       <c r="E64" t="n">
-        <v>28.87</v>
+        <v>29.19</v>
       </c>
       <c r="F64" t="n">
-        <v>0.67977</v>
+        <v>3.22174</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>74.8</v>
+        <v>104.89</v>
       </c>
       <c r="D65" t="n">
-        <v>91.14</v>
+        <v>122.41</v>
       </c>
       <c r="E65" t="n">
-        <v>21.84</v>
+        <v>16.7</v>
       </c>
       <c r="F65" t="n">
-        <v>1.02845</v>
+        <v>2.6088</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>165.69</v>
+        <v>45.57</v>
       </c>
       <c r="D66" t="n">
-        <v>212.17</v>
+        <v>56.05</v>
       </c>
       <c r="E66" t="n">
-        <v>28.05</v>
+        <v>23</v>
       </c>
       <c r="F66" t="n">
-        <v>3.14062</v>
+        <v>0.48828</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,22 +2020,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>103.22</v>
+        <v>40.25</v>
       </c>
       <c r="D67" t="n">
-        <v>136.67</v>
+        <v>50.23</v>
       </c>
       <c r="E67" t="n">
-        <v>32.41</v>
+        <v>24.8</v>
       </c>
       <c r="F67" t="n">
-        <v>2.02987</v>
+        <v>0.7184199999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2044,22 +2044,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.99</v>
+        <v>103.22</v>
       </c>
       <c r="D68" t="n">
-        <v>51.29</v>
+        <v>137.35</v>
       </c>
       <c r="E68" t="n">
-        <v>22.15</v>
+        <v>33.07</v>
       </c>
       <c r="F68" t="n">
-        <v>0.38063</v>
+        <v>2.07196</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>20.48</v>
+        <v>47.94</v>
       </c>
       <c r="D69" t="n">
-        <v>26.51</v>
+        <v>61.46</v>
       </c>
       <c r="E69" t="n">
-        <v>29.44</v>
+        <v>28.2</v>
       </c>
       <c r="F69" t="n">
-        <v>0.19225</v>
+        <v>0.6323800000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2092,622 +2092,622 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>31.87</v>
+        <v>171.96</v>
       </c>
       <c r="D70" t="n">
-        <v>45.03</v>
+        <v>204.97</v>
       </c>
       <c r="E70" t="n">
-        <v>41.29</v>
+        <v>19.2</v>
       </c>
       <c r="F70" t="n">
-        <v>0.89874</v>
+        <v>0.6839499999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>124.44</v>
+        <v>45.09</v>
       </c>
       <c r="D71" t="n">
-        <v>195</v>
+        <v>56.06</v>
       </c>
       <c r="E71" t="n">
-        <v>56.7</v>
+        <v>24.33</v>
       </c>
       <c r="F71" t="n">
-        <v>0.72958</v>
+        <v>0.4946</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>55.53</v>
+        <v>31.87</v>
       </c>
       <c r="D72" t="n">
-        <v>60.91</v>
+        <v>44.73</v>
       </c>
       <c r="E72" t="n">
-        <v>9.69</v>
+        <v>40.35</v>
       </c>
       <c r="F72" t="n">
-        <v>0.22128</v>
+        <v>0.83755</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>62.05</v>
+        <v>38.92</v>
       </c>
       <c r="D73" t="n">
-        <v>81.22</v>
+        <v>50.07</v>
       </c>
       <c r="E73" t="n">
-        <v>30.89</v>
+        <v>28.65</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.5008899999999999</v>
+        <v>0.41042</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13.31</v>
+        <v>17.26</v>
       </c>
       <c r="D74" t="n">
-        <v>25.76</v>
+        <v>19.9</v>
       </c>
       <c r="E74" t="n">
-        <v>93.54000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="F74" t="n">
-        <v>0.71191</v>
+        <v>0.16707</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13.43</v>
+        <v>17.93</v>
       </c>
       <c r="D75" t="n">
-        <v>15.26</v>
+        <v>23.78</v>
       </c>
       <c r="E75" t="n">
-        <v>13.63</v>
+        <v>32.63</v>
       </c>
       <c r="F75" t="n">
-        <v>0.08839</v>
+        <v>0.30747</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>38.73</v>
+        <v>36.15</v>
       </c>
       <c r="D76" t="n">
-        <v>64.09999999999999</v>
+        <v>46.1</v>
       </c>
       <c r="E76" t="n">
-        <v>65.5</v>
+        <v>27.52</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.10866</v>
+        <v>0.82077</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>167.73</v>
+        <v>74.8</v>
       </c>
       <c r="D77" t="n">
-        <v>182.9</v>
+        <v>91.89</v>
       </c>
       <c r="E77" t="n">
-        <v>9.039999999999999</v>
+        <v>22.85</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.58001</v>
+        <v>1.02724</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>218.58</v>
+        <v>41.99</v>
       </c>
       <c r="D78" t="n">
-        <v>280.46</v>
+        <v>50.61</v>
       </c>
       <c r="E78" t="n">
-        <v>28.31</v>
+        <v>20.53</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2297</v>
+        <v>0.32806</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>122.91</v>
+        <v>20.48</v>
       </c>
       <c r="D79" t="n">
-        <v>157.75</v>
+        <v>26.06</v>
       </c>
       <c r="E79" t="n">
-        <v>28.35</v>
+        <v>27.25</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.37771</v>
+        <v>0.11669</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7.67</v>
+        <v>236.5</v>
       </c>
       <c r="D80" t="n">
-        <v>9.199999999999999</v>
+        <v>284.75</v>
       </c>
       <c r="E80" t="n">
-        <v>19.95</v>
+        <v>20.4</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1771</v>
+        <v>3.75135</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>135.44</v>
+        <v>14.49</v>
       </c>
       <c r="D81" t="n">
-        <v>174.39</v>
+        <v>19.11</v>
       </c>
       <c r="E81" t="n">
-        <v>28.76</v>
+        <v>31.88</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.62645</v>
+        <v>0.62325</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>136.06</v>
+        <v>15.99</v>
       </c>
       <c r="D82" t="n">
-        <v>165.08</v>
+        <v>21.2</v>
       </c>
       <c r="E82" t="n">
-        <v>21.33</v>
+        <v>32.58</v>
       </c>
       <c r="F82" t="n">
-        <v>1.65744</v>
+        <v>0.66898</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>18.94</v>
+        <v>124.44</v>
       </c>
       <c r="D83" t="n">
-        <v>23.74</v>
+        <v>183.9</v>
       </c>
       <c r="E83" t="n">
-        <v>25.34</v>
+        <v>47.78</v>
       </c>
       <c r="F83" t="n">
-        <v>0.19609</v>
+        <v>-0.87468</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>31.03</v>
+        <v>55.53</v>
       </c>
       <c r="D84" t="n">
-        <v>44.54</v>
+        <v>58.49</v>
       </c>
       <c r="E84" t="n">
-        <v>43.54</v>
+        <v>5.33</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9863499999999999</v>
+        <v>-0.14595</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>56.4</v>
+        <v>13.31</v>
       </c>
       <c r="D85" t="n">
-        <v>80.81</v>
+        <v>25.03</v>
       </c>
       <c r="E85" t="n">
-        <v>43.28</v>
+        <v>88.05</v>
       </c>
       <c r="F85" t="n">
-        <v>1.6696</v>
+        <v>0.68264</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>82.31</v>
+        <v>13.43</v>
       </c>
       <c r="D86" t="n">
-        <v>136.94</v>
+        <v>14.94</v>
       </c>
       <c r="E86" t="n">
-        <v>66.37</v>
+        <v>11.24</v>
       </c>
       <c r="F86" t="n">
-        <v>3.45518</v>
+        <v>0.07875</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>39.54</v>
+        <v>167.73</v>
       </c>
       <c r="D87" t="n">
-        <v>51.41</v>
+        <v>182.33</v>
       </c>
       <c r="E87" t="n">
-        <v>30.02</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>0.11249</v>
+        <v>-0.7684299999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>76.53</v>
+        <v>136.06</v>
       </c>
       <c r="D88" t="n">
-        <v>96.45</v>
+        <v>165.99</v>
       </c>
       <c r="E88" t="n">
-        <v>26.03</v>
+        <v>22</v>
       </c>
       <c r="F88" t="n">
-        <v>1.45245</v>
+        <v>1.36664</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>107.27</v>
+        <v>7.67</v>
       </c>
       <c r="D89" t="n">
-        <v>173.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E89" t="n">
-        <v>61.56</v>
+        <v>22.03</v>
       </c>
       <c r="F89" t="n">
-        <v>-1.05801</v>
+        <v>0.1989</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>59.71</v>
+        <v>218.58</v>
       </c>
       <c r="D90" t="n">
-        <v>79.11</v>
+        <v>275.54</v>
       </c>
       <c r="E90" t="n">
-        <v>32.49</v>
+        <v>26.06</v>
       </c>
       <c r="F90" t="n">
-        <v>0.59687</v>
+        <v>0.01914</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EDU</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>44.44</v>
+        <v>18.94</v>
       </c>
       <c r="D91" t="n">
-        <v>56.82</v>
+        <v>23.69</v>
       </c>
       <c r="E91" t="n">
-        <v>27.86</v>
+        <v>25.08</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.38143</v>
+        <v>0.18936</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>255.07</v>
+        <v>76.53</v>
       </c>
       <c r="D92" t="n">
-        <v>339.15</v>
+        <v>96.77</v>
       </c>
       <c r="E92" t="n">
-        <v>32.96</v>
+        <v>26.45</v>
       </c>
       <c r="F92" t="n">
-        <v>-6.00233</v>
+        <v>1.4864</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>19.32</v>
+        <v>82.31</v>
       </c>
       <c r="D93" t="n">
-        <v>24.47</v>
+        <v>130.97</v>
       </c>
       <c r="E93" t="n">
-        <v>26.66</v>
+        <v>59.12</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.0342</v>
+        <v>3.77468</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>166.5</v>
+        <v>56.4</v>
       </c>
       <c r="D94" t="n">
-        <v>197.56</v>
+        <v>78.87</v>
       </c>
       <c r="E94" t="n">
-        <v>18.65</v>
+        <v>39.84</v>
       </c>
       <c r="F94" t="n">
-        <v>0.66935</v>
+        <v>1.3485</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>42.46</v>
+        <v>31.03</v>
       </c>
       <c r="D95" t="n">
-        <v>69.76000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="E95" t="n">
-        <v>64.3</v>
+        <v>44.38</v>
       </c>
       <c r="F95" t="n">
-        <v>1.2992</v>
+        <v>0.96912</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2716,22 +2716,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>170.28</v>
+        <v>42.46</v>
       </c>
       <c r="D96" t="n">
-        <v>250.61</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E96" t="n">
-        <v>47.18</v>
+        <v>54.62</v>
       </c>
       <c r="F96" t="n">
-        <v>-2.75775</v>
+        <v>0.94333</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2740,16 +2740,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>142.52</v>
+        <v>59.71</v>
       </c>
       <c r="D97" t="n">
-        <v>191.45</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E97" t="n">
-        <v>34.33</v>
+        <v>27.11</v>
       </c>
       <c r="F97" t="n">
-        <v>1.43195</v>
+        <v>-0.07714</v>
       </c>
     </row>
     <row r="98">
@@ -2767,19 +2767,19 @@
         <v>352.83</v>
       </c>
       <c r="D98" t="n">
-        <v>505.41</v>
+        <v>495.63</v>
       </c>
       <c r="E98" t="n">
-        <v>43.24</v>
+        <v>40.47</v>
       </c>
       <c r="F98" t="n">
-        <v>2.09735</v>
+        <v>1.11181</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2788,22 +2788,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>136.68</v>
+        <v>49.87</v>
       </c>
       <c r="D99" t="n">
-        <v>153.4</v>
+        <v>61.42</v>
       </c>
       <c r="E99" t="n">
-        <v>12.23</v>
+        <v>23.16</v>
       </c>
       <c r="F99" t="n">
-        <v>-2.51046</v>
+        <v>-0.11501</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2812,22 +2812,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>49.87</v>
+        <v>166.5</v>
       </c>
       <c r="D100" t="n">
-        <v>63.17</v>
+        <v>198.2</v>
       </c>
       <c r="E100" t="n">
-        <v>26.67</v>
+        <v>19.04</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2007</v>
+        <v>0.09665</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2836,40 +2836,40 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>44.39</v>
+        <v>19.32</v>
       </c>
       <c r="D101" t="n">
-        <v>61.14</v>
+        <v>23.9</v>
       </c>
       <c r="E101" t="n">
-        <v>37.73</v>
+        <v>23.71</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.05927</v>
+        <v>-0.13674</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10.51</v>
+        <v>142.52</v>
       </c>
       <c r="D102" t="n">
-        <v>15.27</v>
+        <v>175.26</v>
       </c>
       <c r="E102" t="n">
-        <v>45.29</v>
+        <v>22.97</v>
       </c>
       <c r="F102" t="n">
-        <v>0.40451</v>
+        <v>0.26584</v>
       </c>
     </row>
     <row r="103">
@@ -2887,13 +2887,13 @@
         <v>62.12</v>
       </c>
       <c r="D103" t="n">
-        <v>79.13</v>
+        <v>77.67</v>
       </c>
       <c r="E103" t="n">
-        <v>27.38</v>
+        <v>25.03</v>
       </c>
       <c r="F103" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.6581</v>
       </c>
     </row>
     <row r="104">
@@ -2911,115 +2911,115 @@
         <v>60.37</v>
       </c>
       <c r="D104" t="n">
-        <v>77</v>
+        <v>78.45</v>
       </c>
       <c r="E104" t="n">
-        <v>27.55</v>
+        <v>29.95</v>
       </c>
       <c r="F104" t="n">
-        <v>1.31187</v>
+        <v>1.83733</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>102.17</v>
+        <v>36.09</v>
       </c>
       <c r="D105" t="n">
-        <v>131.24</v>
+        <v>38.9</v>
       </c>
       <c r="E105" t="n">
-        <v>28.45</v>
+        <v>7.79</v>
       </c>
       <c r="F105" t="n">
-        <v>1.86006</v>
+        <v>0.13144</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>48.79</v>
+        <v>10.51</v>
       </c>
       <c r="D106" t="n">
-        <v>68.53</v>
+        <v>15.8</v>
       </c>
       <c r="E106" t="n">
-        <v>40.46</v>
+        <v>50.33</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.01588</v>
+        <v>0.39025</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>76.04000000000001</v>
+        <v>48.79</v>
       </c>
       <c r="D107" t="n">
-        <v>123.61</v>
+        <v>65.94</v>
       </c>
       <c r="E107" t="n">
-        <v>62.56</v>
+        <v>35.15</v>
       </c>
       <c r="F107" t="n">
-        <v>2.41344</v>
+        <v>-0.36491</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>30.83</v>
+        <v>102.17</v>
       </c>
       <c r="D108" t="n">
-        <v>35.72</v>
+        <v>133.07</v>
       </c>
       <c r="E108" t="n">
-        <v>15.86</v>
+        <v>30.24</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.35242</v>
+        <v>2.38111</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3028,22 +3028,22 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>83.81999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D109" t="n">
-        <v>95.31</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>13.71</v>
+        <v>30.78</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.43033</v>
+        <v>-0.77002</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>275.27</v>
+        <v>150.12</v>
       </c>
       <c r="D110" t="n">
-        <v>359.54</v>
+        <v>247.72</v>
       </c>
       <c r="E110" t="n">
-        <v>30.61</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.74832</v>
+        <v>6.07809</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3076,2998 +3076,2998 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>125.73</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D111" t="n">
-        <v>197.07</v>
+        <v>117.91</v>
       </c>
       <c r="E111" t="n">
-        <v>56.74</v>
+        <v>55.06</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.80321</v>
+        <v>1.7938</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>150.12</v>
+        <v>141.17</v>
       </c>
       <c r="D112" t="n">
-        <v>259.43</v>
+        <v>174.83</v>
       </c>
       <c r="E112" t="n">
-        <v>72.81999999999999</v>
+        <v>23.84</v>
       </c>
       <c r="F112" t="n">
-        <v>6.48113</v>
+        <v>1.12639</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>74.98999999999999</v>
+        <v>33.22</v>
       </c>
       <c r="D113" t="n">
-        <v>104.47</v>
+        <v>38.43</v>
       </c>
       <c r="E113" t="n">
-        <v>39.31</v>
+        <v>15.68</v>
       </c>
       <c r="F113" t="n">
-        <v>0.40712</v>
+        <v>0.28995</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>140.71</v>
+        <v>32.47</v>
       </c>
       <c r="D114" t="n">
-        <v>182.91</v>
+        <v>38.04</v>
       </c>
       <c r="E114" t="n">
-        <v>29.99</v>
+        <v>17.15</v>
       </c>
       <c r="F114" t="n">
-        <v>-1.36471</v>
+        <v>0.14645</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>76.55</v>
+        <v>450.75</v>
       </c>
       <c r="D115" t="n">
-        <v>105.82</v>
+        <v>546.78</v>
       </c>
       <c r="E115" t="n">
-        <v>38.23</v>
+        <v>21.3</v>
       </c>
       <c r="F115" t="n">
-        <v>-1.58394</v>
+        <v>2.73475</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>123.42</v>
+        <v>16.44</v>
       </c>
       <c r="D116" t="n">
-        <v>164.55</v>
+        <v>33</v>
       </c>
       <c r="E116" t="n">
-        <v>33.33</v>
+        <v>100.73</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.65884</v>
+        <v>0.4888</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>141.17</v>
+        <v>53.82</v>
       </c>
       <c r="D117" t="n">
-        <v>173.25</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>22.72</v>
+        <v>40.26</v>
       </c>
       <c r="F117" t="n">
-        <v>1.14864</v>
+        <v>0.47907</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>61.28</v>
+        <v>19.82</v>
       </c>
       <c r="D118" t="n">
-        <v>72.91</v>
+        <v>25.19</v>
       </c>
       <c r="E118" t="n">
-        <v>18.98</v>
+        <v>27.09</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.98211</v>
+        <v>0.59848</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>48.87</v>
+        <v>91.88</v>
       </c>
       <c r="D119" t="n">
-        <v>58.74</v>
+        <v>129.41</v>
       </c>
       <c r="E119" t="n">
-        <v>20.2</v>
+        <v>40.85</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.40747</v>
+        <v>1.61547</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>450.75</v>
+        <v>2.86</v>
       </c>
       <c r="D120" t="n">
-        <v>548.65</v>
+        <v>3.2</v>
       </c>
       <c r="E120" t="n">
-        <v>21.72</v>
+        <v>11.89</v>
       </c>
       <c r="F120" t="n">
-        <v>2.41907</v>
+        <v>0.02074</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>32.47</v>
+        <v>14.05</v>
       </c>
       <c r="D121" t="n">
-        <v>38.43</v>
+        <v>19.78</v>
       </c>
       <c r="E121" t="n">
-        <v>18.36</v>
+        <v>40.78</v>
       </c>
       <c r="F121" t="n">
-        <v>0.22774</v>
+        <v>0.23666</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>147.13</v>
+        <v>14.94</v>
       </c>
       <c r="D122" t="n">
-        <v>174.93</v>
+        <v>19.86</v>
       </c>
       <c r="E122" t="n">
-        <v>18.89</v>
+        <v>32.93</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.59992</v>
+        <v>0.61757</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>62.47</v>
+        <v>205.81</v>
       </c>
       <c r="D123" t="n">
-        <v>90.19</v>
+        <v>263.52</v>
       </c>
       <c r="E123" t="n">
-        <v>44.37</v>
+        <v>28.04</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.65359</v>
+        <v>2.01368</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>53.82</v>
+        <v>361.32</v>
       </c>
       <c r="D124" t="n">
-        <v>75</v>
+        <v>426.94</v>
       </c>
       <c r="E124" t="n">
-        <v>39.35</v>
+        <v>18.16</v>
       </c>
       <c r="F124" t="n">
-        <v>0.53725</v>
+        <v>2.42172</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>121.48</v>
+        <v>161.37</v>
       </c>
       <c r="D125" t="n">
-        <v>146.41</v>
+        <v>263.69</v>
       </c>
       <c r="E125" t="n">
-        <v>20.52</v>
+        <v>63.41</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04863</v>
+        <v>0.33828</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2.86</v>
+        <v>43.67</v>
       </c>
       <c r="D126" t="n">
-        <v>3.18</v>
+        <v>46.99</v>
       </c>
       <c r="E126" t="n">
-        <v>11.19</v>
+        <v>7.6</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02543</v>
+        <v>0.02819</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>19.82</v>
+        <v>15.03</v>
       </c>
       <c r="D127" t="n">
-        <v>25.05</v>
+        <v>18.26</v>
       </c>
       <c r="E127" t="n">
-        <v>26.39</v>
+        <v>21.49</v>
       </c>
       <c r="F127" t="n">
-        <v>0.40053</v>
+        <v>0.06938</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>14.94</v>
+        <v>140.19</v>
       </c>
       <c r="D128" t="n">
-        <v>19.59</v>
+        <v>145.27</v>
       </c>
       <c r="E128" t="n">
-        <v>31.16</v>
+        <v>3.62</v>
       </c>
       <c r="F128" t="n">
-        <v>0.52114</v>
+        <v>-0.49238</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>16.44</v>
+        <v>195.11</v>
       </c>
       <c r="D129" t="n">
-        <v>33.97</v>
+        <v>248.72</v>
       </c>
       <c r="E129" t="n">
-        <v>106.63</v>
+        <v>27.48</v>
       </c>
       <c r="F129" t="n">
-        <v>0.60034</v>
+        <v>0.26006</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>91.88</v>
+        <v>68.77</v>
       </c>
       <c r="D130" t="n">
-        <v>125.3</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>36.37</v>
+        <v>19.54</v>
       </c>
       <c r="F130" t="n">
-        <v>1.50067</v>
+        <v>-0.70053</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABVX</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>361.32</v>
+        <v>72.5</v>
       </c>
       <c r="D131" t="n">
-        <v>425.49</v>
+        <v>118.64</v>
       </c>
       <c r="E131" t="n">
-        <v>17.76</v>
+        <v>63.64</v>
       </c>
       <c r="F131" t="n">
-        <v>4.42632</v>
+        <v>0.29802</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>205.81</v>
+        <v>275.99</v>
       </c>
       <c r="D132" t="n">
-        <v>264.92</v>
+        <v>322.82</v>
       </c>
       <c r="E132" t="n">
-        <v>28.72</v>
+        <v>16.97</v>
       </c>
       <c r="F132" t="n">
-        <v>1.32952</v>
+        <v>1.51503</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>28.18</v>
+        <v>9.85</v>
       </c>
       <c r="D133" t="n">
-        <v>37.03</v>
+        <v>13.58</v>
       </c>
       <c r="E133" t="n">
-        <v>31.41</v>
+        <v>37.87</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.01107</v>
+        <v>0.5505</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>43.67</v>
+        <v>33.54</v>
       </c>
       <c r="D134" t="n">
-        <v>47.34</v>
+        <v>42.85</v>
       </c>
       <c r="E134" t="n">
-        <v>8.4</v>
+        <v>27.76</v>
       </c>
       <c r="F134" t="n">
-        <v>0.05503</v>
+        <v>0.17598</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>161.37</v>
+        <v>63.54</v>
       </c>
       <c r="D135" t="n">
-        <v>264.51</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E135" t="n">
-        <v>63.92</v>
+        <v>10.01</v>
       </c>
       <c r="F135" t="n">
-        <v>0.82511</v>
+        <v>0.1817</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>55.05</v>
+        <v>190.4</v>
       </c>
       <c r="D136" t="n">
-        <v>63.57</v>
+        <v>217.62</v>
       </c>
       <c r="E136" t="n">
-        <v>15.48</v>
+        <v>14.3</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.4736</v>
+        <v>-0.59803</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>IDCC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>72.55</v>
+        <v>250.75</v>
       </c>
       <c r="D137" t="n">
-        <v>76.29000000000001</v>
+        <v>350.13</v>
       </c>
       <c r="E137" t="n">
-        <v>5.16</v>
+        <v>39.63</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.36496</v>
+        <v>4.34655</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>195.11</v>
+        <v>529.12</v>
       </c>
       <c r="D138" t="n">
-        <v>249.05</v>
+        <v>675.74</v>
       </c>
       <c r="E138" t="n">
-        <v>27.65</v>
+        <v>27.71</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4172</v>
+        <v>10.73877</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>SGI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>15.03</v>
+        <v>61.49</v>
       </c>
       <c r="D139" t="n">
-        <v>18.6</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="E139" t="n">
-        <v>23.75</v>
+        <v>8.57</v>
       </c>
       <c r="F139" t="n">
-        <v>0.08944000000000001</v>
+        <v>0.42927</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>140.19</v>
+        <v>196.07</v>
       </c>
       <c r="D140" t="n">
-        <v>146.13</v>
+        <v>211.96</v>
       </c>
       <c r="E140" t="n">
-        <v>4.24</v>
+        <v>8.1</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.3931</v>
+        <v>0.04079</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>207.24</v>
+        <v>108.01</v>
       </c>
       <c r="D141" t="n">
-        <v>253.88</v>
+        <v>126.94</v>
       </c>
       <c r="E141" t="n">
-        <v>22.51</v>
+        <v>17.53</v>
       </c>
       <c r="F141" t="n">
-        <v>-2.67569</v>
+        <v>0.60472</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>277.69</v>
+        <v>134.71</v>
       </c>
       <c r="D142" t="n">
-        <v>330.62</v>
+        <v>148.38</v>
       </c>
       <c r="E142" t="n">
-        <v>19.06</v>
+        <v>10.15</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.14398</v>
+        <v>2.1441</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>BMRN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>275.99</v>
+        <v>49.67</v>
       </c>
       <c r="D143" t="n">
-        <v>322.99</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E143" t="n">
-        <v>17.03</v>
+        <v>32.23</v>
       </c>
       <c r="F143" t="n">
-        <v>1.92883</v>
+        <v>-0.14491</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>73.75</v>
+        <v>26.18</v>
       </c>
       <c r="D144" t="n">
-        <v>93.8</v>
+        <v>36.49</v>
       </c>
       <c r="E144" t="n">
-        <v>27.19</v>
+        <v>39.38</v>
       </c>
       <c r="F144" t="n">
-        <v>0.31456</v>
+        <v>0.03658</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>36.25</v>
+        <v>438.34</v>
       </c>
       <c r="D145" t="n">
-        <v>41.61</v>
+        <v>609.8200000000001</v>
       </c>
       <c r="E145" t="n">
-        <v>14.79</v>
+        <v>39.12</v>
       </c>
       <c r="F145" t="n">
-        <v>0.22556</v>
+        <v>-0.56321</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>121.13</v>
+        <v>63.16</v>
       </c>
       <c r="D146" t="n">
-        <v>138.92</v>
+        <v>102.04</v>
       </c>
       <c r="E146" t="n">
-        <v>14.69</v>
+        <v>61.56</v>
       </c>
       <c r="F146" t="n">
-        <v>0.41111</v>
+        <v>1.24569</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>9.85</v>
+        <v>225.75</v>
       </c>
       <c r="D147" t="n">
-        <v>13.75</v>
+        <v>282.67</v>
       </c>
       <c r="E147" t="n">
-        <v>39.59</v>
+        <v>25.21</v>
       </c>
       <c r="F147" t="n">
-        <v>0.51236</v>
+        <v>-3.23344</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>309.78</v>
+        <v>73.42</v>
       </c>
       <c r="D148" t="n">
-        <v>341.85</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="E148" t="n">
-        <v>10.35</v>
+        <v>22.98</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.13236</v>
+        <v>0.77528</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>132.79</v>
+        <v>92.38</v>
       </c>
       <c r="D149" t="n">
-        <v>163.39</v>
+        <v>100.56</v>
       </c>
       <c r="E149" t="n">
-        <v>23.04</v>
+        <v>8.85</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.12699</v>
+        <v>-0.08179</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>33.54</v>
+        <v>163.43</v>
       </c>
       <c r="D150" t="n">
-        <v>42.61</v>
+        <v>192.61</v>
       </c>
       <c r="E150" t="n">
-        <v>27.04</v>
+        <v>17.85</v>
       </c>
       <c r="F150" t="n">
-        <v>0.13446</v>
+        <v>-0.61748</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C151" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="D151" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E151" t="n">
         <v>63.54</v>
       </c>
-      <c r="D151" t="n">
-        <v>70.87</v>
-      </c>
-      <c r="E151" t="n">
-        <v>11.54</v>
-      </c>
       <c r="F151" t="n">
-        <v>0.26916</v>
+        <v>1.21071</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>190.4</v>
+        <v>163.55</v>
       </c>
       <c r="D152" t="n">
-        <v>221.02</v>
+        <v>201.5</v>
       </c>
       <c r="E152" t="n">
-        <v>16.08</v>
+        <v>23.2</v>
       </c>
       <c r="F152" t="n">
-        <v>0.04179</v>
+        <v>-0.56516</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>MKC-V</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>250.75</v>
+        <v>45.59</v>
       </c>
       <c r="D153" t="n">
-        <v>340.38</v>
+        <v>56.53</v>
       </c>
       <c r="E153" t="n">
-        <v>35.74</v>
+        <v>24</v>
       </c>
       <c r="F153" t="n">
-        <v>3.87926</v>
+        <v>0.71097</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>529.12</v>
+        <v>99.3</v>
       </c>
       <c r="D154" t="n">
-        <v>681.46</v>
+        <v>153.79</v>
       </c>
       <c r="E154" t="n">
-        <v>28.79</v>
+        <v>54.87</v>
       </c>
       <c r="F154" t="n">
-        <v>9.785550000000001</v>
+        <v>0.5426299999999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SGI</t>
+          <t>BSAC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>61.49</v>
+        <v>29.79</v>
       </c>
       <c r="D155" t="n">
-        <v>68.12</v>
+        <v>35.19</v>
       </c>
       <c r="E155" t="n">
-        <v>10.78</v>
+        <v>18.13</v>
       </c>
       <c r="F155" t="n">
-        <v>0.25125</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>57.4</v>
+        <v>197.73</v>
       </c>
       <c r="D156" t="n">
-        <v>104.79</v>
+        <v>222.74</v>
       </c>
       <c r="E156" t="n">
-        <v>82.56</v>
+        <v>12.65</v>
       </c>
       <c r="F156" t="n">
-        <v>0.21284</v>
+        <v>0.63872</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BMRN</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>49.67</v>
+        <v>12.64</v>
       </c>
       <c r="D157" t="n">
-        <v>66.41</v>
+        <v>17.75</v>
       </c>
       <c r="E157" t="n">
-        <v>33.7</v>
+        <v>40.43</v>
       </c>
       <c r="F157" t="n">
-        <v>0.03841</v>
+        <v>0.27258</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>186.61</v>
+        <v>255.54</v>
       </c>
       <c r="D158" t="n">
-        <v>237.89</v>
+        <v>365.08</v>
       </c>
       <c r="E158" t="n">
-        <v>27.48</v>
+        <v>42.87</v>
       </c>
       <c r="F158" t="n">
-        <v>-1.00997</v>
+        <v>3.6115</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>MPLX</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>63.16</v>
+        <v>54</v>
       </c>
       <c r="D159" t="n">
-        <v>101.84</v>
+        <v>59.84</v>
       </c>
       <c r="E159" t="n">
-        <v>61.24</v>
+        <v>10.81</v>
       </c>
       <c r="F159" t="n">
-        <v>1.43086</v>
+        <v>0.28289</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5563.62</v>
+        <v>32.32</v>
       </c>
       <c r="D160" t="n">
-        <v>6299.56</v>
+        <v>37.99</v>
       </c>
       <c r="E160" t="n">
-        <v>13.23</v>
+        <v>17.54</v>
       </c>
       <c r="F160" t="n">
-        <v>-44.26965</v>
+        <v>0.23389</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>43.3</v>
+        <v>699965</v>
       </c>
       <c r="D161" t="n">
-        <v>72.27</v>
+        <v>771770</v>
       </c>
       <c r="E161" t="n">
-        <v>66.91</v>
+        <v>10.26</v>
       </c>
       <c r="F161" t="n">
-        <v>-0</v>
+        <v>2523.34448</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>73.42</v>
+        <v>139.71</v>
       </c>
       <c r="D162" t="n">
-        <v>88.70999999999999</v>
+        <v>192.6</v>
       </c>
       <c r="E162" t="n">
-        <v>20.83</v>
+        <v>37.86</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7728699999999999</v>
+        <v>1.1005</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>92.38</v>
+        <v>45.37</v>
       </c>
       <c r="D163" t="n">
-        <v>100.65</v>
+        <v>143.97</v>
       </c>
       <c r="E163" t="n">
-        <v>8.949999999999999</v>
+        <v>217.32</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.07876</v>
+        <v>5.1164</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>438.34</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D164" t="n">
-        <v>613.62</v>
+        <v>124.31</v>
       </c>
       <c r="E164" t="n">
-        <v>39.99</v>
+        <v>51.12</v>
       </c>
       <c r="F164" t="n">
-        <v>0.49995</v>
+        <v>-0.05317</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>26.18</v>
+        <v>156.66</v>
       </c>
       <c r="D165" t="n">
-        <v>36.71</v>
+        <v>261.77</v>
       </c>
       <c r="E165" t="n">
-        <v>40.22</v>
+        <v>67.09</v>
       </c>
       <c r="F165" t="n">
-        <v>0.135</v>
+        <v>1.57783</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>163.43</v>
+        <v>13.06</v>
       </c>
       <c r="D166" t="n">
-        <v>200.67</v>
+        <v>19.65</v>
       </c>
       <c r="E166" t="n">
-        <v>22.79</v>
+        <v>50.46</v>
       </c>
       <c r="F166" t="n">
-        <v>0.62133</v>
+        <v>-0.07116</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>156.84</v>
+        <v>197.38</v>
       </c>
       <c r="D167" t="n">
-        <v>187.03</v>
+        <v>257.12</v>
       </c>
       <c r="E167" t="n">
-        <v>19.25</v>
+        <v>30.27</v>
       </c>
       <c r="F167" t="n">
-        <v>-2.68499</v>
+        <v>-1.42463</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>101.75</v>
+        <v>56.06</v>
       </c>
       <c r="D168" t="n">
-        <v>129.17</v>
+        <v>62.44</v>
       </c>
       <c r="E168" t="n">
-        <v>26.95</v>
+        <v>11.38</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.25082</v>
+        <v>-0.03757</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>55.52</v>
+        <v>465.4</v>
       </c>
       <c r="D169" t="n">
-        <v>94.83</v>
+        <v>510.37</v>
       </c>
       <c r="E169" t="n">
-        <v>70.8</v>
+        <v>9.66</v>
       </c>
       <c r="F169" t="n">
-        <v>1.61921</v>
+        <v>0.88445</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>99.3</v>
+        <v>153.25</v>
       </c>
       <c r="D170" t="n">
-        <v>151.7</v>
+        <v>191.06</v>
       </c>
       <c r="E170" t="n">
-        <v>52.77</v>
+        <v>24.67</v>
       </c>
       <c r="F170" t="n">
-        <v>1.17857</v>
+        <v>-0.11953</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>725.17</v>
+        <v>231.51</v>
       </c>
       <c r="D171" t="n">
-        <v>910.95</v>
+        <v>290.25</v>
       </c>
       <c r="E171" t="n">
-        <v>25.62</v>
+        <v>25.37</v>
       </c>
       <c r="F171" t="n">
-        <v>1.91142</v>
+        <v>1.4568</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>197.73</v>
+        <v>20.96</v>
       </c>
       <c r="D172" t="n">
-        <v>225.85</v>
+        <v>26.1</v>
       </c>
       <c r="E172" t="n">
-        <v>14.22</v>
+        <v>24.52</v>
       </c>
       <c r="F172" t="n">
-        <v>0.9798</v>
+        <v>0.32599</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>68.98999999999999</v>
+        <v>155.75</v>
       </c>
       <c r="D173" t="n">
-        <v>88.93000000000001</v>
+        <v>259.47</v>
       </c>
       <c r="E173" t="n">
-        <v>28.9</v>
+        <v>66.59</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.34243</v>
+        <v>6.56374</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>255.54</v>
+        <v>213.69</v>
       </c>
       <c r="D174" t="n">
-        <v>365.08</v>
+        <v>395.93</v>
       </c>
       <c r="E174" t="n">
-        <v>42.87</v>
+        <v>85.28</v>
       </c>
       <c r="F174" t="n">
-        <v>3.6115</v>
+        <v>11.53328</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>383.99</v>
+        <v>40.59</v>
       </c>
       <c r="D175" t="n">
-        <v>474.13</v>
+        <v>55.55</v>
       </c>
       <c r="E175" t="n">
-        <v>23.47</v>
+        <v>36.86</v>
       </c>
       <c r="F175" t="n">
-        <v>-1.53084</v>
+        <v>1.21178</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>12.64</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="D176" t="n">
-        <v>17.74</v>
+        <v>96.62</v>
       </c>
       <c r="E176" t="n">
-        <v>40.35</v>
+        <v>15.7</v>
       </c>
       <c r="F176" t="n">
-        <v>0.24281</v>
+        <v>0.7579900000000001</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>417.83</v>
+        <v>223.65</v>
       </c>
       <c r="D177" t="n">
-        <v>556.3099999999999</v>
+        <v>390.42</v>
       </c>
       <c r="E177" t="n">
-        <v>33.14</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="F177" t="n">
-        <v>0.43871</v>
+        <v>13.30066</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>32.32</v>
+        <v>128.43</v>
       </c>
       <c r="D178" t="n">
-        <v>37.72</v>
+        <v>147.36</v>
       </c>
       <c r="E178" t="n">
-        <v>16.71</v>
+        <v>14.74</v>
       </c>
       <c r="F178" t="n">
-        <v>0.15923</v>
+        <v>0.39775</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>252.74</v>
+        <v>18.71</v>
       </c>
       <c r="D179" t="n">
-        <v>326.23</v>
+        <v>21.55</v>
       </c>
       <c r="E179" t="n">
-        <v>29.08</v>
+        <v>15.18</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.21978</v>
+        <v>0.15383</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>699965</v>
+        <v>66.95</v>
       </c>
       <c r="D180" t="n">
-        <v>771770</v>
+        <v>86.72</v>
       </c>
       <c r="E180" t="n">
-        <v>10.26</v>
+        <v>29.53</v>
       </c>
       <c r="F180" t="n">
-        <v>2523.34448</v>
+        <v>1.46018</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>WES</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>139.71</v>
+        <v>40.41</v>
       </c>
       <c r="D181" t="n">
-        <v>193.61</v>
+        <v>49.03</v>
       </c>
       <c r="E181" t="n">
-        <v>38.58</v>
+        <v>21.33</v>
       </c>
       <c r="F181" t="n">
-        <v>1.72426</v>
+        <v>0.19255</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>45.37</v>
+        <v>83</v>
       </c>
       <c r="D182" t="n">
-        <v>146.69</v>
+        <v>132.53</v>
       </c>
       <c r="E182" t="n">
-        <v>223.32</v>
+        <v>59.67</v>
       </c>
       <c r="F182" t="n">
-        <v>5.23484</v>
+        <v>-0.01342</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>112.47</v>
+        <v>166.99</v>
       </c>
       <c r="D183" t="n">
-        <v>138.49</v>
+        <v>306.53</v>
       </c>
       <c r="E183" t="n">
-        <v>23.14</v>
+        <v>83.56</v>
       </c>
       <c r="F183" t="n">
-        <v>0.30959</v>
+        <v>5.16986</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>13.06</v>
+        <v>151.43</v>
       </c>
       <c r="D184" t="n">
-        <v>19.91</v>
+        <v>262.4</v>
       </c>
       <c r="E184" t="n">
-        <v>52.45</v>
+        <v>73.28</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.009140000000000001</v>
+        <v>1.63232</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>82.26000000000001</v>
+        <v>57.15</v>
       </c>
       <c r="D185" t="n">
-        <v>128.49</v>
+        <v>179.7</v>
       </c>
       <c r="E185" t="n">
-        <v>56.2</v>
+        <v>214.44</v>
       </c>
       <c r="F185" t="n">
-        <v>0.08618000000000001</v>
+        <v>2.90762</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>156.66</v>
+        <v>32.36</v>
       </c>
       <c r="D186" t="n">
-        <v>265.67</v>
+        <v>51.07</v>
       </c>
       <c r="E186" t="n">
-        <v>69.58</v>
+        <v>57.82</v>
       </c>
       <c r="F186" t="n">
-        <v>2.0428</v>
+        <v>0.08409</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>40.41</v>
+        <v>121.11</v>
       </c>
       <c r="D187" t="n">
-        <v>51.96</v>
+        <v>328.99</v>
       </c>
       <c r="E187" t="n">
-        <v>28.58</v>
+        <v>171.65</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.19889</v>
+        <v>2.63639</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>197.38</v>
+        <v>17.89</v>
       </c>
       <c r="D188" t="n">
-        <v>261.77</v>
+        <v>30.26</v>
       </c>
       <c r="E188" t="n">
-        <v>32.62</v>
+        <v>69.14</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.05181</v>
+        <v>0.14219</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>393.42</v>
+        <v>18.26</v>
       </c>
       <c r="D189" t="n">
-        <v>595.41</v>
+        <v>35.48</v>
       </c>
       <c r="E189" t="n">
-        <v>51.34</v>
+        <v>94.3</v>
       </c>
       <c r="F189" t="n">
-        <v>-2.04834</v>
+        <v>0.97924</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>74.63</v>
+        <v>62.93</v>
       </c>
       <c r="D190" t="n">
-        <v>89.34999999999999</v>
+        <v>166.5</v>
       </c>
       <c r="E190" t="n">
-        <v>19.72</v>
+        <v>164.58</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.05535</v>
+        <v>4.92156</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>465.4</v>
+        <v>95.67</v>
       </c>
       <c r="D191" t="n">
-        <v>514.95</v>
+        <v>199.28</v>
       </c>
       <c r="E191" t="n">
-        <v>10.65</v>
+        <v>108.3</v>
       </c>
       <c r="F191" t="n">
-        <v>1.66879</v>
+        <v>0.61832</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>56.06</v>
+        <v>56.43</v>
       </c>
       <c r="D192" t="n">
-        <v>62.39</v>
+        <v>107.84</v>
       </c>
       <c r="E192" t="n">
-        <v>11.29</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F192" t="n">
-        <v>0.03839</v>
+        <v>3.47715</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>153.25</v>
+        <v>23.49</v>
       </c>
       <c r="D193" t="n">
-        <v>194.86</v>
+        <v>32.52</v>
       </c>
       <c r="E193" t="n">
-        <v>27.15</v>
+        <v>38.44</v>
       </c>
       <c r="F193" t="n">
-        <v>0.85662</v>
+        <v>-0.04284</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>155.75</v>
+        <v>52.39</v>
       </c>
       <c r="D194" t="n">
-        <v>257.06</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E194" t="n">
-        <v>65.05</v>
+        <v>27.22</v>
       </c>
       <c r="F194" t="n">
-        <v>5.74053</v>
+        <v>0.09493</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>20.96</v>
+        <v>23.63</v>
       </c>
       <c r="D195" t="n">
-        <v>25.85</v>
+        <v>25.44</v>
       </c>
       <c r="E195" t="n">
-        <v>23.33</v>
+        <v>7.68</v>
       </c>
       <c r="F195" t="n">
-        <v>0.28351</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>STRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>40.59</v>
+        <v>382.22</v>
       </c>
       <c r="D196" t="n">
-        <v>56.33</v>
+        <v>511.04</v>
       </c>
       <c r="E196" t="n">
-        <v>38.78</v>
+        <v>33.7</v>
       </c>
       <c r="F196" t="n">
-        <v>1.40494</v>
+        <v>-4.01339</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>213.69</v>
+        <v>22.77</v>
       </c>
       <c r="D197" t="n">
-        <v>396.45</v>
+        <v>32.28</v>
       </c>
       <c r="E197" t="n">
-        <v>85.53</v>
+        <v>41.77</v>
       </c>
       <c r="F197" t="n">
-        <v>10.30916</v>
+        <v>0.00061</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>83.51000000000001</v>
+        <v>124.07</v>
       </c>
       <c r="D198" t="n">
-        <v>96.97</v>
+        <v>181.97</v>
       </c>
       <c r="E198" t="n">
-        <v>16.12</v>
+        <v>46.67</v>
       </c>
       <c r="F198" t="n">
-        <v>0.63437</v>
+        <v>3.9716</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>223.65</v>
+        <v>430.4</v>
       </c>
       <c r="D199" t="n">
-        <v>382.95</v>
+        <v>557.61</v>
       </c>
       <c r="E199" t="n">
-        <v>71.23</v>
+        <v>29.56</v>
       </c>
       <c r="F199" t="n">
-        <v>12.04345</v>
+        <v>0.09331</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>128.43</v>
+        <v>172.34</v>
       </c>
       <c r="D200" t="n">
-        <v>148.54</v>
+        <v>217.15</v>
       </c>
       <c r="E200" t="n">
-        <v>15.66</v>
+        <v>26</v>
       </c>
       <c r="F200" t="n">
-        <v>0.66273</v>
+        <v>-0.72394</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>18.71</v>
+        <v>96.73</v>
       </c>
       <c r="D201" t="n">
-        <v>21.49</v>
+        <v>121.71</v>
       </c>
       <c r="E201" t="n">
-        <v>14.86</v>
+        <v>25.82</v>
       </c>
       <c r="F201" t="n">
-        <v>0.13728</v>
+        <v>0.25986</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>66.95</v>
+        <v>164.13</v>
       </c>
       <c r="D202" t="n">
-        <v>86.44</v>
+        <v>567.29</v>
       </c>
       <c r="E202" t="n">
-        <v>29.11</v>
+        <v>245.63</v>
       </c>
       <c r="F202" t="n">
-        <v>1.50588</v>
+        <v>23.53755</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>126.32</v>
+        <v>817.35</v>
       </c>
       <c r="D203" t="n">
-        <v>157.22</v>
+        <v>957.27</v>
       </c>
       <c r="E203" t="n">
-        <v>24.46</v>
+        <v>17.12</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.32127</v>
+        <v>-2.74535</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>118.05</v>
+        <v>19.02</v>
       </c>
       <c r="D204" t="n">
-        <v>191.73</v>
+        <v>27.29</v>
       </c>
       <c r="E204" t="n">
-        <v>62.41</v>
+        <v>43.48</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.40022</v>
+        <v>0.26062</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>17.89</v>
+        <v>343.53</v>
       </c>
       <c r="D205" t="n">
-        <v>31.41</v>
+        <v>425.37</v>
       </c>
       <c r="E205" t="n">
-        <v>75.56999999999999</v>
+        <v>23.82</v>
       </c>
       <c r="F205" t="n">
-        <v>0.28103</v>
+        <v>1.55336</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>78.59999999999999</v>
+        <v>107.27</v>
       </c>
       <c r="D206" t="n">
-        <v>167.84</v>
+        <v>138.82</v>
       </c>
       <c r="E206" t="n">
-        <v>113.54</v>
+        <v>29.41</v>
       </c>
       <c r="F206" t="n">
-        <v>-0.11311</v>
+        <v>1.16703</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>57.15</v>
+        <v>41.19</v>
       </c>
       <c r="D207" t="n">
-        <v>192.77</v>
+        <v>102.94</v>
       </c>
       <c r="E207" t="n">
-        <v>237.31</v>
+        <v>149.92</v>
       </c>
       <c r="F207" t="n">
-        <v>4.18785</v>
+        <v>3.32896</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>151.43</v>
+        <v>16.32</v>
       </c>
       <c r="D208" t="n">
-        <v>265.67</v>
+        <v>23.89</v>
       </c>
       <c r="E208" t="n">
-        <v>75.44</v>
+        <v>46.38</v>
       </c>
       <c r="F208" t="n">
-        <v>1.55591</v>
+        <v>0.22921</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>LSCC</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>34.41</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="D209" t="n">
-        <v>67.69</v>
+        <v>119.76</v>
       </c>
       <c r="E209" t="n">
-        <v>96.72</v>
+        <v>40.37</v>
       </c>
       <c r="F209" t="n">
-        <v>0.14027</v>
+        <v>-0.8095</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>62.93</v>
+        <v>59.58</v>
       </c>
       <c r="D210" t="n">
-        <v>186.45</v>
+        <v>83.92</v>
       </c>
       <c r="E210" t="n">
-        <v>196.28</v>
+        <v>40.86</v>
       </c>
       <c r="F210" t="n">
-        <v>6.24855</v>
+        <v>0.38935</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>43.81</v>
+        <v>220.86</v>
       </c>
       <c r="D211" t="n">
-        <v>100.2</v>
+        <v>345.71</v>
       </c>
       <c r="E211" t="n">
-        <v>128.71</v>
+        <v>56.53</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.42056</v>
+        <v>1.06733</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ONTO</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>166.99</v>
+        <v>189.27</v>
       </c>
       <c r="D212" t="n">
-        <v>330.36</v>
+        <v>281.26</v>
       </c>
       <c r="E212" t="n">
-        <v>97.83</v>
+        <v>48.6</v>
       </c>
       <c r="F212" t="n">
-        <v>9.064159999999999</v>
+        <v>-1.39091</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>120.88</v>
+        <v>28.61</v>
       </c>
       <c r="D213" t="n">
-        <v>211.54</v>
+        <v>37.87</v>
       </c>
       <c r="E213" t="n">
-        <v>75</v>
+        <v>32.37</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.8151</v>
+        <v>-0.008959999999999999</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>WCC</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>32.36</v>
+        <v>257.14</v>
       </c>
       <c r="D214" t="n">
-        <v>53.34</v>
+        <v>356.32</v>
       </c>
       <c r="E214" t="n">
-        <v>64.83</v>
+        <v>38.57</v>
       </c>
       <c r="F214" t="n">
-        <v>0.36656</v>
+        <v>2.95633</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>112.5</v>
+        <v>73.13</v>
       </c>
       <c r="D215" t="n">
-        <v>194.21</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="E215" t="n">
-        <v>72.63</v>
+        <v>32.2</v>
       </c>
       <c r="F215" t="n">
-        <v>-1.0532</v>
+        <v>0.53833</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>121.11</v>
+        <v>3.88</v>
       </c>
       <c r="D216" t="n">
-        <v>332.35</v>
+        <v>6.43</v>
       </c>
       <c r="E216" t="n">
-        <v>174.42</v>
+        <v>65.72</v>
       </c>
       <c r="F216" t="n">
-        <v>2.08531</v>
+        <v>0.10428</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>SANM</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>83</v>
+        <v>124.03</v>
       </c>
       <c r="D217" t="n">
-        <v>142.35</v>
+        <v>216</v>
       </c>
       <c r="E217" t="n">
-        <v>71.51000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F217" t="n">
-        <v>0.76309</v>
+        <v>3.76432</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>GLXY</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>76.7</v>
+        <v>17.15</v>
       </c>
       <c r="D218" t="n">
-        <v>170.18</v>
+        <v>24.4</v>
       </c>
       <c r="E218" t="n">
-        <v>121.88</v>
+        <v>42.27</v>
       </c>
       <c r="F218" t="n">
-        <v>0.67575</v>
+        <v>0.44284</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>105.37</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D219" t="n">
-        <v>230.05</v>
+        <v>102.7</v>
       </c>
       <c r="E219" t="n">
-        <v>118.33</v>
+        <v>14.1</v>
       </c>
       <c r="F219" t="n">
-        <v>-1.90231</v>
+        <v>-0.07063999999999999</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>188.79</v>
+        <v>52.5</v>
       </c>
       <c r="D220" t="n">
-        <v>276.63</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="E220" t="n">
-        <v>46.53</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="F220" t="n">
-        <v>-2.28574</v>
+        <v>4.42311</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>18.26</v>
+        <v>321.8</v>
       </c>
       <c r="D221" t="n">
-        <v>34.02</v>
+        <v>975.26</v>
       </c>
       <c r="E221" t="n">
-        <v>86.31</v>
+        <v>203.06</v>
       </c>
       <c r="F221" t="n">
-        <v>1.1574</v>
+        <v>16.22983</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>25.85</v>
+        <v>316.5</v>
       </c>
       <c r="D222" t="n">
-        <v>42.91</v>
+        <v>433.24</v>
       </c>
       <c r="E222" t="n">
-        <v>66</v>
+        <v>36.88</v>
       </c>
       <c r="F222" t="n">
-        <v>0.12798</v>
+        <v>5.00493</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>117.65</v>
+        <v>196.04</v>
       </c>
       <c r="D223" t="n">
-        <v>231.88</v>
+        <v>516.13</v>
       </c>
       <c r="E223" t="n">
-        <v>97.09</v>
+        <v>163.28</v>
       </c>
       <c r="F223" t="n">
-        <v>0.40682</v>
+        <v>12.17477</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VMI</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>10.49</v>
+        <v>384.03</v>
       </c>
       <c r="D224" t="n">
-        <v>19.88</v>
+        <v>483.44</v>
       </c>
       <c r="E224" t="n">
-        <v>89.51000000000001</v>
+        <v>25.89</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.15382</v>
+        <v>-0.2071</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>56.43</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="D225" t="n">
-        <v>106.91</v>
+        <v>112.13</v>
       </c>
       <c r="E225" t="n">
-        <v>89.45999999999999</v>
+        <v>45.55</v>
       </c>
       <c r="F225" t="n">
-        <v>3.01266</v>
+        <v>-0.71745</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>TTMI</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>23.63</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="D226" t="n">
-        <v>25.41</v>
+        <v>126.44</v>
       </c>
       <c r="E226" t="n">
-        <v>7.53</v>
+        <v>43.21</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0601</v>
+        <v>1.06978</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>190.63</v>
+        <v>20.33</v>
       </c>
       <c r="D227" t="n">
-        <v>218.57</v>
+        <v>29.55</v>
       </c>
       <c r="E227" t="n">
-        <v>14.66</v>
+        <v>45.35</v>
       </c>
       <c r="F227" t="n">
-        <v>-1.51875</v>
+        <v>0.15953</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>124.07</v>
+        <v>116.13</v>
       </c>
       <c r="D228" t="n">
-        <v>180.15</v>
+        <v>199.59</v>
       </c>
       <c r="E228" t="n">
-        <v>45.2</v>
+        <v>71.87</v>
       </c>
       <c r="F228" t="n">
-        <v>4.1705</v>
+        <v>0.93349</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>23.49</v>
+        <v>303.1</v>
       </c>
       <c r="D229" t="n">
-        <v>32.49</v>
+        <v>378.78</v>
       </c>
       <c r="E229" t="n">
-        <v>38.31</v>
+        <v>24.97</v>
       </c>
       <c r="F229" t="n">
-        <v>0.09743</v>
+        <v>-0.37386</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>62.49</v>
+        <v>131.47</v>
       </c>
       <c r="D230" t="n">
-        <v>89.81999999999999</v>
+        <v>204.23</v>
       </c>
       <c r="E230" t="n">
-        <v>43.73</v>
+        <v>55.34</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.23607</v>
+        <v>-0.85663</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>172.34</v>
+        <v>186.42</v>
       </c>
       <c r="D231" t="n">
-        <v>217.36</v>
+        <v>268.7</v>
       </c>
       <c r="E231" t="n">
-        <v>26.12</v>
+        <v>44.14</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.19213</v>
+        <v>-0.8937</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>430.4</v>
+        <v>41.25</v>
       </c>
       <c r="D232" t="n">
-        <v>558.54</v>
+        <v>51.73</v>
       </c>
       <c r="E232" t="n">
-        <v>29.77</v>
+        <v>25.41</v>
       </c>
       <c r="F232" t="n">
-        <v>0.26252</v>
+        <v>0.04002</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SITM</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>72.54000000000001</v>
+        <v>311.23</v>
       </c>
       <c r="D233" t="n">
-        <v>87.16</v>
+        <v>635.66</v>
       </c>
       <c r="E233" t="n">
-        <v>20.15</v>
+        <v>104.24</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.10751</v>
+        <v>2.45158</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MTSI</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>164.13</v>
+        <v>209.49</v>
       </c>
       <c r="D234" t="n">
-        <v>534.28</v>
+        <v>274.9</v>
       </c>
       <c r="E234" t="n">
-        <v>225.52</v>
+        <v>31.22</v>
       </c>
       <c r="F234" t="n">
-        <v>21.33398</v>
+        <v>1.16397</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>96.73</v>
+        <v>55.66</v>
       </c>
       <c r="D235" t="n">
-        <v>122.53</v>
+        <v>76.14</v>
       </c>
       <c r="E235" t="n">
-        <v>26.67</v>
+        <v>36.79</v>
       </c>
       <c r="F235" t="n">
-        <v>0.4313</v>
+        <v>-1.33547</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6076,22 +6076,22 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>73.13</v>
+        <v>24.77</v>
       </c>
       <c r="D236" t="n">
-        <v>95.43000000000001</v>
+        <v>37.27</v>
       </c>
       <c r="E236" t="n">
-        <v>30.49</v>
+        <v>50.46</v>
       </c>
       <c r="F236" t="n">
-        <v>0.43563</v>
+        <v>0.47609</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6100,22 +6100,22 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>199.3</v>
+        <v>258.08</v>
       </c>
       <c r="D237" t="n">
-        <v>351.81</v>
+        <v>280.76</v>
       </c>
       <c r="E237" t="n">
-        <v>76.52</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F237" t="n">
-        <v>-1.44191</v>
+        <v>-0.53063</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6124,22 +6124,22 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3.88</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="D238" t="n">
-        <v>6.46</v>
+        <v>224.55</v>
       </c>
       <c r="E238" t="n">
-        <v>66.48999999999999</v>
+        <v>143.39</v>
       </c>
       <c r="F238" t="n">
-        <v>0.08959</v>
+        <v>5.71318</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>52.5</v>
+        <v>60.57</v>
       </c>
       <c r="D239" t="n">
-        <v>79.26000000000001</v>
+        <v>115.78</v>
       </c>
       <c r="E239" t="n">
-        <v>50.97</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="F239" t="n">
-        <v>4.37139</v>
+        <v>-0.17589</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>131.47</v>
+        <v>87.81</v>
       </c>
       <c r="D240" t="n">
-        <v>214.07</v>
+        <v>236.1</v>
       </c>
       <c r="E240" t="n">
-        <v>62.83</v>
+        <v>168.88</v>
       </c>
       <c r="F240" t="n">
-        <v>0.91734</v>
+        <v>3.38837</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>273.5</v>
+        <v>126.58</v>
       </c>
       <c r="D241" t="n">
-        <v>349.39</v>
+        <v>146.01</v>
       </c>
       <c r="E241" t="n">
-        <v>27.75</v>
+        <v>15.35</v>
       </c>
       <c r="F241" t="n">
-        <v>-1.43004</v>
+        <v>0.38161</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,22 +6220,22 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>28.35</v>
+        <v>247.48</v>
       </c>
       <c r="D242" t="n">
-        <v>38.72</v>
+        <v>318.08</v>
       </c>
       <c r="E242" t="n">
-        <v>36.58</v>
+        <v>28.53</v>
       </c>
       <c r="F242" t="n">
-        <v>0.29357</v>
+        <v>-1.78538</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6244,22 +6244,22 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>273.14</v>
+        <v>57.45</v>
       </c>
       <c r="D243" t="n">
-        <v>345.71</v>
+        <v>70.48</v>
       </c>
       <c r="E243" t="n">
-        <v>26.57</v>
+        <v>22.68</v>
       </c>
       <c r="F243" t="n">
-        <v>-1.43948</v>
+        <v>-0.27768</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>22.61</v>
+        <v>533.78</v>
       </c>
       <c r="D244" t="n">
-        <v>55.41</v>
+        <v>650.58</v>
       </c>
       <c r="E244" t="n">
-        <v>145.07</v>
+        <v>21.88</v>
       </c>
       <c r="F244" t="n">
-        <v>1.53437</v>
+        <v>-0.02439</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>8.609999999999999</v>
+        <v>59.66</v>
       </c>
       <c r="D245" t="n">
-        <v>21.9</v>
+        <v>84.06</v>
       </c>
       <c r="E245" t="n">
-        <v>154.36</v>
+        <v>40.9</v>
       </c>
       <c r="F245" t="n">
-        <v>0.80893</v>
+        <v>1.6949</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,22 +6316,22 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>166</v>
+        <v>572.5</v>
       </c>
       <c r="D246" t="n">
-        <v>407.02</v>
+        <v>1633.35</v>
       </c>
       <c r="E246" t="n">
-        <v>145.19</v>
+        <v>185.3</v>
       </c>
       <c r="F246" t="n">
-        <v>4.5493</v>
+        <v>55.17344</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>119.51</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D247" t="n">
-        <v>257.05</v>
+        <v>22.64</v>
       </c>
       <c r="E247" t="n">
-        <v>115.09</v>
+        <v>162.95</v>
       </c>
       <c r="F247" t="n">
-        <v>12.83332</v>
+        <v>0.88566</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>29.16</v>
+        <v>219.65</v>
       </c>
       <c r="D248" t="n">
-        <v>39.94</v>
+        <v>305.37</v>
       </c>
       <c r="E248" t="n">
-        <v>36.97</v>
+        <v>39.03</v>
       </c>
       <c r="F248" t="n">
-        <v>0.01199</v>
+        <v>3.42654</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>97.52</v>
+        <v>166</v>
       </c>
       <c r="D249" t="n">
-        <v>132.88</v>
+        <v>409.8</v>
       </c>
       <c r="E249" t="n">
-        <v>36.26</v>
+        <v>146.87</v>
       </c>
       <c r="F249" t="n">
-        <v>2.17585</v>
+        <v>4.61449</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>69.3</v>
+        <v>119.51</v>
       </c>
       <c r="D250" t="n">
-        <v>83.54000000000001</v>
+        <v>275.75</v>
       </c>
       <c r="E250" t="n">
-        <v>20.55</v>
+        <v>130.73</v>
       </c>
       <c r="F250" t="n">
-        <v>0.20672</v>
+        <v>16.30736</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>258.08</v>
+        <v>29.16</v>
       </c>
       <c r="D251" t="n">
-        <v>290.05</v>
+        <v>40.11</v>
       </c>
       <c r="E251" t="n">
-        <v>12.39</v>
+        <v>37.55</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8742</v>
+        <v>-0.06358</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>24.77</v>
+        <v>97.52</v>
       </c>
       <c r="D252" t="n">
-        <v>36.96</v>
+        <v>132.01</v>
       </c>
       <c r="E252" t="n">
-        <v>49.21</v>
+        <v>35.37</v>
       </c>
       <c r="F252" t="n">
-        <v>0.4117</v>
+        <v>2.04384</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>284.79</v>
+        <v>187.39</v>
       </c>
       <c r="D253" t="n">
-        <v>424.24</v>
+        <v>236.62</v>
       </c>
       <c r="E253" t="n">
-        <v>48.97</v>
+        <v>26.27</v>
       </c>
       <c r="F253" t="n">
-        <v>5.01403</v>
+        <v>-0.63052</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>67.39</v>
+        <v>257.27</v>
       </c>
       <c r="D254" t="n">
-        <v>93.43000000000001</v>
+        <v>346.55</v>
       </c>
       <c r="E254" t="n">
-        <v>38.64</v>
+        <v>34.7</v>
       </c>
       <c r="F254" t="n">
-        <v>0.55682</v>
+        <v>8.016030000000001</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>65.16</v>
+        <v>69.3</v>
       </c>
       <c r="D255" t="n">
-        <v>114.33</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="E255" t="n">
-        <v>75.45999999999999</v>
+        <v>20.07</v>
       </c>
       <c r="F255" t="n">
-        <v>2.2454</v>
+        <v>-0.161</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>19.02</v>
+        <v>269.41</v>
       </c>
       <c r="D256" t="n">
-        <v>27.24</v>
+        <v>338.64</v>
       </c>
       <c r="E256" t="n">
-        <v>43.22</v>
+        <v>25.7</v>
       </c>
       <c r="F256" t="n">
-        <v>0.27865</v>
+        <v>2.12017</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>20.33</v>
+        <v>276.35</v>
       </c>
       <c r="D257" t="n">
-        <v>29.1</v>
+        <v>379.72</v>
       </c>
       <c r="E257" t="n">
-        <v>43.14</v>
+        <v>37.41</v>
       </c>
       <c r="F257" t="n">
-        <v>0.12624</v>
+        <v>3.99115</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>16.32</v>
+        <v>28.35</v>
       </c>
       <c r="D258" t="n">
-        <v>23.89</v>
+        <v>37.09</v>
       </c>
       <c r="E258" t="n">
-        <v>46.38</v>
+        <v>30.83</v>
       </c>
       <c r="F258" t="n">
-        <v>0.235</v>
+        <v>0.11815</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>41.19</v>
+        <v>7.96</v>
       </c>
       <c r="D259" t="n">
-        <v>97.19</v>
+        <v>11.13</v>
       </c>
       <c r="E259" t="n">
-        <v>135.96</v>
+        <v>39.82</v>
       </c>
       <c r="F259" t="n">
-        <v>2.31858</v>
+        <v>0.2286</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>107.27</v>
+        <v>1273.18</v>
       </c>
       <c r="D260" t="n">
-        <v>136.18</v>
+        <v>1690.82</v>
       </c>
       <c r="E260" t="n">
-        <v>26.95</v>
+        <v>32.8</v>
       </c>
       <c r="F260" t="n">
-        <v>1.00255</v>
+        <v>2.09023</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>196.04</v>
+        <v>20.89</v>
       </c>
       <c r="D261" t="n">
-        <v>493.41</v>
+        <v>39.47</v>
       </c>
       <c r="E261" t="n">
-        <v>151.69</v>
+        <v>88.94</v>
       </c>
       <c r="F261" t="n">
-        <v>9.84099</v>
+        <v>0.8488599999999999</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>246.63</v>
+        <v>31.8</v>
       </c>
       <c r="D262" t="n">
-        <v>333.08</v>
+        <v>66.42</v>
       </c>
       <c r="E262" t="n">
-        <v>35.05</v>
+        <v>108.87</v>
       </c>
       <c r="F262" t="n">
-        <v>3.52767</v>
+        <v>-0.1597</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>59.66</v>
+        <v>246.63</v>
       </c>
       <c r="D263" t="n">
-        <v>84.11</v>
+        <v>332.27</v>
       </c>
       <c r="E263" t="n">
-        <v>40.98</v>
+        <v>34.72</v>
       </c>
       <c r="F263" t="n">
-        <v>1.58777</v>
+        <v>2.12426</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>57.45</v>
+        <v>26.41</v>
       </c>
       <c r="D264" t="n">
-        <v>70.54000000000001</v>
+        <v>40.82</v>
       </c>
       <c r="E264" t="n">
-        <v>22.79</v>
+        <v>54.56</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.19886</v>
+        <v>1.9156</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>279.73</v>
+        <v>208.37</v>
       </c>
       <c r="D265" t="n">
-        <v>411.49</v>
+        <v>241.87</v>
       </c>
       <c r="E265" t="n">
-        <v>47.1</v>
+        <v>16.08</v>
       </c>
       <c r="F265" t="n">
-        <v>3.73943</v>
+        <v>-0.99486</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>26.41</v>
+        <v>67.39</v>
       </c>
       <c r="D266" t="n">
-        <v>41.02</v>
+        <v>93.45</v>
       </c>
       <c r="E266" t="n">
-        <v>55.32</v>
+        <v>38.67</v>
       </c>
       <c r="F266" t="n">
-        <v>1.68935</v>
+        <v>0.55333</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>90.01000000000001</v>
+        <v>21.06</v>
       </c>
       <c r="D267" t="n">
-        <v>100.36</v>
+        <v>40.1</v>
       </c>
       <c r="E267" t="n">
-        <v>11.5</v>
+        <v>90.41</v>
       </c>
       <c r="F267" t="n">
-        <v>0.11228</v>
+        <v>0.93479</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>31.8</v>
+        <v>65.16</v>
       </c>
       <c r="D268" t="n">
-        <v>69.41</v>
+        <v>112.57</v>
       </c>
       <c r="E268" t="n">
-        <v>118.27</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F268" t="n">
-        <v>0.31551</v>
+        <v>2.79859</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>204.77</v>
+        <v>112.75</v>
       </c>
       <c r="D269" t="n">
-        <v>274.99</v>
+        <v>162.38</v>
       </c>
       <c r="E269" t="n">
-        <v>34.29</v>
+        <v>44.02</v>
       </c>
       <c r="F269" t="n">
-        <v>0.55032</v>
+        <v>1.48447</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6892,94 +6892,94 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>12.96</v>
+        <v>107.11</v>
       </c>
       <c r="D270" t="n">
-        <v>16.66</v>
+        <v>126.4</v>
       </c>
       <c r="E270" t="n">
-        <v>28.55</v>
+        <v>18.01</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.0515</v>
+        <v>-0.54744</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>147.02</v>
+        <v>284.79</v>
       </c>
       <c r="D271" t="n">
-        <v>373.94</v>
+        <v>418.72</v>
       </c>
       <c r="E271" t="n">
-        <v>154.35</v>
+        <v>47.03</v>
       </c>
       <c r="F271" t="n">
-        <v>-2.08465</v>
+        <v>3.19445</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>156.35</v>
+        <v>279.73</v>
       </c>
       <c r="D272" t="n">
-        <v>216.58</v>
+        <v>411.71</v>
       </c>
       <c r="E272" t="n">
-        <v>38.52</v>
+        <v>47.18</v>
       </c>
       <c r="F272" t="n">
-        <v>1.76572</v>
+        <v>1.83095</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>92.39</v>
+        <v>181.03</v>
       </c>
       <c r="D273" t="n">
-        <v>235.38</v>
+        <v>204.14</v>
       </c>
       <c r="E273" t="n">
-        <v>154.75</v>
+        <v>12.77</v>
       </c>
       <c r="F273" t="n">
-        <v>2.36905</v>
+        <v>-1.65921</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>7.63</v>
+        <v>122.52</v>
       </c>
       <c r="D274" t="n">
-        <v>11.33</v>
+        <v>193.4</v>
       </c>
       <c r="E274" t="n">
-        <v>48.49</v>
+        <v>57.85</v>
       </c>
       <c r="F274" t="n">
-        <v>0.16084</v>
+        <v>0.72575</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>284.93</v>
+        <v>35.34</v>
       </c>
       <c r="D275" t="n">
-        <v>412.56</v>
+        <v>53.34</v>
       </c>
       <c r="E275" t="n">
-        <v>44.79</v>
+        <v>50.93</v>
       </c>
       <c r="F275" t="n">
-        <v>0.67323</v>
+        <v>0.64798</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>67.56999999999999</v>
+        <v>46.97</v>
       </c>
       <c r="D276" t="n">
-        <v>79.81999999999999</v>
+        <v>62.69</v>
       </c>
       <c r="E276" t="n">
-        <v>18.13</v>
+        <v>33.47</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.43807</v>
+        <v>0.03608</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,22 +7060,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>285.27</v>
+        <v>525.72</v>
       </c>
       <c r="D277" t="n">
-        <v>378.05</v>
+        <v>648.03</v>
       </c>
       <c r="E277" t="n">
-        <v>32.52</v>
+        <v>23.27</v>
       </c>
       <c r="F277" t="n">
-        <v>1.30077</v>
+        <v>18.95295</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7084,22 +7084,22 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>33.63</v>
+        <v>7.63</v>
       </c>
       <c r="D278" t="n">
-        <v>43.55</v>
+        <v>11.45</v>
       </c>
       <c r="E278" t="n">
-        <v>29.5</v>
+        <v>50.07</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.00236</v>
+        <v>0.15777</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7108,22 +7108,22 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>202.71</v>
+        <v>317.4</v>
       </c>
       <c r="D279" t="n">
-        <v>258.48</v>
+        <v>413.78</v>
       </c>
       <c r="E279" t="n">
-        <v>27.51</v>
+        <v>30.37</v>
       </c>
       <c r="F279" t="n">
-        <v>-1.41316</v>
+        <v>-1.68102</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7132,22 +7132,22 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>67.7</v>
+        <v>33.63</v>
       </c>
       <c r="D280" t="n">
-        <v>97.75</v>
+        <v>43.49</v>
       </c>
       <c r="E280" t="n">
-        <v>44.39</v>
+        <v>29.32</v>
       </c>
       <c r="F280" t="n">
-        <v>0.25783</v>
+        <v>-0.02051</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7156,22 +7156,22 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>87.15000000000001</v>
+        <v>87.98</v>
       </c>
       <c r="D281" t="n">
-        <v>157.45</v>
+        <v>107.75</v>
       </c>
       <c r="E281" t="n">
-        <v>80.67</v>
+        <v>22.47</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.08858000000000001</v>
+        <v>-0.06295000000000001</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7180,22 +7180,22 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>91.37</v>
+        <v>285.27</v>
       </c>
       <c r="D282" t="n">
-        <v>120.93</v>
+        <v>375.2</v>
       </c>
       <c r="E282" t="n">
-        <v>32.35</v>
+        <v>31.52</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.10485</v>
+        <v>0.13349</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>AXSM</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7204,22 +7204,22 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>22.3</v>
+        <v>156.35</v>
       </c>
       <c r="D283" t="n">
-        <v>34.8</v>
+        <v>220.75</v>
       </c>
       <c r="E283" t="n">
-        <v>56.05</v>
+        <v>41.19</v>
       </c>
       <c r="F283" t="n">
-        <v>0.45747</v>
+        <v>1.02948</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>SPG-PJ</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7228,22 +7228,22 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>52.49</v>
+        <v>121.84</v>
       </c>
       <c r="D284" t="n">
-        <v>55.78</v>
+        <v>157.77</v>
       </c>
       <c r="E284" t="n">
-        <v>6.27</v>
+        <v>29.49</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.04614</v>
+        <v>-1.31209</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7252,22 +7252,22 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>10.65</v>
+        <v>79.19</v>
       </c>
       <c r="D285" t="n">
-        <v>14.74</v>
+        <v>105.3</v>
       </c>
       <c r="E285" t="n">
-        <v>38.4</v>
+        <v>32.97</v>
       </c>
       <c r="F285" t="n">
-        <v>0.05009</v>
+        <v>0.32431</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7276,22 +7276,22 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>92.42</v>
+        <v>282.84</v>
       </c>
       <c r="D286" t="n">
-        <v>108.59</v>
+        <v>356.23</v>
       </c>
       <c r="E286" t="n">
-        <v>17.5</v>
+        <v>25.95</v>
       </c>
       <c r="F286" t="n">
-        <v>0.1877</v>
+        <v>-0.63374</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7300,22 +7300,22 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>20.72</v>
+        <v>22.3</v>
       </c>
       <c r="D287" t="n">
-        <v>24.85</v>
+        <v>34.67</v>
       </c>
       <c r="E287" t="n">
-        <v>19.93</v>
+        <v>55.47</v>
       </c>
       <c r="F287" t="n">
-        <v>-0.07012</v>
+        <v>0.3951</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ARCC</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7324,22 +7324,22 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>17.45</v>
+        <v>182.65</v>
       </c>
       <c r="D288" t="n">
-        <v>19.8</v>
+        <v>328.93</v>
       </c>
       <c r="E288" t="n">
-        <v>13.47</v>
+        <v>80.09</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.03105</v>
+        <v>3.00967</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>LYG</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7348,22 +7348,22 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>55.4</v>
+        <v>4.83</v>
       </c>
       <c r="D289" t="n">
-        <v>69.18000000000001</v>
+        <v>6.01</v>
       </c>
       <c r="E289" t="n">
-        <v>24.87</v>
+        <v>24.43</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.03903</v>
+        <v>-0.02334</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7372,22 +7372,22 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>295.52</v>
+        <v>134.99</v>
       </c>
       <c r="D290" t="n">
-        <v>375.28</v>
+        <v>189.19</v>
       </c>
       <c r="E290" t="n">
-        <v>26.99</v>
+        <v>40.15</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.74265</v>
+        <v>0.28198</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7396,22 +7396,22 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3.42</v>
+        <v>14.27</v>
       </c>
       <c r="D291" t="n">
-        <v>4.89</v>
+        <v>18.89</v>
       </c>
       <c r="E291" t="n">
-        <v>42.98</v>
+        <v>32.38</v>
       </c>
       <c r="F291" t="n">
-        <v>0.09469</v>
+        <v>-0.00158</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7420,22 +7420,22 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>525.72</v>
+        <v>28.37</v>
       </c>
       <c r="D292" t="n">
-        <v>665.6</v>
+        <v>40.48</v>
       </c>
       <c r="E292" t="n">
-        <v>26.61</v>
+        <v>42.69</v>
       </c>
       <c r="F292" t="n">
-        <v>22.11172</v>
+        <v>0.44352</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7444,22 +7444,22 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>289.16</v>
+        <v>10.65</v>
       </c>
       <c r="D293" t="n">
-        <v>410.01</v>
+        <v>14.96</v>
       </c>
       <c r="E293" t="n">
-        <v>41.79</v>
+        <v>40.47</v>
       </c>
       <c r="F293" t="n">
-        <v>-0.38142</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7468,22 +7468,22 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>39.84</v>
+        <v>67.7</v>
       </c>
       <c r="D294" t="n">
-        <v>58.53</v>
+        <v>97.14</v>
       </c>
       <c r="E294" t="n">
-        <v>46.91</v>
+        <v>43.49</v>
       </c>
       <c r="F294" t="n">
-        <v>-0.08142000000000001</v>
+        <v>0.04813</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7492,22 +7492,22 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>61.37</v>
+        <v>284.93</v>
       </c>
       <c r="D295" t="n">
-        <v>80.23</v>
+        <v>408.22</v>
       </c>
       <c r="E295" t="n">
-        <v>30.73</v>
+        <v>43.27</v>
       </c>
       <c r="F295" t="n">
-        <v>-0.09644999999999999</v>
+        <v>0.1641</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7516,22 +7516,22 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>317.93</v>
+        <v>52.49</v>
       </c>
       <c r="D296" t="n">
-        <v>379.54</v>
+        <v>55.78</v>
       </c>
       <c r="E296" t="n">
-        <v>19.38</v>
+        <v>6.27</v>
       </c>
       <c r="F296" t="n">
-        <v>-0.71048</v>
+        <v>-0.04614</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7540,22 +7540,22 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>153.68</v>
+        <v>92.42</v>
       </c>
       <c r="D297" t="n">
-        <v>172.02</v>
+        <v>106.55</v>
       </c>
       <c r="E297" t="n">
-        <v>11.93</v>
+        <v>15.29</v>
       </c>
       <c r="F297" t="n">
-        <v>-0.63445</v>
+        <v>-0.16412</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7564,22 +7564,22 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>7.58</v>
+        <v>289.16</v>
       </c>
       <c r="D298" t="n">
-        <v>10.73</v>
+        <v>408.34</v>
       </c>
       <c r="E298" t="n">
-        <v>41.56</v>
+        <v>41.22</v>
       </c>
       <c r="F298" t="n">
-        <v>0.17999</v>
+        <v>-1.16894</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7588,22 +7588,22 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>213.28</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D299" t="n">
-        <v>283.27</v>
+        <v>94.42</v>
       </c>
       <c r="E299" t="n">
-        <v>32.82</v>
+        <v>29.52</v>
       </c>
       <c r="F299" t="n">
-        <v>-0.5633</v>
+        <v>0.73445</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7612,22 +7612,22 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>157.12</v>
+        <v>39.84</v>
       </c>
       <c r="D300" t="n">
-        <v>261.12</v>
+        <v>58.55</v>
       </c>
       <c r="E300" t="n">
-        <v>66.19</v>
+        <v>46.96</v>
       </c>
       <c r="F300" t="n">
-        <v>1.88244</v>
+        <v>-0.18999</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7636,22 +7636,22 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>87.01000000000001</v>
+        <v>91.37</v>
       </c>
       <c r="D301" t="n">
-        <v>116.9</v>
+        <v>120.97</v>
       </c>
       <c r="E301" t="n">
-        <v>34.35</v>
+        <v>32.4</v>
       </c>
       <c r="F301" t="n">
-        <v>0.85321</v>
+        <v>-0.15904</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7660,22 +7660,22 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>71.42</v>
+        <v>50.85</v>
       </c>
       <c r="D302" t="n">
-        <v>78.89</v>
+        <v>62.84</v>
       </c>
       <c r="E302" t="n">
-        <v>10.46</v>
+        <v>23.58</v>
       </c>
       <c r="F302" t="n">
-        <v>-0.24064</v>
+        <v>-0.14971</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7684,22 +7684,22 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>243.35</v>
+        <v>20.72</v>
       </c>
       <c r="D303" t="n">
-        <v>355.2</v>
+        <v>24.74</v>
       </c>
       <c r="E303" t="n">
-        <v>45.96</v>
+        <v>19.4</v>
       </c>
       <c r="F303" t="n">
-        <v>0.55648</v>
+        <v>-0.18065</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7708,22 +7708,22 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>182.65</v>
+        <v>36.41</v>
       </c>
       <c r="D304" t="n">
-        <v>341.79</v>
+        <v>54.58</v>
       </c>
       <c r="E304" t="n">
-        <v>87.13</v>
+        <v>49.9</v>
       </c>
       <c r="F304" t="n">
-        <v>4.40399</v>
+        <v>0.12294</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7732,22 +7732,22 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>3.93</v>
+        <v>14</v>
       </c>
       <c r="D305" t="n">
-        <v>5.84</v>
+        <v>14.79</v>
       </c>
       <c r="E305" t="n">
-        <v>48.6</v>
+        <v>5.64</v>
       </c>
       <c r="F305" t="n">
-        <v>0.07327</v>
+        <v>0.01762</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7756,22 +7756,22 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>87.98</v>
+        <v>7.58</v>
       </c>
       <c r="D306" t="n">
-        <v>108.99</v>
+        <v>10.86</v>
       </c>
       <c r="E306" t="n">
-        <v>23.88</v>
+        <v>43.27</v>
       </c>
       <c r="F306" t="n">
-        <v>0.3621</v>
+        <v>0.18842</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7780,448 +7780,424 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>72.90000000000001</v>
+        <v>3.93</v>
       </c>
       <c r="D307" t="n">
-        <v>94.92</v>
+        <v>5.68</v>
       </c>
       <c r="E307" t="n">
-        <v>30.21</v>
+        <v>44.53</v>
       </c>
       <c r="F307" t="n">
-        <v>0.7454499999999999</v>
+        <v>0.03783</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>35.34</v>
+        <v>17.13</v>
       </c>
       <c r="D308" t="n">
-        <v>53.67</v>
+        <v>43.96</v>
       </c>
       <c r="E308" t="n">
-        <v>51.87</v>
+        <v>156.63</v>
       </c>
       <c r="F308" t="n">
-        <v>0.74151</v>
+        <v>0.24682</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>125.78</v>
+        <v>63.78</v>
       </c>
       <c r="D309" t="n">
-        <v>143.7</v>
+        <v>68.98</v>
       </c>
       <c r="E309" t="n">
-        <v>14.25</v>
+        <v>8.15</v>
       </c>
       <c r="F309" t="n">
-        <v>-0.39666</v>
+        <v>0.05541</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>35.72</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D310" t="n">
-        <v>49.48</v>
+        <v>169.31</v>
       </c>
       <c r="E310" t="n">
-        <v>38.52</v>
+        <v>69.33</v>
       </c>
       <c r="F310" t="n">
-        <v>-0.54794</v>
+        <v>-0.89257</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>67.23</v>
+        <v>2.78</v>
       </c>
       <c r="D311" t="n">
-        <v>98.22</v>
+        <v>3.02</v>
       </c>
       <c r="E311" t="n">
-        <v>46.1</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F311" t="n">
-        <v>-0.14265</v>
+        <v>0.03112</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>HMY</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="D312" t="n">
-        <v>14.8</v>
+        <v>20.64</v>
       </c>
       <c r="E312" t="n">
-        <v>5.71</v>
+        <v>48.92</v>
       </c>
       <c r="F312" t="n">
-        <v>0.01308</v>
+        <v>0.12952</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>121.84</v>
+        <v>23.65</v>
       </c>
       <c r="D313" t="n">
-        <v>162.38</v>
+        <v>28.33</v>
       </c>
       <c r="E313" t="n">
-        <v>33.27</v>
+        <v>19.79</v>
       </c>
       <c r="F313" t="n">
-        <v>0.05096</v>
+        <v>0.11786</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>17.13</v>
+        <v>134.96</v>
       </c>
       <c r="D314" t="n">
-        <v>43.45</v>
+        <v>264.79</v>
       </c>
       <c r="E314" t="n">
-        <v>153.65</v>
+        <v>96.2</v>
       </c>
       <c r="F314" t="n">
-        <v>0.28998</v>
+        <v>3.15965</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MDGL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>63.78</v>
+        <v>445.04</v>
       </c>
       <c r="D315" t="n">
-        <v>70.61</v>
+        <v>534.49</v>
       </c>
       <c r="E315" t="n">
-        <v>10.71</v>
+        <v>20.1</v>
       </c>
       <c r="F315" t="n">
-        <v>0.28252</v>
+        <v>1.8121</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>99.98999999999999</v>
+        <v>160.62</v>
       </c>
       <c r="D316" t="n">
-        <v>168.93</v>
+        <v>259.43</v>
       </c>
       <c r="E316" t="n">
-        <v>68.95</v>
+        <v>61.52</v>
       </c>
       <c r="F316" t="n">
-        <v>0.20101</v>
+        <v>0.38868</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>27.17</v>
+        <v>241.4</v>
       </c>
       <c r="D317" t="n">
-        <v>33.86</v>
+        <v>346.23</v>
       </c>
       <c r="E317" t="n">
-        <v>24.62</v>
+        <v>43.43</v>
       </c>
       <c r="F317" t="n">
-        <v>-0.24679</v>
+        <v>-1.22178</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>241.14</v>
+        <v>55.05</v>
       </c>
       <c r="D318" t="n">
-        <v>298.6</v>
+        <v>68.75</v>
       </c>
       <c r="E318" t="n">
-        <v>23.83</v>
+        <v>24.89</v>
       </c>
       <c r="F318" t="n">
-        <v>1.64228</v>
+        <v>-0.12841</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>MDGL</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>445.04</v>
+        <v>22.32</v>
       </c>
       <c r="D319" t="n">
-        <v>540.0599999999999</v>
+        <v>62.09</v>
       </c>
       <c r="E319" t="n">
-        <v>21.35</v>
+        <v>178.18</v>
       </c>
       <c r="F319" t="n">
-        <v>2.20142</v>
+        <v>1.76115</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>94.23999999999999</v>
+        <v>240.92</v>
       </c>
       <c r="D320" t="n">
-        <v>112.01</v>
+        <v>292.71</v>
       </c>
       <c r="E320" t="n">
-        <v>18.86</v>
+        <v>21.5</v>
       </c>
       <c r="F320" t="n">
-        <v>-0.19592</v>
+        <v>0.08883000000000001</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>23.65</v>
+        <v>156.37</v>
       </c>
       <c r="D321" t="n">
-        <v>29.25</v>
+        <v>269.21</v>
       </c>
       <c r="E321" t="n">
-        <v>23.66</v>
+        <v>72.16</v>
       </c>
       <c r="F321" t="n">
-        <v>0.22235</v>
+        <v>1.81533</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>FMX</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>105.8</v>
+        <v>3.41</v>
       </c>
       <c r="D322" t="n">
-        <v>121.26</v>
+        <v>5.15</v>
       </c>
       <c r="E322" t="n">
-        <v>14.61</v>
+        <v>51.03</v>
       </c>
       <c r="F322" t="n">
-        <v>-0.80715</v>
+        <v>0.12255</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>146.17</v>
+        <v>202.78</v>
       </c>
       <c r="D323" t="n">
-        <v>217.15</v>
+        <v>270.45</v>
       </c>
       <c r="E323" t="n">
-        <v>48.56</v>
+        <v>33.37</v>
       </c>
       <c r="F323" t="n">
-        <v>0.01127</v>
+        <v>0.5861499999999999</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>23.97</v>
+        <v>86.55</v>
       </c>
       <c r="D324" t="n">
-        <v>30.56</v>
+        <v>116.17</v>
       </c>
       <c r="E324" t="n">
-        <v>27.49</v>
+        <v>34.22</v>
       </c>
       <c r="F324" t="n">
-        <v>-0.08098</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>ABEV</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="D325" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E325" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="F325" t="n">
-        <v>0.02721</v>
+        <v>0.7472299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F324"/>
+  <dimension ref="A1:F326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,151 +451,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.84</v>
+        <v>2876.75</v>
       </c>
       <c r="D2" t="n">
-        <v>23.34</v>
+        <v>2965.52</v>
       </c>
       <c r="E2" t="n">
-        <v>6.87</v>
+        <v>3.09</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.27475</v>
+        <v>-26.725</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38.22</v>
+        <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>42.13</v>
+        <v>57.29</v>
       </c>
       <c r="E3" t="n">
-        <v>10.23</v>
+        <v>5.45</v>
       </c>
       <c r="F3" t="n">
-        <v>0.37088</v>
+        <v>-0.33941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.87</v>
+        <v>38.22</v>
       </c>
       <c r="D4" t="n">
-        <v>21.15</v>
+        <v>41.6</v>
       </c>
       <c r="E4" t="n">
-        <v>18.35</v>
+        <v>8.84</v>
       </c>
       <c r="F4" t="n">
-        <v>0.44142</v>
+        <v>0.17365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.03</v>
+        <v>17.87</v>
       </c>
       <c r="D5" t="n">
-        <v>14.34</v>
+        <v>21.62</v>
       </c>
       <c r="E5" t="n">
-        <v>10.05</v>
+        <v>20.98</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1198</v>
+        <v>0.65938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.67</v>
+        <v>102.63</v>
       </c>
       <c r="D6" t="n">
-        <v>6.94</v>
+        <v>109.08</v>
       </c>
       <c r="E6" t="n">
-        <v>22.4</v>
+        <v>6.28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1411</v>
+        <v>-0.22351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>298.59</v>
+        <v>13.03</v>
       </c>
       <c r="D7" t="n">
-        <v>323.96</v>
+        <v>14.97</v>
       </c>
       <c r="E7" t="n">
-        <v>8.5</v>
+        <v>14.89</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.06779</v>
+        <v>-0.01791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -604,70 +604,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55.36</v>
+        <v>298.59</v>
       </c>
       <c r="D8" t="n">
-        <v>61.53</v>
+        <v>334.24</v>
       </c>
       <c r="E8" t="n">
-        <v>11.15</v>
+        <v>11.94</v>
       </c>
       <c r="F8" t="n">
-        <v>0.65096</v>
+        <v>-1.56324</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>141.63</v>
+        <v>5.67</v>
       </c>
       <c r="D9" t="n">
-        <v>152.78</v>
+        <v>7.03</v>
       </c>
       <c r="E9" t="n">
-        <v>7.87</v>
+        <v>23.99</v>
       </c>
       <c r="F9" t="n">
-        <v>0.47217</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.23</v>
+        <v>141.63</v>
       </c>
       <c r="D10" t="n">
-        <v>11.85</v>
+        <v>157.31</v>
       </c>
       <c r="E10" t="n">
-        <v>5.52</v>
+        <v>11.07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02603</v>
+        <v>1.11386</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12.43</v>
+        <v>11.23</v>
       </c>
       <c r="D11" t="n">
-        <v>17.55</v>
+        <v>11.89</v>
       </c>
       <c r="E11" t="n">
-        <v>41.19</v>
+        <v>5.88</v>
       </c>
       <c r="F11" t="n">
-        <v>0.96113</v>
+        <v>0.03212</v>
       </c>
     </row>
     <row r="12">
@@ -703,13 +703,13 @@
         <v>2.98</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="E12" t="n">
-        <v>20.81</v>
+        <v>18.79</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0764</v>
+        <v>0.06816999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -727,19 +727,19 @@
         <v>7.17</v>
       </c>
       <c r="D13" t="n">
-        <v>8.33</v>
+        <v>8.23</v>
       </c>
       <c r="E13" t="n">
-        <v>16.18</v>
+        <v>14.78</v>
       </c>
       <c r="F13" t="n">
-        <v>0.15793</v>
+        <v>0.13527</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,46 +748,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.46</v>
+        <v>12.43</v>
       </c>
       <c r="D14" t="n">
-        <v>5.29</v>
+        <v>18.42</v>
       </c>
       <c r="E14" t="n">
-        <v>18.61</v>
+        <v>48.19</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09936</v>
+        <v>0.97816</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KEP</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.18</v>
+        <v>4.46</v>
       </c>
       <c r="D15" t="n">
-        <v>12.21</v>
+        <v>5.22</v>
       </c>
       <c r="E15" t="n">
-        <v>9.210000000000001</v>
+        <v>17.04</v>
       </c>
       <c r="F15" t="n">
-        <v>0.13627</v>
+        <v>0.08513999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STLA</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.05</v>
+        <v>17.28</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4</v>
+        <v>19.12</v>
       </c>
       <c r="E16" t="n">
-        <v>6.93</v>
+        <v>10.65</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.02486</v>
+        <v>0.22309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,184 +820,184 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.28</v>
+        <v>98.45</v>
       </c>
       <c r="D17" t="n">
-        <v>18.89</v>
+        <v>122.3</v>
       </c>
       <c r="E17" t="n">
-        <v>9.32</v>
+        <v>24.23</v>
       </c>
       <c r="F17" t="n">
-        <v>0.20552</v>
+        <v>2.28707</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>98.45</v>
+        <v>35.54</v>
       </c>
       <c r="D18" t="n">
-        <v>121.1</v>
+        <v>51.29</v>
       </c>
       <c r="E18" t="n">
-        <v>23.01</v>
+        <v>44.32</v>
       </c>
       <c r="F18" t="n">
-        <v>3.05519</v>
+        <v>1.98244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VALE</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13.63</v>
+        <v>123.39</v>
       </c>
       <c r="D19" t="n">
-        <v>15.23</v>
+        <v>137.82</v>
       </c>
       <c r="E19" t="n">
-        <v>11.74</v>
+        <v>11.69</v>
       </c>
       <c r="F19" t="n">
-        <v>0.14495</v>
+        <v>1.38289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>52.62</v>
+        <v>63.54</v>
       </c>
       <c r="D20" t="n">
-        <v>57.39</v>
+        <v>70.34</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>10.7</v>
       </c>
       <c r="F20" t="n">
-        <v>0.73467</v>
+        <v>0.02608</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.54</v>
+        <v>155.62</v>
       </c>
       <c r="D21" t="n">
-        <v>45.5</v>
+        <v>163.78</v>
       </c>
       <c r="E21" t="n">
-        <v>28.02</v>
+        <v>5.24</v>
       </c>
       <c r="F21" t="n">
-        <v>1.51007</v>
+        <v>-1.00319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>123.39</v>
+        <v>60.35</v>
       </c>
       <c r="D22" t="n">
-        <v>136.61</v>
+        <v>97.42</v>
       </c>
       <c r="E22" t="n">
-        <v>10.71</v>
+        <v>61.43</v>
       </c>
       <c r="F22" t="n">
-        <v>1.27266</v>
+        <v>1.96052</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>FIGR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>60.35</v>
+        <v>24.91</v>
       </c>
       <c r="D23" t="n">
-        <v>90.59999999999999</v>
+        <v>35.65</v>
       </c>
       <c r="E23" t="n">
-        <v>50.12</v>
+        <v>43.12</v>
       </c>
       <c r="F23" t="n">
-        <v>2.03637</v>
+        <v>0.36343</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.83</v>
+        <v>7.81</v>
       </c>
       <c r="D24" t="n">
-        <v>35.92</v>
+        <v>10.87</v>
       </c>
       <c r="E24" t="n">
-        <v>29.07</v>
+        <v>39.18</v>
       </c>
       <c r="F24" t="n">
-        <v>0.21349</v>
+        <v>0.04366</v>
       </c>
     </row>
     <row r="25">
@@ -1015,43 +1015,43 @@
         <v>205.48</v>
       </c>
       <c r="D25" t="n">
-        <v>248.68</v>
+        <v>249.99</v>
       </c>
       <c r="E25" t="n">
-        <v>21.02</v>
+        <v>21.66</v>
       </c>
       <c r="F25" t="n">
-        <v>2.43479</v>
+        <v>1.24005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7.81</v>
+        <v>41.55</v>
       </c>
       <c r="D26" t="n">
-        <v>10.6</v>
+        <v>62.21</v>
       </c>
       <c r="E26" t="n">
-        <v>35.72</v>
+        <v>49.72</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04089</v>
+        <v>-0.39774</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>124.05</v>
+        <v>298.32</v>
       </c>
       <c r="D27" t="n">
-        <v>166.4</v>
+        <v>358.97</v>
       </c>
       <c r="E27" t="n">
-        <v>34.14</v>
+        <v>20.33</v>
       </c>
       <c r="F27" t="n">
-        <v>4.52517</v>
+        <v>3.38165</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1084,814 +1084,814 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>252.49</v>
+        <v>29.31</v>
       </c>
       <c r="D28" t="n">
-        <v>287.25</v>
+        <v>43.17</v>
       </c>
       <c r="E28" t="n">
-        <v>13.77</v>
+        <v>47.29</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.70983</v>
+        <v>0.92178</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29.31</v>
+        <v>25.28</v>
       </c>
       <c r="D29" t="n">
-        <v>43.83</v>
+        <v>28.1</v>
       </c>
       <c r="E29" t="n">
-        <v>49.54</v>
+        <v>11.16</v>
       </c>
       <c r="F29" t="n">
-        <v>1.41459</v>
+        <v>-0.01151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>107.01</v>
+        <v>11.03</v>
       </c>
       <c r="D30" t="n">
-        <v>140.37</v>
+        <v>12.72</v>
       </c>
       <c r="E30" t="n">
-        <v>31.17</v>
+        <v>15.32</v>
       </c>
       <c r="F30" t="n">
-        <v>0.26141</v>
+        <v>-0.09100999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>298.32</v>
+        <v>27.14</v>
       </c>
       <c r="D31" t="n">
-        <v>365.44</v>
+        <v>31.52</v>
       </c>
       <c r="E31" t="n">
-        <v>22.5</v>
+        <v>16.14</v>
       </c>
       <c r="F31" t="n">
-        <v>4.70499</v>
+        <v>-0.35749</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>602.35</v>
+        <v>332.02</v>
       </c>
       <c r="D32" t="n">
-        <v>927.03</v>
+        <v>377.94</v>
       </c>
       <c r="E32" t="n">
-        <v>53.9</v>
+        <v>13.83</v>
       </c>
       <c r="F32" t="n">
-        <v>27.68843</v>
+        <v>-2.21821</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13.93</v>
+        <v>146.38</v>
       </c>
       <c r="D33" t="n">
-        <v>20.26</v>
+        <v>218.28</v>
       </c>
       <c r="E33" t="n">
-        <v>45.44</v>
+        <v>49.12</v>
       </c>
       <c r="F33" t="n">
-        <v>0.19565</v>
+        <v>0.00649</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>672.48</v>
+        <v>179.43</v>
       </c>
       <c r="D34" t="n">
-        <v>780.66</v>
+        <v>193.72</v>
       </c>
       <c r="E34" t="n">
-        <v>16.09</v>
+        <v>7.96</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.09502</v>
+        <v>0.57955</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.68</v>
+        <v>25.99</v>
       </c>
       <c r="D35" t="n">
-        <v>62.94</v>
+        <v>38.71</v>
       </c>
       <c r="E35" t="n">
-        <v>29.29</v>
+        <v>48.94</v>
       </c>
       <c r="F35" t="n">
-        <v>0.93229</v>
+        <v>0.54466</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>31.19</v>
+        <v>205.77</v>
       </c>
       <c r="D36" t="n">
-        <v>35.84</v>
+        <v>249.09</v>
       </c>
       <c r="E36" t="n">
-        <v>14.91</v>
+        <v>21.05</v>
       </c>
       <c r="F36" t="n">
-        <v>0.31383</v>
+        <v>2.72288</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>114.99</v>
+        <v>440.76</v>
       </c>
       <c r="D37" t="n">
-        <v>150.28</v>
+        <v>637.16</v>
       </c>
       <c r="E37" t="n">
-        <v>30.69</v>
+        <v>44.56</v>
       </c>
       <c r="F37" t="n">
-        <v>2.96523</v>
+        <v>1.42976</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9.31</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>10.31</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>10.74</v>
+        <v>18.82</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00165</v>
+        <v>-0.45827</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>179.43</v>
+        <v>103.45</v>
       </c>
       <c r="D39" t="n">
-        <v>190.31</v>
+        <v>149.67</v>
       </c>
       <c r="E39" t="n">
-        <v>6.06</v>
+        <v>44.68</v>
       </c>
       <c r="F39" t="n">
-        <v>0.80898</v>
+        <v>1.89428</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>205.77</v>
+        <v>198.14</v>
       </c>
       <c r="D40" t="n">
-        <v>243.29</v>
+        <v>261.67</v>
       </c>
       <c r="E40" t="n">
-        <v>18.23</v>
+        <v>32.06</v>
       </c>
       <c r="F40" t="n">
-        <v>1.22002</v>
+        <v>2.64766</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.99</v>
+        <v>41.44</v>
       </c>
       <c r="D41" t="n">
-        <v>36.24</v>
+        <v>45.25</v>
       </c>
       <c r="E41" t="n">
-        <v>39.44</v>
+        <v>9.19</v>
       </c>
       <c r="F41" t="n">
-        <v>0.29568</v>
+        <v>0.51531</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>440.76</v>
+        <v>510.39</v>
       </c>
       <c r="D42" t="n">
-        <v>621.17</v>
+        <v>652.39</v>
       </c>
       <c r="E42" t="n">
-        <v>40.93</v>
+        <v>27.82</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3329</v>
+        <v>4.4847</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>103.45</v>
+        <v>5.04</v>
       </c>
       <c r="D43" t="n">
-        <v>154.12</v>
+        <v>5.95</v>
       </c>
       <c r="E43" t="n">
-        <v>48.98</v>
+        <v>18.06</v>
       </c>
       <c r="F43" t="n">
-        <v>2.66631</v>
+        <v>0.05247</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GFI</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>31.25</v>
+        <v>176.25</v>
       </c>
       <c r="D44" t="n">
-        <v>45.1</v>
+        <v>249.59</v>
       </c>
       <c r="E44" t="n">
-        <v>44.32</v>
+        <v>41.61</v>
       </c>
       <c r="F44" t="n">
-        <v>0.62857</v>
+        <v>0.95658</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>187.36</v>
+        <v>162.11</v>
       </c>
       <c r="D45" t="n">
-        <v>252.28</v>
+        <v>176.94</v>
       </c>
       <c r="E45" t="n">
-        <v>34.65</v>
+        <v>9.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2.43143</v>
+        <v>0.35777</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>14.16</v>
+        <v>40.48</v>
       </c>
       <c r="D46" t="n">
-        <v>20.58</v>
+        <v>44.64</v>
       </c>
       <c r="E46" t="n">
-        <v>45.34</v>
+        <v>10.28</v>
       </c>
       <c r="F46" t="n">
-        <v>0.16176</v>
+        <v>0.1977</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>89.2</v>
+        <v>24.36</v>
       </c>
       <c r="D47" t="n">
-        <v>126.81</v>
+        <v>33.27</v>
       </c>
       <c r="E47" t="n">
-        <v>42.16</v>
+        <v>36.58</v>
       </c>
       <c r="F47" t="n">
-        <v>1.41665</v>
+        <v>0.5132100000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>136.34</v>
+        <v>31.45</v>
       </c>
       <c r="D48" t="n">
-        <v>200.36</v>
+        <v>36.65</v>
       </c>
       <c r="E48" t="n">
-        <v>46.96</v>
+        <v>16.53</v>
       </c>
       <c r="F48" t="n">
-        <v>1.09963</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EGO</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27.73</v>
+        <v>20.87</v>
       </c>
       <c r="D49" t="n">
-        <v>43.75</v>
+        <v>23.47</v>
       </c>
       <c r="E49" t="n">
-        <v>57.77</v>
+        <v>12.46</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4759</v>
+        <v>0.00191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SBSW</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>14.49</v>
       </c>
       <c r="D50" t="n">
-        <v>12.54</v>
+        <v>19.07</v>
       </c>
       <c r="E50" t="n">
-        <v>56.75</v>
+        <v>31.61</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3557</v>
+        <v>0.58389</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>28.05</v>
+        <v>15.99</v>
       </c>
       <c r="D51" t="n">
-        <v>36.03</v>
+        <v>21.15</v>
       </c>
       <c r="E51" t="n">
-        <v>28.45</v>
+        <v>32.27</v>
       </c>
       <c r="F51" t="n">
-        <v>0.23283</v>
+        <v>0.63574</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>198.14</v>
+        <v>38.92</v>
       </c>
       <c r="D52" t="n">
-        <v>266</v>
+        <v>50.32</v>
       </c>
       <c r="E52" t="n">
-        <v>34.25</v>
+        <v>29.29</v>
       </c>
       <c r="F52" t="n">
-        <v>3.20426</v>
+        <v>0.31609</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>41.44</v>
+        <v>165.69</v>
       </c>
       <c r="D53" t="n">
-        <v>44.85</v>
+        <v>212.17</v>
       </c>
       <c r="E53" t="n">
-        <v>8.23</v>
+        <v>28.05</v>
       </c>
       <c r="F53" t="n">
-        <v>0.46218</v>
+        <v>3.14062</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>510.39</v>
+        <v>40.25</v>
       </c>
       <c r="D54" t="n">
-        <v>650.5700000000001</v>
+        <v>49.73</v>
       </c>
       <c r="E54" t="n">
-        <v>27.47</v>
+        <v>23.55</v>
       </c>
       <c r="F54" t="n">
-        <v>4.1894</v>
+        <v>0.77667</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GAP</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>18.35</v>
+        <v>53.57</v>
       </c>
       <c r="D55" t="n">
-        <v>21.51</v>
+        <v>68.72</v>
       </c>
       <c r="E55" t="n">
-        <v>17.22</v>
+        <v>28.28</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07675</v>
+        <v>0.74953</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.04</v>
+        <v>45.57</v>
       </c>
       <c r="D56" t="n">
-        <v>6.02</v>
+        <v>55.4</v>
       </c>
       <c r="E56" t="n">
-        <v>19.44</v>
+        <v>21.57</v>
       </c>
       <c r="F56" t="n">
-        <v>0.05799</v>
+        <v>0.48559</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>176.25</v>
+        <v>17.93</v>
       </c>
       <c r="D57" t="n">
-        <v>244.6</v>
+        <v>23.76</v>
       </c>
       <c r="E57" t="n">
-        <v>38.78</v>
+        <v>32.52</v>
       </c>
       <c r="F57" t="n">
-        <v>1.52885</v>
+        <v>0.28866</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20.87</v>
+        <v>17.26</v>
       </c>
       <c r="D58" t="n">
-        <v>23.39</v>
+        <v>19.97</v>
       </c>
       <c r="E58" t="n">
-        <v>12.07</v>
+        <v>15.7</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02106</v>
+        <v>0.16925</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>40.48</v>
+        <v>13.01</v>
       </c>
       <c r="D59" t="n">
-        <v>44.71</v>
+        <v>17.53</v>
       </c>
       <c r="E59" t="n">
-        <v>10.45</v>
+        <v>34.74</v>
       </c>
       <c r="F59" t="n">
-        <v>0.24483</v>
+        <v>0.37919</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>24.36</v>
+        <v>110.99</v>
       </c>
       <c r="D60" t="n">
-        <v>33.11</v>
+        <v>131.83</v>
       </c>
       <c r="E60" t="n">
-        <v>35.92</v>
+        <v>18.78</v>
       </c>
       <c r="F60" t="n">
-        <v>0.55881</v>
+        <v>-0.18184</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>162.11</v>
+        <v>51.98</v>
       </c>
       <c r="D61" t="n">
-        <v>177.85</v>
+        <v>65.36</v>
       </c>
       <c r="E61" t="n">
-        <v>9.710000000000001</v>
+        <v>25.74</v>
       </c>
       <c r="F61" t="n">
-        <v>0.26806</v>
+        <v>-0.02228</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>13.01</v>
+        <v>171.96</v>
       </c>
       <c r="D62" t="n">
-        <v>17.4</v>
+        <v>205.72</v>
       </c>
       <c r="E62" t="n">
-        <v>33.74</v>
+        <v>19.63</v>
       </c>
       <c r="F62" t="n">
-        <v>0.39595</v>
+        <v>1.19691</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>53.57</v>
+        <v>36.15</v>
       </c>
       <c r="D63" t="n">
-        <v>68.83</v>
+        <v>45.93</v>
       </c>
       <c r="E63" t="n">
-        <v>28.49</v>
+        <v>27.05</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7410600000000001</v>
+        <v>0.8426</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>165.69</v>
+        <v>47.94</v>
       </c>
       <c r="D64" t="n">
-        <v>214.06</v>
+        <v>61.78</v>
       </c>
       <c r="E64" t="n">
-        <v>29.19</v>
+        <v>28.87</v>
       </c>
       <c r="F64" t="n">
-        <v>3.22174</v>
+        <v>0.67977</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>104.89</v>
+        <v>74.8</v>
       </c>
       <c r="D65" t="n">
-        <v>122.41</v>
+        <v>91.14</v>
       </c>
       <c r="E65" t="n">
-        <v>16.7</v>
+        <v>21.84</v>
       </c>
       <c r="F65" t="n">
-        <v>2.6088</v>
+        <v>1.02845</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>45.57</v>
+        <v>20.48</v>
       </c>
       <c r="D66" t="n">
-        <v>56.05</v>
+        <v>26.51</v>
       </c>
       <c r="E66" t="n">
-        <v>23</v>
+        <v>29.44</v>
       </c>
       <c r="F66" t="n">
-        <v>0.48828</v>
+        <v>0.19225</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,22 +2020,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>40.25</v>
+        <v>104.89</v>
       </c>
       <c r="D67" t="n">
-        <v>50.23</v>
+        <v>121.23</v>
       </c>
       <c r="E67" t="n">
-        <v>24.8</v>
+        <v>15.58</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7184199999999999</v>
+        <v>2.10701</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2044,22 +2044,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>103.22</v>
+        <v>31.87</v>
       </c>
       <c r="D68" t="n">
-        <v>137.35</v>
+        <v>45.03</v>
       </c>
       <c r="E68" t="n">
-        <v>33.07</v>
+        <v>41.29</v>
       </c>
       <c r="F68" t="n">
-        <v>2.07196</v>
+        <v>0.89874</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>47.94</v>
+        <v>103.22</v>
       </c>
       <c r="D69" t="n">
-        <v>61.46</v>
+        <v>136.67</v>
       </c>
       <c r="E69" t="n">
-        <v>28.2</v>
+        <v>32.41</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6323800000000001</v>
+        <v>2.02987</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2092,622 +2092,622 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>171.96</v>
+        <v>41.99</v>
       </c>
       <c r="D70" t="n">
-        <v>204.97</v>
+        <v>51.29</v>
       </c>
       <c r="E70" t="n">
-        <v>19.2</v>
+        <v>22.15</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6839499999999999</v>
+        <v>0.38063</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>45.09</v>
+        <v>167.73</v>
       </c>
       <c r="D71" t="n">
-        <v>56.06</v>
+        <v>182.9</v>
       </c>
       <c r="E71" t="n">
-        <v>24.33</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4946</v>
+        <v>-0.58001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>31.87</v>
+        <v>13.43</v>
       </c>
       <c r="D72" t="n">
-        <v>44.73</v>
+        <v>15.26</v>
       </c>
       <c r="E72" t="n">
-        <v>40.35</v>
+        <v>13.63</v>
       </c>
       <c r="F72" t="n">
-        <v>0.83755</v>
+        <v>0.08839</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>38.92</v>
+        <v>55.53</v>
       </c>
       <c r="D73" t="n">
-        <v>50.07</v>
+        <v>60.91</v>
       </c>
       <c r="E73" t="n">
-        <v>28.65</v>
+        <v>9.69</v>
       </c>
       <c r="F73" t="n">
-        <v>0.41042</v>
+        <v>0.22128</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>17.26</v>
+        <v>124.44</v>
       </c>
       <c r="D74" t="n">
-        <v>19.9</v>
+        <v>195</v>
       </c>
       <c r="E74" t="n">
-        <v>15.3</v>
+        <v>56.7</v>
       </c>
       <c r="F74" t="n">
-        <v>0.16707</v>
+        <v>0.72958</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>17.93</v>
+        <v>38.73</v>
       </c>
       <c r="D75" t="n">
-        <v>23.78</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>32.63</v>
+        <v>65.5</v>
       </c>
       <c r="F75" t="n">
-        <v>0.30747</v>
+        <v>-0.10866</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>36.15</v>
+        <v>62.05</v>
       </c>
       <c r="D76" t="n">
-        <v>46.1</v>
+        <v>81.22</v>
       </c>
       <c r="E76" t="n">
-        <v>27.52</v>
+        <v>30.89</v>
       </c>
       <c r="F76" t="n">
-        <v>0.82077</v>
+        <v>-0.5008899999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>74.8</v>
+        <v>13.31</v>
       </c>
       <c r="D77" t="n">
-        <v>91.89</v>
+        <v>25.76</v>
       </c>
       <c r="E77" t="n">
-        <v>22.85</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>1.02724</v>
+        <v>0.71191</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>41.99</v>
+        <v>135.44</v>
       </c>
       <c r="D78" t="n">
-        <v>50.61</v>
+        <v>174.39</v>
       </c>
       <c r="E78" t="n">
-        <v>20.53</v>
+        <v>28.76</v>
       </c>
       <c r="F78" t="n">
-        <v>0.32806</v>
+        <v>-1.62645</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>20.48</v>
+        <v>7.67</v>
       </c>
       <c r="D79" t="n">
-        <v>26.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E79" t="n">
-        <v>27.25</v>
+        <v>19.95</v>
       </c>
       <c r="F79" t="n">
-        <v>0.11669</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>236.5</v>
+        <v>218.58</v>
       </c>
       <c r="D80" t="n">
-        <v>284.75</v>
+        <v>280.46</v>
       </c>
       <c r="E80" t="n">
-        <v>20.4</v>
+        <v>28.31</v>
       </c>
       <c r="F80" t="n">
-        <v>3.75135</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>14.49</v>
+        <v>136.06</v>
       </c>
       <c r="D81" t="n">
-        <v>19.11</v>
+        <v>165.08</v>
       </c>
       <c r="E81" t="n">
-        <v>31.88</v>
+        <v>21.33</v>
       </c>
       <c r="F81" t="n">
-        <v>0.62325</v>
+        <v>1.65744</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>15.99</v>
+        <v>122.91</v>
       </c>
       <c r="D82" t="n">
-        <v>21.2</v>
+        <v>157.75</v>
       </c>
       <c r="E82" t="n">
-        <v>32.58</v>
+        <v>28.35</v>
       </c>
       <c r="F82" t="n">
-        <v>0.66898</v>
+        <v>-0.37771</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>124.44</v>
+        <v>82.31</v>
       </c>
       <c r="D83" t="n">
-        <v>183.9</v>
+        <v>136.94</v>
       </c>
       <c r="E83" t="n">
-        <v>47.78</v>
+        <v>66.37</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.87468</v>
+        <v>3.45518</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>55.53</v>
+        <v>18.94</v>
       </c>
       <c r="D84" t="n">
-        <v>58.49</v>
+        <v>23.74</v>
       </c>
       <c r="E84" t="n">
-        <v>5.33</v>
+        <v>25.34</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.14595</v>
+        <v>0.19609</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>13.31</v>
+        <v>39.54</v>
       </c>
       <c r="D85" t="n">
-        <v>25.03</v>
+        <v>51.41</v>
       </c>
       <c r="E85" t="n">
-        <v>88.05</v>
+        <v>30.02</v>
       </c>
       <c r="F85" t="n">
-        <v>0.68264</v>
+        <v>0.11249</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>13.43</v>
+        <v>56.4</v>
       </c>
       <c r="D86" t="n">
-        <v>14.94</v>
+        <v>80.81</v>
       </c>
       <c r="E86" t="n">
-        <v>11.24</v>
+        <v>43.28</v>
       </c>
       <c r="F86" t="n">
-        <v>0.07875</v>
+        <v>1.6696</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>167.73</v>
+        <v>31.03</v>
       </c>
       <c r="D87" t="n">
-        <v>182.33</v>
+        <v>44.54</v>
       </c>
       <c r="E87" t="n">
-        <v>8.699999999999999</v>
+        <v>43.54</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.7684299999999999</v>
+        <v>0.9863499999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>136.06</v>
+        <v>76.53</v>
       </c>
       <c r="D88" t="n">
-        <v>165.99</v>
+        <v>96.77</v>
       </c>
       <c r="E88" t="n">
-        <v>22</v>
+        <v>26.45</v>
       </c>
       <c r="F88" t="n">
-        <v>1.36664</v>
+        <v>1.4864</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7.67</v>
+        <v>142.52</v>
       </c>
       <c r="D89" t="n">
-        <v>9.359999999999999</v>
+        <v>191.45</v>
       </c>
       <c r="E89" t="n">
-        <v>22.03</v>
+        <v>34.33</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1989</v>
+        <v>1.43195</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>218.58</v>
+        <v>255.07</v>
       </c>
       <c r="D90" t="n">
-        <v>275.54</v>
+        <v>339.15</v>
       </c>
       <c r="E90" t="n">
-        <v>26.06</v>
+        <v>32.96</v>
       </c>
       <c r="F90" t="n">
-        <v>0.01914</v>
+        <v>-6.00233</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>18.94</v>
+        <v>44.39</v>
       </c>
       <c r="D91" t="n">
-        <v>23.69</v>
+        <v>61.14</v>
       </c>
       <c r="E91" t="n">
-        <v>25.08</v>
+        <v>37.73</v>
       </c>
       <c r="F91" t="n">
-        <v>0.18936</v>
+        <v>-0.05927</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>76.53</v>
+        <v>170.28</v>
       </c>
       <c r="D92" t="n">
-        <v>96.77</v>
+        <v>250.61</v>
       </c>
       <c r="E92" t="n">
-        <v>26.45</v>
+        <v>47.18</v>
       </c>
       <c r="F92" t="n">
-        <v>1.4864</v>
+        <v>-2.75775</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>82.31</v>
+        <v>352.83</v>
       </c>
       <c r="D93" t="n">
-        <v>130.97</v>
+        <v>505.41</v>
       </c>
       <c r="E93" t="n">
-        <v>59.12</v>
+        <v>43.24</v>
       </c>
       <c r="F93" t="n">
-        <v>3.77468</v>
+        <v>2.09735</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>56.4</v>
+        <v>59.71</v>
       </c>
       <c r="D94" t="n">
-        <v>78.87</v>
+        <v>79.11</v>
       </c>
       <c r="E94" t="n">
-        <v>39.84</v>
+        <v>32.49</v>
       </c>
       <c r="F94" t="n">
-        <v>1.3485</v>
+        <v>0.59687</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>31.03</v>
+        <v>42.46</v>
       </c>
       <c r="D95" t="n">
-        <v>44.8</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>44.38</v>
+        <v>64.3</v>
       </c>
       <c r="F95" t="n">
-        <v>0.96912</v>
+        <v>1.2992</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2716,22 +2716,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>42.46</v>
+        <v>107.27</v>
       </c>
       <c r="D96" t="n">
-        <v>65.65000000000001</v>
+        <v>173.31</v>
       </c>
       <c r="E96" t="n">
-        <v>54.62</v>
+        <v>61.56</v>
       </c>
       <c r="F96" t="n">
-        <v>0.94333</v>
+        <v>-1.05801</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2740,22 +2740,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>59.71</v>
+        <v>19.32</v>
       </c>
       <c r="D97" t="n">
-        <v>75.90000000000001</v>
+        <v>24.47</v>
       </c>
       <c r="E97" t="n">
-        <v>27.11</v>
+        <v>26.66</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.07714</v>
+        <v>-0.0342</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2764,22 +2764,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>352.83</v>
+        <v>49.87</v>
       </c>
       <c r="D98" t="n">
-        <v>495.63</v>
+        <v>63.17</v>
       </c>
       <c r="E98" t="n">
-        <v>40.47</v>
+        <v>26.67</v>
       </c>
       <c r="F98" t="n">
-        <v>1.11181</v>
+        <v>0.2007</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>EDU</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>49.87</v>
+        <v>44.44</v>
       </c>
       <c r="D99" t="n">
-        <v>61.42</v>
+        <v>56.82</v>
       </c>
       <c r="E99" t="n">
-        <v>23.16</v>
+        <v>27.86</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.11501</v>
+        <v>-0.38143</v>
       </c>
     </row>
     <row r="100">
@@ -2815,19 +2815,19 @@
         <v>166.5</v>
       </c>
       <c r="D100" t="n">
-        <v>198.2</v>
+        <v>197.56</v>
       </c>
       <c r="E100" t="n">
-        <v>19.04</v>
+        <v>18.65</v>
       </c>
       <c r="F100" t="n">
-        <v>0.09665</v>
+        <v>0.66935</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2836,40 +2836,40 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>19.32</v>
+        <v>136.68</v>
       </c>
       <c r="D101" t="n">
-        <v>23.9</v>
+        <v>153.4</v>
       </c>
       <c r="E101" t="n">
-        <v>23.71</v>
+        <v>12.23</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.13674</v>
+        <v>-2.51046</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>142.52</v>
+        <v>60.37</v>
       </c>
       <c r="D102" t="n">
-        <v>175.26</v>
+        <v>77</v>
       </c>
       <c r="E102" t="n">
-        <v>22.97</v>
+        <v>27.55</v>
       </c>
       <c r="F102" t="n">
-        <v>0.26584</v>
+        <v>1.31187</v>
       </c>
     </row>
     <row r="103">
@@ -2887,19 +2887,19 @@
         <v>62.12</v>
       </c>
       <c r="D103" t="n">
-        <v>77.67</v>
+        <v>79.13</v>
       </c>
       <c r="E103" t="n">
-        <v>25.03</v>
+        <v>27.38</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6581</v>
+        <v>0.8058999999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2908,118 +2908,118 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>60.37</v>
+        <v>10.51</v>
       </c>
       <c r="D104" t="n">
-        <v>78.45</v>
+        <v>15.27</v>
       </c>
       <c r="E104" t="n">
-        <v>29.95</v>
+        <v>45.29</v>
       </c>
       <c r="F104" t="n">
-        <v>1.83733</v>
+        <v>0.40451</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>36.09</v>
+        <v>48.79</v>
       </c>
       <c r="D105" t="n">
-        <v>38.9</v>
+        <v>68.53</v>
       </c>
       <c r="E105" t="n">
-        <v>7.79</v>
+        <v>40.46</v>
       </c>
       <c r="F105" t="n">
-        <v>0.13144</v>
+        <v>-0.01588</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10.51</v>
+        <v>102.17</v>
       </c>
       <c r="D106" t="n">
-        <v>15.8</v>
+        <v>131.24</v>
       </c>
       <c r="E106" t="n">
-        <v>50.33</v>
+        <v>28.45</v>
       </c>
       <c r="F106" t="n">
-        <v>0.39025</v>
+        <v>1.86006</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>48.79</v>
+        <v>76.55</v>
       </c>
       <c r="D107" t="n">
-        <v>65.94</v>
+        <v>105.82</v>
       </c>
       <c r="E107" t="n">
-        <v>35.15</v>
+        <v>38.24</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.36491</v>
+        <v>-1.58346</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>102.17</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D108" t="n">
-        <v>133.07</v>
+        <v>123.61</v>
       </c>
       <c r="E108" t="n">
-        <v>30.24</v>
+        <v>62.56</v>
       </c>
       <c r="F108" t="n">
-        <v>2.38111</v>
+        <v>2.41344</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3028,22 +3028,22 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>74.98999999999999</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D109" t="n">
-        <v>98.06999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="E109" t="n">
-        <v>30.78</v>
+        <v>13.71</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.77002</v>
+        <v>-0.43033</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>150.12</v>
+        <v>125.73</v>
       </c>
       <c r="D110" t="n">
-        <v>247.72</v>
+        <v>197.07</v>
       </c>
       <c r="E110" t="n">
-        <v>65.01000000000001</v>
+        <v>56.74</v>
       </c>
       <c r="F110" t="n">
-        <v>6.07809</v>
+        <v>-1.80321</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3076,3046 +3076,3046 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>76.04000000000001</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D111" t="n">
-        <v>117.91</v>
+        <v>104.47</v>
       </c>
       <c r="E111" t="n">
-        <v>55.06</v>
+        <v>39.31</v>
       </c>
       <c r="F111" t="n">
-        <v>1.7938</v>
+        <v>0.40712</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>141.17</v>
+        <v>275.27</v>
       </c>
       <c r="D112" t="n">
-        <v>174.83</v>
+        <v>359.54</v>
       </c>
       <c r="E112" t="n">
-        <v>23.84</v>
+        <v>30.61</v>
       </c>
       <c r="F112" t="n">
-        <v>1.12639</v>
+        <v>-2.74832</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>33.22</v>
+        <v>140.71</v>
       </c>
       <c r="D113" t="n">
-        <v>38.43</v>
+        <v>182.91</v>
       </c>
       <c r="E113" t="n">
-        <v>15.68</v>
+        <v>29.99</v>
       </c>
       <c r="F113" t="n">
-        <v>0.28995</v>
+        <v>-1.36471</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>32.47</v>
+        <v>150.12</v>
       </c>
       <c r="D114" t="n">
-        <v>38.04</v>
+        <v>259.43</v>
       </c>
       <c r="E114" t="n">
-        <v>17.15</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>0.14645</v>
+        <v>6.48113</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>450.75</v>
+        <v>123.42</v>
       </c>
       <c r="D115" t="n">
-        <v>546.78</v>
+        <v>164.55</v>
       </c>
       <c r="E115" t="n">
-        <v>21.3</v>
+        <v>33.33</v>
       </c>
       <c r="F115" t="n">
-        <v>2.73475</v>
+        <v>-0.65884</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>16.44</v>
+        <v>30.83</v>
       </c>
       <c r="D116" t="n">
-        <v>33</v>
+        <v>35.72</v>
       </c>
       <c r="E116" t="n">
-        <v>100.73</v>
+        <v>15.86</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4888</v>
+        <v>-0.35242</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>53.82</v>
+        <v>141.17</v>
       </c>
       <c r="D117" t="n">
-        <v>75.48999999999999</v>
+        <v>173.25</v>
       </c>
       <c r="E117" t="n">
-        <v>40.26</v>
+        <v>22.72</v>
       </c>
       <c r="F117" t="n">
-        <v>0.47907</v>
+        <v>1.14864</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>19.82</v>
+        <v>61.28</v>
       </c>
       <c r="D118" t="n">
-        <v>25.19</v>
+        <v>72.91</v>
       </c>
       <c r="E118" t="n">
-        <v>27.09</v>
+        <v>18.98</v>
       </c>
       <c r="F118" t="n">
-        <v>0.59848</v>
+        <v>-0.98211</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>91.88</v>
+        <v>48.87</v>
       </c>
       <c r="D119" t="n">
-        <v>129.41</v>
+        <v>58.74</v>
       </c>
       <c r="E119" t="n">
-        <v>40.85</v>
+        <v>20.2</v>
       </c>
       <c r="F119" t="n">
-        <v>1.61547</v>
+        <v>-0.40747</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2.86</v>
+        <v>450.75</v>
       </c>
       <c r="D120" t="n">
-        <v>3.2</v>
+        <v>548.65</v>
       </c>
       <c r="E120" t="n">
-        <v>11.89</v>
+        <v>21.72</v>
       </c>
       <c r="F120" t="n">
-        <v>0.02074</v>
+        <v>2.41907</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>14.05</v>
+        <v>32.47</v>
       </c>
       <c r="D121" t="n">
-        <v>19.78</v>
+        <v>38.43</v>
       </c>
       <c r="E121" t="n">
-        <v>40.78</v>
+        <v>18.36</v>
       </c>
       <c r="F121" t="n">
-        <v>0.23666</v>
+        <v>0.22774</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>ENSG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>14.94</v>
+        <v>147.13</v>
       </c>
       <c r="D122" t="n">
-        <v>19.86</v>
+        <v>174.93</v>
       </c>
       <c r="E122" t="n">
-        <v>32.93</v>
+        <v>18.89</v>
       </c>
       <c r="F122" t="n">
-        <v>0.61757</v>
+        <v>-0.59992</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>205.81</v>
+        <v>91.88</v>
       </c>
       <c r="D123" t="n">
-        <v>263.52</v>
+        <v>125.3</v>
       </c>
       <c r="E123" t="n">
-        <v>28.04</v>
+        <v>36.37</v>
       </c>
       <c r="F123" t="n">
-        <v>2.01368</v>
+        <v>1.50067</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>361.32</v>
+        <v>14.94</v>
       </c>
       <c r="D124" t="n">
-        <v>426.94</v>
+        <v>19.59</v>
       </c>
       <c r="E124" t="n">
-        <v>18.16</v>
+        <v>31.16</v>
       </c>
       <c r="F124" t="n">
-        <v>2.42172</v>
+        <v>0.52114</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>161.37</v>
+        <v>62.47</v>
       </c>
       <c r="D125" t="n">
-        <v>263.69</v>
+        <v>90.19</v>
       </c>
       <c r="E125" t="n">
-        <v>63.41</v>
+        <v>44.37</v>
       </c>
       <c r="F125" t="n">
-        <v>0.33828</v>
+        <v>-0.65359</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>43.67</v>
+        <v>16.44</v>
       </c>
       <c r="D126" t="n">
-        <v>46.99</v>
+        <v>33.97</v>
       </c>
       <c r="E126" t="n">
-        <v>7.6</v>
+        <v>106.63</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02819</v>
+        <v>0.60034</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>15.03</v>
+        <v>19.82</v>
       </c>
       <c r="D127" t="n">
-        <v>18.26</v>
+        <v>25.05</v>
       </c>
       <c r="E127" t="n">
-        <v>21.49</v>
+        <v>26.39</v>
       </c>
       <c r="F127" t="n">
-        <v>0.06938</v>
+        <v>0.40053</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>140.19</v>
+        <v>53.82</v>
       </c>
       <c r="D128" t="n">
-        <v>145.27</v>
+        <v>75</v>
       </c>
       <c r="E128" t="n">
-        <v>3.62</v>
+        <v>39.35</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.49238</v>
+        <v>0.53725</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>195.11</v>
+        <v>121.48</v>
       </c>
       <c r="D129" t="n">
-        <v>248.72</v>
+        <v>146.41</v>
       </c>
       <c r="E129" t="n">
-        <v>27.48</v>
+        <v>20.52</v>
       </c>
       <c r="F129" t="n">
-        <v>0.26006</v>
+        <v>0.04863</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>68.77</v>
+        <v>2.86</v>
       </c>
       <c r="D130" t="n">
-        <v>82.20999999999999</v>
+        <v>3.18</v>
       </c>
       <c r="E130" t="n">
-        <v>19.54</v>
+        <v>11.19</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.70053</v>
+        <v>0.02543</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ABVX</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>72.5</v>
+        <v>361.32</v>
       </c>
       <c r="D131" t="n">
-        <v>118.64</v>
+        <v>425.49</v>
       </c>
       <c r="E131" t="n">
-        <v>63.64</v>
+        <v>17.76</v>
       </c>
       <c r="F131" t="n">
-        <v>0.29802</v>
+        <v>4.42632</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>275.99</v>
+        <v>205.81</v>
       </c>
       <c r="D132" t="n">
-        <v>322.82</v>
+        <v>264.92</v>
       </c>
       <c r="E132" t="n">
-        <v>16.97</v>
+        <v>28.72</v>
       </c>
       <c r="F132" t="n">
-        <v>1.51503</v>
+        <v>1.32952</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>9.85</v>
+        <v>43.67</v>
       </c>
       <c r="D133" t="n">
-        <v>13.58</v>
+        <v>47.34</v>
       </c>
       <c r="E133" t="n">
-        <v>37.87</v>
+        <v>8.4</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5505</v>
+        <v>0.05503</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>33.54</v>
+        <v>161.37</v>
       </c>
       <c r="D134" t="n">
-        <v>42.85</v>
+        <v>264.51</v>
       </c>
       <c r="E134" t="n">
-        <v>27.76</v>
+        <v>63.92</v>
       </c>
       <c r="F134" t="n">
-        <v>0.17598</v>
+        <v>0.82511</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>63.54</v>
+        <v>55.05</v>
       </c>
       <c r="D135" t="n">
-        <v>69.90000000000001</v>
+        <v>63.57</v>
       </c>
       <c r="E135" t="n">
-        <v>10.01</v>
+        <v>15.48</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1817</v>
+        <v>-0.4736</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>190.4</v>
+        <v>28.18</v>
       </c>
       <c r="D136" t="n">
-        <v>217.62</v>
+        <v>37.03</v>
       </c>
       <c r="E136" t="n">
-        <v>14.3</v>
+        <v>31.41</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.59803</v>
+        <v>-0.01107</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>250.75</v>
+        <v>140.19</v>
       </c>
       <c r="D137" t="n">
-        <v>350.13</v>
+        <v>146.13</v>
       </c>
       <c r="E137" t="n">
-        <v>39.63</v>
+        <v>4.24</v>
       </c>
       <c r="F137" t="n">
-        <v>4.34655</v>
+        <v>-0.3931</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>529.12</v>
+        <v>195.11</v>
       </c>
       <c r="D138" t="n">
-        <v>675.74</v>
+        <v>249.05</v>
       </c>
       <c r="E138" t="n">
-        <v>27.71</v>
+        <v>27.65</v>
       </c>
       <c r="F138" t="n">
-        <v>10.73877</v>
+        <v>0.4172</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SGI</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>61.49</v>
+        <v>72.55</v>
       </c>
       <c r="D139" t="n">
-        <v>66.76000000000001</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E139" t="n">
-        <v>8.57</v>
+        <v>5.16</v>
       </c>
       <c r="F139" t="n">
-        <v>0.42927</v>
+        <v>-0.36496</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>196.07</v>
+        <v>207.24</v>
       </c>
       <c r="D140" t="n">
-        <v>211.96</v>
+        <v>253.88</v>
       </c>
       <c r="E140" t="n">
-        <v>8.1</v>
+        <v>22.51</v>
       </c>
       <c r="F140" t="n">
-        <v>0.04079</v>
+        <v>-2.67569</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>108.01</v>
+        <v>15.03</v>
       </c>
       <c r="D141" t="n">
-        <v>126.94</v>
+        <v>18.6</v>
       </c>
       <c r="E141" t="n">
-        <v>17.53</v>
+        <v>23.75</v>
       </c>
       <c r="F141" t="n">
-        <v>0.60472</v>
+        <v>0.08944000000000001</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>134.71</v>
+        <v>73.75</v>
       </c>
       <c r="D142" t="n">
-        <v>148.38</v>
+        <v>93.8</v>
       </c>
       <c r="E142" t="n">
-        <v>10.15</v>
+        <v>27.19</v>
       </c>
       <c r="F142" t="n">
-        <v>2.1441</v>
+        <v>0.31456</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BMRN</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>49.67</v>
+        <v>277.69</v>
       </c>
       <c r="D143" t="n">
-        <v>65.68000000000001</v>
+        <v>330.62</v>
       </c>
       <c r="E143" t="n">
-        <v>32.23</v>
+        <v>19.06</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.14491</v>
+        <v>-0.14398</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>26.18</v>
+        <v>275.99</v>
       </c>
       <c r="D144" t="n">
-        <v>36.49</v>
+        <v>322.99</v>
       </c>
       <c r="E144" t="n">
-        <v>39.38</v>
+        <v>17.03</v>
       </c>
       <c r="F144" t="n">
-        <v>0.03658</v>
+        <v>1.92883</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>438.34</v>
+        <v>36.25</v>
       </c>
       <c r="D145" t="n">
-        <v>609.8200000000001</v>
+        <v>41.61</v>
       </c>
       <c r="E145" t="n">
-        <v>39.12</v>
+        <v>14.79</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.56321</v>
+        <v>0.22556</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>63.16</v>
+        <v>309.78</v>
       </c>
       <c r="D146" t="n">
-        <v>102.04</v>
+        <v>341.85</v>
       </c>
       <c r="E146" t="n">
-        <v>61.56</v>
+        <v>10.35</v>
       </c>
       <c r="F146" t="n">
-        <v>1.24569</v>
+        <v>-1.13236</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>225.75</v>
+        <v>121.13</v>
       </c>
       <c r="D147" t="n">
-        <v>282.67</v>
+        <v>138.92</v>
       </c>
       <c r="E147" t="n">
-        <v>25.21</v>
+        <v>14.69</v>
       </c>
       <c r="F147" t="n">
-        <v>-3.23344</v>
+        <v>0.41111</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>73.42</v>
+        <v>132.79</v>
       </c>
       <c r="D148" t="n">
-        <v>90.29000000000001</v>
+        <v>163.39</v>
       </c>
       <c r="E148" t="n">
-        <v>22.98</v>
+        <v>23.04</v>
       </c>
       <c r="F148" t="n">
-        <v>0.77528</v>
+        <v>-0.12699</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>92.38</v>
+        <v>9.85</v>
       </c>
       <c r="D149" t="n">
-        <v>100.56</v>
+        <v>13.75</v>
       </c>
       <c r="E149" t="n">
-        <v>8.85</v>
+        <v>39.59</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.08179</v>
+        <v>0.51236</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>163.43</v>
+        <v>190.4</v>
       </c>
       <c r="D150" t="n">
-        <v>192.61</v>
+        <v>221.02</v>
       </c>
       <c r="E150" t="n">
-        <v>17.85</v>
+        <v>16.08</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.61748</v>
+        <v>0.04179</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>55.52</v>
+        <v>33.54</v>
       </c>
       <c r="D151" t="n">
-        <v>90.8</v>
+        <v>42.61</v>
       </c>
       <c r="E151" t="n">
-        <v>63.54</v>
+        <v>27.04</v>
       </c>
       <c r="F151" t="n">
-        <v>1.21071</v>
+        <v>0.13446</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>163.55</v>
+        <v>63.54</v>
       </c>
       <c r="D152" t="n">
-        <v>201.5</v>
+        <v>70.87</v>
       </c>
       <c r="E152" t="n">
-        <v>23.2</v>
+        <v>11.54</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.56516</v>
+        <v>0.26916</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MKC-V</t>
+          <t>IDCC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>45.59</v>
+        <v>250.75</v>
       </c>
       <c r="D153" t="n">
-        <v>56.53</v>
+        <v>340.38</v>
       </c>
       <c r="E153" t="n">
-        <v>24</v>
+        <v>35.74</v>
       </c>
       <c r="F153" t="n">
-        <v>0.71097</v>
+        <v>3.87926</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>99.3</v>
+        <v>529.12</v>
       </c>
       <c r="D154" t="n">
-        <v>153.79</v>
+        <v>681.46</v>
       </c>
       <c r="E154" t="n">
-        <v>54.87</v>
+        <v>28.79</v>
       </c>
       <c r="F154" t="n">
-        <v>0.5426299999999999</v>
+        <v>9.785550000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BSAC</t>
+          <t>SGI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>29.79</v>
+        <v>61.49</v>
       </c>
       <c r="D155" t="n">
-        <v>35.19</v>
+        <v>68.12</v>
       </c>
       <c r="E155" t="n">
-        <v>18.13</v>
+        <v>10.78</v>
       </c>
       <c r="F155" t="n">
-        <v>0.065</v>
+        <v>0.25125</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>197.73</v>
+        <v>57.4</v>
       </c>
       <c r="D156" t="n">
-        <v>222.74</v>
+        <v>104.79</v>
       </c>
       <c r="E156" t="n">
-        <v>12.65</v>
+        <v>82.56</v>
       </c>
       <c r="F156" t="n">
-        <v>0.63872</v>
+        <v>0.21284</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BMRN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>12.64</v>
+        <v>49.67</v>
       </c>
       <c r="D157" t="n">
-        <v>17.75</v>
+        <v>66.41</v>
       </c>
       <c r="E157" t="n">
-        <v>40.43</v>
+        <v>33.7</v>
       </c>
       <c r="F157" t="n">
-        <v>0.27258</v>
+        <v>0.03841</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>255.54</v>
+        <v>186.61</v>
       </c>
       <c r="D158" t="n">
-        <v>365.08</v>
+        <v>237.89</v>
       </c>
       <c r="E158" t="n">
-        <v>42.87</v>
+        <v>27.48</v>
       </c>
       <c r="F158" t="n">
-        <v>3.6115</v>
+        <v>-1.00997</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MPLX</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>54</v>
+        <v>5563.62</v>
       </c>
       <c r="D159" t="n">
-        <v>59.84</v>
+        <v>6299.56</v>
       </c>
       <c r="E159" t="n">
-        <v>10.81</v>
+        <v>13.23</v>
       </c>
       <c r="F159" t="n">
-        <v>0.28289</v>
+        <v>-44.26965</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>32.32</v>
+        <v>26.18</v>
       </c>
       <c r="D160" t="n">
-        <v>37.99</v>
+        <v>36.71</v>
       </c>
       <c r="E160" t="n">
-        <v>17.54</v>
+        <v>40.22</v>
       </c>
       <c r="F160" t="n">
-        <v>0.23389</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>699965</v>
+        <v>73.42</v>
       </c>
       <c r="D161" t="n">
-        <v>771770</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E161" t="n">
-        <v>10.26</v>
+        <v>20.83</v>
       </c>
       <c r="F161" t="n">
-        <v>2523.34448</v>
+        <v>0.7728699999999999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>139.71</v>
+        <v>63.16</v>
       </c>
       <c r="D162" t="n">
-        <v>192.6</v>
+        <v>101.84</v>
       </c>
       <c r="E162" t="n">
-        <v>37.86</v>
+        <v>61.24</v>
       </c>
       <c r="F162" t="n">
-        <v>1.1005</v>
+        <v>1.43086</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>45.37</v>
+        <v>438.34</v>
       </c>
       <c r="D163" t="n">
-        <v>143.97</v>
+        <v>613.62</v>
       </c>
       <c r="E163" t="n">
-        <v>217.32</v>
+        <v>39.99</v>
       </c>
       <c r="F163" t="n">
-        <v>5.1164</v>
+        <v>0.49995</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>82.26000000000001</v>
+        <v>92.38</v>
       </c>
       <c r="D164" t="n">
-        <v>124.31</v>
+        <v>100.65</v>
       </c>
       <c r="E164" t="n">
-        <v>51.12</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.05317</v>
+        <v>-0.07876</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>156.66</v>
+        <v>43.3</v>
       </c>
       <c r="D165" t="n">
-        <v>261.77</v>
+        <v>72.27</v>
       </c>
       <c r="E165" t="n">
-        <v>67.09</v>
+        <v>66.91</v>
       </c>
       <c r="F165" t="n">
-        <v>1.57783</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>13.06</v>
+        <v>163.43</v>
       </c>
       <c r="D166" t="n">
-        <v>19.65</v>
+        <v>200.67</v>
       </c>
       <c r="E166" t="n">
-        <v>50.46</v>
+        <v>22.79</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.07116</v>
+        <v>0.62133</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>197.38</v>
+        <v>156.84</v>
       </c>
       <c r="D167" t="n">
-        <v>257.12</v>
+        <v>187.03</v>
       </c>
       <c r="E167" t="n">
-        <v>30.27</v>
+        <v>19.25</v>
       </c>
       <c r="F167" t="n">
-        <v>-1.42463</v>
+        <v>-2.68499</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>56.06</v>
+        <v>55.52</v>
       </c>
       <c r="D168" t="n">
-        <v>62.44</v>
+        <v>94.83</v>
       </c>
       <c r="E168" t="n">
-        <v>11.38</v>
+        <v>70.8</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.03757</v>
+        <v>1.61921</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>465.4</v>
+        <v>101.75</v>
       </c>
       <c r="D169" t="n">
-        <v>510.37</v>
+        <v>129.17</v>
       </c>
       <c r="E169" t="n">
-        <v>9.66</v>
+        <v>26.95</v>
       </c>
       <c r="F169" t="n">
-        <v>0.88445</v>
+        <v>-0.25082</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>153.25</v>
+        <v>99.3</v>
       </c>
       <c r="D170" t="n">
-        <v>191.06</v>
+        <v>151.7</v>
       </c>
       <c r="E170" t="n">
-        <v>24.67</v>
+        <v>52.77</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.11953</v>
+        <v>1.17857</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>231.51</v>
+        <v>197.73</v>
       </c>
       <c r="D171" t="n">
-        <v>290.25</v>
+        <v>225.85</v>
       </c>
       <c r="E171" t="n">
-        <v>25.37</v>
+        <v>14.22</v>
       </c>
       <c r="F171" t="n">
-        <v>1.4568</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>20.96</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D172" t="n">
-        <v>26.1</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E172" t="n">
-        <v>24.52</v>
+        <v>28.9</v>
       </c>
       <c r="F172" t="n">
-        <v>0.32599</v>
+        <v>-0.34243</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>155.75</v>
+        <v>725.17</v>
       </c>
       <c r="D173" t="n">
-        <v>259.47</v>
+        <v>910.95</v>
       </c>
       <c r="E173" t="n">
-        <v>66.59</v>
+        <v>25.62</v>
       </c>
       <c r="F173" t="n">
-        <v>6.56374</v>
+        <v>1.91142</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>213.69</v>
+        <v>383.99</v>
       </c>
       <c r="D174" t="n">
-        <v>395.93</v>
+        <v>474.13</v>
       </c>
       <c r="E174" t="n">
-        <v>85.28</v>
+        <v>23.47</v>
       </c>
       <c r="F174" t="n">
-        <v>11.53328</v>
+        <v>-1.53084</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>40.59</v>
+        <v>12.64</v>
       </c>
       <c r="D175" t="n">
-        <v>55.55</v>
+        <v>17.74</v>
       </c>
       <c r="E175" t="n">
-        <v>36.86</v>
+        <v>40.35</v>
       </c>
       <c r="F175" t="n">
-        <v>1.21178</v>
+        <v>0.24281</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>83.51000000000001</v>
+        <v>255.54</v>
       </c>
       <c r="D176" t="n">
-        <v>96.62</v>
+        <v>365.08</v>
       </c>
       <c r="E176" t="n">
-        <v>15.7</v>
+        <v>42.87</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7579900000000001</v>
+        <v>3.26755</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>223.65</v>
+        <v>417.83</v>
       </c>
       <c r="D177" t="n">
-        <v>390.42</v>
+        <v>556.3099999999999</v>
       </c>
       <c r="E177" t="n">
-        <v>74.56999999999999</v>
+        <v>33.14</v>
       </c>
       <c r="F177" t="n">
-        <v>13.30066</v>
+        <v>0.43871</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>128.43</v>
+        <v>32.32</v>
       </c>
       <c r="D178" t="n">
-        <v>147.36</v>
+        <v>37.72</v>
       </c>
       <c r="E178" t="n">
-        <v>14.74</v>
+        <v>16.71</v>
       </c>
       <c r="F178" t="n">
-        <v>0.39775</v>
+        <v>0.15923</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>18.71</v>
+        <v>252.74</v>
       </c>
       <c r="D179" t="n">
-        <v>21.55</v>
+        <v>326.23</v>
       </c>
       <c r="E179" t="n">
-        <v>15.18</v>
+        <v>29.08</v>
       </c>
       <c r="F179" t="n">
-        <v>0.15383</v>
+        <v>-0.21978</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>66.95</v>
+        <v>699965</v>
       </c>
       <c r="D180" t="n">
-        <v>86.72</v>
+        <v>771770</v>
       </c>
       <c r="E180" t="n">
-        <v>29.53</v>
+        <v>10.26</v>
       </c>
       <c r="F180" t="n">
-        <v>1.46018</v>
+        <v>2523.34448</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>WES</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>40.41</v>
+        <v>139.71</v>
       </c>
       <c r="D181" t="n">
-        <v>49.03</v>
+        <v>193.61</v>
       </c>
       <c r="E181" t="n">
-        <v>21.33</v>
+        <v>38.58</v>
       </c>
       <c r="F181" t="n">
-        <v>0.19255</v>
+        <v>1.72426</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>83</v>
+        <v>45.37</v>
       </c>
       <c r="D182" t="n">
-        <v>132.53</v>
+        <v>146.69</v>
       </c>
       <c r="E182" t="n">
-        <v>59.67</v>
+        <v>223.32</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.01342</v>
+        <v>5.23484</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>166.99</v>
+        <v>112.47</v>
       </c>
       <c r="D183" t="n">
-        <v>306.53</v>
+        <v>138.5</v>
       </c>
       <c r="E183" t="n">
-        <v>83.56</v>
+        <v>23.14</v>
       </c>
       <c r="F183" t="n">
-        <v>5.16986</v>
+        <v>0.31006</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>151.43</v>
+        <v>156.66</v>
       </c>
       <c r="D184" t="n">
-        <v>262.4</v>
+        <v>265.67</v>
       </c>
       <c r="E184" t="n">
-        <v>73.28</v>
+        <v>69.58</v>
       </c>
       <c r="F184" t="n">
-        <v>1.63232</v>
+        <v>2.0428</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>57.15</v>
+        <v>13.06</v>
       </c>
       <c r="D185" t="n">
-        <v>179.7</v>
+        <v>19.91</v>
       </c>
       <c r="E185" t="n">
-        <v>214.44</v>
+        <v>52.45</v>
       </c>
       <c r="F185" t="n">
-        <v>2.90762</v>
+        <v>-0.009140000000000001</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>32.36</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D186" t="n">
-        <v>51.07</v>
+        <v>128.49</v>
       </c>
       <c r="E186" t="n">
-        <v>57.82</v>
+        <v>56.2</v>
       </c>
       <c r="F186" t="n">
-        <v>0.08409</v>
+        <v>0.08618000000000001</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>121.11</v>
+        <v>40.41</v>
       </c>
       <c r="D187" t="n">
-        <v>328.99</v>
+        <v>51.96</v>
       </c>
       <c r="E187" t="n">
-        <v>171.65</v>
+        <v>28.58</v>
       </c>
       <c r="F187" t="n">
-        <v>2.63639</v>
+        <v>-0.19889</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>17.89</v>
+        <v>197.38</v>
       </c>
       <c r="D188" t="n">
-        <v>30.26</v>
+        <v>261.77</v>
       </c>
       <c r="E188" t="n">
-        <v>69.14</v>
+        <v>32.62</v>
       </c>
       <c r="F188" t="n">
-        <v>0.14219</v>
+        <v>-0.05181</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>18.26</v>
+        <v>393.42</v>
       </c>
       <c r="D189" t="n">
-        <v>35.48</v>
+        <v>595.41</v>
       </c>
       <c r="E189" t="n">
-        <v>94.3</v>
+        <v>51.34</v>
       </c>
       <c r="F189" t="n">
-        <v>0.97924</v>
+        <v>-2.04834</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>62.93</v>
+        <v>465.4</v>
       </c>
       <c r="D190" t="n">
-        <v>166.5</v>
+        <v>514.95</v>
       </c>
       <c r="E190" t="n">
-        <v>164.58</v>
+        <v>10.65</v>
       </c>
       <c r="F190" t="n">
-        <v>4.92156</v>
+        <v>1.66879</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>95.67</v>
+        <v>56.06</v>
       </c>
       <c r="D191" t="n">
-        <v>199.28</v>
+        <v>62.39</v>
       </c>
       <c r="E191" t="n">
-        <v>108.3</v>
+        <v>11.29</v>
       </c>
       <c r="F191" t="n">
-        <v>0.61832</v>
+        <v>0.03839</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>56.43</v>
+        <v>74.63</v>
       </c>
       <c r="D192" t="n">
-        <v>107.84</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E192" t="n">
-        <v>91.09999999999999</v>
+        <v>19.72</v>
       </c>
       <c r="F192" t="n">
-        <v>3.47715</v>
+        <v>-0.05535</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>23.49</v>
+        <v>153.25</v>
       </c>
       <c r="D193" t="n">
-        <v>32.52</v>
+        <v>194.86</v>
       </c>
       <c r="E193" t="n">
-        <v>38.44</v>
+        <v>27.15</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.04284</v>
+        <v>0.85662</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>52.39</v>
+        <v>155.75</v>
       </c>
       <c r="D194" t="n">
-        <v>66.65000000000001</v>
+        <v>257.06</v>
       </c>
       <c r="E194" t="n">
-        <v>27.22</v>
+        <v>65.05</v>
       </c>
       <c r="F194" t="n">
-        <v>0.09493</v>
+        <v>5.74053</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>23.63</v>
+        <v>20.96</v>
       </c>
       <c r="D195" t="n">
-        <v>25.44</v>
+        <v>25.85</v>
       </c>
       <c r="E195" t="n">
-        <v>7.68</v>
+        <v>23.33</v>
       </c>
       <c r="F195" t="n">
-        <v>0.058</v>
+        <v>0.28351</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STRL</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>382.22</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="D196" t="n">
-        <v>511.04</v>
+        <v>96.97</v>
       </c>
       <c r="E196" t="n">
-        <v>33.7</v>
+        <v>16.12</v>
       </c>
       <c r="F196" t="n">
-        <v>-4.01339</v>
+        <v>0.63437</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>22.77</v>
+        <v>128.43</v>
       </c>
       <c r="D197" t="n">
-        <v>32.28</v>
+        <v>148.54</v>
       </c>
       <c r="E197" t="n">
-        <v>41.77</v>
+        <v>15.66</v>
       </c>
       <c r="F197" t="n">
-        <v>0.00061</v>
+        <v>0.66273</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>124.07</v>
+        <v>40.59</v>
       </c>
       <c r="D198" t="n">
-        <v>181.97</v>
+        <v>56.33</v>
       </c>
       <c r="E198" t="n">
-        <v>46.67</v>
+        <v>38.78</v>
       </c>
       <c r="F198" t="n">
-        <v>3.9716</v>
+        <v>1.40494</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>430.4</v>
+        <v>213.69</v>
       </c>
       <c r="D199" t="n">
-        <v>557.61</v>
+        <v>396.45</v>
       </c>
       <c r="E199" t="n">
-        <v>29.56</v>
+        <v>85.53</v>
       </c>
       <c r="F199" t="n">
-        <v>0.09331</v>
+        <v>10.30916</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>172.34</v>
+        <v>223.65</v>
       </c>
       <c r="D200" t="n">
-        <v>217.15</v>
+        <v>382.95</v>
       </c>
       <c r="E200" t="n">
-        <v>26</v>
+        <v>71.23</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.72394</v>
+        <v>12.04345</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>96.73</v>
+        <v>66.95</v>
       </c>
       <c r="D201" t="n">
-        <v>121.71</v>
+        <v>86.44</v>
       </c>
       <c r="E201" t="n">
-        <v>25.82</v>
+        <v>29.11</v>
       </c>
       <c r="F201" t="n">
-        <v>0.25986</v>
+        <v>1.50588</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>164.13</v>
+        <v>18.71</v>
       </c>
       <c r="D202" t="n">
-        <v>567.29</v>
+        <v>21.49</v>
       </c>
       <c r="E202" t="n">
-        <v>245.63</v>
+        <v>14.86</v>
       </c>
       <c r="F202" t="n">
-        <v>23.53755</v>
+        <v>0.13728</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>817.35</v>
+        <v>126.32</v>
       </c>
       <c r="D203" t="n">
-        <v>957.27</v>
+        <v>157.22</v>
       </c>
       <c r="E203" t="n">
-        <v>17.12</v>
+        <v>24.46</v>
       </c>
       <c r="F203" t="n">
-        <v>-2.74535</v>
+        <v>-0.32127</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>19.02</v>
+        <v>62.93</v>
       </c>
       <c r="D204" t="n">
-        <v>27.29</v>
+        <v>186.45</v>
       </c>
       <c r="E204" t="n">
-        <v>43.48</v>
+        <v>196.28</v>
       </c>
       <c r="F204" t="n">
-        <v>0.26062</v>
+        <v>6.24855</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>343.53</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D205" t="n">
-        <v>425.37</v>
+        <v>167.84</v>
       </c>
       <c r="E205" t="n">
-        <v>23.82</v>
+        <v>113.54</v>
       </c>
       <c r="F205" t="n">
-        <v>1.55336</v>
+        <v>-0.11311</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>107.27</v>
+        <v>17.89</v>
       </c>
       <c r="D206" t="n">
-        <v>138.82</v>
+        <v>31.41</v>
       </c>
       <c r="E206" t="n">
-        <v>29.41</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F206" t="n">
-        <v>1.16703</v>
+        <v>0.28103</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>41.19</v>
+        <v>43.81</v>
       </c>
       <c r="D207" t="n">
-        <v>102.94</v>
+        <v>100.2</v>
       </c>
       <c r="E207" t="n">
-        <v>149.92</v>
+        <v>128.71</v>
       </c>
       <c r="F207" t="n">
-        <v>3.32896</v>
+        <v>-0.42056</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>16.32</v>
+        <v>121.11</v>
       </c>
       <c r="D208" t="n">
-        <v>23.89</v>
+        <v>332.35</v>
       </c>
       <c r="E208" t="n">
-        <v>46.38</v>
+        <v>174.42</v>
       </c>
       <c r="F208" t="n">
-        <v>0.22921</v>
+        <v>2.08531</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>85.31999999999999</v>
+        <v>32.36</v>
       </c>
       <c r="D209" t="n">
-        <v>119.76</v>
+        <v>53.34</v>
       </c>
       <c r="E209" t="n">
-        <v>40.37</v>
+        <v>64.83</v>
       </c>
       <c r="F209" t="n">
-        <v>-0.8095</v>
+        <v>0.36656</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>59.58</v>
+        <v>76.7</v>
       </c>
       <c r="D210" t="n">
-        <v>83.92</v>
+        <v>170.18</v>
       </c>
       <c r="E210" t="n">
-        <v>40.86</v>
+        <v>121.88</v>
       </c>
       <c r="F210" t="n">
-        <v>0.38935</v>
+        <v>0.67575</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>220.86</v>
+        <v>118.05</v>
       </c>
       <c r="D211" t="n">
-        <v>345.71</v>
+        <v>191.73</v>
       </c>
       <c r="E211" t="n">
-        <v>56.53</v>
+        <v>62.41</v>
       </c>
       <c r="F211" t="n">
-        <v>1.06733</v>
+        <v>-0.40022</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ONTO</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>189.27</v>
+        <v>10.49</v>
       </c>
       <c r="D212" t="n">
-        <v>281.26</v>
+        <v>19.88</v>
       </c>
       <c r="E212" t="n">
-        <v>48.6</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="F212" t="n">
-        <v>-1.39091</v>
+        <v>-0.15382</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>28.61</v>
+        <v>112.5</v>
       </c>
       <c r="D213" t="n">
-        <v>37.87</v>
+        <v>194.21</v>
       </c>
       <c r="E213" t="n">
-        <v>32.37</v>
+        <v>72.63</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.008959999999999999</v>
+        <v>-1.0532</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>257.14</v>
+        <v>188.79</v>
       </c>
       <c r="D214" t="n">
-        <v>356.32</v>
+        <v>276.63</v>
       </c>
       <c r="E214" t="n">
-        <v>38.57</v>
+        <v>46.53</v>
       </c>
       <c r="F214" t="n">
-        <v>2.95633</v>
+        <v>-2.28574</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>73.13</v>
+        <v>120.88</v>
       </c>
       <c r="D215" t="n">
-        <v>96.68000000000001</v>
+        <v>211.54</v>
       </c>
       <c r="E215" t="n">
-        <v>32.2</v>
+        <v>75</v>
       </c>
       <c r="F215" t="n">
-        <v>0.53833</v>
+        <v>-0.8151</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3.88</v>
+        <v>57.15</v>
       </c>
       <c r="D216" t="n">
-        <v>6.43</v>
+        <v>192.77</v>
       </c>
       <c r="E216" t="n">
-        <v>65.72</v>
+        <v>237.31</v>
       </c>
       <c r="F216" t="n">
-        <v>0.10428</v>
+        <v>4.18785</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>124.03</v>
+        <v>151.43</v>
       </c>
       <c r="D217" t="n">
-        <v>216</v>
+        <v>265.67</v>
       </c>
       <c r="E217" t="n">
-        <v>74.15000000000001</v>
+        <v>75.44</v>
       </c>
       <c r="F217" t="n">
-        <v>3.76432</v>
+        <v>1.55591</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GLXY</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>17.15</v>
+        <v>34.41</v>
       </c>
       <c r="D218" t="n">
-        <v>24.4</v>
+        <v>67.69</v>
       </c>
       <c r="E218" t="n">
-        <v>42.27</v>
+        <v>96.72</v>
       </c>
       <c r="F218" t="n">
-        <v>0.44284</v>
+        <v>0.14027</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>90.01000000000001</v>
+        <v>117.65</v>
       </c>
       <c r="D219" t="n">
-        <v>102.7</v>
+        <v>231.88</v>
       </c>
       <c r="E219" t="n">
-        <v>14.1</v>
+        <v>97.09</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.07063999999999999</v>
+        <v>0.40682</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>52.5</v>
+        <v>83</v>
       </c>
       <c r="D220" t="n">
-        <v>88.34999999999999</v>
+        <v>142.35</v>
       </c>
       <c r="E220" t="n">
-        <v>68.29000000000001</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F220" t="n">
-        <v>4.42311</v>
+        <v>0.76309</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>321.8</v>
+        <v>25.85</v>
       </c>
       <c r="D221" t="n">
-        <v>975.26</v>
+        <v>42.91</v>
       </c>
       <c r="E221" t="n">
-        <v>203.06</v>
+        <v>66</v>
       </c>
       <c r="F221" t="n">
-        <v>16.22983</v>
+        <v>0.12798</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>316.5</v>
+        <v>105.37</v>
       </c>
       <c r="D222" t="n">
-        <v>433.24</v>
+        <v>230.05</v>
       </c>
       <c r="E222" t="n">
-        <v>36.88</v>
+        <v>118.33</v>
       </c>
       <c r="F222" t="n">
-        <v>5.00493</v>
+        <v>-1.90231</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>196.04</v>
+        <v>18.26</v>
       </c>
       <c r="D223" t="n">
-        <v>516.13</v>
+        <v>34.02</v>
       </c>
       <c r="E223" t="n">
-        <v>163.28</v>
+        <v>86.31</v>
       </c>
       <c r="F223" t="n">
-        <v>12.17477</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>VMI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>384.03</v>
+        <v>166.99</v>
       </c>
       <c r="D224" t="n">
-        <v>483.44</v>
+        <v>330.36</v>
       </c>
       <c r="E224" t="n">
-        <v>25.89</v>
+        <v>97.83</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.2071</v>
+        <v>9.064159999999999</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>77.04000000000001</v>
+        <v>56.43</v>
       </c>
       <c r="D225" t="n">
-        <v>112.13</v>
+        <v>106.91</v>
       </c>
       <c r="E225" t="n">
-        <v>45.55</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.71745</v>
+        <v>3.01266</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TTMI</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>88.29000000000001</v>
+        <v>23.49</v>
       </c>
       <c r="D226" t="n">
-        <v>126.44</v>
+        <v>32.49</v>
       </c>
       <c r="E226" t="n">
-        <v>43.21</v>
+        <v>38.31</v>
       </c>
       <c r="F226" t="n">
-        <v>1.06978</v>
+        <v>0.09743</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>20.33</v>
+        <v>23.63</v>
       </c>
       <c r="D227" t="n">
-        <v>29.55</v>
+        <v>25.41</v>
       </c>
       <c r="E227" t="n">
-        <v>45.35</v>
+        <v>7.53</v>
       </c>
       <c r="F227" t="n">
-        <v>0.15953</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>116.13</v>
+        <v>190.63</v>
       </c>
       <c r="D228" t="n">
-        <v>199.59</v>
+        <v>218.57</v>
       </c>
       <c r="E228" t="n">
-        <v>71.87</v>
+        <v>14.66</v>
       </c>
       <c r="F228" t="n">
-        <v>0.93349</v>
+        <v>-1.51875</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>303.1</v>
+        <v>124.07</v>
       </c>
       <c r="D229" t="n">
-        <v>378.78</v>
+        <v>180.15</v>
       </c>
       <c r="E229" t="n">
-        <v>24.97</v>
+        <v>45.2</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.37386</v>
+        <v>4.1705</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>131.47</v>
+        <v>62.49</v>
       </c>
       <c r="D230" t="n">
-        <v>204.23</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="E230" t="n">
-        <v>55.34</v>
+        <v>43.73</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.85663</v>
+        <v>-0.23607</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>186.42</v>
+        <v>172.34</v>
       </c>
       <c r="D231" t="n">
-        <v>268.7</v>
+        <v>217.36</v>
       </c>
       <c r="E231" t="n">
-        <v>44.14</v>
+        <v>26.12</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.8937</v>
+        <v>-0.19213</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>41.25</v>
+        <v>430.4</v>
       </c>
       <c r="D232" t="n">
-        <v>51.73</v>
+        <v>558.54</v>
       </c>
       <c r="E232" t="n">
-        <v>25.41</v>
+        <v>29.77</v>
       </c>
       <c r="F232" t="n">
-        <v>0.04002</v>
+        <v>0.26252</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SITM</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>311.23</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="D233" t="n">
-        <v>635.66</v>
+        <v>87.16</v>
       </c>
       <c r="E233" t="n">
-        <v>104.24</v>
+        <v>20.15</v>
       </c>
       <c r="F233" t="n">
-        <v>2.45158</v>
+        <v>-0.10751</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>BAC-PL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>209.49</v>
+        <v>1180</v>
       </c>
       <c r="D234" t="n">
-        <v>274.9</v>
+        <v>1297.24</v>
       </c>
       <c r="E234" t="n">
-        <v>31.22</v>
+        <v>9.94</v>
       </c>
       <c r="F234" t="n">
-        <v>1.16397</v>
+        <v>0.77758</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>55.66</v>
+        <v>96.73</v>
       </c>
       <c r="D235" t="n">
-        <v>76.14</v>
+        <v>122.53</v>
       </c>
       <c r="E235" t="n">
-        <v>36.79</v>
+        <v>26.67</v>
       </c>
       <c r="F235" t="n">
-        <v>-1.33547</v>
+        <v>0.4313</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>24.77</v>
+        <v>164.13</v>
       </c>
       <c r="D236" t="n">
-        <v>37.27</v>
+        <v>534.28</v>
       </c>
       <c r="E236" t="n">
-        <v>50.46</v>
+        <v>225.52</v>
       </c>
       <c r="F236" t="n">
-        <v>0.47609</v>
+        <v>21.33398</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>RF-PC</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>258.08</v>
+        <v>23.5</v>
       </c>
       <c r="D237" t="n">
-        <v>280.76</v>
+        <v>24.64</v>
       </c>
       <c r="E237" t="n">
-        <v>8.789999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="F237" t="n">
-        <v>-0.53063</v>
+        <v>0.07706</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6124,22 +6124,22 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>92.26000000000001</v>
+        <v>3.88</v>
       </c>
       <c r="D238" t="n">
-        <v>224.55</v>
+        <v>6.46</v>
       </c>
       <c r="E238" t="n">
-        <v>143.39</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F238" t="n">
-        <v>5.71318</v>
+        <v>0.08959</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>60.57</v>
+        <v>52.5</v>
       </c>
       <c r="D239" t="n">
-        <v>115.78</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="E239" t="n">
-        <v>91.15000000000001</v>
+        <v>50.97</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.17589</v>
+        <v>4.37139</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>87.81</v>
+        <v>131.47</v>
       </c>
       <c r="D240" t="n">
-        <v>236.1</v>
+        <v>214.07</v>
       </c>
       <c r="E240" t="n">
-        <v>168.88</v>
+        <v>62.83</v>
       </c>
       <c r="F240" t="n">
-        <v>3.38837</v>
+        <v>0.91734</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>126.58</v>
+        <v>199.3</v>
       </c>
       <c r="D241" t="n">
-        <v>146.01</v>
+        <v>351.81</v>
       </c>
       <c r="E241" t="n">
-        <v>15.35</v>
+        <v>76.52</v>
       </c>
       <c r="F241" t="n">
-        <v>0.38161</v>
+        <v>-1.44191</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,22 +6220,22 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>247.48</v>
+        <v>73.13</v>
       </c>
       <c r="D242" t="n">
-        <v>318.08</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E242" t="n">
-        <v>28.53</v>
+        <v>30.49</v>
       </c>
       <c r="F242" t="n">
-        <v>-1.78538</v>
+        <v>0.43563</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6244,22 +6244,22 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>57.45</v>
+        <v>273.5</v>
       </c>
       <c r="D243" t="n">
-        <v>70.48</v>
+        <v>349.39</v>
       </c>
       <c r="E243" t="n">
-        <v>22.68</v>
+        <v>27.75</v>
       </c>
       <c r="F243" t="n">
-        <v>-0.27768</v>
+        <v>-1.43004</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>533.78</v>
+        <v>69.3</v>
       </c>
       <c r="D244" t="n">
-        <v>650.58</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E244" t="n">
-        <v>21.88</v>
+        <v>20.55</v>
       </c>
       <c r="F244" t="n">
-        <v>-0.02439</v>
+        <v>0.20672</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>59.66</v>
+        <v>273.14</v>
       </c>
       <c r="D245" t="n">
-        <v>84.06</v>
+        <v>345.71</v>
       </c>
       <c r="E245" t="n">
-        <v>40.9</v>
+        <v>26.57</v>
       </c>
       <c r="F245" t="n">
-        <v>1.6949</v>
+        <v>-1.43948</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,16 +6316,16 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>572.5</v>
+        <v>22.61</v>
       </c>
       <c r="D246" t="n">
-        <v>1633.35</v>
+        <v>55.41</v>
       </c>
       <c r="E246" t="n">
-        <v>185.3</v>
+        <v>145.07</v>
       </c>
       <c r="F246" t="n">
-        <v>55.17344</v>
+        <v>1.53437</v>
       </c>
     </row>
     <row r="247">
@@ -6343,19 +6343,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="D247" t="n">
-        <v>22.64</v>
+        <v>21.9</v>
       </c>
       <c r="E247" t="n">
-        <v>162.95</v>
+        <v>154.36</v>
       </c>
       <c r="F247" t="n">
-        <v>0.88566</v>
+        <v>0.80893</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>219.65</v>
+        <v>166</v>
       </c>
       <c r="D248" t="n">
-        <v>305.37</v>
+        <v>407.02</v>
       </c>
       <c r="E248" t="n">
-        <v>39.03</v>
+        <v>145.19</v>
       </c>
       <c r="F248" t="n">
-        <v>3.42654</v>
+        <v>4.5493</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>166</v>
+        <v>119.51</v>
       </c>
       <c r="D249" t="n">
-        <v>409.8</v>
+        <v>257.05</v>
       </c>
       <c r="E249" t="n">
-        <v>146.87</v>
+        <v>115.09</v>
       </c>
       <c r="F249" t="n">
-        <v>4.61449</v>
+        <v>12.83332</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>119.51</v>
+        <v>29.16</v>
       </c>
       <c r="D250" t="n">
-        <v>275.75</v>
+        <v>39.94</v>
       </c>
       <c r="E250" t="n">
-        <v>130.73</v>
+        <v>36.97</v>
       </c>
       <c r="F250" t="n">
-        <v>16.30736</v>
+        <v>0.01199</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>29.16</v>
+        <v>97.52</v>
       </c>
       <c r="D251" t="n">
-        <v>40.11</v>
+        <v>132.88</v>
       </c>
       <c r="E251" t="n">
-        <v>37.55</v>
+        <v>36.26</v>
       </c>
       <c r="F251" t="n">
-        <v>-0.06358</v>
+        <v>2.17585</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>97.52</v>
+        <v>28.35</v>
       </c>
       <c r="D252" t="n">
-        <v>132.01</v>
+        <v>38.72</v>
       </c>
       <c r="E252" t="n">
-        <v>35.37</v>
+        <v>36.58</v>
       </c>
       <c r="F252" t="n">
-        <v>2.04384</v>
+        <v>0.29357</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>187.39</v>
+        <v>258.08</v>
       </c>
       <c r="D253" t="n">
-        <v>236.62</v>
+        <v>290.05</v>
       </c>
       <c r="E253" t="n">
-        <v>26.27</v>
+        <v>12.39</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.63052</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>257.27</v>
+        <v>24.77</v>
       </c>
       <c r="D254" t="n">
-        <v>346.55</v>
+        <v>36.96</v>
       </c>
       <c r="E254" t="n">
-        <v>34.7</v>
+        <v>49.21</v>
       </c>
       <c r="F254" t="n">
-        <v>8.016030000000001</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>69.3</v>
+        <v>284.79</v>
       </c>
       <c r="D255" t="n">
-        <v>83.20999999999999</v>
+        <v>424.24</v>
       </c>
       <c r="E255" t="n">
-        <v>20.07</v>
+        <v>48.97</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.161</v>
+        <v>5.01403</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>269.41</v>
+        <v>67.39</v>
       </c>
       <c r="D256" t="n">
-        <v>338.64</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E256" t="n">
-        <v>25.7</v>
+        <v>38.64</v>
       </c>
       <c r="F256" t="n">
-        <v>2.12017</v>
+        <v>0.55682</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>276.35</v>
+        <v>65.16</v>
       </c>
       <c r="D257" t="n">
-        <v>379.72</v>
+        <v>114.33</v>
       </c>
       <c r="E257" t="n">
-        <v>37.41</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="F257" t="n">
-        <v>3.99115</v>
+        <v>2.2454</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>28.35</v>
+        <v>19.02</v>
       </c>
       <c r="D258" t="n">
-        <v>37.09</v>
+        <v>27.24</v>
       </c>
       <c r="E258" t="n">
-        <v>30.83</v>
+        <v>43.22</v>
       </c>
       <c r="F258" t="n">
-        <v>0.11815</v>
+        <v>0.27865</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>7.96</v>
+        <v>20.33</v>
       </c>
       <c r="D259" t="n">
-        <v>11.13</v>
+        <v>29.1</v>
       </c>
       <c r="E259" t="n">
-        <v>39.82</v>
+        <v>43.14</v>
       </c>
       <c r="F259" t="n">
-        <v>0.2286</v>
+        <v>0.12624</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1273.18</v>
+        <v>16.32</v>
       </c>
       <c r="D260" t="n">
-        <v>1690.82</v>
+        <v>23.89</v>
       </c>
       <c r="E260" t="n">
-        <v>32.8</v>
+        <v>46.38</v>
       </c>
       <c r="F260" t="n">
-        <v>2.09023</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>20.89</v>
+        <v>41.19</v>
       </c>
       <c r="D261" t="n">
-        <v>39.47</v>
+        <v>97.19</v>
       </c>
       <c r="E261" t="n">
-        <v>88.94</v>
+        <v>135.96</v>
       </c>
       <c r="F261" t="n">
-        <v>0.8488599999999999</v>
+        <v>2.31858</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>31.8</v>
+        <v>107.27</v>
       </c>
       <c r="D262" t="n">
-        <v>66.42</v>
+        <v>136.18</v>
       </c>
       <c r="E262" t="n">
-        <v>108.87</v>
+        <v>26.95</v>
       </c>
       <c r="F262" t="n">
-        <v>-0.1597</v>
+        <v>1.00255</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>246.63</v>
+        <v>196.04</v>
       </c>
       <c r="D263" t="n">
-        <v>332.27</v>
+        <v>493.41</v>
       </c>
       <c r="E263" t="n">
-        <v>34.72</v>
+        <v>151.69</v>
       </c>
       <c r="F263" t="n">
-        <v>2.12426</v>
+        <v>9.84099</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>26.41</v>
+        <v>246.63</v>
       </c>
       <c r="D264" t="n">
-        <v>40.82</v>
+        <v>333.08</v>
       </c>
       <c r="E264" t="n">
-        <v>54.56</v>
+        <v>35.05</v>
       </c>
       <c r="F264" t="n">
-        <v>1.9156</v>
+        <v>3.52767</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>208.37</v>
+        <v>59.66</v>
       </c>
       <c r="D265" t="n">
-        <v>241.87</v>
+        <v>84.11</v>
       </c>
       <c r="E265" t="n">
-        <v>16.08</v>
+        <v>40.98</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.99486</v>
+        <v>1.58777</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>67.39</v>
+        <v>57.45</v>
       </c>
       <c r="D266" t="n">
-        <v>93.45</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E266" t="n">
-        <v>38.67</v>
+        <v>22.79</v>
       </c>
       <c r="F266" t="n">
-        <v>0.55333</v>
+        <v>-0.19886</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>21.06</v>
+        <v>279.73</v>
       </c>
       <c r="D267" t="n">
-        <v>40.1</v>
+        <v>411.49</v>
       </c>
       <c r="E267" t="n">
-        <v>90.41</v>
+        <v>47.1</v>
       </c>
       <c r="F267" t="n">
-        <v>0.93479</v>
+        <v>3.73943</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>65.16</v>
+        <v>26.41</v>
       </c>
       <c r="D268" t="n">
-        <v>112.57</v>
+        <v>41.02</v>
       </c>
       <c r="E268" t="n">
-        <v>72.76000000000001</v>
+        <v>55.32</v>
       </c>
       <c r="F268" t="n">
-        <v>2.79859</v>
+        <v>1.68935</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>112.75</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D269" t="n">
-        <v>162.38</v>
+        <v>100.36</v>
       </c>
       <c r="E269" t="n">
-        <v>44.02</v>
+        <v>11.5</v>
       </c>
       <c r="F269" t="n">
-        <v>1.48447</v>
+        <v>0.11228</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6892,22 +6892,22 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>107.11</v>
+        <v>31.8</v>
       </c>
       <c r="D270" t="n">
-        <v>126.4</v>
+        <v>69.41</v>
       </c>
       <c r="E270" t="n">
-        <v>18.01</v>
+        <v>118.27</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.54744</v>
+        <v>0.31551</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6916,22 +6916,22 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>284.79</v>
+        <v>204.77</v>
       </c>
       <c r="D271" t="n">
-        <v>418.72</v>
+        <v>274.99</v>
       </c>
       <c r="E271" t="n">
-        <v>47.03</v>
+        <v>34.29</v>
       </c>
       <c r="F271" t="n">
-        <v>3.19445</v>
+        <v>0.55032</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,46 +6940,46 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>279.73</v>
+        <v>12.96</v>
       </c>
       <c r="D272" t="n">
-        <v>411.71</v>
+        <v>16.66</v>
       </c>
       <c r="E272" t="n">
-        <v>47.18</v>
+        <v>28.55</v>
       </c>
       <c r="F272" t="n">
-        <v>1.83095</v>
+        <v>-0.0515</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>181.03</v>
+        <v>147.02</v>
       </c>
       <c r="D273" t="n">
-        <v>204.14</v>
+        <v>373.94</v>
       </c>
       <c r="E273" t="n">
-        <v>12.77</v>
+        <v>154.35</v>
       </c>
       <c r="F273" t="n">
-        <v>-1.65921</v>
+        <v>-2.08465</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>AXSM</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>122.52</v>
+        <v>156.35</v>
       </c>
       <c r="D274" t="n">
-        <v>193.4</v>
+        <v>216.58</v>
       </c>
       <c r="E274" t="n">
-        <v>57.85</v>
+        <v>38.52</v>
       </c>
       <c r="F274" t="n">
-        <v>0.72575</v>
+        <v>1.76572</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>35.34</v>
+        <v>92.39</v>
       </c>
       <c r="D275" t="n">
-        <v>53.34</v>
+        <v>235.38</v>
       </c>
       <c r="E275" t="n">
-        <v>50.93</v>
+        <v>154.75</v>
       </c>
       <c r="F275" t="n">
-        <v>0.64798</v>
+        <v>2.36905</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>46.97</v>
+        <v>7.63</v>
       </c>
       <c r="D276" t="n">
-        <v>62.69</v>
+        <v>11.33</v>
       </c>
       <c r="E276" t="n">
-        <v>33.47</v>
+        <v>48.49</v>
       </c>
       <c r="F276" t="n">
-        <v>0.03608</v>
+        <v>0.16084</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,22 +7060,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>525.72</v>
+        <v>284.93</v>
       </c>
       <c r="D277" t="n">
-        <v>648.03</v>
+        <v>412.56</v>
       </c>
       <c r="E277" t="n">
-        <v>23.27</v>
+        <v>44.79</v>
       </c>
       <c r="F277" t="n">
-        <v>18.95295</v>
+        <v>0.67323</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7084,22 +7084,22 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>7.63</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D278" t="n">
-        <v>11.45</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="E278" t="n">
-        <v>50.07</v>
+        <v>18.13</v>
       </c>
       <c r="F278" t="n">
-        <v>0.15777</v>
+        <v>-0.43807</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7108,22 +7108,22 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>317.4</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D279" t="n">
-        <v>413.78</v>
+        <v>94.92</v>
       </c>
       <c r="E279" t="n">
-        <v>30.37</v>
+        <v>30.21</v>
       </c>
       <c r="F279" t="n">
-        <v>-1.68102</v>
+        <v>0.7454499999999999</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7132,22 +7132,22 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>33.63</v>
+        <v>285.27</v>
       </c>
       <c r="D280" t="n">
-        <v>43.49</v>
+        <v>378.05</v>
       </c>
       <c r="E280" t="n">
-        <v>29.32</v>
+        <v>32.52</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.02051</v>
+        <v>1.30077</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7156,22 +7156,22 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>87.98</v>
+        <v>33.63</v>
       </c>
       <c r="D281" t="n">
-        <v>107.75</v>
+        <v>43.55</v>
       </c>
       <c r="E281" t="n">
-        <v>22.47</v>
+        <v>29.5</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.06295000000000001</v>
+        <v>-0.00236</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7180,22 +7180,22 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>285.27</v>
+        <v>202.71</v>
       </c>
       <c r="D282" t="n">
-        <v>375.2</v>
+        <v>258.48</v>
       </c>
       <c r="E282" t="n">
-        <v>31.52</v>
+        <v>27.51</v>
       </c>
       <c r="F282" t="n">
-        <v>0.13349</v>
+        <v>-1.41316</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7204,22 +7204,22 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>156.35</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D283" t="n">
-        <v>220.75</v>
+        <v>157.45</v>
       </c>
       <c r="E283" t="n">
-        <v>41.19</v>
+        <v>80.67</v>
       </c>
       <c r="F283" t="n">
-        <v>1.02948</v>
+        <v>-0.08858000000000001</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7228,22 +7228,22 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>121.84</v>
+        <v>91.37</v>
       </c>
       <c r="D284" t="n">
-        <v>157.77</v>
+        <v>120.93</v>
       </c>
       <c r="E284" t="n">
-        <v>29.49</v>
+        <v>32.35</v>
       </c>
       <c r="F284" t="n">
-        <v>-1.31209</v>
+        <v>-0.10485</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7252,22 +7252,22 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>79.19</v>
+        <v>22.3</v>
       </c>
       <c r="D285" t="n">
-        <v>105.3</v>
+        <v>34.8</v>
       </c>
       <c r="E285" t="n">
-        <v>32.97</v>
+        <v>56.05</v>
       </c>
       <c r="F285" t="n">
-        <v>0.32431</v>
+        <v>0.45747</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7276,22 +7276,22 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>282.84</v>
+        <v>39.84</v>
       </c>
       <c r="D286" t="n">
-        <v>356.23</v>
+        <v>58.53</v>
       </c>
       <c r="E286" t="n">
-        <v>25.95</v>
+        <v>46.91</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.63374</v>
+        <v>-0.08142000000000001</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7300,22 +7300,22 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>22.3</v>
+        <v>10.65</v>
       </c>
       <c r="D287" t="n">
-        <v>34.67</v>
+        <v>14.74</v>
       </c>
       <c r="E287" t="n">
-        <v>55.47</v>
+        <v>38.4</v>
       </c>
       <c r="F287" t="n">
-        <v>0.3951</v>
+        <v>0.05009</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7324,22 +7324,22 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>182.65</v>
+        <v>92.42</v>
       </c>
       <c r="D288" t="n">
-        <v>328.93</v>
+        <v>108.59</v>
       </c>
       <c r="E288" t="n">
-        <v>80.09</v>
+        <v>17.5</v>
       </c>
       <c r="F288" t="n">
-        <v>3.00967</v>
+        <v>0.1877</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>LYG</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7348,22 +7348,22 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>4.83</v>
+        <v>20.72</v>
       </c>
       <c r="D289" t="n">
-        <v>6.01</v>
+        <v>24.85</v>
       </c>
       <c r="E289" t="n">
-        <v>24.43</v>
+        <v>19.93</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.02334</v>
+        <v>-0.07012</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7372,22 +7372,22 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>134.99</v>
+        <v>17.45</v>
       </c>
       <c r="D290" t="n">
-        <v>189.19</v>
+        <v>19.8</v>
       </c>
       <c r="E290" t="n">
-        <v>40.15</v>
+        <v>13.47</v>
       </c>
       <c r="F290" t="n">
-        <v>0.28198</v>
+        <v>-0.03105</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7396,22 +7396,22 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>14.27</v>
+        <v>55.4</v>
       </c>
       <c r="D291" t="n">
-        <v>18.89</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E291" t="n">
-        <v>32.38</v>
+        <v>24.87</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.00158</v>
+        <v>-0.03903</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7420,22 +7420,22 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>28.37</v>
+        <v>295.52</v>
       </c>
       <c r="D292" t="n">
-        <v>40.48</v>
+        <v>375.28</v>
       </c>
       <c r="E292" t="n">
-        <v>42.69</v>
+        <v>26.99</v>
       </c>
       <c r="F292" t="n">
-        <v>0.44352</v>
+        <v>-0.74265</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7444,22 +7444,22 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>10.65</v>
+        <v>3.42</v>
       </c>
       <c r="D293" t="n">
-        <v>14.96</v>
+        <v>4.89</v>
       </c>
       <c r="E293" t="n">
-        <v>40.47</v>
+        <v>42.98</v>
       </c>
       <c r="F293" t="n">
-        <v>0.068</v>
+        <v>0.09469</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7468,22 +7468,22 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>67.7</v>
+        <v>525.72</v>
       </c>
       <c r="D294" t="n">
-        <v>97.14</v>
+        <v>665.6</v>
       </c>
       <c r="E294" t="n">
-        <v>43.49</v>
+        <v>26.61</v>
       </c>
       <c r="F294" t="n">
-        <v>0.04813</v>
+        <v>22.11172</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7492,22 +7492,22 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>284.93</v>
+        <v>289.16</v>
       </c>
       <c r="D295" t="n">
-        <v>408.22</v>
+        <v>410.01</v>
       </c>
       <c r="E295" t="n">
-        <v>43.27</v>
+        <v>41.79</v>
       </c>
       <c r="F295" t="n">
-        <v>0.1641</v>
+        <v>-0.38142</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SPG-PJ</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7516,22 +7516,22 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>52.49</v>
+        <v>67.7</v>
       </c>
       <c r="D296" t="n">
-        <v>55.78</v>
+        <v>97.75</v>
       </c>
       <c r="E296" t="n">
-        <v>6.27</v>
+        <v>44.39</v>
       </c>
       <c r="F296" t="n">
-        <v>-0.04614</v>
+        <v>0.25783</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7540,22 +7540,22 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>92.42</v>
+        <v>317.93</v>
       </c>
       <c r="D297" t="n">
-        <v>106.55</v>
+        <v>379.54</v>
       </c>
       <c r="E297" t="n">
-        <v>15.29</v>
+        <v>19.38</v>
       </c>
       <c r="F297" t="n">
-        <v>-0.16412</v>
+        <v>-0.71048</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7564,22 +7564,22 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>289.16</v>
+        <v>125.78</v>
       </c>
       <c r="D298" t="n">
-        <v>408.34</v>
+        <v>143.7</v>
       </c>
       <c r="E298" t="n">
-        <v>41.22</v>
+        <v>14.25</v>
       </c>
       <c r="F298" t="n">
-        <v>-1.16894</v>
+        <v>-0.39666</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7588,22 +7588,22 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>72.90000000000001</v>
+        <v>157.12</v>
       </c>
       <c r="D299" t="n">
-        <v>94.42</v>
+        <v>261.12</v>
       </c>
       <c r="E299" t="n">
-        <v>29.52</v>
+        <v>66.19</v>
       </c>
       <c r="F299" t="n">
-        <v>0.73445</v>
+        <v>1.88244</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7612,22 +7612,22 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>39.84</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D300" t="n">
-        <v>58.55</v>
+        <v>116.9</v>
       </c>
       <c r="E300" t="n">
-        <v>46.96</v>
+        <v>34.35</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.18999</v>
+        <v>0.85321</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>QSR</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7636,22 +7636,22 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>91.37</v>
+        <v>71.42</v>
       </c>
       <c r="D301" t="n">
-        <v>120.97</v>
+        <v>78.89</v>
       </c>
       <c r="E301" t="n">
-        <v>32.4</v>
+        <v>10.46</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.15904</v>
+        <v>-0.24064</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7660,22 +7660,22 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>50.85</v>
+        <v>243.35</v>
       </c>
       <c r="D302" t="n">
-        <v>62.84</v>
+        <v>355.2</v>
       </c>
       <c r="E302" t="n">
-        <v>23.58</v>
+        <v>45.96</v>
       </c>
       <c r="F302" t="n">
-        <v>-0.14971</v>
+        <v>0.55648</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7684,22 +7684,22 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>20.72</v>
+        <v>182.65</v>
       </c>
       <c r="D303" t="n">
-        <v>24.74</v>
+        <v>341.79</v>
       </c>
       <c r="E303" t="n">
-        <v>19.4</v>
+        <v>87.13</v>
       </c>
       <c r="F303" t="n">
-        <v>-0.18065</v>
+        <v>4.40399</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7708,22 +7708,22 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>36.41</v>
+        <v>87.98</v>
       </c>
       <c r="D304" t="n">
-        <v>54.58</v>
+        <v>108.99</v>
       </c>
       <c r="E304" t="n">
-        <v>49.9</v>
+        <v>23.88</v>
       </c>
       <c r="F304" t="n">
-        <v>0.12294</v>
+        <v>0.3621</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7732,22 +7732,22 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>14</v>
+        <v>61.37</v>
       </c>
       <c r="D305" t="n">
-        <v>14.79</v>
+        <v>80.23</v>
       </c>
       <c r="E305" t="n">
-        <v>5.64</v>
+        <v>30.73</v>
       </c>
       <c r="F305" t="n">
-        <v>0.01762</v>
+        <v>-0.09644999999999999</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7756,22 +7756,22 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>7.58</v>
+        <v>35.34</v>
       </c>
       <c r="D306" t="n">
-        <v>10.86</v>
+        <v>53.67</v>
       </c>
       <c r="E306" t="n">
-        <v>43.27</v>
+        <v>51.87</v>
       </c>
       <c r="F306" t="n">
-        <v>0.18842</v>
+        <v>0.74151</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7780,424 +7780,472 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3.93</v>
+        <v>35.72</v>
       </c>
       <c r="D307" t="n">
-        <v>5.68</v>
+        <v>49.48</v>
       </c>
       <c r="E307" t="n">
-        <v>44.53</v>
+        <v>38.52</v>
       </c>
       <c r="F307" t="n">
-        <v>0.03783</v>
+        <v>-0.54794</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>17.13</v>
+        <v>213.28</v>
       </c>
       <c r="D308" t="n">
-        <v>43.96</v>
+        <v>283.27</v>
       </c>
       <c r="E308" t="n">
-        <v>156.63</v>
+        <v>32.82</v>
       </c>
       <c r="F308" t="n">
-        <v>0.24682</v>
+        <v>-0.5633</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>63.78</v>
+        <v>7.58</v>
       </c>
       <c r="D309" t="n">
-        <v>68.98</v>
+        <v>10.73</v>
       </c>
       <c r="E309" t="n">
-        <v>8.15</v>
+        <v>41.56</v>
       </c>
       <c r="F309" t="n">
-        <v>0.05541</v>
+        <v>0.17999</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>99.98999999999999</v>
+        <v>3.93</v>
       </c>
       <c r="D310" t="n">
-        <v>169.31</v>
+        <v>5.84</v>
       </c>
       <c r="E310" t="n">
-        <v>69.33</v>
+        <v>48.6</v>
       </c>
       <c r="F310" t="n">
-        <v>-0.89257</v>
+        <v>0.07327</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ABEV</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2.78</v>
+        <v>153.68</v>
       </c>
       <c r="D311" t="n">
-        <v>3.02</v>
+        <v>172.02</v>
       </c>
       <c r="E311" t="n">
-        <v>8.630000000000001</v>
+        <v>11.93</v>
       </c>
       <c r="F311" t="n">
-        <v>0.03112</v>
+        <v>-0.63445</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>HMY</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="D312" t="n">
-        <v>20.64</v>
+        <v>14.8</v>
       </c>
       <c r="E312" t="n">
-        <v>48.92</v>
+        <v>5.71</v>
       </c>
       <c r="F312" t="n">
-        <v>0.12952</v>
+        <v>0.01308</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>23.65</v>
+        <v>121.84</v>
       </c>
       <c r="D313" t="n">
-        <v>28.33</v>
+        <v>162.38</v>
       </c>
       <c r="E313" t="n">
-        <v>19.79</v>
+        <v>33.27</v>
       </c>
       <c r="F313" t="n">
-        <v>0.11786</v>
+        <v>0.05096</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>134.96</v>
+        <v>67.23</v>
       </c>
       <c r="D314" t="n">
-        <v>264.79</v>
+        <v>98.22</v>
       </c>
       <c r="E314" t="n">
-        <v>96.2</v>
+        <v>46.1</v>
       </c>
       <c r="F314" t="n">
-        <v>3.15965</v>
+        <v>-0.14265</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MDGL</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>445.04</v>
+        <v>17.13</v>
       </c>
       <c r="D315" t="n">
-        <v>534.49</v>
+        <v>43.45</v>
       </c>
       <c r="E315" t="n">
-        <v>20.1</v>
+        <v>153.65</v>
       </c>
       <c r="F315" t="n">
-        <v>1.8121</v>
+        <v>0.28998</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>160.62</v>
+        <v>63.78</v>
       </c>
       <c r="D316" t="n">
-        <v>259.43</v>
+        <v>70.61</v>
       </c>
       <c r="E316" t="n">
-        <v>61.52</v>
+        <v>10.71</v>
       </c>
       <c r="F316" t="n">
-        <v>0.38868</v>
+        <v>0.28252</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>241.4</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D317" t="n">
-        <v>346.23</v>
+        <v>168.93</v>
       </c>
       <c r="E317" t="n">
-        <v>43.43</v>
+        <v>68.95</v>
       </c>
       <c r="F317" t="n">
-        <v>-1.22178</v>
+        <v>0.20101</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>55.05</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D318" t="n">
-        <v>68.75</v>
+        <v>112.01</v>
       </c>
       <c r="E318" t="n">
-        <v>24.89</v>
+        <v>18.86</v>
       </c>
       <c r="F318" t="n">
-        <v>-0.12841</v>
+        <v>-0.19592</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>22.32</v>
+        <v>241.14</v>
       </c>
       <c r="D319" t="n">
-        <v>62.09</v>
+        <v>298.6</v>
       </c>
       <c r="E319" t="n">
-        <v>178.18</v>
+        <v>23.83</v>
       </c>
       <c r="F319" t="n">
-        <v>1.76115</v>
+        <v>1.64228</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>240.92</v>
+        <v>2.78</v>
       </c>
       <c r="D320" t="n">
-        <v>292.71</v>
+        <v>3.03</v>
       </c>
       <c r="E320" t="n">
-        <v>21.5</v>
+        <v>8.99</v>
       </c>
       <c r="F320" t="n">
-        <v>0.08883000000000001</v>
+        <v>0.02721</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>MDGL</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>156.37</v>
+        <v>445.04</v>
       </c>
       <c r="D321" t="n">
-        <v>269.21</v>
+        <v>540.0599999999999</v>
       </c>
       <c r="E321" t="n">
-        <v>72.16</v>
+        <v>21.35</v>
       </c>
       <c r="F321" t="n">
-        <v>1.81533</v>
+        <v>2.20142</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3.41</v>
+        <v>146.17</v>
       </c>
       <c r="D322" t="n">
-        <v>5.15</v>
+        <v>217.15</v>
       </c>
       <c r="E322" t="n">
-        <v>51.03</v>
+        <v>48.56</v>
       </c>
       <c r="F322" t="n">
-        <v>0.12255</v>
+        <v>0.01127</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>202.78</v>
+        <v>23.97</v>
       </c>
       <c r="D323" t="n">
-        <v>270.45</v>
+        <v>30.56</v>
       </c>
       <c r="E323" t="n">
-        <v>33.37</v>
+        <v>27.49</v>
       </c>
       <c r="F323" t="n">
-        <v>0.5861499999999999</v>
+        <v>-0.08098</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>FMX</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>86.55</v>
+        <v>105.8</v>
       </c>
       <c r="D324" t="n">
-        <v>116.17</v>
+        <v>121.26</v>
       </c>
       <c r="E324" t="n">
-        <v>34.22</v>
+        <v>14.61</v>
       </c>
       <c r="F324" t="n">
-        <v>0.7472299999999999</v>
+        <v>-0.80715</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="D325" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E325" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0.22235</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>NWS</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="D326" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="E326" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="F326" t="n">
+        <v>-0.24679</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F326"/>
+  <dimension ref="A1:F325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -676,22 +676,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11.23</v>
+        <v>12.43</v>
       </c>
       <c r="D11" t="n">
-        <v>11.89</v>
+        <v>18.42</v>
       </c>
       <c r="E11" t="n">
-        <v>5.88</v>
+        <v>48.19</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03212</v>
+        <v>0.97816</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.98</v>
+        <v>11.23</v>
       </c>
       <c r="D12" t="n">
-        <v>3.54</v>
+        <v>11.89</v>
       </c>
       <c r="E12" t="n">
-        <v>18.79</v>
+        <v>5.88</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06816999999999999</v>
+        <v>0.03212</v>
       </c>
     </row>
     <row r="13">
@@ -739,7 +739,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.43</v>
+        <v>4.46</v>
       </c>
       <c r="D14" t="n">
-        <v>18.42</v>
+        <v>5.22</v>
       </c>
       <c r="E14" t="n">
-        <v>48.19</v>
+        <v>17.04</v>
       </c>
       <c r="F14" t="n">
-        <v>0.97816</v>
+        <v>0.08513999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.46</v>
+        <v>2.98</v>
       </c>
       <c r="D15" t="n">
-        <v>5.22</v>
+        <v>3.54</v>
       </c>
       <c r="E15" t="n">
-        <v>17.04</v>
+        <v>18.79</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08513999999999999</v>
+        <v>0.06816999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -988,22 +988,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.81</v>
+        <v>205.48</v>
       </c>
       <c r="D24" t="n">
-        <v>10.87</v>
+        <v>249.99</v>
       </c>
       <c r="E24" t="n">
-        <v>39.18</v>
+        <v>21.66</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04366</v>
+        <v>1.24005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1012,22 +1012,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>205.48</v>
+        <v>7.81</v>
       </c>
       <c r="D25" t="n">
-        <v>249.99</v>
+        <v>10.87</v>
       </c>
       <c r="E25" t="n">
-        <v>21.66</v>
+        <v>39.18</v>
       </c>
       <c r="F25" t="n">
-        <v>1.24005</v>
+        <v>0.04366</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41.55</v>
+        <v>298.32</v>
       </c>
       <c r="D26" t="n">
-        <v>62.21</v>
+        <v>358.97</v>
       </c>
       <c r="E26" t="n">
-        <v>49.72</v>
+        <v>20.33</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.39774</v>
+        <v>3.38165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>298.32</v>
+        <v>29.31</v>
       </c>
       <c r="D27" t="n">
-        <v>358.97</v>
+        <v>43.17</v>
       </c>
       <c r="E27" t="n">
-        <v>20.33</v>
+        <v>47.29</v>
       </c>
       <c r="F27" t="n">
-        <v>3.38165</v>
+        <v>0.92178</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29.31</v>
+        <v>41.55</v>
       </c>
       <c r="D28" t="n">
-        <v>43.17</v>
+        <v>62.21</v>
       </c>
       <c r="E28" t="n">
-        <v>47.29</v>
+        <v>49.72</v>
       </c>
       <c r="F28" t="n">
-        <v>0.92178</v>
+        <v>-0.39774</v>
       </c>
     </row>
     <row r="29">
@@ -1147,7 +1147,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.14</v>
+        <v>332.02</v>
       </c>
       <c r="D31" t="n">
-        <v>31.52</v>
+        <v>377.94</v>
       </c>
       <c r="E31" t="n">
-        <v>16.14</v>
+        <v>13.83</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.35749</v>
+        <v>-2.21821</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1180,22 +1180,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>332.02</v>
+        <v>179.43</v>
       </c>
       <c r="D32" t="n">
-        <v>377.94</v>
+        <v>193.72</v>
       </c>
       <c r="E32" t="n">
-        <v>13.83</v>
+        <v>7.96</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.21821</v>
+        <v>0.57955</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1204,22 +1204,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>146.38</v>
+        <v>27.14</v>
       </c>
       <c r="D33" t="n">
-        <v>218.28</v>
+        <v>31.52</v>
       </c>
       <c r="E33" t="n">
-        <v>49.12</v>
+        <v>16.14</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00649</v>
+        <v>-0.35749</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>179.43</v>
+        <v>146.38</v>
       </c>
       <c r="D34" t="n">
-        <v>193.72</v>
+        <v>218.28</v>
       </c>
       <c r="E34" t="n">
-        <v>7.96</v>
+        <v>49.12</v>
       </c>
       <c r="F34" t="n">
-        <v>0.57955</v>
+        <v>0.00649</v>
       </c>
     </row>
     <row r="35">
@@ -1315,7 +1315,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>67.59999999999999</v>
+        <v>103.45</v>
       </c>
       <c r="D38" t="n">
-        <v>80.31999999999999</v>
+        <v>149.67</v>
       </c>
       <c r="E38" t="n">
-        <v>18.82</v>
+        <v>44.68</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.45827</v>
+        <v>1.89428</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>103.45</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>149.67</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>44.68</v>
+        <v>18.82</v>
       </c>
       <c r="F39" t="n">
-        <v>1.89428</v>
+        <v>-0.45827</v>
       </c>
     </row>
     <row r="40">
@@ -1483,7 +1483,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>162.11</v>
+        <v>20.87</v>
       </c>
       <c r="D45" t="n">
-        <v>176.94</v>
+        <v>23.47</v>
       </c>
       <c r="E45" t="n">
-        <v>9.15</v>
+        <v>12.46</v>
       </c>
       <c r="F45" t="n">
-        <v>0.35777</v>
+        <v>0.00191</v>
       </c>
     </row>
     <row r="46">
@@ -1579,7 +1579,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1588,22 +1588,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>20.87</v>
+        <v>162.11</v>
       </c>
       <c r="D49" t="n">
-        <v>23.47</v>
+        <v>176.94</v>
       </c>
       <c r="E49" t="n">
-        <v>12.46</v>
+        <v>9.15</v>
       </c>
       <c r="F49" t="n">
-        <v>0.00191</v>
+        <v>0.35777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.49</v>
+        <v>15.99</v>
       </c>
       <c r="D50" t="n">
-        <v>19.07</v>
+        <v>21.15</v>
       </c>
       <c r="E50" t="n">
-        <v>31.61</v>
+        <v>32.27</v>
       </c>
       <c r="F50" t="n">
-        <v>0.58389</v>
+        <v>0.63574</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1636,16 +1636,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>15.99</v>
+        <v>14.49</v>
       </c>
       <c r="D51" t="n">
-        <v>21.15</v>
+        <v>19.07</v>
       </c>
       <c r="E51" t="n">
-        <v>32.27</v>
+        <v>31.61</v>
       </c>
       <c r="F51" t="n">
-        <v>0.63574</v>
+        <v>0.58389</v>
       </c>
     </row>
     <row r="52">
@@ -1675,7 +1675,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>165.69</v>
+        <v>104.89</v>
       </c>
       <c r="D53" t="n">
-        <v>212.17</v>
+        <v>121.23</v>
       </c>
       <c r="E53" t="n">
-        <v>28.05</v>
+        <v>15.58</v>
       </c>
       <c r="F53" t="n">
-        <v>3.14062</v>
+        <v>2.10701</v>
       </c>
     </row>
     <row r="54">
@@ -1723,7 +1723,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>53.57</v>
+        <v>51.98</v>
       </c>
       <c r="D55" t="n">
-        <v>68.72</v>
+        <v>65.36</v>
       </c>
       <c r="E55" t="n">
-        <v>28.28</v>
+        <v>25.74</v>
       </c>
       <c r="F55" t="n">
-        <v>0.74953</v>
+        <v>-0.02228</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>45.57</v>
+        <v>17.26</v>
       </c>
       <c r="D56" t="n">
-        <v>55.4</v>
+        <v>19.97</v>
       </c>
       <c r="E56" t="n">
-        <v>21.57</v>
+        <v>15.7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.48559</v>
+        <v>0.16925</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>17.93</v>
+        <v>53.57</v>
       </c>
       <c r="D57" t="n">
-        <v>23.76</v>
+        <v>68.72</v>
       </c>
       <c r="E57" t="n">
-        <v>32.52</v>
+        <v>28.28</v>
       </c>
       <c r="F57" t="n">
-        <v>0.28866</v>
+        <v>0.74953</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,16 +1804,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>17.26</v>
+        <v>45.57</v>
       </c>
       <c r="D58" t="n">
-        <v>19.97</v>
+        <v>55.4</v>
       </c>
       <c r="E58" t="n">
-        <v>15.7</v>
+        <v>21.57</v>
       </c>
       <c r="F58" t="n">
-        <v>0.16925</v>
+        <v>0.48559</v>
       </c>
     </row>
     <row r="59">
@@ -1867,7 +1867,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>51.98</v>
+        <v>17.93</v>
       </c>
       <c r="D61" t="n">
-        <v>65.36</v>
+        <v>23.76</v>
       </c>
       <c r="E61" t="n">
-        <v>25.74</v>
+        <v>32.52</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.02228</v>
+        <v>0.28866</v>
       </c>
     </row>
     <row r="62">
@@ -1987,7 +1987,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>20.48</v>
+        <v>165.69</v>
       </c>
       <c r="D66" t="n">
-        <v>26.51</v>
+        <v>212.17</v>
       </c>
       <c r="E66" t="n">
-        <v>29.44</v>
+        <v>28.05</v>
       </c>
       <c r="F66" t="n">
-        <v>0.19225</v>
+        <v>3.14062</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,22 +2020,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>104.89</v>
+        <v>103.22</v>
       </c>
       <c r="D67" t="n">
-        <v>121.23</v>
+        <v>136.67</v>
       </c>
       <c r="E67" t="n">
-        <v>15.58</v>
+        <v>32.41</v>
       </c>
       <c r="F67" t="n">
-        <v>2.10701</v>
+        <v>2.02987</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2044,22 +2044,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>31.87</v>
+        <v>41.99</v>
       </c>
       <c r="D68" t="n">
-        <v>45.03</v>
+        <v>51.29</v>
       </c>
       <c r="E68" t="n">
-        <v>41.29</v>
+        <v>22.15</v>
       </c>
       <c r="F68" t="n">
-        <v>0.89874</v>
+        <v>0.38063</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>103.22</v>
+        <v>20.48</v>
       </c>
       <c r="D69" t="n">
-        <v>136.67</v>
+        <v>26.51</v>
       </c>
       <c r="E69" t="n">
-        <v>32.41</v>
+        <v>29.44</v>
       </c>
       <c r="F69" t="n">
-        <v>2.02987</v>
+        <v>0.19225</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>41.99</v>
+        <v>31.87</v>
       </c>
       <c r="D70" t="n">
-        <v>51.29</v>
+        <v>45.03</v>
       </c>
       <c r="E70" t="n">
-        <v>22.15</v>
+        <v>41.29</v>
       </c>
       <c r="F70" t="n">
-        <v>0.38063</v>
+        <v>0.89874</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2116,22 +2116,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>167.73</v>
+        <v>124.44</v>
       </c>
       <c r="D71" t="n">
-        <v>182.9</v>
+        <v>195</v>
       </c>
       <c r="E71" t="n">
-        <v>9.039999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.58001</v>
+        <v>0.72958</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>13.43</v>
+        <v>55.53</v>
       </c>
       <c r="D72" t="n">
-        <v>15.26</v>
+        <v>60.91</v>
       </c>
       <c r="E72" t="n">
-        <v>13.63</v>
+        <v>9.69</v>
       </c>
       <c r="F72" t="n">
-        <v>0.08839</v>
+        <v>0.22128</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,22 +2164,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>55.53</v>
+        <v>62.05</v>
       </c>
       <c r="D73" t="n">
-        <v>60.91</v>
+        <v>81.22</v>
       </c>
       <c r="E73" t="n">
-        <v>9.69</v>
+        <v>30.89</v>
       </c>
       <c r="F73" t="n">
-        <v>0.22128</v>
+        <v>-0.5008899999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2188,22 +2188,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>124.44</v>
+        <v>13.31</v>
       </c>
       <c r="D74" t="n">
-        <v>195</v>
+        <v>25.76</v>
       </c>
       <c r="E74" t="n">
-        <v>56.7</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>0.72958</v>
+        <v>0.71191</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2212,22 +2212,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38.73</v>
+        <v>13.43</v>
       </c>
       <c r="D75" t="n">
-        <v>64.09999999999999</v>
+        <v>15.26</v>
       </c>
       <c r="E75" t="n">
-        <v>65.5</v>
+        <v>13.63</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.10866</v>
+        <v>0.08839</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2236,22 +2236,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>62.05</v>
+        <v>38.73</v>
       </c>
       <c r="D76" t="n">
-        <v>81.22</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>30.89</v>
+        <v>65.5</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.5008899999999999</v>
+        <v>-0.10866</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2260,22 +2260,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>13.31</v>
+        <v>167.73</v>
       </c>
       <c r="D77" t="n">
-        <v>25.76</v>
+        <v>182.9</v>
       </c>
       <c r="E77" t="n">
-        <v>93.54000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>0.71191</v>
+        <v>-0.58001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2284,22 +2284,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>135.44</v>
+        <v>218.58</v>
       </c>
       <c r="D78" t="n">
-        <v>174.39</v>
+        <v>280.46</v>
       </c>
       <c r="E78" t="n">
-        <v>28.76</v>
+        <v>28.31</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.62645</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2308,22 +2308,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7.67</v>
+        <v>122.91</v>
       </c>
       <c r="D79" t="n">
-        <v>9.199999999999999</v>
+        <v>157.75</v>
       </c>
       <c r="E79" t="n">
-        <v>19.95</v>
+        <v>28.35</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1771</v>
+        <v>-0.37771</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2332,22 +2332,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>218.58</v>
+        <v>7.67</v>
       </c>
       <c r="D80" t="n">
-        <v>280.46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>28.31</v>
+        <v>19.95</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2297</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2356,22 +2356,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>136.06</v>
+        <v>135.44</v>
       </c>
       <c r="D81" t="n">
-        <v>165.08</v>
+        <v>174.39</v>
       </c>
       <c r="E81" t="n">
-        <v>21.33</v>
+        <v>28.76</v>
       </c>
       <c r="F81" t="n">
-        <v>1.65744</v>
+        <v>-1.62645</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2380,22 +2380,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>122.91</v>
+        <v>136.06</v>
       </c>
       <c r="D82" t="n">
-        <v>157.75</v>
+        <v>165.08</v>
       </c>
       <c r="E82" t="n">
-        <v>28.35</v>
+        <v>21.33</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.37771</v>
+        <v>1.65744</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2404,22 +2404,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>82.31</v>
+        <v>18.94</v>
       </c>
       <c r="D83" t="n">
-        <v>136.94</v>
+        <v>23.74</v>
       </c>
       <c r="E83" t="n">
-        <v>66.37</v>
+        <v>25.34</v>
       </c>
       <c r="F83" t="n">
-        <v>3.45518</v>
+        <v>0.19609</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>18.94</v>
+        <v>31.03</v>
       </c>
       <c r="D84" t="n">
-        <v>23.74</v>
+        <v>44.54</v>
       </c>
       <c r="E84" t="n">
-        <v>25.34</v>
+        <v>43.54</v>
       </c>
       <c r="F84" t="n">
-        <v>0.19609</v>
+        <v>0.9863499999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2452,22 +2452,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>39.54</v>
+        <v>56.4</v>
       </c>
       <c r="D85" t="n">
-        <v>51.41</v>
+        <v>80.81</v>
       </c>
       <c r="E85" t="n">
-        <v>30.02</v>
+        <v>43.28</v>
       </c>
       <c r="F85" t="n">
-        <v>0.11249</v>
+        <v>1.6696</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2476,22 +2476,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>56.4</v>
+        <v>82.31</v>
       </c>
       <c r="D86" t="n">
-        <v>80.81</v>
+        <v>136.94</v>
       </c>
       <c r="E86" t="n">
-        <v>43.28</v>
+        <v>66.37</v>
       </c>
       <c r="F86" t="n">
-        <v>1.6696</v>
+        <v>3.45518</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2500,16 +2500,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>31.03</v>
+        <v>39.54</v>
       </c>
       <c r="D87" t="n">
-        <v>44.54</v>
+        <v>51.41</v>
       </c>
       <c r="E87" t="n">
-        <v>43.54</v>
+        <v>30.02</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9863499999999999</v>
+        <v>0.11249</v>
       </c>
     </row>
     <row r="88">
@@ -2527,19 +2527,19 @@
         <v>76.53</v>
       </c>
       <c r="D88" t="n">
-        <v>96.77</v>
+        <v>96.45</v>
       </c>
       <c r="E88" t="n">
-        <v>26.45</v>
+        <v>26.03</v>
       </c>
       <c r="F88" t="n">
-        <v>1.4864</v>
+        <v>1.45245</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>142.52</v>
+        <v>107.27</v>
       </c>
       <c r="D89" t="n">
-        <v>191.45</v>
+        <v>173.31</v>
       </c>
       <c r="E89" t="n">
-        <v>34.33</v>
+        <v>61.56</v>
       </c>
       <c r="F89" t="n">
-        <v>1.43195</v>
+        <v>-1.05801</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2572,22 +2572,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>255.07</v>
+        <v>59.71</v>
       </c>
       <c r="D90" t="n">
-        <v>339.15</v>
+        <v>79.11</v>
       </c>
       <c r="E90" t="n">
-        <v>32.96</v>
+        <v>32.49</v>
       </c>
       <c r="F90" t="n">
-        <v>-6.00233</v>
+        <v>0.59687</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>EDU</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2596,22 +2596,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>44.39</v>
+        <v>44.44</v>
       </c>
       <c r="D91" t="n">
-        <v>61.14</v>
+        <v>56.82</v>
       </c>
       <c r="E91" t="n">
-        <v>37.73</v>
+        <v>27.86</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.05927</v>
+        <v>-0.38143</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2620,22 +2620,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>170.28</v>
+        <v>255.07</v>
       </c>
       <c r="D92" t="n">
-        <v>250.61</v>
+        <v>339.15</v>
       </c>
       <c r="E92" t="n">
-        <v>47.18</v>
+        <v>32.96</v>
       </c>
       <c r="F92" t="n">
-        <v>-2.75775</v>
+        <v>-6.00233</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2644,22 +2644,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>352.83</v>
+        <v>19.32</v>
       </c>
       <c r="D93" t="n">
-        <v>505.41</v>
+        <v>24.47</v>
       </c>
       <c r="E93" t="n">
-        <v>43.24</v>
+        <v>26.66</v>
       </c>
       <c r="F93" t="n">
-        <v>2.09735</v>
+        <v>-0.0342</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2668,16 +2668,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>59.71</v>
+        <v>166.5</v>
       </c>
       <c r="D94" t="n">
-        <v>79.11</v>
+        <v>197.56</v>
       </c>
       <c r="E94" t="n">
-        <v>32.49</v>
+        <v>18.65</v>
       </c>
       <c r="F94" t="n">
-        <v>0.59687</v>
+        <v>0.66935</v>
       </c>
     </row>
     <row r="95">
@@ -2707,7 +2707,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2716,22 +2716,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>107.27</v>
+        <v>170.28</v>
       </c>
       <c r="D96" t="n">
-        <v>173.31</v>
+        <v>250.61</v>
       </c>
       <c r="E96" t="n">
-        <v>61.56</v>
+        <v>47.18</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.05801</v>
+        <v>-2.75775</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2740,22 +2740,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>19.32</v>
+        <v>142.52</v>
       </c>
       <c r="D97" t="n">
-        <v>24.47</v>
+        <v>191.45</v>
       </c>
       <c r="E97" t="n">
-        <v>26.66</v>
+        <v>34.33</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.0342</v>
+        <v>1.43195</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2764,22 +2764,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>49.87</v>
+        <v>352.83</v>
       </c>
       <c r="D98" t="n">
-        <v>63.17</v>
+        <v>505.41</v>
       </c>
       <c r="E98" t="n">
-        <v>26.67</v>
+        <v>43.24</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2007</v>
+        <v>2.09735</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EDU</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2788,22 +2788,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>44.44</v>
+        <v>136.68</v>
       </c>
       <c r="D99" t="n">
-        <v>56.82</v>
+        <v>153.4</v>
       </c>
       <c r="E99" t="n">
-        <v>27.86</v>
+        <v>12.23</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.38143</v>
+        <v>-2.51046</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2812,22 +2812,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>166.5</v>
+        <v>49.87</v>
       </c>
       <c r="D100" t="n">
-        <v>197.56</v>
+        <v>63.17</v>
       </c>
       <c r="E100" t="n">
-        <v>18.65</v>
+        <v>26.67</v>
       </c>
       <c r="F100" t="n">
-        <v>0.66935</v>
+        <v>0.2007</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2836,22 +2836,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>136.68</v>
+        <v>44.39</v>
       </c>
       <c r="D101" t="n">
-        <v>153.4</v>
+        <v>61.14</v>
       </c>
       <c r="E101" t="n">
-        <v>12.23</v>
+        <v>37.73</v>
       </c>
       <c r="F101" t="n">
-        <v>-2.51046</v>
+        <v>-0.05927</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2860,16 +2860,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>60.37</v>
+        <v>10.51</v>
       </c>
       <c r="D102" t="n">
-        <v>77</v>
+        <v>15.27</v>
       </c>
       <c r="E102" t="n">
-        <v>27.55</v>
+        <v>45.29</v>
       </c>
       <c r="F102" t="n">
-        <v>1.31187</v>
+        <v>0.40451</v>
       </c>
     </row>
     <row r="103">
@@ -2899,7 +2899,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2908,22 +2908,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.51</v>
+        <v>60.37</v>
       </c>
       <c r="D104" t="n">
-        <v>15.27</v>
+        <v>77</v>
       </c>
       <c r="E104" t="n">
-        <v>45.29</v>
+        <v>27.55</v>
       </c>
       <c r="F104" t="n">
-        <v>0.40451</v>
+        <v>1.31187</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2932,22 +2932,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>48.79</v>
+        <v>102.17</v>
       </c>
       <c r="D105" t="n">
-        <v>68.53</v>
+        <v>131.24</v>
       </c>
       <c r="E105" t="n">
-        <v>40.46</v>
+        <v>28.45</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.01588</v>
+        <v>1.86006</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2956,22 +2956,22 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>102.17</v>
+        <v>48.79</v>
       </c>
       <c r="D106" t="n">
-        <v>131.24</v>
+        <v>68.53</v>
       </c>
       <c r="E106" t="n">
-        <v>28.45</v>
+        <v>40.46</v>
       </c>
       <c r="F106" t="n">
-        <v>1.86006</v>
+        <v>-0.01588</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>76.55</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D107" t="n">
-        <v>105.82</v>
+        <v>123.61</v>
       </c>
       <c r="E107" t="n">
-        <v>38.24</v>
+        <v>62.56</v>
       </c>
       <c r="F107" t="n">
-        <v>-1.58346</v>
+        <v>2.41344</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3004,16 +3004,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>76.04000000000001</v>
+        <v>30.83</v>
       </c>
       <c r="D108" t="n">
-        <v>123.61</v>
+        <v>35.72</v>
       </c>
       <c r="E108" t="n">
-        <v>62.56</v>
+        <v>15.86</v>
       </c>
       <c r="F108" t="n">
-        <v>2.41344</v>
+        <v>-0.35242</v>
       </c>
     </row>
     <row r="109">
@@ -3043,7 +3043,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>125.73</v>
+        <v>275.27</v>
       </c>
       <c r="D110" t="n">
-        <v>197.07</v>
+        <v>359.54</v>
       </c>
       <c r="E110" t="n">
-        <v>56.74</v>
+        <v>30.61</v>
       </c>
       <c r="F110" t="n">
-        <v>-1.80321</v>
+        <v>-2.74832</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3076,22 +3076,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>74.98999999999999</v>
+        <v>125.73</v>
       </c>
       <c r="D111" t="n">
-        <v>104.47</v>
+        <v>197.07</v>
       </c>
       <c r="E111" t="n">
-        <v>39.31</v>
+        <v>56.74</v>
       </c>
       <c r="F111" t="n">
-        <v>0.40712</v>
+        <v>-1.80321</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3100,22 +3100,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>275.27</v>
+        <v>150.12</v>
       </c>
       <c r="D112" t="n">
-        <v>359.54</v>
+        <v>259.43</v>
       </c>
       <c r="E112" t="n">
-        <v>30.61</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="F112" t="n">
-        <v>-2.74832</v>
+        <v>6.48113</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3124,22 +3124,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>140.71</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D113" t="n">
-        <v>182.91</v>
+        <v>104.47</v>
       </c>
       <c r="E113" t="n">
-        <v>29.99</v>
+        <v>39.31</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.36471</v>
+        <v>0.40712</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3148,22 +3148,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>150.12</v>
+        <v>140.71</v>
       </c>
       <c r="D114" t="n">
-        <v>259.43</v>
+        <v>182.91</v>
       </c>
       <c r="E114" t="n">
-        <v>72.81999999999999</v>
+        <v>29.99</v>
       </c>
       <c r="F114" t="n">
-        <v>6.48113</v>
+        <v>-1.36471</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3172,22 +3172,22 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>123.42</v>
+        <v>76.55</v>
       </c>
       <c r="D115" t="n">
-        <v>164.55</v>
+        <v>105.82</v>
       </c>
       <c r="E115" t="n">
-        <v>33.33</v>
+        <v>38.24</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.65884</v>
+        <v>-1.58346</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3196,16 +3196,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>30.83</v>
+        <v>123.42</v>
       </c>
       <c r="D116" t="n">
-        <v>35.72</v>
+        <v>164.55</v>
       </c>
       <c r="E116" t="n">
-        <v>15.86</v>
+        <v>33.33</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.35242</v>
+        <v>-0.65884</v>
       </c>
     </row>
     <row r="117">
@@ -3355,7 +3355,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>91.88</v>
+        <v>62.47</v>
       </c>
       <c r="D123" t="n">
-        <v>125.3</v>
+        <v>90.19</v>
       </c>
       <c r="E123" t="n">
-        <v>36.37</v>
+        <v>44.37</v>
       </c>
       <c r="F123" t="n">
-        <v>1.50067</v>
+        <v>-0.65359</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3388,22 +3388,22 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>14.94</v>
+        <v>53.82</v>
       </c>
       <c r="D124" t="n">
-        <v>19.59</v>
+        <v>75</v>
       </c>
       <c r="E124" t="n">
-        <v>31.16</v>
+        <v>39.35</v>
       </c>
       <c r="F124" t="n">
-        <v>0.52114</v>
+        <v>0.53725</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3412,22 +3412,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>62.47</v>
+        <v>121.48</v>
       </c>
       <c r="D125" t="n">
-        <v>90.19</v>
+        <v>146.41</v>
       </c>
       <c r="E125" t="n">
-        <v>44.37</v>
+        <v>20.52</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.65359</v>
+        <v>0.04863</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>16.44</v>
+        <v>2.86</v>
       </c>
       <c r="D126" t="n">
-        <v>33.97</v>
+        <v>3.18</v>
       </c>
       <c r="E126" t="n">
-        <v>106.63</v>
+        <v>11.19</v>
       </c>
       <c r="F126" t="n">
-        <v>0.60034</v>
+        <v>0.02543</v>
       </c>
     </row>
     <row r="127">
@@ -3475,7 +3475,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3484,22 +3484,22 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>53.82</v>
+        <v>14.94</v>
       </c>
       <c r="D128" t="n">
-        <v>75</v>
+        <v>19.59</v>
       </c>
       <c r="E128" t="n">
-        <v>39.35</v>
+        <v>31.16</v>
       </c>
       <c r="F128" t="n">
-        <v>0.53725</v>
+        <v>0.52114</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3508,22 +3508,22 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>121.48</v>
+        <v>16.44</v>
       </c>
       <c r="D129" t="n">
-        <v>146.41</v>
+        <v>33.97</v>
       </c>
       <c r="E129" t="n">
-        <v>20.52</v>
+        <v>106.63</v>
       </c>
       <c r="F129" t="n">
-        <v>0.04863</v>
+        <v>0.60034</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2.86</v>
+        <v>91.88</v>
       </c>
       <c r="D130" t="n">
-        <v>3.18</v>
+        <v>125.3</v>
       </c>
       <c r="E130" t="n">
-        <v>11.19</v>
+        <v>36.37</v>
       </c>
       <c r="F130" t="n">
-        <v>0.02543</v>
+        <v>1.50067</v>
       </c>
     </row>
     <row r="131">
@@ -3595,7 +3595,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3604,22 +3604,22 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>43.67</v>
+        <v>28.18</v>
       </c>
       <c r="D133" t="n">
-        <v>47.34</v>
+        <v>37.03</v>
       </c>
       <c r="E133" t="n">
-        <v>8.4</v>
+        <v>31.41</v>
       </c>
       <c r="F133" t="n">
-        <v>0.05503</v>
+        <v>-0.01107</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3628,22 +3628,22 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>161.37</v>
+        <v>43.67</v>
       </c>
       <c r="D134" t="n">
-        <v>264.51</v>
+        <v>47.34</v>
       </c>
       <c r="E134" t="n">
-        <v>63.92</v>
+        <v>8.4</v>
       </c>
       <c r="F134" t="n">
-        <v>0.82511</v>
+        <v>0.05503</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3652,22 +3652,22 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>55.05</v>
+        <v>161.37</v>
       </c>
       <c r="D135" t="n">
-        <v>63.57</v>
+        <v>264.51</v>
       </c>
       <c r="E135" t="n">
-        <v>15.48</v>
+        <v>63.92</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.4736</v>
+        <v>0.82511</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3676,22 +3676,22 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>28.18</v>
+        <v>55.05</v>
       </c>
       <c r="D136" t="n">
-        <v>37.03</v>
+        <v>63.57</v>
       </c>
       <c r="E136" t="n">
-        <v>31.41</v>
+        <v>15.48</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.01107</v>
+        <v>-0.4736</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3700,16 +3700,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>140.19</v>
+        <v>72.55</v>
       </c>
       <c r="D137" t="n">
-        <v>146.13</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>4.24</v>
+        <v>5.16</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.3931</v>
+        <v>-0.36496</v>
       </c>
     </row>
     <row r="138">
@@ -3739,7 +3739,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3748,22 +3748,22 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>72.55</v>
+        <v>15.03</v>
       </c>
       <c r="D139" t="n">
-        <v>76.29000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="E139" t="n">
-        <v>5.16</v>
+        <v>23.75</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.36496</v>
+        <v>0.08944000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3772,22 +3772,22 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>207.24</v>
+        <v>140.19</v>
       </c>
       <c r="D140" t="n">
-        <v>253.88</v>
+        <v>146.13</v>
       </c>
       <c r="E140" t="n">
-        <v>22.51</v>
+        <v>4.24</v>
       </c>
       <c r="F140" t="n">
-        <v>-2.67569</v>
+        <v>-0.3931</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3796,22 +3796,22 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>15.03</v>
+        <v>207.24</v>
       </c>
       <c r="D141" t="n">
-        <v>18.6</v>
+        <v>253.88</v>
       </c>
       <c r="E141" t="n">
-        <v>23.75</v>
+        <v>22.51</v>
       </c>
       <c r="F141" t="n">
-        <v>0.08944000000000001</v>
+        <v>-2.67569</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3820,22 +3820,22 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>73.75</v>
+        <v>277.69</v>
       </c>
       <c r="D142" t="n">
-        <v>93.8</v>
+        <v>330.62</v>
       </c>
       <c r="E142" t="n">
-        <v>27.19</v>
+        <v>19.06</v>
       </c>
       <c r="F142" t="n">
-        <v>0.31456</v>
+        <v>-0.14398</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3844,22 +3844,22 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>277.69</v>
+        <v>275.99</v>
       </c>
       <c r="D143" t="n">
-        <v>330.62</v>
+        <v>322.99</v>
       </c>
       <c r="E143" t="n">
-        <v>19.06</v>
+        <v>17.03</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.14398</v>
+        <v>1.92883</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3868,16 +3868,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>275.99</v>
+        <v>73.75</v>
       </c>
       <c r="D144" t="n">
-        <v>322.99</v>
+        <v>93.8</v>
       </c>
       <c r="E144" t="n">
-        <v>17.03</v>
+        <v>27.19</v>
       </c>
       <c r="F144" t="n">
-        <v>1.92883</v>
+        <v>0.31456</v>
       </c>
     </row>
     <row r="145">
@@ -3907,7 +3907,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3916,22 +3916,22 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>309.78</v>
+        <v>121.13</v>
       </c>
       <c r="D146" t="n">
-        <v>341.85</v>
+        <v>138.92</v>
       </c>
       <c r="E146" t="n">
-        <v>10.35</v>
+        <v>14.69</v>
       </c>
       <c r="F146" t="n">
-        <v>-1.13236</v>
+        <v>0.41111</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3940,22 +3940,22 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>121.13</v>
+        <v>9.85</v>
       </c>
       <c r="D147" t="n">
-        <v>138.92</v>
+        <v>13.75</v>
       </c>
       <c r="E147" t="n">
-        <v>14.69</v>
+        <v>39.59</v>
       </c>
       <c r="F147" t="n">
-        <v>0.41111</v>
+        <v>0.51236</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3964,22 +3964,22 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>132.79</v>
+        <v>309.78</v>
       </c>
       <c r="D148" t="n">
-        <v>163.39</v>
+        <v>341.85</v>
       </c>
       <c r="E148" t="n">
-        <v>23.04</v>
+        <v>10.35</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.12699</v>
+        <v>-1.13236</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3988,22 +3988,22 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>9.85</v>
+        <v>132.79</v>
       </c>
       <c r="D149" t="n">
-        <v>13.75</v>
+        <v>163.39</v>
       </c>
       <c r="E149" t="n">
-        <v>39.59</v>
+        <v>23.04</v>
       </c>
       <c r="F149" t="n">
-        <v>0.51236</v>
+        <v>-0.12699</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4012,22 +4012,22 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>190.4</v>
+        <v>33.54</v>
       </c>
       <c r="D150" t="n">
-        <v>221.02</v>
+        <v>42.61</v>
       </c>
       <c r="E150" t="n">
-        <v>16.08</v>
+        <v>27.04</v>
       </c>
       <c r="F150" t="n">
-        <v>0.04179</v>
+        <v>0.13446</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4036,22 +4036,22 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>33.54</v>
+        <v>63.54</v>
       </c>
       <c r="D151" t="n">
-        <v>42.61</v>
+        <v>70.87</v>
       </c>
       <c r="E151" t="n">
-        <v>27.04</v>
+        <v>11.54</v>
       </c>
       <c r="F151" t="n">
-        <v>0.13446</v>
+        <v>0.26916</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4060,16 +4060,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>63.54</v>
+        <v>190.4</v>
       </c>
       <c r="D152" t="n">
-        <v>70.87</v>
+        <v>221.02</v>
       </c>
       <c r="E152" t="n">
-        <v>11.54</v>
+        <v>16.08</v>
       </c>
       <c r="F152" t="n">
-        <v>0.26916</v>
+        <v>0.04179</v>
       </c>
     </row>
     <row r="153">
@@ -4219,7 +4219,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4228,22 +4228,22 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5563.62</v>
+        <v>63.16</v>
       </c>
       <c r="D159" t="n">
-        <v>6299.56</v>
+        <v>101.84</v>
       </c>
       <c r="E159" t="n">
-        <v>13.23</v>
+        <v>61.24</v>
       </c>
       <c r="F159" t="n">
-        <v>-44.26965</v>
+        <v>1.43086</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4252,22 +4252,22 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>26.18</v>
+        <v>5563.62</v>
       </c>
       <c r="D160" t="n">
-        <v>36.71</v>
+        <v>6299.56</v>
       </c>
       <c r="E160" t="n">
-        <v>40.22</v>
+        <v>13.23</v>
       </c>
       <c r="F160" t="n">
-        <v>0.135</v>
+        <v>-44.26965</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4276,22 +4276,22 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>73.42</v>
+        <v>43.3</v>
       </c>
       <c r="D161" t="n">
-        <v>88.70999999999999</v>
+        <v>72.27</v>
       </c>
       <c r="E161" t="n">
-        <v>20.83</v>
+        <v>66.91</v>
       </c>
       <c r="F161" t="n">
-        <v>0.7728699999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4300,22 +4300,22 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>63.16</v>
+        <v>73.42</v>
       </c>
       <c r="D162" t="n">
-        <v>101.84</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E162" t="n">
-        <v>61.24</v>
+        <v>20.83</v>
       </c>
       <c r="F162" t="n">
-        <v>1.43086</v>
+        <v>0.7728699999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4324,22 +4324,22 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>438.34</v>
+        <v>92.38</v>
       </c>
       <c r="D163" t="n">
-        <v>613.62</v>
+        <v>100.65</v>
       </c>
       <c r="E163" t="n">
-        <v>39.99</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F163" t="n">
-        <v>0.49995</v>
+        <v>-0.07876</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>92.38</v>
+        <v>438.34</v>
       </c>
       <c r="D164" t="n">
-        <v>100.65</v>
+        <v>613.62</v>
       </c>
       <c r="E164" t="n">
-        <v>8.949999999999999</v>
+        <v>39.99</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.07876</v>
+        <v>0.49995</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4372,16 +4372,16 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>43.3</v>
+        <v>26.18</v>
       </c>
       <c r="D165" t="n">
-        <v>72.27</v>
+        <v>36.71</v>
       </c>
       <c r="E165" t="n">
-        <v>66.91</v>
+        <v>40.22</v>
       </c>
       <c r="F165" t="n">
-        <v>-0</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="166">
@@ -4435,7 +4435,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4444,22 +4444,22 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>55.52</v>
+        <v>101.75</v>
       </c>
       <c r="D168" t="n">
-        <v>94.83</v>
+        <v>129.17</v>
       </c>
       <c r="E168" t="n">
-        <v>70.8</v>
+        <v>26.95</v>
       </c>
       <c r="F168" t="n">
-        <v>1.61921</v>
+        <v>-0.25082</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4468,16 +4468,16 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>101.75</v>
+        <v>55.52</v>
       </c>
       <c r="D169" t="n">
-        <v>129.17</v>
+        <v>94.83</v>
       </c>
       <c r="E169" t="n">
-        <v>26.95</v>
+        <v>70.8</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.25082</v>
+        <v>1.61921</v>
       </c>
     </row>
     <row r="170">
@@ -4507,7 +4507,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4516,22 +4516,22 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>197.73</v>
+        <v>725.17</v>
       </c>
       <c r="D171" t="n">
-        <v>225.85</v>
+        <v>910.95</v>
       </c>
       <c r="E171" t="n">
-        <v>14.22</v>
+        <v>25.62</v>
       </c>
       <c r="F171" t="n">
-        <v>0.9798</v>
+        <v>1.91142</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4540,22 +4540,22 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>68.98999999999999</v>
+        <v>197.73</v>
       </c>
       <c r="D172" t="n">
-        <v>88.93000000000001</v>
+        <v>225.85</v>
       </c>
       <c r="E172" t="n">
-        <v>28.9</v>
+        <v>14.22</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.34243</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4564,22 +4564,22 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>725.17</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D173" t="n">
-        <v>910.95</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E173" t="n">
-        <v>25.62</v>
+        <v>28.9</v>
       </c>
       <c r="F173" t="n">
-        <v>1.91142</v>
+        <v>-0.34243</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4588,22 +4588,22 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>383.99</v>
+        <v>255.54</v>
       </c>
       <c r="D174" t="n">
-        <v>474.13</v>
+        <v>365.08</v>
       </c>
       <c r="E174" t="n">
-        <v>23.47</v>
+        <v>42.87</v>
       </c>
       <c r="F174" t="n">
-        <v>-1.53084</v>
+        <v>3.26755</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4612,22 +4612,22 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>12.64</v>
+        <v>383.99</v>
       </c>
       <c r="D175" t="n">
-        <v>17.74</v>
+        <v>474.13</v>
       </c>
       <c r="E175" t="n">
-        <v>40.35</v>
+        <v>23.47</v>
       </c>
       <c r="F175" t="n">
-        <v>0.24281</v>
+        <v>-1.53084</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4636,16 +4636,16 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>255.54</v>
+        <v>12.64</v>
       </c>
       <c r="D176" t="n">
-        <v>365.08</v>
+        <v>17.74</v>
       </c>
       <c r="E176" t="n">
-        <v>42.87</v>
+        <v>40.35</v>
       </c>
       <c r="F176" t="n">
-        <v>3.26755</v>
+        <v>0.24281</v>
       </c>
     </row>
     <row r="177">
@@ -4819,7 +4819,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4828,22 +4828,22 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>156.66</v>
+        <v>13.06</v>
       </c>
       <c r="D184" t="n">
-        <v>265.67</v>
+        <v>19.91</v>
       </c>
       <c r="E184" t="n">
-        <v>69.58</v>
+        <v>52.45</v>
       </c>
       <c r="F184" t="n">
-        <v>2.0428</v>
+        <v>-0.009140000000000001</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4852,22 +4852,22 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>13.06</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D185" t="n">
-        <v>19.91</v>
+        <v>128.49</v>
       </c>
       <c r="E185" t="n">
-        <v>52.45</v>
+        <v>56.2</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.009140000000000001</v>
+        <v>0.08618000000000001</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4876,16 +4876,16 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>82.26000000000001</v>
+        <v>156.66</v>
       </c>
       <c r="D186" t="n">
-        <v>128.49</v>
+        <v>265.67</v>
       </c>
       <c r="E186" t="n">
-        <v>56.2</v>
+        <v>69.58</v>
       </c>
       <c r="F186" t="n">
-        <v>0.08618000000000001</v>
+        <v>2.0428</v>
       </c>
     </row>
     <row r="187">
@@ -4963,7 +4963,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4972,22 +4972,22 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>465.4</v>
+        <v>74.63</v>
       </c>
       <c r="D190" t="n">
-        <v>514.95</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E190" t="n">
-        <v>10.65</v>
+        <v>19.72</v>
       </c>
       <c r="F190" t="n">
-        <v>1.66879</v>
+        <v>-0.05535</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4996,22 +4996,22 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>56.06</v>
+        <v>465.4</v>
       </c>
       <c r="D191" t="n">
-        <v>62.39</v>
+        <v>514.95</v>
       </c>
       <c r="E191" t="n">
-        <v>11.29</v>
+        <v>10.65</v>
       </c>
       <c r="F191" t="n">
-        <v>0.03839</v>
+        <v>1.66879</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5020,16 +5020,16 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>74.63</v>
+        <v>56.06</v>
       </c>
       <c r="D192" t="n">
-        <v>89.34999999999999</v>
+        <v>62.39</v>
       </c>
       <c r="E192" t="n">
-        <v>19.72</v>
+        <v>11.29</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.05535</v>
+        <v>0.03839</v>
       </c>
     </row>
     <row r="193">
@@ -5107,7 +5107,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5116,22 +5116,22 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>83.51000000000001</v>
+        <v>40.59</v>
       </c>
       <c r="D196" t="n">
-        <v>96.97</v>
+        <v>56.33</v>
       </c>
       <c r="E196" t="n">
-        <v>16.12</v>
+        <v>38.78</v>
       </c>
       <c r="F196" t="n">
-        <v>0.63437</v>
+        <v>1.40494</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5140,22 +5140,22 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>128.43</v>
+        <v>213.69</v>
       </c>
       <c r="D197" t="n">
-        <v>148.54</v>
+        <v>396.45</v>
       </c>
       <c r="E197" t="n">
-        <v>15.66</v>
+        <v>85.53</v>
       </c>
       <c r="F197" t="n">
-        <v>0.66273</v>
+        <v>10.30916</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5164,22 +5164,22 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>40.59</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="D198" t="n">
-        <v>56.33</v>
+        <v>96.97</v>
       </c>
       <c r="E198" t="n">
-        <v>38.78</v>
+        <v>16.12</v>
       </c>
       <c r="F198" t="n">
-        <v>1.40494</v>
+        <v>0.63437</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5188,22 +5188,22 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>213.69</v>
+        <v>223.65</v>
       </c>
       <c r="D199" t="n">
-        <v>396.45</v>
+        <v>382.95</v>
       </c>
       <c r="E199" t="n">
-        <v>85.53</v>
+        <v>71.23</v>
       </c>
       <c r="F199" t="n">
-        <v>10.30916</v>
+        <v>12.04345</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5212,22 +5212,22 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>223.65</v>
+        <v>128.43</v>
       </c>
       <c r="D200" t="n">
-        <v>382.95</v>
+        <v>148.54</v>
       </c>
       <c r="E200" t="n">
-        <v>71.23</v>
+        <v>15.66</v>
       </c>
       <c r="F200" t="n">
-        <v>12.04345</v>
+        <v>0.66273</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5236,22 +5236,22 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>66.95</v>
+        <v>18.71</v>
       </c>
       <c r="D201" t="n">
-        <v>86.44</v>
+        <v>21.49</v>
       </c>
       <c r="E201" t="n">
-        <v>29.11</v>
+        <v>14.86</v>
       </c>
       <c r="F201" t="n">
-        <v>1.50588</v>
+        <v>0.13728</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5260,16 +5260,16 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>18.71</v>
+        <v>66.95</v>
       </c>
       <c r="D202" t="n">
-        <v>21.49</v>
+        <v>86.44</v>
       </c>
       <c r="E202" t="n">
-        <v>14.86</v>
+        <v>29.11</v>
       </c>
       <c r="F202" t="n">
-        <v>0.13728</v>
+        <v>1.50588</v>
       </c>
     </row>
     <row r="203">
@@ -5299,7 +5299,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5308,22 +5308,22 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>62.93</v>
+        <v>118.05</v>
       </c>
       <c r="D204" t="n">
-        <v>186.45</v>
+        <v>191.73</v>
       </c>
       <c r="E204" t="n">
-        <v>196.28</v>
+        <v>62.41</v>
       </c>
       <c r="F204" t="n">
-        <v>6.24855</v>
+        <v>-0.40022</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5332,22 +5332,22 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>78.59999999999999</v>
+        <v>17.89</v>
       </c>
       <c r="D205" t="n">
-        <v>167.84</v>
+        <v>31.41</v>
       </c>
       <c r="E205" t="n">
-        <v>113.54</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F205" t="n">
-        <v>-0.11311</v>
+        <v>0.28103</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5356,22 +5356,22 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>17.89</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D206" t="n">
-        <v>31.41</v>
+        <v>167.84</v>
       </c>
       <c r="E206" t="n">
-        <v>75.56999999999999</v>
+        <v>113.54</v>
       </c>
       <c r="F206" t="n">
-        <v>0.28103</v>
+        <v>-0.11311</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5380,22 +5380,22 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>43.81</v>
+        <v>57.15</v>
       </c>
       <c r="D207" t="n">
-        <v>100.2</v>
+        <v>192.77</v>
       </c>
       <c r="E207" t="n">
-        <v>128.71</v>
+        <v>237.31</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.42056</v>
+        <v>4.18785</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5404,22 +5404,22 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>121.11</v>
+        <v>151.43</v>
       </c>
       <c r="D208" t="n">
-        <v>332.35</v>
+        <v>265.67</v>
       </c>
       <c r="E208" t="n">
-        <v>174.42</v>
+        <v>75.44</v>
       </c>
       <c r="F208" t="n">
-        <v>2.08531</v>
+        <v>1.55591</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5428,22 +5428,22 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>32.36</v>
+        <v>34.41</v>
       </c>
       <c r="D209" t="n">
-        <v>53.34</v>
+        <v>67.69</v>
       </c>
       <c r="E209" t="n">
-        <v>64.83</v>
+        <v>96.72</v>
       </c>
       <c r="F209" t="n">
-        <v>0.36656</v>
+        <v>0.14027</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>76.7</v>
+        <v>62.93</v>
       </c>
       <c r="D210" t="n">
-        <v>170.18</v>
+        <v>186.45</v>
       </c>
       <c r="E210" t="n">
-        <v>121.88</v>
+        <v>196.28</v>
       </c>
       <c r="F210" t="n">
-        <v>0.67575</v>
+        <v>6.24855</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5476,22 +5476,22 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>118.05</v>
+        <v>43.81</v>
       </c>
       <c r="D211" t="n">
-        <v>191.73</v>
+        <v>100.2</v>
       </c>
       <c r="E211" t="n">
-        <v>62.41</v>
+        <v>128.71</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.40022</v>
+        <v>-0.42056</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>10.49</v>
+        <v>166.99</v>
       </c>
       <c r="D212" t="n">
-        <v>19.88</v>
+        <v>330.36</v>
       </c>
       <c r="E212" t="n">
-        <v>89.51000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.15382</v>
+        <v>9.064159999999999</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5524,22 +5524,22 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>112.5</v>
+        <v>120.88</v>
       </c>
       <c r="D213" t="n">
-        <v>194.21</v>
+        <v>211.54</v>
       </c>
       <c r="E213" t="n">
-        <v>72.63</v>
+        <v>75</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.0532</v>
+        <v>-0.8151</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>188.79</v>
+        <v>32.36</v>
       </c>
       <c r="D214" t="n">
-        <v>276.63</v>
+        <v>53.34</v>
       </c>
       <c r="E214" t="n">
-        <v>46.53</v>
+        <v>64.83</v>
       </c>
       <c r="F214" t="n">
-        <v>-2.28574</v>
+        <v>0.36656</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5572,22 +5572,22 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>120.88</v>
+        <v>112.5</v>
       </c>
       <c r="D215" t="n">
-        <v>211.54</v>
+        <v>194.21</v>
       </c>
       <c r="E215" t="n">
-        <v>75</v>
+        <v>72.63</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.8151</v>
+        <v>-1.0532</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5596,22 +5596,22 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>57.15</v>
+        <v>121.11</v>
       </c>
       <c r="D216" t="n">
-        <v>192.77</v>
+        <v>332.35</v>
       </c>
       <c r="E216" t="n">
-        <v>237.31</v>
+        <v>174.42</v>
       </c>
       <c r="F216" t="n">
-        <v>4.18785</v>
+        <v>2.08531</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5620,22 +5620,22 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>151.43</v>
+        <v>83</v>
       </c>
       <c r="D217" t="n">
-        <v>265.67</v>
+        <v>142.35</v>
       </c>
       <c r="E217" t="n">
-        <v>75.44</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F217" t="n">
-        <v>1.55591</v>
+        <v>0.76309</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5644,22 +5644,22 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>34.41</v>
+        <v>76.7</v>
       </c>
       <c r="D218" t="n">
-        <v>67.69</v>
+        <v>170.18</v>
       </c>
       <c r="E218" t="n">
-        <v>96.72</v>
+        <v>121.88</v>
       </c>
       <c r="F218" t="n">
-        <v>0.14027</v>
+        <v>0.67575</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5668,22 +5668,22 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>117.65</v>
+        <v>105.37</v>
       </c>
       <c r="D219" t="n">
-        <v>231.88</v>
+        <v>230.05</v>
       </c>
       <c r="E219" t="n">
-        <v>97.09</v>
+        <v>118.33</v>
       </c>
       <c r="F219" t="n">
-        <v>0.40682</v>
+        <v>-1.90231</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5692,22 +5692,22 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>83</v>
+        <v>188.79</v>
       </c>
       <c r="D220" t="n">
-        <v>142.35</v>
+        <v>276.63</v>
       </c>
       <c r="E220" t="n">
-        <v>71.51000000000001</v>
+        <v>46.53</v>
       </c>
       <c r="F220" t="n">
-        <v>0.76309</v>
+        <v>-2.28574</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5716,22 +5716,22 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>25.85</v>
+        <v>18.26</v>
       </c>
       <c r="D221" t="n">
-        <v>42.91</v>
+        <v>34.02</v>
       </c>
       <c r="E221" t="n">
-        <v>66</v>
+        <v>86.31</v>
       </c>
       <c r="F221" t="n">
-        <v>0.12798</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5740,22 +5740,22 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>105.37</v>
+        <v>25.85</v>
       </c>
       <c r="D222" t="n">
-        <v>230.05</v>
+        <v>42.91</v>
       </c>
       <c r="E222" t="n">
-        <v>118.33</v>
+        <v>66</v>
       </c>
       <c r="F222" t="n">
-        <v>-1.90231</v>
+        <v>0.12798</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5764,22 +5764,22 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>18.26</v>
+        <v>117.65</v>
       </c>
       <c r="D223" t="n">
-        <v>34.02</v>
+        <v>231.88</v>
       </c>
       <c r="E223" t="n">
-        <v>86.31</v>
+        <v>97.09</v>
       </c>
       <c r="F223" t="n">
-        <v>1.1574</v>
+        <v>0.40682</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>166.99</v>
+        <v>10.49</v>
       </c>
       <c r="D224" t="n">
-        <v>330.36</v>
+        <v>19.88</v>
       </c>
       <c r="E224" t="n">
-        <v>97.83</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="F224" t="n">
-        <v>9.064159999999999</v>
+        <v>-0.15382</v>
       </c>
     </row>
     <row r="225">
@@ -5827,7 +5827,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5836,22 +5836,22 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>23.49</v>
+        <v>23.63</v>
       </c>
       <c r="D226" t="n">
-        <v>32.49</v>
+        <v>25.41</v>
       </c>
       <c r="E226" t="n">
-        <v>38.31</v>
+        <v>7.53</v>
       </c>
       <c r="F226" t="n">
-        <v>0.09743</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5860,22 +5860,22 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>23.63</v>
+        <v>190.63</v>
       </c>
       <c r="D227" t="n">
-        <v>25.41</v>
+        <v>218.57</v>
       </c>
       <c r="E227" t="n">
-        <v>7.53</v>
+        <v>14.66</v>
       </c>
       <c r="F227" t="n">
-        <v>0.0601</v>
+        <v>-1.51875</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5884,22 +5884,22 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>190.63</v>
+        <v>124.07</v>
       </c>
       <c r="D228" t="n">
-        <v>218.57</v>
+        <v>180.15</v>
       </c>
       <c r="E228" t="n">
-        <v>14.66</v>
+        <v>45.2</v>
       </c>
       <c r="F228" t="n">
-        <v>-1.51875</v>
+        <v>4.1705</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5908,16 +5908,16 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>124.07</v>
+        <v>23.49</v>
       </c>
       <c r="D229" t="n">
-        <v>180.15</v>
+        <v>32.49</v>
       </c>
       <c r="E229" t="n">
-        <v>45.2</v>
+        <v>38.31</v>
       </c>
       <c r="F229" t="n">
-        <v>4.1705</v>
+        <v>0.09743</v>
       </c>
     </row>
     <row r="230">
@@ -6019,25 +6019,25 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BAC-PL</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1180</v>
+        <v>164.13</v>
       </c>
       <c r="D234" t="n">
-        <v>1297.24</v>
+        <v>534.28</v>
       </c>
       <c r="E234" t="n">
-        <v>9.94</v>
+        <v>225.52</v>
       </c>
       <c r="F234" t="n">
-        <v>0.77758</v>
+        <v>21.33398</v>
       </c>
     </row>
     <row r="235">
@@ -6067,49 +6067,49 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>164.13</v>
+        <v>73.13</v>
       </c>
       <c r="D236" t="n">
-        <v>534.28</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E236" t="n">
-        <v>225.52</v>
+        <v>30.49</v>
       </c>
       <c r="F236" t="n">
-        <v>21.33398</v>
+        <v>0.43563</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RF-PC</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>23.5</v>
+        <v>199.3</v>
       </c>
       <c r="D237" t="n">
-        <v>24.64</v>
+        <v>351.81</v>
       </c>
       <c r="E237" t="n">
-        <v>4.85</v>
+        <v>76.52</v>
       </c>
       <c r="F237" t="n">
-        <v>0.07706</v>
+        <v>-1.44191</v>
       </c>
     </row>
     <row r="238">
@@ -6187,7 +6187,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>199.3</v>
+        <v>273.5</v>
       </c>
       <c r="D241" t="n">
-        <v>351.81</v>
+        <v>349.39</v>
       </c>
       <c r="E241" t="n">
-        <v>76.52</v>
+        <v>27.75</v>
       </c>
       <c r="F241" t="n">
-        <v>-1.44191</v>
+        <v>-1.43004</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,22 +6220,22 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>73.13</v>
+        <v>28.35</v>
       </c>
       <c r="D242" t="n">
-        <v>95.43000000000001</v>
+        <v>38.72</v>
       </c>
       <c r="E242" t="n">
-        <v>30.49</v>
+        <v>36.58</v>
       </c>
       <c r="F242" t="n">
-        <v>0.43563</v>
+        <v>0.29357</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6244,22 +6244,22 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>273.5</v>
+        <v>273.14</v>
       </c>
       <c r="D243" t="n">
-        <v>349.39</v>
+        <v>345.71</v>
       </c>
       <c r="E243" t="n">
-        <v>27.75</v>
+        <v>26.57</v>
       </c>
       <c r="F243" t="n">
-        <v>-1.43004</v>
+        <v>-1.43948</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>69.3</v>
+        <v>22.61</v>
       </c>
       <c r="D244" t="n">
-        <v>83.54000000000001</v>
+        <v>55.41</v>
       </c>
       <c r="E244" t="n">
-        <v>20.55</v>
+        <v>145.07</v>
       </c>
       <c r="F244" t="n">
-        <v>0.20672</v>
+        <v>1.53437</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>273.14</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D245" t="n">
-        <v>345.71</v>
+        <v>21.9</v>
       </c>
       <c r="E245" t="n">
-        <v>26.57</v>
+        <v>154.36</v>
       </c>
       <c r="F245" t="n">
-        <v>-1.43948</v>
+        <v>0.80893</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,22 +6316,22 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>22.61</v>
+        <v>166</v>
       </c>
       <c r="D246" t="n">
-        <v>55.41</v>
+        <v>407.02</v>
       </c>
       <c r="E246" t="n">
-        <v>145.07</v>
+        <v>145.19</v>
       </c>
       <c r="F246" t="n">
-        <v>1.53437</v>
+        <v>4.5493</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>8.609999999999999</v>
+        <v>119.51</v>
       </c>
       <c r="D247" t="n">
-        <v>21.9</v>
+        <v>257.05</v>
       </c>
       <c r="E247" t="n">
-        <v>154.36</v>
+        <v>115.09</v>
       </c>
       <c r="F247" t="n">
-        <v>0.80893</v>
+        <v>12.83332</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>166</v>
+        <v>29.16</v>
       </c>
       <c r="D248" t="n">
-        <v>407.02</v>
+        <v>39.94</v>
       </c>
       <c r="E248" t="n">
-        <v>145.19</v>
+        <v>36.97</v>
       </c>
       <c r="F248" t="n">
-        <v>4.5493</v>
+        <v>0.01199</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>119.51</v>
+        <v>97.52</v>
       </c>
       <c r="D249" t="n">
-        <v>257.05</v>
+        <v>132.88</v>
       </c>
       <c r="E249" t="n">
-        <v>115.09</v>
+        <v>36.26</v>
       </c>
       <c r="F249" t="n">
-        <v>12.83332</v>
+        <v>2.17585</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>29.16</v>
+        <v>69.3</v>
       </c>
       <c r="D250" t="n">
-        <v>39.94</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E250" t="n">
-        <v>36.97</v>
+        <v>20.55</v>
       </c>
       <c r="F250" t="n">
-        <v>0.01199</v>
+        <v>0.20672</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>97.52</v>
+        <v>258.08</v>
       </c>
       <c r="D251" t="n">
-        <v>132.88</v>
+        <v>290.05</v>
       </c>
       <c r="E251" t="n">
-        <v>36.26</v>
+        <v>12.39</v>
       </c>
       <c r="F251" t="n">
-        <v>2.17585</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>28.35</v>
+        <v>24.77</v>
       </c>
       <c r="D252" t="n">
-        <v>38.72</v>
+        <v>36.96</v>
       </c>
       <c r="E252" t="n">
-        <v>36.58</v>
+        <v>49.21</v>
       </c>
       <c r="F252" t="n">
-        <v>0.29357</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>258.08</v>
+        <v>284.79</v>
       </c>
       <c r="D253" t="n">
-        <v>290.05</v>
+        <v>424.24</v>
       </c>
       <c r="E253" t="n">
-        <v>12.39</v>
+        <v>48.97</v>
       </c>
       <c r="F253" t="n">
-        <v>0.8742</v>
+        <v>5.01403</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>24.77</v>
+        <v>67.39</v>
       </c>
       <c r="D254" t="n">
-        <v>36.96</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E254" t="n">
-        <v>49.21</v>
+        <v>38.64</v>
       </c>
       <c r="F254" t="n">
-        <v>0.4117</v>
+        <v>0.55682</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>284.79</v>
+        <v>65.16</v>
       </c>
       <c r="D255" t="n">
-        <v>424.24</v>
+        <v>114.33</v>
       </c>
       <c r="E255" t="n">
-        <v>48.97</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="F255" t="n">
-        <v>5.01403</v>
+        <v>2.2454</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>67.39</v>
+        <v>19.02</v>
       </c>
       <c r="D256" t="n">
-        <v>93.43000000000001</v>
+        <v>27.24</v>
       </c>
       <c r="E256" t="n">
-        <v>38.64</v>
+        <v>43.22</v>
       </c>
       <c r="F256" t="n">
-        <v>0.55682</v>
+        <v>0.27865</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>65.16</v>
+        <v>20.33</v>
       </c>
       <c r="D257" t="n">
-        <v>114.33</v>
+        <v>29.1</v>
       </c>
       <c r="E257" t="n">
-        <v>75.45999999999999</v>
+        <v>43.14</v>
       </c>
       <c r="F257" t="n">
-        <v>2.2454</v>
+        <v>0.12624</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>19.02</v>
+        <v>16.32</v>
       </c>
       <c r="D258" t="n">
-        <v>27.24</v>
+        <v>23.89</v>
       </c>
       <c r="E258" t="n">
-        <v>43.22</v>
+        <v>46.38</v>
       </c>
       <c r="F258" t="n">
-        <v>0.27865</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>20.33</v>
+        <v>41.19</v>
       </c>
       <c r="D259" t="n">
-        <v>29.1</v>
+        <v>97.19</v>
       </c>
       <c r="E259" t="n">
-        <v>43.14</v>
+        <v>135.96</v>
       </c>
       <c r="F259" t="n">
-        <v>0.12624</v>
+        <v>2.31858</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>16.32</v>
+        <v>107.27</v>
       </c>
       <c r="D260" t="n">
-        <v>23.89</v>
+        <v>136.18</v>
       </c>
       <c r="E260" t="n">
-        <v>46.38</v>
+        <v>26.95</v>
       </c>
       <c r="F260" t="n">
-        <v>0.235</v>
+        <v>1.00255</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>41.19</v>
+        <v>196.04</v>
       </c>
       <c r="D261" t="n">
-        <v>97.19</v>
+        <v>493.41</v>
       </c>
       <c r="E261" t="n">
-        <v>135.96</v>
+        <v>151.69</v>
       </c>
       <c r="F261" t="n">
-        <v>2.31858</v>
+        <v>9.84099</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>107.27</v>
+        <v>246.63</v>
       </c>
       <c r="D262" t="n">
-        <v>136.18</v>
+        <v>333.08</v>
       </c>
       <c r="E262" t="n">
-        <v>26.95</v>
+        <v>35.05</v>
       </c>
       <c r="F262" t="n">
-        <v>1.00255</v>
+        <v>3.52767</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>196.04</v>
+        <v>59.66</v>
       </c>
       <c r="D263" t="n">
-        <v>493.41</v>
+        <v>84.11</v>
       </c>
       <c r="E263" t="n">
-        <v>151.69</v>
+        <v>40.98</v>
       </c>
       <c r="F263" t="n">
-        <v>9.84099</v>
+        <v>1.58777</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>246.63</v>
+        <v>57.45</v>
       </c>
       <c r="D264" t="n">
-        <v>333.08</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E264" t="n">
-        <v>35.05</v>
+        <v>22.79</v>
       </c>
       <c r="F264" t="n">
-        <v>3.52767</v>
+        <v>-0.19886</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>59.66</v>
+        <v>279.73</v>
       </c>
       <c r="D265" t="n">
-        <v>84.11</v>
+        <v>411.49</v>
       </c>
       <c r="E265" t="n">
-        <v>40.98</v>
+        <v>47.1</v>
       </c>
       <c r="F265" t="n">
-        <v>1.58777</v>
+        <v>3.73943</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>57.45</v>
+        <v>26.41</v>
       </c>
       <c r="D266" t="n">
-        <v>70.54000000000001</v>
+        <v>41.02</v>
       </c>
       <c r="E266" t="n">
-        <v>22.79</v>
+        <v>55.32</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.19886</v>
+        <v>1.68935</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>279.73</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D267" t="n">
-        <v>411.49</v>
+        <v>100.36</v>
       </c>
       <c r="E267" t="n">
-        <v>47.1</v>
+        <v>11.5</v>
       </c>
       <c r="F267" t="n">
-        <v>3.73943</v>
+        <v>0.11228</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>26.41</v>
+        <v>31.8</v>
       </c>
       <c r="D268" t="n">
-        <v>41.02</v>
+        <v>69.41</v>
       </c>
       <c r="E268" t="n">
-        <v>55.32</v>
+        <v>118.27</v>
       </c>
       <c r="F268" t="n">
-        <v>1.68935</v>
+        <v>0.31551</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>90.01000000000001</v>
+        <v>204.77</v>
       </c>
       <c r="D269" t="n">
-        <v>100.36</v>
+        <v>274.99</v>
       </c>
       <c r="E269" t="n">
-        <v>11.5</v>
+        <v>34.29</v>
       </c>
       <c r="F269" t="n">
-        <v>0.11228</v>
+        <v>0.55032</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6892,70 +6892,70 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>31.8</v>
+        <v>12.96</v>
       </c>
       <c r="D270" t="n">
-        <v>69.41</v>
+        <v>16.66</v>
       </c>
       <c r="E270" t="n">
-        <v>118.27</v>
+        <v>28.55</v>
       </c>
       <c r="F270" t="n">
-        <v>0.31551</v>
+        <v>-0.0515</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>204.77</v>
+        <v>147.02</v>
       </c>
       <c r="D271" t="n">
-        <v>274.99</v>
+        <v>373.94</v>
       </c>
       <c r="E271" t="n">
-        <v>34.29</v>
+        <v>154.35</v>
       </c>
       <c r="F271" t="n">
-        <v>0.55032</v>
+        <v>-2.08465</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>AXSM</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>12.96</v>
+        <v>156.35</v>
       </c>
       <c r="D272" t="n">
-        <v>16.66</v>
+        <v>216.58</v>
       </c>
       <c r="E272" t="n">
-        <v>28.55</v>
+        <v>38.52</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.0515</v>
+        <v>1.76572</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,22 +6964,22 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>147.02</v>
+        <v>92.39</v>
       </c>
       <c r="D273" t="n">
-        <v>373.94</v>
+        <v>235.38</v>
       </c>
       <c r="E273" t="n">
-        <v>154.35</v>
+        <v>154.75</v>
       </c>
       <c r="F273" t="n">
-        <v>-2.08465</v>
+        <v>2.36905</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>156.35</v>
+        <v>7.63</v>
       </c>
       <c r="D274" t="n">
-        <v>216.58</v>
+        <v>11.33</v>
       </c>
       <c r="E274" t="n">
-        <v>38.52</v>
+        <v>48.49</v>
       </c>
       <c r="F274" t="n">
-        <v>1.76572</v>
+        <v>0.16084</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>92.39</v>
+        <v>284.93</v>
       </c>
       <c r="D275" t="n">
-        <v>235.38</v>
+        <v>412.56</v>
       </c>
       <c r="E275" t="n">
-        <v>154.75</v>
+        <v>44.79</v>
       </c>
       <c r="F275" t="n">
-        <v>2.36905</v>
+        <v>0.67323</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>7.63</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D276" t="n">
-        <v>11.33</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="E276" t="n">
-        <v>48.49</v>
+        <v>18.13</v>
       </c>
       <c r="F276" t="n">
-        <v>0.16084</v>
+        <v>-0.43807</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,22 +7060,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>284.93</v>
+        <v>285.27</v>
       </c>
       <c r="D277" t="n">
-        <v>412.56</v>
+        <v>378.05</v>
       </c>
       <c r="E277" t="n">
-        <v>44.79</v>
+        <v>32.52</v>
       </c>
       <c r="F277" t="n">
-        <v>0.67323</v>
+        <v>1.30077</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7084,22 +7084,22 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>67.56999999999999</v>
+        <v>33.63</v>
       </c>
       <c r="D278" t="n">
-        <v>79.81999999999999</v>
+        <v>43.55</v>
       </c>
       <c r="E278" t="n">
-        <v>18.13</v>
+        <v>29.5</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.43807</v>
+        <v>-0.00236</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7108,22 +7108,22 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>72.90000000000001</v>
+        <v>202.71</v>
       </c>
       <c r="D279" t="n">
-        <v>94.92</v>
+        <v>258.48</v>
       </c>
       <c r="E279" t="n">
-        <v>30.21</v>
+        <v>27.51</v>
       </c>
       <c r="F279" t="n">
-        <v>0.7454499999999999</v>
+        <v>-1.41316</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7132,22 +7132,22 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>285.27</v>
+        <v>67.7</v>
       </c>
       <c r="D280" t="n">
-        <v>378.05</v>
+        <v>97.75</v>
       </c>
       <c r="E280" t="n">
-        <v>32.52</v>
+        <v>44.39</v>
       </c>
       <c r="F280" t="n">
-        <v>1.30077</v>
+        <v>0.25783</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7156,22 +7156,22 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>33.63</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D281" t="n">
-        <v>43.55</v>
+        <v>157.45</v>
       </c>
       <c r="E281" t="n">
-        <v>29.5</v>
+        <v>80.67</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.00236</v>
+        <v>-0.08858000000000001</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7180,22 +7180,22 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>202.71</v>
+        <v>91.37</v>
       </c>
       <c r="D282" t="n">
-        <v>258.48</v>
+        <v>120.93</v>
       </c>
       <c r="E282" t="n">
-        <v>27.51</v>
+        <v>32.35</v>
       </c>
       <c r="F282" t="n">
-        <v>-1.41316</v>
+        <v>-0.10485</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7204,22 +7204,22 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>87.15000000000001</v>
+        <v>22.3</v>
       </c>
       <c r="D283" t="n">
-        <v>157.45</v>
+        <v>34.8</v>
       </c>
       <c r="E283" t="n">
-        <v>80.67</v>
+        <v>56.05</v>
       </c>
       <c r="F283" t="n">
-        <v>-0.08858000000000001</v>
+        <v>0.45747</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7228,22 +7228,22 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>91.37</v>
+        <v>52.49</v>
       </c>
       <c r="D284" t="n">
-        <v>120.93</v>
+        <v>55.78</v>
       </c>
       <c r="E284" t="n">
-        <v>32.35</v>
+        <v>6.27</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.10485</v>
+        <v>-0.04614</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7252,22 +7252,22 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>22.3</v>
+        <v>10.65</v>
       </c>
       <c r="D285" t="n">
-        <v>34.8</v>
+        <v>14.74</v>
       </c>
       <c r="E285" t="n">
-        <v>56.05</v>
+        <v>38.4</v>
       </c>
       <c r="F285" t="n">
-        <v>0.45747</v>
+        <v>0.05009</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7276,22 +7276,22 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>39.84</v>
+        <v>92.42</v>
       </c>
       <c r="D286" t="n">
-        <v>58.53</v>
+        <v>108.59</v>
       </c>
       <c r="E286" t="n">
-        <v>46.91</v>
+        <v>17.5</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.08142000000000001</v>
+        <v>0.1877</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7300,22 +7300,22 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>10.65</v>
+        <v>20.72</v>
       </c>
       <c r="D287" t="n">
-        <v>14.74</v>
+        <v>24.85</v>
       </c>
       <c r="E287" t="n">
-        <v>38.4</v>
+        <v>19.93</v>
       </c>
       <c r="F287" t="n">
-        <v>0.05009</v>
+        <v>-0.07012</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7324,22 +7324,22 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>92.42</v>
+        <v>17.45</v>
       </c>
       <c r="D288" t="n">
-        <v>108.59</v>
+        <v>19.8</v>
       </c>
       <c r="E288" t="n">
-        <v>17.5</v>
+        <v>13.47</v>
       </c>
       <c r="F288" t="n">
-        <v>0.1877</v>
+        <v>-0.03105</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7348,22 +7348,22 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>20.72</v>
+        <v>55.4</v>
       </c>
       <c r="D289" t="n">
-        <v>24.85</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E289" t="n">
-        <v>19.93</v>
+        <v>24.87</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.07012</v>
+        <v>-0.03903</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ARCC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7372,22 +7372,22 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>17.45</v>
+        <v>295.52</v>
       </c>
       <c r="D290" t="n">
-        <v>19.8</v>
+        <v>375.28</v>
       </c>
       <c r="E290" t="n">
-        <v>13.47</v>
+        <v>26.99</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.03105</v>
+        <v>-0.74265</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7396,22 +7396,22 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>55.4</v>
+        <v>3.42</v>
       </c>
       <c r="D291" t="n">
-        <v>69.18000000000001</v>
+        <v>4.89</v>
       </c>
       <c r="E291" t="n">
-        <v>24.87</v>
+        <v>42.98</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.03903</v>
+        <v>0.09469</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7420,22 +7420,22 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>295.52</v>
+        <v>525.72</v>
       </c>
       <c r="D292" t="n">
-        <v>375.28</v>
+        <v>665.6</v>
       </c>
       <c r="E292" t="n">
-        <v>26.99</v>
+        <v>26.61</v>
       </c>
       <c r="F292" t="n">
-        <v>-0.74265</v>
+        <v>22.11172</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7444,22 +7444,22 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3.42</v>
+        <v>289.16</v>
       </c>
       <c r="D293" t="n">
-        <v>4.89</v>
+        <v>410.01</v>
       </c>
       <c r="E293" t="n">
-        <v>42.98</v>
+        <v>41.79</v>
       </c>
       <c r="F293" t="n">
-        <v>0.09469</v>
+        <v>-0.38142</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7468,22 +7468,22 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>525.72</v>
+        <v>39.84</v>
       </c>
       <c r="D294" t="n">
-        <v>665.6</v>
+        <v>58.53</v>
       </c>
       <c r="E294" t="n">
-        <v>26.61</v>
+        <v>46.91</v>
       </c>
       <c r="F294" t="n">
-        <v>22.11172</v>
+        <v>-0.08142000000000001</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7492,22 +7492,22 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>289.16</v>
+        <v>61.37</v>
       </c>
       <c r="D295" t="n">
-        <v>410.01</v>
+        <v>80.23</v>
       </c>
       <c r="E295" t="n">
-        <v>41.79</v>
+        <v>30.73</v>
       </c>
       <c r="F295" t="n">
-        <v>-0.38142</v>
+        <v>-0.09644999999999999</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7516,22 +7516,22 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>67.7</v>
+        <v>317.93</v>
       </c>
       <c r="D296" t="n">
-        <v>97.75</v>
+        <v>379.54</v>
       </c>
       <c r="E296" t="n">
-        <v>44.39</v>
+        <v>19.38</v>
       </c>
       <c r="F296" t="n">
-        <v>0.25783</v>
+        <v>-0.71048</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7540,22 +7540,22 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>317.93</v>
+        <v>153.68</v>
       </c>
       <c r="D297" t="n">
-        <v>379.54</v>
+        <v>172.02</v>
       </c>
       <c r="E297" t="n">
-        <v>19.38</v>
+        <v>11.93</v>
       </c>
       <c r="F297" t="n">
-        <v>-0.71048</v>
+        <v>-0.63445</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7564,22 +7564,22 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>125.78</v>
+        <v>7.58</v>
       </c>
       <c r="D298" t="n">
-        <v>143.7</v>
+        <v>10.73</v>
       </c>
       <c r="E298" t="n">
-        <v>14.25</v>
+        <v>41.56</v>
       </c>
       <c r="F298" t="n">
-        <v>-0.39666</v>
+        <v>0.17999</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7588,22 +7588,22 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>157.12</v>
+        <v>213.28</v>
       </c>
       <c r="D299" t="n">
-        <v>261.12</v>
+        <v>283.27</v>
       </c>
       <c r="E299" t="n">
-        <v>66.19</v>
+        <v>32.82</v>
       </c>
       <c r="F299" t="n">
-        <v>1.88244</v>
+        <v>-0.5633</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7612,22 +7612,22 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>87.01000000000001</v>
+        <v>157.12</v>
       </c>
       <c r="D300" t="n">
-        <v>116.9</v>
+        <v>261.12</v>
       </c>
       <c r="E300" t="n">
-        <v>34.35</v>
+        <v>66.19</v>
       </c>
       <c r="F300" t="n">
-        <v>0.85321</v>
+        <v>1.88244</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7636,22 +7636,22 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>71.42</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D301" t="n">
-        <v>78.89</v>
+        <v>116.9</v>
       </c>
       <c r="E301" t="n">
-        <v>10.46</v>
+        <v>34.35</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.24064</v>
+        <v>0.85321</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>QSR</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7660,22 +7660,22 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>243.35</v>
+        <v>71.42</v>
       </c>
       <c r="D302" t="n">
-        <v>355.2</v>
+        <v>78.89</v>
       </c>
       <c r="E302" t="n">
-        <v>45.96</v>
+        <v>10.46</v>
       </c>
       <c r="F302" t="n">
-        <v>0.55648</v>
+        <v>-0.24064</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7684,22 +7684,22 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>182.65</v>
+        <v>243.35</v>
       </c>
       <c r="D303" t="n">
-        <v>341.79</v>
+        <v>355.2</v>
       </c>
       <c r="E303" t="n">
-        <v>87.13</v>
+        <v>45.96</v>
       </c>
       <c r="F303" t="n">
-        <v>4.40399</v>
+        <v>0.55648</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7708,22 +7708,22 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>87.98</v>
+        <v>182.65</v>
       </c>
       <c r="D304" t="n">
-        <v>108.99</v>
+        <v>341.79</v>
       </c>
       <c r="E304" t="n">
-        <v>23.88</v>
+        <v>87.13</v>
       </c>
       <c r="F304" t="n">
-        <v>0.3621</v>
+        <v>4.40399</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7732,22 +7732,22 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>61.37</v>
+        <v>3.93</v>
       </c>
       <c r="D305" t="n">
-        <v>80.23</v>
+        <v>5.84</v>
       </c>
       <c r="E305" t="n">
-        <v>30.73</v>
+        <v>48.6</v>
       </c>
       <c r="F305" t="n">
-        <v>-0.09644999999999999</v>
+        <v>0.07327</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7756,22 +7756,22 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>35.34</v>
+        <v>87.98</v>
       </c>
       <c r="D306" t="n">
-        <v>53.67</v>
+        <v>108.99</v>
       </c>
       <c r="E306" t="n">
-        <v>51.87</v>
+        <v>23.88</v>
       </c>
       <c r="F306" t="n">
-        <v>0.74151</v>
+        <v>0.3621</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7780,22 +7780,22 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>35.72</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D307" t="n">
-        <v>49.48</v>
+        <v>94.92</v>
       </c>
       <c r="E307" t="n">
-        <v>38.52</v>
+        <v>30.21</v>
       </c>
       <c r="F307" t="n">
-        <v>-0.54794</v>
+        <v>0.7454499999999999</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7804,22 +7804,22 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>213.28</v>
+        <v>35.34</v>
       </c>
       <c r="D308" t="n">
-        <v>283.27</v>
+        <v>53.67</v>
       </c>
       <c r="E308" t="n">
-        <v>32.82</v>
+        <v>51.87</v>
       </c>
       <c r="F308" t="n">
-        <v>-0.5633</v>
+        <v>0.74151</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7828,22 +7828,22 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>7.58</v>
+        <v>125.78</v>
       </c>
       <c r="D309" t="n">
-        <v>10.73</v>
+        <v>143.7</v>
       </c>
       <c r="E309" t="n">
-        <v>41.56</v>
+        <v>14.25</v>
       </c>
       <c r="F309" t="n">
-        <v>0.17999</v>
+        <v>-0.39666</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7852,22 +7852,22 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3.93</v>
+        <v>35.72</v>
       </c>
       <c r="D310" t="n">
-        <v>5.84</v>
+        <v>49.48</v>
       </c>
       <c r="E310" t="n">
-        <v>48.6</v>
+        <v>38.52</v>
       </c>
       <c r="F310" t="n">
-        <v>0.07327</v>
+        <v>-0.54794</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7876,16 +7876,16 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>153.68</v>
+        <v>67.23</v>
       </c>
       <c r="D311" t="n">
-        <v>172.02</v>
+        <v>98.22</v>
       </c>
       <c r="E311" t="n">
-        <v>11.93</v>
+        <v>46.1</v>
       </c>
       <c r="F311" t="n">
-        <v>-0.63445</v>
+        <v>-0.14265</v>
       </c>
     </row>
     <row r="312">
@@ -7939,55 +7939,55 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>67.23</v>
+        <v>17.13</v>
       </c>
       <c r="D314" t="n">
-        <v>98.22</v>
+        <v>43.45</v>
       </c>
       <c r="E314" t="n">
-        <v>46.1</v>
+        <v>153.65</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.14265</v>
+        <v>0.28998</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>17.13</v>
+        <v>63.78</v>
       </c>
       <c r="D315" t="n">
-        <v>43.45</v>
+        <v>70.61</v>
       </c>
       <c r="E315" t="n">
-        <v>153.65</v>
+        <v>10.71</v>
       </c>
       <c r="F315" t="n">
-        <v>0.28998</v>
+        <v>0.28252</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7996,46 +7996,46 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>63.78</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D316" t="n">
-        <v>70.61</v>
+        <v>168.93</v>
       </c>
       <c r="E316" t="n">
-        <v>10.71</v>
+        <v>68.95</v>
       </c>
       <c r="F316" t="n">
-        <v>0.28252</v>
+        <v>0.20101</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>99.98999999999999</v>
+        <v>27.17</v>
       </c>
       <c r="D317" t="n">
-        <v>168.93</v>
+        <v>33.86</v>
       </c>
       <c r="E317" t="n">
-        <v>68.95</v>
+        <v>24.62</v>
       </c>
       <c r="F317" t="n">
-        <v>0.20101</v>
+        <v>-0.24679</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -8044,22 +8044,22 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>94.23999999999999</v>
+        <v>241.14</v>
       </c>
       <c r="D318" t="n">
-        <v>112.01</v>
+        <v>298.6</v>
       </c>
       <c r="E318" t="n">
-        <v>18.86</v>
+        <v>23.83</v>
       </c>
       <c r="F318" t="n">
-        <v>-0.19592</v>
+        <v>1.64228</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>MDGL</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -8068,22 +8068,22 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>241.14</v>
+        <v>445.04</v>
       </c>
       <c r="D319" t="n">
-        <v>298.6</v>
+        <v>540.0599999999999</v>
       </c>
       <c r="E319" t="n">
-        <v>23.83</v>
+        <v>21.35</v>
       </c>
       <c r="F319" t="n">
-        <v>1.64228</v>
+        <v>2.20142</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ABEV</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -8092,22 +8092,22 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2.78</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D320" t="n">
-        <v>3.03</v>
+        <v>112.01</v>
       </c>
       <c r="E320" t="n">
-        <v>8.99</v>
+        <v>18.86</v>
       </c>
       <c r="F320" t="n">
-        <v>0.02721</v>
+        <v>-0.19592</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>MDGL</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -8116,22 +8116,22 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>445.04</v>
+        <v>23.65</v>
       </c>
       <c r="D321" t="n">
-        <v>540.0599999999999</v>
+        <v>29.25</v>
       </c>
       <c r="E321" t="n">
-        <v>21.35</v>
+        <v>23.66</v>
       </c>
       <c r="F321" t="n">
-        <v>2.20142</v>
+        <v>0.22235</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>FMX</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -8140,22 +8140,22 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>146.17</v>
+        <v>105.8</v>
       </c>
       <c r="D322" t="n">
-        <v>217.15</v>
+        <v>121.26</v>
       </c>
       <c r="E322" t="n">
-        <v>48.56</v>
+        <v>14.61</v>
       </c>
       <c r="F322" t="n">
-        <v>0.01127</v>
+        <v>-0.80715</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -8164,22 +8164,22 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>23.97</v>
+        <v>146.17</v>
       </c>
       <c r="D323" t="n">
-        <v>30.56</v>
+        <v>217.15</v>
       </c>
       <c r="E323" t="n">
-        <v>27.49</v>
+        <v>48.56</v>
       </c>
       <c r="F323" t="n">
-        <v>-0.08098</v>
+        <v>0.01127</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>FMX</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -8188,22 +8188,22 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>105.8</v>
+        <v>23.97</v>
       </c>
       <c r="D324" t="n">
-        <v>121.26</v>
+        <v>30.56</v>
       </c>
       <c r="E324" t="n">
-        <v>14.61</v>
+        <v>27.49</v>
       </c>
       <c r="F324" t="n">
-        <v>-0.80715</v>
+        <v>-0.08098</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -8212,40 +8212,16 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>23.65</v>
+        <v>2.78</v>
       </c>
       <c r="D325" t="n">
-        <v>29.25</v>
+        <v>3.03</v>
       </c>
       <c r="E325" t="n">
-        <v>23.66</v>
+        <v>8.99</v>
       </c>
       <c r="F325" t="n">
-        <v>0.22235</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>NWS</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C326" t="n">
-        <v>27.17</v>
-      </c>
-      <c r="D326" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="E326" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="F326" t="n">
-        <v>-0.24679</v>
+        <v>0.02721</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F325"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,25 +451,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2876.75</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>2965.52</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.09</v>
+        <v>7.17</v>
       </c>
       <c r="F2" t="n">
-        <v>-26.725</v>
+        <v>-0.94382</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>57.29</v>
+        <v>56.65</v>
       </c>
       <c r="E3" t="n">
-        <v>5.45</v>
+        <v>4.28</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.33941</v>
+        <v>-0.08566</v>
       </c>
     </row>
     <row r="4">
@@ -511,13 +511,13 @@
         <v>38.22</v>
       </c>
       <c r="D4" t="n">
-        <v>41.6</v>
+        <v>42.41</v>
       </c>
       <c r="E4" t="n">
-        <v>8.84</v>
+        <v>10.96</v>
       </c>
       <c r="F4" t="n">
-        <v>0.17365</v>
+        <v>0.13711</v>
       </c>
     </row>
     <row r="5">
@@ -535,13 +535,13 @@
         <v>17.87</v>
       </c>
       <c r="D5" t="n">
-        <v>21.62</v>
+        <v>21.24</v>
       </c>
       <c r="E5" t="n">
-        <v>20.98</v>
+        <v>18.86</v>
       </c>
       <c r="F5" t="n">
-        <v>0.65938</v>
+        <v>0.72516</v>
       </c>
     </row>
     <row r="6">
@@ -559,13 +559,13 @@
         <v>102.63</v>
       </c>
       <c r="D6" t="n">
-        <v>109.08</v>
+        <v>108.51</v>
       </c>
       <c r="E6" t="n">
-        <v>6.28</v>
+        <v>5.73</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22351</v>
+        <v>0.05302</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>13.03</v>
       </c>
       <c r="D7" t="n">
-        <v>14.97</v>
+        <v>15.02</v>
       </c>
       <c r="E7" t="n">
-        <v>14.89</v>
+        <v>15.23</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01791</v>
+        <v>0.09189</v>
       </c>
     </row>
     <row r="8">
@@ -607,13 +607,13 @@
         <v>298.59</v>
       </c>
       <c r="D8" t="n">
-        <v>334.24</v>
+        <v>328.18</v>
       </c>
       <c r="E8" t="n">
-        <v>11.94</v>
+        <v>9.91</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.56324</v>
+        <v>0.78755</v>
       </c>
     </row>
     <row r="9">
@@ -631,13 +631,13 @@
         <v>5.67</v>
       </c>
       <c r="D9" t="n">
-        <v>7.03</v>
+        <v>7.05</v>
       </c>
       <c r="E9" t="n">
-        <v>23.99</v>
+        <v>24.34</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1648</v>
+        <v>0.17197</v>
       </c>
     </row>
     <row r="10">
@@ -655,19 +655,19 @@
         <v>141.63</v>
       </c>
       <c r="D10" t="n">
-        <v>157.31</v>
+        <v>156.93</v>
       </c>
       <c r="E10" t="n">
-        <v>11.07</v>
+        <v>10.81</v>
       </c>
       <c r="F10" t="n">
-        <v>1.11386</v>
+        <v>1.6254</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -676,22 +676,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12.43</v>
+        <v>2.98</v>
       </c>
       <c r="D11" t="n">
-        <v>18.42</v>
+        <v>3.52</v>
       </c>
       <c r="E11" t="n">
-        <v>48.19</v>
+        <v>18.12</v>
       </c>
       <c r="F11" t="n">
-        <v>0.97816</v>
+        <v>0.07025000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.23</v>
+        <v>7.17</v>
       </c>
       <c r="D12" t="n">
-        <v>11.89</v>
+        <v>8.24</v>
       </c>
       <c r="E12" t="n">
-        <v>5.88</v>
+        <v>14.99</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03212</v>
+        <v>0.1381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.17</v>
+        <v>12.43</v>
       </c>
       <c r="D13" t="n">
-        <v>8.23</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="n">
-        <v>14.78</v>
+        <v>39.98</v>
       </c>
       <c r="F13" t="n">
-        <v>0.13527</v>
+        <v>0.8716699999999999</v>
       </c>
     </row>
     <row r="14">
@@ -751,19 +751,19 @@
         <v>4.46</v>
       </c>
       <c r="D14" t="n">
-        <v>5.22</v>
+        <v>5.24</v>
       </c>
       <c r="E14" t="n">
-        <v>17.04</v>
+        <v>17.38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08513999999999999</v>
+        <v>0.08227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.98</v>
+        <v>11.23</v>
       </c>
       <c r="D15" t="n">
-        <v>3.54</v>
+        <v>11.87</v>
       </c>
       <c r="E15" t="n">
-        <v>18.79</v>
+        <v>5.67</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06816999999999999</v>
+        <v>0.03632</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.28</v>
+        <v>98.45</v>
       </c>
       <c r="D16" t="n">
-        <v>19.12</v>
+        <v>124.94</v>
       </c>
       <c r="E16" t="n">
-        <v>10.65</v>
+        <v>26.91</v>
       </c>
       <c r="F16" t="n">
-        <v>0.22309</v>
+        <v>1.8845</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,184 +820,184 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>98.45</v>
+        <v>17.28</v>
       </c>
       <c r="D17" t="n">
-        <v>122.3</v>
+        <v>19.14</v>
       </c>
       <c r="E17" t="n">
-        <v>24.23</v>
+        <v>10.73</v>
       </c>
       <c r="F17" t="n">
-        <v>2.28707</v>
+        <v>0.21851</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35.54</v>
+        <v>2.78</v>
       </c>
       <c r="D18" t="n">
-        <v>51.29</v>
+        <v>3.03</v>
       </c>
       <c r="E18" t="n">
-        <v>44.32</v>
+        <v>8.81</v>
       </c>
       <c r="F18" t="n">
-        <v>1.98244</v>
+        <v>0.02604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>123.39</v>
+        <v>52.62</v>
       </c>
       <c r="D19" t="n">
-        <v>137.82</v>
+        <v>56.64</v>
       </c>
       <c r="E19" t="n">
-        <v>11.69</v>
+        <v>7.64</v>
       </c>
       <c r="F19" t="n">
-        <v>1.38289</v>
+        <v>0.35581</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63.54</v>
+        <v>35.54</v>
       </c>
       <c r="D20" t="n">
-        <v>70.34</v>
+        <v>50.1</v>
       </c>
       <c r="E20" t="n">
-        <v>10.7</v>
+        <v>40.97</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02608</v>
+        <v>2.32507</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>155.62</v>
+        <v>123.39</v>
       </c>
       <c r="D21" t="n">
-        <v>163.78</v>
+        <v>136.92</v>
       </c>
       <c r="E21" t="n">
-        <v>5.24</v>
+        <v>10.97</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.00319</v>
+        <v>1.40833</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60.35</v>
+        <v>340.65</v>
       </c>
       <c r="D22" t="n">
-        <v>97.42</v>
+        <v>373.32</v>
       </c>
       <c r="E22" t="n">
-        <v>61.43</v>
+        <v>9.59</v>
       </c>
       <c r="F22" t="n">
-        <v>1.96052</v>
+        <v>-1.04944</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FIGR</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.91</v>
+        <v>63.54</v>
       </c>
       <c r="D23" t="n">
-        <v>35.65</v>
+        <v>72.53</v>
       </c>
       <c r="E23" t="n">
-        <v>43.12</v>
+        <v>14.14</v>
       </c>
       <c r="F23" t="n">
-        <v>0.36343</v>
+        <v>0.58789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>205.48</v>
+        <v>155.62</v>
       </c>
       <c r="D24" t="n">
-        <v>249.99</v>
+        <v>163.19</v>
       </c>
       <c r="E24" t="n">
-        <v>21.66</v>
+        <v>4.86</v>
       </c>
       <c r="F24" t="n">
-        <v>1.24005</v>
+        <v>-0.31241</v>
       </c>
     </row>
     <row r="25">
@@ -1015,13 +1015,13 @@
         <v>7.81</v>
       </c>
       <c r="D25" t="n">
-        <v>10.87</v>
+        <v>10.94</v>
       </c>
       <c r="E25" t="n">
-        <v>39.18</v>
+        <v>40.08</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04366</v>
+        <v>0.10807</v>
       </c>
     </row>
     <row r="26">
@@ -1039,19 +1039,19 @@
         <v>298.32</v>
       </c>
       <c r="D26" t="n">
-        <v>358.97</v>
+        <v>360.9</v>
       </c>
       <c r="E26" t="n">
-        <v>20.33</v>
+        <v>20.98</v>
       </c>
       <c r="F26" t="n">
-        <v>3.38165</v>
+        <v>2.4015</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>29.31</v>
+        <v>48.68</v>
       </c>
       <c r="D27" t="n">
-        <v>43.17</v>
+        <v>60.73</v>
       </c>
       <c r="E27" t="n">
-        <v>47.29</v>
+        <v>24.75</v>
       </c>
       <c r="F27" t="n">
-        <v>0.92178</v>
+        <v>0.43632</v>
       </c>
     </row>
     <row r="28">
@@ -1087,67 +1087,67 @@
         <v>41.55</v>
       </c>
       <c r="D28" t="n">
-        <v>62.21</v>
+        <v>65.78</v>
       </c>
       <c r="E28" t="n">
-        <v>49.72</v>
+        <v>58.32</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.39774</v>
+        <v>0.06870999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.28</v>
+        <v>11.03</v>
       </c>
       <c r="D29" t="n">
-        <v>28.1</v>
+        <v>12.73</v>
       </c>
       <c r="E29" t="n">
-        <v>11.16</v>
+        <v>15.37</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01151</v>
+        <v>0.00099</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.03</v>
+        <v>332.02</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72</v>
+        <v>375.93</v>
       </c>
       <c r="E30" t="n">
-        <v>15.32</v>
+        <v>13.23</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.09100999999999999</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>332.02</v>
+        <v>146.38</v>
       </c>
       <c r="D31" t="n">
-        <v>377.94</v>
+        <v>217.56</v>
       </c>
       <c r="E31" t="n">
-        <v>13.83</v>
+        <v>48.63</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.21821</v>
+        <v>0.80786</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1180,22 +1180,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>179.43</v>
+        <v>27.14</v>
       </c>
       <c r="D32" t="n">
-        <v>193.72</v>
+        <v>31.17</v>
       </c>
       <c r="E32" t="n">
-        <v>7.96</v>
+        <v>14.85</v>
       </c>
       <c r="F32" t="n">
-        <v>0.57955</v>
+        <v>-0.17201</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1204,40 +1204,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.14</v>
+        <v>179.43</v>
       </c>
       <c r="D33" t="n">
-        <v>31.52</v>
+        <v>192.07</v>
       </c>
       <c r="E33" t="n">
-        <v>16.14</v>
+        <v>7.04</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.35749</v>
+        <v>0.61816</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>146.38</v>
+        <v>205.77</v>
       </c>
       <c r="D34" t="n">
-        <v>218.28</v>
+        <v>249.79</v>
       </c>
       <c r="E34" t="n">
-        <v>49.12</v>
+        <v>21.39</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00649</v>
+        <v>3.40117</v>
       </c>
     </row>
     <row r="35">
@@ -1255,235 +1255,235 @@
         <v>25.99</v>
       </c>
       <c r="D35" t="n">
-        <v>38.71</v>
+        <v>38.69</v>
       </c>
       <c r="E35" t="n">
-        <v>48.94</v>
+        <v>48.85</v>
       </c>
       <c r="F35" t="n">
-        <v>0.54466</v>
+        <v>0.84088</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>205.77</v>
+        <v>440.76</v>
       </c>
       <c r="D36" t="n">
-        <v>249.09</v>
+        <v>633.47</v>
       </c>
       <c r="E36" t="n">
-        <v>21.05</v>
+        <v>43.72</v>
       </c>
       <c r="F36" t="n">
-        <v>2.72288</v>
+        <v>3.82931</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>440.76</v>
+        <v>103.45</v>
       </c>
       <c r="D37" t="n">
-        <v>637.16</v>
+        <v>148.95</v>
       </c>
       <c r="E37" t="n">
-        <v>44.56</v>
+        <v>43.98</v>
       </c>
       <c r="F37" t="n">
-        <v>1.42976</v>
+        <v>0.97007</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>103.45</v>
+        <v>198.14</v>
       </c>
       <c r="D38" t="n">
-        <v>149.67</v>
+        <v>261.4</v>
       </c>
       <c r="E38" t="n">
-        <v>44.68</v>
+        <v>31.93</v>
       </c>
       <c r="F38" t="n">
-        <v>1.89428</v>
+        <v>2.0117</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>67.59999999999999</v>
+        <v>35.49</v>
       </c>
       <c r="D39" t="n">
-        <v>80.31999999999999</v>
+        <v>41.88</v>
       </c>
       <c r="E39" t="n">
-        <v>18.82</v>
+        <v>18.01</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.45827</v>
+        <v>0.08749</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>198.14</v>
+        <v>41.44</v>
       </c>
       <c r="D40" t="n">
-        <v>261.67</v>
+        <v>45.47</v>
       </c>
       <c r="E40" t="n">
-        <v>32.06</v>
+        <v>9.73</v>
       </c>
       <c r="F40" t="n">
-        <v>2.64766</v>
+        <v>0.56647</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>41.44</v>
+        <v>510.39</v>
       </c>
       <c r="D41" t="n">
-        <v>45.25</v>
+        <v>646.76</v>
       </c>
       <c r="E41" t="n">
-        <v>9.19</v>
+        <v>26.72</v>
       </c>
       <c r="F41" t="n">
-        <v>0.51531</v>
+        <v>6.25783</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>510.39</v>
+        <v>5.04</v>
       </c>
       <c r="D42" t="n">
-        <v>652.39</v>
+        <v>5.86</v>
       </c>
       <c r="E42" t="n">
-        <v>27.82</v>
+        <v>16.17</v>
       </c>
       <c r="F42" t="n">
-        <v>4.4847</v>
+        <v>0.04414</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>PSNYW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5.04</v>
+        <v>2.2</v>
       </c>
       <c r="D43" t="n">
-        <v>5.95</v>
+        <v>4.43</v>
       </c>
       <c r="E43" t="n">
-        <v>18.06</v>
+        <v>101.36</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05247</v>
+        <v>-0.04196</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>176.25</v>
+        <v>40.48</v>
       </c>
       <c r="D44" t="n">
-        <v>249.59</v>
+        <v>45.93</v>
       </c>
       <c r="E44" t="n">
-        <v>41.61</v>
+        <v>13.46</v>
       </c>
       <c r="F44" t="n">
-        <v>0.95658</v>
+        <v>0.24173</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>20.87</v>
+        <v>162.11</v>
       </c>
       <c r="D45" t="n">
-        <v>23.47</v>
+        <v>177.03</v>
       </c>
       <c r="E45" t="n">
-        <v>12.46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.00191</v>
+        <v>0.47607</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1516,94 +1516,94 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>40.48</v>
+        <v>24.36</v>
       </c>
       <c r="D46" t="n">
-        <v>44.64</v>
+        <v>33.74</v>
       </c>
       <c r="E46" t="n">
-        <v>10.28</v>
+        <v>38.53</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1977</v>
+        <v>0.49148</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.36</v>
+        <v>14.49</v>
       </c>
       <c r="D47" t="n">
-        <v>33.27</v>
+        <v>19.53</v>
       </c>
       <c r="E47" t="n">
-        <v>36.58</v>
+        <v>34.78</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5132100000000001</v>
+        <v>0.5797099999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>31.45</v>
+        <v>40.25</v>
       </c>
       <c r="D48" t="n">
-        <v>36.65</v>
+        <v>51.29</v>
       </c>
       <c r="E48" t="n">
-        <v>16.53</v>
+        <v>27.44</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.014</v>
+        <v>0.92317</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>162.11</v>
+        <v>15.99</v>
       </c>
       <c r="D49" t="n">
-        <v>176.94</v>
+        <v>21.75</v>
       </c>
       <c r="E49" t="n">
-        <v>9.15</v>
+        <v>36.05</v>
       </c>
       <c r="F49" t="n">
-        <v>0.35777</v>
+        <v>0.65376</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15.99</v>
+        <v>36.15</v>
       </c>
       <c r="D50" t="n">
-        <v>21.15</v>
+        <v>46.9</v>
       </c>
       <c r="E50" t="n">
-        <v>32.27</v>
+        <v>29.72</v>
       </c>
       <c r="F50" t="n">
-        <v>0.63574</v>
+        <v>0.87806</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>14.49</v>
+        <v>104.89</v>
       </c>
       <c r="D51" t="n">
-        <v>19.07</v>
+        <v>121.96</v>
       </c>
       <c r="E51" t="n">
-        <v>31.61</v>
+        <v>16.27</v>
       </c>
       <c r="F51" t="n">
-        <v>0.58389</v>
+        <v>1.75968</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38.92</v>
+        <v>47.94</v>
       </c>
       <c r="D52" t="n">
-        <v>50.32</v>
+        <v>63.34</v>
       </c>
       <c r="E52" t="n">
-        <v>29.29</v>
+        <v>32.12</v>
       </c>
       <c r="F52" t="n">
-        <v>0.31609</v>
+        <v>0.80932</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,22 +1684,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>104.89</v>
+        <v>53.57</v>
       </c>
       <c r="D53" t="n">
-        <v>121.23</v>
+        <v>71.34</v>
       </c>
       <c r="E53" t="n">
-        <v>15.58</v>
+        <v>33.17</v>
       </c>
       <c r="F53" t="n">
-        <v>2.10701</v>
+        <v>0.8991</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>40.25</v>
+        <v>45.57</v>
       </c>
       <c r="D54" t="n">
-        <v>49.73</v>
+        <v>56.46</v>
       </c>
       <c r="E54" t="n">
-        <v>23.55</v>
+        <v>23.9</v>
       </c>
       <c r="F54" t="n">
-        <v>0.77667</v>
+        <v>0.47743</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>51.98</v>
+        <v>52.58</v>
       </c>
       <c r="D55" t="n">
-        <v>65.36</v>
+        <v>64.91</v>
       </c>
       <c r="E55" t="n">
-        <v>25.74</v>
+        <v>23.45</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.02228</v>
+        <v>-0.04387</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.26</v>
+        <v>110.99</v>
       </c>
       <c r="D56" t="n">
-        <v>19.97</v>
+        <v>134.88</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7</v>
+        <v>21.52</v>
       </c>
       <c r="F56" t="n">
-        <v>0.16925</v>
+        <v>0.1469</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>53.57</v>
+        <v>13.01</v>
       </c>
       <c r="D57" t="n">
-        <v>68.72</v>
+        <v>17.61</v>
       </c>
       <c r="E57" t="n">
-        <v>28.28</v>
+        <v>35.36</v>
       </c>
       <c r="F57" t="n">
-        <v>0.74953</v>
+        <v>0.38882</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>45.57</v>
+        <v>171.96</v>
       </c>
       <c r="D58" t="n">
-        <v>55.4</v>
+        <v>212.71</v>
       </c>
       <c r="E58" t="n">
-        <v>21.57</v>
+        <v>23.7</v>
       </c>
       <c r="F58" t="n">
-        <v>0.48559</v>
+        <v>2.04339</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13.01</v>
+        <v>38.92</v>
       </c>
       <c r="D59" t="n">
-        <v>17.53</v>
+        <v>51.31</v>
       </c>
       <c r="E59" t="n">
-        <v>34.74</v>
+        <v>31.85</v>
       </c>
       <c r="F59" t="n">
-        <v>0.37919</v>
+        <v>0.28265</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1852,22 +1852,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>110.99</v>
+        <v>17.93</v>
       </c>
       <c r="D60" t="n">
-        <v>131.83</v>
+        <v>24.39</v>
       </c>
       <c r="E60" t="n">
-        <v>18.78</v>
+        <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.18184</v>
+        <v>0.33403</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>17.93</v>
+        <v>74.8</v>
       </c>
       <c r="D61" t="n">
-        <v>23.76</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>32.52</v>
+        <v>24.46</v>
       </c>
       <c r="F61" t="n">
-        <v>0.28866</v>
+        <v>1.06908</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>171.96</v>
+        <v>165.69</v>
       </c>
       <c r="D62" t="n">
-        <v>205.72</v>
+        <v>216.63</v>
       </c>
       <c r="E62" t="n">
-        <v>19.63</v>
+        <v>30.74</v>
       </c>
       <c r="F62" t="n">
-        <v>1.19691</v>
+        <v>3.11009</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>36.15</v>
+        <v>17.26</v>
       </c>
       <c r="D63" t="n">
-        <v>45.93</v>
+        <v>19.88</v>
       </c>
       <c r="E63" t="n">
-        <v>27.05</v>
+        <v>15.18</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8426</v>
+        <v>0.16646</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>47.94</v>
+        <v>41.99</v>
       </c>
       <c r="D64" t="n">
-        <v>61.78</v>
+        <v>51.44</v>
       </c>
       <c r="E64" t="n">
-        <v>28.87</v>
+        <v>22.49</v>
       </c>
       <c r="F64" t="n">
-        <v>0.67977</v>
+        <v>0.50581</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>74.8</v>
+        <v>51.98</v>
       </c>
       <c r="D65" t="n">
-        <v>91.14</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>21.84</v>
+        <v>28.33</v>
       </c>
       <c r="F65" t="n">
-        <v>1.02845</v>
+        <v>0.20223</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>165.69</v>
+        <v>103.22</v>
       </c>
       <c r="D66" t="n">
-        <v>212.17</v>
+        <v>140.59</v>
       </c>
       <c r="E66" t="n">
-        <v>28.05</v>
+        <v>36.2</v>
       </c>
       <c r="F66" t="n">
-        <v>3.14062</v>
+        <v>2.22322</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,22 +2020,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>103.22</v>
+        <v>20.48</v>
       </c>
       <c r="D67" t="n">
-        <v>136.67</v>
+        <v>26.74</v>
       </c>
       <c r="E67" t="n">
-        <v>32.41</v>
+        <v>30.54</v>
       </c>
       <c r="F67" t="n">
-        <v>2.02987</v>
+        <v>0.32489</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2044,64 +2044,64 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.99</v>
+        <v>31.87</v>
       </c>
       <c r="D68" t="n">
-        <v>51.29</v>
+        <v>47.13</v>
       </c>
       <c r="E68" t="n">
-        <v>22.15</v>
+        <v>47.88</v>
       </c>
       <c r="F68" t="n">
-        <v>0.38063</v>
+        <v>1.03124</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>20.48</v>
+        <v>62.05</v>
       </c>
       <c r="D69" t="n">
-        <v>26.51</v>
+        <v>81.14</v>
       </c>
       <c r="E69" t="n">
-        <v>29.44</v>
+        <v>30.77</v>
       </c>
       <c r="F69" t="n">
-        <v>0.19225</v>
+        <v>-0.28176</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>31.87</v>
+        <v>13.43</v>
       </c>
       <c r="D70" t="n">
-        <v>45.03</v>
+        <v>15.07</v>
       </c>
       <c r="E70" t="n">
-        <v>41.29</v>
+        <v>12.21</v>
       </c>
       <c r="F70" t="n">
-        <v>0.89874</v>
+        <v>0.08663</v>
       </c>
     </row>
     <row r="71">
@@ -2119,19 +2119,19 @@
         <v>124.44</v>
       </c>
       <c r="D71" t="n">
-        <v>195</v>
+        <v>197.12</v>
       </c>
       <c r="E71" t="n">
-        <v>56.7</v>
+        <v>58.41</v>
       </c>
       <c r="F71" t="n">
-        <v>0.72958</v>
+        <v>2.69104</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>55.53</v>
+        <v>167.73</v>
       </c>
       <c r="D72" t="n">
-        <v>60.91</v>
+        <v>181.48</v>
       </c>
       <c r="E72" t="n">
-        <v>9.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>0.22128</v>
+        <v>-0.13029</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,22 +2164,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>62.05</v>
+        <v>38.73</v>
       </c>
       <c r="D73" t="n">
-        <v>81.22</v>
+        <v>64.36</v>
       </c>
       <c r="E73" t="n">
-        <v>30.89</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.5008899999999999</v>
+        <v>0.48836</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2188,22 +2188,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13.31</v>
+        <v>55.53</v>
       </c>
       <c r="D74" t="n">
-        <v>25.76</v>
+        <v>61.72</v>
       </c>
       <c r="E74" t="n">
-        <v>93.54000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F74" t="n">
-        <v>0.71191</v>
+        <v>0.70259</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2212,70 +2212,70 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13.43</v>
+        <v>13.31</v>
       </c>
       <c r="D75" t="n">
-        <v>15.26</v>
+        <v>24.33</v>
       </c>
       <c r="E75" t="n">
-        <v>13.63</v>
+        <v>82.83</v>
       </c>
       <c r="F75" t="n">
-        <v>0.08839</v>
+        <v>0.65601</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>38.73</v>
+        <v>218.58</v>
       </c>
       <c r="D76" t="n">
-        <v>64.09999999999999</v>
+        <v>277.11</v>
       </c>
       <c r="E76" t="n">
-        <v>65.5</v>
+        <v>26.78</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.10866</v>
+        <v>0.43734</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>167.73</v>
+        <v>136.06</v>
       </c>
       <c r="D77" t="n">
-        <v>182.9</v>
+        <v>169.4</v>
       </c>
       <c r="E77" t="n">
-        <v>9.039999999999999</v>
+        <v>24.5</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.58001</v>
+        <v>1.99197</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2284,112 +2284,112 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>218.58</v>
+        <v>7.67</v>
       </c>
       <c r="D78" t="n">
-        <v>280.46</v>
+        <v>9.25</v>
       </c>
       <c r="E78" t="n">
-        <v>28.31</v>
+        <v>20.6</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2297</v>
+        <v>0.15833</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>122.91</v>
+        <v>82.31</v>
       </c>
       <c r="D79" t="n">
-        <v>157.75</v>
+        <v>131.9</v>
       </c>
       <c r="E79" t="n">
-        <v>28.35</v>
+        <v>60.25</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.37771</v>
+        <v>3.05027</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7.67</v>
+        <v>56.4</v>
       </c>
       <c r="D80" t="n">
-        <v>9.199999999999999</v>
+        <v>79.39</v>
       </c>
       <c r="E80" t="n">
-        <v>19.95</v>
+        <v>40.75</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1771</v>
+        <v>1.99488</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>135.44</v>
+        <v>76.53</v>
       </c>
       <c r="D81" t="n">
-        <v>174.39</v>
+        <v>98.67</v>
       </c>
       <c r="E81" t="n">
-        <v>28.76</v>
+        <v>28.93</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.62645</v>
+        <v>1.60651</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>136.06</v>
+        <v>31.03</v>
       </c>
       <c r="D82" t="n">
-        <v>165.08</v>
+        <v>45.7</v>
       </c>
       <c r="E82" t="n">
-        <v>21.33</v>
+        <v>47.28</v>
       </c>
       <c r="F82" t="n">
-        <v>1.65744</v>
+        <v>0.9371699999999999</v>
       </c>
     </row>
     <row r="83">
@@ -2407,19 +2407,19 @@
         <v>18.94</v>
       </c>
       <c r="D83" t="n">
-        <v>23.74</v>
+        <v>23.86</v>
       </c>
       <c r="E83" t="n">
-        <v>25.34</v>
+        <v>25.98</v>
       </c>
       <c r="F83" t="n">
-        <v>0.19609</v>
+        <v>0.14599</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2428,118 +2428,118 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>31.03</v>
+        <v>39.54</v>
       </c>
       <c r="D84" t="n">
-        <v>44.54</v>
+        <v>50.34</v>
       </c>
       <c r="E84" t="n">
-        <v>43.54</v>
+        <v>27.31</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9863499999999999</v>
+        <v>0.13987</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>56.4</v>
+        <v>136.68</v>
       </c>
       <c r="D85" t="n">
-        <v>80.81</v>
+        <v>154.34</v>
       </c>
       <c r="E85" t="n">
-        <v>43.28</v>
+        <v>12.92</v>
       </c>
       <c r="F85" t="n">
-        <v>1.6696</v>
+        <v>-0.98185</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>82.31</v>
+        <v>352.83</v>
       </c>
       <c r="D86" t="n">
-        <v>136.94</v>
+        <v>500.03</v>
       </c>
       <c r="E86" t="n">
-        <v>66.37</v>
+        <v>41.72</v>
       </c>
       <c r="F86" t="n">
-        <v>3.45518</v>
+        <v>2.6957</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>39.54</v>
+        <v>44.39</v>
       </c>
       <c r="D87" t="n">
-        <v>51.41</v>
+        <v>60.25</v>
       </c>
       <c r="E87" t="n">
-        <v>30.02</v>
+        <v>35.73</v>
       </c>
       <c r="F87" t="n">
-        <v>0.11249</v>
+        <v>0.24638</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>76.53</v>
+        <v>42.46</v>
       </c>
       <c r="D88" t="n">
-        <v>96.45</v>
+        <v>73.62</v>
       </c>
       <c r="E88" t="n">
-        <v>26.03</v>
+        <v>73.39</v>
       </c>
       <c r="F88" t="n">
-        <v>1.45245</v>
+        <v>2.0488</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>107.27</v>
+        <v>59.71</v>
       </c>
       <c r="D89" t="n">
-        <v>173.31</v>
+        <v>80.12</v>
       </c>
       <c r="E89" t="n">
-        <v>61.56</v>
+        <v>34.19</v>
       </c>
       <c r="F89" t="n">
-        <v>-1.05801</v>
+        <v>1.29479</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2572,22 +2572,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>59.71</v>
+        <v>170.28</v>
       </c>
       <c r="D90" t="n">
-        <v>79.11</v>
+        <v>251.84</v>
       </c>
       <c r="E90" t="n">
-        <v>32.49</v>
+        <v>47.9</v>
       </c>
       <c r="F90" t="n">
-        <v>0.59687</v>
+        <v>-0.4332</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EDU</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2596,22 +2596,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>44.44</v>
+        <v>166.5</v>
       </c>
       <c r="D91" t="n">
-        <v>56.82</v>
+        <v>195.41</v>
       </c>
       <c r="E91" t="n">
-        <v>27.86</v>
+        <v>17.36</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.38143</v>
+        <v>1.02847</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2620,22 +2620,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>255.07</v>
+        <v>49.87</v>
       </c>
       <c r="D92" t="n">
-        <v>339.15</v>
+        <v>63.51</v>
       </c>
       <c r="E92" t="n">
-        <v>32.96</v>
+        <v>27.36</v>
       </c>
       <c r="F92" t="n">
-        <v>-6.00233</v>
+        <v>0.53445</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2644,22 +2644,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>19.32</v>
+        <v>142.52</v>
       </c>
       <c r="D93" t="n">
-        <v>24.47</v>
+        <v>180.09</v>
       </c>
       <c r="E93" t="n">
-        <v>26.66</v>
+        <v>26.36</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.0342</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2668,304 +2668,304 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>166.5</v>
+        <v>107.27</v>
       </c>
       <c r="D94" t="n">
-        <v>197.56</v>
+        <v>173.36</v>
       </c>
       <c r="E94" t="n">
-        <v>18.65</v>
+        <v>61.61</v>
       </c>
       <c r="F94" t="n">
-        <v>0.66935</v>
+        <v>-0.59248</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>42.46</v>
+        <v>10.51</v>
       </c>
       <c r="D95" t="n">
-        <v>69.76000000000001</v>
+        <v>15.23</v>
       </c>
       <c r="E95" t="n">
-        <v>64.3</v>
+        <v>44.86</v>
       </c>
       <c r="F95" t="n">
-        <v>1.2992</v>
+        <v>0.3598</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>170.28</v>
+        <v>60.37</v>
       </c>
       <c r="D96" t="n">
-        <v>250.61</v>
+        <v>78.7</v>
       </c>
       <c r="E96" t="n">
-        <v>47.18</v>
+        <v>30.36</v>
       </c>
       <c r="F96" t="n">
-        <v>-2.75775</v>
+        <v>0.99455</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>142.52</v>
+        <v>36.09</v>
       </c>
       <c r="D97" t="n">
-        <v>191.45</v>
+        <v>38.88</v>
       </c>
       <c r="E97" t="n">
-        <v>34.33</v>
+        <v>7.72</v>
       </c>
       <c r="F97" t="n">
-        <v>1.43195</v>
+        <v>0.05401</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>352.83</v>
+        <v>62.12</v>
       </c>
       <c r="D98" t="n">
-        <v>505.41</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>43.24</v>
+        <v>28.4</v>
       </c>
       <c r="F98" t="n">
-        <v>2.09735</v>
+        <v>0.9172400000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>136.68</v>
+        <v>102.17</v>
       </c>
       <c r="D99" t="n">
-        <v>153.4</v>
+        <v>134.93</v>
       </c>
       <c r="E99" t="n">
-        <v>12.23</v>
+        <v>32.06</v>
       </c>
       <c r="F99" t="n">
-        <v>-2.51046</v>
+        <v>1.38005</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>49.87</v>
+        <v>247.22</v>
       </c>
       <c r="D100" t="n">
-        <v>63.17</v>
+        <v>297.56</v>
       </c>
       <c r="E100" t="n">
-        <v>26.67</v>
+        <v>20.36</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2007</v>
+        <v>2.4973</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>44.39</v>
+        <v>48.79</v>
       </c>
       <c r="D101" t="n">
-        <v>61.14</v>
+        <v>67.77</v>
       </c>
       <c r="E101" t="n">
-        <v>37.73</v>
+        <v>38.9</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.05927</v>
+        <v>0.35802</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10.51</v>
+        <v>275.27</v>
       </c>
       <c r="D102" t="n">
-        <v>15.27</v>
+        <v>354.76</v>
       </c>
       <c r="E102" t="n">
-        <v>45.29</v>
+        <v>28.88</v>
       </c>
       <c r="F102" t="n">
-        <v>0.40451</v>
+        <v>-1.33658</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>62.12</v>
+        <v>150.12</v>
       </c>
       <c r="D103" t="n">
-        <v>79.13</v>
+        <v>261.45</v>
       </c>
       <c r="E103" t="n">
-        <v>27.38</v>
+        <v>74.16</v>
       </c>
       <c r="F103" t="n">
-        <v>0.8058999999999999</v>
+        <v>7.51054</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>60.37</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>77</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>27.55</v>
+        <v>13.68</v>
       </c>
       <c r="F104" t="n">
-        <v>1.31187</v>
+        <v>0.25637</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>102.17</v>
+        <v>140.71</v>
       </c>
       <c r="D105" t="n">
-        <v>131.24</v>
+        <v>185.79</v>
       </c>
       <c r="E105" t="n">
-        <v>28.45</v>
+        <v>32.04</v>
       </c>
       <c r="F105" t="n">
-        <v>1.86006</v>
+        <v>-0.66379</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>48.79</v>
+        <v>125.73</v>
       </c>
       <c r="D106" t="n">
-        <v>68.53</v>
+        <v>202.56</v>
       </c>
       <c r="E106" t="n">
-        <v>40.46</v>
+        <v>61.11</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.01588</v>
+        <v>1.499</v>
       </c>
     </row>
     <row r="107">
@@ -2983,19 +2983,19 @@
         <v>76.04000000000001</v>
       </c>
       <c r="D107" t="n">
-        <v>123.61</v>
+        <v>125.49</v>
       </c>
       <c r="E107" t="n">
-        <v>62.56</v>
+        <v>65.03</v>
       </c>
       <c r="F107" t="n">
-        <v>2.41344</v>
+        <v>3.21311</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3004,22 +3004,22 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>30.83</v>
+        <v>123.42</v>
       </c>
       <c r="D108" t="n">
-        <v>35.72</v>
+        <v>165.82</v>
       </c>
       <c r="E108" t="n">
-        <v>15.86</v>
+        <v>34.36</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.35242</v>
+        <v>0.10343</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3028,22 +3028,22 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>83.81999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="D109" t="n">
-        <v>95.31</v>
+        <v>104.01</v>
       </c>
       <c r="E109" t="n">
-        <v>13.71</v>
+        <v>35.87</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.43033</v>
+        <v>-0.76313</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3052,3022 +3052,3022 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>275.27</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D110" t="n">
-        <v>359.54</v>
+        <v>104.39</v>
       </c>
       <c r="E110" t="n">
-        <v>30.61</v>
+        <v>39.21</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.74832</v>
+        <v>1.39645</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>125.73</v>
+        <v>61.28</v>
       </c>
       <c r="D111" t="n">
-        <v>197.07</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>56.74</v>
+        <v>19.24</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.80321</v>
+        <v>-0.48667</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>150.12</v>
+        <v>141.17</v>
       </c>
       <c r="D112" t="n">
-        <v>259.43</v>
+        <v>176.57</v>
       </c>
       <c r="E112" t="n">
-        <v>72.81999999999999</v>
+        <v>25.07</v>
       </c>
       <c r="F112" t="n">
-        <v>6.48113</v>
+        <v>1.11401</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>74.98999999999999</v>
+        <v>33.22</v>
       </c>
       <c r="D113" t="n">
-        <v>104.47</v>
+        <v>39.15</v>
       </c>
       <c r="E113" t="n">
-        <v>39.31</v>
+        <v>17.85</v>
       </c>
       <c r="F113" t="n">
-        <v>0.40712</v>
+        <v>0.15577</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>140.71</v>
+        <v>32.47</v>
       </c>
       <c r="D114" t="n">
-        <v>182.91</v>
+        <v>39.04</v>
       </c>
       <c r="E114" t="n">
-        <v>29.99</v>
+        <v>20.23</v>
       </c>
       <c r="F114" t="n">
-        <v>-1.36471</v>
+        <v>0.39367</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>76.55</v>
+        <v>450.75</v>
       </c>
       <c r="D115" t="n">
-        <v>105.82</v>
+        <v>539.5</v>
       </c>
       <c r="E115" t="n">
-        <v>38.24</v>
+        <v>19.69</v>
       </c>
       <c r="F115" t="n">
-        <v>-1.58346</v>
+        <v>1.96392</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>123.42</v>
+        <v>48.87</v>
       </c>
       <c r="D116" t="n">
-        <v>164.55</v>
+        <v>59.26</v>
       </c>
       <c r="E116" t="n">
-        <v>33.33</v>
+        <v>21.25</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.65884</v>
+        <v>-0.192</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>141.17</v>
+        <v>14.94</v>
       </c>
       <c r="D117" t="n">
-        <v>173.25</v>
+        <v>19.56</v>
       </c>
       <c r="E117" t="n">
-        <v>22.72</v>
+        <v>30.92</v>
       </c>
       <c r="F117" t="n">
-        <v>1.14864</v>
+        <v>0.52103</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>61.28</v>
+        <v>19.82</v>
       </c>
       <c r="D118" t="n">
-        <v>72.91</v>
+        <v>25.15</v>
       </c>
       <c r="E118" t="n">
-        <v>18.98</v>
+        <v>26.87</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.98211</v>
+        <v>0.26096</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>48.87</v>
+        <v>53.82</v>
       </c>
       <c r="D119" t="n">
-        <v>58.74</v>
+        <v>74.44</v>
       </c>
       <c r="E119" t="n">
-        <v>20.2</v>
+        <v>38.31</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.40747</v>
+        <v>0.49656</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>450.75</v>
+        <v>16.44</v>
       </c>
       <c r="D120" t="n">
-        <v>548.65</v>
+        <v>33.38</v>
       </c>
       <c r="E120" t="n">
-        <v>21.72</v>
+        <v>103.04</v>
       </c>
       <c r="F120" t="n">
-        <v>2.41907</v>
+        <v>0.43174</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>32.47</v>
+        <v>2.86</v>
       </c>
       <c r="D121" t="n">
-        <v>38.43</v>
+        <v>3.17</v>
       </c>
       <c r="E121" t="n">
-        <v>18.36</v>
+        <v>11.01</v>
       </c>
       <c r="F121" t="n">
-        <v>0.22774</v>
+        <v>0.02634</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>147.13</v>
+        <v>121.48</v>
       </c>
       <c r="D122" t="n">
-        <v>174.93</v>
+        <v>145.67</v>
       </c>
       <c r="E122" t="n">
-        <v>18.89</v>
+        <v>19.91</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.59992</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>62.47</v>
+        <v>361.32</v>
       </c>
       <c r="D123" t="n">
-        <v>90.19</v>
+        <v>424.32</v>
       </c>
       <c r="E123" t="n">
-        <v>44.37</v>
+        <v>17.44</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.65359</v>
+        <v>4.24191</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>53.82</v>
+        <v>43.67</v>
       </c>
       <c r="D124" t="n">
-        <v>75</v>
+        <v>47.19</v>
       </c>
       <c r="E124" t="n">
-        <v>39.35</v>
+        <v>8.07</v>
       </c>
       <c r="F124" t="n">
-        <v>0.53725</v>
+        <v>0.05027</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>121.48</v>
+        <v>140.19</v>
       </c>
       <c r="D125" t="n">
-        <v>146.41</v>
+        <v>146.88</v>
       </c>
       <c r="E125" t="n">
-        <v>20.52</v>
+        <v>4.77</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04863</v>
+        <v>0.04815</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2.86</v>
+        <v>15.03</v>
       </c>
       <c r="D126" t="n">
-        <v>3.18</v>
+        <v>18.69</v>
       </c>
       <c r="E126" t="n">
-        <v>11.19</v>
+        <v>24.35</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02543</v>
+        <v>0.12664</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>19.82</v>
+        <v>73.75</v>
       </c>
       <c r="D127" t="n">
-        <v>25.05</v>
+        <v>94.17</v>
       </c>
       <c r="E127" t="n">
-        <v>26.39</v>
+        <v>27.69</v>
       </c>
       <c r="F127" t="n">
-        <v>0.40053</v>
+        <v>0.50174</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>14.94</v>
+        <v>275.99</v>
       </c>
       <c r="D128" t="n">
-        <v>19.59</v>
+        <v>321.39</v>
       </c>
       <c r="E128" t="n">
-        <v>31.16</v>
+        <v>16.45</v>
       </c>
       <c r="F128" t="n">
-        <v>0.52114</v>
+        <v>2.28704</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>16.44</v>
+        <v>182.82</v>
       </c>
       <c r="D129" t="n">
-        <v>33.97</v>
+        <v>233.65</v>
       </c>
       <c r="E129" t="n">
-        <v>106.63</v>
+        <v>27.81</v>
       </c>
       <c r="F129" t="n">
-        <v>0.60034</v>
+        <v>-0.90196</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>91.88</v>
+        <v>23.85</v>
       </c>
       <c r="D130" t="n">
-        <v>125.3</v>
+        <v>33.53</v>
       </c>
       <c r="E130" t="n">
-        <v>36.37</v>
+        <v>40.61</v>
       </c>
       <c r="F130" t="n">
-        <v>1.50067</v>
+        <v>-0.0459</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>361.32</v>
+        <v>36.25</v>
       </c>
       <c r="D131" t="n">
-        <v>425.49</v>
+        <v>41.44</v>
       </c>
       <c r="E131" t="n">
-        <v>17.76</v>
+        <v>14.33</v>
       </c>
       <c r="F131" t="n">
-        <v>4.42632</v>
+        <v>0.15122</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>205.81</v>
+        <v>9.85</v>
       </c>
       <c r="D132" t="n">
-        <v>264.92</v>
+        <v>14.21</v>
       </c>
       <c r="E132" t="n">
-        <v>28.72</v>
+        <v>44.26</v>
       </c>
       <c r="F132" t="n">
-        <v>1.32952</v>
+        <v>0.49308</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>28.18</v>
+        <v>121.13</v>
       </c>
       <c r="D133" t="n">
-        <v>37.03</v>
+        <v>138.41</v>
       </c>
       <c r="E133" t="n">
-        <v>31.41</v>
+        <v>14.27</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.01107</v>
+        <v>0.1891</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>43.67</v>
+        <v>33.54</v>
       </c>
       <c r="D134" t="n">
-        <v>47.34</v>
+        <v>42.26</v>
       </c>
       <c r="E134" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="F134" t="n">
-        <v>0.05503</v>
+        <v>0.14642</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>161.37</v>
+        <v>63.54</v>
       </c>
       <c r="D135" t="n">
-        <v>264.51</v>
+        <v>70.78</v>
       </c>
       <c r="E135" t="n">
-        <v>63.92</v>
+        <v>11.39</v>
       </c>
       <c r="F135" t="n">
-        <v>0.82511</v>
+        <v>0.32638</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>55.05</v>
+        <v>190.4</v>
       </c>
       <c r="D136" t="n">
-        <v>63.57</v>
+        <v>221.04</v>
       </c>
       <c r="E136" t="n">
-        <v>15.48</v>
+        <v>16.09</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.4736</v>
+        <v>0.56543</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>72.55</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="D137" t="n">
-        <v>76.29000000000001</v>
+        <v>108.32</v>
       </c>
       <c r="E137" t="n">
-        <v>5.16</v>
+        <v>26.91</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.36496</v>
+        <v>-0.34839</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>195.11</v>
+        <v>529.12</v>
       </c>
       <c r="D138" t="n">
-        <v>249.05</v>
+        <v>683.13</v>
       </c>
       <c r="E138" t="n">
-        <v>27.65</v>
+        <v>29.11</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4172</v>
+        <v>9.41741</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>15.03</v>
+        <v>57.4</v>
       </c>
       <c r="D139" t="n">
-        <v>18.6</v>
+        <v>104.2</v>
       </c>
       <c r="E139" t="n">
-        <v>23.75</v>
+        <v>81.53</v>
       </c>
       <c r="F139" t="n">
-        <v>0.08944000000000001</v>
+        <v>0.58114</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>140.19</v>
+        <v>73.42</v>
       </c>
       <c r="D140" t="n">
-        <v>146.13</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E140" t="n">
-        <v>4.24</v>
+        <v>20.68</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.3931</v>
+        <v>0.59771</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>207.24</v>
+        <v>161.91</v>
       </c>
       <c r="D141" t="n">
-        <v>253.88</v>
+        <v>207.75</v>
       </c>
       <c r="E141" t="n">
-        <v>22.51</v>
+        <v>28.31</v>
       </c>
       <c r="F141" t="n">
-        <v>-2.67569</v>
+        <v>-1.68085</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>277.69</v>
+        <v>43.3</v>
       </c>
       <c r="D142" t="n">
-        <v>330.62</v>
+        <v>72.28</v>
       </c>
       <c r="E142" t="n">
-        <v>19.06</v>
+        <v>66.92</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.14398</v>
+        <v>0.00238</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>275.99</v>
+        <v>92.38</v>
       </c>
       <c r="D143" t="n">
-        <v>322.99</v>
+        <v>101.15</v>
       </c>
       <c r="E143" t="n">
-        <v>17.03</v>
+        <v>9.5</v>
       </c>
       <c r="F143" t="n">
-        <v>1.92883</v>
+        <v>0.10255</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>73.75</v>
+        <v>186.61</v>
       </c>
       <c r="D144" t="n">
-        <v>93.8</v>
+        <v>246.51</v>
       </c>
       <c r="E144" t="n">
-        <v>27.19</v>
+        <v>32.1</v>
       </c>
       <c r="F144" t="n">
-        <v>0.31456</v>
+        <v>0.13859</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>36.25</v>
+        <v>438.34</v>
       </c>
       <c r="D145" t="n">
-        <v>41.61</v>
+        <v>633.62</v>
       </c>
       <c r="E145" t="n">
-        <v>14.79</v>
+        <v>44.55</v>
       </c>
       <c r="F145" t="n">
-        <v>0.22556</v>
+        <v>3.11233</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>121.13</v>
+        <v>5563.62</v>
       </c>
       <c r="D146" t="n">
-        <v>138.92</v>
+        <v>6280.62</v>
       </c>
       <c r="E146" t="n">
-        <v>14.69</v>
+        <v>12.89</v>
       </c>
       <c r="F146" t="n">
-        <v>0.41111</v>
+        <v>-31.16585</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>9.85</v>
+        <v>63.16</v>
       </c>
       <c r="D147" t="n">
-        <v>13.75</v>
+        <v>100.17</v>
       </c>
       <c r="E147" t="n">
-        <v>39.59</v>
+        <v>58.6</v>
       </c>
       <c r="F147" t="n">
-        <v>0.51236</v>
+        <v>1.30697</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>309.78</v>
+        <v>102.87</v>
       </c>
       <c r="D148" t="n">
-        <v>341.85</v>
+        <v>175.46</v>
       </c>
       <c r="E148" t="n">
-        <v>10.35</v>
+        <v>70.56</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.13236</v>
+        <v>-0.29873</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>132.79</v>
+        <v>26.18</v>
       </c>
       <c r="D149" t="n">
-        <v>163.39</v>
+        <v>36.78</v>
       </c>
       <c r="E149" t="n">
-        <v>23.04</v>
+        <v>40.49</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.12699</v>
+        <v>0.2431</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>33.54</v>
+        <v>163.43</v>
       </c>
       <c r="D150" t="n">
-        <v>42.61</v>
+        <v>199.15</v>
       </c>
       <c r="E150" t="n">
-        <v>27.04</v>
+        <v>21.85</v>
       </c>
       <c r="F150" t="n">
-        <v>0.13446</v>
+        <v>1.52644</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>63.54</v>
+        <v>55.52</v>
       </c>
       <c r="D151" t="n">
-        <v>70.87</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="E151" t="n">
-        <v>11.54</v>
+        <v>68.34</v>
       </c>
       <c r="F151" t="n">
-        <v>0.26916</v>
+        <v>1.98214</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>190.4</v>
+        <v>99.3</v>
       </c>
       <c r="D152" t="n">
-        <v>221.02</v>
+        <v>152.34</v>
       </c>
       <c r="E152" t="n">
-        <v>16.08</v>
+        <v>53.41</v>
       </c>
       <c r="F152" t="n">
-        <v>0.04179</v>
+        <v>2.01537</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>250.75</v>
+        <v>725.17</v>
       </c>
       <c r="D153" t="n">
-        <v>340.38</v>
+        <v>895.48</v>
       </c>
       <c r="E153" t="n">
-        <v>35.74</v>
+        <v>23.49</v>
       </c>
       <c r="F153" t="n">
-        <v>3.87926</v>
+        <v>2.09128</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>529.12</v>
+        <v>197.73</v>
       </c>
       <c r="D154" t="n">
-        <v>681.46</v>
+        <v>225.51</v>
       </c>
       <c r="E154" t="n">
-        <v>28.79</v>
+        <v>14.05</v>
       </c>
       <c r="F154" t="n">
-        <v>9.785550000000001</v>
+        <v>1.17553</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SGI</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>61.49</v>
+        <v>79.58</v>
       </c>
       <c r="D155" t="n">
-        <v>68.12</v>
+        <v>97.92</v>
       </c>
       <c r="E155" t="n">
-        <v>10.78</v>
+        <v>23.05</v>
       </c>
       <c r="F155" t="n">
-        <v>0.25125</v>
+        <v>-0.87924</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>QGEN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>57.4</v>
+        <v>32.63</v>
       </c>
       <c r="D156" t="n">
-        <v>104.79</v>
+        <v>42.99</v>
       </c>
       <c r="E156" t="n">
-        <v>82.56</v>
+        <v>31.75</v>
       </c>
       <c r="F156" t="n">
-        <v>0.21284</v>
+        <v>-0.21737</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BMRN</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>49.67</v>
+        <v>417.83</v>
       </c>
       <c r="D157" t="n">
-        <v>66.41</v>
+        <v>559.46</v>
       </c>
       <c r="E157" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="F157" t="n">
-        <v>0.03841</v>
+        <v>3.86931</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>186.61</v>
+        <v>383.99</v>
       </c>
       <c r="D158" t="n">
-        <v>237.89</v>
+        <v>472.52</v>
       </c>
       <c r="E158" t="n">
-        <v>27.48</v>
+        <v>23.05</v>
       </c>
       <c r="F158" t="n">
-        <v>-1.00997</v>
+        <v>-0.18266</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>63.16</v>
+        <v>255.54</v>
       </c>
       <c r="D159" t="n">
-        <v>101.84</v>
+        <v>365.08</v>
       </c>
       <c r="E159" t="n">
-        <v>61.24</v>
+        <v>42.87</v>
       </c>
       <c r="F159" t="n">
-        <v>1.43086</v>
+        <v>3.26755</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5563.62</v>
+        <v>12.64</v>
       </c>
       <c r="D160" t="n">
-        <v>6299.56</v>
+        <v>18.32</v>
       </c>
       <c r="E160" t="n">
-        <v>13.23</v>
+        <v>44.9</v>
       </c>
       <c r="F160" t="n">
-        <v>-44.26965</v>
+        <v>0.26593</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>43.3</v>
+        <v>699965</v>
       </c>
       <c r="D161" t="n">
-        <v>72.27</v>
+        <v>772763.12</v>
       </c>
       <c r="E161" t="n">
-        <v>66.91</v>
+        <v>10.4</v>
       </c>
       <c r="F161" t="n">
-        <v>-0</v>
+        <v>3580.3712</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>73.42</v>
+        <v>139.71</v>
       </c>
       <c r="D162" t="n">
-        <v>88.70999999999999</v>
+        <v>193.18</v>
       </c>
       <c r="E162" t="n">
-        <v>20.83</v>
+        <v>38.27</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7728699999999999</v>
+        <v>2.02385</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>92.38</v>
+        <v>45.37</v>
       </c>
       <c r="D163" t="n">
-        <v>100.65</v>
+        <v>142.61</v>
       </c>
       <c r="E163" t="n">
-        <v>8.949999999999999</v>
+        <v>214.33</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.07876</v>
+        <v>5.40295</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>438.34</v>
+        <v>112.47</v>
       </c>
       <c r="D164" t="n">
-        <v>613.62</v>
+        <v>137.75</v>
       </c>
       <c r="E164" t="n">
-        <v>39.99</v>
+        <v>22.48</v>
       </c>
       <c r="F164" t="n">
-        <v>0.49995</v>
+        <v>0.53672</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>26.18</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D165" t="n">
-        <v>36.71</v>
+        <v>138.32</v>
       </c>
       <c r="E165" t="n">
-        <v>40.22</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="F165" t="n">
-        <v>0.135</v>
+        <v>1.45607</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>163.43</v>
+        <v>156.66</v>
       </c>
       <c r="D166" t="n">
-        <v>200.67</v>
+        <v>271.1</v>
       </c>
       <c r="E166" t="n">
-        <v>22.79</v>
+        <v>73.05</v>
       </c>
       <c r="F166" t="n">
-        <v>0.62133</v>
+        <v>3.19301</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>156.84</v>
+        <v>40.41</v>
       </c>
       <c r="D167" t="n">
-        <v>187.03</v>
+        <v>52.52</v>
       </c>
       <c r="E167" t="n">
-        <v>19.25</v>
+        <v>29.97</v>
       </c>
       <c r="F167" t="n">
-        <v>-2.68499</v>
+        <v>0.02767</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>101.75</v>
+        <v>197.38</v>
       </c>
       <c r="D168" t="n">
-        <v>129.17</v>
+        <v>263.37</v>
       </c>
       <c r="E168" t="n">
-        <v>26.95</v>
+        <v>33.43</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.25082</v>
+        <v>1.13979</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>55.52</v>
+        <v>393.42</v>
       </c>
       <c r="D169" t="n">
-        <v>94.83</v>
+        <v>618.02</v>
       </c>
       <c r="E169" t="n">
-        <v>70.8</v>
+        <v>57.09</v>
       </c>
       <c r="F169" t="n">
-        <v>1.61921</v>
+        <v>1.16794</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>99.3</v>
+        <v>465.4</v>
       </c>
       <c r="D170" t="n">
-        <v>151.7</v>
+        <v>514.51</v>
       </c>
       <c r="E170" t="n">
-        <v>52.77</v>
+        <v>10.55</v>
       </c>
       <c r="F170" t="n">
-        <v>1.17857</v>
+        <v>2.25176</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>725.17</v>
+        <v>153.25</v>
       </c>
       <c r="D171" t="n">
-        <v>910.95</v>
+        <v>194.32</v>
       </c>
       <c r="E171" t="n">
-        <v>25.62</v>
+        <v>26.8</v>
       </c>
       <c r="F171" t="n">
-        <v>1.91142</v>
+        <v>1.59503</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>197.73</v>
+        <v>20.96</v>
       </c>
       <c r="D172" t="n">
-        <v>225.85</v>
+        <v>25.72</v>
       </c>
       <c r="E172" t="n">
-        <v>14.22</v>
+        <v>22.71</v>
       </c>
       <c r="F172" t="n">
-        <v>0.9798</v>
+        <v>0.24413</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>68.98999999999999</v>
+        <v>155.75</v>
       </c>
       <c r="D173" t="n">
-        <v>88.93000000000001</v>
+        <v>264</v>
       </c>
       <c r="E173" t="n">
-        <v>28.9</v>
+        <v>69.5</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.34243</v>
+        <v>5.50048</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>255.54</v>
+        <v>40.59</v>
       </c>
       <c r="D174" t="n">
-        <v>365.08</v>
+        <v>57.65</v>
       </c>
       <c r="E174" t="n">
-        <v>42.87</v>
+        <v>42.02</v>
       </c>
       <c r="F174" t="n">
-        <v>3.26755</v>
+        <v>1.56019</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>383.99</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="D175" t="n">
-        <v>474.13</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="E175" t="n">
-        <v>23.47</v>
+        <v>15.64</v>
       </c>
       <c r="F175" t="n">
-        <v>-1.53084</v>
+        <v>0.64538</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>12.64</v>
+        <v>128.43</v>
       </c>
       <c r="D176" t="n">
-        <v>17.74</v>
+        <v>153.21</v>
       </c>
       <c r="E176" t="n">
-        <v>40.35</v>
+        <v>19.29</v>
       </c>
       <c r="F176" t="n">
-        <v>0.24281</v>
+        <v>1.19009</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>417.83</v>
+        <v>213.69</v>
       </c>
       <c r="D177" t="n">
-        <v>556.3099999999999</v>
+        <v>408.39</v>
       </c>
       <c r="E177" t="n">
-        <v>33.14</v>
+        <v>91.11</v>
       </c>
       <c r="F177" t="n">
-        <v>0.43871</v>
+        <v>10.17924</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>32.32</v>
+        <v>223.65</v>
       </c>
       <c r="D178" t="n">
-        <v>37.72</v>
+        <v>391.67</v>
       </c>
       <c r="E178" t="n">
-        <v>16.71</v>
+        <v>75.13</v>
       </c>
       <c r="F178" t="n">
-        <v>0.15923</v>
+        <v>11.15527</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>252.74</v>
+        <v>18.71</v>
       </c>
       <c r="D179" t="n">
-        <v>326.23</v>
+        <v>21.38</v>
       </c>
       <c r="E179" t="n">
-        <v>29.08</v>
+        <v>14.24</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.21978</v>
+        <v>0.09515999999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>699965</v>
+        <v>66.95</v>
       </c>
       <c r="D180" t="n">
-        <v>771770</v>
+        <v>86.83</v>
       </c>
       <c r="E180" t="n">
-        <v>10.26</v>
+        <v>29.7</v>
       </c>
       <c r="F180" t="n">
-        <v>2523.34448</v>
+        <v>1.3896</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>139.71</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D181" t="n">
-        <v>193.61</v>
+        <v>175.15</v>
       </c>
       <c r="E181" t="n">
-        <v>38.58</v>
+        <v>122.84</v>
       </c>
       <c r="F181" t="n">
-        <v>1.72426</v>
+        <v>1.07576</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>45.37</v>
+        <v>34.41</v>
       </c>
       <c r="D182" t="n">
-        <v>146.69</v>
+        <v>68.81</v>
       </c>
       <c r="E182" t="n">
-        <v>223.32</v>
+        <v>99.97</v>
       </c>
       <c r="F182" t="n">
-        <v>5.23484</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>112.47</v>
+        <v>76.7</v>
       </c>
       <c r="D183" t="n">
-        <v>138.5</v>
+        <v>170.64</v>
       </c>
       <c r="E183" t="n">
-        <v>23.14</v>
+        <v>122.48</v>
       </c>
       <c r="F183" t="n">
-        <v>0.31006</v>
+        <v>1.88937</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>13.06</v>
+        <v>166.99</v>
       </c>
       <c r="D184" t="n">
-        <v>19.91</v>
+        <v>331.36</v>
       </c>
       <c r="E184" t="n">
-        <v>52.45</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.009140000000000001</v>
+        <v>9.837569999999999</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>82.26000000000001</v>
+        <v>17.89</v>
       </c>
       <c r="D185" t="n">
-        <v>128.49</v>
+        <v>31.22</v>
       </c>
       <c r="E185" t="n">
-        <v>56.2</v>
+        <v>74.48</v>
       </c>
       <c r="F185" t="n">
-        <v>0.08618000000000001</v>
+        <v>0.39284</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>156.66</v>
+        <v>188.79</v>
       </c>
       <c r="D186" t="n">
-        <v>265.67</v>
+        <v>278.2</v>
       </c>
       <c r="E186" t="n">
-        <v>69.58</v>
+        <v>47.36</v>
       </c>
       <c r="F186" t="n">
-        <v>2.0428</v>
+        <v>-0.83234</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>40.41</v>
+        <v>32.36</v>
       </c>
       <c r="D187" t="n">
-        <v>51.96</v>
+        <v>54.94</v>
       </c>
       <c r="E187" t="n">
-        <v>28.58</v>
+        <v>69.78</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.19889</v>
+        <v>0.74498</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>197.38</v>
+        <v>43.81</v>
       </c>
       <c r="D188" t="n">
-        <v>261.77</v>
+        <v>100.11</v>
       </c>
       <c r="E188" t="n">
-        <v>32.62</v>
+        <v>128.51</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.05181</v>
+        <v>0.69474</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>393.42</v>
+        <v>121.11</v>
       </c>
       <c r="D189" t="n">
-        <v>595.41</v>
+        <v>326.72</v>
       </c>
       <c r="E189" t="n">
-        <v>51.34</v>
+        <v>169.77</v>
       </c>
       <c r="F189" t="n">
-        <v>-2.04834</v>
+        <v>1.43337</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>74.63</v>
+        <v>83</v>
       </c>
       <c r="D190" t="n">
-        <v>89.34999999999999</v>
+        <v>146.04</v>
       </c>
       <c r="E190" t="n">
-        <v>19.72</v>
+        <v>75.95</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.05535</v>
+        <v>2.11232</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>465.4</v>
+        <v>118.05</v>
       </c>
       <c r="D191" t="n">
-        <v>514.95</v>
+        <v>193.13</v>
       </c>
       <c r="E191" t="n">
-        <v>10.65</v>
+        <v>63.6</v>
       </c>
       <c r="F191" t="n">
-        <v>1.66879</v>
+        <v>2.21219</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>56.06</v>
+        <v>105.37</v>
       </c>
       <c r="D192" t="n">
-        <v>62.39</v>
+        <v>230.98</v>
       </c>
       <c r="E192" t="n">
-        <v>11.29</v>
+        <v>119.21</v>
       </c>
       <c r="F192" t="n">
-        <v>0.03839</v>
+        <v>-1.17733</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>153.25</v>
+        <v>18.26</v>
       </c>
       <c r="D193" t="n">
-        <v>194.86</v>
+        <v>34.1</v>
       </c>
       <c r="E193" t="n">
-        <v>27.15</v>
+        <v>86.72</v>
       </c>
       <c r="F193" t="n">
-        <v>0.85662</v>
+        <v>1.20956</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>155.75</v>
+        <v>62.93</v>
       </c>
       <c r="D194" t="n">
-        <v>257.06</v>
+        <v>187.43</v>
       </c>
       <c r="E194" t="n">
-        <v>65.05</v>
+        <v>197.84</v>
       </c>
       <c r="F194" t="n">
-        <v>5.74053</v>
+        <v>7.0525</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>20.96</v>
+        <v>10.49</v>
       </c>
       <c r="D195" t="n">
-        <v>25.85</v>
+        <v>20.03</v>
       </c>
       <c r="E195" t="n">
-        <v>23.33</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F195" t="n">
-        <v>0.28351</v>
+        <v>0.09464</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>40.59</v>
+        <v>120.88</v>
       </c>
       <c r="D196" t="n">
-        <v>56.33</v>
+        <v>213.74</v>
       </c>
       <c r="E196" t="n">
-        <v>38.78</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="F196" t="n">
-        <v>1.40494</v>
+        <v>-0.009849999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>213.69</v>
+        <v>112.5</v>
       </c>
       <c r="D197" t="n">
-        <v>396.45</v>
+        <v>194.38</v>
       </c>
       <c r="E197" t="n">
-        <v>85.53</v>
+        <v>72.78</v>
       </c>
       <c r="F197" t="n">
-        <v>10.30916</v>
+        <v>-0.15956</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>83.51000000000001</v>
+        <v>57.15</v>
       </c>
       <c r="D198" t="n">
-        <v>96.97</v>
+        <v>192.91</v>
       </c>
       <c r="E198" t="n">
-        <v>16.12</v>
+        <v>237.55</v>
       </c>
       <c r="F198" t="n">
-        <v>0.63437</v>
+        <v>5.23377</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>223.65</v>
+        <v>117.65</v>
       </c>
       <c r="D199" t="n">
-        <v>382.95</v>
+        <v>240.17</v>
       </c>
       <c r="E199" t="n">
-        <v>71.23</v>
+        <v>104.14</v>
       </c>
       <c r="F199" t="n">
-        <v>12.04345</v>
+        <v>1.60426</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>128.43</v>
+        <v>151.43</v>
       </c>
       <c r="D200" t="n">
-        <v>148.54</v>
+        <v>271.73</v>
       </c>
       <c r="E200" t="n">
-        <v>15.66</v>
+        <v>79.44</v>
       </c>
       <c r="F200" t="n">
-        <v>0.66273</v>
+        <v>2.44869</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>18.71</v>
+        <v>25.85</v>
       </c>
       <c r="D201" t="n">
-        <v>21.49</v>
+        <v>42.87</v>
       </c>
       <c r="E201" t="n">
-        <v>14.86</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F201" t="n">
-        <v>0.13728</v>
+        <v>0.51722</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>66.95</v>
+        <v>95.67</v>
       </c>
       <c r="D202" t="n">
-        <v>86.44</v>
+        <v>191.38</v>
       </c>
       <c r="E202" t="n">
-        <v>29.11</v>
+        <v>100.04</v>
       </c>
       <c r="F202" t="n">
-        <v>1.50588</v>
+        <v>1.06529</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>126.32</v>
+        <v>56.43</v>
       </c>
       <c r="D203" t="n">
-        <v>157.22</v>
+        <v>110.65</v>
       </c>
       <c r="E203" t="n">
-        <v>24.46</v>
+        <v>96.08</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.32127</v>
+        <v>2.9648</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>118.05</v>
+        <v>23.49</v>
       </c>
       <c r="D204" t="n">
-        <v>191.73</v>
+        <v>32.24</v>
       </c>
       <c r="E204" t="n">
-        <v>62.41</v>
+        <v>37.23</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.40022</v>
+        <v>0.1772</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>17.89</v>
+        <v>23.63</v>
       </c>
       <c r="D205" t="n">
-        <v>31.41</v>
+        <v>25.45</v>
       </c>
       <c r="E205" t="n">
-        <v>75.56999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="F205" t="n">
-        <v>0.28103</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>78.59999999999999</v>
+        <v>124.07</v>
       </c>
       <c r="D206" t="n">
-        <v>167.84</v>
+        <v>187.41</v>
       </c>
       <c r="E206" t="n">
-        <v>113.54</v>
+        <v>51.05</v>
       </c>
       <c r="F206" t="n">
-        <v>-0.11311</v>
+        <v>4.82188</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>57.15</v>
+        <v>62.49</v>
       </c>
       <c r="D207" t="n">
-        <v>192.77</v>
+        <v>91.37</v>
       </c>
       <c r="E207" t="n">
-        <v>237.31</v>
+        <v>46.22</v>
       </c>
       <c r="F207" t="n">
-        <v>4.18785</v>
+        <v>-0.08597</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>151.43</v>
+        <v>96.73</v>
       </c>
       <c r="D208" t="n">
-        <v>265.67</v>
+        <v>121.62</v>
       </c>
       <c r="E208" t="n">
-        <v>75.44</v>
+        <v>25.73</v>
       </c>
       <c r="F208" t="n">
-        <v>1.55591</v>
+        <v>0.39975</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>34.41</v>
+        <v>164.13</v>
       </c>
       <c r="D209" t="n">
-        <v>67.69</v>
+        <v>547.5700000000001</v>
       </c>
       <c r="E209" t="n">
-        <v>96.72</v>
+        <v>233.62</v>
       </c>
       <c r="F209" t="n">
-        <v>0.14027</v>
+        <v>20.4755</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>62.93</v>
+        <v>41.19</v>
       </c>
       <c r="D210" t="n">
-        <v>186.45</v>
+        <v>98.05</v>
       </c>
       <c r="E210" t="n">
-        <v>196.28</v>
+        <v>138.04</v>
       </c>
       <c r="F210" t="n">
-        <v>6.24855</v>
+        <v>1.31754</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>43.81</v>
+        <v>196.04</v>
       </c>
       <c r="D211" t="n">
-        <v>100.2</v>
+        <v>502.43</v>
       </c>
       <c r="E211" t="n">
-        <v>128.71</v>
+        <v>156.29</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.42056</v>
+        <v>7.12566</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>166.99</v>
+        <v>65.16</v>
       </c>
       <c r="D212" t="n">
-        <v>330.36</v>
+        <v>111.75</v>
       </c>
       <c r="E212" t="n">
-        <v>97.83</v>
+        <v>71.5</v>
       </c>
       <c r="F212" t="n">
-        <v>9.064159999999999</v>
+        <v>1.69536</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>120.88</v>
+        <v>16.32</v>
       </c>
       <c r="D213" t="n">
-        <v>211.54</v>
+        <v>23.55</v>
       </c>
       <c r="E213" t="n">
-        <v>75</v>
+        <v>44.27</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.8151</v>
+        <v>0.25119</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>32.36</v>
+        <v>52.5</v>
       </c>
       <c r="D214" t="n">
-        <v>53.34</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="E214" t="n">
-        <v>64.83</v>
+        <v>68.5</v>
       </c>
       <c r="F214" t="n">
-        <v>0.36656</v>
+        <v>5.0903</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>112.5</v>
+        <v>131.47</v>
       </c>
       <c r="D215" t="n">
-        <v>194.21</v>
+        <v>209.02</v>
       </c>
       <c r="E215" t="n">
-        <v>72.63</v>
+        <v>58.99</v>
       </c>
       <c r="F215" t="n">
-        <v>-1.0532</v>
+        <v>2.24854</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>121.11</v>
+        <v>73.13</v>
       </c>
       <c r="D216" t="n">
-        <v>332.35</v>
+        <v>95.25</v>
       </c>
       <c r="E216" t="n">
-        <v>174.42</v>
+        <v>30.25</v>
       </c>
       <c r="F216" t="n">
-        <v>2.08531</v>
+        <v>0.55414</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>83</v>
+        <v>3.88</v>
       </c>
       <c r="D217" t="n">
-        <v>142.35</v>
+        <v>6.42</v>
       </c>
       <c r="E217" t="n">
-        <v>71.51000000000001</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F217" t="n">
-        <v>0.76309</v>
+        <v>0.07343</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>76.7</v>
+        <v>19.02</v>
       </c>
       <c r="D218" t="n">
-        <v>170.18</v>
+        <v>26.58</v>
       </c>
       <c r="E218" t="n">
-        <v>121.88</v>
+        <v>39.75</v>
       </c>
       <c r="F218" t="n">
-        <v>0.67575</v>
+        <v>0.27783</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>105.37</v>
+        <v>284.79</v>
       </c>
       <c r="D219" t="n">
-        <v>230.05</v>
+        <v>419.61</v>
       </c>
       <c r="E219" t="n">
-        <v>118.33</v>
+        <v>47.34</v>
       </c>
       <c r="F219" t="n">
-        <v>-1.90231</v>
+        <v>6.69888</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>188.79</v>
+        <v>246.63</v>
       </c>
       <c r="D220" t="n">
-        <v>276.63</v>
+        <v>330.16</v>
       </c>
       <c r="E220" t="n">
-        <v>46.53</v>
+        <v>33.87</v>
       </c>
       <c r="F220" t="n">
-        <v>-2.28574</v>
+        <v>4.60313</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>18.26</v>
+        <v>116.13</v>
       </c>
       <c r="D221" t="n">
-        <v>34.02</v>
+        <v>193.42</v>
       </c>
       <c r="E221" t="n">
-        <v>86.31</v>
+        <v>66.55</v>
       </c>
       <c r="F221" t="n">
-        <v>1.1574</v>
+        <v>0.19471</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>25.85</v>
+        <v>67.39</v>
       </c>
       <c r="D222" t="n">
-        <v>42.91</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="E222" t="n">
-        <v>66</v>
+        <v>37.33</v>
       </c>
       <c r="F222" t="n">
-        <v>0.12798</v>
+        <v>0.54522</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>117.65</v>
+        <v>59.66</v>
       </c>
       <c r="D223" t="n">
-        <v>231.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="E223" t="n">
-        <v>97.09</v>
+        <v>37.76</v>
       </c>
       <c r="F223" t="n">
-        <v>0.40682</v>
+        <v>1.48179</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>10.49</v>
+        <v>273.5</v>
       </c>
       <c r="D224" t="n">
-        <v>19.88</v>
+        <v>344.33</v>
       </c>
       <c r="E224" t="n">
-        <v>89.51000000000001</v>
+        <v>25.9</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.15382</v>
+        <v>0.009010000000000001</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>56.43</v>
+        <v>22.61</v>
       </c>
       <c r="D225" t="n">
-        <v>106.91</v>
+        <v>56.38</v>
       </c>
       <c r="E225" t="n">
-        <v>89.45999999999999</v>
+        <v>149.36</v>
       </c>
       <c r="F225" t="n">
-        <v>3.01266</v>
+        <v>1.14824</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>23.63</v>
+        <v>204.77</v>
       </c>
       <c r="D226" t="n">
-        <v>25.41</v>
+        <v>273.97</v>
       </c>
       <c r="E226" t="n">
-        <v>7.53</v>
+        <v>33.79</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0601</v>
+        <v>1.08553</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>190.63</v>
+        <v>28.35</v>
       </c>
       <c r="D227" t="n">
-        <v>218.57</v>
+        <v>38.88</v>
       </c>
       <c r="E227" t="n">
-        <v>14.66</v>
+        <v>37.16</v>
       </c>
       <c r="F227" t="n">
-        <v>-1.51875</v>
+        <v>0.45939</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>124.07</v>
+        <v>97.52</v>
       </c>
       <c r="D228" t="n">
-        <v>180.15</v>
+        <v>129.05</v>
       </c>
       <c r="E228" t="n">
-        <v>45.2</v>
+        <v>32.33</v>
       </c>
       <c r="F228" t="n">
-        <v>4.1705</v>
+        <v>2.19434</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>23.49</v>
+        <v>31.8</v>
       </c>
       <c r="D229" t="n">
-        <v>32.49</v>
+        <v>67.41</v>
       </c>
       <c r="E229" t="n">
-        <v>38.31</v>
+        <v>111.98</v>
       </c>
       <c r="F229" t="n">
-        <v>0.09743</v>
+        <v>0.60451</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>62.49</v>
+        <v>26.41</v>
       </c>
       <c r="D230" t="n">
-        <v>89.81999999999999</v>
+        <v>39.83</v>
       </c>
       <c r="E230" t="n">
-        <v>43.73</v>
+        <v>50.81</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.23607</v>
+        <v>1.33989</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>172.34</v>
+        <v>279.73</v>
       </c>
       <c r="D231" t="n">
-        <v>217.36</v>
+        <v>422.73</v>
       </c>
       <c r="E231" t="n">
-        <v>26.12</v>
+        <v>51.12</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.19213</v>
+        <v>5.1071</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>430.4</v>
+        <v>273.14</v>
       </c>
       <c r="D232" t="n">
-        <v>558.54</v>
+        <v>340.76</v>
       </c>
       <c r="E232" t="n">
-        <v>29.77</v>
+        <v>24.76</v>
       </c>
       <c r="F232" t="n">
-        <v>0.26252</v>
+        <v>-0.12334</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>72.54000000000001</v>
+        <v>119.51</v>
       </c>
       <c r="D233" t="n">
-        <v>87.16</v>
+        <v>263.11</v>
       </c>
       <c r="E233" t="n">
-        <v>20.15</v>
+        <v>120.16</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.10751</v>
+        <v>11.02348</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>164.13</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D234" t="n">
-        <v>534.28</v>
+        <v>21.7</v>
       </c>
       <c r="E234" t="n">
-        <v>225.52</v>
+        <v>152.09</v>
       </c>
       <c r="F234" t="n">
-        <v>21.33398</v>
+        <v>0.63808</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>96.73</v>
+        <v>24.77</v>
       </c>
       <c r="D235" t="n">
-        <v>122.53</v>
+        <v>36.51</v>
       </c>
       <c r="E235" t="n">
-        <v>26.67</v>
+        <v>47.38</v>
       </c>
       <c r="F235" t="n">
-        <v>0.4313</v>
+        <v>0.35868</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6076,22 +6076,22 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>73.13</v>
+        <v>258.08</v>
       </c>
       <c r="D236" t="n">
-        <v>95.43000000000001</v>
+        <v>289.68</v>
       </c>
       <c r="E236" t="n">
-        <v>30.49</v>
+        <v>12.24</v>
       </c>
       <c r="F236" t="n">
-        <v>0.43563</v>
+        <v>1.88713</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6100,814 +6100,814 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>199.3</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D237" t="n">
-        <v>351.81</v>
+        <v>100.54</v>
       </c>
       <c r="E237" t="n">
-        <v>76.52</v>
+        <v>11.69</v>
       </c>
       <c r="F237" t="n">
-        <v>-1.44191</v>
+        <v>0.2773</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3.88</v>
+        <v>525.72</v>
       </c>
       <c r="D238" t="n">
-        <v>6.46</v>
+        <v>666.38</v>
       </c>
       <c r="E238" t="n">
-        <v>66.48999999999999</v>
+        <v>26.76</v>
       </c>
       <c r="F238" t="n">
-        <v>0.08959</v>
+        <v>21.21441</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>52.5</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D239" t="n">
-        <v>79.26000000000001</v>
+        <v>117.05</v>
       </c>
       <c r="E239" t="n">
-        <v>50.97</v>
+        <v>34.52</v>
       </c>
       <c r="F239" t="n">
-        <v>4.37139</v>
+        <v>1.06053</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>131.47</v>
+        <v>110.24</v>
       </c>
       <c r="D240" t="n">
-        <v>214.07</v>
+        <v>150.33</v>
       </c>
       <c r="E240" t="n">
-        <v>62.83</v>
+        <v>36.37</v>
       </c>
       <c r="F240" t="n">
-        <v>0.91734</v>
+        <v>-0.84824</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>273.5</v>
+        <v>61.37</v>
       </c>
       <c r="D241" t="n">
-        <v>349.39</v>
+        <v>79.97</v>
       </c>
       <c r="E241" t="n">
-        <v>27.75</v>
+        <v>30.31</v>
       </c>
       <c r="F241" t="n">
-        <v>-1.43004</v>
+        <v>0.05464</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>28.35</v>
+        <v>3.42</v>
       </c>
       <c r="D242" t="n">
-        <v>38.72</v>
+        <v>5.01</v>
       </c>
       <c r="E242" t="n">
-        <v>36.58</v>
+        <v>46.49</v>
       </c>
       <c r="F242" t="n">
-        <v>0.29357</v>
+        <v>0.08568000000000001</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>273.14</v>
+        <v>7.58</v>
       </c>
       <c r="D243" t="n">
-        <v>345.71</v>
+        <v>10.55</v>
       </c>
       <c r="E243" t="n">
-        <v>26.57</v>
+        <v>39.12</v>
       </c>
       <c r="F243" t="n">
-        <v>-1.43948</v>
+        <v>0.1719</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>22.61</v>
+        <v>284.93</v>
       </c>
       <c r="D244" t="n">
-        <v>55.41</v>
+        <v>411.83</v>
       </c>
       <c r="E244" t="n">
-        <v>145.07</v>
+        <v>44.54</v>
       </c>
       <c r="F244" t="n">
-        <v>1.53437</v>
+        <v>1.15578</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>8.609999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="D245" t="n">
-        <v>21.9</v>
+        <v>68.87</v>
       </c>
       <c r="E245" t="n">
-        <v>154.36</v>
+        <v>24.31</v>
       </c>
       <c r="F245" t="n">
-        <v>0.80893</v>
+        <v>0.03706</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>166</v>
+        <v>182.65</v>
       </c>
       <c r="D246" t="n">
-        <v>407.02</v>
+        <v>346.11</v>
       </c>
       <c r="E246" t="n">
-        <v>145.19</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F246" t="n">
-        <v>4.5493</v>
+        <v>5.48885</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>119.51</v>
+        <v>289.16</v>
       </c>
       <c r="D247" t="n">
-        <v>257.05</v>
+        <v>418.32</v>
       </c>
       <c r="E247" t="n">
-        <v>115.09</v>
+        <v>44.67</v>
       </c>
       <c r="F247" t="n">
-        <v>12.83332</v>
+        <v>0.94158</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>29.16</v>
+        <v>295.52</v>
       </c>
       <c r="D248" t="n">
-        <v>39.94</v>
+        <v>374.38</v>
       </c>
       <c r="E248" t="n">
-        <v>36.97</v>
+        <v>26.69</v>
       </c>
       <c r="F248" t="n">
-        <v>0.01199</v>
+        <v>-0.00621</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>97.52</v>
+        <v>87.98</v>
       </c>
       <c r="D249" t="n">
-        <v>132.88</v>
+        <v>107.81</v>
       </c>
       <c r="E249" t="n">
-        <v>36.26</v>
+        <v>22.54</v>
       </c>
       <c r="F249" t="n">
-        <v>2.17585</v>
+        <v>0.73714</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>69.3</v>
+        <v>117.67</v>
       </c>
       <c r="D250" t="n">
-        <v>83.54000000000001</v>
+        <v>223.01</v>
       </c>
       <c r="E250" t="n">
-        <v>20.55</v>
+        <v>89.52</v>
       </c>
       <c r="F250" t="n">
-        <v>0.20672</v>
+        <v>0.14636</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>258.08</v>
+        <v>1835.67</v>
       </c>
       <c r="D251" t="n">
-        <v>290.05</v>
+        <v>2180.06</v>
       </c>
       <c r="E251" t="n">
-        <v>12.39</v>
+        <v>18.76</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8742</v>
+        <v>-1.5421</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>24.77</v>
+        <v>121.84</v>
       </c>
       <c r="D252" t="n">
-        <v>36.96</v>
+        <v>159.3</v>
       </c>
       <c r="E252" t="n">
-        <v>49.21</v>
+        <v>30.75</v>
       </c>
       <c r="F252" t="n">
-        <v>0.4117</v>
+        <v>1.27087</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>284.79</v>
+        <v>3.93</v>
       </c>
       <c r="D253" t="n">
-        <v>424.24</v>
+        <v>5.95</v>
       </c>
       <c r="E253" t="n">
-        <v>48.97</v>
+        <v>51.53</v>
       </c>
       <c r="F253" t="n">
-        <v>5.01403</v>
+        <v>0.12772</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>67.39</v>
+        <v>22.3</v>
       </c>
       <c r="D254" t="n">
-        <v>93.43000000000001</v>
+        <v>34.93</v>
       </c>
       <c r="E254" t="n">
-        <v>38.64</v>
+        <v>56.64</v>
       </c>
       <c r="F254" t="n">
-        <v>0.55682</v>
+        <v>0.51962</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>65.16</v>
+        <v>24.24</v>
       </c>
       <c r="D255" t="n">
-        <v>114.33</v>
+        <v>30.34</v>
       </c>
       <c r="E255" t="n">
-        <v>75.45999999999999</v>
+        <v>25.19</v>
       </c>
       <c r="F255" t="n">
-        <v>2.2454</v>
+        <v>-0.00327</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>19.02</v>
+        <v>317.93</v>
       </c>
       <c r="D256" t="n">
-        <v>27.24</v>
+        <v>378.54</v>
       </c>
       <c r="E256" t="n">
-        <v>43.22</v>
+        <v>19.06</v>
       </c>
       <c r="F256" t="n">
-        <v>0.27865</v>
+        <v>0.37337</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>20.33</v>
+        <v>157.12</v>
       </c>
       <c r="D257" t="n">
-        <v>29.1</v>
+        <v>263.33</v>
       </c>
       <c r="E257" t="n">
-        <v>43.14</v>
+        <v>67.59</v>
       </c>
       <c r="F257" t="n">
-        <v>0.12624</v>
+        <v>2.1884</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>16.32</v>
+        <v>35.34</v>
       </c>
       <c r="D258" t="n">
-        <v>23.89</v>
+        <v>53.69</v>
       </c>
       <c r="E258" t="n">
-        <v>46.38</v>
+        <v>51.91</v>
       </c>
       <c r="F258" t="n">
-        <v>0.235</v>
+        <v>0.82279</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>41.19</v>
+        <v>7.63</v>
       </c>
       <c r="D259" t="n">
-        <v>97.19</v>
+        <v>11.05</v>
       </c>
       <c r="E259" t="n">
-        <v>135.96</v>
+        <v>44.82</v>
       </c>
       <c r="F259" t="n">
-        <v>2.31858</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>107.27</v>
+        <v>92.39</v>
       </c>
       <c r="D260" t="n">
-        <v>136.18</v>
+        <v>240.17</v>
       </c>
       <c r="E260" t="n">
-        <v>26.95</v>
+        <v>159.94</v>
       </c>
       <c r="F260" t="n">
-        <v>1.00255</v>
+        <v>5.22628</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>196.04</v>
+        <v>285.27</v>
       </c>
       <c r="D261" t="n">
-        <v>493.41</v>
+        <v>377.26</v>
       </c>
       <c r="E261" t="n">
-        <v>151.69</v>
+        <v>32.24</v>
       </c>
       <c r="F261" t="n">
-        <v>9.84099</v>
+        <v>2.16784</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>246.63</v>
+        <v>147.02</v>
       </c>
       <c r="D262" t="n">
-        <v>333.08</v>
+        <v>373.51</v>
       </c>
       <c r="E262" t="n">
-        <v>35.05</v>
+        <v>154.05</v>
       </c>
       <c r="F262" t="n">
-        <v>3.52767</v>
+        <v>1.77198</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>59.66</v>
+        <v>33.63</v>
       </c>
       <c r="D263" t="n">
-        <v>84.11</v>
+        <v>43.53</v>
       </c>
       <c r="E263" t="n">
-        <v>40.98</v>
+        <v>29.45</v>
       </c>
       <c r="F263" t="n">
-        <v>1.58777</v>
+        <v>0.05453</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>57.45</v>
+        <v>20.72</v>
       </c>
       <c r="D264" t="n">
-        <v>70.54000000000001</v>
+        <v>24.81</v>
       </c>
       <c r="E264" t="n">
-        <v>22.79</v>
+        <v>19.74</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.19886</v>
+        <v>0.04605</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>279.73</v>
+        <v>39.84</v>
       </c>
       <c r="D265" t="n">
-        <v>411.49</v>
+        <v>58.55</v>
       </c>
       <c r="E265" t="n">
-        <v>47.1</v>
+        <v>46.96</v>
       </c>
       <c r="F265" t="n">
-        <v>3.73943</v>
+        <v>0.08252</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>26.41</v>
+        <v>52.49</v>
       </c>
       <c r="D266" t="n">
-        <v>41.02</v>
+        <v>55.75</v>
       </c>
       <c r="E266" t="n">
-        <v>55.32</v>
+        <v>6.21</v>
       </c>
       <c r="F266" t="n">
-        <v>1.68935</v>
+        <v>-0.01794</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>90.01000000000001</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D267" t="n">
-        <v>100.36</v>
+        <v>156.81</v>
       </c>
       <c r="E267" t="n">
-        <v>11.5</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F267" t="n">
-        <v>0.11228</v>
+        <v>0.29224</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>31.8</v>
+        <v>23.77</v>
       </c>
       <c r="D268" t="n">
-        <v>69.41</v>
+        <v>28.91</v>
       </c>
       <c r="E268" t="n">
-        <v>118.27</v>
+        <v>21.62</v>
       </c>
       <c r="F268" t="n">
-        <v>0.31551</v>
+        <v>0.2726</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>204.77</v>
+        <v>67.7</v>
       </c>
       <c r="D269" t="n">
-        <v>274.99</v>
+        <v>97.48</v>
       </c>
       <c r="E269" t="n">
-        <v>34.29</v>
+        <v>43.99</v>
       </c>
       <c r="F269" t="n">
-        <v>0.55032</v>
+        <v>0.40375</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>12.96</v>
+        <v>243.35</v>
       </c>
       <c r="D270" t="n">
-        <v>16.66</v>
+        <v>368.58</v>
       </c>
       <c r="E270" t="n">
-        <v>28.55</v>
+        <v>51.46</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.0515</v>
+        <v>3.51682</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6916,22 +6916,22 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>147.02</v>
+        <v>14</v>
       </c>
       <c r="D271" t="n">
-        <v>373.94</v>
+        <v>14.81</v>
       </c>
       <c r="E271" t="n">
-        <v>154.35</v>
+        <v>5.79</v>
       </c>
       <c r="F271" t="n">
-        <v>-2.08465</v>
+        <v>0.01087</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>156.35</v>
+        <v>92.42</v>
       </c>
       <c r="D272" t="n">
-        <v>216.58</v>
+        <v>107.44</v>
       </c>
       <c r="E272" t="n">
-        <v>38.52</v>
+        <v>16.25</v>
       </c>
       <c r="F272" t="n">
-        <v>1.76572</v>
+        <v>0.4803</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,1264 +6964,160 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>92.39</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D273" t="n">
-        <v>235.38</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E273" t="n">
-        <v>154.75</v>
+        <v>30.45</v>
       </c>
       <c r="F273" t="n">
-        <v>2.36905</v>
+        <v>0.86779</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>7.63</v>
+        <v>95.48</v>
       </c>
       <c r="D274" t="n">
-        <v>11.33</v>
+        <v>112</v>
       </c>
       <c r="E274" t="n">
-        <v>48.49</v>
+        <v>17.3</v>
       </c>
       <c r="F274" t="n">
-        <v>0.16084</v>
+        <v>0.09274</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>284.93</v>
+        <v>27.55</v>
       </c>
       <c r="D275" t="n">
-        <v>412.56</v>
+        <v>33.66</v>
       </c>
       <c r="E275" t="n">
-        <v>44.79</v>
+        <v>22.18</v>
       </c>
       <c r="F275" t="n">
-        <v>0.67323</v>
+        <v>-0.16805</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>FMX</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>67.56999999999999</v>
+        <v>106.96</v>
       </c>
       <c r="D276" t="n">
-        <v>79.81999999999999</v>
+        <v>121.26</v>
       </c>
       <c r="E276" t="n">
-        <v>18.13</v>
+        <v>13.37</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.43807</v>
+        <v>-0.41742</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>285.27</v>
+        <v>17.13</v>
       </c>
       <c r="D277" t="n">
-        <v>378.05</v>
+        <v>42.6</v>
       </c>
       <c r="E277" t="n">
-        <v>32.52</v>
+        <v>148.7</v>
       </c>
       <c r="F277" t="n">
-        <v>1.30077</v>
+        <v>0.26831</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>33.63</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D278" t="n">
-        <v>43.55</v>
+        <v>172.48</v>
       </c>
       <c r="E278" t="n">
-        <v>29.5</v>
+        <v>72.5</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.00236</v>
+        <v>1.4171</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>202.71</v>
+        <v>63.78</v>
       </c>
       <c r="D279" t="n">
-        <v>258.48</v>
+        <v>70.05</v>
       </c>
       <c r="E279" t="n">
-        <v>27.51</v>
+        <v>9.83</v>
       </c>
       <c r="F279" t="n">
-        <v>-1.41316</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="D280" t="n">
-        <v>97.75</v>
-      </c>
-      <c r="E280" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.25783</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>87.15000000000001</v>
-      </c>
-      <c r="D281" t="n">
-        <v>157.45</v>
-      </c>
-      <c r="E281" t="n">
-        <v>80.67</v>
-      </c>
-      <c r="F281" t="n">
-        <v>-0.08858000000000001</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>91.37</v>
-      </c>
-      <c r="D282" t="n">
-        <v>120.93</v>
-      </c>
-      <c r="E282" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="F282" t="n">
-        <v>-0.10485</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>CRBG</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="D283" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E283" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="F283" t="n">
-        <v>0.45747</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>SPG-PJ</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="D284" t="n">
-        <v>55.78</v>
-      </c>
-      <c r="E284" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="F284" t="n">
-        <v>-0.04614</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>SAN</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="D285" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="E285" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="F285" t="n">
-        <v>0.05009</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>92.42</v>
-      </c>
-      <c r="D286" t="n">
-        <v>108.59</v>
-      </c>
-      <c r="E286" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F286" t="n">
-        <v>0.1877</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>DKNG</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="D287" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="E287" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="F287" t="n">
-        <v>-0.07012</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>ARCC</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="D288" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="E288" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="F288" t="n">
-        <v>-0.03105</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>ZION</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="D289" t="n">
-        <v>69.18000000000001</v>
-      </c>
-      <c r="E289" t="n">
-        <v>24.87</v>
-      </c>
-      <c r="F289" t="n">
-        <v>-0.03903</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="D290" t="n">
-        <v>375.28</v>
-      </c>
-      <c r="E290" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="F290" t="n">
-        <v>-0.74265</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>GGB</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="D291" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="E291" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="F291" t="n">
-        <v>0.09469</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>525.72</v>
-      </c>
-      <c r="D292" t="n">
-        <v>665.6</v>
-      </c>
-      <c r="E292" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="F292" t="n">
-        <v>22.11172</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>WAT</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>289.16</v>
-      </c>
-      <c r="D293" t="n">
-        <v>410.01</v>
-      </c>
-      <c r="E293" t="n">
-        <v>41.79</v>
-      </c>
-      <c r="F293" t="n">
-        <v>-0.38142</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>ARMK</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>39.84</v>
-      </c>
-      <c r="D294" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="E294" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="F294" t="n">
-        <v>-0.08142000000000001</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>61.37</v>
-      </c>
-      <c r="D295" t="n">
-        <v>80.23</v>
-      </c>
-      <c r="E295" t="n">
-        <v>30.73</v>
-      </c>
-      <c r="F295" t="n">
-        <v>-0.09644999999999999</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>317.93</v>
-      </c>
-      <c r="D296" t="n">
-        <v>379.54</v>
-      </c>
-      <c r="E296" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="F296" t="n">
-        <v>-0.71048</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>CINF</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>153.68</v>
-      </c>
-      <c r="D297" t="n">
-        <v>172.02</v>
-      </c>
-      <c r="E297" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="F297" t="n">
-        <v>-0.63445</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>NMR</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="D298" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="E298" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="F298" t="n">
-        <v>0.17999</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>AIZ</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>213.28</v>
-      </c>
-      <c r="D299" t="n">
-        <v>283.27</v>
-      </c>
-      <c r="E299" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="F299" t="n">
-        <v>-0.5633</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>SNX</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>157.12</v>
-      </c>
-      <c r="D300" t="n">
-        <v>261.12</v>
-      </c>
-      <c r="E300" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="F300" t="n">
-        <v>1.88244</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>87.01000000000001</v>
-      </c>
-      <c r="D301" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="E301" t="n">
-        <v>34.35</v>
-      </c>
-      <c r="F301" t="n">
-        <v>0.85321</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>QSR</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>71.42</v>
-      </c>
-      <c r="D302" t="n">
-        <v>78.89</v>
-      </c>
-      <c r="E302" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="F302" t="n">
-        <v>-0.24064</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>WST</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>243.35</v>
-      </c>
-      <c r="D303" t="n">
-        <v>355.2</v>
-      </c>
-      <c r="E303" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="F303" t="n">
-        <v>0.55648</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>NTRA</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>182.65</v>
-      </c>
-      <c r="D304" t="n">
-        <v>341.79</v>
-      </c>
-      <c r="E304" t="n">
-        <v>87.13</v>
-      </c>
-      <c r="F304" t="n">
-        <v>4.40399</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>SNAP</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="D305" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E305" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="F305" t="n">
-        <v>0.07327</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>EBAY</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>87.98</v>
-      </c>
-      <c r="D306" t="n">
-        <v>108.99</v>
-      </c>
-      <c r="E306" t="n">
-        <v>23.88</v>
-      </c>
-      <c r="F306" t="n">
-        <v>0.3621</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>UNM</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="D307" t="n">
-        <v>94.92</v>
-      </c>
-      <c r="E307" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="F307" t="n">
-        <v>0.7454499999999999</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>EQH</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="D308" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="E308" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="F308" t="n">
-        <v>0.74151</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>AFG</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>125.78</v>
-      </c>
-      <c r="D309" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="E309" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="F309" t="n">
-        <v>-0.39666</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>CART</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>35.72</v>
-      </c>
-      <c r="D310" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="E310" t="n">
-        <v>38.52</v>
-      </c>
-      <c r="F310" t="n">
-        <v>-0.54794</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="D311" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="E311" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="F311" t="n">
-        <v>-0.14265</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>AES</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>14</v>
-      </c>
-      <c r="D312" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="E312" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="F312" t="n">
-        <v>0.01308</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>RDDT</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>121.84</v>
-      </c>
-      <c r="D313" t="n">
-        <v>162.38</v>
-      </c>
-      <c r="E313" t="n">
-        <v>33.27</v>
-      </c>
-      <c r="F313" t="n">
-        <v>0.05096</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="D314" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="E314" t="n">
-        <v>153.65</v>
-      </c>
-      <c r="F314" t="n">
-        <v>0.28998</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="D315" t="n">
-        <v>70.61</v>
-      </c>
-      <c r="E315" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="F315" t="n">
-        <v>0.28252</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>ICLR</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="D316" t="n">
-        <v>168.93</v>
-      </c>
-      <c r="E316" t="n">
-        <v>68.95</v>
-      </c>
-      <c r="F316" t="n">
-        <v>0.20101</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>NWS</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>27.17</v>
-      </c>
-      <c r="D317" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="E317" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="F317" t="n">
-        <v>-0.24679</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>VRSN</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>241.14</v>
-      </c>
-      <c r="D318" t="n">
-        <v>298.6</v>
-      </c>
-      <c r="E318" t="n">
-        <v>23.83</v>
-      </c>
-      <c r="F318" t="n">
-        <v>1.64228</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>MDGL</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>445.04</v>
-      </c>
-      <c r="D319" t="n">
-        <v>540.0599999999999</v>
-      </c>
-      <c r="E319" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F319" t="n">
-        <v>2.20142</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>KOF</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>94.23999999999999</v>
-      </c>
-      <c r="D320" t="n">
-        <v>112.01</v>
-      </c>
-      <c r="E320" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="F320" t="n">
-        <v>-0.19592</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>WMG</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="D321" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E321" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="F321" t="n">
-        <v>0.22235</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>FMX</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>105.8</v>
-      </c>
-      <c r="D322" t="n">
-        <v>121.26</v>
-      </c>
-      <c r="E322" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="F322" t="n">
-        <v>-0.80715</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>PAG</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>146.17</v>
-      </c>
-      <c r="D323" t="n">
-        <v>217.15</v>
-      </c>
-      <c r="E323" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="F323" t="n">
-        <v>0.01127</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>NWSA</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>23.97</v>
-      </c>
-      <c r="D324" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="E324" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="F324" t="n">
-        <v>-0.08098</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>ABEV</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="D325" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E325" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="F325" t="n">
-        <v>0.02721</v>
+        <v>0.46132</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,13 +463,13 @@
         <v>80.54000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>86.31999999999999</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.17</v>
+        <v>6.97</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.94382</v>
+        <v>-0.95953</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>56.65</v>
+        <v>56.5</v>
       </c>
       <c r="E3" t="n">
-        <v>4.28</v>
+        <v>3.99</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.08566</v>
+        <v>-0.10042</v>
       </c>
     </row>
     <row r="4">
@@ -511,109 +511,109 @@
         <v>38.22</v>
       </c>
       <c r="D4" t="n">
-        <v>42.41</v>
+        <v>42.77</v>
       </c>
       <c r="E4" t="n">
-        <v>10.96</v>
+        <v>11.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.13711</v>
+        <v>0.1714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>ESLT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.87</v>
+        <v>700.51</v>
       </c>
       <c r="D5" t="n">
-        <v>21.24</v>
+        <v>731.75</v>
       </c>
       <c r="E5" t="n">
-        <v>18.86</v>
+        <v>4.46</v>
       </c>
       <c r="F5" t="n">
-        <v>0.72516</v>
+        <v>-1.9792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>102.63</v>
+        <v>17.87</v>
       </c>
       <c r="D6" t="n">
-        <v>108.51</v>
+        <v>21.45</v>
       </c>
       <c r="E6" t="n">
-        <v>5.73</v>
+        <v>20.03</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05302</v>
+        <v>0.74516</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13.03</v>
+        <v>102.63</v>
       </c>
       <c r="D7" t="n">
-        <v>15.02</v>
+        <v>108.11</v>
       </c>
       <c r="E7" t="n">
-        <v>15.23</v>
+        <v>5.33</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09189</v>
+        <v>0.01445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>298.59</v>
+        <v>13.03</v>
       </c>
       <c r="D8" t="n">
-        <v>328.18</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>9.91</v>
+        <v>15.12</v>
       </c>
       <c r="F8" t="n">
-        <v>0.78755</v>
+        <v>0.09046</v>
       </c>
     </row>
     <row r="9">
@@ -631,67 +631,67 @@
         <v>5.67</v>
       </c>
       <c r="D9" t="n">
-        <v>7.05</v>
+        <v>6.84</v>
       </c>
       <c r="E9" t="n">
-        <v>24.34</v>
+        <v>20.55</v>
       </c>
       <c r="F9" t="n">
-        <v>0.17197</v>
+        <v>0.15149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>141.63</v>
+        <v>298.59</v>
       </c>
       <c r="D10" t="n">
-        <v>156.93</v>
+        <v>331.28</v>
       </c>
       <c r="E10" t="n">
-        <v>10.81</v>
+        <v>10.95</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6254</v>
+        <v>1.08278</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.98</v>
+        <v>141.63</v>
       </c>
       <c r="D11" t="n">
-        <v>3.52</v>
+        <v>157.63</v>
       </c>
       <c r="E11" t="n">
-        <v>18.12</v>
+        <v>11.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07025000000000001</v>
+        <v>1.69159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.17</v>
+        <v>4.46</v>
       </c>
       <c r="D12" t="n">
-        <v>8.24</v>
+        <v>5.22</v>
       </c>
       <c r="E12" t="n">
-        <v>14.99</v>
+        <v>17.15</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1381</v>
+        <v>0.08130999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12.43</v>
+        <v>11.23</v>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>11.89</v>
       </c>
       <c r="E13" t="n">
-        <v>39.98</v>
+        <v>5.88</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8716699999999999</v>
+        <v>0.03859</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.46</v>
+        <v>12.43</v>
       </c>
       <c r="D14" t="n">
-        <v>5.24</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="n">
-        <v>17.38</v>
+        <v>39.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08227</v>
+        <v>0.8716699999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -772,46 +772,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.23</v>
+        <v>2.98</v>
       </c>
       <c r="D15" t="n">
-        <v>11.87</v>
+        <v>3.49</v>
       </c>
       <c r="E15" t="n">
-        <v>5.67</v>
+        <v>17.11</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03632</v>
+        <v>0.06739000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>98.45</v>
+        <v>7.17</v>
       </c>
       <c r="D16" t="n">
-        <v>124.94</v>
+        <v>8.26</v>
       </c>
       <c r="E16" t="n">
-        <v>26.91</v>
+        <v>15.13</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8845</v>
+        <v>0.13905</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,142 +820,142 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.28</v>
+        <v>98.45</v>
       </c>
       <c r="D17" t="n">
-        <v>19.14</v>
+        <v>123.82</v>
       </c>
       <c r="E17" t="n">
-        <v>10.73</v>
+        <v>25.77</v>
       </c>
       <c r="F17" t="n">
-        <v>0.21851</v>
+        <v>1.77783</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ABEV</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.78</v>
+        <v>17.28</v>
       </c>
       <c r="D18" t="n">
-        <v>3.03</v>
+        <v>19.04</v>
       </c>
       <c r="E18" t="n">
-        <v>8.81</v>
+        <v>10.19</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02604</v>
+        <v>0.20946</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>52.62</v>
+        <v>2.78</v>
       </c>
       <c r="D19" t="n">
-        <v>56.64</v>
+        <v>3.03</v>
       </c>
       <c r="E19" t="n">
-        <v>7.64</v>
+        <v>8.81</v>
       </c>
       <c r="F19" t="n">
-        <v>0.35581</v>
+        <v>0.02604</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35.54</v>
+        <v>52.62</v>
       </c>
       <c r="D20" t="n">
-        <v>50.1</v>
+        <v>56.63</v>
       </c>
       <c r="E20" t="n">
-        <v>40.97</v>
+        <v>7.62</v>
       </c>
       <c r="F20" t="n">
-        <v>2.32507</v>
+        <v>0.35486</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>123.39</v>
+        <v>35.54</v>
       </c>
       <c r="D21" t="n">
-        <v>136.92</v>
+        <v>50.25</v>
       </c>
       <c r="E21" t="n">
-        <v>10.97</v>
+        <v>41.39</v>
       </c>
       <c r="F21" t="n">
-        <v>1.40833</v>
+        <v>2.33935</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>340.65</v>
+        <v>123.39</v>
       </c>
       <c r="D22" t="n">
-        <v>373.32</v>
+        <v>133.75</v>
       </c>
       <c r="E22" t="n">
-        <v>9.59</v>
+        <v>8.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.04944</v>
+        <v>1.10642</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -964,40 +964,40 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.54</v>
+        <v>340.65</v>
       </c>
       <c r="D23" t="n">
-        <v>72.53</v>
+        <v>372.02</v>
       </c>
       <c r="E23" t="n">
-        <v>14.14</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.58789</v>
+        <v>-1.17278</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>155.62</v>
+        <v>63.54</v>
       </c>
       <c r="D24" t="n">
-        <v>163.19</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>4.86</v>
+        <v>13.08</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.31241</v>
+        <v>0.5236</v>
       </c>
     </row>
     <row r="25">
@@ -1015,19 +1015,19 @@
         <v>7.81</v>
       </c>
       <c r="D25" t="n">
-        <v>10.94</v>
+        <v>11.01</v>
       </c>
       <c r="E25" t="n">
-        <v>40.08</v>
+        <v>40.97</v>
       </c>
       <c r="F25" t="n">
-        <v>0.10807</v>
+        <v>0.11474</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>298.32</v>
+        <v>48.68</v>
       </c>
       <c r="D26" t="n">
-        <v>360.9</v>
+        <v>61.09</v>
       </c>
       <c r="E26" t="n">
-        <v>20.98</v>
+        <v>25.49</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4015</v>
+        <v>0.4706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,64 +1060,64 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>48.68</v>
+        <v>41.55</v>
       </c>
       <c r="D27" t="n">
-        <v>60.73</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>24.75</v>
+        <v>65.7</v>
       </c>
       <c r="F27" t="n">
-        <v>0.43632</v>
+        <v>0.36109</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41.55</v>
+        <v>11.03</v>
       </c>
       <c r="D28" t="n">
-        <v>65.78</v>
+        <v>12.86</v>
       </c>
       <c r="E28" t="n">
-        <v>58.32</v>
+        <v>16.59</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06870999999999999</v>
+        <v>0.01385</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11.03</v>
+        <v>27.14</v>
       </c>
       <c r="D29" t="n">
-        <v>12.73</v>
+        <v>31.56</v>
       </c>
       <c r="E29" t="n">
-        <v>15.37</v>
+        <v>16.29</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00099</v>
+        <v>-0.13487</v>
       </c>
     </row>
     <row r="30">
@@ -1135,13 +1135,13 @@
         <v>332.02</v>
       </c>
       <c r="D30" t="n">
-        <v>375.93</v>
+        <v>377.17</v>
       </c>
       <c r="E30" t="n">
-        <v>13.23</v>
+        <v>13.6</v>
       </c>
       <c r="F30" t="n">
-        <v>0.154</v>
+        <v>0.2721</v>
       </c>
     </row>
     <row r="31">
@@ -1159,19 +1159,19 @@
         <v>146.38</v>
       </c>
       <c r="D31" t="n">
-        <v>217.56</v>
+        <v>215.82</v>
       </c>
       <c r="E31" t="n">
-        <v>48.63</v>
+        <v>47.44</v>
       </c>
       <c r="F31" t="n">
-        <v>0.80786</v>
+        <v>0.64206</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.14</v>
+        <v>179.43</v>
       </c>
       <c r="D32" t="n">
-        <v>31.17</v>
+        <v>190.21</v>
       </c>
       <c r="E32" t="n">
-        <v>14.85</v>
+        <v>6.01</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.17201</v>
+        <v>0.4415</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>179.43</v>
+        <v>25.99</v>
       </c>
       <c r="D33" t="n">
-        <v>192.07</v>
+        <v>37.63</v>
       </c>
       <c r="E33" t="n">
-        <v>7.04</v>
+        <v>44.79</v>
       </c>
       <c r="F33" t="n">
-        <v>0.61816</v>
+        <v>0.74041</v>
       </c>
     </row>
     <row r="34">
@@ -1231,115 +1231,115 @@
         <v>205.77</v>
       </c>
       <c r="D34" t="n">
-        <v>249.79</v>
+        <v>248.18</v>
       </c>
       <c r="E34" t="n">
-        <v>21.39</v>
+        <v>20.61</v>
       </c>
       <c r="F34" t="n">
-        <v>3.40117</v>
+        <v>3.24784</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>25.99</v>
+        <v>440.76</v>
       </c>
       <c r="D35" t="n">
-        <v>38.69</v>
+        <v>637.04</v>
       </c>
       <c r="E35" t="n">
-        <v>48.85</v>
+        <v>44.53</v>
       </c>
       <c r="F35" t="n">
-        <v>0.84088</v>
+        <v>4.16883</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>440.76</v>
+        <v>103.45</v>
       </c>
       <c r="D36" t="n">
-        <v>633.47</v>
+        <v>150.06</v>
       </c>
       <c r="E36" t="n">
-        <v>43.72</v>
+        <v>45.06</v>
       </c>
       <c r="F36" t="n">
-        <v>3.82931</v>
+        <v>1.07578</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>103.45</v>
+        <v>198.14</v>
       </c>
       <c r="D37" t="n">
-        <v>148.95</v>
+        <v>263.04</v>
       </c>
       <c r="E37" t="n">
-        <v>43.98</v>
+        <v>32.75</v>
       </c>
       <c r="F37" t="n">
-        <v>0.97007</v>
+        <v>2.16789</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>198.14</v>
+        <v>35.49</v>
       </c>
       <c r="D38" t="n">
-        <v>261.4</v>
+        <v>41.91</v>
       </c>
       <c r="E38" t="n">
-        <v>31.93</v>
+        <v>18.09</v>
       </c>
       <c r="F38" t="n">
-        <v>2.0117</v>
+        <v>0.09035</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RRC</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1348,112 +1348,112 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35.49</v>
+        <v>41.44</v>
       </c>
       <c r="D39" t="n">
-        <v>41.88</v>
+        <v>45.38</v>
       </c>
       <c r="E39" t="n">
-        <v>18.01</v>
+        <v>9.51</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08749</v>
+        <v>0.55766</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>41.44</v>
+        <v>510.39</v>
       </c>
       <c r="D40" t="n">
-        <v>45.47</v>
+        <v>643.61</v>
       </c>
       <c r="E40" t="n">
-        <v>9.73</v>
+        <v>26.1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.56647</v>
+        <v>5.95759</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>510.39</v>
+        <v>5.04</v>
       </c>
       <c r="D41" t="n">
-        <v>646.76</v>
+        <v>5.88</v>
       </c>
       <c r="E41" t="n">
-        <v>26.72</v>
+        <v>16.67</v>
       </c>
       <c r="F41" t="n">
-        <v>6.25783</v>
+        <v>0.04652</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>PSNYW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5.04</v>
+        <v>2.2</v>
       </c>
       <c r="D42" t="n">
-        <v>5.86</v>
+        <v>4.68</v>
       </c>
       <c r="E42" t="n">
-        <v>16.17</v>
+        <v>112.73</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04414</v>
+        <v>-0.01815</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PSNYW</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.2</v>
+        <v>162.11</v>
       </c>
       <c r="D43" t="n">
-        <v>4.43</v>
+        <v>177.74</v>
       </c>
       <c r="E43" t="n">
-        <v>101.36</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.04196</v>
+        <v>0.54369</v>
       </c>
     </row>
     <row r="44">
@@ -1471,19 +1471,19 @@
         <v>40.48</v>
       </c>
       <c r="D44" t="n">
-        <v>45.93</v>
+        <v>45.96</v>
       </c>
       <c r="E44" t="n">
-        <v>13.46</v>
+        <v>13.54</v>
       </c>
       <c r="F44" t="n">
-        <v>0.24173</v>
+        <v>0.24459</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1492,46 +1492,46 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>162.11</v>
+        <v>24.36</v>
       </c>
       <c r="D45" t="n">
-        <v>177.03</v>
+        <v>33.92</v>
       </c>
       <c r="E45" t="n">
-        <v>9.199999999999999</v>
+        <v>39.24</v>
       </c>
       <c r="F45" t="n">
-        <v>0.47607</v>
+        <v>0.50814</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24.36</v>
+        <v>51.98</v>
       </c>
       <c r="D46" t="n">
-        <v>33.74</v>
+        <v>66.94</v>
       </c>
       <c r="E46" t="n">
-        <v>38.53</v>
+        <v>28.78</v>
       </c>
       <c r="F46" t="n">
-        <v>0.49148</v>
+        <v>0.22461</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1540,22 +1540,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>14.49</v>
+        <v>13.01</v>
       </c>
       <c r="D47" t="n">
-        <v>19.53</v>
+        <v>17.68</v>
       </c>
       <c r="E47" t="n">
-        <v>34.78</v>
+        <v>35.9</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5797099999999999</v>
+        <v>0.39546</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1564,22 +1564,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>40.25</v>
+        <v>47.94</v>
       </c>
       <c r="D48" t="n">
-        <v>51.29</v>
+        <v>63.51</v>
       </c>
       <c r="E48" t="n">
-        <v>27.44</v>
+        <v>32.49</v>
       </c>
       <c r="F48" t="n">
-        <v>0.92317</v>
+        <v>0.82599</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1588,22 +1588,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>15.99</v>
+        <v>171.96</v>
       </c>
       <c r="D49" t="n">
-        <v>21.75</v>
+        <v>211.52</v>
       </c>
       <c r="E49" t="n">
-        <v>36.05</v>
+        <v>23.01</v>
       </c>
       <c r="F49" t="n">
-        <v>0.65376</v>
+        <v>1.93006</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>36.15</v>
+        <v>14.49</v>
       </c>
       <c r="D50" t="n">
-        <v>46.9</v>
+        <v>19.55</v>
       </c>
       <c r="E50" t="n">
-        <v>29.72</v>
+        <v>34.89</v>
       </c>
       <c r="F50" t="n">
-        <v>0.87806</v>
+        <v>0.58114</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>104.89</v>
+        <v>15.99</v>
       </c>
       <c r="D51" t="n">
-        <v>121.96</v>
+        <v>21.75</v>
       </c>
       <c r="E51" t="n">
-        <v>16.27</v>
+        <v>36.05</v>
       </c>
       <c r="F51" t="n">
-        <v>1.75968</v>
+        <v>0.65376</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>47.94</v>
+        <v>53.57</v>
       </c>
       <c r="D52" t="n">
-        <v>63.34</v>
+        <v>71.89</v>
       </c>
       <c r="E52" t="n">
-        <v>32.12</v>
+        <v>34.2</v>
       </c>
       <c r="F52" t="n">
-        <v>0.80932</v>
+        <v>0.95148</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53.57</v>
+        <v>36.15</v>
       </c>
       <c r="D53" t="n">
-        <v>71.34</v>
+        <v>46.96</v>
       </c>
       <c r="E53" t="n">
-        <v>33.17</v>
+        <v>29.9</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8991</v>
+        <v>0.88425</v>
       </c>
     </row>
     <row r="54">
@@ -1711,19 +1711,19 @@
         <v>45.57</v>
       </c>
       <c r="D54" t="n">
-        <v>56.46</v>
+        <v>56.65</v>
       </c>
       <c r="E54" t="n">
-        <v>23.9</v>
+        <v>24.31</v>
       </c>
       <c r="F54" t="n">
-        <v>0.47743</v>
+        <v>0.49553</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>52.58</v>
+        <v>17.93</v>
       </c>
       <c r="D55" t="n">
-        <v>64.91</v>
+        <v>24.5</v>
       </c>
       <c r="E55" t="n">
-        <v>23.45</v>
+        <v>36.64</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.04387</v>
+        <v>0.34498</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>110.99</v>
+        <v>38.92</v>
       </c>
       <c r="D56" t="n">
-        <v>134.88</v>
+        <v>51.52</v>
       </c>
       <c r="E56" t="n">
-        <v>21.52</v>
+        <v>32.37</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1469</v>
+        <v>0.30218</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13.01</v>
+        <v>110.99</v>
       </c>
       <c r="D57" t="n">
-        <v>17.61</v>
+        <v>135.18</v>
       </c>
       <c r="E57" t="n">
-        <v>35.36</v>
+        <v>21.79</v>
       </c>
       <c r="F57" t="n">
-        <v>0.38882</v>
+        <v>0.17548</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>171.96</v>
+        <v>74.8</v>
       </c>
       <c r="D58" t="n">
-        <v>212.71</v>
+        <v>93.14</v>
       </c>
       <c r="E58" t="n">
-        <v>23.7</v>
+        <v>24.53</v>
       </c>
       <c r="F58" t="n">
-        <v>2.04339</v>
+        <v>1.07384</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38.92</v>
+        <v>52.58</v>
       </c>
       <c r="D59" t="n">
-        <v>51.31</v>
+        <v>65.42</v>
       </c>
       <c r="E59" t="n">
-        <v>31.85</v>
+        <v>24.42</v>
       </c>
       <c r="F59" t="n">
-        <v>0.28265</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1852,22 +1852,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>17.93</v>
+        <v>31.87</v>
       </c>
       <c r="D60" t="n">
-        <v>24.39</v>
+        <v>47.41</v>
       </c>
       <c r="E60" t="n">
-        <v>36</v>
+        <v>48.76</v>
       </c>
       <c r="F60" t="n">
-        <v>0.33403</v>
+        <v>1.0579</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>74.8</v>
+        <v>103.22</v>
       </c>
       <c r="D61" t="n">
-        <v>93.09999999999999</v>
+        <v>141.18</v>
       </c>
       <c r="E61" t="n">
-        <v>24.46</v>
+        <v>36.78</v>
       </c>
       <c r="F61" t="n">
-        <v>1.06908</v>
+        <v>2.27941</v>
       </c>
     </row>
     <row r="62">
@@ -1903,13 +1903,13 @@
         <v>165.69</v>
       </c>
       <c r="D62" t="n">
-        <v>216.63</v>
+        <v>217.54</v>
       </c>
       <c r="E62" t="n">
-        <v>30.74</v>
+        <v>31.3</v>
       </c>
       <c r="F62" t="n">
-        <v>3.11009</v>
+        <v>3.19723</v>
       </c>
     </row>
     <row r="63">
@@ -1927,19 +1927,19 @@
         <v>17.26</v>
       </c>
       <c r="D63" t="n">
-        <v>19.88</v>
+        <v>19.86</v>
       </c>
       <c r="E63" t="n">
-        <v>15.18</v>
+        <v>15.05</v>
       </c>
       <c r="F63" t="n">
-        <v>0.16646</v>
+        <v>0.16437</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>41.99</v>
+        <v>40.25</v>
       </c>
       <c r="D64" t="n">
-        <v>51.44</v>
+        <v>51.35</v>
       </c>
       <c r="E64" t="n">
-        <v>22.49</v>
+        <v>27.58</v>
       </c>
       <c r="F64" t="n">
-        <v>0.50581</v>
+        <v>0.92841</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51.98</v>
+        <v>104.89</v>
       </c>
       <c r="D65" t="n">
-        <v>66.70999999999999</v>
+        <v>121.78</v>
       </c>
       <c r="E65" t="n">
-        <v>28.33</v>
+        <v>16.1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.20223</v>
+        <v>1.74253</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,16 +1996,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>103.22</v>
+        <v>41.99</v>
       </c>
       <c r="D66" t="n">
-        <v>140.59</v>
+        <v>51.44</v>
       </c>
       <c r="E66" t="n">
-        <v>36.2</v>
+        <v>22.49</v>
       </c>
       <c r="F66" t="n">
-        <v>2.22322</v>
+        <v>0.50581</v>
       </c>
     </row>
     <row r="67">
@@ -2023,43 +2023,43 @@
         <v>20.48</v>
       </c>
       <c r="D67" t="n">
-        <v>26.74</v>
+        <v>26.75</v>
       </c>
       <c r="E67" t="n">
-        <v>30.54</v>
+        <v>30.59</v>
       </c>
       <c r="F67" t="n">
-        <v>0.32489</v>
+        <v>0.32584</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>31.87</v>
+        <v>38.73</v>
       </c>
       <c r="D68" t="n">
-        <v>47.13</v>
+        <v>63.28</v>
       </c>
       <c r="E68" t="n">
-        <v>47.88</v>
+        <v>63.39</v>
       </c>
       <c r="F68" t="n">
-        <v>1.03124</v>
+        <v>0.3855</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>62.05</v>
+        <v>124.44</v>
       </c>
       <c r="D69" t="n">
-        <v>81.14</v>
+        <v>193.58</v>
       </c>
       <c r="E69" t="n">
-        <v>30.77</v>
+        <v>55.56</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.28176</v>
+        <v>2.35319</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>13.43</v>
+        <v>55.53</v>
       </c>
       <c r="D70" t="n">
-        <v>15.07</v>
+        <v>62.27</v>
       </c>
       <c r="E70" t="n">
-        <v>12.21</v>
+        <v>12.14</v>
       </c>
       <c r="F70" t="n">
-        <v>0.08663</v>
+        <v>0.75545</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2116,22 +2116,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>124.44</v>
+        <v>13.31</v>
       </c>
       <c r="D71" t="n">
-        <v>197.12</v>
+        <v>23.6</v>
       </c>
       <c r="E71" t="n">
-        <v>58.41</v>
+        <v>77.31</v>
       </c>
       <c r="F71" t="n">
-        <v>2.69104</v>
+        <v>0.58601</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>167.73</v>
+        <v>62.05</v>
       </c>
       <c r="D72" t="n">
-        <v>181.48</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>8.199999999999999</v>
+        <v>31.01</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.13029</v>
+        <v>-0.26747</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,142 +2164,142 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>38.73</v>
+        <v>13.43</v>
       </c>
       <c r="D73" t="n">
-        <v>64.36</v>
+        <v>15.03</v>
       </c>
       <c r="E73" t="n">
-        <v>66.18000000000001</v>
+        <v>11.93</v>
       </c>
       <c r="F73" t="n">
-        <v>0.48836</v>
+        <v>0.08302</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>55.53</v>
+        <v>136.06</v>
       </c>
       <c r="D74" t="n">
-        <v>61.72</v>
+        <v>169.29</v>
       </c>
       <c r="E74" t="n">
-        <v>11.14</v>
+        <v>24.42</v>
       </c>
       <c r="F74" t="n">
-        <v>0.70259</v>
+        <v>1.98149</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13.31</v>
+        <v>7.67</v>
       </c>
       <c r="D75" t="n">
-        <v>24.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>82.83</v>
+        <v>20.21</v>
       </c>
       <c r="F75" t="n">
-        <v>0.65601</v>
+        <v>0.15547</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>218.58</v>
+        <v>76.53</v>
       </c>
       <c r="D76" t="n">
-        <v>277.11</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>26.78</v>
+        <v>29.27</v>
       </c>
       <c r="F76" t="n">
-        <v>0.43734</v>
+        <v>1.63127</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>136.06</v>
+        <v>82.31</v>
       </c>
       <c r="D77" t="n">
-        <v>169.4</v>
+        <v>129.6</v>
       </c>
       <c r="E77" t="n">
-        <v>24.5</v>
+        <v>57.45</v>
       </c>
       <c r="F77" t="n">
-        <v>1.99197</v>
+        <v>2.83088</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7.67</v>
+        <v>56.4</v>
       </c>
       <c r="D78" t="n">
-        <v>9.25</v>
+        <v>79.17</v>
       </c>
       <c r="E78" t="n">
-        <v>20.6</v>
+        <v>40.37</v>
       </c>
       <c r="F78" t="n">
-        <v>0.15833</v>
+        <v>1.9744</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2308,22 +2308,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>82.31</v>
+        <v>31.03</v>
       </c>
       <c r="D79" t="n">
-        <v>131.9</v>
+        <v>45.74</v>
       </c>
       <c r="E79" t="n">
-        <v>60.25</v>
+        <v>47.41</v>
       </c>
       <c r="F79" t="n">
-        <v>3.05027</v>
+        <v>0.94098</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2332,112 +2332,112 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>56.4</v>
+        <v>18.94</v>
       </c>
       <c r="D80" t="n">
-        <v>79.39</v>
+        <v>23.95</v>
       </c>
       <c r="E80" t="n">
-        <v>40.75</v>
+        <v>26.45</v>
       </c>
       <c r="F80" t="n">
-        <v>1.99488</v>
+        <v>0.15456</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>76.53</v>
+        <v>352.83</v>
       </c>
       <c r="D81" t="n">
-        <v>98.67</v>
+        <v>496.77</v>
       </c>
       <c r="E81" t="n">
-        <v>28.93</v>
+        <v>40.79</v>
       </c>
       <c r="F81" t="n">
-        <v>1.60651</v>
+        <v>2.38475</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>31.03</v>
+        <v>59.71</v>
       </c>
       <c r="D82" t="n">
-        <v>45.7</v>
+        <v>80.02</v>
       </c>
       <c r="E82" t="n">
-        <v>47.28</v>
+        <v>34.01</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9371699999999999</v>
+        <v>1.28479</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>18.94</v>
+        <v>44.39</v>
       </c>
       <c r="D83" t="n">
-        <v>23.86</v>
+        <v>60.34</v>
       </c>
       <c r="E83" t="n">
-        <v>25.98</v>
+        <v>35.93</v>
       </c>
       <c r="F83" t="n">
-        <v>0.14599</v>
+        <v>0.25495</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>39.54</v>
+        <v>170.28</v>
       </c>
       <c r="D84" t="n">
-        <v>50.34</v>
+        <v>242.28</v>
       </c>
       <c r="E84" t="n">
-        <v>27.31</v>
+        <v>42.28</v>
       </c>
       <c r="F84" t="n">
-        <v>0.13987</v>
+        <v>-1.34406</v>
       </c>
     </row>
     <row r="85">
@@ -2455,19 +2455,19 @@
         <v>136.68</v>
       </c>
       <c r="D85" t="n">
-        <v>154.34</v>
+        <v>156.99</v>
       </c>
       <c r="E85" t="n">
-        <v>12.92</v>
+        <v>14.86</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.98185</v>
+        <v>-0.72946</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2476,22 +2476,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>352.83</v>
+        <v>107.27</v>
       </c>
       <c r="D86" t="n">
-        <v>500.03</v>
+        <v>172.57</v>
       </c>
       <c r="E86" t="n">
-        <v>41.72</v>
+        <v>60.87</v>
       </c>
       <c r="F86" t="n">
-        <v>2.6957</v>
+        <v>-0.66772</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2500,16 +2500,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>44.39</v>
+        <v>166.5</v>
       </c>
       <c r="D87" t="n">
-        <v>60.25</v>
+        <v>195.23</v>
       </c>
       <c r="E87" t="n">
-        <v>35.73</v>
+        <v>17.26</v>
       </c>
       <c r="F87" t="n">
-        <v>0.24638</v>
+        <v>1.01132</v>
       </c>
     </row>
     <row r="88">
@@ -2527,19 +2527,19 @@
         <v>42.46</v>
       </c>
       <c r="D88" t="n">
-        <v>73.62</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>73.39</v>
+        <v>69.22</v>
       </c>
       <c r="F88" t="n">
-        <v>2.0488</v>
+        <v>1.88023</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>59.71</v>
+        <v>49.87</v>
       </c>
       <c r="D89" t="n">
-        <v>80.12</v>
+        <v>62.3</v>
       </c>
       <c r="E89" t="n">
-        <v>34.19</v>
+        <v>24.92</v>
       </c>
       <c r="F89" t="n">
-        <v>1.29479</v>
+        <v>0.41873</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2572,286 +2572,286 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>170.28</v>
+        <v>19.32</v>
       </c>
       <c r="D90" t="n">
-        <v>251.84</v>
+        <v>23.95</v>
       </c>
       <c r="E90" t="n">
-        <v>47.9</v>
+        <v>23.99</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.4332</v>
+        <v>0.01811</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>166.5</v>
+        <v>10.51</v>
       </c>
       <c r="D91" t="n">
-        <v>195.41</v>
+        <v>15.3</v>
       </c>
       <c r="E91" t="n">
-        <v>17.36</v>
+        <v>45.58</v>
       </c>
       <c r="F91" t="n">
-        <v>1.02847</v>
+        <v>0.36694</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>49.87</v>
+        <v>36.09</v>
       </c>
       <c r="D92" t="n">
-        <v>63.51</v>
+        <v>38.82</v>
       </c>
       <c r="E92" t="n">
-        <v>27.36</v>
+        <v>7.56</v>
       </c>
       <c r="F92" t="n">
-        <v>0.53445</v>
+        <v>0.04877</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>142.52</v>
+        <v>60.37</v>
       </c>
       <c r="D93" t="n">
-        <v>180.09</v>
+        <v>78.78</v>
       </c>
       <c r="E93" t="n">
-        <v>26.36</v>
+        <v>30.5</v>
       </c>
       <c r="F93" t="n">
-        <v>1.807</v>
+        <v>1.00216</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>107.27</v>
+        <v>62.12</v>
       </c>
       <c r="D94" t="n">
-        <v>173.36</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="E94" t="n">
-        <v>61.61</v>
+        <v>28.67</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.59248</v>
+        <v>0.93296</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10.51</v>
+        <v>247.22</v>
       </c>
       <c r="D95" t="n">
-        <v>15.23</v>
+        <v>297.26</v>
       </c>
       <c r="E95" t="n">
-        <v>44.86</v>
+        <v>20.24</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3598</v>
+        <v>2.46873</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>60.37</v>
+        <v>48.79</v>
       </c>
       <c r="D96" t="n">
-        <v>78.7</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="E96" t="n">
-        <v>30.36</v>
+        <v>38.49</v>
       </c>
       <c r="F96" t="n">
-        <v>0.99455</v>
+        <v>0.33897</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>36.09</v>
+        <v>102.17</v>
       </c>
       <c r="D97" t="n">
-        <v>38.88</v>
+        <v>135.51</v>
       </c>
       <c r="E97" t="n">
-        <v>7.72</v>
+        <v>32.63</v>
       </c>
       <c r="F97" t="n">
-        <v>0.05401</v>
+        <v>1.43529</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>62.12</v>
+        <v>275.27</v>
       </c>
       <c r="D98" t="n">
-        <v>79.76000000000001</v>
+        <v>353.11</v>
       </c>
       <c r="E98" t="n">
-        <v>28.4</v>
+        <v>28.28</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9172400000000001</v>
+        <v>-1.49324</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>102.17</v>
+        <v>76.55</v>
       </c>
       <c r="D99" t="n">
-        <v>134.93</v>
+        <v>102.61</v>
       </c>
       <c r="E99" t="n">
-        <v>32.06</v>
+        <v>34.04</v>
       </c>
       <c r="F99" t="n">
-        <v>1.38005</v>
+        <v>-0.89647</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>247.22</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D100" t="n">
-        <v>297.56</v>
+        <v>102.4</v>
       </c>
       <c r="E100" t="n">
-        <v>20.36</v>
+        <v>36.56</v>
       </c>
       <c r="F100" t="n">
-        <v>2.4973</v>
+        <v>1.20692</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>48.79</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D101" t="n">
-        <v>67.77</v>
+        <v>123.54</v>
       </c>
       <c r="E101" t="n">
-        <v>38.9</v>
+        <v>62.47</v>
       </c>
       <c r="F101" t="n">
-        <v>0.35802</v>
+        <v>3.02739</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2860,22 +2860,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>275.27</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>354.76</v>
+        <v>95.06</v>
       </c>
       <c r="E102" t="n">
-        <v>28.88</v>
+        <v>13.41</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.33658</v>
+        <v>0.23447</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2884,22 +2884,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>150.12</v>
+        <v>125.73</v>
       </c>
       <c r="D103" t="n">
-        <v>261.45</v>
+        <v>195.59</v>
       </c>
       <c r="E103" t="n">
-        <v>74.16</v>
+        <v>55.56</v>
       </c>
       <c r="F103" t="n">
-        <v>7.51054</v>
+        <v>0.83519</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2908,16 +2908,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>83.81999999999999</v>
+        <v>150.12</v>
       </c>
       <c r="D104" t="n">
-        <v>95.29000000000001</v>
+        <v>255.41</v>
       </c>
       <c r="E104" t="n">
-        <v>13.68</v>
+        <v>70.14</v>
       </c>
       <c r="F104" t="n">
-        <v>0.25637</v>
+        <v>6.93578</v>
       </c>
     </row>
     <row r="105">
@@ -2935,835 +2935,835 @@
         <v>140.71</v>
       </c>
       <c r="D105" t="n">
-        <v>185.79</v>
+        <v>185.9</v>
       </c>
       <c r="E105" t="n">
-        <v>32.04</v>
+        <v>32.12</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.66379</v>
+        <v>-0.65379</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>125.73</v>
+        <v>141.17</v>
       </c>
       <c r="D106" t="n">
-        <v>202.56</v>
+        <v>177</v>
       </c>
       <c r="E106" t="n">
-        <v>61.11</v>
+        <v>25.38</v>
       </c>
       <c r="F106" t="n">
-        <v>1.499</v>
+        <v>1.15544</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>76.04000000000001</v>
+        <v>33.22</v>
       </c>
       <c r="D107" t="n">
-        <v>125.49</v>
+        <v>38.84</v>
       </c>
       <c r="E107" t="n">
-        <v>65.03</v>
+        <v>16.92</v>
       </c>
       <c r="F107" t="n">
-        <v>3.21311</v>
+        <v>0.12624</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>123.42</v>
+        <v>450.75</v>
       </c>
       <c r="D108" t="n">
-        <v>165.82</v>
+        <v>544.3200000000001</v>
       </c>
       <c r="E108" t="n">
-        <v>34.36</v>
+        <v>20.76</v>
       </c>
       <c r="F108" t="n">
-        <v>0.10343</v>
+        <v>2.42297</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>76.55</v>
+        <v>32.47</v>
       </c>
       <c r="D109" t="n">
-        <v>104.01</v>
+        <v>38.62</v>
       </c>
       <c r="E109" t="n">
-        <v>35.87</v>
+        <v>18.96</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.76313</v>
+        <v>0.35415</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>74.98999999999999</v>
+        <v>48.87</v>
       </c>
       <c r="D110" t="n">
-        <v>104.39</v>
+        <v>58.8</v>
       </c>
       <c r="E110" t="n">
-        <v>39.21</v>
+        <v>20.32</v>
       </c>
       <c r="F110" t="n">
-        <v>1.39645</v>
+        <v>-0.23533</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>61.28</v>
+        <v>16.44</v>
       </c>
       <c r="D111" t="n">
-        <v>73.06999999999999</v>
+        <v>33.61</v>
       </c>
       <c r="E111" t="n">
-        <v>19.24</v>
+        <v>104.44</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.48667</v>
+        <v>0.45364</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>141.17</v>
+        <v>2.86</v>
       </c>
       <c r="D112" t="n">
-        <v>176.57</v>
+        <v>3.14</v>
       </c>
       <c r="E112" t="n">
-        <v>25.07</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>1.11401</v>
+        <v>0.02348</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>33.22</v>
+        <v>14.94</v>
       </c>
       <c r="D113" t="n">
-        <v>39.15</v>
+        <v>19.53</v>
       </c>
       <c r="E113" t="n">
-        <v>17.85</v>
+        <v>30.72</v>
       </c>
       <c r="F113" t="n">
-        <v>0.15577</v>
+        <v>0.51817</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>32.47</v>
+        <v>53.82</v>
       </c>
       <c r="D114" t="n">
-        <v>39.04</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>20.23</v>
+        <v>37.63</v>
       </c>
       <c r="F114" t="n">
-        <v>0.39367</v>
+        <v>0.46133</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>450.75</v>
+        <v>121.48</v>
       </c>
       <c r="D115" t="n">
-        <v>539.5</v>
+        <v>146.29</v>
       </c>
       <c r="E115" t="n">
-        <v>19.69</v>
+        <v>20.42</v>
       </c>
       <c r="F115" t="n">
-        <v>1.96392</v>
+        <v>0.10495</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>48.87</v>
+        <v>19.82</v>
       </c>
       <c r="D116" t="n">
-        <v>59.26</v>
+        <v>25.44</v>
       </c>
       <c r="E116" t="n">
-        <v>21.25</v>
+        <v>28.36</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.192</v>
+        <v>0.28905</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>14.94</v>
+        <v>361.32</v>
       </c>
       <c r="D117" t="n">
-        <v>19.56</v>
+        <v>423.47</v>
       </c>
       <c r="E117" t="n">
-        <v>30.92</v>
+        <v>17.2</v>
       </c>
       <c r="F117" t="n">
-        <v>0.52103</v>
+        <v>4.16096</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>19.82</v>
+        <v>43.67</v>
       </c>
       <c r="D118" t="n">
-        <v>25.15</v>
+        <v>47.13</v>
       </c>
       <c r="E118" t="n">
-        <v>26.87</v>
+        <v>7.92</v>
       </c>
       <c r="F118" t="n">
-        <v>0.26096</v>
+        <v>0.04408</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>53.82</v>
+        <v>140.19</v>
       </c>
       <c r="D119" t="n">
-        <v>74.44</v>
+        <v>146.64</v>
       </c>
       <c r="E119" t="n">
-        <v>38.31</v>
+        <v>4.6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.49656</v>
+        <v>0.02529</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>16.44</v>
+        <v>15.03</v>
       </c>
       <c r="D120" t="n">
-        <v>33.38</v>
+        <v>18.72</v>
       </c>
       <c r="E120" t="n">
-        <v>103.04</v>
+        <v>24.55</v>
       </c>
       <c r="F120" t="n">
-        <v>0.43174</v>
+        <v>0.1295</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2.86</v>
+        <v>195.11</v>
       </c>
       <c r="D121" t="n">
-        <v>3.17</v>
+        <v>248.3</v>
       </c>
       <c r="E121" t="n">
-        <v>11.01</v>
+        <v>27.26</v>
       </c>
       <c r="F121" t="n">
-        <v>0.02634</v>
+        <v>0.68889</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>121.48</v>
+        <v>277.69</v>
       </c>
       <c r="D122" t="n">
-        <v>145.67</v>
+        <v>328.55</v>
       </c>
       <c r="E122" t="n">
-        <v>19.91</v>
+        <v>18.32</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0459</v>
+        <v>0.44306</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>361.32</v>
+        <v>275.99</v>
       </c>
       <c r="D123" t="n">
-        <v>424.32</v>
+        <v>318.23</v>
       </c>
       <c r="E123" t="n">
-        <v>17.44</v>
+        <v>15.3</v>
       </c>
       <c r="F123" t="n">
-        <v>4.24191</v>
+        <v>1.98561</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>43.67</v>
+        <v>182.82</v>
       </c>
       <c r="D124" t="n">
-        <v>47.19</v>
+        <v>229.65</v>
       </c>
       <c r="E124" t="n">
-        <v>8.07</v>
+        <v>25.62</v>
       </c>
       <c r="F124" t="n">
-        <v>0.05027</v>
+        <v>-1.28339</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>140.19</v>
+        <v>23.85</v>
       </c>
       <c r="D125" t="n">
-        <v>146.88</v>
+        <v>34.15</v>
       </c>
       <c r="E125" t="n">
-        <v>4.77</v>
+        <v>43.19</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04815</v>
+        <v>0.01267</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>15.03</v>
+        <v>73.75</v>
       </c>
       <c r="D126" t="n">
-        <v>18.69</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E126" t="n">
-        <v>24.35</v>
+        <v>27.13</v>
       </c>
       <c r="F126" t="n">
-        <v>0.12664</v>
+        <v>0.46269</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>73.75</v>
+        <v>36.25</v>
       </c>
       <c r="D127" t="n">
-        <v>94.17</v>
+        <v>41.47</v>
       </c>
       <c r="E127" t="n">
-        <v>27.69</v>
+        <v>14.4</v>
       </c>
       <c r="F127" t="n">
-        <v>0.50174</v>
+        <v>0.1536</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>275.99</v>
+        <v>9.85</v>
       </c>
       <c r="D128" t="n">
-        <v>321.39</v>
+        <v>14.03</v>
       </c>
       <c r="E128" t="n">
-        <v>16.45</v>
+        <v>42.44</v>
       </c>
       <c r="F128" t="n">
-        <v>2.28704</v>
+        <v>0.47594</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>182.82</v>
+        <v>309.78</v>
       </c>
       <c r="D129" t="n">
-        <v>233.65</v>
+        <v>341.9</v>
       </c>
       <c r="E129" t="n">
-        <v>27.81</v>
+        <v>10.37</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.90196</v>
+        <v>-0.61642</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>23.85</v>
+        <v>190.4</v>
       </c>
       <c r="D130" t="n">
-        <v>33.53</v>
+        <v>221.15</v>
       </c>
       <c r="E130" t="n">
-        <v>40.61</v>
+        <v>16.15</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.0459</v>
+        <v>0.57638</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>36.25</v>
+        <v>33.54</v>
       </c>
       <c r="D131" t="n">
-        <v>41.44</v>
+        <v>42.16</v>
       </c>
       <c r="E131" t="n">
-        <v>14.33</v>
+        <v>25.7</v>
       </c>
       <c r="F131" t="n">
-        <v>0.15122</v>
+        <v>0.13689</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>9.85</v>
+        <v>63.54</v>
       </c>
       <c r="D132" t="n">
-        <v>14.21</v>
+        <v>71.28</v>
       </c>
       <c r="E132" t="n">
-        <v>44.26</v>
+        <v>12.18</v>
       </c>
       <c r="F132" t="n">
-        <v>0.49308</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>121.13</v>
+        <v>529.12</v>
       </c>
       <c r="D133" t="n">
-        <v>138.41</v>
+        <v>683.88</v>
       </c>
       <c r="E133" t="n">
-        <v>14.27</v>
+        <v>29.25</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1891</v>
+        <v>9.48836</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>33.54</v>
+        <v>57.4</v>
       </c>
       <c r="D134" t="n">
-        <v>42.26</v>
+        <v>103.61</v>
       </c>
       <c r="E134" t="n">
-        <v>26</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>0.14642</v>
+        <v>0.52495</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>63.54</v>
+        <v>186.61</v>
       </c>
       <c r="D135" t="n">
-        <v>70.78</v>
+        <v>247.29</v>
       </c>
       <c r="E135" t="n">
-        <v>11.39</v>
+        <v>32.52</v>
       </c>
       <c r="F135" t="n">
-        <v>0.32638</v>
+        <v>0.21288</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>190.4</v>
+        <v>43.3</v>
       </c>
       <c r="D136" t="n">
-        <v>221.04</v>
+        <v>72.34</v>
       </c>
       <c r="E136" t="n">
-        <v>16.09</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F136" t="n">
-        <v>0.56543</v>
+        <v>0.008569999999999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>85.34999999999999</v>
+        <v>63.16</v>
       </c>
       <c r="D137" t="n">
-        <v>108.32</v>
+        <v>100.71</v>
       </c>
       <c r="E137" t="n">
-        <v>26.91</v>
+        <v>59.45</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.34839</v>
+        <v>1.3584</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>529.12</v>
+        <v>73.42</v>
       </c>
       <c r="D138" t="n">
-        <v>683.13</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>29.11</v>
+        <v>22.26</v>
       </c>
       <c r="F138" t="n">
-        <v>9.41741</v>
+        <v>0.70783</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>57.4</v>
+        <v>161.91</v>
       </c>
       <c r="D139" t="n">
-        <v>104.2</v>
+        <v>209.26</v>
       </c>
       <c r="E139" t="n">
-        <v>81.53</v>
+        <v>29.24</v>
       </c>
       <c r="F139" t="n">
-        <v>0.58114</v>
+        <v>-1.53704</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3772,22 +3772,22 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>73.42</v>
+        <v>250.4</v>
       </c>
       <c r="D140" t="n">
-        <v>88.59999999999999</v>
+        <v>323.85</v>
       </c>
       <c r="E140" t="n">
-        <v>20.68</v>
+        <v>29.33</v>
       </c>
       <c r="F140" t="n">
-        <v>0.59771</v>
+        <v>-3.62754</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3796,22 +3796,22 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>161.91</v>
+        <v>102.87</v>
       </c>
       <c r="D141" t="n">
-        <v>207.75</v>
+        <v>174.73</v>
       </c>
       <c r="E141" t="n">
-        <v>28.31</v>
+        <v>69.86</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.68085</v>
+        <v>-0.36801</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3820,22 +3820,22 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>43.3</v>
+        <v>26.18</v>
       </c>
       <c r="D142" t="n">
-        <v>72.28</v>
+        <v>36.72</v>
       </c>
       <c r="E142" t="n">
-        <v>66.92</v>
+        <v>40.26</v>
       </c>
       <c r="F142" t="n">
-        <v>0.00238</v>
+        <v>0.23738</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3844,910 +3844,910 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>92.38</v>
+        <v>438.34</v>
       </c>
       <c r="D143" t="n">
-        <v>101.15</v>
+        <v>641.49</v>
       </c>
       <c r="E143" t="n">
-        <v>9.5</v>
+        <v>46.35</v>
       </c>
       <c r="F143" t="n">
-        <v>0.10255</v>
+        <v>3.86233</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>186.61</v>
+        <v>163.43</v>
       </c>
       <c r="D144" t="n">
-        <v>246.51</v>
+        <v>198.63</v>
       </c>
       <c r="E144" t="n">
-        <v>32.1</v>
+        <v>21.54</v>
       </c>
       <c r="F144" t="n">
-        <v>0.13859</v>
+        <v>1.4774</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>438.34</v>
+        <v>107.27</v>
       </c>
       <c r="D145" t="n">
-        <v>633.62</v>
+        <v>144.93</v>
       </c>
       <c r="E145" t="n">
-        <v>44.55</v>
+        <v>35.11</v>
       </c>
       <c r="F145" t="n">
-        <v>3.11233</v>
+        <v>-0.92318</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>5563.62</v>
+        <v>55.52</v>
       </c>
       <c r="D146" t="n">
-        <v>6280.62</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="E146" t="n">
-        <v>12.89</v>
+        <v>67.89</v>
       </c>
       <c r="F146" t="n">
-        <v>-31.16585</v>
+        <v>1.95833</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>63.16</v>
+        <v>99.3</v>
       </c>
       <c r="D147" t="n">
-        <v>100.17</v>
+        <v>153.74</v>
       </c>
       <c r="E147" t="n">
-        <v>58.6</v>
+        <v>54.82</v>
       </c>
       <c r="F147" t="n">
-        <v>1.30697</v>
+        <v>2.14918</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>102.87</v>
+        <v>197.73</v>
       </c>
       <c r="D148" t="n">
-        <v>175.46</v>
+        <v>222.98</v>
       </c>
       <c r="E148" t="n">
-        <v>70.56</v>
+        <v>12.77</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.29873</v>
+        <v>0.93505</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>26.18</v>
+        <v>79.58</v>
       </c>
       <c r="D149" t="n">
-        <v>36.78</v>
+        <v>98.39</v>
       </c>
       <c r="E149" t="n">
-        <v>40.49</v>
+        <v>23.64</v>
       </c>
       <c r="F149" t="n">
-        <v>0.2431</v>
+        <v>-0.83448</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>163.43</v>
+        <v>725.17</v>
       </c>
       <c r="D150" t="n">
-        <v>199.15</v>
+        <v>899.3200000000001</v>
       </c>
       <c r="E150" t="n">
-        <v>21.85</v>
+        <v>24.02</v>
       </c>
       <c r="F150" t="n">
-        <v>1.52644</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>55.52</v>
+        <v>12.64</v>
       </c>
       <c r="D151" t="n">
-        <v>93.45999999999999</v>
+        <v>18.24</v>
       </c>
       <c r="E151" t="n">
-        <v>68.34</v>
+        <v>44.3</v>
       </c>
       <c r="F151" t="n">
-        <v>1.98214</v>
+        <v>0.25874</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>99.3</v>
+        <v>417.83</v>
       </c>
       <c r="D152" t="n">
-        <v>152.34</v>
+        <v>558.9</v>
       </c>
       <c r="E152" t="n">
-        <v>53.41</v>
+        <v>33.76</v>
       </c>
       <c r="F152" t="n">
-        <v>2.01537</v>
+        <v>3.8155</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>725.17</v>
+        <v>255.54</v>
       </c>
       <c r="D153" t="n">
-        <v>895.48</v>
+        <v>365.08</v>
       </c>
       <c r="E153" t="n">
-        <v>23.49</v>
+        <v>42.87</v>
       </c>
       <c r="F153" t="n">
-        <v>2.09128</v>
+        <v>3.26755</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>197.73</v>
+        <v>32.32</v>
       </c>
       <c r="D154" t="n">
-        <v>225.51</v>
+        <v>37.84</v>
       </c>
       <c r="E154" t="n">
-        <v>14.05</v>
+        <v>17.08</v>
       </c>
       <c r="F154" t="n">
-        <v>1.17553</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>79.58</v>
+        <v>699965</v>
       </c>
       <c r="D155" t="n">
-        <v>97.92</v>
+        <v>773432.0600000001</v>
       </c>
       <c r="E155" t="n">
-        <v>23.05</v>
+        <v>10.5</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.87924</v>
+        <v>3644.07953</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>QGEN</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>32.63</v>
+        <v>139.71</v>
       </c>
       <c r="D156" t="n">
-        <v>42.99</v>
+        <v>193.84</v>
       </c>
       <c r="E156" t="n">
-        <v>31.75</v>
+        <v>38.74</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.21737</v>
+        <v>2.08671</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>417.83</v>
+        <v>45.37</v>
       </c>
       <c r="D157" t="n">
-        <v>559.46</v>
+        <v>143.77</v>
       </c>
       <c r="E157" t="n">
-        <v>33.9</v>
+        <v>216.88</v>
       </c>
       <c r="F157" t="n">
-        <v>3.86931</v>
+        <v>5.51342</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>383.99</v>
+        <v>112.47</v>
       </c>
       <c r="D158" t="n">
-        <v>472.52</v>
+        <v>137.79</v>
       </c>
       <c r="E158" t="n">
-        <v>23.05</v>
+        <v>22.51</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.18266</v>
+        <v>0.54053</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>255.54</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D159" t="n">
-        <v>365.08</v>
+        <v>140.14</v>
       </c>
       <c r="E159" t="n">
-        <v>42.87</v>
+        <v>70.36</v>
       </c>
       <c r="F159" t="n">
-        <v>3.26755</v>
+        <v>1.6294</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>12.64</v>
+        <v>156.66</v>
       </c>
       <c r="D160" t="n">
-        <v>18.32</v>
+        <v>269.5</v>
       </c>
       <c r="E160" t="n">
-        <v>44.9</v>
+        <v>72.03</v>
       </c>
       <c r="F160" t="n">
-        <v>0.26593</v>
+        <v>3.04062</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>699965</v>
+        <v>40.41</v>
       </c>
       <c r="D161" t="n">
-        <v>772763.12</v>
+        <v>52.94</v>
       </c>
       <c r="E161" t="n">
-        <v>10.4</v>
+        <v>31.01</v>
       </c>
       <c r="F161" t="n">
-        <v>3580.3712</v>
+        <v>0.06766999999999999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>139.71</v>
+        <v>197.38</v>
       </c>
       <c r="D162" t="n">
-        <v>193.18</v>
+        <v>262.94</v>
       </c>
       <c r="E162" t="n">
-        <v>38.27</v>
+        <v>33.22</v>
       </c>
       <c r="F162" t="n">
-        <v>2.02385</v>
+        <v>1.09884</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>45.37</v>
+        <v>393.42</v>
       </c>
       <c r="D163" t="n">
-        <v>142.61</v>
+        <v>620.48</v>
       </c>
       <c r="E163" t="n">
-        <v>214.33</v>
+        <v>57.71</v>
       </c>
       <c r="F163" t="n">
-        <v>5.40295</v>
+        <v>1.40198</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>112.47</v>
+        <v>74.63</v>
       </c>
       <c r="D164" t="n">
-        <v>137.75</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E164" t="n">
-        <v>22.48</v>
+        <v>18.86</v>
       </c>
       <c r="F164" t="n">
-        <v>0.53672</v>
+        <v>0.05992</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>82.26000000000001</v>
+        <v>465.4</v>
       </c>
       <c r="D165" t="n">
-        <v>138.32</v>
+        <v>516.77</v>
       </c>
       <c r="E165" t="n">
-        <v>68.15000000000001</v>
+        <v>11.04</v>
       </c>
       <c r="F165" t="n">
-        <v>1.45607</v>
+        <v>2.46652</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>156.66</v>
+        <v>153.25</v>
       </c>
       <c r="D166" t="n">
-        <v>271.1</v>
+        <v>194.09</v>
       </c>
       <c r="E166" t="n">
-        <v>73.05</v>
+        <v>26.65</v>
       </c>
       <c r="F166" t="n">
-        <v>3.19301</v>
+        <v>1.57313</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>40.41</v>
+        <v>155.75</v>
       </c>
       <c r="D167" t="n">
-        <v>52.52</v>
+        <v>265.01</v>
       </c>
       <c r="E167" t="n">
-        <v>29.97</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F167" t="n">
-        <v>0.02767</v>
+        <v>5.59667</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>197.38</v>
+        <v>20.96</v>
       </c>
       <c r="D168" t="n">
-        <v>263.37</v>
+        <v>25.77</v>
       </c>
       <c r="E168" t="n">
-        <v>33.43</v>
+        <v>22.95</v>
       </c>
       <c r="F168" t="n">
-        <v>1.13979</v>
+        <v>0.24889</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>393.42</v>
+        <v>223.65</v>
       </c>
       <c r="D169" t="n">
-        <v>618.02</v>
+        <v>396.95</v>
       </c>
       <c r="E169" t="n">
-        <v>57.09</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>1.16794</v>
+        <v>11.65836</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>465.4</v>
+        <v>40.59</v>
       </c>
       <c r="D170" t="n">
-        <v>514.51</v>
+        <v>57.63</v>
       </c>
       <c r="E170" t="n">
-        <v>10.55</v>
+        <v>41.98</v>
       </c>
       <c r="F170" t="n">
-        <v>2.25176</v>
+        <v>1.55876</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>153.25</v>
+        <v>128.43</v>
       </c>
       <c r="D171" t="n">
-        <v>194.32</v>
+        <v>153.79</v>
       </c>
       <c r="E171" t="n">
-        <v>26.8</v>
+        <v>19.75</v>
       </c>
       <c r="F171" t="n">
-        <v>1.59503</v>
+        <v>1.24532</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>20.96</v>
+        <v>213.69</v>
       </c>
       <c r="D172" t="n">
-        <v>25.72</v>
+        <v>410.73</v>
       </c>
       <c r="E172" t="n">
-        <v>22.71</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>0.24413</v>
+        <v>10.40258</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>155.75</v>
+        <v>66.95</v>
       </c>
       <c r="D173" t="n">
-        <v>264</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E173" t="n">
-        <v>69.5</v>
+        <v>29.35</v>
       </c>
       <c r="F173" t="n">
-        <v>5.50048</v>
+        <v>1.36722</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>40.59</v>
+        <v>18.71</v>
       </c>
       <c r="D174" t="n">
-        <v>57.65</v>
+        <v>21.34</v>
       </c>
       <c r="E174" t="n">
-        <v>42.02</v>
+        <v>14.06</v>
       </c>
       <c r="F174" t="n">
-        <v>1.56019</v>
+        <v>0.09182</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>83.51000000000001</v>
+        <v>112.5</v>
       </c>
       <c r="D175" t="n">
-        <v>96.56999999999999</v>
+        <v>190.67</v>
       </c>
       <c r="E175" t="n">
-        <v>15.64</v>
+        <v>69.48</v>
       </c>
       <c r="F175" t="n">
-        <v>0.64538</v>
+        <v>-0.51289</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>128.43</v>
+        <v>10.49</v>
       </c>
       <c r="D176" t="n">
-        <v>153.21</v>
+        <v>19.98</v>
       </c>
       <c r="E176" t="n">
-        <v>19.29</v>
+        <v>90.47</v>
       </c>
       <c r="F176" t="n">
-        <v>1.19009</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>213.69</v>
+        <v>32.36</v>
       </c>
       <c r="D177" t="n">
-        <v>408.39</v>
+        <v>55.17</v>
       </c>
       <c r="E177" t="n">
-        <v>91.11</v>
+        <v>70.47</v>
       </c>
       <c r="F177" t="n">
-        <v>10.17924</v>
+        <v>0.76641</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>223.65</v>
+        <v>118.05</v>
       </c>
       <c r="D178" t="n">
-        <v>391.67</v>
+        <v>193.89</v>
       </c>
       <c r="E178" t="n">
-        <v>75.13</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="F178" t="n">
-        <v>11.15527</v>
+        <v>2.28457</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>18.71</v>
+        <v>57.15</v>
       </c>
       <c r="D179" t="n">
-        <v>21.38</v>
+        <v>189.81</v>
       </c>
       <c r="E179" t="n">
-        <v>14.24</v>
+        <v>232.13</v>
       </c>
       <c r="F179" t="n">
-        <v>0.09515999999999999</v>
+        <v>4.93853</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>66.95</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D180" t="n">
-        <v>86.83</v>
+        <v>175.65</v>
       </c>
       <c r="E180" t="n">
-        <v>29.7</v>
+        <v>123.47</v>
       </c>
       <c r="F180" t="n">
-        <v>1.3896</v>
+        <v>1.12337</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>78.59999999999999</v>
+        <v>17.89</v>
       </c>
       <c r="D181" t="n">
-        <v>175.15</v>
+        <v>31.23</v>
       </c>
       <c r="E181" t="n">
-        <v>122.84</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="F181" t="n">
-        <v>1.07576</v>
+        <v>0.39427</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4780,22 +4780,22 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>34.41</v>
+        <v>151.43</v>
       </c>
       <c r="D182" t="n">
-        <v>68.81</v>
+        <v>266.67</v>
       </c>
       <c r="E182" t="n">
-        <v>99.97</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F182" t="n">
-        <v>0.305</v>
+        <v>1.96631</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4804,22 +4804,22 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>76.7</v>
+        <v>188.79</v>
       </c>
       <c r="D183" t="n">
-        <v>170.64</v>
+        <v>276.53</v>
       </c>
       <c r="E183" t="n">
-        <v>122.48</v>
+        <v>46.47</v>
       </c>
       <c r="F183" t="n">
-        <v>1.88937</v>
+        <v>-0.99091</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4828,22 +4828,22 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>166.99</v>
+        <v>62.93</v>
       </c>
       <c r="D184" t="n">
-        <v>331.36</v>
+        <v>190.45</v>
       </c>
       <c r="E184" t="n">
-        <v>98.43000000000001</v>
+        <v>202.64</v>
       </c>
       <c r="F184" t="n">
-        <v>9.837569999999999</v>
+        <v>7.34012</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4852,22 +4852,22 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>17.89</v>
+        <v>117.65</v>
       </c>
       <c r="D185" t="n">
-        <v>31.22</v>
+        <v>242.36</v>
       </c>
       <c r="E185" t="n">
-        <v>74.48</v>
+        <v>106</v>
       </c>
       <c r="F185" t="n">
-        <v>0.39284</v>
+        <v>1.81283</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4876,22 +4876,22 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>188.79</v>
+        <v>120.88</v>
       </c>
       <c r="D186" t="n">
-        <v>278.2</v>
+        <v>209.62</v>
       </c>
       <c r="E186" t="n">
-        <v>47.36</v>
+        <v>73.41</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.83234</v>
+        <v>-0.40223</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4900,22 +4900,22 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>32.36</v>
+        <v>105.37</v>
       </c>
       <c r="D187" t="n">
-        <v>54.94</v>
+        <v>230.27</v>
       </c>
       <c r="E187" t="n">
-        <v>69.78</v>
+        <v>118.53</v>
       </c>
       <c r="F187" t="n">
-        <v>0.74498</v>
+        <v>-1.24495</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4924,22 +4924,22 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>43.81</v>
+        <v>34.41</v>
       </c>
       <c r="D188" t="n">
-        <v>100.11</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E188" t="n">
-        <v>128.51</v>
+        <v>97.59</v>
       </c>
       <c r="F188" t="n">
-        <v>0.69474</v>
+        <v>0.22691</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4948,22 +4948,22 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>121.11</v>
+        <v>18.26</v>
       </c>
       <c r="D189" t="n">
-        <v>326.72</v>
+        <v>33.82</v>
       </c>
       <c r="E189" t="n">
-        <v>169.77</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="F189" t="n">
-        <v>1.43337</v>
+        <v>1.18337</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4972,22 +4972,22 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>83</v>
+        <v>43.81</v>
       </c>
       <c r="D190" t="n">
-        <v>146.04</v>
+        <v>103.52</v>
       </c>
       <c r="E190" t="n">
-        <v>75.95</v>
+        <v>136.29</v>
       </c>
       <c r="F190" t="n">
-        <v>2.11232</v>
+        <v>1.01949</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4996,22 +4996,22 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>118.05</v>
+        <v>25.85</v>
       </c>
       <c r="D191" t="n">
-        <v>193.13</v>
+        <v>41.64</v>
       </c>
       <c r="E191" t="n">
-        <v>63.6</v>
+        <v>61.08</v>
       </c>
       <c r="F191" t="n">
-        <v>2.21219</v>
+        <v>0.40056</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>105.37</v>
+        <v>83</v>
       </c>
       <c r="D192" t="n">
-        <v>230.98</v>
+        <v>141.91</v>
       </c>
       <c r="E192" t="n">
-        <v>119.21</v>
+        <v>70.98</v>
       </c>
       <c r="F192" t="n">
-        <v>-1.17733</v>
+        <v>1.71899</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5044,22 +5044,22 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>18.26</v>
+        <v>76.7</v>
       </c>
       <c r="D193" t="n">
-        <v>34.1</v>
+        <v>172.37</v>
       </c>
       <c r="E193" t="n">
-        <v>86.72</v>
+        <v>124.73</v>
       </c>
       <c r="F193" t="n">
-        <v>1.20956</v>
+        <v>2.05425</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5068,382 +5068,382 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>62.93</v>
+        <v>166.99</v>
       </c>
       <c r="D194" t="n">
-        <v>187.43</v>
+        <v>327.11</v>
       </c>
       <c r="E194" t="n">
-        <v>197.84</v>
+        <v>95.89</v>
       </c>
       <c r="F194" t="n">
-        <v>7.0525</v>
+        <v>9.43233</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>10.49</v>
+        <v>95.67</v>
       </c>
       <c r="D195" t="n">
-        <v>20.03</v>
+        <v>189.93</v>
       </c>
       <c r="E195" t="n">
-        <v>90.98999999999999</v>
+        <v>98.53</v>
       </c>
       <c r="F195" t="n">
-        <v>0.09464</v>
+        <v>0.92719</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>120.88</v>
+        <v>56.43</v>
       </c>
       <c r="D196" t="n">
-        <v>213.74</v>
+        <v>112.31</v>
       </c>
       <c r="E196" t="n">
-        <v>76.81999999999999</v>
+        <v>99.03</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.009849999999999999</v>
+        <v>3.12288</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>112.5</v>
+        <v>23.63</v>
       </c>
       <c r="D197" t="n">
-        <v>194.38</v>
+        <v>25.4</v>
       </c>
       <c r="E197" t="n">
-        <v>72.78</v>
+        <v>7.49</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.15956</v>
+        <v>0.05914</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>57.15</v>
+        <v>62.49</v>
       </c>
       <c r="D198" t="n">
-        <v>192.91</v>
+        <v>90.08</v>
       </c>
       <c r="E198" t="n">
-        <v>237.55</v>
+        <v>44.15</v>
       </c>
       <c r="F198" t="n">
-        <v>5.23377</v>
+        <v>-0.20883</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>117.65</v>
+        <v>124.07</v>
       </c>
       <c r="D199" t="n">
-        <v>240.17</v>
+        <v>187.84</v>
       </c>
       <c r="E199" t="n">
-        <v>104.14</v>
+        <v>51.4</v>
       </c>
       <c r="F199" t="n">
-        <v>1.60426</v>
+        <v>4.86283</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>151.43</v>
+        <v>23.49</v>
       </c>
       <c r="D200" t="n">
-        <v>271.73</v>
+        <v>32.23</v>
       </c>
       <c r="E200" t="n">
-        <v>79.44</v>
+        <v>37.21</v>
       </c>
       <c r="F200" t="n">
-        <v>2.44869</v>
+        <v>0.17672</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>25.85</v>
+        <v>172.34</v>
       </c>
       <c r="D201" t="n">
-        <v>42.87</v>
+        <v>216.17</v>
       </c>
       <c r="E201" t="n">
-        <v>65.81999999999999</v>
+        <v>25.43</v>
       </c>
       <c r="F201" t="n">
-        <v>0.51722</v>
+        <v>0.34426</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>95.67</v>
+        <v>430.4</v>
       </c>
       <c r="D202" t="n">
-        <v>191.38</v>
+        <v>559.3099999999999</v>
       </c>
       <c r="E202" t="n">
-        <v>100.04</v>
+        <v>29.95</v>
       </c>
       <c r="F202" t="n">
-        <v>1.06529</v>
+        <v>0.94514</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>56.43</v>
+        <v>96.73</v>
       </c>
       <c r="D203" t="n">
-        <v>110.65</v>
+        <v>121.88</v>
       </c>
       <c r="E203" t="n">
-        <v>96.08</v>
+        <v>26</v>
       </c>
       <c r="F203" t="n">
-        <v>2.9648</v>
+        <v>0.42451</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>23.49</v>
+        <v>164.13</v>
       </c>
       <c r="D204" t="n">
-        <v>32.24</v>
+        <v>543.51</v>
       </c>
       <c r="E204" t="n">
-        <v>37.23</v>
+        <v>231.15</v>
       </c>
       <c r="F204" t="n">
-        <v>0.1772</v>
+        <v>20.08884</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>BML-PJ</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>23.63</v>
+        <v>19.05</v>
       </c>
       <c r="D205" t="n">
-        <v>25.45</v>
+        <v>19.64</v>
       </c>
       <c r="E205" t="n">
-        <v>7.7</v>
+        <v>3.1</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0639</v>
+        <v>0.02454</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>RF-PC</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>124.07</v>
+        <v>23.5</v>
       </c>
       <c r="D206" t="n">
-        <v>187.41</v>
+        <v>24.51</v>
       </c>
       <c r="E206" t="n">
-        <v>51.05</v>
+        <v>4.3</v>
       </c>
       <c r="F206" t="n">
-        <v>4.82188</v>
+        <v>0.02458</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>62.49</v>
+        <v>273.5</v>
       </c>
       <c r="D207" t="n">
-        <v>91.37</v>
+        <v>345.04</v>
       </c>
       <c r="E207" t="n">
-        <v>46.22</v>
+        <v>26.16</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.08597</v>
+        <v>0.07615</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>96.73</v>
+        <v>59.66</v>
       </c>
       <c r="D208" t="n">
-        <v>121.62</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E208" t="n">
-        <v>25.73</v>
+        <v>38.54</v>
       </c>
       <c r="F208" t="n">
-        <v>0.39975</v>
+        <v>1.52607</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>164.13</v>
+        <v>22.61</v>
       </c>
       <c r="D209" t="n">
-        <v>547.5700000000001</v>
+        <v>55.88</v>
       </c>
       <c r="E209" t="n">
-        <v>233.62</v>
+        <v>147.15</v>
       </c>
       <c r="F209" t="n">
-        <v>20.4755</v>
+        <v>1.10062</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>41.19</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D210" t="n">
-        <v>98.05</v>
+        <v>21.61</v>
       </c>
       <c r="E210" t="n">
-        <v>138.04</v>
+        <v>150.99</v>
       </c>
       <c r="F210" t="n">
-        <v>1.31754</v>
+        <v>0.62903</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5476,22 +5476,22 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>196.04</v>
+        <v>166</v>
       </c>
       <c r="D211" t="n">
-        <v>502.43</v>
+        <v>396.82</v>
       </c>
       <c r="E211" t="n">
-        <v>156.29</v>
+        <v>139.05</v>
       </c>
       <c r="F211" t="n">
-        <v>7.12566</v>
+        <v>3.81127</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>65.16</v>
+        <v>119.51</v>
       </c>
       <c r="D212" t="n">
-        <v>111.75</v>
+        <v>258.96</v>
       </c>
       <c r="E212" t="n">
-        <v>71.5</v>
+        <v>116.68</v>
       </c>
       <c r="F212" t="n">
-        <v>1.69536</v>
+        <v>10.62825</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5524,22 +5524,22 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>16.32</v>
+        <v>29.16</v>
       </c>
       <c r="D213" t="n">
-        <v>23.55</v>
+        <v>39.67</v>
       </c>
       <c r="E213" t="n">
-        <v>44.27</v>
+        <v>36.06</v>
       </c>
       <c r="F213" t="n">
-        <v>0.25119</v>
+        <v>0.07323</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>52.5</v>
+        <v>65.16</v>
       </c>
       <c r="D214" t="n">
-        <v>88.45999999999999</v>
+        <v>110.45</v>
       </c>
       <c r="E214" t="n">
-        <v>68.5</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="F214" t="n">
-        <v>5.0903</v>
+        <v>1.57155</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5572,22 +5572,22 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>131.47</v>
+        <v>97.52</v>
       </c>
       <c r="D215" t="n">
-        <v>209.02</v>
+        <v>129.54</v>
       </c>
       <c r="E215" t="n">
-        <v>58.99</v>
+        <v>32.83</v>
       </c>
       <c r="F215" t="n">
-        <v>2.24854</v>
+        <v>2.24073</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5596,22 +5596,22 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>73.13</v>
+        <v>19.02</v>
       </c>
       <c r="D216" t="n">
-        <v>95.25</v>
+        <v>26.77</v>
       </c>
       <c r="E216" t="n">
-        <v>30.25</v>
+        <v>40.77</v>
       </c>
       <c r="F216" t="n">
-        <v>0.55414</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5620,22 +5620,22 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3.88</v>
+        <v>28.35</v>
       </c>
       <c r="D217" t="n">
-        <v>6.42</v>
+        <v>39.21</v>
       </c>
       <c r="E217" t="n">
-        <v>65.45999999999999</v>
+        <v>38.31</v>
       </c>
       <c r="F217" t="n">
-        <v>0.07343</v>
+        <v>0.49037</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5644,16 +5644,16 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>19.02</v>
+        <v>67.39</v>
       </c>
       <c r="D218" t="n">
-        <v>26.58</v>
+        <v>93.27</v>
       </c>
       <c r="E218" t="n">
-        <v>39.75</v>
+        <v>38.4</v>
       </c>
       <c r="F218" t="n">
-        <v>0.27783</v>
+        <v>0.61426</v>
       </c>
     </row>
     <row r="219">
@@ -5671,19 +5671,19 @@
         <v>284.79</v>
       </c>
       <c r="D219" t="n">
-        <v>419.61</v>
+        <v>417.14</v>
       </c>
       <c r="E219" t="n">
-        <v>47.34</v>
+        <v>46.47</v>
       </c>
       <c r="F219" t="n">
-        <v>6.69888</v>
+        <v>6.4646</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5692,22 +5692,22 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>246.63</v>
+        <v>73.13</v>
       </c>
       <c r="D220" t="n">
-        <v>330.16</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E220" t="n">
-        <v>33.87</v>
+        <v>31.03</v>
       </c>
       <c r="F220" t="n">
-        <v>4.60313</v>
+        <v>0.60843</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5716,22 +5716,22 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>116.13</v>
+        <v>24.77</v>
       </c>
       <c r="D221" t="n">
-        <v>193.42</v>
+        <v>36.78</v>
       </c>
       <c r="E221" t="n">
-        <v>66.55</v>
+        <v>48.47</v>
       </c>
       <c r="F221" t="n">
-        <v>0.19471</v>
+        <v>0.38439</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5740,22 +5740,22 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>67.39</v>
+        <v>258.08</v>
       </c>
       <c r="D222" t="n">
-        <v>92.54000000000001</v>
+        <v>288.93</v>
       </c>
       <c r="E222" t="n">
-        <v>37.33</v>
+        <v>11.95</v>
       </c>
       <c r="F222" t="n">
-        <v>0.54522</v>
+        <v>1.8157</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5764,22 +5764,22 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>59.66</v>
+        <v>273.14</v>
       </c>
       <c r="D223" t="n">
-        <v>82.18000000000001</v>
+        <v>341.4</v>
       </c>
       <c r="E223" t="n">
-        <v>37.76</v>
+        <v>24.99</v>
       </c>
       <c r="F223" t="n">
-        <v>1.48179</v>
+        <v>-0.06191</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5788,22 +5788,22 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>273.5</v>
+        <v>131.47</v>
       </c>
       <c r="D224" t="n">
-        <v>344.33</v>
+        <v>207.1</v>
       </c>
       <c r="E224" t="n">
-        <v>25.9</v>
+        <v>57.53</v>
       </c>
       <c r="F224" t="n">
-        <v>0.009010000000000001</v>
+        <v>2.06521</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5812,22 +5812,22 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>22.61</v>
+        <v>196.04</v>
       </c>
       <c r="D225" t="n">
-        <v>56.38</v>
+        <v>504.4</v>
       </c>
       <c r="E225" t="n">
-        <v>149.36</v>
+        <v>157.29</v>
       </c>
       <c r="F225" t="n">
-        <v>1.14824</v>
+        <v>7.31328</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5836,22 +5836,22 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>204.77</v>
+        <v>41.19</v>
       </c>
       <c r="D226" t="n">
-        <v>273.97</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="E226" t="n">
-        <v>33.79</v>
+        <v>135.66</v>
       </c>
       <c r="F226" t="n">
-        <v>1.08553</v>
+        <v>1.22443</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5860,22 +5860,22 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>28.35</v>
+        <v>26.41</v>
       </c>
       <c r="D227" t="n">
-        <v>38.88</v>
+        <v>39.5</v>
       </c>
       <c r="E227" t="n">
-        <v>37.16</v>
+        <v>49.56</v>
       </c>
       <c r="F227" t="n">
-        <v>0.45939</v>
+        <v>1.30846</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5884,22 +5884,22 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>97.52</v>
+        <v>116.13</v>
       </c>
       <c r="D228" t="n">
-        <v>129.05</v>
+        <v>192.78</v>
       </c>
       <c r="E228" t="n">
-        <v>32.33</v>
+        <v>66</v>
       </c>
       <c r="F228" t="n">
-        <v>2.19434</v>
+        <v>0.13376</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5908,22 +5908,22 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>31.8</v>
+        <v>107.27</v>
       </c>
       <c r="D229" t="n">
-        <v>67.41</v>
+        <v>136.26</v>
       </c>
       <c r="E229" t="n">
-        <v>111.98</v>
+        <v>27.02</v>
       </c>
       <c r="F229" t="n">
-        <v>0.60451</v>
+        <v>0.75992</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>26.41</v>
+        <v>246.63</v>
       </c>
       <c r="D230" t="n">
-        <v>39.83</v>
+        <v>331.18</v>
       </c>
       <c r="E230" t="n">
-        <v>50.81</v>
+        <v>34.28</v>
       </c>
       <c r="F230" t="n">
-        <v>1.33989</v>
+        <v>4.70027</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>279.73</v>
+        <v>204.77</v>
       </c>
       <c r="D231" t="n">
-        <v>422.73</v>
+        <v>273.05</v>
       </c>
       <c r="E231" t="n">
-        <v>51.12</v>
+        <v>33.34</v>
       </c>
       <c r="F231" t="n">
-        <v>5.1071</v>
+        <v>0.99791</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5980,22 +5980,22 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>273.14</v>
+        <v>52.5</v>
       </c>
       <c r="D232" t="n">
-        <v>340.76</v>
+        <v>90</v>
       </c>
       <c r="E232" t="n">
-        <v>24.76</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.12334</v>
+        <v>5.23697</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6004,22 +6004,22 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>119.51</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D233" t="n">
-        <v>263.11</v>
+        <v>101.14</v>
       </c>
       <c r="E233" t="n">
-        <v>120.16</v>
+        <v>12.37</v>
       </c>
       <c r="F233" t="n">
-        <v>11.02348</v>
+        <v>0.33492</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6028,22 +6028,22 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>8.609999999999999</v>
+        <v>16.32</v>
       </c>
       <c r="D234" t="n">
-        <v>21.7</v>
+        <v>23.68</v>
       </c>
       <c r="E234" t="n">
-        <v>152.09</v>
+        <v>45.13</v>
       </c>
       <c r="F234" t="n">
-        <v>0.63808</v>
+        <v>0.26452</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6052,22 +6052,22 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>24.77</v>
+        <v>31.8</v>
       </c>
       <c r="D235" t="n">
-        <v>36.51</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E235" t="n">
-        <v>47.38</v>
+        <v>112.74</v>
       </c>
       <c r="F235" t="n">
-        <v>0.35868</v>
+        <v>0.62737</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6076,22 +6076,22 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>258.08</v>
+        <v>279.73</v>
       </c>
       <c r="D236" t="n">
-        <v>289.68</v>
+        <v>430.88</v>
       </c>
       <c r="E236" t="n">
-        <v>12.24</v>
+        <v>54.03</v>
       </c>
       <c r="F236" t="n">
-        <v>1.88713</v>
+        <v>5.88329</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6100,46 +6100,46 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>90.01000000000001</v>
+        <v>12.96</v>
       </c>
       <c r="D237" t="n">
-        <v>100.54</v>
+        <v>16.65</v>
       </c>
       <c r="E237" t="n">
-        <v>11.69</v>
+        <v>28.47</v>
       </c>
       <c r="F237" t="n">
-        <v>0.2773</v>
+        <v>-0.03231</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>525.72</v>
+        <v>3.88</v>
       </c>
       <c r="D238" t="n">
-        <v>666.38</v>
+        <v>6.44</v>
       </c>
       <c r="E238" t="n">
-        <v>26.76</v>
+        <v>65.98</v>
       </c>
       <c r="F238" t="n">
-        <v>21.21441</v>
+        <v>0.07534</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>87.01000000000001</v>
+        <v>3.42</v>
       </c>
       <c r="D239" t="n">
-        <v>117.05</v>
+        <v>5.05</v>
       </c>
       <c r="E239" t="n">
-        <v>34.52</v>
+        <v>47.51</v>
       </c>
       <c r="F239" t="n">
-        <v>1.06053</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>110.24</v>
+        <v>125.78</v>
       </c>
       <c r="D240" t="n">
-        <v>150.33</v>
+        <v>143.85</v>
       </c>
       <c r="E240" t="n">
-        <v>36.37</v>
+        <v>14.37</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.84824</v>
+        <v>-0.03793</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>61.37</v>
+        <v>14</v>
       </c>
       <c r="D241" t="n">
-        <v>79.97</v>
+        <v>14.8</v>
       </c>
       <c r="E241" t="n">
-        <v>30.31</v>
+        <v>5.71</v>
       </c>
       <c r="F241" t="n">
-        <v>0.05464</v>
+        <v>0.00993</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,22 +6220,22 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3.42</v>
+        <v>14.27</v>
       </c>
       <c r="D242" t="n">
-        <v>5.01</v>
+        <v>18.63</v>
       </c>
       <c r="E242" t="n">
-        <v>46.49</v>
+        <v>30.55</v>
       </c>
       <c r="F242" t="n">
-        <v>0.08568000000000001</v>
+        <v>-0.01186</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6244,22 +6244,22 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>7.58</v>
+        <v>91.37</v>
       </c>
       <c r="D243" t="n">
-        <v>10.55</v>
+        <v>121.46</v>
       </c>
       <c r="E243" t="n">
-        <v>39.12</v>
+        <v>32.93</v>
       </c>
       <c r="F243" t="n">
-        <v>0.1719</v>
+        <v>0.12562</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>284.93</v>
+        <v>39.84</v>
       </c>
       <c r="D244" t="n">
-        <v>411.83</v>
+        <v>58.29</v>
       </c>
       <c r="E244" t="n">
-        <v>44.54</v>
+        <v>46.31</v>
       </c>
       <c r="F244" t="n">
-        <v>1.15578</v>
+        <v>0.05776</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>55.4</v>
+        <v>525.72</v>
       </c>
       <c r="D245" t="n">
-        <v>68.87</v>
+        <v>670.46</v>
       </c>
       <c r="E245" t="n">
-        <v>24.31</v>
+        <v>27.53</v>
       </c>
       <c r="F245" t="n">
-        <v>0.03706</v>
+        <v>21.60299</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,22 +6316,22 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>182.65</v>
+        <v>295.52</v>
       </c>
       <c r="D246" t="n">
-        <v>346.11</v>
+        <v>376.27</v>
       </c>
       <c r="E246" t="n">
-        <v>89.48999999999999</v>
+        <v>27.32</v>
       </c>
       <c r="F246" t="n">
-        <v>5.48885</v>
+        <v>0.17332</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>289.16</v>
+        <v>7.63</v>
       </c>
       <c r="D247" t="n">
-        <v>418.32</v>
+        <v>11.15</v>
       </c>
       <c r="E247" t="n">
-        <v>44.67</v>
+        <v>46.07</v>
       </c>
       <c r="F247" t="n">
-        <v>0.94158</v>
+        <v>0.16505</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>295.52</v>
+        <v>92.39</v>
       </c>
       <c r="D248" t="n">
-        <v>374.38</v>
+        <v>242.51</v>
       </c>
       <c r="E248" t="n">
-        <v>26.69</v>
+        <v>162.47</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.00621</v>
+        <v>5.44914</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>87.98</v>
+        <v>147.02</v>
       </c>
       <c r="D249" t="n">
-        <v>107.81</v>
+        <v>375.09</v>
       </c>
       <c r="E249" t="n">
-        <v>22.54</v>
+        <v>155.13</v>
       </c>
       <c r="F249" t="n">
-        <v>0.73714</v>
+        <v>1.92246</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>117.67</v>
+        <v>92.42</v>
       </c>
       <c r="D250" t="n">
-        <v>223.01</v>
+        <v>106.4</v>
       </c>
       <c r="E250" t="n">
-        <v>89.52</v>
+        <v>15.13</v>
       </c>
       <c r="F250" t="n">
-        <v>0.14636</v>
+        <v>0.38173</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1835.67</v>
+        <v>285.27</v>
       </c>
       <c r="D251" t="n">
-        <v>2180.06</v>
+        <v>378.05</v>
       </c>
       <c r="E251" t="n">
-        <v>18.76</v>
+        <v>32.52</v>
       </c>
       <c r="F251" t="n">
-        <v>-1.5421</v>
+        <v>2.24356</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>121.84</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D252" t="n">
-        <v>159.3</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="E252" t="n">
-        <v>30.75</v>
+        <v>17.55</v>
       </c>
       <c r="F252" t="n">
-        <v>1.27087</v>
+        <v>-0.25825</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>3.93</v>
+        <v>22.3</v>
       </c>
       <c r="D253" t="n">
-        <v>5.95</v>
+        <v>35.03</v>
       </c>
       <c r="E253" t="n">
-        <v>51.53</v>
+        <v>57.09</v>
       </c>
       <c r="F253" t="n">
-        <v>0.12772</v>
+        <v>0.5291400000000001</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>22.3</v>
+        <v>33.63</v>
       </c>
       <c r="D254" t="n">
-        <v>34.93</v>
+        <v>43.87</v>
       </c>
       <c r="E254" t="n">
-        <v>56.64</v>
+        <v>30.45</v>
       </c>
       <c r="F254" t="n">
-        <v>0.51962</v>
+        <v>0.08643000000000001</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>24.24</v>
+        <v>3.93</v>
       </c>
       <c r="D255" t="n">
-        <v>30.34</v>
+        <v>5.84</v>
       </c>
       <c r="E255" t="n">
-        <v>25.19</v>
+        <v>48.6</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.00327</v>
+        <v>0.11677</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>317.93</v>
+        <v>24.24</v>
       </c>
       <c r="D256" t="n">
-        <v>378.54</v>
+        <v>30.43</v>
       </c>
       <c r="E256" t="n">
-        <v>19.06</v>
+        <v>25.56</v>
       </c>
       <c r="F256" t="n">
-        <v>0.37337</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>157.12</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D257" t="n">
-        <v>263.33</v>
+        <v>156.62</v>
       </c>
       <c r="E257" t="n">
-        <v>67.59</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="F257" t="n">
-        <v>2.1884</v>
+        <v>0.27415</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>35.34</v>
+        <v>23.77</v>
       </c>
       <c r="D258" t="n">
-        <v>53.69</v>
+        <v>29.05</v>
       </c>
       <c r="E258" t="n">
-        <v>51.91</v>
+        <v>22.21</v>
       </c>
       <c r="F258" t="n">
-        <v>0.82279</v>
+        <v>0.28593</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>7.63</v>
+        <v>243.35</v>
       </c>
       <c r="D259" t="n">
-        <v>11.05</v>
+        <v>364.87</v>
       </c>
       <c r="E259" t="n">
-        <v>44.82</v>
+        <v>49.94</v>
       </c>
       <c r="F259" t="n">
-        <v>0.156</v>
+        <v>3.16348</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>92.39</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D260" t="n">
-        <v>240.17</v>
+        <v>118.37</v>
       </c>
       <c r="E260" t="n">
-        <v>159.94</v>
+        <v>36.04</v>
       </c>
       <c r="F260" t="n">
-        <v>5.22628</v>
+        <v>1.18624</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>285.27</v>
+        <v>35.34</v>
       </c>
       <c r="D261" t="n">
-        <v>377.26</v>
+        <v>53.98</v>
       </c>
       <c r="E261" t="n">
-        <v>32.24</v>
+        <v>52.74</v>
       </c>
       <c r="F261" t="n">
-        <v>2.16784</v>
+        <v>0.85089</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>147.02</v>
+        <v>317.93</v>
       </c>
       <c r="D262" t="n">
-        <v>373.51</v>
+        <v>379.72</v>
       </c>
       <c r="E262" t="n">
-        <v>154.05</v>
+        <v>19.44</v>
       </c>
       <c r="F262" t="n">
-        <v>1.77198</v>
+        <v>0.48575</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>33.63</v>
+        <v>284.93</v>
       </c>
       <c r="D263" t="n">
-        <v>43.53</v>
+        <v>407.79</v>
       </c>
       <c r="E263" t="n">
-        <v>29.45</v>
+        <v>43.12</v>
       </c>
       <c r="F263" t="n">
-        <v>0.05453</v>
+        <v>0.77102</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>20.72</v>
+        <v>289.16</v>
       </c>
       <c r="D264" t="n">
-        <v>24.81</v>
+        <v>417.06</v>
       </c>
       <c r="E264" t="n">
-        <v>19.74</v>
+        <v>44.23</v>
       </c>
       <c r="F264" t="n">
-        <v>0.04605</v>
+        <v>0.82157</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>39.84</v>
+        <v>117.67</v>
       </c>
       <c r="D265" t="n">
-        <v>58.55</v>
+        <v>222.29</v>
       </c>
       <c r="E265" t="n">
-        <v>46.96</v>
+        <v>88.91</v>
       </c>
       <c r="F265" t="n">
-        <v>0.08252</v>
+        <v>0.07779</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SPG-PJ</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>52.49</v>
+        <v>153.68</v>
       </c>
       <c r="D266" t="n">
-        <v>55.75</v>
+        <v>171.67</v>
       </c>
       <c r="E266" t="n">
-        <v>6.21</v>
+        <v>11.71</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.01794</v>
+        <v>-0.33974</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>87.15000000000001</v>
+        <v>106.41</v>
       </c>
       <c r="D267" t="n">
-        <v>156.81</v>
+        <v>117.56</v>
       </c>
       <c r="E267" t="n">
-        <v>79.93000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="F267" t="n">
-        <v>0.29224</v>
+        <v>-0.5614</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>23.77</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D268" t="n">
-        <v>28.91</v>
+        <v>95.89</v>
       </c>
       <c r="E268" t="n">
-        <v>21.62</v>
+        <v>31.54</v>
       </c>
       <c r="F268" t="n">
-        <v>0.2726</v>
+        <v>0.94303</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>67.7</v>
+        <v>7.58</v>
       </c>
       <c r="D269" t="n">
-        <v>97.48</v>
+        <v>10.62</v>
       </c>
       <c r="E269" t="n">
-        <v>43.99</v>
+        <v>40.11</v>
       </c>
       <c r="F269" t="n">
-        <v>0.40375</v>
+        <v>0.17904</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6892,22 +6892,22 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>243.35</v>
+        <v>20.72</v>
       </c>
       <c r="D270" t="n">
-        <v>368.58</v>
+        <v>24.64</v>
       </c>
       <c r="E270" t="n">
-        <v>51.46</v>
+        <v>18.92</v>
       </c>
       <c r="F270" t="n">
-        <v>3.51682</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6916,22 +6916,22 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>14</v>
+        <v>41.53</v>
       </c>
       <c r="D271" t="n">
-        <v>14.81</v>
+        <v>56.9</v>
       </c>
       <c r="E271" t="n">
-        <v>5.79</v>
+        <v>37.01</v>
       </c>
       <c r="F271" t="n">
-        <v>0.01087</v>
+        <v>0.18075</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>92.42</v>
+        <v>67.7</v>
       </c>
       <c r="D272" t="n">
-        <v>107.44</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="E272" t="n">
-        <v>16.25</v>
+        <v>45.07</v>
       </c>
       <c r="F272" t="n">
-        <v>0.4803</v>
+        <v>0.47328</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,160 +6964,352 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>72.90000000000001</v>
+        <v>52.49</v>
       </c>
       <c r="D273" t="n">
-        <v>95.09999999999999</v>
+        <v>56.44</v>
       </c>
       <c r="E273" t="n">
-        <v>30.45</v>
+        <v>7.53</v>
       </c>
       <c r="F273" t="n">
-        <v>0.86779</v>
+        <v>0.04777</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>95.48</v>
+        <v>87.98</v>
       </c>
       <c r="D274" t="n">
-        <v>112</v>
+        <v>108.03</v>
       </c>
       <c r="E274" t="n">
-        <v>17.3</v>
+        <v>22.79</v>
       </c>
       <c r="F274" t="n">
-        <v>0.09274</v>
+        <v>0.75809</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>27.55</v>
+        <v>163.37</v>
       </c>
       <c r="D275" t="n">
-        <v>33.66</v>
+        <v>258.77</v>
       </c>
       <c r="E275" t="n">
-        <v>22.18</v>
+        <v>58.4</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.16805</v>
+        <v>0.24756</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>FMX</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>106.96</v>
+        <v>157.12</v>
       </c>
       <c r="D276" t="n">
-        <v>121.26</v>
+        <v>262.49</v>
       </c>
       <c r="E276" t="n">
-        <v>13.37</v>
+        <v>67.06</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.41742</v>
+        <v>2.10887</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>17.13</v>
+        <v>121.84</v>
       </c>
       <c r="D277" t="n">
-        <v>42.6</v>
+        <v>159.66</v>
       </c>
       <c r="E277" t="n">
-        <v>148.7</v>
+        <v>31.04</v>
       </c>
       <c r="F277" t="n">
-        <v>0.26831</v>
+        <v>1.30516</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>99.98999999999999</v>
+        <v>213.28</v>
       </c>
       <c r="D278" t="n">
-        <v>172.48</v>
+        <v>286.25</v>
       </c>
       <c r="E278" t="n">
-        <v>72.5</v>
+        <v>34.21</v>
       </c>
       <c r="F278" t="n">
-        <v>1.4171</v>
+        <v>0.04368</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>110.24</v>
+      </c>
+      <c r="D279" t="n">
+        <v>150.18</v>
+      </c>
+      <c r="E279" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="F279" t="n">
+        <v>-0.86253</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SLF</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="D280" t="n">
+        <v>80.54000000000001</v>
+      </c>
+      <c r="E280" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0.10893</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>NTRA</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="D281" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="E281" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="F281" t="n">
+        <v>5.93408</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>KOF</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="D282" t="n">
+        <v>111.53</v>
+      </c>
+      <c r="E282" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0.04846</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="D283" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="E283" t="n">
+        <v>151.37</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.31188</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>NWS</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="D284" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="E284" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="F284" t="n">
+        <v>-0.15662</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>FMX</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>106.96</v>
+      </c>
+      <c r="D285" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="E285" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="F285" t="n">
+        <v>-0.38552</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ICLR</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="D286" t="n">
+        <v>172.45</v>
+      </c>
+      <c r="E286" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1.41425</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
           <t>MO</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C279" t="n">
+      <c r="C287" t="n">
         <v>63.78</v>
       </c>
-      <c r="D279" t="n">
-        <v>70.05</v>
-      </c>
-      <c r="E279" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0.46132</v>
+      <c r="D287" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="E287" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.43466</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F287"/>
+  <dimension ref="A1:F284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,13 +463,13 @@
         <v>80.54000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>86.15000000000001</v>
+        <v>86.11</v>
       </c>
       <c r="E2" t="n">
-        <v>6.97</v>
+        <v>6.92</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.95953</v>
+        <v>-0.96334</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>56.5</v>
+        <v>56.52</v>
       </c>
       <c r="E3" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.10042</v>
+        <v>-0.09851</v>
       </c>
     </row>
     <row r="4">
@@ -559,13 +559,13 @@
         <v>17.87</v>
       </c>
       <c r="D6" t="n">
-        <v>21.45</v>
+        <v>21.44</v>
       </c>
       <c r="E6" t="n">
-        <v>20.03</v>
+        <v>19.98</v>
       </c>
       <c r="F6" t="n">
-        <v>0.74516</v>
+        <v>0.7442</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>102.63</v>
       </c>
       <c r="D7" t="n">
-        <v>108.11</v>
+        <v>108.09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.33</v>
+        <v>5.32</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01445</v>
+        <v>0.01302</v>
       </c>
     </row>
     <row r="8">
@@ -631,13 +631,13 @@
         <v>5.67</v>
       </c>
       <c r="D9" t="n">
-        <v>6.84</v>
+        <v>6.83</v>
       </c>
       <c r="E9" t="n">
-        <v>20.55</v>
+        <v>20.46</v>
       </c>
       <c r="F9" t="n">
-        <v>0.15149</v>
+        <v>0.15101</v>
       </c>
     </row>
     <row r="10">
@@ -655,13 +655,13 @@
         <v>298.59</v>
       </c>
       <c r="D10" t="n">
-        <v>331.28</v>
+        <v>331.46</v>
       </c>
       <c r="E10" t="n">
-        <v>10.95</v>
+        <v>11.01</v>
       </c>
       <c r="F10" t="n">
-        <v>1.08278</v>
+        <v>1.09993</v>
       </c>
     </row>
     <row r="11">
@@ -691,7 +691,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.46</v>
+        <v>12.43</v>
       </c>
       <c r="D12" t="n">
-        <v>5.22</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="n">
-        <v>17.15</v>
+        <v>39.98</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08130999999999999</v>
+        <v>0.8716699999999999</v>
       </c>
     </row>
     <row r="13">
@@ -739,7 +739,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.43</v>
+        <v>2.98</v>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>3.5</v>
       </c>
       <c r="E14" t="n">
-        <v>39.98</v>
+        <v>17.45</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8716699999999999</v>
+        <v>0.06834</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.98</v>
+        <v>7.17</v>
       </c>
       <c r="D15" t="n">
-        <v>3.49</v>
+        <v>8.26</v>
       </c>
       <c r="E15" t="n">
-        <v>17.11</v>
+        <v>15.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06739000000000001</v>
+        <v>0.13953</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.17</v>
+        <v>4.46</v>
       </c>
       <c r="D16" t="n">
-        <v>8.26</v>
+        <v>5.24</v>
       </c>
       <c r="E16" t="n">
-        <v>15.13</v>
+        <v>17.49</v>
       </c>
       <c r="F16" t="n">
-        <v>0.13905</v>
+        <v>0.08273999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>98.45</v>
+        <v>17.28</v>
       </c>
       <c r="D17" t="n">
-        <v>123.82</v>
+        <v>19.03</v>
       </c>
       <c r="E17" t="n">
-        <v>25.77</v>
+        <v>10.13</v>
       </c>
       <c r="F17" t="n">
-        <v>1.77783</v>
+        <v>0.20851</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.28</v>
+        <v>98.45</v>
       </c>
       <c r="D18" t="n">
-        <v>19.04</v>
+        <v>123.79</v>
       </c>
       <c r="E18" t="n">
-        <v>10.19</v>
+        <v>25.74</v>
       </c>
       <c r="F18" t="n">
-        <v>0.20946</v>
+        <v>1.77497</v>
       </c>
     </row>
     <row r="19">
@@ -871,13 +871,13 @@
         <v>2.78</v>
       </c>
       <c r="D19" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E19" t="n">
-        <v>8.81</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02604</v>
+        <v>0.02557</v>
       </c>
     </row>
     <row r="20">
@@ -895,13 +895,13 @@
         <v>52.62</v>
       </c>
       <c r="D20" t="n">
-        <v>56.63</v>
+        <v>56.64</v>
       </c>
       <c r="E20" t="n">
-        <v>7.62</v>
+        <v>7.64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.35486</v>
+        <v>0.35581</v>
       </c>
     </row>
     <row r="21">
@@ -919,13 +919,13 @@
         <v>35.54</v>
       </c>
       <c r="D21" t="n">
-        <v>50.25</v>
+        <v>50.24</v>
       </c>
       <c r="E21" t="n">
-        <v>41.39</v>
+        <v>41.36</v>
       </c>
       <c r="F21" t="n">
-        <v>2.33935</v>
+        <v>2.3384</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         <v>123.39</v>
       </c>
       <c r="D22" t="n">
-        <v>133.75</v>
+        <v>133.73</v>
       </c>
       <c r="E22" t="n">
-        <v>8.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.10642</v>
+        <v>1.10452</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -964,22 +964,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>340.65</v>
+        <v>63.54</v>
       </c>
       <c r="D23" t="n">
-        <v>372.02</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>9.210000000000001</v>
+        <v>12.86</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.17278</v>
+        <v>0.51027</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63.54</v>
+        <v>340.65</v>
       </c>
       <c r="D24" t="n">
-        <v>71.84999999999999</v>
+        <v>371.63</v>
       </c>
       <c r="E24" t="n">
-        <v>13.08</v>
+        <v>9.09</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5236</v>
+        <v>-1.20992</v>
       </c>
     </row>
     <row r="25">
@@ -1027,7 +1027,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>48.68</v>
+        <v>41.55</v>
       </c>
       <c r="D26" t="n">
-        <v>61.09</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>25.49</v>
+        <v>65.7</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4706</v>
+        <v>0.36109</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>41.55</v>
+        <v>48.68</v>
       </c>
       <c r="D27" t="n">
-        <v>68.84999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="E27" t="n">
-        <v>65.7</v>
+        <v>25.51</v>
       </c>
       <c r="F27" t="n">
-        <v>0.36109</v>
+        <v>0.47155</v>
       </c>
     </row>
     <row r="28">
@@ -1087,19 +1087,19 @@
         <v>11.03</v>
       </c>
       <c r="D28" t="n">
-        <v>12.86</v>
+        <v>12.84</v>
       </c>
       <c r="E28" t="n">
-        <v>16.59</v>
+        <v>16.41</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01385</v>
+        <v>0.01194</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.14</v>
+        <v>332.02</v>
       </c>
       <c r="D29" t="n">
-        <v>31.56</v>
+        <v>377.16</v>
       </c>
       <c r="E29" t="n">
-        <v>16.29</v>
+        <v>13.6</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.13487</v>
+        <v>0.27114</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1132,16 +1132,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>332.02</v>
+        <v>27.14</v>
       </c>
       <c r="D30" t="n">
-        <v>377.17</v>
+        <v>31.56</v>
       </c>
       <c r="E30" t="n">
-        <v>13.6</v>
+        <v>16.29</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2721</v>
+        <v>-0.13487</v>
       </c>
     </row>
     <row r="31">
@@ -1159,13 +1159,13 @@
         <v>146.38</v>
       </c>
       <c r="D31" t="n">
-        <v>215.82</v>
+        <v>215.67</v>
       </c>
       <c r="E31" t="n">
-        <v>47.44</v>
+        <v>47.34</v>
       </c>
       <c r="F31" t="n">
-        <v>0.64206</v>
+        <v>0.62778</v>
       </c>
     </row>
     <row r="32">
@@ -1183,13 +1183,13 @@
         <v>179.43</v>
       </c>
       <c r="D32" t="n">
-        <v>190.21</v>
+        <v>190.13</v>
       </c>
       <c r="E32" t="n">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4415</v>
+        <v>0.43388</v>
       </c>
     </row>
     <row r="33">
@@ -1231,13 +1231,13 @@
         <v>205.77</v>
       </c>
       <c r="D34" t="n">
-        <v>248.18</v>
+        <v>248.37</v>
       </c>
       <c r="E34" t="n">
-        <v>20.61</v>
+        <v>20.7</v>
       </c>
       <c r="F34" t="n">
-        <v>3.24784</v>
+        <v>3.26641</v>
       </c>
     </row>
     <row r="35">
@@ -1255,19 +1255,19 @@
         <v>440.76</v>
       </c>
       <c r="D35" t="n">
-        <v>637.04</v>
+        <v>636.4</v>
       </c>
       <c r="E35" t="n">
-        <v>44.53</v>
+        <v>44.39</v>
       </c>
       <c r="F35" t="n">
-        <v>4.16883</v>
+        <v>4.10788</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1276,70 +1276,70 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>103.45</v>
+        <v>89.2</v>
       </c>
       <c r="D36" t="n">
-        <v>150.06</v>
+        <v>124.19</v>
       </c>
       <c r="E36" t="n">
-        <v>45.06</v>
+        <v>39.23</v>
       </c>
       <c r="F36" t="n">
-        <v>1.07578</v>
+        <v>0.38279</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>198.14</v>
+        <v>103.45</v>
       </c>
       <c r="D37" t="n">
-        <v>263.04</v>
+        <v>150.02</v>
       </c>
       <c r="E37" t="n">
-        <v>32.75</v>
+        <v>45.02</v>
       </c>
       <c r="F37" t="n">
-        <v>2.16789</v>
+        <v>1.07197</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RRC</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35.49</v>
+        <v>198.14</v>
       </c>
       <c r="D38" t="n">
-        <v>41.91</v>
+        <v>263.09</v>
       </c>
       <c r="E38" t="n">
-        <v>18.09</v>
+        <v>32.78</v>
       </c>
       <c r="F38" t="n">
-        <v>0.09035</v>
+        <v>2.17265</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1348,118 +1348,118 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>41.44</v>
+        <v>35.49</v>
       </c>
       <c r="D39" t="n">
-        <v>45.38</v>
+        <v>41.9</v>
       </c>
       <c r="E39" t="n">
-        <v>9.51</v>
+        <v>18.06</v>
       </c>
       <c r="F39" t="n">
-        <v>0.55766</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>510.39</v>
+        <v>41.44</v>
       </c>
       <c r="D40" t="n">
-        <v>643.61</v>
+        <v>45.37</v>
       </c>
       <c r="E40" t="n">
-        <v>26.1</v>
+        <v>9.48</v>
       </c>
       <c r="F40" t="n">
-        <v>5.95759</v>
+        <v>0.55671</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.04</v>
+        <v>510.39</v>
       </c>
       <c r="D41" t="n">
-        <v>5.88</v>
+        <v>643.33</v>
       </c>
       <c r="E41" t="n">
-        <v>16.67</v>
+        <v>26.05</v>
       </c>
       <c r="F41" t="n">
-        <v>0.04652</v>
+        <v>5.93092</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PSNYW</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.2</v>
+        <v>5.04</v>
       </c>
       <c r="D42" t="n">
-        <v>4.68</v>
+        <v>5.86</v>
       </c>
       <c r="E42" t="n">
-        <v>112.73</v>
+        <v>16.27</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.01815</v>
+        <v>0.04462</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>PSNYW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>162.11</v>
+        <v>2.2</v>
       </c>
       <c r="D43" t="n">
-        <v>177.74</v>
+        <v>4.68</v>
       </c>
       <c r="E43" t="n">
-        <v>9.640000000000001</v>
+        <v>112.73</v>
       </c>
       <c r="F43" t="n">
-        <v>0.54369</v>
+        <v>-0.01815</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>40.48</v>
+        <v>162.11</v>
       </c>
       <c r="D44" t="n">
-        <v>45.96</v>
+        <v>177.71</v>
       </c>
       <c r="E44" t="n">
-        <v>13.54</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.24459</v>
+        <v>0.54084</v>
       </c>
     </row>
     <row r="45">
@@ -1507,31 +1507,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>51.98</v>
+        <v>40.48</v>
       </c>
       <c r="D46" t="n">
-        <v>66.94</v>
+        <v>45.96</v>
       </c>
       <c r="E46" t="n">
-        <v>28.78</v>
+        <v>13.54</v>
       </c>
       <c r="F46" t="n">
-        <v>0.22461</v>
+        <v>0.24459</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1540,22 +1540,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13.01</v>
+        <v>165.69</v>
       </c>
       <c r="D47" t="n">
-        <v>17.68</v>
+        <v>217.77</v>
       </c>
       <c r="E47" t="n">
-        <v>35.9</v>
+        <v>31.43</v>
       </c>
       <c r="F47" t="n">
-        <v>0.39546</v>
+        <v>3.21866</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1564,22 +1564,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>47.94</v>
+        <v>15.99</v>
       </c>
       <c r="D48" t="n">
-        <v>63.51</v>
+        <v>21.77</v>
       </c>
       <c r="E48" t="n">
-        <v>32.49</v>
+        <v>36.15</v>
       </c>
       <c r="F48" t="n">
-        <v>0.82599</v>
+        <v>0.6551900000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>171.96</v>
+        <v>51.98</v>
       </c>
       <c r="D49" t="n">
-        <v>211.52</v>
+        <v>66.97</v>
       </c>
       <c r="E49" t="n">
-        <v>23.01</v>
+        <v>28.84</v>
       </c>
       <c r="F49" t="n">
-        <v>1.93006</v>
+        <v>0.22746</v>
       </c>
     </row>
     <row r="50">
@@ -1615,19 +1615,19 @@
         <v>14.49</v>
       </c>
       <c r="D50" t="n">
-        <v>19.55</v>
+        <v>19.57</v>
       </c>
       <c r="E50" t="n">
-        <v>34.89</v>
+        <v>35.06</v>
       </c>
       <c r="F50" t="n">
-        <v>0.58114</v>
+        <v>0.58352</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>15.99</v>
+        <v>38.92</v>
       </c>
       <c r="D51" t="n">
-        <v>21.75</v>
+        <v>51.55</v>
       </c>
       <c r="E51" t="n">
-        <v>36.05</v>
+        <v>32.45</v>
       </c>
       <c r="F51" t="n">
-        <v>0.65376</v>
+        <v>0.30504</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>53.57</v>
+        <v>47.94</v>
       </c>
       <c r="D52" t="n">
-        <v>71.89</v>
+        <v>63.52</v>
       </c>
       <c r="E52" t="n">
-        <v>34.2</v>
+        <v>32.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.95148</v>
+        <v>0.82646</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>36.15</v>
+        <v>53.57</v>
       </c>
       <c r="D53" t="n">
-        <v>46.96</v>
+        <v>71.87</v>
       </c>
       <c r="E53" t="n">
-        <v>29.9</v>
+        <v>34.16</v>
       </c>
       <c r="F53" t="n">
-        <v>0.88425</v>
+        <v>0.94957</v>
       </c>
     </row>
     <row r="54">
@@ -1711,19 +1711,19 @@
         <v>45.57</v>
       </c>
       <c r="D54" t="n">
-        <v>56.65</v>
+        <v>56.66</v>
       </c>
       <c r="E54" t="n">
-        <v>24.31</v>
+        <v>24.34</v>
       </c>
       <c r="F54" t="n">
-        <v>0.49553</v>
+        <v>0.49648</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17.93</v>
+        <v>171.96</v>
       </c>
       <c r="D55" t="n">
-        <v>24.5</v>
+        <v>211.52</v>
       </c>
       <c r="E55" t="n">
-        <v>36.64</v>
+        <v>23.01</v>
       </c>
       <c r="F55" t="n">
-        <v>0.34498</v>
+        <v>1.93006</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38.92</v>
+        <v>17.93</v>
       </c>
       <c r="D56" t="n">
-        <v>51.52</v>
+        <v>24.49</v>
       </c>
       <c r="E56" t="n">
-        <v>32.37</v>
+        <v>36.59</v>
       </c>
       <c r="F56" t="n">
-        <v>0.30218</v>
+        <v>0.34403</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>110.99</v>
+        <v>36.15</v>
       </c>
       <c r="D57" t="n">
-        <v>135.18</v>
+        <v>46.96</v>
       </c>
       <c r="E57" t="n">
-        <v>21.79</v>
+        <v>29.9</v>
       </c>
       <c r="F57" t="n">
-        <v>0.17548</v>
+        <v>0.88425</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>74.8</v>
+        <v>110.99</v>
       </c>
       <c r="D58" t="n">
-        <v>93.14</v>
+        <v>135.35</v>
       </c>
       <c r="E58" t="n">
-        <v>24.53</v>
+        <v>21.95</v>
       </c>
       <c r="F58" t="n">
-        <v>1.07384</v>
+        <v>0.19167</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>52.58</v>
+        <v>104.89</v>
       </c>
       <c r="D59" t="n">
-        <v>65.42</v>
+        <v>121.76</v>
       </c>
       <c r="E59" t="n">
-        <v>24.42</v>
+        <v>16.08</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0047</v>
+        <v>1.74063</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1852,22 +1852,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>31.87</v>
+        <v>13.01</v>
       </c>
       <c r="D60" t="n">
-        <v>47.41</v>
+        <v>17.68</v>
       </c>
       <c r="E60" t="n">
-        <v>48.76</v>
+        <v>35.9</v>
       </c>
       <c r="F60" t="n">
-        <v>1.0579</v>
+        <v>0.39546</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>103.22</v>
+        <v>52.58</v>
       </c>
       <c r="D61" t="n">
-        <v>141.18</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>36.78</v>
+        <v>24.44</v>
       </c>
       <c r="F61" t="n">
-        <v>2.27941</v>
+        <v>0.00565</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>165.69</v>
+        <v>103.22</v>
       </c>
       <c r="D62" t="n">
-        <v>217.54</v>
+        <v>141.22</v>
       </c>
       <c r="E62" t="n">
-        <v>31.3</v>
+        <v>36.81</v>
       </c>
       <c r="F62" t="n">
-        <v>3.19723</v>
+        <v>2.28322</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>17.26</v>
+        <v>31.87</v>
       </c>
       <c r="D63" t="n">
-        <v>19.86</v>
+        <v>47.41</v>
       </c>
       <c r="E63" t="n">
-        <v>15.05</v>
+        <v>48.76</v>
       </c>
       <c r="F63" t="n">
-        <v>0.16437</v>
+        <v>1.0579</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>40.25</v>
+        <v>17.26</v>
       </c>
       <c r="D64" t="n">
-        <v>51.35</v>
+        <v>19.84</v>
       </c>
       <c r="E64" t="n">
-        <v>27.58</v>
+        <v>14.95</v>
       </c>
       <c r="F64" t="n">
-        <v>0.92841</v>
+        <v>0.16265</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>104.89</v>
+        <v>40.25</v>
       </c>
       <c r="D65" t="n">
-        <v>121.78</v>
+        <v>51.33</v>
       </c>
       <c r="E65" t="n">
-        <v>16.1</v>
+        <v>27.53</v>
       </c>
       <c r="F65" t="n">
-        <v>1.74253</v>
+        <v>0.9265099999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>41.99</v>
+        <v>74.8</v>
       </c>
       <c r="D66" t="n">
-        <v>51.44</v>
+        <v>93.12</v>
       </c>
       <c r="E66" t="n">
-        <v>22.49</v>
+        <v>24.49</v>
       </c>
       <c r="F66" t="n">
-        <v>0.50581</v>
+        <v>1.07146</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,46 +2020,46 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20.48</v>
+        <v>41.99</v>
       </c>
       <c r="D67" t="n">
-        <v>26.75</v>
+        <v>51.45</v>
       </c>
       <c r="E67" t="n">
-        <v>30.59</v>
+        <v>22.53</v>
       </c>
       <c r="F67" t="n">
-        <v>0.32584</v>
+        <v>0.50723</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>38.73</v>
+        <v>20.48</v>
       </c>
       <c r="D68" t="n">
-        <v>63.28</v>
+        <v>26.72</v>
       </c>
       <c r="E68" t="n">
-        <v>63.39</v>
+        <v>30.47</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3855</v>
+        <v>0.32346</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>124.44</v>
+        <v>38.73</v>
       </c>
       <c r="D69" t="n">
-        <v>193.58</v>
+        <v>63.28</v>
       </c>
       <c r="E69" t="n">
-        <v>55.56</v>
+        <v>63.39</v>
       </c>
       <c r="F69" t="n">
-        <v>2.35319</v>
+        <v>0.3855</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>55.53</v>
+        <v>62.05</v>
       </c>
       <c r="D70" t="n">
-        <v>62.27</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>12.14</v>
+        <v>31.01</v>
       </c>
       <c r="F70" t="n">
-        <v>0.75545</v>
+        <v>-0.26747</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2116,22 +2116,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>13.31</v>
+        <v>124.44</v>
       </c>
       <c r="D71" t="n">
-        <v>23.6</v>
+        <v>193.4</v>
       </c>
       <c r="E71" t="n">
-        <v>77.31</v>
+        <v>55.42</v>
       </c>
       <c r="F71" t="n">
-        <v>0.58601</v>
+        <v>2.33628</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>62.05</v>
+        <v>55.53</v>
       </c>
       <c r="D72" t="n">
-        <v>81.29000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="E72" t="n">
-        <v>31.01</v>
+        <v>12.1</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.26747</v>
+        <v>0.75354</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,46 +2164,46 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13.43</v>
+        <v>13.31</v>
       </c>
       <c r="D73" t="n">
-        <v>15.03</v>
+        <v>23.6</v>
       </c>
       <c r="E73" t="n">
-        <v>11.93</v>
+        <v>77.31</v>
       </c>
       <c r="F73" t="n">
-        <v>0.08302</v>
+        <v>0.58601</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>136.06</v>
+        <v>13.43</v>
       </c>
       <c r="D74" t="n">
-        <v>169.29</v>
+        <v>15.03</v>
       </c>
       <c r="E74" t="n">
-        <v>24.42</v>
+        <v>11.91</v>
       </c>
       <c r="F74" t="n">
-        <v>1.98149</v>
+        <v>0.08283</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2212,46 +2212,46 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7.67</v>
+        <v>136.06</v>
       </c>
       <c r="D75" t="n">
-        <v>9.220000000000001</v>
+        <v>169.32</v>
       </c>
       <c r="E75" t="n">
-        <v>20.21</v>
+        <v>24.45</v>
       </c>
       <c r="F75" t="n">
-        <v>0.15547</v>
+        <v>1.98435</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>76.53</v>
+        <v>7.67</v>
       </c>
       <c r="D76" t="n">
-        <v>98.93000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="E76" t="n">
-        <v>29.27</v>
+        <v>20.34</v>
       </c>
       <c r="F76" t="n">
-        <v>1.63127</v>
+        <v>0.15642</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2260,16 +2260,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>82.31</v>
+        <v>31.03</v>
       </c>
       <c r="D77" t="n">
-        <v>129.6</v>
+        <v>45.75</v>
       </c>
       <c r="E77" t="n">
-        <v>57.45</v>
+        <v>47.44</v>
       </c>
       <c r="F77" t="n">
-        <v>2.83088</v>
+        <v>0.94193</v>
       </c>
     </row>
     <row r="78">
@@ -2287,19 +2287,19 @@
         <v>56.4</v>
       </c>
       <c r="D78" t="n">
-        <v>79.17</v>
+        <v>79.48</v>
       </c>
       <c r="E78" t="n">
-        <v>40.37</v>
+        <v>40.92</v>
       </c>
       <c r="F78" t="n">
-        <v>1.9744</v>
+        <v>2.00392</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2308,22 +2308,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>31.03</v>
+        <v>76.53</v>
       </c>
       <c r="D79" t="n">
-        <v>45.74</v>
+        <v>98.95</v>
       </c>
       <c r="E79" t="n">
-        <v>47.41</v>
+        <v>29.3</v>
       </c>
       <c r="F79" t="n">
-        <v>0.94098</v>
+        <v>1.63317</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2332,46 +2332,46 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>18.94</v>
+        <v>82.31</v>
       </c>
       <c r="D80" t="n">
-        <v>23.95</v>
+        <v>129.6</v>
       </c>
       <c r="E80" t="n">
-        <v>26.45</v>
+        <v>57.45</v>
       </c>
       <c r="F80" t="n">
-        <v>0.15456</v>
+        <v>2.83088</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>352.83</v>
+        <v>18.94</v>
       </c>
       <c r="D81" t="n">
-        <v>496.77</v>
+        <v>23.98</v>
       </c>
       <c r="E81" t="n">
-        <v>40.79</v>
+        <v>26.61</v>
       </c>
       <c r="F81" t="n">
-        <v>2.38475</v>
+        <v>0.15742</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2380,22 +2380,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>59.71</v>
+        <v>107.27</v>
       </c>
       <c r="D82" t="n">
-        <v>80.02</v>
+        <v>172.56</v>
       </c>
       <c r="E82" t="n">
-        <v>34.01</v>
+        <v>60.87</v>
       </c>
       <c r="F82" t="n">
-        <v>1.28479</v>
+        <v>-0.66867</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2404,22 +2404,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>44.39</v>
+        <v>59.71</v>
       </c>
       <c r="D83" t="n">
-        <v>60.34</v>
+        <v>80.06</v>
       </c>
       <c r="E83" t="n">
-        <v>35.93</v>
+        <v>34.08</v>
       </c>
       <c r="F83" t="n">
-        <v>0.25495</v>
+        <v>1.2886</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>170.28</v>
+        <v>42.46</v>
       </c>
       <c r="D84" t="n">
-        <v>242.28</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E84" t="n">
-        <v>42.28</v>
+        <v>69.22</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.34406</v>
+        <v>1.88023</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2452,22 +2452,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>136.68</v>
+        <v>352.83</v>
       </c>
       <c r="D85" t="n">
-        <v>156.99</v>
+        <v>497.12</v>
       </c>
       <c r="E85" t="n">
-        <v>14.86</v>
+        <v>40.9</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.72946</v>
+        <v>2.41856</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2476,22 +2476,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>107.27</v>
+        <v>44.39</v>
       </c>
       <c r="D86" t="n">
-        <v>172.57</v>
+        <v>60.34</v>
       </c>
       <c r="E86" t="n">
-        <v>60.87</v>
+        <v>35.93</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.66772</v>
+        <v>0.25495</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2500,22 +2500,22 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>166.5</v>
+        <v>170.28</v>
       </c>
       <c r="D87" t="n">
-        <v>195.23</v>
+        <v>241.96</v>
       </c>
       <c r="E87" t="n">
-        <v>17.26</v>
+        <v>42.1</v>
       </c>
       <c r="F87" t="n">
-        <v>1.01132</v>
+        <v>-1.37415</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2524,16 +2524,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>42.46</v>
+        <v>136.68</v>
       </c>
       <c r="D88" t="n">
-        <v>71.84999999999999</v>
+        <v>156.99</v>
       </c>
       <c r="E88" t="n">
-        <v>69.22</v>
+        <v>14.86</v>
       </c>
       <c r="F88" t="n">
-        <v>1.88023</v>
+        <v>-0.72946</v>
       </c>
     </row>
     <row r="89">
@@ -2563,7 +2563,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2572,22 +2572,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>19.32</v>
+        <v>166.5</v>
       </c>
       <c r="D90" t="n">
-        <v>23.95</v>
+        <v>195.47</v>
       </c>
       <c r="E90" t="n">
-        <v>23.99</v>
+        <v>17.4</v>
       </c>
       <c r="F90" t="n">
-        <v>0.01811</v>
+        <v>1.03418</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2596,22 +2596,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10.51</v>
+        <v>60.37</v>
       </c>
       <c r="D91" t="n">
-        <v>15.3</v>
+        <v>78.72</v>
       </c>
       <c r="E91" t="n">
-        <v>45.58</v>
+        <v>30.4</v>
       </c>
       <c r="F91" t="n">
-        <v>0.36694</v>
+        <v>0.9964499999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2620,22 +2620,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>36.09</v>
+        <v>10.51</v>
       </c>
       <c r="D92" t="n">
-        <v>38.82</v>
+        <v>15.29</v>
       </c>
       <c r="E92" t="n">
-        <v>7.56</v>
+        <v>45.48</v>
       </c>
       <c r="F92" t="n">
-        <v>0.04877</v>
+        <v>0.36599</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2644,40 +2644,40 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>60.37</v>
+        <v>62.12</v>
       </c>
       <c r="D93" t="n">
-        <v>78.78</v>
+        <v>79.97</v>
       </c>
       <c r="E93" t="n">
-        <v>30.5</v>
+        <v>28.73</v>
       </c>
       <c r="F93" t="n">
-        <v>1.00216</v>
+        <v>0.93677</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>62.12</v>
+        <v>48.79</v>
       </c>
       <c r="D94" t="n">
-        <v>79.93000000000001</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>28.67</v>
+        <v>38.49</v>
       </c>
       <c r="F94" t="n">
-        <v>0.93296</v>
+        <v>0.33897</v>
       </c>
     </row>
     <row r="95">
@@ -2707,7 +2707,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2716,46 +2716,46 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>48.79</v>
+        <v>102.17</v>
       </c>
       <c r="D96" t="n">
-        <v>67.56999999999999</v>
+        <v>135.54</v>
       </c>
       <c r="E96" t="n">
-        <v>38.49</v>
+        <v>32.66</v>
       </c>
       <c r="F96" t="n">
-        <v>0.33897</v>
+        <v>1.43815</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>102.17</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D97" t="n">
-        <v>135.51</v>
+        <v>123.51</v>
       </c>
       <c r="E97" t="n">
-        <v>32.63</v>
+        <v>62.43</v>
       </c>
       <c r="F97" t="n">
-        <v>1.43529</v>
+        <v>3.02454</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2764,22 +2764,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>275.27</v>
+        <v>125.73</v>
       </c>
       <c r="D98" t="n">
-        <v>353.11</v>
+        <v>195.62</v>
       </c>
       <c r="E98" t="n">
-        <v>28.28</v>
+        <v>55.59</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.49324</v>
+        <v>0.83805</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2788,22 +2788,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>76.55</v>
+        <v>150.12</v>
       </c>
       <c r="D99" t="n">
-        <v>102.61</v>
+        <v>255.65</v>
       </c>
       <c r="E99" t="n">
-        <v>34.04</v>
+        <v>70.3</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.89647</v>
+        <v>6.95816</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2812,22 +2812,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>74.98999999999999</v>
+        <v>275.27</v>
       </c>
       <c r="D100" t="n">
-        <v>102.4</v>
+        <v>353.13</v>
       </c>
       <c r="E100" t="n">
-        <v>36.56</v>
+        <v>28.28</v>
       </c>
       <c r="F100" t="n">
-        <v>1.20692</v>
+        <v>-1.49134</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2836,22 +2836,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>76.04000000000001</v>
+        <v>140.71</v>
       </c>
       <c r="D101" t="n">
-        <v>123.54</v>
+        <v>185.92</v>
       </c>
       <c r="E101" t="n">
-        <v>62.47</v>
+        <v>32.13</v>
       </c>
       <c r="F101" t="n">
-        <v>3.02739</v>
+        <v>-0.65188</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2860,22 +2860,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>83.81999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>95.06</v>
+        <v>102.38</v>
       </c>
       <c r="E102" t="n">
-        <v>13.41</v>
+        <v>36.52</v>
       </c>
       <c r="F102" t="n">
-        <v>0.23447</v>
+        <v>1.20454</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2884,22 +2884,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>125.73</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D103" t="n">
-        <v>195.59</v>
+        <v>95.06</v>
       </c>
       <c r="E103" t="n">
-        <v>55.56</v>
+        <v>13.41</v>
       </c>
       <c r="F103" t="n">
-        <v>0.83519</v>
+        <v>0.23447</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2908,46 +2908,46 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>150.12</v>
+        <v>76.55</v>
       </c>
       <c r="D104" t="n">
-        <v>255.41</v>
+        <v>102.61</v>
       </c>
       <c r="E104" t="n">
-        <v>70.14</v>
+        <v>34.04</v>
       </c>
       <c r="F104" t="n">
-        <v>6.93578</v>
+        <v>-0.89647</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>140.71</v>
+        <v>141.17</v>
       </c>
       <c r="D105" t="n">
-        <v>185.9</v>
+        <v>176.85</v>
       </c>
       <c r="E105" t="n">
-        <v>32.12</v>
+        <v>25.27</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.65379</v>
+        <v>1.14115</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2956,46 +2956,46 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>141.17</v>
+        <v>33.22</v>
       </c>
       <c r="D106" t="n">
-        <v>177</v>
+        <v>38.83</v>
       </c>
       <c r="E106" t="n">
-        <v>25.38</v>
+        <v>16.89</v>
       </c>
       <c r="F106" t="n">
-        <v>1.15544</v>
+        <v>0.12529</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>33.22</v>
+        <v>450.75</v>
       </c>
       <c r="D107" t="n">
-        <v>38.84</v>
+        <v>544.3200000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>16.92</v>
+        <v>20.76</v>
       </c>
       <c r="F107" t="n">
-        <v>0.12624</v>
+        <v>2.42297</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3004,16 +3004,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>450.75</v>
+        <v>48.87</v>
       </c>
       <c r="D108" t="n">
-        <v>544.3200000000001</v>
+        <v>58.8</v>
       </c>
       <c r="E108" t="n">
-        <v>20.76</v>
+        <v>20.32</v>
       </c>
       <c r="F108" t="n">
-        <v>2.42297</v>
+        <v>-0.23533</v>
       </c>
     </row>
     <row r="109">
@@ -3034,34 +3034,34 @@
         <v>38.62</v>
       </c>
       <c r="E109" t="n">
-        <v>18.96</v>
+        <v>18.94</v>
       </c>
       <c r="F109" t="n">
-        <v>0.35415</v>
+        <v>0.35367</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>48.87</v>
+        <v>2.86</v>
       </c>
       <c r="D110" t="n">
-        <v>58.8</v>
+        <v>3.16</v>
       </c>
       <c r="E110" t="n">
-        <v>20.32</v>
+        <v>10.49</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.23533</v>
+        <v>0.02491</v>
       </c>
     </row>
     <row r="111">
@@ -3091,7 +3091,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3100,22 +3100,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2.86</v>
+        <v>14.94</v>
       </c>
       <c r="D112" t="n">
-        <v>3.14</v>
+        <v>19.53</v>
       </c>
       <c r="E112" t="n">
-        <v>9.970000000000001</v>
+        <v>30.72</v>
       </c>
       <c r="F112" t="n">
-        <v>0.02348</v>
+        <v>0.51817</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>14.94</v>
+        <v>121.48</v>
       </c>
       <c r="D113" t="n">
-        <v>19.53</v>
+        <v>146.3</v>
       </c>
       <c r="E113" t="n">
-        <v>30.72</v>
+        <v>20.43</v>
       </c>
       <c r="F113" t="n">
-        <v>0.51817</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="114">
@@ -3151,19 +3151,19 @@
         <v>53.82</v>
       </c>
       <c r="D114" t="n">
-        <v>74.06999999999999</v>
+        <v>74.08</v>
       </c>
       <c r="E114" t="n">
-        <v>37.63</v>
+        <v>37.64</v>
       </c>
       <c r="F114" t="n">
-        <v>0.46133</v>
+        <v>0.46228</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3172,88 +3172,88 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>121.48</v>
+        <v>19.82</v>
       </c>
       <c r="D115" t="n">
-        <v>146.29</v>
+        <v>25.46</v>
       </c>
       <c r="E115" t="n">
-        <v>20.42</v>
+        <v>28.46</v>
       </c>
       <c r="F115" t="n">
-        <v>0.10495</v>
+        <v>0.29096</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>19.82</v>
+        <v>361.32</v>
       </c>
       <c r="D116" t="n">
-        <v>25.44</v>
+        <v>423.82</v>
       </c>
       <c r="E116" t="n">
-        <v>28.36</v>
+        <v>17.3</v>
       </c>
       <c r="F116" t="n">
-        <v>0.28905</v>
+        <v>4.19429</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>361.32</v>
+        <v>43.67</v>
       </c>
       <c r="D117" t="n">
-        <v>423.47</v>
+        <v>47.13</v>
       </c>
       <c r="E117" t="n">
-        <v>17.2</v>
+        <v>7.92</v>
       </c>
       <c r="F117" t="n">
-        <v>4.16096</v>
+        <v>0.04408</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>43.67</v>
+        <v>15.03</v>
       </c>
       <c r="D118" t="n">
-        <v>47.13</v>
+        <v>18.7</v>
       </c>
       <c r="E118" t="n">
-        <v>7.92</v>
+        <v>24.42</v>
       </c>
       <c r="F118" t="n">
-        <v>0.04408</v>
+        <v>0.12759</v>
       </c>
     </row>
     <row r="119">
@@ -3271,19 +3271,19 @@
         <v>140.19</v>
       </c>
       <c r="D119" t="n">
-        <v>146.64</v>
+        <v>146.67</v>
       </c>
       <c r="E119" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02529</v>
+        <v>0.02814</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3292,46 +3292,46 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>15.03</v>
+        <v>195.11</v>
       </c>
       <c r="D120" t="n">
-        <v>18.72</v>
+        <v>248.36</v>
       </c>
       <c r="E120" t="n">
-        <v>24.55</v>
+        <v>27.29</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1295</v>
+        <v>0.6946099999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>195.11</v>
+        <v>275.99</v>
       </c>
       <c r="D121" t="n">
-        <v>248.3</v>
+        <v>318.2</v>
       </c>
       <c r="E121" t="n">
-        <v>27.26</v>
+        <v>15.29</v>
       </c>
       <c r="F121" t="n">
-        <v>0.68889</v>
+        <v>1.98323</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3340,22 +3340,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>277.69</v>
+        <v>23.85</v>
       </c>
       <c r="D122" t="n">
-        <v>328.55</v>
+        <v>34.15</v>
       </c>
       <c r="E122" t="n">
-        <v>18.32</v>
+        <v>43.19</v>
       </c>
       <c r="F122" t="n">
-        <v>0.44306</v>
+        <v>0.01267</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3364,16 +3364,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>275.99</v>
+        <v>277.69</v>
       </c>
       <c r="D123" t="n">
-        <v>318.23</v>
+        <v>328.7</v>
       </c>
       <c r="E123" t="n">
-        <v>15.3</v>
+        <v>18.37</v>
       </c>
       <c r="F123" t="n">
-        <v>1.98561</v>
+        <v>0.45735</v>
       </c>
     </row>
     <row r="124">
@@ -3391,19 +3391,19 @@
         <v>182.82</v>
       </c>
       <c r="D124" t="n">
-        <v>229.65</v>
+        <v>229.44</v>
       </c>
       <c r="E124" t="n">
-        <v>25.62</v>
+        <v>25.5</v>
       </c>
       <c r="F124" t="n">
-        <v>-1.28339</v>
+        <v>-1.30339</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3412,46 +3412,46 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>23.85</v>
+        <v>73.75</v>
       </c>
       <c r="D125" t="n">
-        <v>34.15</v>
+        <v>93.75</v>
       </c>
       <c r="E125" t="n">
-        <v>43.19</v>
+        <v>27.12</v>
       </c>
       <c r="F125" t="n">
-        <v>0.01267</v>
+        <v>0.46174</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>73.75</v>
+        <v>9.85</v>
       </c>
       <c r="D126" t="n">
-        <v>93.76000000000001</v>
+        <v>14</v>
       </c>
       <c r="E126" t="n">
-        <v>27.13</v>
+        <v>42.13</v>
       </c>
       <c r="F126" t="n">
-        <v>0.46269</v>
+        <v>0.47309</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3460,22 +3460,22 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>36.25</v>
+        <v>309.78</v>
       </c>
       <c r="D127" t="n">
-        <v>41.47</v>
+        <v>341.86</v>
       </c>
       <c r="E127" t="n">
-        <v>14.4</v>
+        <v>10.36</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1536</v>
+        <v>-0.62071</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3484,46 +3484,46 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>9.85</v>
+        <v>36.25</v>
       </c>
       <c r="D128" t="n">
-        <v>14.03</v>
+        <v>41.48</v>
       </c>
       <c r="E128" t="n">
-        <v>42.44</v>
+        <v>14.43</v>
       </c>
       <c r="F128" t="n">
-        <v>0.47594</v>
+        <v>0.15456</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>309.78</v>
+        <v>190.4</v>
       </c>
       <c r="D129" t="n">
-        <v>341.9</v>
+        <v>221.31</v>
       </c>
       <c r="E129" t="n">
-        <v>10.37</v>
+        <v>16.23</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.61642</v>
+        <v>0.59114</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>190.4</v>
+        <v>63.54</v>
       </c>
       <c r="D130" t="n">
-        <v>221.15</v>
+        <v>71.28</v>
       </c>
       <c r="E130" t="n">
-        <v>16.15</v>
+        <v>12.18</v>
       </c>
       <c r="F130" t="n">
-        <v>0.57638</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="131">
@@ -3559,91 +3559,91 @@
         <v>33.54</v>
       </c>
       <c r="D131" t="n">
-        <v>42.16</v>
+        <v>42.18</v>
       </c>
       <c r="E131" t="n">
-        <v>25.7</v>
+        <v>25.76</v>
       </c>
       <c r="F131" t="n">
-        <v>0.13689</v>
+        <v>0.1388</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>63.54</v>
+        <v>529.12</v>
       </c>
       <c r="D132" t="n">
-        <v>71.28</v>
+        <v>684.04</v>
       </c>
       <c r="E132" t="n">
-        <v>12.18</v>
+        <v>29.28</v>
       </c>
       <c r="F132" t="n">
-        <v>0.374</v>
+        <v>9.50407</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>529.12</v>
+        <v>57.4</v>
       </c>
       <c r="D133" t="n">
-        <v>683.88</v>
+        <v>103.69</v>
       </c>
       <c r="E133" t="n">
-        <v>29.25</v>
+        <v>80.64</v>
       </c>
       <c r="F133" t="n">
-        <v>9.48836</v>
+        <v>0.53257</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>57.4</v>
+        <v>161.91</v>
       </c>
       <c r="D134" t="n">
-        <v>103.61</v>
+        <v>209.36</v>
       </c>
       <c r="E134" t="n">
-        <v>80.51000000000001</v>
+        <v>29.31</v>
       </c>
       <c r="F134" t="n">
-        <v>0.52495</v>
+        <v>-1.52751</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3652,22 +3652,22 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>186.61</v>
+        <v>63.16</v>
       </c>
       <c r="D135" t="n">
-        <v>247.29</v>
+        <v>100.67</v>
       </c>
       <c r="E135" t="n">
-        <v>32.52</v>
+        <v>59.39</v>
       </c>
       <c r="F135" t="n">
-        <v>0.21288</v>
+        <v>1.35459</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3676,22 +3676,22 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>43.3</v>
+        <v>250.4</v>
       </c>
       <c r="D136" t="n">
-        <v>72.34</v>
+        <v>323.97</v>
       </c>
       <c r="E136" t="n">
-        <v>67.06999999999999</v>
+        <v>29.38</v>
       </c>
       <c r="F136" t="n">
-        <v>0.008569999999999999</v>
+        <v>-3.61611</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3700,22 +3700,22 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>63.16</v>
+        <v>102.87</v>
       </c>
       <c r="D137" t="n">
-        <v>100.71</v>
+        <v>174.73</v>
       </c>
       <c r="E137" t="n">
-        <v>59.45</v>
+        <v>69.86</v>
       </c>
       <c r="F137" t="n">
-        <v>1.3584</v>
+        <v>-0.36801</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3724,22 +3724,22 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>73.42</v>
+        <v>186.61</v>
       </c>
       <c r="D138" t="n">
-        <v>89.76000000000001</v>
+        <v>247.08</v>
       </c>
       <c r="E138" t="n">
-        <v>22.26</v>
+        <v>32.4</v>
       </c>
       <c r="F138" t="n">
-        <v>0.70783</v>
+        <v>0.19288</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3748,22 +3748,22 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>161.91</v>
+        <v>26.18</v>
       </c>
       <c r="D139" t="n">
-        <v>209.26</v>
+        <v>36.72</v>
       </c>
       <c r="E139" t="n">
-        <v>29.24</v>
+        <v>40.26</v>
       </c>
       <c r="F139" t="n">
-        <v>-1.53704</v>
+        <v>0.23738</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3772,22 +3772,22 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>250.4</v>
+        <v>43.3</v>
       </c>
       <c r="D140" t="n">
-        <v>323.85</v>
+        <v>72.34</v>
       </c>
       <c r="E140" t="n">
-        <v>29.33</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F140" t="n">
-        <v>-3.62754</v>
+        <v>0.008569999999999999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3796,22 +3796,22 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>102.87</v>
+        <v>73.42</v>
       </c>
       <c r="D141" t="n">
-        <v>174.73</v>
+        <v>89.72</v>
       </c>
       <c r="E141" t="n">
-        <v>69.86</v>
+        <v>22.2</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.36801</v>
+        <v>0.70402</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3820,142 +3820,142 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>26.18</v>
+        <v>438.34</v>
       </c>
       <c r="D142" t="n">
-        <v>36.72</v>
+        <v>641.39</v>
       </c>
       <c r="E142" t="n">
-        <v>40.26</v>
+        <v>46.32</v>
       </c>
       <c r="F142" t="n">
-        <v>0.23738</v>
+        <v>3.85233</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>438.34</v>
+        <v>163.43</v>
       </c>
       <c r="D143" t="n">
-        <v>641.49</v>
+        <v>198.63</v>
       </c>
       <c r="E143" t="n">
-        <v>46.35</v>
+        <v>21.54</v>
       </c>
       <c r="F143" t="n">
-        <v>3.86233</v>
+        <v>1.4774</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>163.43</v>
+        <v>55.52</v>
       </c>
       <c r="D144" t="n">
-        <v>198.63</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="E144" t="n">
-        <v>21.54</v>
+        <v>67.94</v>
       </c>
       <c r="F144" t="n">
-        <v>1.4774</v>
+        <v>1.96119</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>107.27</v>
+        <v>99.3</v>
       </c>
       <c r="D145" t="n">
-        <v>144.93</v>
+        <v>153.74</v>
       </c>
       <c r="E145" t="n">
-        <v>35.11</v>
+        <v>54.82</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.92318</v>
+        <v>2.14918</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>55.52</v>
+        <v>197.73</v>
       </c>
       <c r="D146" t="n">
-        <v>93.20999999999999</v>
+        <v>223.04</v>
       </c>
       <c r="E146" t="n">
-        <v>67.89</v>
+        <v>12.8</v>
       </c>
       <c r="F146" t="n">
-        <v>1.95833</v>
+        <v>0.94077</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>99.3</v>
+        <v>725.17</v>
       </c>
       <c r="D147" t="n">
-        <v>153.74</v>
+        <v>899.5599999999999</v>
       </c>
       <c r="E147" t="n">
-        <v>54.82</v>
+        <v>24.05</v>
       </c>
       <c r="F147" t="n">
-        <v>2.14918</v>
+        <v>2.47985</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3964,64 +3964,64 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>197.73</v>
+        <v>79.58</v>
       </c>
       <c r="D148" t="n">
-        <v>222.98</v>
+        <v>98.41</v>
       </c>
       <c r="E148" t="n">
-        <v>12.77</v>
+        <v>23.66</v>
       </c>
       <c r="F148" t="n">
-        <v>0.93505</v>
+        <v>-0.83257</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>79.58</v>
+        <v>255.54</v>
       </c>
       <c r="D149" t="n">
-        <v>98.39</v>
+        <v>365.08</v>
       </c>
       <c r="E149" t="n">
-        <v>23.64</v>
+        <v>42.87</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.83448</v>
+        <v>3.26755</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>725.17</v>
+        <v>417.83</v>
       </c>
       <c r="D150" t="n">
-        <v>899.3200000000001</v>
+        <v>558.26</v>
       </c>
       <c r="E150" t="n">
-        <v>24.02</v>
+        <v>33.61</v>
       </c>
       <c r="F150" t="n">
-        <v>2.457</v>
+        <v>3.75502</v>
       </c>
     </row>
     <row r="151">
@@ -4039,181 +4039,181 @@
         <v>12.64</v>
       </c>
       <c r="D151" t="n">
-        <v>18.24</v>
+        <v>18.26</v>
       </c>
       <c r="E151" t="n">
-        <v>44.3</v>
+        <v>44.46</v>
       </c>
       <c r="F151" t="n">
-        <v>0.25874</v>
+        <v>0.26064</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>417.83</v>
+        <v>32.32</v>
       </c>
       <c r="D152" t="n">
-        <v>558.9</v>
+        <v>37.81</v>
       </c>
       <c r="E152" t="n">
-        <v>33.76</v>
+        <v>16.99</v>
       </c>
       <c r="F152" t="n">
-        <v>3.8155</v>
+        <v>0.07455000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>255.54</v>
+        <v>699965</v>
       </c>
       <c r="D153" t="n">
-        <v>365.08</v>
+        <v>773825</v>
       </c>
       <c r="E153" t="n">
-        <v>42.87</v>
+        <v>10.55</v>
       </c>
       <c r="F153" t="n">
-        <v>3.26755</v>
+        <v>3681.50215</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>FMS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>32.32</v>
+        <v>20.19</v>
       </c>
       <c r="D154" t="n">
-        <v>37.84</v>
+        <v>22.96</v>
       </c>
       <c r="E154" t="n">
-        <v>17.08</v>
+        <v>13.72</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0774</v>
+        <v>-0.15989</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>699965</v>
+        <v>139.71</v>
       </c>
       <c r="D155" t="n">
-        <v>773432.0600000001</v>
+        <v>193.9</v>
       </c>
       <c r="E155" t="n">
-        <v>10.5</v>
+        <v>38.79</v>
       </c>
       <c r="F155" t="n">
-        <v>3644.07953</v>
+        <v>2.09242</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>139.71</v>
+        <v>45.37</v>
       </c>
       <c r="D156" t="n">
-        <v>193.84</v>
+        <v>143.77</v>
       </c>
       <c r="E156" t="n">
-        <v>38.74</v>
+        <v>216.88</v>
       </c>
       <c r="F156" t="n">
-        <v>2.08671</v>
+        <v>5.51342</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>45.37</v>
+        <v>112.47</v>
       </c>
       <c r="D157" t="n">
-        <v>143.77</v>
+        <v>137.79</v>
       </c>
       <c r="E157" t="n">
-        <v>216.88</v>
+        <v>22.51</v>
       </c>
       <c r="F157" t="n">
-        <v>5.51342</v>
+        <v>0.54053</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>112.47</v>
+        <v>156.66</v>
       </c>
       <c r="D158" t="n">
-        <v>137.79</v>
+        <v>269.67</v>
       </c>
       <c r="E158" t="n">
-        <v>22.51</v>
+        <v>72.14</v>
       </c>
       <c r="F158" t="n">
-        <v>0.54053</v>
+        <v>3.05682</v>
       </c>
     </row>
     <row r="159">
@@ -4231,115 +4231,115 @@
         <v>82.26000000000001</v>
       </c>
       <c r="D159" t="n">
-        <v>140.14</v>
+        <v>140.19</v>
       </c>
       <c r="E159" t="n">
-        <v>70.36</v>
+        <v>70.42</v>
       </c>
       <c r="F159" t="n">
-        <v>1.6294</v>
+        <v>1.63417</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>156.66</v>
+        <v>40.41</v>
       </c>
       <c r="D160" t="n">
-        <v>269.5</v>
+        <v>52.93</v>
       </c>
       <c r="E160" t="n">
-        <v>72.03</v>
+        <v>30.98</v>
       </c>
       <c r="F160" t="n">
-        <v>3.04062</v>
+        <v>0.06672</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>40.41</v>
+        <v>197.38</v>
       </c>
       <c r="D161" t="n">
-        <v>52.94</v>
+        <v>263.04</v>
       </c>
       <c r="E161" t="n">
-        <v>31.01</v>
+        <v>33.27</v>
       </c>
       <c r="F161" t="n">
-        <v>0.06766999999999999</v>
+        <v>1.10836</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>197.38</v>
+        <v>393.42</v>
       </c>
       <c r="D162" t="n">
-        <v>262.94</v>
+        <v>620.48</v>
       </c>
       <c r="E162" t="n">
-        <v>33.22</v>
+        <v>57.71</v>
       </c>
       <c r="F162" t="n">
-        <v>1.09884</v>
+        <v>1.40198</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>393.42</v>
+        <v>74.63</v>
       </c>
       <c r="D163" t="n">
-        <v>620.48</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E163" t="n">
-        <v>57.71</v>
+        <v>18.87</v>
       </c>
       <c r="F163" t="n">
-        <v>1.40198</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4348,64 +4348,64 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>74.63</v>
+        <v>465.4</v>
       </c>
       <c r="D164" t="n">
-        <v>88.70999999999999</v>
+        <v>516.76</v>
       </c>
       <c r="E164" t="n">
-        <v>18.86</v>
+        <v>11.04</v>
       </c>
       <c r="F164" t="n">
-        <v>0.05992</v>
+        <v>2.46605</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>465.4</v>
+        <v>153.25</v>
       </c>
       <c r="D165" t="n">
-        <v>516.77</v>
+        <v>194.11</v>
       </c>
       <c r="E165" t="n">
-        <v>11.04</v>
+        <v>26.66</v>
       </c>
       <c r="F165" t="n">
-        <v>2.46652</v>
+        <v>1.57503</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>153.25</v>
+        <v>20.96</v>
       </c>
       <c r="D166" t="n">
-        <v>194.09</v>
+        <v>25.77</v>
       </c>
       <c r="E166" t="n">
-        <v>26.65</v>
+        <v>22.95</v>
       </c>
       <c r="F166" t="n">
-        <v>1.57313</v>
+        <v>0.24889</v>
       </c>
     </row>
     <row r="167">
@@ -4423,43 +4423,43 @@
         <v>155.75</v>
       </c>
       <c r="D167" t="n">
-        <v>265.01</v>
+        <v>264.93</v>
       </c>
       <c r="E167" t="n">
-        <v>70.15000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F167" t="n">
-        <v>5.59667</v>
+        <v>5.58905</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>20.96</v>
+        <v>40.59</v>
       </c>
       <c r="D168" t="n">
-        <v>25.77</v>
+        <v>57.61</v>
       </c>
       <c r="E168" t="n">
-        <v>22.95</v>
+        <v>41.93</v>
       </c>
       <c r="F168" t="n">
-        <v>0.24889</v>
+        <v>1.55685</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4468,22 +4468,22 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>223.65</v>
+        <v>213.69</v>
       </c>
       <c r="D169" t="n">
-        <v>396.95</v>
+        <v>410.84</v>
       </c>
       <c r="E169" t="n">
-        <v>77.48999999999999</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F169" t="n">
-        <v>11.65836</v>
+        <v>10.41305</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>40.59</v>
+        <v>223.65</v>
       </c>
       <c r="D170" t="n">
-        <v>57.63</v>
+        <v>397.04</v>
       </c>
       <c r="E170" t="n">
-        <v>41.98</v>
+        <v>77.53</v>
       </c>
       <c r="F170" t="n">
-        <v>1.55876</v>
+        <v>11.66693</v>
       </c>
     </row>
     <row r="171">
@@ -4519,37 +4519,37 @@
         <v>128.43</v>
       </c>
       <c r="D171" t="n">
-        <v>153.79</v>
+        <v>153.74</v>
       </c>
       <c r="E171" t="n">
-        <v>19.75</v>
+        <v>19.71</v>
       </c>
       <c r="F171" t="n">
-        <v>1.24532</v>
+        <v>1.24056</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>213.69</v>
+        <v>18.71</v>
       </c>
       <c r="D172" t="n">
-        <v>410.73</v>
+        <v>21.33</v>
       </c>
       <c r="E172" t="n">
-        <v>92.20999999999999</v>
+        <v>14</v>
       </c>
       <c r="F172" t="n">
-        <v>10.40258</v>
+        <v>0.09087000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -4567,43 +4567,43 @@
         <v>66.95</v>
       </c>
       <c r="D173" t="n">
-        <v>86.59999999999999</v>
+        <v>86.61</v>
       </c>
       <c r="E173" t="n">
-        <v>29.35</v>
+        <v>29.37</v>
       </c>
       <c r="F173" t="n">
-        <v>1.36722</v>
+        <v>1.36817</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>18.71</v>
+        <v>151.43</v>
       </c>
       <c r="D174" t="n">
-        <v>21.34</v>
+        <v>266.62</v>
       </c>
       <c r="E174" t="n">
-        <v>14.06</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F174" t="n">
-        <v>0.09182</v>
+        <v>1.96202</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4612,22 +4612,22 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>112.5</v>
+        <v>105.37</v>
       </c>
       <c r="D175" t="n">
-        <v>190.67</v>
+        <v>230.27</v>
       </c>
       <c r="E175" t="n">
-        <v>69.48</v>
+        <v>118.53</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.51289</v>
+        <v>-1.24495</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4636,22 +4636,22 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>10.49</v>
+        <v>120.88</v>
       </c>
       <c r="D176" t="n">
-        <v>19.98</v>
+        <v>209.62</v>
       </c>
       <c r="E176" t="n">
-        <v>90.47</v>
+        <v>73.41</v>
       </c>
       <c r="F176" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.40223</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4660,22 +4660,22 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>32.36</v>
+        <v>62.93</v>
       </c>
       <c r="D177" t="n">
-        <v>55.17</v>
+        <v>190.45</v>
       </c>
       <c r="E177" t="n">
-        <v>70.47</v>
+        <v>202.64</v>
       </c>
       <c r="F177" t="n">
-        <v>0.76641</v>
+        <v>7.34012</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4684,22 +4684,22 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>118.05</v>
+        <v>76.7</v>
       </c>
       <c r="D178" t="n">
-        <v>193.89</v>
+        <v>172.37</v>
       </c>
       <c r="E178" t="n">
-        <v>64.23999999999999</v>
+        <v>124.73</v>
       </c>
       <c r="F178" t="n">
-        <v>2.28457</v>
+        <v>2.05425</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4708,22 +4708,22 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>57.15</v>
+        <v>166.99</v>
       </c>
       <c r="D179" t="n">
-        <v>189.81</v>
+        <v>327.23</v>
       </c>
       <c r="E179" t="n">
-        <v>232.13</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="F179" t="n">
-        <v>4.93853</v>
+        <v>9.443759999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4732,22 +4732,22 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>78.59999999999999</v>
+        <v>34.41</v>
       </c>
       <c r="D180" t="n">
-        <v>175.65</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E180" t="n">
-        <v>123.47</v>
+        <v>97.59</v>
       </c>
       <c r="F180" t="n">
-        <v>1.12337</v>
+        <v>0.22691</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>17.89</v>
+        <v>10.49</v>
       </c>
       <c r="D181" t="n">
-        <v>31.23</v>
+        <v>19.98</v>
       </c>
       <c r="E181" t="n">
-        <v>74.56999999999999</v>
+        <v>90.47</v>
       </c>
       <c r="F181" t="n">
-        <v>0.39427</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4780,22 +4780,22 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>151.43</v>
+        <v>57.15</v>
       </c>
       <c r="D182" t="n">
-        <v>266.67</v>
+        <v>189.81</v>
       </c>
       <c r="E182" t="n">
-        <v>76.09999999999999</v>
+        <v>232.13</v>
       </c>
       <c r="F182" t="n">
-        <v>1.96631</v>
+        <v>4.93853</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4804,22 +4804,22 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>188.79</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D183" t="n">
-        <v>276.53</v>
+        <v>175.65</v>
       </c>
       <c r="E183" t="n">
-        <v>46.47</v>
+        <v>123.47</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.99091</v>
+        <v>1.12337</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4828,22 +4828,22 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>62.93</v>
+        <v>118.05</v>
       </c>
       <c r="D184" t="n">
-        <v>190.45</v>
+        <v>193.89</v>
       </c>
       <c r="E184" t="n">
-        <v>202.64</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="F184" t="n">
-        <v>7.34012</v>
+        <v>2.28457</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4852,22 +4852,22 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>117.65</v>
+        <v>188.79</v>
       </c>
       <c r="D185" t="n">
-        <v>242.36</v>
+        <v>276.53</v>
       </c>
       <c r="E185" t="n">
-        <v>106</v>
+        <v>46.47</v>
       </c>
       <c r="F185" t="n">
-        <v>1.81283</v>
+        <v>-0.99091</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4876,22 +4876,22 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>120.88</v>
+        <v>32.36</v>
       </c>
       <c r="D186" t="n">
-        <v>209.62</v>
+        <v>55.17</v>
       </c>
       <c r="E186" t="n">
-        <v>73.41</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.40223</v>
+        <v>0.76689</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4900,22 +4900,22 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>105.37</v>
+        <v>83</v>
       </c>
       <c r="D187" t="n">
-        <v>230.27</v>
+        <v>141.9</v>
       </c>
       <c r="E187" t="n">
-        <v>118.53</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F187" t="n">
-        <v>-1.24495</v>
+        <v>1.71804</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4924,22 +4924,22 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>34.41</v>
+        <v>18.26</v>
       </c>
       <c r="D188" t="n">
-        <v>67.98999999999999</v>
+        <v>33.82</v>
       </c>
       <c r="E188" t="n">
-        <v>97.59</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="F188" t="n">
-        <v>0.22691</v>
+        <v>1.18337</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4948,22 +4948,22 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>18.26</v>
+        <v>112.5</v>
       </c>
       <c r="D189" t="n">
-        <v>33.82</v>
+        <v>190.67</v>
       </c>
       <c r="E189" t="n">
-        <v>85.20999999999999</v>
+        <v>69.48</v>
       </c>
       <c r="F189" t="n">
-        <v>1.18337</v>
+        <v>-0.51289</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4972,22 +4972,22 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>43.81</v>
+        <v>25.85</v>
       </c>
       <c r="D190" t="n">
-        <v>103.52</v>
+        <v>41.65</v>
       </c>
       <c r="E190" t="n">
-        <v>136.29</v>
+        <v>61.12</v>
       </c>
       <c r="F190" t="n">
-        <v>1.01949</v>
+        <v>0.40151</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4996,22 +4996,22 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>25.85</v>
+        <v>43.81</v>
       </c>
       <c r="D191" t="n">
-        <v>41.64</v>
+        <v>103.55</v>
       </c>
       <c r="E191" t="n">
-        <v>61.08</v>
+        <v>136.36</v>
       </c>
       <c r="F191" t="n">
-        <v>0.40056</v>
+        <v>1.02235</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>83</v>
+        <v>117.65</v>
       </c>
       <c r="D192" t="n">
-        <v>141.91</v>
+        <v>242.16</v>
       </c>
       <c r="E192" t="n">
-        <v>70.98</v>
+        <v>105.83</v>
       </c>
       <c r="F192" t="n">
-        <v>1.71899</v>
+        <v>1.79379</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5044,46 +5044,46 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>76.7</v>
+        <v>17.89</v>
       </c>
       <c r="D193" t="n">
-        <v>172.37</v>
+        <v>31.23</v>
       </c>
       <c r="E193" t="n">
-        <v>124.73</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="F193" t="n">
-        <v>2.05425</v>
+        <v>0.39427</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>166.99</v>
+        <v>95.67</v>
       </c>
       <c r="D194" t="n">
-        <v>327.11</v>
+        <v>189.93</v>
       </c>
       <c r="E194" t="n">
-        <v>95.89</v>
+        <v>98.53</v>
       </c>
       <c r="F194" t="n">
-        <v>9.43233</v>
+        <v>0.92719</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5092,40 +5092,40 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>95.67</v>
+        <v>56.43</v>
       </c>
       <c r="D195" t="n">
-        <v>189.93</v>
+        <v>112.25</v>
       </c>
       <c r="E195" t="n">
-        <v>98.53</v>
+        <v>98.92</v>
       </c>
       <c r="F195" t="n">
-        <v>0.92719</v>
+        <v>3.11717</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>56.43</v>
+        <v>62.49</v>
       </c>
       <c r="D196" t="n">
-        <v>112.31</v>
+        <v>90.06</v>
       </c>
       <c r="E196" t="n">
-        <v>99.03</v>
+        <v>44.12</v>
       </c>
       <c r="F196" t="n">
-        <v>3.12288</v>
+        <v>-0.21073</v>
       </c>
     </row>
     <row r="197">
@@ -5155,7 +5155,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5164,22 +5164,22 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>62.49</v>
+        <v>124.07</v>
       </c>
       <c r="D198" t="n">
-        <v>90.08</v>
+        <v>187.8</v>
       </c>
       <c r="E198" t="n">
-        <v>44.15</v>
+        <v>51.37</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.20883</v>
+        <v>4.85902</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5188,46 +5188,46 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>124.07</v>
+        <v>23.49</v>
       </c>
       <c r="D199" t="n">
-        <v>187.84</v>
+        <v>32.21</v>
       </c>
       <c r="E199" t="n">
-        <v>51.4</v>
+        <v>37.12</v>
       </c>
       <c r="F199" t="n">
-        <v>4.86283</v>
+        <v>0.17481</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>23.49</v>
+        <v>172.34</v>
       </c>
       <c r="D200" t="n">
-        <v>32.23</v>
+        <v>216.17</v>
       </c>
       <c r="E200" t="n">
-        <v>37.21</v>
+        <v>25.43</v>
       </c>
       <c r="F200" t="n">
-        <v>0.17672</v>
+        <v>0.34426</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5236,46 +5236,46 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>172.34</v>
+        <v>430.4</v>
       </c>
       <c r="D201" t="n">
-        <v>216.17</v>
+        <v>559.34</v>
       </c>
       <c r="E201" t="n">
-        <v>25.43</v>
+        <v>29.96</v>
       </c>
       <c r="F201" t="n">
-        <v>0.34426</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>BML-PJ</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>430.4</v>
+        <v>19.05</v>
       </c>
       <c r="D202" t="n">
-        <v>559.3099999999999</v>
+        <v>19.64</v>
       </c>
       <c r="E202" t="n">
-        <v>29.95</v>
+        <v>3.1</v>
       </c>
       <c r="F202" t="n">
-        <v>0.94514</v>
+        <v>0.02454</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5284,22 +5284,22 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>96.73</v>
+        <v>164.13</v>
       </c>
       <c r="D203" t="n">
-        <v>121.88</v>
+        <v>543.51</v>
       </c>
       <c r="E203" t="n">
-        <v>26</v>
+        <v>231.15</v>
       </c>
       <c r="F203" t="n">
-        <v>0.42451</v>
+        <v>20.08884</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5308,70 +5308,70 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>164.13</v>
+        <v>96.73</v>
       </c>
       <c r="D204" t="n">
-        <v>543.51</v>
+        <v>122</v>
       </c>
       <c r="E204" t="n">
-        <v>231.15</v>
+        <v>26.12</v>
       </c>
       <c r="F204" t="n">
-        <v>20.08884</v>
+        <v>0.43594</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BML-PJ</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>19.05</v>
+        <v>12.96</v>
       </c>
       <c r="D205" t="n">
-        <v>19.64</v>
+        <v>16.65</v>
       </c>
       <c r="E205" t="n">
-        <v>3.1</v>
+        <v>28.47</v>
       </c>
       <c r="F205" t="n">
-        <v>0.02454</v>
+        <v>-0.03231</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RF-PC</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>23.5</v>
+        <v>284.79</v>
       </c>
       <c r="D206" t="n">
-        <v>24.51</v>
+        <v>417.54</v>
       </c>
       <c r="E206" t="n">
-        <v>4.3</v>
+        <v>46.61</v>
       </c>
       <c r="F206" t="n">
-        <v>0.02458</v>
+        <v>6.50222</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5380,22 +5380,22 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>273.5</v>
+        <v>166</v>
       </c>
       <c r="D207" t="n">
-        <v>345.04</v>
+        <v>396.62</v>
       </c>
       <c r="E207" t="n">
-        <v>26.16</v>
+        <v>138.93</v>
       </c>
       <c r="F207" t="n">
-        <v>0.07615</v>
+        <v>3.79223</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5404,22 +5404,22 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>59.66</v>
+        <v>119.51</v>
       </c>
       <c r="D208" t="n">
-        <v>82.65000000000001</v>
+        <v>259.35</v>
       </c>
       <c r="E208" t="n">
-        <v>38.54</v>
+        <v>117.01</v>
       </c>
       <c r="F208" t="n">
-        <v>1.52607</v>
+        <v>10.66539</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5428,22 +5428,22 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>22.61</v>
+        <v>29.16</v>
       </c>
       <c r="D209" t="n">
-        <v>55.88</v>
+        <v>39.69</v>
       </c>
       <c r="E209" t="n">
-        <v>147.15</v>
+        <v>36.11</v>
       </c>
       <c r="F209" t="n">
-        <v>1.10062</v>
+        <v>0.07466</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>8.609999999999999</v>
+        <v>97.52</v>
       </c>
       <c r="D210" t="n">
-        <v>21.61</v>
+        <v>129.59</v>
       </c>
       <c r="E210" t="n">
-        <v>150.99</v>
+        <v>32.89</v>
       </c>
       <c r="F210" t="n">
-        <v>0.62903</v>
+        <v>2.24577</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5476,22 +5476,22 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>166</v>
+        <v>28.35</v>
       </c>
       <c r="D211" t="n">
-        <v>396.82</v>
+        <v>39.25</v>
       </c>
       <c r="E211" t="n">
-        <v>139.05</v>
+        <v>38.45</v>
       </c>
       <c r="F211" t="n">
-        <v>3.81127</v>
+        <v>0.49418</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>119.51</v>
+        <v>131.47</v>
       </c>
       <c r="D212" t="n">
-        <v>258.96</v>
+        <v>206.99</v>
       </c>
       <c r="E212" t="n">
-        <v>116.68</v>
+        <v>57.44</v>
       </c>
       <c r="F212" t="n">
-        <v>10.62825</v>
+        <v>2.05473</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5524,22 +5524,22 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>29.16</v>
+        <v>258.08</v>
       </c>
       <c r="D213" t="n">
-        <v>39.67</v>
+        <v>288.9</v>
       </c>
       <c r="E213" t="n">
-        <v>36.06</v>
+        <v>11.94</v>
       </c>
       <c r="F213" t="n">
-        <v>0.07323</v>
+        <v>1.81284</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>65.16</v>
+        <v>24.77</v>
       </c>
       <c r="D214" t="n">
-        <v>110.45</v>
+        <v>36.78</v>
       </c>
       <c r="E214" t="n">
-        <v>69.51000000000001</v>
+        <v>48.49</v>
       </c>
       <c r="F214" t="n">
-        <v>1.57155</v>
+        <v>0.38487</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5572,22 +5572,22 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>97.52</v>
+        <v>73.13</v>
       </c>
       <c r="D215" t="n">
-        <v>129.54</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E215" t="n">
-        <v>32.83</v>
+        <v>31.03</v>
       </c>
       <c r="F215" t="n">
-        <v>2.24073</v>
+        <v>0.60843</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5596,22 +5596,22 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>19.02</v>
+        <v>67.39</v>
       </c>
       <c r="D216" t="n">
-        <v>26.77</v>
+        <v>93.28</v>
       </c>
       <c r="E216" t="n">
-        <v>40.77</v>
+        <v>38.42</v>
       </c>
       <c r="F216" t="n">
-        <v>0.2964</v>
+        <v>0.61522</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5620,22 +5620,22 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>28.35</v>
+        <v>22.61</v>
       </c>
       <c r="D217" t="n">
-        <v>39.21</v>
+        <v>55.88</v>
       </c>
       <c r="E217" t="n">
-        <v>38.31</v>
+        <v>147.15</v>
       </c>
       <c r="F217" t="n">
-        <v>0.49037</v>
+        <v>1.10062</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5644,22 +5644,22 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>67.39</v>
+        <v>65.16</v>
       </c>
       <c r="D218" t="n">
-        <v>93.27</v>
+        <v>110.45</v>
       </c>
       <c r="E218" t="n">
-        <v>38.4</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="F218" t="n">
-        <v>0.61426</v>
+        <v>1.57155</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5668,22 +5668,22 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>284.79</v>
+        <v>19.02</v>
       </c>
       <c r="D219" t="n">
-        <v>417.14</v>
+        <v>26.78</v>
       </c>
       <c r="E219" t="n">
-        <v>46.47</v>
+        <v>40.8</v>
       </c>
       <c r="F219" t="n">
-        <v>6.4646</v>
+        <v>0.29688</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5692,22 +5692,22 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>73.13</v>
+        <v>116.13</v>
       </c>
       <c r="D220" t="n">
-        <v>95.81999999999999</v>
+        <v>192.84</v>
       </c>
       <c r="E220" t="n">
-        <v>31.03</v>
+        <v>66.06</v>
       </c>
       <c r="F220" t="n">
-        <v>0.60843</v>
+        <v>0.13947</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5716,22 +5716,22 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>24.77</v>
+        <v>16.32</v>
       </c>
       <c r="D221" t="n">
-        <v>36.78</v>
+        <v>23.71</v>
       </c>
       <c r="E221" t="n">
-        <v>48.47</v>
+        <v>45.28</v>
       </c>
       <c r="F221" t="n">
-        <v>0.38439</v>
+        <v>0.26691</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5740,22 +5740,22 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>258.08</v>
+        <v>41.19</v>
       </c>
       <c r="D222" t="n">
-        <v>288.93</v>
+        <v>97.14</v>
       </c>
       <c r="E222" t="n">
-        <v>11.95</v>
+        <v>135.83</v>
       </c>
       <c r="F222" t="n">
-        <v>1.8157</v>
+        <v>1.2311</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5764,22 +5764,22 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>273.14</v>
+        <v>52.5</v>
       </c>
       <c r="D223" t="n">
-        <v>341.4</v>
+        <v>90</v>
       </c>
       <c r="E223" t="n">
-        <v>24.99</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.06191</v>
+        <v>5.23697</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>131.47</v>
+        <v>107.27</v>
       </c>
       <c r="D224" t="n">
-        <v>207.1</v>
+        <v>136.17</v>
       </c>
       <c r="E224" t="n">
-        <v>57.53</v>
+        <v>26.94</v>
       </c>
       <c r="F224" t="n">
-        <v>2.06521</v>
+        <v>0.75183</v>
       </c>
     </row>
     <row r="225">
@@ -5815,19 +5815,19 @@
         <v>196.04</v>
       </c>
       <c r="D225" t="n">
-        <v>504.4</v>
+        <v>504.2</v>
       </c>
       <c r="E225" t="n">
-        <v>157.29</v>
+        <v>157.19</v>
       </c>
       <c r="F225" t="n">
-        <v>7.31328</v>
+        <v>7.29423</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5836,22 +5836,22 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>41.19</v>
+        <v>3.88</v>
       </c>
       <c r="D226" t="n">
-        <v>97.06999999999999</v>
+        <v>6.44</v>
       </c>
       <c r="E226" t="n">
-        <v>135.66</v>
+        <v>65.98</v>
       </c>
       <c r="F226" t="n">
-        <v>1.22443</v>
+        <v>0.07534</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5860,22 +5860,22 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>26.41</v>
+        <v>246.63</v>
       </c>
       <c r="D227" t="n">
-        <v>39.5</v>
+        <v>331.34</v>
       </c>
       <c r="E227" t="n">
-        <v>49.56</v>
+        <v>34.35</v>
       </c>
       <c r="F227" t="n">
-        <v>1.30846</v>
+        <v>4.71551</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5884,22 +5884,22 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>116.13</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D228" t="n">
-        <v>192.78</v>
+        <v>21.61</v>
       </c>
       <c r="E228" t="n">
-        <v>66</v>
+        <v>150.99</v>
       </c>
       <c r="F228" t="n">
-        <v>0.13376</v>
+        <v>0.62903</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5908,22 +5908,22 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>107.27</v>
+        <v>273.5</v>
       </c>
       <c r="D229" t="n">
-        <v>136.26</v>
+        <v>344.98</v>
       </c>
       <c r="E229" t="n">
-        <v>27.02</v>
+        <v>26.14</v>
       </c>
       <c r="F229" t="n">
-        <v>0.75992</v>
+        <v>0.07092</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>246.63</v>
+        <v>59.66</v>
       </c>
       <c r="D230" t="n">
-        <v>331.18</v>
+        <v>82.63</v>
       </c>
       <c r="E230" t="n">
-        <v>34.28</v>
+        <v>38.5</v>
       </c>
       <c r="F230" t="n">
-        <v>4.70027</v>
+        <v>1.52417</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>204.77</v>
+        <v>273.14</v>
       </c>
       <c r="D231" t="n">
-        <v>273.05</v>
+        <v>341.43</v>
       </c>
       <c r="E231" t="n">
-        <v>33.34</v>
+        <v>25</v>
       </c>
       <c r="F231" t="n">
-        <v>0.99791</v>
+        <v>-0.05953</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5980,16 +5980,16 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>52.5</v>
+        <v>204.77</v>
       </c>
       <c r="D232" t="n">
-        <v>90</v>
+        <v>273.05</v>
       </c>
       <c r="E232" t="n">
-        <v>71.43000000000001</v>
+        <v>33.34</v>
       </c>
       <c r="F232" t="n">
-        <v>5.23697</v>
+        <v>0.99791</v>
       </c>
     </row>
     <row r="233">
@@ -6019,7 +6019,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6028,16 +6028,16 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>16.32</v>
+        <v>26.41</v>
       </c>
       <c r="D234" t="n">
-        <v>23.68</v>
+        <v>39.5</v>
       </c>
       <c r="E234" t="n">
-        <v>45.13</v>
+        <v>49.56</v>
       </c>
       <c r="F234" t="n">
-        <v>0.26452</v>
+        <v>1.30846</v>
       </c>
     </row>
     <row r="235">
@@ -6055,13 +6055,13 @@
         <v>31.8</v>
       </c>
       <c r="D235" t="n">
-        <v>67.65000000000001</v>
+        <v>67.66</v>
       </c>
       <c r="E235" t="n">
-        <v>112.74</v>
+        <v>112.77</v>
       </c>
       <c r="F235" t="n">
-        <v>0.62737</v>
+        <v>0.62832</v>
       </c>
     </row>
     <row r="236">
@@ -6091,55 +6091,55 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>12.96</v>
+        <v>525.72</v>
       </c>
       <c r="D237" t="n">
-        <v>16.65</v>
+        <v>670.24</v>
       </c>
       <c r="E237" t="n">
-        <v>28.47</v>
+        <v>27.49</v>
       </c>
       <c r="F237" t="n">
-        <v>-0.03231</v>
+        <v>21.58203</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3.88</v>
+        <v>92.39</v>
       </c>
       <c r="D238" t="n">
-        <v>6.44</v>
+        <v>242.49</v>
       </c>
       <c r="E238" t="n">
-        <v>65.98</v>
+        <v>162.45</v>
       </c>
       <c r="F238" t="n">
-        <v>0.07534</v>
+        <v>5.44723</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>3.42</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D239" t="n">
-        <v>5.05</v>
+        <v>118.37</v>
       </c>
       <c r="E239" t="n">
-        <v>47.51</v>
+        <v>36.04</v>
       </c>
       <c r="F239" t="n">
-        <v>0.089</v>
+        <v>1.18624</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>125.78</v>
+        <v>39.84</v>
       </c>
       <c r="D240" t="n">
-        <v>143.85</v>
+        <v>58.28</v>
       </c>
       <c r="E240" t="n">
-        <v>14.37</v>
+        <v>46.29</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.03793</v>
+        <v>0.05681</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>14</v>
+        <v>22.3</v>
       </c>
       <c r="D241" t="n">
-        <v>14.8</v>
+        <v>35.02</v>
       </c>
       <c r="E241" t="n">
-        <v>5.71</v>
+        <v>57.04</v>
       </c>
       <c r="F241" t="n">
-        <v>0.00993</v>
+        <v>0.52819</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,22 +6220,22 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>14.27</v>
+        <v>317.93</v>
       </c>
       <c r="D242" t="n">
-        <v>18.63</v>
+        <v>379.55</v>
       </c>
       <c r="E242" t="n">
-        <v>30.55</v>
+        <v>19.38</v>
       </c>
       <c r="F242" t="n">
-        <v>-0.01186</v>
+        <v>0.46956</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6244,22 +6244,22 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>91.37</v>
+        <v>35.34</v>
       </c>
       <c r="D243" t="n">
-        <v>121.46</v>
+        <v>53.97</v>
       </c>
       <c r="E243" t="n">
-        <v>32.93</v>
+        <v>52.72</v>
       </c>
       <c r="F243" t="n">
-        <v>0.12562</v>
+        <v>0.84994</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>39.84</v>
+        <v>7.63</v>
       </c>
       <c r="D244" t="n">
-        <v>58.29</v>
+        <v>11.15</v>
       </c>
       <c r="E244" t="n">
-        <v>46.31</v>
+        <v>46.13</v>
       </c>
       <c r="F244" t="n">
-        <v>0.05776</v>
+        <v>0.16553</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>525.72</v>
+        <v>3.42</v>
       </c>
       <c r="D245" t="n">
-        <v>670.46</v>
+        <v>5.06</v>
       </c>
       <c r="E245" t="n">
-        <v>27.53</v>
+        <v>47.95</v>
       </c>
       <c r="F245" t="n">
-        <v>21.60299</v>
+        <v>0.09043</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,22 +6316,22 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>295.52</v>
+        <v>147.02</v>
       </c>
       <c r="D246" t="n">
-        <v>376.27</v>
+        <v>375.09</v>
       </c>
       <c r="E246" t="n">
-        <v>27.32</v>
+        <v>155.13</v>
       </c>
       <c r="F246" t="n">
-        <v>0.17332</v>
+        <v>1.92246</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>7.63</v>
+        <v>295.52</v>
       </c>
       <c r="D247" t="n">
-        <v>11.15</v>
+        <v>375.62</v>
       </c>
       <c r="E247" t="n">
-        <v>46.07</v>
+        <v>27.1</v>
       </c>
       <c r="F247" t="n">
-        <v>0.16505</v>
+        <v>0.11189</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>92.39</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D248" t="n">
-        <v>242.51</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="E248" t="n">
-        <v>162.47</v>
+        <v>17.6</v>
       </c>
       <c r="F248" t="n">
-        <v>5.44914</v>
+        <v>-0.25539</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>147.02</v>
+        <v>91.37</v>
       </c>
       <c r="D249" t="n">
-        <v>375.09</v>
+        <v>121.47</v>
       </c>
       <c r="E249" t="n">
-        <v>155.13</v>
+        <v>32.94</v>
       </c>
       <c r="F249" t="n">
-        <v>1.92246</v>
+        <v>0.12704</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>92.42</v>
+        <v>7.58</v>
       </c>
       <c r="D250" t="n">
-        <v>106.4</v>
+        <v>10.61</v>
       </c>
       <c r="E250" t="n">
-        <v>15.13</v>
+        <v>39.97</v>
       </c>
       <c r="F250" t="n">
-        <v>0.38173</v>
+        <v>0.17809</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>285.27</v>
+        <v>92.42</v>
       </c>
       <c r="D251" t="n">
-        <v>378.05</v>
+        <v>106.42</v>
       </c>
       <c r="E251" t="n">
-        <v>32.52</v>
+        <v>15.15</v>
       </c>
       <c r="F251" t="n">
-        <v>2.24356</v>
+        <v>0.38316</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>67.56999999999999</v>
+        <v>23.77</v>
       </c>
       <c r="D252" t="n">
-        <v>79.43000000000001</v>
+        <v>29.05</v>
       </c>
       <c r="E252" t="n">
-        <v>17.55</v>
+        <v>22.21</v>
       </c>
       <c r="F252" t="n">
-        <v>-0.25825</v>
+        <v>0.28593</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>22.3</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D253" t="n">
-        <v>35.03</v>
+        <v>156.62</v>
       </c>
       <c r="E253" t="n">
-        <v>57.09</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="F253" t="n">
-        <v>0.5291400000000001</v>
+        <v>0.27415</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>33.63</v>
+        <v>24.24</v>
       </c>
       <c r="D254" t="n">
-        <v>43.87</v>
+        <v>30.43</v>
       </c>
       <c r="E254" t="n">
-        <v>30.45</v>
+        <v>25.56</v>
       </c>
       <c r="F254" t="n">
-        <v>0.08643000000000001</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3.93</v>
+        <v>243.35</v>
       </c>
       <c r="D255" t="n">
-        <v>5.84</v>
+        <v>365</v>
       </c>
       <c r="E255" t="n">
-        <v>48.6</v>
+        <v>49.99</v>
       </c>
       <c r="F255" t="n">
-        <v>0.11677</v>
+        <v>3.17586</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>24.24</v>
+        <v>121.84</v>
       </c>
       <c r="D256" t="n">
-        <v>30.43</v>
+        <v>159.63</v>
       </c>
       <c r="E256" t="n">
-        <v>25.56</v>
+        <v>31.02</v>
       </c>
       <c r="F256" t="n">
-        <v>0.0053</v>
+        <v>1.3023</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>87.15000000000001</v>
+        <v>14</v>
       </c>
       <c r="D257" t="n">
-        <v>156.62</v>
+        <v>14.8</v>
       </c>
       <c r="E257" t="n">
-        <v>79.70999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="F257" t="n">
-        <v>0.27415</v>
+        <v>0.00993</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>23.77</v>
+        <v>163.37</v>
       </c>
       <c r="D258" t="n">
-        <v>29.05</v>
+        <v>258.82</v>
       </c>
       <c r="E258" t="n">
-        <v>22.21</v>
+        <v>58.43</v>
       </c>
       <c r="F258" t="n">
-        <v>0.28593</v>
+        <v>0.25232</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>243.35</v>
+        <v>3.93</v>
       </c>
       <c r="D259" t="n">
-        <v>364.87</v>
+        <v>5.83</v>
       </c>
       <c r="E259" t="n">
-        <v>49.94</v>
+        <v>48.35</v>
       </c>
       <c r="F259" t="n">
-        <v>3.16348</v>
+        <v>0.11582</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>87.01000000000001</v>
+        <v>157.12</v>
       </c>
       <c r="D260" t="n">
-        <v>118.37</v>
+        <v>262.48</v>
       </c>
       <c r="E260" t="n">
-        <v>36.04</v>
+        <v>67.06</v>
       </c>
       <c r="F260" t="n">
-        <v>1.18624</v>
+        <v>2.10792</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>35.34</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D261" t="n">
-        <v>53.98</v>
+        <v>95.88</v>
       </c>
       <c r="E261" t="n">
-        <v>52.74</v>
+        <v>31.52</v>
       </c>
       <c r="F261" t="n">
-        <v>0.85089</v>
+        <v>0.94208</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>317.93</v>
+        <v>182.65</v>
       </c>
       <c r="D262" t="n">
-        <v>379.72</v>
+        <v>350.78</v>
       </c>
       <c r="E262" t="n">
-        <v>19.44</v>
+        <v>92.05</v>
       </c>
       <c r="F262" t="n">
-        <v>0.48575</v>
+        <v>5.93408</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>284.93</v>
+        <v>61.37</v>
       </c>
       <c r="D263" t="n">
-        <v>407.79</v>
+        <v>80.53</v>
       </c>
       <c r="E263" t="n">
-        <v>43.12</v>
+        <v>31.22</v>
       </c>
       <c r="F263" t="n">
-        <v>0.77102</v>
+        <v>0.10797</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>289.16</v>
+        <v>153.68</v>
       </c>
       <c r="D264" t="n">
-        <v>417.06</v>
+        <v>171.67</v>
       </c>
       <c r="E264" t="n">
-        <v>44.23</v>
+        <v>11.71</v>
       </c>
       <c r="F264" t="n">
-        <v>0.82157</v>
+        <v>-0.33974</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>117.67</v>
+        <v>213.28</v>
       </c>
       <c r="D265" t="n">
-        <v>222.29</v>
+        <v>286.11</v>
       </c>
       <c r="E265" t="n">
-        <v>88.91</v>
+        <v>34.15</v>
       </c>
       <c r="F265" t="n">
-        <v>0.07779</v>
+        <v>0.03034</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>153.68</v>
+        <v>41.53</v>
       </c>
       <c r="D266" t="n">
-        <v>171.67</v>
+        <v>56.9</v>
       </c>
       <c r="E266" t="n">
-        <v>11.71</v>
+        <v>37.01</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.33974</v>
+        <v>0.18075</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>106.41</v>
+        <v>110.24</v>
       </c>
       <c r="D267" t="n">
-        <v>117.56</v>
+        <v>150.27</v>
       </c>
       <c r="E267" t="n">
-        <v>10.48</v>
+        <v>36.31</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.5614</v>
+        <v>-0.85395</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>72.90000000000001</v>
+        <v>284.93</v>
       </c>
       <c r="D268" t="n">
-        <v>95.89</v>
+        <v>407.75</v>
       </c>
       <c r="E268" t="n">
-        <v>31.54</v>
+        <v>43.11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.94303</v>
+        <v>0.7672099999999999</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>7.58</v>
+        <v>20.72</v>
       </c>
       <c r="D269" t="n">
-        <v>10.62</v>
+        <v>24.64</v>
       </c>
       <c r="E269" t="n">
-        <v>40.11</v>
+        <v>18.92</v>
       </c>
       <c r="F269" t="n">
-        <v>0.17904</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6892,22 +6892,22 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>20.72</v>
+        <v>87.98</v>
       </c>
       <c r="D270" t="n">
-        <v>24.64</v>
+        <v>108.03</v>
       </c>
       <c r="E270" t="n">
-        <v>18.92</v>
+        <v>22.79</v>
       </c>
       <c r="F270" t="n">
-        <v>0.0299</v>
+        <v>0.75809</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6916,22 +6916,22 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>41.53</v>
+        <v>52.49</v>
       </c>
       <c r="D271" t="n">
-        <v>56.9</v>
+        <v>56.12</v>
       </c>
       <c r="E271" t="n">
-        <v>37.01</v>
+        <v>6.92</v>
       </c>
       <c r="F271" t="n">
-        <v>0.18075</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>67.7</v>
+        <v>117.67</v>
       </c>
       <c r="D272" t="n">
-        <v>98.20999999999999</v>
+        <v>222.29</v>
       </c>
       <c r="E272" t="n">
-        <v>45.07</v>
+        <v>88.91</v>
       </c>
       <c r="F272" t="n">
-        <v>0.47328</v>
+        <v>0.07779</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SPG-PJ</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,22 +6964,22 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>52.49</v>
+        <v>67.7</v>
       </c>
       <c r="D273" t="n">
-        <v>56.44</v>
+        <v>98.22</v>
       </c>
       <c r="E273" t="n">
-        <v>7.53</v>
+        <v>45.08</v>
       </c>
       <c r="F273" t="n">
-        <v>0.04777</v>
+        <v>0.47423</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>87.98</v>
+        <v>289.16</v>
       </c>
       <c r="D274" t="n">
-        <v>108.03</v>
+        <v>417.09</v>
       </c>
       <c r="E274" t="n">
-        <v>22.79</v>
+        <v>44.24</v>
       </c>
       <c r="F274" t="n">
-        <v>0.75809</v>
+        <v>0.82443</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>163.37</v>
+        <v>106.41</v>
       </c>
       <c r="D275" t="n">
-        <v>258.77</v>
+        <v>117.55</v>
       </c>
       <c r="E275" t="n">
-        <v>58.4</v>
+        <v>10.47</v>
       </c>
       <c r="F275" t="n">
-        <v>0.24756</v>
+        <v>-0.56235</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>157.12</v>
+        <v>33.63</v>
       </c>
       <c r="D276" t="n">
-        <v>262.49</v>
+        <v>43.87</v>
       </c>
       <c r="E276" t="n">
-        <v>67.06</v>
+        <v>30.45</v>
       </c>
       <c r="F276" t="n">
-        <v>2.10887</v>
+        <v>0.08643000000000001</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,22 +7060,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>121.84</v>
+        <v>285.27</v>
       </c>
       <c r="D277" t="n">
-        <v>159.66</v>
+        <v>377.97</v>
       </c>
       <c r="E277" t="n">
-        <v>31.04</v>
+        <v>32.5</v>
       </c>
       <c r="F277" t="n">
-        <v>1.30516</v>
+        <v>2.23594</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7084,88 +7084,88 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>213.28</v>
+        <v>125.78</v>
       </c>
       <c r="D278" t="n">
-        <v>286.25</v>
+        <v>143.79</v>
       </c>
       <c r="E278" t="n">
-        <v>34.21</v>
+        <v>14.32</v>
       </c>
       <c r="F278" t="n">
-        <v>0.04368</v>
+        <v>-0.04365</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>110.24</v>
+        <v>17.13</v>
       </c>
       <c r="D279" t="n">
-        <v>150.18</v>
+        <v>43.01</v>
       </c>
       <c r="E279" t="n">
-        <v>36.23</v>
+        <v>151.08</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.86253</v>
+        <v>0.30712</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>61.37</v>
+        <v>27.55</v>
       </c>
       <c r="D280" t="n">
-        <v>80.54000000000001</v>
+        <v>33.78</v>
       </c>
       <c r="E280" t="n">
-        <v>31.24</v>
+        <v>22.61</v>
       </c>
       <c r="F280" t="n">
-        <v>0.10893</v>
+        <v>-0.15662</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>FMX</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>182.65</v>
+        <v>106.96</v>
       </c>
       <c r="D281" t="n">
-        <v>350.78</v>
+        <v>121.6</v>
       </c>
       <c r="E281" t="n">
-        <v>92.05</v>
+        <v>13.69</v>
       </c>
       <c r="F281" t="n">
-        <v>5.93408</v>
+        <v>-0.38552</v>
       </c>
     </row>
     <row r="282">
@@ -7183,133 +7183,61 @@
         <v>95.48</v>
       </c>
       <c r="D282" t="n">
-        <v>111.53</v>
+        <v>111.5</v>
       </c>
       <c r="E282" t="n">
-        <v>16.81</v>
+        <v>16.78</v>
       </c>
       <c r="F282" t="n">
-        <v>0.04846</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>17.13</v>
+        <v>63.78</v>
       </c>
       <c r="D283" t="n">
-        <v>43.06</v>
+        <v>69.81</v>
       </c>
       <c r="E283" t="n">
-        <v>151.37</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F283" t="n">
-        <v>0.31188</v>
+        <v>0.43847</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>27.55</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D284" t="n">
-        <v>33.78</v>
+        <v>172.45</v>
       </c>
       <c r="E284" t="n">
-        <v>22.61</v>
+        <v>72.47</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.15662</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>FMX</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
-        <v>106.96</v>
-      </c>
-      <c r="D285" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="E285" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="F285" t="n">
-        <v>-0.38552</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>ICLR</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="D286" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="E286" t="n">
-        <v>72.47</v>
-      </c>
-      <c r="F286" t="n">
         <v>1.41425</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="D287" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="E287" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="F287" t="n">
-        <v>0.43466</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F284"/>
+  <dimension ref="A1:F326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,25 +451,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.54000000000001</v>
+        <v>2876.75</v>
       </c>
       <c r="D2" t="n">
-        <v>86.11</v>
+        <v>2965.52</v>
       </c>
       <c r="E2" t="n">
-        <v>6.92</v>
+        <v>3.09</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.96334</v>
+        <v>-26.725</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>56.52</v>
+        <v>57.29</v>
       </c>
       <c r="E3" t="n">
-        <v>4.03</v>
+        <v>5.45</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09851</v>
+        <v>-0.33941</v>
       </c>
     </row>
     <row r="4">
@@ -511,115 +511,115 @@
         <v>38.22</v>
       </c>
       <c r="D4" t="n">
-        <v>42.77</v>
+        <v>41.6</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9</v>
+        <v>8.84</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1714</v>
+        <v>0.17365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>700.51</v>
+        <v>17.87</v>
       </c>
       <c r="D5" t="n">
-        <v>731.75</v>
+        <v>21.62</v>
       </c>
       <c r="E5" t="n">
-        <v>4.46</v>
+        <v>20.98</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9792</v>
+        <v>0.65938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.87</v>
+        <v>102.63</v>
       </c>
       <c r="D6" t="n">
-        <v>21.44</v>
+        <v>109.08</v>
       </c>
       <c r="E6" t="n">
-        <v>19.98</v>
+        <v>6.28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7442</v>
+        <v>-0.22351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>102.63</v>
+        <v>13.03</v>
       </c>
       <c r="D7" t="n">
-        <v>108.09</v>
+        <v>14.97</v>
       </c>
       <c r="E7" t="n">
-        <v>5.32</v>
+        <v>14.89</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01302</v>
+        <v>-0.01791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.03</v>
+        <v>5.67</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>7.03</v>
       </c>
       <c r="E8" t="n">
-        <v>15.12</v>
+        <v>23.99</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09046</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -628,70 +628,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.67</v>
+        <v>298.59</v>
       </c>
       <c r="D9" t="n">
-        <v>6.83</v>
+        <v>334.24</v>
       </c>
       <c r="E9" t="n">
-        <v>20.46</v>
+        <v>11.94</v>
       </c>
       <c r="F9" t="n">
-        <v>0.15101</v>
+        <v>-1.56324</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>298.59</v>
+        <v>141.63</v>
       </c>
       <c r="D10" t="n">
-        <v>331.46</v>
+        <v>157.31</v>
       </c>
       <c r="E10" t="n">
-        <v>11.01</v>
+        <v>11.07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.09993</v>
+        <v>1.11386</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>141.63</v>
+        <v>4.46</v>
       </c>
       <c r="D11" t="n">
-        <v>157.63</v>
+        <v>5.22</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3</v>
+        <v>17.04</v>
       </c>
       <c r="F11" t="n">
-        <v>1.69159</v>
+        <v>0.08513999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12.43</v>
+        <v>2.98</v>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>3.54</v>
       </c>
       <c r="E12" t="n">
-        <v>39.98</v>
+        <v>18.79</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8716699999999999</v>
+        <v>0.06816999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.23</v>
+        <v>12.43</v>
       </c>
       <c r="D13" t="n">
-        <v>11.89</v>
+        <v>18.42</v>
       </c>
       <c r="E13" t="n">
-        <v>5.88</v>
+        <v>48.19</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03859</v>
+        <v>0.97816</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.98</v>
+        <v>7.17</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5</v>
+        <v>8.23</v>
       </c>
       <c r="E14" t="n">
-        <v>17.45</v>
+        <v>14.78</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06834</v>
+        <v>0.13527</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -772,46 +772,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.17</v>
+        <v>11.23</v>
       </c>
       <c r="D15" t="n">
-        <v>8.26</v>
+        <v>11.89</v>
       </c>
       <c r="E15" t="n">
-        <v>15.2</v>
+        <v>5.88</v>
       </c>
       <c r="F15" t="n">
-        <v>0.13953</v>
+        <v>0.03212</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.46</v>
+        <v>17.28</v>
       </c>
       <c r="D16" t="n">
-        <v>5.24</v>
+        <v>19.12</v>
       </c>
       <c r="E16" t="n">
-        <v>17.49</v>
+        <v>10.65</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08273999999999999</v>
+        <v>0.22309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,190 +820,190 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.28</v>
+        <v>98.45</v>
       </c>
       <c r="D17" t="n">
-        <v>19.03</v>
+        <v>122.3</v>
       </c>
       <c r="E17" t="n">
-        <v>10.13</v>
+        <v>24.23</v>
       </c>
       <c r="F17" t="n">
-        <v>0.20851</v>
+        <v>2.28707</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>98.45</v>
+        <v>35.54</v>
       </c>
       <c r="D18" t="n">
-        <v>123.79</v>
+        <v>51.29</v>
       </c>
       <c r="E18" t="n">
-        <v>25.74</v>
+        <v>44.32</v>
       </c>
       <c r="F18" t="n">
-        <v>1.77497</v>
+        <v>1.98244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ABEV</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.78</v>
+        <v>123.39</v>
       </c>
       <c r="D19" t="n">
-        <v>3.02</v>
+        <v>137.82</v>
       </c>
       <c r="E19" t="n">
-        <v>8.630000000000001</v>
+        <v>11.69</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02557</v>
+        <v>1.38289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>52.62</v>
+        <v>63.54</v>
       </c>
       <c r="D20" t="n">
-        <v>56.64</v>
+        <v>70.34</v>
       </c>
       <c r="E20" t="n">
-        <v>7.64</v>
+        <v>10.7</v>
       </c>
       <c r="F20" t="n">
-        <v>0.35581</v>
+        <v>0.02608</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.54</v>
+        <v>155.62</v>
       </c>
       <c r="D21" t="n">
-        <v>50.24</v>
+        <v>163.78</v>
       </c>
       <c r="E21" t="n">
-        <v>41.36</v>
+        <v>5.24</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3384</v>
+        <v>-1.00319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>123.39</v>
+        <v>60.35</v>
       </c>
       <c r="D22" t="n">
-        <v>133.73</v>
+        <v>97.42</v>
       </c>
       <c r="E22" t="n">
-        <v>8.380000000000001</v>
+        <v>61.43</v>
       </c>
       <c r="F22" t="n">
-        <v>1.10452</v>
+        <v>1.96052</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>FIGR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.54</v>
+        <v>24.91</v>
       </c>
       <c r="D23" t="n">
-        <v>71.70999999999999</v>
+        <v>35.65</v>
       </c>
       <c r="E23" t="n">
-        <v>12.86</v>
+        <v>43.12</v>
       </c>
       <c r="F23" t="n">
-        <v>0.51027</v>
+        <v>0.36343</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>340.65</v>
+        <v>7.81</v>
       </c>
       <c r="D24" t="n">
-        <v>371.63</v>
+        <v>10.87</v>
       </c>
       <c r="E24" t="n">
-        <v>9.09</v>
+        <v>39.18</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.20992</v>
+        <v>0.04366</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1012,22 +1012,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.81</v>
+        <v>205.48</v>
       </c>
       <c r="D25" t="n">
-        <v>11.01</v>
+        <v>249.99</v>
       </c>
       <c r="E25" t="n">
-        <v>40.97</v>
+        <v>21.66</v>
       </c>
       <c r="F25" t="n">
-        <v>0.11474</v>
+        <v>1.24005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41.55</v>
+        <v>29.31</v>
       </c>
       <c r="D26" t="n">
-        <v>68.84999999999999</v>
+        <v>43.17</v>
       </c>
       <c r="E26" t="n">
-        <v>65.7</v>
+        <v>47.29</v>
       </c>
       <c r="F26" t="n">
-        <v>0.36109</v>
+        <v>0.92178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,94 +1060,94 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>48.68</v>
+        <v>298.32</v>
       </c>
       <c r="D27" t="n">
-        <v>61.1</v>
+        <v>358.97</v>
       </c>
       <c r="E27" t="n">
-        <v>25.51</v>
+        <v>20.33</v>
       </c>
       <c r="F27" t="n">
-        <v>0.47155</v>
+        <v>3.38165</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11.03</v>
+        <v>41.55</v>
       </c>
       <c r="D28" t="n">
-        <v>12.84</v>
+        <v>62.21</v>
       </c>
       <c r="E28" t="n">
-        <v>16.41</v>
+        <v>49.72</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01194</v>
+        <v>-0.39774</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>332.02</v>
+        <v>25.28</v>
       </c>
       <c r="D29" t="n">
-        <v>377.16</v>
+        <v>28.1</v>
       </c>
       <c r="E29" t="n">
-        <v>13.6</v>
+        <v>11.16</v>
       </c>
       <c r="F29" t="n">
-        <v>0.27114</v>
+        <v>-0.01151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.14</v>
+        <v>11.03</v>
       </c>
       <c r="D30" t="n">
-        <v>31.56</v>
+        <v>12.72</v>
       </c>
       <c r="E30" t="n">
-        <v>16.29</v>
+        <v>15.32</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.13487</v>
+        <v>-0.09100999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>146.38</v>
+        <v>179.43</v>
       </c>
       <c r="D31" t="n">
-        <v>215.67</v>
+        <v>193.72</v>
       </c>
       <c r="E31" t="n">
-        <v>47.34</v>
+        <v>7.96</v>
       </c>
       <c r="F31" t="n">
-        <v>0.62778</v>
+        <v>0.57955</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1180,310 +1180,310 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>179.43</v>
+        <v>332.02</v>
       </c>
       <c r="D32" t="n">
-        <v>190.13</v>
+        <v>377.94</v>
       </c>
       <c r="E32" t="n">
-        <v>5.96</v>
+        <v>13.83</v>
       </c>
       <c r="F32" t="n">
-        <v>0.43388</v>
+        <v>-2.21821</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.99</v>
+        <v>27.14</v>
       </c>
       <c r="D33" t="n">
-        <v>37.63</v>
+        <v>31.52</v>
       </c>
       <c r="E33" t="n">
-        <v>44.79</v>
+        <v>16.14</v>
       </c>
       <c r="F33" t="n">
-        <v>0.74041</v>
+        <v>-0.35749</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>205.77</v>
+        <v>146.38</v>
       </c>
       <c r="D34" t="n">
-        <v>248.37</v>
+        <v>218.28</v>
       </c>
       <c r="E34" t="n">
-        <v>20.7</v>
+        <v>49.12</v>
       </c>
       <c r="F34" t="n">
-        <v>3.26641</v>
+        <v>0.00649</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>440.76</v>
+        <v>205.77</v>
       </c>
       <c r="D35" t="n">
-        <v>636.4</v>
+        <v>249.09</v>
       </c>
       <c r="E35" t="n">
-        <v>44.39</v>
+        <v>21.05</v>
       </c>
       <c r="F35" t="n">
-        <v>4.10788</v>
+        <v>2.72288</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>89.2</v>
+        <v>25.99</v>
       </c>
       <c r="D36" t="n">
-        <v>124.19</v>
+        <v>38.71</v>
       </c>
       <c r="E36" t="n">
-        <v>39.23</v>
+        <v>48.94</v>
       </c>
       <c r="F36" t="n">
-        <v>0.38279</v>
+        <v>0.54466</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>103.45</v>
+        <v>440.76</v>
       </c>
       <c r="D37" t="n">
-        <v>150.02</v>
+        <v>637.16</v>
       </c>
       <c r="E37" t="n">
-        <v>45.02</v>
+        <v>44.56</v>
       </c>
       <c r="F37" t="n">
-        <v>1.07197</v>
+        <v>1.42976</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>198.14</v>
+        <v>103.45</v>
       </c>
       <c r="D38" t="n">
-        <v>263.09</v>
+        <v>149.67</v>
       </c>
       <c r="E38" t="n">
-        <v>32.78</v>
+        <v>44.68</v>
       </c>
       <c r="F38" t="n">
-        <v>2.17265</v>
+        <v>1.89428</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RRC</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35.49</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>41.9</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>18.06</v>
+        <v>18.82</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.45827</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>41.44</v>
+        <v>198.14</v>
       </c>
       <c r="D40" t="n">
-        <v>45.37</v>
+        <v>261.67</v>
       </c>
       <c r="E40" t="n">
-        <v>9.48</v>
+        <v>32.06</v>
       </c>
       <c r="F40" t="n">
-        <v>0.55671</v>
+        <v>2.64766</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>510.39</v>
+        <v>41.44</v>
       </c>
       <c r="D41" t="n">
-        <v>643.33</v>
+        <v>45.25</v>
       </c>
       <c r="E41" t="n">
-        <v>26.05</v>
+        <v>9.19</v>
       </c>
       <c r="F41" t="n">
-        <v>5.93092</v>
+        <v>0.51531</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5.04</v>
+        <v>510.39</v>
       </c>
       <c r="D42" t="n">
-        <v>5.86</v>
+        <v>652.39</v>
       </c>
       <c r="E42" t="n">
-        <v>16.27</v>
+        <v>27.82</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04462</v>
+        <v>4.4847</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PSNYW</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.2</v>
+        <v>5.04</v>
       </c>
       <c r="D43" t="n">
-        <v>4.68</v>
+        <v>5.95</v>
       </c>
       <c r="E43" t="n">
-        <v>112.73</v>
+        <v>18.06</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.01815</v>
+        <v>0.05247</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>162.11</v>
+        <v>176.25</v>
       </c>
       <c r="D44" t="n">
-        <v>177.71</v>
+        <v>249.59</v>
       </c>
       <c r="E44" t="n">
-        <v>9.619999999999999</v>
+        <v>41.61</v>
       </c>
       <c r="F44" t="n">
-        <v>0.54084</v>
+        <v>0.95658</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>24.36</v>
+        <v>162.11</v>
       </c>
       <c r="D45" t="n">
-        <v>33.92</v>
+        <v>176.94</v>
       </c>
       <c r="E45" t="n">
-        <v>39.24</v>
+        <v>9.15</v>
       </c>
       <c r="F45" t="n">
-        <v>0.50814</v>
+        <v>0.35777</v>
       </c>
     </row>
     <row r="46">
@@ -1519,91 +1519,91 @@
         <v>40.48</v>
       </c>
       <c r="D46" t="n">
-        <v>45.96</v>
+        <v>44.64</v>
       </c>
       <c r="E46" t="n">
-        <v>13.54</v>
+        <v>10.28</v>
       </c>
       <c r="F46" t="n">
-        <v>0.24459</v>
+        <v>0.1977</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>165.69</v>
+        <v>20.87</v>
       </c>
       <c r="D47" t="n">
-        <v>217.77</v>
+        <v>23.47</v>
       </c>
       <c r="E47" t="n">
-        <v>31.43</v>
+        <v>12.46</v>
       </c>
       <c r="F47" t="n">
-        <v>3.21866</v>
+        <v>0.00191</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.99</v>
+        <v>24.36</v>
       </c>
       <c r="D48" t="n">
-        <v>21.77</v>
+        <v>33.27</v>
       </c>
       <c r="E48" t="n">
-        <v>36.15</v>
+        <v>36.58</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6551900000000001</v>
+        <v>0.5132100000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>51.98</v>
+        <v>31.45</v>
       </c>
       <c r="D49" t="n">
-        <v>66.97</v>
+        <v>36.65</v>
       </c>
       <c r="E49" t="n">
-        <v>28.84</v>
+        <v>16.53</v>
       </c>
       <c r="F49" t="n">
-        <v>0.22746</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.49</v>
+        <v>110.99</v>
       </c>
       <c r="D50" t="n">
-        <v>19.57</v>
+        <v>131.83</v>
       </c>
       <c r="E50" t="n">
-        <v>35.06</v>
+        <v>18.78</v>
       </c>
       <c r="F50" t="n">
-        <v>0.58352</v>
+        <v>-0.18184</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38.92</v>
+        <v>53.57</v>
       </c>
       <c r="D51" t="n">
-        <v>51.55</v>
+        <v>68.72</v>
       </c>
       <c r="E51" t="n">
-        <v>32.45</v>
+        <v>28.28</v>
       </c>
       <c r="F51" t="n">
-        <v>0.30504</v>
+        <v>0.74953</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>47.94</v>
+        <v>31.87</v>
       </c>
       <c r="D52" t="n">
-        <v>63.52</v>
+        <v>45.03</v>
       </c>
       <c r="E52" t="n">
-        <v>32.5</v>
+        <v>41.29</v>
       </c>
       <c r="F52" t="n">
-        <v>0.82646</v>
+        <v>0.89874</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,22 +1684,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53.57</v>
+        <v>17.93</v>
       </c>
       <c r="D53" t="n">
-        <v>71.87</v>
+        <v>23.76</v>
       </c>
       <c r="E53" t="n">
-        <v>34.16</v>
+        <v>32.52</v>
       </c>
       <c r="F53" t="n">
-        <v>0.94957</v>
+        <v>0.28866</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>45.57</v>
+        <v>171.96</v>
       </c>
       <c r="D54" t="n">
-        <v>56.66</v>
+        <v>205.72</v>
       </c>
       <c r="E54" t="n">
-        <v>24.34</v>
+        <v>19.63</v>
       </c>
       <c r="F54" t="n">
-        <v>0.49648</v>
+        <v>1.19691</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>171.96</v>
+        <v>47.94</v>
       </c>
       <c r="D55" t="n">
-        <v>211.52</v>
+        <v>61.78</v>
       </c>
       <c r="E55" t="n">
-        <v>23.01</v>
+        <v>28.87</v>
       </c>
       <c r="F55" t="n">
-        <v>1.93006</v>
+        <v>0.67977</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.93</v>
+        <v>38.92</v>
       </c>
       <c r="D56" t="n">
-        <v>24.49</v>
+        <v>50.32</v>
       </c>
       <c r="E56" t="n">
-        <v>36.59</v>
+        <v>29.29</v>
       </c>
       <c r="F56" t="n">
-        <v>0.34403</v>
+        <v>0.31609</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>36.15</v>
+        <v>13.01</v>
       </c>
       <c r="D57" t="n">
-        <v>46.96</v>
+        <v>17.53</v>
       </c>
       <c r="E57" t="n">
-        <v>29.9</v>
+        <v>34.74</v>
       </c>
       <c r="F57" t="n">
-        <v>0.88425</v>
+        <v>0.37919</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>110.99</v>
+        <v>104.89</v>
       </c>
       <c r="D58" t="n">
-        <v>135.35</v>
+        <v>121.23</v>
       </c>
       <c r="E58" t="n">
-        <v>21.95</v>
+        <v>15.58</v>
       </c>
       <c r="F58" t="n">
-        <v>0.19167</v>
+        <v>2.10701</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>104.89</v>
+        <v>14.49</v>
       </c>
       <c r="D59" t="n">
-        <v>121.76</v>
+        <v>19.07</v>
       </c>
       <c r="E59" t="n">
-        <v>16.08</v>
+        <v>31.61</v>
       </c>
       <c r="F59" t="n">
-        <v>1.74063</v>
+        <v>0.58389</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1852,22 +1852,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.01</v>
+        <v>15.99</v>
       </c>
       <c r="D60" t="n">
-        <v>17.68</v>
+        <v>21.15</v>
       </c>
       <c r="E60" t="n">
-        <v>35.9</v>
+        <v>32.27</v>
       </c>
       <c r="F60" t="n">
-        <v>0.39546</v>
+        <v>0.63574</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>52.58</v>
+        <v>40.25</v>
       </c>
       <c r="D61" t="n">
-        <v>65.43000000000001</v>
+        <v>49.73</v>
       </c>
       <c r="E61" t="n">
-        <v>24.44</v>
+        <v>23.55</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00565</v>
+        <v>0.77667</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>103.22</v>
+        <v>36.15</v>
       </c>
       <c r="D62" t="n">
-        <v>141.22</v>
+        <v>45.93</v>
       </c>
       <c r="E62" t="n">
-        <v>36.81</v>
+        <v>27.05</v>
       </c>
       <c r="F62" t="n">
-        <v>2.28322</v>
+        <v>0.8426</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>31.87</v>
+        <v>45.57</v>
       </c>
       <c r="D63" t="n">
-        <v>47.41</v>
+        <v>55.4</v>
       </c>
       <c r="E63" t="n">
-        <v>48.76</v>
+        <v>21.57</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0579</v>
+        <v>0.48559</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>17.26</v>
+        <v>165.69</v>
       </c>
       <c r="D64" t="n">
-        <v>19.84</v>
+        <v>212.17</v>
       </c>
       <c r="E64" t="n">
-        <v>14.95</v>
+        <v>28.05</v>
       </c>
       <c r="F64" t="n">
-        <v>0.16265</v>
+        <v>3.14062</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,16 +1972,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>40.25</v>
+        <v>103.22</v>
       </c>
       <c r="D65" t="n">
-        <v>51.33</v>
+        <v>136.67</v>
       </c>
       <c r="E65" t="n">
-        <v>27.53</v>
+        <v>32.41</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9265099999999999</v>
+        <v>2.02987</v>
       </c>
     </row>
     <row r="66">
@@ -1999,19 +1999,19 @@
         <v>74.8</v>
       </c>
       <c r="D66" t="n">
-        <v>93.12</v>
+        <v>91.14</v>
       </c>
       <c r="E66" t="n">
-        <v>24.49</v>
+        <v>21.84</v>
       </c>
       <c r="F66" t="n">
-        <v>1.07146</v>
+        <v>1.02845</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,16 +2020,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>41.99</v>
+        <v>51.98</v>
       </c>
       <c r="D67" t="n">
-        <v>51.45</v>
+        <v>65.36</v>
       </c>
       <c r="E67" t="n">
-        <v>22.53</v>
+        <v>25.74</v>
       </c>
       <c r="F67" t="n">
-        <v>0.50723</v>
+        <v>-0.02228</v>
       </c>
     </row>
     <row r="68">
@@ -2047,67 +2047,67 @@
         <v>20.48</v>
       </c>
       <c r="D68" t="n">
-        <v>26.72</v>
+        <v>26.51</v>
       </c>
       <c r="E68" t="n">
-        <v>30.47</v>
+        <v>29.44</v>
       </c>
       <c r="F68" t="n">
-        <v>0.32346</v>
+        <v>0.19225</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>38.73</v>
+        <v>41.99</v>
       </c>
       <c r="D69" t="n">
-        <v>63.28</v>
+        <v>51.29</v>
       </c>
       <c r="E69" t="n">
-        <v>63.39</v>
+        <v>22.15</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3855</v>
+        <v>0.38063</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>62.05</v>
+        <v>17.26</v>
       </c>
       <c r="D70" t="n">
-        <v>81.29000000000001</v>
+        <v>19.97</v>
       </c>
       <c r="E70" t="n">
-        <v>31.01</v>
+        <v>15.7</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.26747</v>
+        <v>0.16925</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2116,22 +2116,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>124.44</v>
+        <v>13.31</v>
       </c>
       <c r="D71" t="n">
-        <v>193.4</v>
+        <v>25.76</v>
       </c>
       <c r="E71" t="n">
-        <v>55.42</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>2.33628</v>
+        <v>0.71191</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>55.53</v>
+        <v>124.44</v>
       </c>
       <c r="D72" t="n">
-        <v>62.25</v>
+        <v>195</v>
       </c>
       <c r="E72" t="n">
-        <v>12.1</v>
+        <v>56.7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.75354</v>
+        <v>0.72958</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,22 +2164,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13.31</v>
+        <v>167.73</v>
       </c>
       <c r="D73" t="n">
-        <v>23.6</v>
+        <v>182.9</v>
       </c>
       <c r="E73" t="n">
-        <v>77.31</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>0.58601</v>
+        <v>-0.58001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2188,352 +2188,352 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13.43</v>
+        <v>62.05</v>
       </c>
       <c r="D74" t="n">
-        <v>15.03</v>
+        <v>81.22</v>
       </c>
       <c r="E74" t="n">
-        <v>11.91</v>
+        <v>30.89</v>
       </c>
       <c r="F74" t="n">
-        <v>0.08283</v>
+        <v>-0.5008899999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>136.06</v>
+        <v>38.73</v>
       </c>
       <c r="D75" t="n">
-        <v>169.32</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>24.45</v>
+        <v>65.5</v>
       </c>
       <c r="F75" t="n">
-        <v>1.98435</v>
+        <v>-0.10866</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7.67</v>
+        <v>13.43</v>
       </c>
       <c r="D76" t="n">
-        <v>9.23</v>
+        <v>15.26</v>
       </c>
       <c r="E76" t="n">
-        <v>20.34</v>
+        <v>13.63</v>
       </c>
       <c r="F76" t="n">
-        <v>0.15642</v>
+        <v>0.08839</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>31.03</v>
+        <v>55.53</v>
       </c>
       <c r="D77" t="n">
-        <v>45.75</v>
+        <v>60.91</v>
       </c>
       <c r="E77" t="n">
-        <v>47.44</v>
+        <v>9.69</v>
       </c>
       <c r="F77" t="n">
-        <v>0.94193</v>
+        <v>0.22128</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>56.4</v>
+        <v>7.67</v>
       </c>
       <c r="D78" t="n">
-        <v>79.48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>40.92</v>
+        <v>19.95</v>
       </c>
       <c r="F78" t="n">
-        <v>2.00392</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>76.53</v>
+        <v>122.91</v>
       </c>
       <c r="D79" t="n">
-        <v>98.95</v>
+        <v>157.75</v>
       </c>
       <c r="E79" t="n">
-        <v>29.3</v>
+        <v>28.35</v>
       </c>
       <c r="F79" t="n">
-        <v>1.63317</v>
+        <v>-0.37771</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>82.31</v>
+        <v>135.44</v>
       </c>
       <c r="D80" t="n">
-        <v>129.6</v>
+        <v>174.39</v>
       </c>
       <c r="E80" t="n">
-        <v>57.45</v>
+        <v>28.76</v>
       </c>
       <c r="F80" t="n">
-        <v>2.83088</v>
+        <v>-1.62645</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>18.94</v>
+        <v>218.58</v>
       </c>
       <c r="D81" t="n">
-        <v>23.98</v>
+        <v>280.46</v>
       </c>
       <c r="E81" t="n">
-        <v>26.61</v>
+        <v>28.31</v>
       </c>
       <c r="F81" t="n">
-        <v>0.15742</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>107.27</v>
+        <v>136.06</v>
       </c>
       <c r="D82" t="n">
-        <v>172.56</v>
+        <v>165.08</v>
       </c>
       <c r="E82" t="n">
-        <v>60.87</v>
+        <v>21.33</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.66867</v>
+        <v>1.65744</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>59.71</v>
+        <v>76.53</v>
       </c>
       <c r="D83" t="n">
-        <v>80.06</v>
+        <v>96.45</v>
       </c>
       <c r="E83" t="n">
-        <v>34.08</v>
+        <v>26.03</v>
       </c>
       <c r="F83" t="n">
-        <v>1.2886</v>
+        <v>1.45245</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>42.46</v>
+        <v>18.94</v>
       </c>
       <c r="D84" t="n">
-        <v>71.84999999999999</v>
+        <v>23.74</v>
       </c>
       <c r="E84" t="n">
-        <v>69.22</v>
+        <v>25.34</v>
       </c>
       <c r="F84" t="n">
-        <v>1.88023</v>
+        <v>0.19609</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>352.83</v>
+        <v>31.03</v>
       </c>
       <c r="D85" t="n">
-        <v>497.12</v>
+        <v>44.54</v>
       </c>
       <c r="E85" t="n">
-        <v>40.9</v>
+        <v>43.54</v>
       </c>
       <c r="F85" t="n">
-        <v>2.41856</v>
+        <v>0.9863499999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>44.39</v>
+        <v>39.54</v>
       </c>
       <c r="D86" t="n">
-        <v>60.34</v>
+        <v>51.41</v>
       </c>
       <c r="E86" t="n">
-        <v>35.93</v>
+        <v>30.02</v>
       </c>
       <c r="F86" t="n">
-        <v>0.25495</v>
+        <v>0.11249</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>170.28</v>
+        <v>82.31</v>
       </c>
       <c r="D87" t="n">
-        <v>241.96</v>
+        <v>136.94</v>
       </c>
       <c r="E87" t="n">
-        <v>42.1</v>
+        <v>66.37</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.37415</v>
+        <v>3.45518</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>136.68</v>
+        <v>56.4</v>
       </c>
       <c r="D88" t="n">
-        <v>156.99</v>
+        <v>80.81</v>
       </c>
       <c r="E88" t="n">
-        <v>14.86</v>
+        <v>43.28</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.72946</v>
+        <v>1.6696</v>
       </c>
     </row>
     <row r="89">
@@ -2551,13 +2551,13 @@
         <v>49.87</v>
       </c>
       <c r="D89" t="n">
-        <v>62.3</v>
+        <v>63.17</v>
       </c>
       <c r="E89" t="n">
-        <v>24.92</v>
+        <v>26.67</v>
       </c>
       <c r="F89" t="n">
-        <v>0.41873</v>
+        <v>0.2007</v>
       </c>
     </row>
     <row r="90">
@@ -2575,4363 +2575,4363 @@
         <v>166.5</v>
       </c>
       <c r="D90" t="n">
-        <v>195.47</v>
+        <v>197.56</v>
       </c>
       <c r="E90" t="n">
-        <v>17.4</v>
+        <v>18.65</v>
       </c>
       <c r="F90" t="n">
-        <v>1.03418</v>
+        <v>0.66935</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>60.37</v>
+        <v>44.39</v>
       </c>
       <c r="D91" t="n">
-        <v>78.72</v>
+        <v>61.14</v>
       </c>
       <c r="E91" t="n">
-        <v>30.4</v>
+        <v>37.73</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9964499999999999</v>
+        <v>-0.05927</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10.51</v>
+        <v>136.68</v>
       </c>
       <c r="D92" t="n">
-        <v>15.29</v>
+        <v>153.4</v>
       </c>
       <c r="E92" t="n">
-        <v>45.48</v>
+        <v>12.23</v>
       </c>
       <c r="F92" t="n">
-        <v>0.36599</v>
+        <v>-2.51046</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>62.12</v>
+        <v>255.07</v>
       </c>
       <c r="D93" t="n">
-        <v>79.97</v>
+        <v>339.15</v>
       </c>
       <c r="E93" t="n">
-        <v>28.73</v>
+        <v>32.96</v>
       </c>
       <c r="F93" t="n">
-        <v>0.93677</v>
+        <v>-6.00233</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>48.79</v>
+        <v>170.28</v>
       </c>
       <c r="D94" t="n">
-        <v>67.56999999999999</v>
+        <v>250.61</v>
       </c>
       <c r="E94" t="n">
-        <v>38.49</v>
+        <v>47.18</v>
       </c>
       <c r="F94" t="n">
-        <v>0.33897</v>
+        <v>-2.75775</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>EDU</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>247.22</v>
+        <v>44.44</v>
       </c>
       <c r="D95" t="n">
-        <v>297.26</v>
+        <v>56.82</v>
       </c>
       <c r="E95" t="n">
-        <v>20.24</v>
+        <v>27.86</v>
       </c>
       <c r="F95" t="n">
-        <v>2.46873</v>
+        <v>-0.38143</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>102.17</v>
+        <v>142.52</v>
       </c>
       <c r="D96" t="n">
-        <v>135.54</v>
+        <v>191.45</v>
       </c>
       <c r="E96" t="n">
-        <v>32.66</v>
+        <v>34.33</v>
       </c>
       <c r="F96" t="n">
-        <v>1.43815</v>
+        <v>1.43195</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>76.04000000000001</v>
+        <v>19.32</v>
       </c>
       <c r="D97" t="n">
-        <v>123.51</v>
+        <v>24.47</v>
       </c>
       <c r="E97" t="n">
-        <v>62.43</v>
+        <v>26.66</v>
       </c>
       <c r="F97" t="n">
-        <v>3.02454</v>
+        <v>-0.0342</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>125.73</v>
+        <v>59.71</v>
       </c>
       <c r="D98" t="n">
-        <v>195.62</v>
+        <v>79.11</v>
       </c>
       <c r="E98" t="n">
-        <v>55.59</v>
+        <v>32.49</v>
       </c>
       <c r="F98" t="n">
-        <v>0.83805</v>
+        <v>0.59687</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>150.12</v>
+        <v>352.83</v>
       </c>
       <c r="D99" t="n">
-        <v>255.65</v>
+        <v>505.41</v>
       </c>
       <c r="E99" t="n">
-        <v>70.3</v>
+        <v>43.24</v>
       </c>
       <c r="F99" t="n">
-        <v>6.95816</v>
+        <v>2.09735</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>275.27</v>
+        <v>42.46</v>
       </c>
       <c r="D100" t="n">
-        <v>353.13</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>28.28</v>
+        <v>64.3</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.49134</v>
+        <v>1.2992</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>140.71</v>
+        <v>107.27</v>
       </c>
       <c r="D101" t="n">
-        <v>185.92</v>
+        <v>173.31</v>
       </c>
       <c r="E101" t="n">
-        <v>32.13</v>
+        <v>61.56</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.65188</v>
+        <v>-1.05801</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>74.98999999999999</v>
+        <v>60.37</v>
       </c>
       <c r="D102" t="n">
-        <v>102.38</v>
+        <v>77</v>
       </c>
       <c r="E102" t="n">
-        <v>36.52</v>
+        <v>27.55</v>
       </c>
       <c r="F102" t="n">
-        <v>1.20454</v>
+        <v>1.31187</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>83.81999999999999</v>
+        <v>62.12</v>
       </c>
       <c r="D103" t="n">
-        <v>95.06</v>
+        <v>79.13</v>
       </c>
       <c r="E103" t="n">
-        <v>13.41</v>
+        <v>27.38</v>
       </c>
       <c r="F103" t="n">
-        <v>0.23447</v>
+        <v>0.8058999999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>76.55</v>
+        <v>10.51</v>
       </c>
       <c r="D104" t="n">
-        <v>102.61</v>
+        <v>15.27</v>
       </c>
       <c r="E104" t="n">
-        <v>34.04</v>
+        <v>45.29</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.89647</v>
+        <v>0.40451</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>141.17</v>
+        <v>48.79</v>
       </c>
       <c r="D105" t="n">
-        <v>176.85</v>
+        <v>68.53</v>
       </c>
       <c r="E105" t="n">
-        <v>25.27</v>
+        <v>40.46</v>
       </c>
       <c r="F105" t="n">
-        <v>1.14115</v>
+        <v>-0.01588</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>33.22</v>
+        <v>102.17</v>
       </c>
       <c r="D106" t="n">
-        <v>38.83</v>
+        <v>131.24</v>
       </c>
       <c r="E106" t="n">
-        <v>16.89</v>
+        <v>28.45</v>
       </c>
       <c r="F106" t="n">
-        <v>0.12529</v>
+        <v>1.86006</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>450.75</v>
+        <v>30.83</v>
       </c>
       <c r="D107" t="n">
-        <v>544.3200000000001</v>
+        <v>35.72</v>
       </c>
       <c r="E107" t="n">
-        <v>20.76</v>
+        <v>15.86</v>
       </c>
       <c r="F107" t="n">
-        <v>2.42297</v>
+        <v>-0.35242</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>48.87</v>
+        <v>275.27</v>
       </c>
       <c r="D108" t="n">
-        <v>58.8</v>
+        <v>359.54</v>
       </c>
       <c r="E108" t="n">
-        <v>20.32</v>
+        <v>30.61</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.23533</v>
+        <v>-2.74832</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>32.47</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>38.62</v>
+        <v>123.61</v>
       </c>
       <c r="E109" t="n">
-        <v>18.94</v>
+        <v>62.56</v>
       </c>
       <c r="F109" t="n">
-        <v>0.35367</v>
+        <v>2.41344</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2.86</v>
+        <v>150.12</v>
       </c>
       <c r="D110" t="n">
-        <v>3.16</v>
+        <v>259.43</v>
       </c>
       <c r="E110" t="n">
-        <v>10.49</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>0.02491</v>
+        <v>6.48113</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>16.44</v>
+        <v>140.71</v>
       </c>
       <c r="D111" t="n">
-        <v>33.61</v>
+        <v>182.91</v>
       </c>
       <c r="E111" t="n">
-        <v>104.44</v>
+        <v>29.99</v>
       </c>
       <c r="F111" t="n">
-        <v>0.45364</v>
+        <v>-1.36471</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>14.94</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D112" t="n">
-        <v>19.53</v>
+        <v>95.31</v>
       </c>
       <c r="E112" t="n">
-        <v>30.72</v>
+        <v>13.71</v>
       </c>
       <c r="F112" t="n">
-        <v>0.51817</v>
+        <v>-0.43033</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>121.48</v>
+        <v>76.55</v>
       </c>
       <c r="D113" t="n">
-        <v>146.3</v>
+        <v>105.82</v>
       </c>
       <c r="E113" t="n">
-        <v>20.43</v>
+        <v>38.24</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1059</v>
+        <v>-1.58346</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>53.82</v>
+        <v>123.42</v>
       </c>
       <c r="D114" t="n">
-        <v>74.08</v>
+        <v>164.55</v>
       </c>
       <c r="E114" t="n">
-        <v>37.64</v>
+        <v>33.33</v>
       </c>
       <c r="F114" t="n">
-        <v>0.46228</v>
+        <v>-0.65884</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>19.82</v>
+        <v>125.73</v>
       </c>
       <c r="D115" t="n">
-        <v>25.46</v>
+        <v>197.07</v>
       </c>
       <c r="E115" t="n">
-        <v>28.46</v>
+        <v>56.74</v>
       </c>
       <c r="F115" t="n">
-        <v>0.29096</v>
+        <v>-1.80321</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>361.32</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>423.82</v>
+        <v>104.47</v>
       </c>
       <c r="E116" t="n">
-        <v>17.3</v>
+        <v>39.31</v>
       </c>
       <c r="F116" t="n">
-        <v>4.19429</v>
+        <v>0.40712</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>43.67</v>
+        <v>61.28</v>
       </c>
       <c r="D117" t="n">
-        <v>47.13</v>
+        <v>72.91</v>
       </c>
       <c r="E117" t="n">
-        <v>7.92</v>
+        <v>18.98</v>
       </c>
       <c r="F117" t="n">
-        <v>0.04408</v>
+        <v>-0.98211</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>15.03</v>
+        <v>141.17</v>
       </c>
       <c r="D118" t="n">
-        <v>18.7</v>
+        <v>173.25</v>
       </c>
       <c r="E118" t="n">
-        <v>24.42</v>
+        <v>22.72</v>
       </c>
       <c r="F118" t="n">
-        <v>0.12759</v>
+        <v>1.14864</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>140.19</v>
+        <v>48.87</v>
       </c>
       <c r="D119" t="n">
-        <v>146.67</v>
+        <v>58.74</v>
       </c>
       <c r="E119" t="n">
-        <v>4.62</v>
+        <v>20.2</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02814</v>
+        <v>-0.40747</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>195.11</v>
+        <v>32.47</v>
       </c>
       <c r="D120" t="n">
-        <v>248.36</v>
+        <v>38.43</v>
       </c>
       <c r="E120" t="n">
-        <v>27.29</v>
+        <v>18.36</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6946099999999999</v>
+        <v>0.22774</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>275.99</v>
+        <v>450.75</v>
       </c>
       <c r="D121" t="n">
-        <v>318.2</v>
+        <v>548.65</v>
       </c>
       <c r="E121" t="n">
-        <v>15.29</v>
+        <v>21.72</v>
       </c>
       <c r="F121" t="n">
-        <v>1.98323</v>
+        <v>2.41907</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>ENSG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>23.85</v>
+        <v>147.13</v>
       </c>
       <c r="D122" t="n">
-        <v>34.15</v>
+        <v>174.93</v>
       </c>
       <c r="E122" t="n">
-        <v>43.19</v>
+        <v>18.89</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01267</v>
+        <v>-0.59992</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>277.69</v>
+        <v>91.88</v>
       </c>
       <c r="D123" t="n">
-        <v>328.7</v>
+        <v>125.3</v>
       </c>
       <c r="E123" t="n">
-        <v>18.37</v>
+        <v>36.37</v>
       </c>
       <c r="F123" t="n">
-        <v>0.45735</v>
+        <v>1.50067</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>182.82</v>
+        <v>53.82</v>
       </c>
       <c r="D124" t="n">
-        <v>229.44</v>
+        <v>75</v>
       </c>
       <c r="E124" t="n">
-        <v>25.5</v>
+        <v>39.35</v>
       </c>
       <c r="F124" t="n">
-        <v>-1.30339</v>
+        <v>0.53725</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>73.75</v>
+        <v>62.47</v>
       </c>
       <c r="D125" t="n">
-        <v>93.75</v>
+        <v>90.19</v>
       </c>
       <c r="E125" t="n">
-        <v>27.12</v>
+        <v>44.37</v>
       </c>
       <c r="F125" t="n">
-        <v>0.46174</v>
+        <v>-0.65359</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9.85</v>
+        <v>16.44</v>
       </c>
       <c r="D126" t="n">
-        <v>14</v>
+        <v>33.97</v>
       </c>
       <c r="E126" t="n">
-        <v>42.13</v>
+        <v>106.63</v>
       </c>
       <c r="F126" t="n">
-        <v>0.47309</v>
+        <v>0.60034</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>309.78</v>
+        <v>2.86</v>
       </c>
       <c r="D127" t="n">
-        <v>341.86</v>
+        <v>3.18</v>
       </c>
       <c r="E127" t="n">
-        <v>10.36</v>
+        <v>11.19</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.62071</v>
+        <v>0.02543</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>36.25</v>
+        <v>121.48</v>
       </c>
       <c r="D128" t="n">
-        <v>41.48</v>
+        <v>146.41</v>
       </c>
       <c r="E128" t="n">
-        <v>14.43</v>
+        <v>20.52</v>
       </c>
       <c r="F128" t="n">
-        <v>0.15456</v>
+        <v>0.04863</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>190.4</v>
+        <v>14.94</v>
       </c>
       <c r="D129" t="n">
-        <v>221.31</v>
+        <v>19.59</v>
       </c>
       <c r="E129" t="n">
-        <v>16.23</v>
+        <v>31.16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.59114</v>
+        <v>0.52114</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>63.54</v>
+        <v>19.82</v>
       </c>
       <c r="D130" t="n">
-        <v>71.28</v>
+        <v>25.05</v>
       </c>
       <c r="E130" t="n">
-        <v>12.18</v>
+        <v>26.39</v>
       </c>
       <c r="F130" t="n">
-        <v>0.374</v>
+        <v>0.40053</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>33.54</v>
+        <v>361.32</v>
       </c>
       <c r="D131" t="n">
-        <v>42.18</v>
+        <v>425.49</v>
       </c>
       <c r="E131" t="n">
-        <v>25.76</v>
+        <v>17.76</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1388</v>
+        <v>4.42632</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>529.12</v>
+        <v>205.81</v>
       </c>
       <c r="D132" t="n">
-        <v>684.04</v>
+        <v>264.92</v>
       </c>
       <c r="E132" t="n">
-        <v>29.28</v>
+        <v>28.72</v>
       </c>
       <c r="F132" t="n">
-        <v>9.50407</v>
+        <v>1.32952</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>57.4</v>
+        <v>43.67</v>
       </c>
       <c r="D133" t="n">
-        <v>103.69</v>
+        <v>47.34</v>
       </c>
       <c r="E133" t="n">
-        <v>80.64</v>
+        <v>8.4</v>
       </c>
       <c r="F133" t="n">
-        <v>0.53257</v>
+        <v>0.05503</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>161.91</v>
+        <v>161.37</v>
       </c>
       <c r="D134" t="n">
-        <v>209.36</v>
+        <v>264.51</v>
       </c>
       <c r="E134" t="n">
-        <v>29.31</v>
+        <v>63.92</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.52751</v>
+        <v>0.82511</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>63.16</v>
+        <v>55.05</v>
       </c>
       <c r="D135" t="n">
-        <v>100.67</v>
+        <v>63.57</v>
       </c>
       <c r="E135" t="n">
-        <v>59.39</v>
+        <v>15.48</v>
       </c>
       <c r="F135" t="n">
-        <v>1.35459</v>
+        <v>-0.4736</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>250.4</v>
+        <v>28.18</v>
       </c>
       <c r="D136" t="n">
-        <v>323.97</v>
+        <v>37.03</v>
       </c>
       <c r="E136" t="n">
-        <v>29.38</v>
+        <v>31.41</v>
       </c>
       <c r="F136" t="n">
-        <v>-3.61611</v>
+        <v>-0.01107</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>102.87</v>
+        <v>195.11</v>
       </c>
       <c r="D137" t="n">
-        <v>174.73</v>
+        <v>249.05</v>
       </c>
       <c r="E137" t="n">
-        <v>69.86</v>
+        <v>27.65</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.36801</v>
+        <v>0.4172</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>186.61</v>
+        <v>140.19</v>
       </c>
       <c r="D138" t="n">
-        <v>247.08</v>
+        <v>146.13</v>
       </c>
       <c r="E138" t="n">
-        <v>32.4</v>
+        <v>4.24</v>
       </c>
       <c r="F138" t="n">
-        <v>0.19288</v>
+        <v>-0.3931</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>26.18</v>
+        <v>207.24</v>
       </c>
       <c r="D139" t="n">
-        <v>36.72</v>
+        <v>253.88</v>
       </c>
       <c r="E139" t="n">
-        <v>40.26</v>
+        <v>22.51</v>
       </c>
       <c r="F139" t="n">
-        <v>0.23738</v>
+        <v>-2.67569</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>43.3</v>
+        <v>15.03</v>
       </c>
       <c r="D140" t="n">
-        <v>72.34</v>
+        <v>18.6</v>
       </c>
       <c r="E140" t="n">
-        <v>67.06999999999999</v>
+        <v>23.75</v>
       </c>
       <c r="F140" t="n">
-        <v>0.008569999999999999</v>
+        <v>0.08944000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>73.42</v>
+        <v>72.55</v>
       </c>
       <c r="D141" t="n">
-        <v>89.72</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>22.2</v>
+        <v>5.16</v>
       </c>
       <c r="F141" t="n">
-        <v>0.70402</v>
+        <v>-0.36496</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>438.34</v>
+        <v>275.99</v>
       </c>
       <c r="D142" t="n">
-        <v>641.39</v>
+        <v>322.99</v>
       </c>
       <c r="E142" t="n">
-        <v>46.32</v>
+        <v>17.03</v>
       </c>
       <c r="F142" t="n">
-        <v>3.85233</v>
+        <v>1.92883</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>163.43</v>
+        <v>277.69</v>
       </c>
       <c r="D143" t="n">
-        <v>198.63</v>
+        <v>330.62</v>
       </c>
       <c r="E143" t="n">
-        <v>21.54</v>
+        <v>19.06</v>
       </c>
       <c r="F143" t="n">
-        <v>1.4774</v>
+        <v>-0.14398</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>55.52</v>
+        <v>73.75</v>
       </c>
       <c r="D144" t="n">
-        <v>93.23999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="E144" t="n">
-        <v>67.94</v>
+        <v>27.19</v>
       </c>
       <c r="F144" t="n">
-        <v>1.96119</v>
+        <v>0.31456</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>99.3</v>
+        <v>121.13</v>
       </c>
       <c r="D145" t="n">
-        <v>153.74</v>
+        <v>138.92</v>
       </c>
       <c r="E145" t="n">
-        <v>54.82</v>
+        <v>14.69</v>
       </c>
       <c r="F145" t="n">
-        <v>2.14918</v>
+        <v>0.41111</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>197.73</v>
+        <v>132.79</v>
       </c>
       <c r="D146" t="n">
-        <v>223.04</v>
+        <v>163.39</v>
       </c>
       <c r="E146" t="n">
-        <v>12.8</v>
+        <v>23.04</v>
       </c>
       <c r="F146" t="n">
-        <v>0.94077</v>
+        <v>-0.12699</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>725.17</v>
+        <v>309.78</v>
       </c>
       <c r="D147" t="n">
-        <v>899.5599999999999</v>
+        <v>341.85</v>
       </c>
       <c r="E147" t="n">
-        <v>24.05</v>
+        <v>10.35</v>
       </c>
       <c r="F147" t="n">
-        <v>2.47985</v>
+        <v>-1.13236</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>79.58</v>
+        <v>36.25</v>
       </c>
       <c r="D148" t="n">
-        <v>98.41</v>
+        <v>41.61</v>
       </c>
       <c r="E148" t="n">
-        <v>23.66</v>
+        <v>14.79</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.83257</v>
+        <v>0.22556</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>255.54</v>
+        <v>9.85</v>
       </c>
       <c r="D149" t="n">
-        <v>365.08</v>
+        <v>13.75</v>
       </c>
       <c r="E149" t="n">
-        <v>42.87</v>
+        <v>39.59</v>
       </c>
       <c r="F149" t="n">
-        <v>3.26755</v>
+        <v>0.51236</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>417.83</v>
+        <v>33.54</v>
       </c>
       <c r="D150" t="n">
-        <v>558.26</v>
+        <v>42.61</v>
       </c>
       <c r="E150" t="n">
-        <v>33.61</v>
+        <v>27.04</v>
       </c>
       <c r="F150" t="n">
-        <v>3.75502</v>
+        <v>0.13446</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>12.64</v>
+        <v>190.4</v>
       </c>
       <c r="D151" t="n">
-        <v>18.26</v>
+        <v>221.02</v>
       </c>
       <c r="E151" t="n">
-        <v>44.46</v>
+        <v>16.08</v>
       </c>
       <c r="F151" t="n">
-        <v>0.26064</v>
+        <v>0.04179</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>32.32</v>
+        <v>63.54</v>
       </c>
       <c r="D152" t="n">
-        <v>37.81</v>
+        <v>70.87</v>
       </c>
       <c r="E152" t="n">
-        <v>16.99</v>
+        <v>11.54</v>
       </c>
       <c r="F152" t="n">
-        <v>0.07455000000000001</v>
+        <v>0.26916</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>IDCC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>699965</v>
+        <v>250.75</v>
       </c>
       <c r="D153" t="n">
-        <v>773825</v>
+        <v>340.38</v>
       </c>
       <c r="E153" t="n">
-        <v>10.55</v>
+        <v>35.74</v>
       </c>
       <c r="F153" t="n">
-        <v>3681.50215</v>
+        <v>3.87926</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FMS</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>20.19</v>
+        <v>529.12</v>
       </c>
       <c r="D154" t="n">
-        <v>22.96</v>
+        <v>681.46</v>
       </c>
       <c r="E154" t="n">
-        <v>13.72</v>
+        <v>28.79</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.15989</v>
+        <v>9.785550000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>139.71</v>
+        <v>57.4</v>
       </c>
       <c r="D155" t="n">
-        <v>193.9</v>
+        <v>104.79</v>
       </c>
       <c r="E155" t="n">
-        <v>38.79</v>
+        <v>82.56</v>
       </c>
       <c r="F155" t="n">
-        <v>2.09242</v>
+        <v>0.21284</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>SGI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>45.37</v>
+        <v>61.49</v>
       </c>
       <c r="D156" t="n">
-        <v>143.77</v>
+        <v>68.12</v>
       </c>
       <c r="E156" t="n">
-        <v>216.88</v>
+        <v>10.78</v>
       </c>
       <c r="F156" t="n">
-        <v>5.51342</v>
+        <v>0.25125</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>BMRN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>112.47</v>
+        <v>49.67</v>
       </c>
       <c r="D157" t="n">
-        <v>137.79</v>
+        <v>66.41</v>
       </c>
       <c r="E157" t="n">
-        <v>22.51</v>
+        <v>33.7</v>
       </c>
       <c r="F157" t="n">
-        <v>0.54053</v>
+        <v>0.03841</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>156.66</v>
+        <v>438.34</v>
       </c>
       <c r="D158" t="n">
-        <v>269.67</v>
+        <v>613.62</v>
       </c>
       <c r="E158" t="n">
-        <v>72.14</v>
+        <v>39.99</v>
       </c>
       <c r="F158" t="n">
-        <v>3.05682</v>
+        <v>0.49995</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>82.26000000000001</v>
+        <v>43.3</v>
       </c>
       <c r="D159" t="n">
-        <v>140.19</v>
+        <v>72.27</v>
       </c>
       <c r="E159" t="n">
-        <v>70.42</v>
+        <v>66.91</v>
       </c>
       <c r="F159" t="n">
-        <v>1.63417</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>40.41</v>
+        <v>73.42</v>
       </c>
       <c r="D160" t="n">
-        <v>52.93</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E160" t="n">
-        <v>30.98</v>
+        <v>20.83</v>
       </c>
       <c r="F160" t="n">
-        <v>0.06672</v>
+        <v>0.7728699999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>197.38</v>
+        <v>63.16</v>
       </c>
       <c r="D161" t="n">
-        <v>263.04</v>
+        <v>101.84</v>
       </c>
       <c r="E161" t="n">
-        <v>33.27</v>
+        <v>61.24</v>
       </c>
       <c r="F161" t="n">
-        <v>1.10836</v>
+        <v>1.43086</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>393.42</v>
+        <v>5563.62</v>
       </c>
       <c r="D162" t="n">
-        <v>620.48</v>
+        <v>6299.56</v>
       </c>
       <c r="E162" t="n">
-        <v>57.71</v>
+        <v>13.23</v>
       </c>
       <c r="F162" t="n">
-        <v>1.40198</v>
+        <v>-44.26965</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>74.63</v>
+        <v>26.18</v>
       </c>
       <c r="D163" t="n">
-        <v>88.70999999999999</v>
+        <v>36.71</v>
       </c>
       <c r="E163" t="n">
-        <v>18.87</v>
+        <v>40.22</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0604</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>465.4</v>
+        <v>186.61</v>
       </c>
       <c r="D164" t="n">
-        <v>516.76</v>
+        <v>237.89</v>
       </c>
       <c r="E164" t="n">
-        <v>11.04</v>
+        <v>27.48</v>
       </c>
       <c r="F164" t="n">
-        <v>2.46605</v>
+        <v>-1.00997</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>153.25</v>
+        <v>92.38</v>
       </c>
       <c r="D165" t="n">
-        <v>194.11</v>
+        <v>100.65</v>
       </c>
       <c r="E165" t="n">
-        <v>26.66</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F165" t="n">
-        <v>1.57503</v>
+        <v>-0.07876</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>20.96</v>
+        <v>163.43</v>
       </c>
       <c r="D166" t="n">
-        <v>25.77</v>
+        <v>200.67</v>
       </c>
       <c r="E166" t="n">
-        <v>22.95</v>
+        <v>22.79</v>
       </c>
       <c r="F166" t="n">
-        <v>0.24889</v>
+        <v>0.62133</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>155.75</v>
+        <v>156.84</v>
       </c>
       <c r="D167" t="n">
-        <v>264.93</v>
+        <v>187.03</v>
       </c>
       <c r="E167" t="n">
-        <v>70.09999999999999</v>
+        <v>19.25</v>
       </c>
       <c r="F167" t="n">
-        <v>5.58905</v>
+        <v>-2.68499</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>40.59</v>
+        <v>101.75</v>
       </c>
       <c r="D168" t="n">
-        <v>57.61</v>
+        <v>129.17</v>
       </c>
       <c r="E168" t="n">
-        <v>41.93</v>
+        <v>26.95</v>
       </c>
       <c r="F168" t="n">
-        <v>1.55685</v>
+        <v>-0.25082</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>213.69</v>
+        <v>55.52</v>
       </c>
       <c r="D169" t="n">
-        <v>410.84</v>
+        <v>94.83</v>
       </c>
       <c r="E169" t="n">
-        <v>92.26000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F169" t="n">
-        <v>10.41305</v>
+        <v>1.61921</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>223.65</v>
+        <v>99.3</v>
       </c>
       <c r="D170" t="n">
-        <v>397.04</v>
+        <v>151.7</v>
       </c>
       <c r="E170" t="n">
-        <v>77.53</v>
+        <v>52.77</v>
       </c>
       <c r="F170" t="n">
-        <v>11.66693</v>
+        <v>1.17857</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>128.43</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="D171" t="n">
-        <v>153.74</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E171" t="n">
-        <v>19.71</v>
+        <v>28.9</v>
       </c>
       <c r="F171" t="n">
-        <v>1.24056</v>
+        <v>-0.34243</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>18.71</v>
+        <v>725.17</v>
       </c>
       <c r="D172" t="n">
-        <v>21.33</v>
+        <v>910.95</v>
       </c>
       <c r="E172" t="n">
-        <v>14</v>
+        <v>25.62</v>
       </c>
       <c r="F172" t="n">
-        <v>0.09087000000000001</v>
+        <v>1.91142</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>66.95</v>
+        <v>197.73</v>
       </c>
       <c r="D173" t="n">
-        <v>86.61</v>
+        <v>225.85</v>
       </c>
       <c r="E173" t="n">
-        <v>29.37</v>
+        <v>14.22</v>
       </c>
       <c r="F173" t="n">
-        <v>1.36817</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>151.43</v>
+        <v>255.54</v>
       </c>
       <c r="D174" t="n">
-        <v>266.62</v>
+        <v>365.08</v>
       </c>
       <c r="E174" t="n">
-        <v>76.06999999999999</v>
+        <v>42.87</v>
       </c>
       <c r="F174" t="n">
-        <v>1.96202</v>
+        <v>3.26755</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>105.37</v>
+        <v>12.64</v>
       </c>
       <c r="D175" t="n">
-        <v>230.27</v>
+        <v>17.74</v>
       </c>
       <c r="E175" t="n">
-        <v>118.53</v>
+        <v>40.35</v>
       </c>
       <c r="F175" t="n">
-        <v>-1.24495</v>
+        <v>0.24281</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>120.88</v>
+        <v>417.83</v>
       </c>
       <c r="D176" t="n">
-        <v>209.62</v>
+        <v>556.3099999999999</v>
       </c>
       <c r="E176" t="n">
-        <v>73.41</v>
+        <v>33.14</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.40223</v>
+        <v>0.43871</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>62.93</v>
+        <v>383.99</v>
       </c>
       <c r="D177" t="n">
-        <v>190.45</v>
+        <v>474.13</v>
       </c>
       <c r="E177" t="n">
-        <v>202.64</v>
+        <v>23.47</v>
       </c>
       <c r="F177" t="n">
-        <v>7.34012</v>
+        <v>-1.53084</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>76.7</v>
+        <v>32.32</v>
       </c>
       <c r="D178" t="n">
-        <v>172.37</v>
+        <v>37.72</v>
       </c>
       <c r="E178" t="n">
-        <v>124.73</v>
+        <v>16.71</v>
       </c>
       <c r="F178" t="n">
-        <v>2.05425</v>
+        <v>0.15923</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>166.99</v>
+        <v>252.74</v>
       </c>
       <c r="D179" t="n">
-        <v>327.23</v>
+        <v>326.23</v>
       </c>
       <c r="E179" t="n">
-        <v>95.95999999999999</v>
+        <v>29.08</v>
       </c>
       <c r="F179" t="n">
-        <v>9.443759999999999</v>
+        <v>-0.21978</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>34.41</v>
+        <v>699965</v>
       </c>
       <c r="D180" t="n">
-        <v>67.98999999999999</v>
+        <v>773825</v>
       </c>
       <c r="E180" t="n">
-        <v>97.59</v>
+        <v>10.55</v>
       </c>
       <c r="F180" t="n">
-        <v>0.22691</v>
+        <v>3681.50215</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>10.49</v>
+        <v>139.71</v>
       </c>
       <c r="D181" t="n">
-        <v>19.98</v>
+        <v>193.61</v>
       </c>
       <c r="E181" t="n">
-        <v>90.47</v>
+        <v>38.58</v>
       </c>
       <c r="F181" t="n">
-        <v>0.08939999999999999</v>
+        <v>1.72426</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>57.15</v>
+        <v>45.37</v>
       </c>
       <c r="D182" t="n">
-        <v>189.81</v>
+        <v>146.69</v>
       </c>
       <c r="E182" t="n">
-        <v>232.13</v>
+        <v>223.32</v>
       </c>
       <c r="F182" t="n">
-        <v>4.93853</v>
+        <v>5.23484</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>78.59999999999999</v>
+        <v>112.47</v>
       </c>
       <c r="D183" t="n">
-        <v>175.65</v>
+        <v>138.5</v>
       </c>
       <c r="E183" t="n">
-        <v>123.47</v>
+        <v>23.14</v>
       </c>
       <c r="F183" t="n">
-        <v>1.12337</v>
+        <v>0.31006</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>118.05</v>
+        <v>156.66</v>
       </c>
       <c r="D184" t="n">
-        <v>193.89</v>
+        <v>265.67</v>
       </c>
       <c r="E184" t="n">
-        <v>64.23999999999999</v>
+        <v>69.58</v>
       </c>
       <c r="F184" t="n">
-        <v>2.28457</v>
+        <v>2.0428</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>188.79</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D185" t="n">
-        <v>276.53</v>
+        <v>128.49</v>
       </c>
       <c r="E185" t="n">
-        <v>46.47</v>
+        <v>56.2</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.99091</v>
+        <v>0.08618000000000001</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>32.36</v>
+        <v>13.06</v>
       </c>
       <c r="D186" t="n">
-        <v>55.17</v>
+        <v>19.91</v>
       </c>
       <c r="E186" t="n">
-        <v>70.48999999999999</v>
+        <v>52.45</v>
       </c>
       <c r="F186" t="n">
-        <v>0.76689</v>
+        <v>-0.009140000000000001</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>83</v>
+        <v>40.41</v>
       </c>
       <c r="D187" t="n">
-        <v>141.9</v>
+        <v>51.96</v>
       </c>
       <c r="E187" t="n">
-        <v>70.95999999999999</v>
+        <v>28.58</v>
       </c>
       <c r="F187" t="n">
-        <v>1.71804</v>
+        <v>-0.19889</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>18.26</v>
+        <v>197.38</v>
       </c>
       <c r="D188" t="n">
-        <v>33.82</v>
+        <v>261.77</v>
       </c>
       <c r="E188" t="n">
-        <v>85.20999999999999</v>
+        <v>32.62</v>
       </c>
       <c r="F188" t="n">
-        <v>1.18337</v>
+        <v>-0.05181</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>112.5</v>
+        <v>393.42</v>
       </c>
       <c r="D189" t="n">
-        <v>190.67</v>
+        <v>595.41</v>
       </c>
       <c r="E189" t="n">
-        <v>69.48</v>
+        <v>51.34</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.51289</v>
+        <v>-2.04834</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>25.85</v>
+        <v>56.06</v>
       </c>
       <c r="D190" t="n">
-        <v>41.65</v>
+        <v>62.39</v>
       </c>
       <c r="E190" t="n">
-        <v>61.12</v>
+        <v>11.29</v>
       </c>
       <c r="F190" t="n">
-        <v>0.40151</v>
+        <v>0.03839</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>43.81</v>
+        <v>74.63</v>
       </c>
       <c r="D191" t="n">
-        <v>103.55</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E191" t="n">
-        <v>136.36</v>
+        <v>19.72</v>
       </c>
       <c r="F191" t="n">
-        <v>1.02235</v>
+        <v>-0.05535</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>117.65</v>
+        <v>465.4</v>
       </c>
       <c r="D192" t="n">
-        <v>242.16</v>
+        <v>514.95</v>
       </c>
       <c r="E192" t="n">
-        <v>105.83</v>
+        <v>10.65</v>
       </c>
       <c r="F192" t="n">
-        <v>1.79379</v>
+        <v>1.66879</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>17.89</v>
+        <v>153.25</v>
       </c>
       <c r="D193" t="n">
-        <v>31.23</v>
+        <v>194.86</v>
       </c>
       <c r="E193" t="n">
-        <v>74.56999999999999</v>
+        <v>27.15</v>
       </c>
       <c r="F193" t="n">
-        <v>0.39427</v>
+        <v>0.85662</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>95.67</v>
+        <v>20.96</v>
       </c>
       <c r="D194" t="n">
-        <v>189.93</v>
+        <v>25.85</v>
       </c>
       <c r="E194" t="n">
-        <v>98.53</v>
+        <v>23.33</v>
       </c>
       <c r="F194" t="n">
-        <v>0.92719</v>
+        <v>0.28351</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>56.43</v>
+        <v>155.75</v>
       </c>
       <c r="D195" t="n">
-        <v>112.25</v>
+        <v>257.06</v>
       </c>
       <c r="E195" t="n">
-        <v>98.92</v>
+        <v>65.05</v>
       </c>
       <c r="F195" t="n">
-        <v>3.11717</v>
+        <v>5.74053</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>62.49</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="D196" t="n">
-        <v>90.06</v>
+        <v>96.97</v>
       </c>
       <c r="E196" t="n">
-        <v>44.12</v>
+        <v>16.12</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.21073</v>
+        <v>0.63437</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>23.63</v>
+        <v>40.59</v>
       </c>
       <c r="D197" t="n">
-        <v>25.4</v>
+        <v>56.33</v>
       </c>
       <c r="E197" t="n">
-        <v>7.49</v>
+        <v>38.78</v>
       </c>
       <c r="F197" t="n">
-        <v>0.05914</v>
+        <v>1.40494</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>124.07</v>
+        <v>213.69</v>
       </c>
       <c r="D198" t="n">
-        <v>187.8</v>
+        <v>396.45</v>
       </c>
       <c r="E198" t="n">
-        <v>51.37</v>
+        <v>85.53</v>
       </c>
       <c r="F198" t="n">
-        <v>4.85902</v>
+        <v>10.30916</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>23.49</v>
+        <v>128.43</v>
       </c>
       <c r="D199" t="n">
-        <v>32.21</v>
+        <v>148.54</v>
       </c>
       <c r="E199" t="n">
-        <v>37.12</v>
+        <v>15.66</v>
       </c>
       <c r="F199" t="n">
-        <v>0.17481</v>
+        <v>0.66273</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>172.34</v>
+        <v>223.65</v>
       </c>
       <c r="D200" t="n">
-        <v>216.17</v>
+        <v>382.95</v>
       </c>
       <c r="E200" t="n">
-        <v>25.43</v>
+        <v>71.23</v>
       </c>
       <c r="F200" t="n">
-        <v>0.34426</v>
+        <v>12.04345</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>430.4</v>
+        <v>18.71</v>
       </c>
       <c r="D201" t="n">
-        <v>559.34</v>
+        <v>21.49</v>
       </c>
       <c r="E201" t="n">
-        <v>29.96</v>
+        <v>14.86</v>
       </c>
       <c r="F201" t="n">
-        <v>0.948</v>
+        <v>0.13728</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BML-PJ</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>19.05</v>
+        <v>66.95</v>
       </c>
       <c r="D202" t="n">
-        <v>19.64</v>
+        <v>86.44</v>
       </c>
       <c r="E202" t="n">
-        <v>3.1</v>
+        <v>29.11</v>
       </c>
       <c r="F202" t="n">
-        <v>0.02454</v>
+        <v>1.50588</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>164.13</v>
+        <v>126.32</v>
       </c>
       <c r="D203" t="n">
-        <v>543.51</v>
+        <v>157.22</v>
       </c>
       <c r="E203" t="n">
-        <v>231.15</v>
+        <v>24.46</v>
       </c>
       <c r="F203" t="n">
-        <v>20.08884</v>
+        <v>-0.32127</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>96.73</v>
+        <v>25.85</v>
       </c>
       <c r="D204" t="n">
-        <v>122</v>
+        <v>42.91</v>
       </c>
       <c r="E204" t="n">
-        <v>26.12</v>
+        <v>66</v>
       </c>
       <c r="F204" t="n">
-        <v>0.43594</v>
+        <v>0.12798</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>12.96</v>
+        <v>188.79</v>
       </c>
       <c r="D205" t="n">
-        <v>16.65</v>
+        <v>276.63</v>
       </c>
       <c r="E205" t="n">
-        <v>28.47</v>
+        <v>46.53</v>
       </c>
       <c r="F205" t="n">
-        <v>-0.03231</v>
+        <v>-2.28574</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>284.79</v>
+        <v>76.7</v>
       </c>
       <c r="D206" t="n">
-        <v>417.54</v>
+        <v>170.18</v>
       </c>
       <c r="E206" t="n">
-        <v>46.61</v>
+        <v>121.88</v>
       </c>
       <c r="F206" t="n">
-        <v>6.50222</v>
+        <v>0.67575</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>166</v>
+        <v>43.81</v>
       </c>
       <c r="D207" t="n">
-        <v>396.62</v>
+        <v>100.2</v>
       </c>
       <c r="E207" t="n">
-        <v>138.93</v>
+        <v>128.71</v>
       </c>
       <c r="F207" t="n">
-        <v>3.79223</v>
+        <v>-0.42056</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>119.51</v>
+        <v>166.99</v>
       </c>
       <c r="D208" t="n">
-        <v>259.35</v>
+        <v>330.36</v>
       </c>
       <c r="E208" t="n">
-        <v>117.01</v>
+        <v>97.83</v>
       </c>
       <c r="F208" t="n">
-        <v>10.66539</v>
+        <v>9.064159999999999</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>29.16</v>
+        <v>32.36</v>
       </c>
       <c r="D209" t="n">
-        <v>39.69</v>
+        <v>53.34</v>
       </c>
       <c r="E209" t="n">
-        <v>36.11</v>
+        <v>64.83</v>
       </c>
       <c r="F209" t="n">
-        <v>0.07466</v>
+        <v>0.36656</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>97.52</v>
+        <v>112.5</v>
       </c>
       <c r="D210" t="n">
-        <v>129.59</v>
+        <v>194.21</v>
       </c>
       <c r="E210" t="n">
-        <v>32.89</v>
+        <v>72.63</v>
       </c>
       <c r="F210" t="n">
-        <v>2.24577</v>
+        <v>-1.0532</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>28.35</v>
+        <v>105.37</v>
       </c>
       <c r="D211" t="n">
-        <v>39.25</v>
+        <v>230.05</v>
       </c>
       <c r="E211" t="n">
-        <v>38.45</v>
+        <v>118.33</v>
       </c>
       <c r="F211" t="n">
-        <v>0.49418</v>
+        <v>-1.90231</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>131.47</v>
+        <v>121.11</v>
       </c>
       <c r="D212" t="n">
-        <v>206.99</v>
+        <v>332.35</v>
       </c>
       <c r="E212" t="n">
-        <v>57.44</v>
+        <v>174.42</v>
       </c>
       <c r="F212" t="n">
-        <v>2.05473</v>
+        <v>2.08531</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>258.08</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D213" t="n">
-        <v>288.9</v>
+        <v>167.84</v>
       </c>
       <c r="E213" t="n">
-        <v>11.94</v>
+        <v>113.54</v>
       </c>
       <c r="F213" t="n">
-        <v>1.81284</v>
+        <v>-0.11311</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>24.77</v>
+        <v>117.65</v>
       </c>
       <c r="D214" t="n">
-        <v>36.78</v>
+        <v>231.88</v>
       </c>
       <c r="E214" t="n">
-        <v>48.49</v>
+        <v>97.09</v>
       </c>
       <c r="F214" t="n">
-        <v>0.38487</v>
+        <v>0.40682</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>73.13</v>
+        <v>34.41</v>
       </c>
       <c r="D215" t="n">
-        <v>95.81999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="E215" t="n">
-        <v>31.03</v>
+        <v>96.72</v>
       </c>
       <c r="F215" t="n">
-        <v>0.60843</v>
+        <v>0.14027</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>67.39</v>
+        <v>17.89</v>
       </c>
       <c r="D216" t="n">
-        <v>93.28</v>
+        <v>31.41</v>
       </c>
       <c r="E216" t="n">
-        <v>38.42</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F216" t="n">
-        <v>0.61522</v>
+        <v>0.28103</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>22.61</v>
+        <v>120.88</v>
       </c>
       <c r="D217" t="n">
-        <v>55.88</v>
+        <v>211.54</v>
       </c>
       <c r="E217" t="n">
-        <v>147.15</v>
+        <v>75</v>
       </c>
       <c r="F217" t="n">
-        <v>1.10062</v>
+        <v>-0.8151</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>65.16</v>
+        <v>151.43</v>
       </c>
       <c r="D218" t="n">
-        <v>110.45</v>
+        <v>265.67</v>
       </c>
       <c r="E218" t="n">
-        <v>69.51000000000001</v>
+        <v>75.44</v>
       </c>
       <c r="F218" t="n">
-        <v>1.57155</v>
+        <v>1.55591</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>19.02</v>
+        <v>83</v>
       </c>
       <c r="D219" t="n">
-        <v>26.78</v>
+        <v>142.35</v>
       </c>
       <c r="E219" t="n">
-        <v>40.8</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F219" t="n">
-        <v>0.29688</v>
+        <v>0.76309</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>116.13</v>
+        <v>62.93</v>
       </c>
       <c r="D220" t="n">
-        <v>192.84</v>
+        <v>186.45</v>
       </c>
       <c r="E220" t="n">
-        <v>66.06</v>
+        <v>196.28</v>
       </c>
       <c r="F220" t="n">
-        <v>0.13947</v>
+        <v>6.24855</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>16.32</v>
+        <v>118.05</v>
       </c>
       <c r="D221" t="n">
-        <v>23.71</v>
+        <v>191.73</v>
       </c>
       <c r="E221" t="n">
-        <v>45.28</v>
+        <v>62.41</v>
       </c>
       <c r="F221" t="n">
-        <v>0.26691</v>
+        <v>-0.40022</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>41.19</v>
+        <v>18.26</v>
       </c>
       <c r="D222" t="n">
-        <v>97.14</v>
+        <v>34.02</v>
       </c>
       <c r="E222" t="n">
-        <v>135.83</v>
+        <v>86.31</v>
       </c>
       <c r="F222" t="n">
-        <v>1.2311</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>52.5</v>
+        <v>10.49</v>
       </c>
       <c r="D223" t="n">
-        <v>90</v>
+        <v>19.88</v>
       </c>
       <c r="E223" t="n">
-        <v>71.43000000000001</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="F223" t="n">
-        <v>5.23697</v>
+        <v>-0.15382</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>107.27</v>
+        <v>57.15</v>
       </c>
       <c r="D224" t="n">
-        <v>136.17</v>
+        <v>192.77</v>
       </c>
       <c r="E224" t="n">
-        <v>26.94</v>
+        <v>237.31</v>
       </c>
       <c r="F224" t="n">
-        <v>0.75183</v>
+        <v>4.18785</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>196.04</v>
+        <v>56.43</v>
       </c>
       <c r="D225" t="n">
-        <v>504.2</v>
+        <v>106.91</v>
       </c>
       <c r="E225" t="n">
-        <v>157.19</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="F225" t="n">
-        <v>7.29423</v>
+        <v>3.01266</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3.88</v>
+        <v>124.07</v>
       </c>
       <c r="D226" t="n">
-        <v>6.44</v>
+        <v>180.15</v>
       </c>
       <c r="E226" t="n">
-        <v>65.98</v>
+        <v>45.2</v>
       </c>
       <c r="F226" t="n">
-        <v>0.07534</v>
+        <v>4.1705</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>246.63</v>
+        <v>62.49</v>
       </c>
       <c r="D227" t="n">
-        <v>331.34</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="E227" t="n">
-        <v>34.35</v>
+        <v>43.73</v>
       </c>
       <c r="F227" t="n">
-        <v>4.71551</v>
+        <v>-0.23607</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>8.609999999999999</v>
+        <v>23.63</v>
       </c>
       <c r="D228" t="n">
-        <v>21.61</v>
+        <v>25.41</v>
       </c>
       <c r="E228" t="n">
-        <v>150.99</v>
+        <v>7.53</v>
       </c>
       <c r="F228" t="n">
-        <v>0.62903</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>273.5</v>
+        <v>190.63</v>
       </c>
       <c r="D229" t="n">
-        <v>344.98</v>
+        <v>218.57</v>
       </c>
       <c r="E229" t="n">
-        <v>26.14</v>
+        <v>14.66</v>
       </c>
       <c r="F229" t="n">
-        <v>0.07092</v>
+        <v>-1.51875</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>59.66</v>
+        <v>23.49</v>
       </c>
       <c r="D230" t="n">
-        <v>82.63</v>
+        <v>32.49</v>
       </c>
       <c r="E230" t="n">
-        <v>38.5</v>
+        <v>38.31</v>
       </c>
       <c r="F230" t="n">
-        <v>1.52417</v>
+        <v>0.09743</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>273.14</v>
+        <v>172.34</v>
       </c>
       <c r="D231" t="n">
-        <v>341.43</v>
+        <v>217.36</v>
       </c>
       <c r="E231" t="n">
-        <v>25</v>
+        <v>26.12</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.05953</v>
+        <v>-0.19213</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>204.77</v>
+        <v>430.4</v>
       </c>
       <c r="D232" t="n">
-        <v>273.05</v>
+        <v>558.54</v>
       </c>
       <c r="E232" t="n">
-        <v>33.34</v>
+        <v>29.77</v>
       </c>
       <c r="F232" t="n">
-        <v>0.99791</v>
+        <v>0.26252</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>90.01000000000001</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="D233" t="n">
-        <v>101.14</v>
+        <v>87.16</v>
       </c>
       <c r="E233" t="n">
-        <v>12.37</v>
+        <v>20.15</v>
       </c>
       <c r="F233" t="n">
-        <v>0.33492</v>
+        <v>-0.10751</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>26.41</v>
+        <v>164.13</v>
       </c>
       <c r="D234" t="n">
-        <v>39.5</v>
+        <v>534.28</v>
       </c>
       <c r="E234" t="n">
-        <v>49.56</v>
+        <v>225.52</v>
       </c>
       <c r="F234" t="n">
-        <v>1.30846</v>
+        <v>21.33398</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>31.8</v>
+        <v>96.73</v>
       </c>
       <c r="D235" t="n">
-        <v>67.66</v>
+        <v>122.53</v>
       </c>
       <c r="E235" t="n">
-        <v>112.77</v>
+        <v>26.67</v>
       </c>
       <c r="F235" t="n">
-        <v>0.62832</v>
+        <v>0.4313</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>BML-PJ</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>279.73</v>
+        <v>19.05</v>
       </c>
       <c r="D236" t="n">
-        <v>430.88</v>
+        <v>19.64</v>
       </c>
       <c r="E236" t="n">
-        <v>54.03</v>
+        <v>3.1</v>
       </c>
       <c r="F236" t="n">
-        <v>5.88329</v>
+        <v>0.02454</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>525.72</v>
+        <v>20.33</v>
       </c>
       <c r="D237" t="n">
-        <v>670.24</v>
+        <v>29.1</v>
       </c>
       <c r="E237" t="n">
-        <v>27.49</v>
+        <v>43.14</v>
       </c>
       <c r="F237" t="n">
-        <v>21.58203</v>
+        <v>0.12624</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>92.39</v>
+        <v>3.88</v>
       </c>
       <c r="D238" t="n">
-        <v>242.49</v>
+        <v>6.46</v>
       </c>
       <c r="E238" t="n">
-        <v>162.45</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F238" t="n">
-        <v>5.44723</v>
+        <v>0.08959</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>87.01000000000001</v>
+        <v>246.63</v>
       </c>
       <c r="D239" t="n">
-        <v>118.37</v>
+        <v>333.08</v>
       </c>
       <c r="E239" t="n">
-        <v>36.04</v>
+        <v>35.05</v>
       </c>
       <c r="F239" t="n">
-        <v>1.18624</v>
+        <v>3.52767</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>39.84</v>
+        <v>199.3</v>
       </c>
       <c r="D240" t="n">
-        <v>58.28</v>
+        <v>351.81</v>
       </c>
       <c r="E240" t="n">
-        <v>46.29</v>
+        <v>76.52</v>
       </c>
       <c r="F240" t="n">
-        <v>0.05681</v>
+        <v>-1.44191</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>22.3</v>
+        <v>73.13</v>
       </c>
       <c r="D241" t="n">
-        <v>35.02</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E241" t="n">
-        <v>57.04</v>
+        <v>30.49</v>
       </c>
       <c r="F241" t="n">
-        <v>0.52819</v>
+        <v>0.43563</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>317.93</v>
+        <v>52.5</v>
       </c>
       <c r="D242" t="n">
-        <v>379.55</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="E242" t="n">
-        <v>19.38</v>
+        <v>50.97</v>
       </c>
       <c r="F242" t="n">
-        <v>0.46956</v>
+        <v>4.37139</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>35.34</v>
+        <v>131.47</v>
       </c>
       <c r="D243" t="n">
-        <v>53.97</v>
+        <v>214.07</v>
       </c>
       <c r="E243" t="n">
-        <v>52.72</v>
+        <v>62.83</v>
       </c>
       <c r="F243" t="n">
-        <v>0.84994</v>
+        <v>0.91734</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>7.63</v>
+        <v>41.19</v>
       </c>
       <c r="D244" t="n">
-        <v>11.15</v>
+        <v>97.19</v>
       </c>
       <c r="E244" t="n">
-        <v>46.13</v>
+        <v>135.96</v>
       </c>
       <c r="F244" t="n">
-        <v>0.16553</v>
+        <v>2.31858</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3.42</v>
+        <v>258.08</v>
       </c>
       <c r="D245" t="n">
-        <v>5.06</v>
+        <v>290.05</v>
       </c>
       <c r="E245" t="n">
-        <v>47.95</v>
+        <v>12.39</v>
       </c>
       <c r="F245" t="n">
-        <v>0.09043</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>147.02</v>
+        <v>196.04</v>
       </c>
       <c r="D246" t="n">
-        <v>375.09</v>
+        <v>493.41</v>
       </c>
       <c r="E246" t="n">
-        <v>155.13</v>
+        <v>151.69</v>
       </c>
       <c r="F246" t="n">
-        <v>1.92246</v>
+        <v>9.84099</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>295.52</v>
+        <v>19.02</v>
       </c>
       <c r="D247" t="n">
-        <v>375.62</v>
+        <v>27.24</v>
       </c>
       <c r="E247" t="n">
-        <v>27.1</v>
+        <v>43.22</v>
       </c>
       <c r="F247" t="n">
-        <v>0.11189</v>
+        <v>0.27865</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>67.56999999999999</v>
+        <v>16.32</v>
       </c>
       <c r="D248" t="n">
-        <v>79.45999999999999</v>
+        <v>23.89</v>
       </c>
       <c r="E248" t="n">
-        <v>17.6</v>
+        <v>46.38</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.25539</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>91.37</v>
+        <v>284.79</v>
       </c>
       <c r="D249" t="n">
-        <v>121.47</v>
+        <v>424.24</v>
       </c>
       <c r="E249" t="n">
-        <v>32.94</v>
+        <v>48.97</v>
       </c>
       <c r="F249" t="n">
-        <v>0.12704</v>
+        <v>5.01403</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>7.58</v>
+        <v>107.27</v>
       </c>
       <c r="D250" t="n">
-        <v>10.61</v>
+        <v>136.18</v>
       </c>
       <c r="E250" t="n">
-        <v>39.97</v>
+        <v>26.95</v>
       </c>
       <c r="F250" t="n">
-        <v>0.17809</v>
+        <v>1.00255</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>92.42</v>
+        <v>67.39</v>
       </c>
       <c r="D251" t="n">
-        <v>106.42</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E251" t="n">
-        <v>15.15</v>
+        <v>38.64</v>
       </c>
       <c r="F251" t="n">
-        <v>0.38316</v>
+        <v>0.55682</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>23.77</v>
+        <v>65.16</v>
       </c>
       <c r="D252" t="n">
-        <v>29.05</v>
+        <v>114.33</v>
       </c>
       <c r="E252" t="n">
-        <v>22.21</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="F252" t="n">
-        <v>0.28593</v>
+        <v>2.2454</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>87.15000000000001</v>
+        <v>24.77</v>
       </c>
       <c r="D253" t="n">
-        <v>156.62</v>
+        <v>36.96</v>
       </c>
       <c r="E253" t="n">
-        <v>79.70999999999999</v>
+        <v>49.21</v>
       </c>
       <c r="F253" t="n">
-        <v>0.27415</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>24.24</v>
+        <v>273.5</v>
       </c>
       <c r="D254" t="n">
-        <v>30.43</v>
+        <v>349.39</v>
       </c>
       <c r="E254" t="n">
-        <v>25.56</v>
+        <v>27.75</v>
       </c>
       <c r="F254" t="n">
-        <v>0.0053</v>
+        <v>-1.43004</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>243.35</v>
+        <v>204.77</v>
       </c>
       <c r="D255" t="n">
-        <v>365</v>
+        <v>274.99</v>
       </c>
       <c r="E255" t="n">
-        <v>49.99</v>
+        <v>34.29</v>
       </c>
       <c r="F255" t="n">
-        <v>3.17586</v>
+        <v>0.55032</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>121.84</v>
+        <v>273.14</v>
       </c>
       <c r="D256" t="n">
-        <v>159.63</v>
+        <v>345.71</v>
       </c>
       <c r="E256" t="n">
-        <v>31.02</v>
+        <v>26.57</v>
       </c>
       <c r="F256" t="n">
-        <v>1.3023</v>
+        <v>-1.43948</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>14</v>
+        <v>29.16</v>
       </c>
       <c r="D257" t="n">
-        <v>14.8</v>
+        <v>39.94</v>
       </c>
       <c r="E257" t="n">
-        <v>5.71</v>
+        <v>36.97</v>
       </c>
       <c r="F257" t="n">
-        <v>0.00993</v>
+        <v>0.01199</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>163.37</v>
+        <v>119.51</v>
       </c>
       <c r="D258" t="n">
-        <v>258.82</v>
+        <v>257.05</v>
       </c>
       <c r="E258" t="n">
-        <v>58.43</v>
+        <v>115.09</v>
       </c>
       <c r="F258" t="n">
-        <v>0.25232</v>
+        <v>12.83332</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>3.93</v>
+        <v>166</v>
       </c>
       <c r="D259" t="n">
-        <v>5.83</v>
+        <v>407.02</v>
       </c>
       <c r="E259" t="n">
-        <v>48.35</v>
+        <v>145.19</v>
       </c>
       <c r="F259" t="n">
-        <v>0.11582</v>
+        <v>4.5493</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>157.12</v>
+        <v>12.96</v>
       </c>
       <c r="D260" t="n">
-        <v>262.48</v>
+        <v>16.66</v>
       </c>
       <c r="E260" t="n">
-        <v>67.06</v>
+        <v>28.55</v>
       </c>
       <c r="F260" t="n">
-        <v>2.10792</v>
+        <v>-0.0515</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>72.90000000000001</v>
+        <v>26.41</v>
       </c>
       <c r="D261" t="n">
-        <v>95.88</v>
+        <v>41.02</v>
       </c>
       <c r="E261" t="n">
-        <v>31.52</v>
+        <v>55.32</v>
       </c>
       <c r="F261" t="n">
-        <v>0.94208</v>
+        <v>1.68935</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>182.65</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D262" t="n">
-        <v>350.78</v>
+        <v>21.9</v>
       </c>
       <c r="E262" t="n">
-        <v>92.05</v>
+        <v>154.36</v>
       </c>
       <c r="F262" t="n">
-        <v>5.93408</v>
+        <v>0.80893</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>61.37</v>
+        <v>22.61</v>
       </c>
       <c r="D263" t="n">
-        <v>80.53</v>
+        <v>55.41</v>
       </c>
       <c r="E263" t="n">
-        <v>31.22</v>
+        <v>145.07</v>
       </c>
       <c r="F263" t="n">
-        <v>0.10797</v>
+        <v>1.53437</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>153.68</v>
+        <v>97.52</v>
       </c>
       <c r="D264" t="n">
-        <v>171.67</v>
+        <v>132.88</v>
       </c>
       <c r="E264" t="n">
-        <v>11.71</v>
+        <v>36.26</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.33974</v>
+        <v>2.17585</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>213.28</v>
+        <v>59.66</v>
       </c>
       <c r="D265" t="n">
-        <v>286.11</v>
+        <v>84.11</v>
       </c>
       <c r="E265" t="n">
-        <v>34.15</v>
+        <v>40.98</v>
       </c>
       <c r="F265" t="n">
-        <v>0.03034</v>
+        <v>1.58777</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>41.53</v>
+        <v>57.45</v>
       </c>
       <c r="D266" t="n">
-        <v>56.9</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="E266" t="n">
-        <v>37.01</v>
+        <v>22.79</v>
       </c>
       <c r="F266" t="n">
-        <v>0.18075</v>
+        <v>-0.19886</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>110.24</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D267" t="n">
-        <v>150.27</v>
+        <v>100.36</v>
       </c>
       <c r="E267" t="n">
-        <v>36.31</v>
+        <v>11.5</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.85395</v>
+        <v>0.11228</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>284.93</v>
+        <v>69.3</v>
       </c>
       <c r="D268" t="n">
-        <v>407.75</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E268" t="n">
-        <v>43.11</v>
+        <v>20.55</v>
       </c>
       <c r="F268" t="n">
-        <v>0.7672099999999999</v>
+        <v>0.20672</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>20.72</v>
+        <v>28.35</v>
       </c>
       <c r="D269" t="n">
-        <v>24.64</v>
+        <v>38.72</v>
       </c>
       <c r="E269" t="n">
-        <v>18.92</v>
+        <v>36.58</v>
       </c>
       <c r="F269" t="n">
-        <v>0.0299</v>
+        <v>0.29357</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>87.98</v>
+        <v>31.8</v>
       </c>
       <c r="D270" t="n">
-        <v>108.03</v>
+        <v>69.41</v>
       </c>
       <c r="E270" t="n">
-        <v>22.79</v>
+        <v>118.27</v>
       </c>
       <c r="F270" t="n">
-        <v>0.75809</v>
+        <v>0.31551</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SPG-PJ</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>52.49</v>
+        <v>279.73</v>
       </c>
       <c r="D271" t="n">
-        <v>56.12</v>
+        <v>411.49</v>
       </c>
       <c r="E271" t="n">
-        <v>6.92</v>
+        <v>47.1</v>
       </c>
       <c r="F271" t="n">
-        <v>0.0173</v>
+        <v>3.73943</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>117.67</v>
+        <v>92.42</v>
       </c>
       <c r="D272" t="n">
-        <v>222.29</v>
+        <v>108.59</v>
       </c>
       <c r="E272" t="n">
-        <v>88.91</v>
+        <v>17.5</v>
       </c>
       <c r="F272" t="n">
-        <v>0.07779</v>
+        <v>0.1877</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,22 +6964,22 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>67.7</v>
+        <v>91.37</v>
       </c>
       <c r="D273" t="n">
-        <v>98.22</v>
+        <v>120.93</v>
       </c>
       <c r="E273" t="n">
-        <v>45.08</v>
+        <v>32.35</v>
       </c>
       <c r="F273" t="n">
-        <v>0.47423</v>
+        <v>-0.10485</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>289.16</v>
+        <v>243.35</v>
       </c>
       <c r="D274" t="n">
-        <v>417.09</v>
+        <v>355.2</v>
       </c>
       <c r="E274" t="n">
-        <v>44.24</v>
+        <v>45.96</v>
       </c>
       <c r="F274" t="n">
-        <v>0.82443</v>
+        <v>0.55648</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>106.41</v>
+        <v>182.65</v>
       </c>
       <c r="D275" t="n">
-        <v>117.55</v>
+        <v>341.79</v>
       </c>
       <c r="E275" t="n">
-        <v>10.47</v>
+        <v>87.13</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.56235</v>
+        <v>4.40399</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>33.63</v>
+        <v>10.65</v>
       </c>
       <c r="D276" t="n">
-        <v>43.87</v>
+        <v>14.74</v>
       </c>
       <c r="E276" t="n">
-        <v>30.45</v>
+        <v>38.4</v>
       </c>
       <c r="F276" t="n">
-        <v>0.08643000000000001</v>
+        <v>0.05009</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,22 +7060,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>285.27</v>
+        <v>39.84</v>
       </c>
       <c r="D277" t="n">
-        <v>377.97</v>
+        <v>58.53</v>
       </c>
       <c r="E277" t="n">
-        <v>32.5</v>
+        <v>46.91</v>
       </c>
       <c r="F277" t="n">
-        <v>2.23594</v>
+        <v>-0.08142000000000001</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7084,160 +7084,1168 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>125.78</v>
+        <v>61.37</v>
       </c>
       <c r="D278" t="n">
-        <v>143.79</v>
+        <v>80.23</v>
       </c>
       <c r="E278" t="n">
-        <v>14.32</v>
+        <v>30.73</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.04365</v>
+        <v>-0.09644999999999999</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>17.13</v>
+        <v>284.93</v>
       </c>
       <c r="D279" t="n">
-        <v>43.01</v>
+        <v>412.56</v>
       </c>
       <c r="E279" t="n">
-        <v>151.08</v>
+        <v>44.79</v>
       </c>
       <c r="F279" t="n">
-        <v>0.30712</v>
+        <v>0.67323</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>27.55</v>
+        <v>33.63</v>
       </c>
       <c r="D280" t="n">
-        <v>33.78</v>
+        <v>43.55</v>
       </c>
       <c r="E280" t="n">
-        <v>22.61</v>
+        <v>29.5</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.15662</v>
+        <v>-0.00236</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>FMX</t>
+          <t>AXSM</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>106.96</v>
+        <v>156.35</v>
       </c>
       <c r="D281" t="n">
-        <v>121.6</v>
+        <v>216.58</v>
       </c>
       <c r="E281" t="n">
-        <v>13.69</v>
+        <v>38.52</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.38552</v>
+        <v>1.76572</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>QSR</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>95.48</v>
+        <v>71.42</v>
       </c>
       <c r="D282" t="n">
-        <v>111.5</v>
+        <v>78.89</v>
       </c>
       <c r="E282" t="n">
-        <v>16.78</v>
+        <v>10.46</v>
       </c>
       <c r="F282" t="n">
-        <v>0.0456</v>
+        <v>-0.24064</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>63.78</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D283" t="n">
-        <v>69.81</v>
+        <v>116.9</v>
       </c>
       <c r="E283" t="n">
-        <v>9.449999999999999</v>
+        <v>34.35</v>
       </c>
       <c r="F283" t="n">
-        <v>0.43847</v>
+        <v>0.85321</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="D284" t="n">
+        <v>375.28</v>
+      </c>
+      <c r="E284" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="F284" t="n">
+        <v>-0.74265</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>NMR</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="D285" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="E285" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0.17999</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ZION</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="D286" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="E286" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="F286" t="n">
+        <v>-0.03903</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>525.72</v>
+      </c>
+      <c r="D287" t="n">
+        <v>665.6</v>
+      </c>
+      <c r="E287" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="F287" t="n">
+        <v>22.11172</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>CINF</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>153.68</v>
+      </c>
+      <c r="D288" t="n">
+        <v>172.02</v>
+      </c>
+      <c r="E288" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="F288" t="n">
+        <v>-0.63445</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="D289" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E289" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0.09469</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>BUD</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="D290" t="n">
+        <v>79.81999999999999</v>
+      </c>
+      <c r="E290" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="F290" t="n">
+        <v>-0.43807</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>AES</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>14</v>
+      </c>
+      <c r="D291" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E291" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0.01308</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>147.02</v>
+      </c>
+      <c r="D292" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="E292" t="n">
+        <v>154.35</v>
+      </c>
+      <c r="F292" t="n">
+        <v>-2.08465</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>121.84</v>
+      </c>
+      <c r="D293" t="n">
+        <v>162.38</v>
+      </c>
+      <c r="E293" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0.05096</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>UNM</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="D294" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="E294" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.7454499999999999</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="D295" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E295" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0.07327</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>285.27</v>
+      </c>
+      <c r="D296" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="E296" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1.30077</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>202.71</v>
+      </c>
+      <c r="D297" t="n">
+        <v>258.48</v>
+      </c>
+      <c r="E297" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="F297" t="n">
+        <v>-1.41316</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>317.93</v>
+      </c>
+      <c r="D298" t="n">
+        <v>379.54</v>
+      </c>
+      <c r="E298" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F298" t="n">
+        <v>-0.71048</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>EQH</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="D299" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="E299" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0.74151</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SNX</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>157.12</v>
+      </c>
+      <c r="D300" t="n">
+        <v>261.12</v>
+      </c>
+      <c r="E300" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1.88244</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="D301" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="E301" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0.25783</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SPG-PJ</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="D302" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="E302" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0.0173</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ARCC</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="D303" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E303" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="F303" t="n">
+        <v>-0.03105</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="D304" t="n">
+        <v>108.99</v>
+      </c>
+      <c r="E304" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0.3621</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>EL</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="D305" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="E305" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F305" t="n">
+        <v>-0.14265</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="D306" t="n">
+        <v>235.38</v>
+      </c>
+      <c r="E306" t="n">
+        <v>154.75</v>
+      </c>
+      <c r="F306" t="n">
+        <v>2.36905</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>AIZ</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>213.28</v>
+      </c>
+      <c r="D307" t="n">
+        <v>283.27</v>
+      </c>
+      <c r="E307" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="F307" t="n">
+        <v>-0.5633</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>289.16</v>
+      </c>
+      <c r="D308" t="n">
+        <v>410.01</v>
+      </c>
+      <c r="E308" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="F308" t="n">
+        <v>-0.38142</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CRBG</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D309" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E309" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.45747</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>MFG</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D310" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="E310" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.16084</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ROKU</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="D311" t="n">
+        <v>157.45</v>
+      </c>
+      <c r="E311" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="F311" t="n">
+        <v>-0.08858000000000001</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>DKNG</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="D312" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="E312" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="F312" t="n">
+        <v>-0.07012</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="D313" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="E313" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="F313" t="n">
+        <v>-0.54794</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>AFG</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>125.78</v>
+      </c>
+      <c r="D314" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="E314" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="F314" t="n">
+        <v>-0.39666</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="D315" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="E315" t="n">
+        <v>153.65</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0.28998</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
           <t>ICLR</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C284" t="n">
+      <c r="C316" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="D284" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="E284" t="n">
-        <v>72.47</v>
-      </c>
-      <c r="F284" t="n">
-        <v>1.41425</v>
+      <c r="D316" t="n">
+        <v>168.93</v>
+      </c>
+      <c r="E316" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0.20101</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="D317" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="E317" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0.28252</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>NWS</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="D318" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="E318" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="F318" t="n">
+        <v>-0.24679</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>PAG</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>146.17</v>
+      </c>
+      <c r="D319" t="n">
+        <v>217.15</v>
+      </c>
+      <c r="E319" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0.01127</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>VRSN</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>241.14</v>
+      </c>
+      <c r="D320" t="n">
+        <v>298.6</v>
+      </c>
+      <c r="E320" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1.64228</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>MDGL</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>445.04</v>
+      </c>
+      <c r="D321" t="n">
+        <v>540.0599999999999</v>
+      </c>
+      <c r="E321" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="F321" t="n">
+        <v>2.20142</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>FMX</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="D322" t="n">
+        <v>121.26</v>
+      </c>
+      <c r="E322" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="F322" t="n">
+        <v>-0.80715</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>KOF</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="D323" t="n">
+        <v>112.01</v>
+      </c>
+      <c r="E323" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="F323" t="n">
+        <v>-0.19592</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>ABEV</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D324" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E324" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F324" t="n">
+        <v>0.02721</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="D325" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="E325" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="F325" t="n">
+        <v>-0.08098</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="D326" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E326" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0.22235</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F326"/>
+  <dimension ref="A1:F283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,25 +451,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2876.75</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>2965.52</v>
+        <v>86.11</v>
       </c>
       <c r="E2" t="n">
-        <v>3.09</v>
+        <v>6.92</v>
       </c>
       <c r="F2" t="n">
-        <v>-26.725</v>
+        <v>-0.96334</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>57.29</v>
+        <v>56.52</v>
       </c>
       <c r="E3" t="n">
-        <v>5.45</v>
+        <v>4.03</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.33941</v>
+        <v>-0.09851</v>
       </c>
     </row>
     <row r="4">
@@ -511,109 +511,109 @@
         <v>38.22</v>
       </c>
       <c r="D4" t="n">
-        <v>41.6</v>
+        <v>42.77</v>
       </c>
       <c r="E4" t="n">
-        <v>8.84</v>
+        <v>11.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.17365</v>
+        <v>0.1714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>ESLT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.87</v>
+        <v>700.51</v>
       </c>
       <c r="D5" t="n">
-        <v>21.62</v>
+        <v>731.75</v>
       </c>
       <c r="E5" t="n">
-        <v>20.98</v>
+        <v>4.46</v>
       </c>
       <c r="F5" t="n">
-        <v>0.65938</v>
+        <v>-1.9792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>102.63</v>
+        <v>17.87</v>
       </c>
       <c r="D6" t="n">
-        <v>109.08</v>
+        <v>21.44</v>
       </c>
       <c r="E6" t="n">
-        <v>6.28</v>
+        <v>19.98</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.22351</v>
+        <v>0.7442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13.03</v>
+        <v>102.63</v>
       </c>
       <c r="D7" t="n">
-        <v>14.97</v>
+        <v>108.09</v>
       </c>
       <c r="E7" t="n">
-        <v>14.89</v>
+        <v>5.32</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01791</v>
+        <v>0.01302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.67</v>
+        <v>13.03</v>
       </c>
       <c r="D8" t="n">
-        <v>7.03</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>23.99</v>
+        <v>15.12</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1648</v>
+        <v>0.09046</v>
       </c>
     </row>
     <row r="9">
@@ -631,67 +631,67 @@
         <v>298.59</v>
       </c>
       <c r="D9" t="n">
-        <v>334.24</v>
+        <v>331.46</v>
       </c>
       <c r="E9" t="n">
-        <v>11.94</v>
+        <v>11.01</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.56324</v>
+        <v>1.09993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>141.63</v>
+        <v>5.67</v>
       </c>
       <c r="D10" t="n">
-        <v>157.31</v>
+        <v>6.83</v>
       </c>
       <c r="E10" t="n">
-        <v>11.07</v>
+        <v>20.46</v>
       </c>
       <c r="F10" t="n">
-        <v>1.11386</v>
+        <v>0.15101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.46</v>
+        <v>141.63</v>
       </c>
       <c r="D11" t="n">
-        <v>5.22</v>
+        <v>157.63</v>
       </c>
       <c r="E11" t="n">
-        <v>17.04</v>
+        <v>11.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08513999999999999</v>
+        <v>1.69159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.98</v>
+        <v>7.17</v>
       </c>
       <c r="D12" t="n">
-        <v>3.54</v>
+        <v>8.26</v>
       </c>
       <c r="E12" t="n">
-        <v>18.79</v>
+        <v>15.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06816999999999999</v>
+        <v>0.13953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12.43</v>
+        <v>4.46</v>
       </c>
       <c r="D13" t="n">
-        <v>18.42</v>
+        <v>5.24</v>
       </c>
       <c r="E13" t="n">
-        <v>48.19</v>
+        <v>17.49</v>
       </c>
       <c r="F13" t="n">
-        <v>0.97816</v>
+        <v>0.08273999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.17</v>
+        <v>2.98</v>
       </c>
       <c r="D14" t="n">
-        <v>8.23</v>
+        <v>3.5</v>
       </c>
       <c r="E14" t="n">
-        <v>14.78</v>
+        <v>17.45</v>
       </c>
       <c r="F14" t="n">
-        <v>0.13527</v>
+        <v>0.06834</v>
       </c>
     </row>
     <row r="15">
@@ -781,37 +781,37 @@
         <v>5.88</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03212</v>
+        <v>0.03859</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.28</v>
+        <v>12.43</v>
       </c>
       <c r="D16" t="n">
-        <v>19.12</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="n">
-        <v>10.65</v>
+        <v>39.98</v>
       </c>
       <c r="F16" t="n">
-        <v>0.22309</v>
+        <v>0.8716699999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,190 +820,190 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>98.45</v>
+        <v>17.28</v>
       </c>
       <c r="D17" t="n">
-        <v>122.3</v>
+        <v>19.03</v>
       </c>
       <c r="E17" t="n">
-        <v>24.23</v>
+        <v>10.13</v>
       </c>
       <c r="F17" t="n">
-        <v>2.28707</v>
+        <v>0.20851</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35.54</v>
+        <v>98.45</v>
       </c>
       <c r="D18" t="n">
-        <v>51.29</v>
+        <v>123.79</v>
       </c>
       <c r="E18" t="n">
-        <v>44.32</v>
+        <v>25.74</v>
       </c>
       <c r="F18" t="n">
-        <v>1.98244</v>
+        <v>1.77497</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>123.39</v>
+        <v>2.78</v>
       </c>
       <c r="D19" t="n">
-        <v>137.82</v>
+        <v>3.02</v>
       </c>
       <c r="E19" t="n">
-        <v>11.69</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.38289</v>
+        <v>0.02557</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63.54</v>
+        <v>52.62</v>
       </c>
       <c r="D20" t="n">
-        <v>70.34</v>
+        <v>56.64</v>
       </c>
       <c r="E20" t="n">
-        <v>10.7</v>
+        <v>7.64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02608</v>
+        <v>0.35581</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>155.62</v>
+        <v>35.54</v>
       </c>
       <c r="D21" t="n">
-        <v>163.78</v>
+        <v>50.24</v>
       </c>
       <c r="E21" t="n">
-        <v>5.24</v>
+        <v>41.36</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.00319</v>
+        <v>2.3384</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60.35</v>
+        <v>123.39</v>
       </c>
       <c r="D22" t="n">
-        <v>97.42</v>
+        <v>133.73</v>
       </c>
       <c r="E22" t="n">
-        <v>61.43</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.96052</v>
+        <v>1.10452</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FIGR</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.91</v>
+        <v>63.54</v>
       </c>
       <c r="D23" t="n">
-        <v>35.65</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>43.12</v>
+        <v>12.86</v>
       </c>
       <c r="F23" t="n">
-        <v>0.36343</v>
+        <v>0.51027</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.81</v>
+        <v>340.65</v>
       </c>
       <c r="D24" t="n">
-        <v>10.87</v>
+        <v>371.63</v>
       </c>
       <c r="E24" t="n">
-        <v>39.18</v>
+        <v>9.09</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04366</v>
+        <v>-1.20992</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1012,22 +1012,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>205.48</v>
+        <v>7.81</v>
       </c>
       <c r="D25" t="n">
-        <v>249.99</v>
+        <v>11.01</v>
       </c>
       <c r="E25" t="n">
-        <v>21.66</v>
+        <v>40.97</v>
       </c>
       <c r="F25" t="n">
-        <v>1.24005</v>
+        <v>0.11474</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29.31</v>
+        <v>41.55</v>
       </c>
       <c r="D26" t="n">
-        <v>43.17</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>47.29</v>
+        <v>65.7</v>
       </c>
       <c r="F26" t="n">
-        <v>0.92178</v>
+        <v>0.36109</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,88 +1060,88 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>298.32</v>
+        <v>48.68</v>
       </c>
       <c r="D27" t="n">
-        <v>358.97</v>
+        <v>61.1</v>
       </c>
       <c r="E27" t="n">
-        <v>20.33</v>
+        <v>25.51</v>
       </c>
       <c r="F27" t="n">
-        <v>3.38165</v>
+        <v>0.47155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41.55</v>
+        <v>11.03</v>
       </c>
       <c r="D28" t="n">
-        <v>62.21</v>
+        <v>12.84</v>
       </c>
       <c r="E28" t="n">
-        <v>49.72</v>
+        <v>16.41</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.39774</v>
+        <v>0.01194</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.28</v>
+        <v>146.38</v>
       </c>
       <c r="D29" t="n">
-        <v>28.1</v>
+        <v>215.67</v>
       </c>
       <c r="E29" t="n">
-        <v>11.16</v>
+        <v>47.34</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01151</v>
+        <v>0.62778</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.03</v>
+        <v>332.02</v>
       </c>
       <c r="D30" t="n">
-        <v>12.72</v>
+        <v>377.16</v>
       </c>
       <c r="E30" t="n">
-        <v>15.32</v>
+        <v>13.6</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.09100999999999999</v>
+        <v>0.27114</v>
       </c>
     </row>
     <row r="31">
@@ -1159,19 +1159,19 @@
         <v>179.43</v>
       </c>
       <c r="D31" t="n">
-        <v>193.72</v>
+        <v>190.13</v>
       </c>
       <c r="E31" t="n">
-        <v>7.96</v>
+        <v>5.96</v>
       </c>
       <c r="F31" t="n">
-        <v>0.57955</v>
+        <v>0.43388</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1180,310 +1180,310 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>332.02</v>
+        <v>27.14</v>
       </c>
       <c r="D32" t="n">
-        <v>377.94</v>
+        <v>31.56</v>
       </c>
       <c r="E32" t="n">
-        <v>13.83</v>
+        <v>16.29</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.21821</v>
+        <v>-0.13487</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.14</v>
+        <v>205.77</v>
       </c>
       <c r="D33" t="n">
-        <v>31.52</v>
+        <v>248.37</v>
       </c>
       <c r="E33" t="n">
-        <v>16.14</v>
+        <v>20.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.35749</v>
+        <v>3.26641</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>146.38</v>
+        <v>25.99</v>
       </c>
       <c r="D34" t="n">
-        <v>218.28</v>
+        <v>37.63</v>
       </c>
       <c r="E34" t="n">
-        <v>49.12</v>
+        <v>44.79</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00649</v>
+        <v>0.74041</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>205.77</v>
+        <v>440.76</v>
       </c>
       <c r="D35" t="n">
-        <v>249.09</v>
+        <v>636.4</v>
       </c>
       <c r="E35" t="n">
-        <v>21.05</v>
+        <v>44.39</v>
       </c>
       <c r="F35" t="n">
-        <v>2.72288</v>
+        <v>4.10788</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>25.99</v>
+        <v>89.2</v>
       </c>
       <c r="D36" t="n">
-        <v>38.71</v>
+        <v>124.19</v>
       </c>
       <c r="E36" t="n">
-        <v>48.94</v>
+        <v>39.23</v>
       </c>
       <c r="F36" t="n">
-        <v>0.54466</v>
+        <v>0.38279</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>440.76</v>
+        <v>103.45</v>
       </c>
       <c r="D37" t="n">
-        <v>637.16</v>
+        <v>150.02</v>
       </c>
       <c r="E37" t="n">
-        <v>44.56</v>
+        <v>45.02</v>
       </c>
       <c r="F37" t="n">
-        <v>1.42976</v>
+        <v>1.07197</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>103.45</v>
+        <v>198.14</v>
       </c>
       <c r="D38" t="n">
-        <v>149.67</v>
+        <v>263.09</v>
       </c>
       <c r="E38" t="n">
-        <v>44.68</v>
+        <v>32.78</v>
       </c>
       <c r="F38" t="n">
-        <v>1.89428</v>
+        <v>2.17265</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>67.59999999999999</v>
+        <v>35.49</v>
       </c>
       <c r="D39" t="n">
-        <v>80.31999999999999</v>
+        <v>41.9</v>
       </c>
       <c r="E39" t="n">
-        <v>18.82</v>
+        <v>18.06</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.45827</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>198.14</v>
+        <v>41.44</v>
       </c>
       <c r="D40" t="n">
-        <v>261.67</v>
+        <v>45.37</v>
       </c>
       <c r="E40" t="n">
-        <v>32.06</v>
+        <v>9.48</v>
       </c>
       <c r="F40" t="n">
-        <v>2.64766</v>
+        <v>0.55671</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>41.44</v>
+        <v>510.39</v>
       </c>
       <c r="D41" t="n">
-        <v>45.25</v>
+        <v>643.33</v>
       </c>
       <c r="E41" t="n">
-        <v>9.19</v>
+        <v>26.05</v>
       </c>
       <c r="F41" t="n">
-        <v>0.51531</v>
+        <v>5.93092</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>BSBR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>510.39</v>
+        <v>5.04</v>
       </c>
       <c r="D42" t="n">
-        <v>652.39</v>
+        <v>5.86</v>
       </c>
       <c r="E42" t="n">
-        <v>27.82</v>
+        <v>16.27</v>
       </c>
       <c r="F42" t="n">
-        <v>4.4847</v>
+        <v>0.04462</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BSBR</t>
+          <t>PSNYW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5.04</v>
+        <v>2.2</v>
       </c>
       <c r="D43" t="n">
-        <v>5.95</v>
+        <v>4.68</v>
       </c>
       <c r="E43" t="n">
-        <v>18.06</v>
+        <v>112.73</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05247</v>
+        <v>-0.01815</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>176.25</v>
+        <v>162.11</v>
       </c>
       <c r="D44" t="n">
-        <v>249.59</v>
+        <v>177.71</v>
       </c>
       <c r="E44" t="n">
-        <v>41.61</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.95658</v>
+        <v>0.54084</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>162.11</v>
+        <v>24.36</v>
       </c>
       <c r="D45" t="n">
-        <v>176.94</v>
+        <v>33.92</v>
       </c>
       <c r="E45" t="n">
-        <v>9.15</v>
+        <v>39.24</v>
       </c>
       <c r="F45" t="n">
-        <v>0.35777</v>
+        <v>0.50814</v>
       </c>
     </row>
     <row r="46">
@@ -1519,91 +1519,91 @@
         <v>40.48</v>
       </c>
       <c r="D46" t="n">
-        <v>44.64</v>
+        <v>45.96</v>
       </c>
       <c r="E46" t="n">
-        <v>10.28</v>
+        <v>13.54</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1977</v>
+        <v>0.24459</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20.87</v>
+        <v>53.57</v>
       </c>
       <c r="D47" t="n">
-        <v>23.47</v>
+        <v>71.87</v>
       </c>
       <c r="E47" t="n">
-        <v>12.46</v>
+        <v>34.16</v>
       </c>
       <c r="F47" t="n">
-        <v>0.00191</v>
+        <v>0.94957</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>24.36</v>
+        <v>45.57</v>
       </c>
       <c r="D48" t="n">
-        <v>33.27</v>
+        <v>56.66</v>
       </c>
       <c r="E48" t="n">
-        <v>36.58</v>
+        <v>24.34</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5132100000000001</v>
+        <v>0.49648</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>31.45</v>
+        <v>41.99</v>
       </c>
       <c r="D49" t="n">
-        <v>36.65</v>
+        <v>51.45</v>
       </c>
       <c r="E49" t="n">
-        <v>16.53</v>
+        <v>22.53</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.014</v>
+        <v>0.50723</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>110.99</v>
+        <v>40.25</v>
       </c>
       <c r="D50" t="n">
-        <v>131.83</v>
+        <v>51.33</v>
       </c>
       <c r="E50" t="n">
-        <v>18.78</v>
+        <v>27.53</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.18184</v>
+        <v>0.9265099999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>53.57</v>
+        <v>171.96</v>
       </c>
       <c r="D51" t="n">
-        <v>68.72</v>
+        <v>211.53</v>
       </c>
       <c r="E51" t="n">
-        <v>28.28</v>
+        <v>23.01</v>
       </c>
       <c r="F51" t="n">
-        <v>0.74953</v>
+        <v>1.93053</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>31.87</v>
+        <v>104.89</v>
       </c>
       <c r="D52" t="n">
-        <v>45.03</v>
+        <v>121.76</v>
       </c>
       <c r="E52" t="n">
-        <v>41.29</v>
+        <v>16.08</v>
       </c>
       <c r="F52" t="n">
-        <v>0.89874</v>
+        <v>1.74063</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,22 +1684,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17.93</v>
+        <v>47.94</v>
       </c>
       <c r="D53" t="n">
-        <v>23.76</v>
+        <v>63.52</v>
       </c>
       <c r="E53" t="n">
-        <v>32.52</v>
+        <v>32.5</v>
       </c>
       <c r="F53" t="n">
-        <v>0.28866</v>
+        <v>0.82646</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>171.96</v>
+        <v>38.92</v>
       </c>
       <c r="D54" t="n">
-        <v>205.72</v>
+        <v>51.55</v>
       </c>
       <c r="E54" t="n">
-        <v>19.63</v>
+        <v>32.45</v>
       </c>
       <c r="F54" t="n">
-        <v>1.19691</v>
+        <v>0.30504</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>47.94</v>
+        <v>110.99</v>
       </c>
       <c r="D55" t="n">
-        <v>61.78</v>
+        <v>135.35</v>
       </c>
       <c r="E55" t="n">
-        <v>28.87</v>
+        <v>21.95</v>
       </c>
       <c r="F55" t="n">
-        <v>0.67977</v>
+        <v>0.19167</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38.92</v>
+        <v>31.87</v>
       </c>
       <c r="D56" t="n">
-        <v>50.32</v>
+        <v>47.41</v>
       </c>
       <c r="E56" t="n">
-        <v>29.29</v>
+        <v>48.76</v>
       </c>
       <c r="F56" t="n">
-        <v>0.31609</v>
+        <v>1.0579</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13.01</v>
+        <v>14.49</v>
       </c>
       <c r="D57" t="n">
-        <v>17.53</v>
+        <v>19.57</v>
       </c>
       <c r="E57" t="n">
-        <v>34.74</v>
+        <v>35.06</v>
       </c>
       <c r="F57" t="n">
-        <v>0.37919</v>
+        <v>0.58352</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>104.89</v>
+        <v>165.69</v>
       </c>
       <c r="D58" t="n">
-        <v>121.23</v>
+        <v>217.77</v>
       </c>
       <c r="E58" t="n">
-        <v>15.58</v>
+        <v>31.43</v>
       </c>
       <c r="F58" t="n">
-        <v>2.10701</v>
+        <v>3.21866</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,16 +1828,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.49</v>
+        <v>51.98</v>
       </c>
       <c r="D59" t="n">
-        <v>19.07</v>
+        <v>66.97</v>
       </c>
       <c r="E59" t="n">
-        <v>31.61</v>
+        <v>28.84</v>
       </c>
       <c r="F59" t="n">
-        <v>0.58389</v>
+        <v>0.22746</v>
       </c>
     </row>
     <row r="60">
@@ -1855,19 +1855,19 @@
         <v>15.99</v>
       </c>
       <c r="D60" t="n">
-        <v>21.15</v>
+        <v>21.77</v>
       </c>
       <c r="E60" t="n">
-        <v>32.27</v>
+        <v>36.15</v>
       </c>
       <c r="F60" t="n">
-        <v>0.63574</v>
+        <v>0.6551900000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>40.25</v>
+        <v>36.15</v>
       </c>
       <c r="D61" t="n">
-        <v>49.73</v>
+        <v>46.96</v>
       </c>
       <c r="E61" t="n">
-        <v>23.55</v>
+        <v>29.9</v>
       </c>
       <c r="F61" t="n">
-        <v>0.77667</v>
+        <v>0.88425</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36.15</v>
+        <v>17.93</v>
       </c>
       <c r="D62" t="n">
-        <v>45.93</v>
+        <v>24.49</v>
       </c>
       <c r="E62" t="n">
-        <v>27.05</v>
+        <v>36.59</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8426</v>
+        <v>0.34403</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>45.57</v>
+        <v>74.8</v>
       </c>
       <c r="D63" t="n">
-        <v>55.4</v>
+        <v>93.12</v>
       </c>
       <c r="E63" t="n">
-        <v>21.57</v>
+        <v>24.49</v>
       </c>
       <c r="F63" t="n">
-        <v>0.48559</v>
+        <v>1.07146</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>165.69</v>
+        <v>13.01</v>
       </c>
       <c r="D64" t="n">
-        <v>212.17</v>
+        <v>17.68</v>
       </c>
       <c r="E64" t="n">
-        <v>28.05</v>
+        <v>35.9</v>
       </c>
       <c r="F64" t="n">
-        <v>3.14062</v>
+        <v>0.39546</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>103.22</v>
+        <v>52.58</v>
       </c>
       <c r="D65" t="n">
-        <v>136.67</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>32.41</v>
+        <v>24.44</v>
       </c>
       <c r="F65" t="n">
-        <v>2.02987</v>
+        <v>0.00565</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>74.8</v>
+        <v>103.22</v>
       </c>
       <c r="D66" t="n">
-        <v>91.14</v>
+        <v>141.22</v>
       </c>
       <c r="E66" t="n">
-        <v>21.84</v>
+        <v>36.81</v>
       </c>
       <c r="F66" t="n">
-        <v>1.02845</v>
+        <v>2.28322</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,16 +2020,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>51.98</v>
+        <v>17.26</v>
       </c>
       <c r="D67" t="n">
-        <v>65.36</v>
+        <v>19.84</v>
       </c>
       <c r="E67" t="n">
-        <v>25.74</v>
+        <v>14.95</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.02228</v>
+        <v>0.16265</v>
       </c>
     </row>
     <row r="68">
@@ -2047,67 +2047,67 @@
         <v>20.48</v>
       </c>
       <c r="D68" t="n">
-        <v>26.51</v>
+        <v>26.72</v>
       </c>
       <c r="E68" t="n">
-        <v>29.44</v>
+        <v>30.47</v>
       </c>
       <c r="F68" t="n">
-        <v>0.19225</v>
+        <v>0.32346</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>41.99</v>
+        <v>124.44</v>
       </c>
       <c r="D69" t="n">
-        <v>51.29</v>
+        <v>193.4</v>
       </c>
       <c r="E69" t="n">
-        <v>22.15</v>
+        <v>55.42</v>
       </c>
       <c r="F69" t="n">
-        <v>0.38063</v>
+        <v>2.33628</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17.26</v>
+        <v>62.05</v>
       </c>
       <c r="D70" t="n">
-        <v>19.97</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>15.7</v>
+        <v>31.01</v>
       </c>
       <c r="F70" t="n">
-        <v>0.16925</v>
+        <v>-0.26747</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2116,22 +2116,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>13.31</v>
+        <v>38.73</v>
       </c>
       <c r="D71" t="n">
-        <v>25.76</v>
+        <v>63.28</v>
       </c>
       <c r="E71" t="n">
-        <v>93.54000000000001</v>
+        <v>63.39</v>
       </c>
       <c r="F71" t="n">
-        <v>0.71191</v>
+        <v>0.3855</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>124.44</v>
+        <v>13.31</v>
       </c>
       <c r="D72" t="n">
-        <v>195</v>
+        <v>23.6</v>
       </c>
       <c r="E72" t="n">
-        <v>56.7</v>
+        <v>77.31</v>
       </c>
       <c r="F72" t="n">
-        <v>0.72958</v>
+        <v>0.58601</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,22 +2164,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>167.73</v>
+        <v>55.53</v>
       </c>
       <c r="D73" t="n">
-        <v>182.9</v>
+        <v>62.25</v>
       </c>
       <c r="E73" t="n">
-        <v>9.039999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.58001</v>
+        <v>0.75354</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2188,352 +2188,352 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>62.05</v>
+        <v>13.43</v>
       </c>
       <c r="D74" t="n">
-        <v>81.22</v>
+        <v>15.03</v>
       </c>
       <c r="E74" t="n">
-        <v>30.89</v>
+        <v>11.91</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.5008899999999999</v>
+        <v>0.08283</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38.73</v>
+        <v>7.67</v>
       </c>
       <c r="D75" t="n">
-        <v>64.09999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="E75" t="n">
-        <v>65.5</v>
+        <v>20.34</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.10866</v>
+        <v>0.15642</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>13.43</v>
+        <v>136.06</v>
       </c>
       <c r="D76" t="n">
-        <v>15.26</v>
+        <v>169.32</v>
       </c>
       <c r="E76" t="n">
-        <v>13.63</v>
+        <v>24.45</v>
       </c>
       <c r="F76" t="n">
-        <v>0.08839</v>
+        <v>1.98435</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>55.53</v>
+        <v>76.53</v>
       </c>
       <c r="D77" t="n">
-        <v>60.91</v>
+        <v>98.95</v>
       </c>
       <c r="E77" t="n">
-        <v>9.69</v>
+        <v>29.3</v>
       </c>
       <c r="F77" t="n">
-        <v>0.22128</v>
+        <v>1.63317</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7.67</v>
+        <v>31.03</v>
       </c>
       <c r="D78" t="n">
-        <v>9.199999999999999</v>
+        <v>45.75</v>
       </c>
       <c r="E78" t="n">
-        <v>19.95</v>
+        <v>47.44</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1771</v>
+        <v>0.94193</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>122.91</v>
+        <v>18.94</v>
       </c>
       <c r="D79" t="n">
-        <v>157.75</v>
+        <v>23.98</v>
       </c>
       <c r="E79" t="n">
-        <v>28.35</v>
+        <v>26.61</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.37771</v>
+        <v>0.15742</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>135.44</v>
+        <v>56.4</v>
       </c>
       <c r="D80" t="n">
-        <v>174.39</v>
+        <v>79.48</v>
       </c>
       <c r="E80" t="n">
-        <v>28.76</v>
+        <v>40.92</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.62645</v>
+        <v>2.00392</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>218.58</v>
+        <v>82.31</v>
       </c>
       <c r="D81" t="n">
-        <v>280.46</v>
+        <v>129.6</v>
       </c>
       <c r="E81" t="n">
-        <v>28.31</v>
+        <v>57.45</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2297</v>
+        <v>2.83088</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>136.06</v>
+        <v>44.39</v>
       </c>
       <c r="D82" t="n">
-        <v>165.08</v>
+        <v>60.34</v>
       </c>
       <c r="E82" t="n">
-        <v>21.33</v>
+        <v>35.93</v>
       </c>
       <c r="F82" t="n">
-        <v>1.65744</v>
+        <v>0.25495</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>76.53</v>
+        <v>42.46</v>
       </c>
       <c r="D83" t="n">
-        <v>96.45</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>26.03</v>
+        <v>69.22</v>
       </c>
       <c r="F83" t="n">
-        <v>1.45245</v>
+        <v>1.88023</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>18.94</v>
+        <v>59.71</v>
       </c>
       <c r="D84" t="n">
-        <v>23.74</v>
+        <v>80.06</v>
       </c>
       <c r="E84" t="n">
-        <v>25.34</v>
+        <v>34.08</v>
       </c>
       <c r="F84" t="n">
-        <v>0.19609</v>
+        <v>1.2886</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>31.03</v>
+        <v>166.5</v>
       </c>
       <c r="D85" t="n">
-        <v>44.54</v>
+        <v>195.47</v>
       </c>
       <c r="E85" t="n">
-        <v>43.54</v>
+        <v>17.4</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9863499999999999</v>
+        <v>1.03418</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>39.54</v>
+        <v>107.27</v>
       </c>
       <c r="D86" t="n">
-        <v>51.41</v>
+        <v>172.56</v>
       </c>
       <c r="E86" t="n">
-        <v>30.02</v>
+        <v>60.87</v>
       </c>
       <c r="F86" t="n">
-        <v>0.11249</v>
+        <v>-0.66867</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>82.31</v>
+        <v>136.68</v>
       </c>
       <c r="D87" t="n">
-        <v>136.94</v>
+        <v>156.99</v>
       </c>
       <c r="E87" t="n">
-        <v>66.37</v>
+        <v>14.86</v>
       </c>
       <c r="F87" t="n">
-        <v>3.45518</v>
+        <v>-0.72946</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>56.4</v>
+        <v>352.83</v>
       </c>
       <c r="D88" t="n">
-        <v>80.81</v>
+        <v>497.12</v>
       </c>
       <c r="E88" t="n">
-        <v>43.28</v>
+        <v>40.9</v>
       </c>
       <c r="F88" t="n">
-        <v>1.6696</v>
+        <v>2.41856</v>
       </c>
     </row>
     <row r="89">
@@ -2551,19 +2551,19 @@
         <v>49.87</v>
       </c>
       <c r="D89" t="n">
-        <v>63.17</v>
+        <v>62.3</v>
       </c>
       <c r="E89" t="n">
-        <v>26.67</v>
+        <v>24.92</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2007</v>
+        <v>0.41873</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2572,4366 +2572,4366 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>166.5</v>
+        <v>170.28</v>
       </c>
       <c r="D90" t="n">
-        <v>197.56</v>
+        <v>241.96</v>
       </c>
       <c r="E90" t="n">
-        <v>18.65</v>
+        <v>42.1</v>
       </c>
       <c r="F90" t="n">
-        <v>0.66935</v>
+        <v>-1.37415</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>44.39</v>
+        <v>60.37</v>
       </c>
       <c r="D91" t="n">
-        <v>61.14</v>
+        <v>78.72</v>
       </c>
       <c r="E91" t="n">
-        <v>37.73</v>
+        <v>30.4</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.05927</v>
+        <v>0.9964499999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>136.68</v>
+        <v>62.12</v>
       </c>
       <c r="D92" t="n">
-        <v>153.4</v>
+        <v>79.97</v>
       </c>
       <c r="E92" t="n">
-        <v>12.23</v>
+        <v>28.73</v>
       </c>
       <c r="F92" t="n">
-        <v>-2.51046</v>
+        <v>0.93677</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>255.07</v>
+        <v>10.51</v>
       </c>
       <c r="D93" t="n">
-        <v>339.15</v>
+        <v>15.29</v>
       </c>
       <c r="E93" t="n">
-        <v>32.96</v>
+        <v>45.48</v>
       </c>
       <c r="F93" t="n">
-        <v>-6.00233</v>
+        <v>0.36599</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>170.28</v>
+        <v>102.17</v>
       </c>
       <c r="D94" t="n">
-        <v>250.61</v>
+        <v>135.54</v>
       </c>
       <c r="E94" t="n">
-        <v>47.18</v>
+        <v>32.66</v>
       </c>
       <c r="F94" t="n">
-        <v>-2.75775</v>
+        <v>1.43815</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EDU</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>44.44</v>
+        <v>48.79</v>
       </c>
       <c r="D95" t="n">
-        <v>56.82</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="E95" t="n">
-        <v>27.86</v>
+        <v>38.49</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.38143</v>
+        <v>0.33897</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>142.52</v>
+        <v>247.22</v>
       </c>
       <c r="D96" t="n">
-        <v>191.45</v>
+        <v>297.26</v>
       </c>
       <c r="E96" t="n">
-        <v>34.33</v>
+        <v>20.24</v>
       </c>
       <c r="F96" t="n">
-        <v>1.43195</v>
+        <v>2.46873</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>19.32</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D97" t="n">
-        <v>24.47</v>
+        <v>123.51</v>
       </c>
       <c r="E97" t="n">
-        <v>26.66</v>
+        <v>62.43</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.0342</v>
+        <v>3.02454</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>59.71</v>
+        <v>125.73</v>
       </c>
       <c r="D98" t="n">
-        <v>79.11</v>
+        <v>195.62</v>
       </c>
       <c r="E98" t="n">
-        <v>32.49</v>
+        <v>55.59</v>
       </c>
       <c r="F98" t="n">
-        <v>0.59687</v>
+        <v>0.83805</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>352.83</v>
+        <v>150.12</v>
       </c>
       <c r="D99" t="n">
-        <v>505.41</v>
+        <v>255.65</v>
       </c>
       <c r="E99" t="n">
-        <v>43.24</v>
+        <v>70.3</v>
       </c>
       <c r="F99" t="n">
-        <v>2.09735</v>
+        <v>6.95816</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>42.46</v>
+        <v>76.55</v>
       </c>
       <c r="D100" t="n">
-        <v>69.76000000000001</v>
+        <v>102.61</v>
       </c>
       <c r="E100" t="n">
-        <v>64.3</v>
+        <v>34.04</v>
       </c>
       <c r="F100" t="n">
-        <v>1.2992</v>
+        <v>-0.89647</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>107.27</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>173.31</v>
+        <v>102.38</v>
       </c>
       <c r="E101" t="n">
-        <v>61.56</v>
+        <v>36.52</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.05801</v>
+        <v>1.20454</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>60.37</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>77</v>
+        <v>95.06</v>
       </c>
       <c r="E102" t="n">
-        <v>27.55</v>
+        <v>13.41</v>
       </c>
       <c r="F102" t="n">
-        <v>1.31187</v>
+        <v>0.23447</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>62.12</v>
+        <v>275.27</v>
       </c>
       <c r="D103" t="n">
-        <v>79.13</v>
+        <v>353.13</v>
       </c>
       <c r="E103" t="n">
-        <v>27.38</v>
+        <v>28.28</v>
       </c>
       <c r="F103" t="n">
-        <v>0.8058999999999999</v>
+        <v>-1.49134</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.51</v>
+        <v>140.71</v>
       </c>
       <c r="D104" t="n">
-        <v>15.27</v>
+        <v>185.92</v>
       </c>
       <c r="E104" t="n">
-        <v>45.29</v>
+        <v>32.13</v>
       </c>
       <c r="F104" t="n">
-        <v>0.40451</v>
+        <v>-0.65188</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>48.79</v>
+        <v>141.17</v>
       </c>
       <c r="D105" t="n">
-        <v>68.53</v>
+        <v>176.85</v>
       </c>
       <c r="E105" t="n">
-        <v>40.46</v>
+        <v>25.27</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.01588</v>
+        <v>1.14115</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>102.17</v>
+        <v>33.22</v>
       </c>
       <c r="D106" t="n">
-        <v>131.24</v>
+        <v>38.83</v>
       </c>
       <c r="E106" t="n">
-        <v>28.45</v>
+        <v>16.89</v>
       </c>
       <c r="F106" t="n">
-        <v>1.86006</v>
+        <v>0.12529</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>30.83</v>
+        <v>32.47</v>
       </c>
       <c r="D107" t="n">
-        <v>35.72</v>
+        <v>38.62</v>
       </c>
       <c r="E107" t="n">
-        <v>15.86</v>
+        <v>18.94</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.35242</v>
+        <v>0.35367</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>275.27</v>
+        <v>450.75</v>
       </c>
       <c r="D108" t="n">
-        <v>359.54</v>
+        <v>544.3200000000001</v>
       </c>
       <c r="E108" t="n">
-        <v>30.61</v>
+        <v>20.76</v>
       </c>
       <c r="F108" t="n">
-        <v>-2.74832</v>
+        <v>2.42297</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>76.04000000000001</v>
+        <v>48.87</v>
       </c>
       <c r="D109" t="n">
-        <v>123.61</v>
+        <v>58.8</v>
       </c>
       <c r="E109" t="n">
-        <v>62.56</v>
+        <v>20.32</v>
       </c>
       <c r="F109" t="n">
-        <v>2.41344</v>
+        <v>-0.23533</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>150.12</v>
+        <v>53.82</v>
       </c>
       <c r="D110" t="n">
-        <v>259.43</v>
+        <v>74.08</v>
       </c>
       <c r="E110" t="n">
-        <v>72.81999999999999</v>
+        <v>37.64</v>
       </c>
       <c r="F110" t="n">
-        <v>6.48113</v>
+        <v>0.46228</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>140.71</v>
+        <v>121.48</v>
       </c>
       <c r="D111" t="n">
-        <v>182.91</v>
+        <v>146.3</v>
       </c>
       <c r="E111" t="n">
-        <v>29.99</v>
+        <v>20.43</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.36471</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>83.81999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="D112" t="n">
-        <v>95.31</v>
+        <v>3.16</v>
       </c>
       <c r="E112" t="n">
-        <v>13.71</v>
+        <v>10.49</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.43033</v>
+        <v>0.02491</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>76.55</v>
+        <v>14.94</v>
       </c>
       <c r="D113" t="n">
-        <v>105.82</v>
+        <v>19.53</v>
       </c>
       <c r="E113" t="n">
-        <v>38.24</v>
+        <v>30.72</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.58346</v>
+        <v>0.51817</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>123.42</v>
+        <v>19.82</v>
       </c>
       <c r="D114" t="n">
-        <v>164.55</v>
+        <v>25.46</v>
       </c>
       <c r="E114" t="n">
-        <v>33.33</v>
+        <v>28.46</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.65884</v>
+        <v>0.29096</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>125.73</v>
+        <v>16.44</v>
       </c>
       <c r="D115" t="n">
-        <v>197.07</v>
+        <v>33.61</v>
       </c>
       <c r="E115" t="n">
-        <v>56.74</v>
+        <v>104.44</v>
       </c>
       <c r="F115" t="n">
-        <v>-1.80321</v>
+        <v>0.45364</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>74.98999999999999</v>
+        <v>361.32</v>
       </c>
       <c r="D116" t="n">
-        <v>104.47</v>
+        <v>423.82</v>
       </c>
       <c r="E116" t="n">
-        <v>39.31</v>
+        <v>17.3</v>
       </c>
       <c r="F116" t="n">
-        <v>0.40712</v>
+        <v>4.19429</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>OHI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>61.28</v>
+        <v>43.67</v>
       </c>
       <c r="D117" t="n">
-        <v>72.91</v>
+        <v>47.13</v>
       </c>
       <c r="E117" t="n">
-        <v>18.98</v>
+        <v>7.92</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.98211</v>
+        <v>0.04408</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>141.17</v>
+        <v>195.11</v>
       </c>
       <c r="D118" t="n">
-        <v>173.25</v>
+        <v>248.36</v>
       </c>
       <c r="E118" t="n">
-        <v>22.72</v>
+        <v>27.29</v>
       </c>
       <c r="F118" t="n">
-        <v>1.14864</v>
+        <v>0.6946099999999999</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>48.87</v>
+        <v>15.03</v>
       </c>
       <c r="D119" t="n">
-        <v>58.74</v>
+        <v>18.7</v>
       </c>
       <c r="E119" t="n">
-        <v>20.2</v>
+        <v>24.42</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.40747</v>
+        <v>0.12759</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>32.47</v>
+        <v>140.19</v>
       </c>
       <c r="D120" t="n">
-        <v>38.43</v>
+        <v>146.67</v>
       </c>
       <c r="E120" t="n">
-        <v>18.36</v>
+        <v>4.62</v>
       </c>
       <c r="F120" t="n">
-        <v>0.22774</v>
+        <v>0.02814</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>450.75</v>
+        <v>182.82</v>
       </c>
       <c r="D121" t="n">
-        <v>548.65</v>
+        <v>229.44</v>
       </c>
       <c r="E121" t="n">
-        <v>21.72</v>
+        <v>25.5</v>
       </c>
       <c r="F121" t="n">
-        <v>2.41907</v>
+        <v>-1.30339</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>147.13</v>
+        <v>275.99</v>
       </c>
       <c r="D122" t="n">
-        <v>174.93</v>
+        <v>318.2</v>
       </c>
       <c r="E122" t="n">
-        <v>18.89</v>
+        <v>15.29</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.59992</v>
+        <v>1.98323</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>91.88</v>
+        <v>23.85</v>
       </c>
       <c r="D123" t="n">
-        <v>125.3</v>
+        <v>34.15</v>
       </c>
       <c r="E123" t="n">
-        <v>36.37</v>
+        <v>43.19</v>
       </c>
       <c r="F123" t="n">
-        <v>1.50067</v>
+        <v>0.01267</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>53.82</v>
+        <v>73.75</v>
       </c>
       <c r="D124" t="n">
-        <v>75</v>
+        <v>93.75</v>
       </c>
       <c r="E124" t="n">
-        <v>39.35</v>
+        <v>27.12</v>
       </c>
       <c r="F124" t="n">
-        <v>0.53725</v>
+        <v>0.46174</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>62.47</v>
+        <v>277.69</v>
       </c>
       <c r="D125" t="n">
-        <v>90.19</v>
+        <v>328.7</v>
       </c>
       <c r="E125" t="n">
-        <v>44.37</v>
+        <v>18.37</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.65359</v>
+        <v>0.45735</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>16.44</v>
+        <v>9.85</v>
       </c>
       <c r="D126" t="n">
-        <v>33.97</v>
+        <v>14</v>
       </c>
       <c r="E126" t="n">
-        <v>106.63</v>
+        <v>42.13</v>
       </c>
       <c r="F126" t="n">
-        <v>0.60034</v>
+        <v>0.47309</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2.86</v>
+        <v>36.25</v>
       </c>
       <c r="D127" t="n">
-        <v>3.18</v>
+        <v>41.48</v>
       </c>
       <c r="E127" t="n">
-        <v>11.19</v>
+        <v>14.43</v>
       </c>
       <c r="F127" t="n">
-        <v>0.02543</v>
+        <v>0.15456</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>121.48</v>
+        <v>309.78</v>
       </c>
       <c r="D128" t="n">
-        <v>146.41</v>
+        <v>341.86</v>
       </c>
       <c r="E128" t="n">
-        <v>20.52</v>
+        <v>10.36</v>
       </c>
       <c r="F128" t="n">
-        <v>0.04863</v>
+        <v>-0.62071</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>14.94</v>
+        <v>63.54</v>
       </c>
       <c r="D129" t="n">
-        <v>19.59</v>
+        <v>71.28</v>
       </c>
       <c r="E129" t="n">
-        <v>31.16</v>
+        <v>12.18</v>
       </c>
       <c r="F129" t="n">
-        <v>0.52114</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>19.82</v>
+        <v>190.4</v>
       </c>
       <c r="D130" t="n">
-        <v>25.05</v>
+        <v>221.31</v>
       </c>
       <c r="E130" t="n">
-        <v>26.39</v>
+        <v>16.23</v>
       </c>
       <c r="F130" t="n">
-        <v>0.40053</v>
+        <v>0.59114</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>GFL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>361.32</v>
+        <v>33.54</v>
       </c>
       <c r="D131" t="n">
-        <v>425.49</v>
+        <v>42.18</v>
       </c>
       <c r="E131" t="n">
-        <v>17.76</v>
+        <v>25.76</v>
       </c>
       <c r="F131" t="n">
-        <v>4.42632</v>
+        <v>0.1388</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>205.81</v>
+        <v>529.12</v>
       </c>
       <c r="D132" t="n">
-        <v>264.92</v>
+        <v>684.04</v>
       </c>
       <c r="E132" t="n">
-        <v>28.72</v>
+        <v>29.28</v>
       </c>
       <c r="F132" t="n">
-        <v>1.32952</v>
+        <v>9.50407</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>43.67</v>
+        <v>57.4</v>
       </c>
       <c r="D133" t="n">
-        <v>47.34</v>
+        <v>103.69</v>
       </c>
       <c r="E133" t="n">
-        <v>8.4</v>
+        <v>80.64</v>
       </c>
       <c r="F133" t="n">
-        <v>0.05503</v>
+        <v>0.53257</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>161.37</v>
+        <v>438.34</v>
       </c>
       <c r="D134" t="n">
-        <v>264.51</v>
+        <v>641.39</v>
       </c>
       <c r="E134" t="n">
-        <v>63.92</v>
+        <v>46.32</v>
       </c>
       <c r="F134" t="n">
-        <v>0.82511</v>
+        <v>3.85233</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>55.05</v>
+        <v>102.87</v>
       </c>
       <c r="D135" t="n">
-        <v>63.57</v>
+        <v>174.73</v>
       </c>
       <c r="E135" t="n">
-        <v>15.48</v>
+        <v>69.86</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.4736</v>
+        <v>-0.36801</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>28.18</v>
+        <v>26.18</v>
       </c>
       <c r="D136" t="n">
-        <v>37.03</v>
+        <v>36.72</v>
       </c>
       <c r="E136" t="n">
-        <v>31.41</v>
+        <v>40.26</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.01107</v>
+        <v>0.23738</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>195.11</v>
+        <v>186.61</v>
       </c>
       <c r="D137" t="n">
-        <v>249.05</v>
+        <v>247.08</v>
       </c>
       <c r="E137" t="n">
-        <v>27.65</v>
+        <v>32.4</v>
       </c>
       <c r="F137" t="n">
-        <v>0.4172</v>
+        <v>0.19288</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>140.19</v>
+        <v>63.16</v>
       </c>
       <c r="D138" t="n">
-        <v>146.13</v>
+        <v>100.67</v>
       </c>
       <c r="E138" t="n">
-        <v>4.24</v>
+        <v>59.39</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.3931</v>
+        <v>1.35459</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>207.24</v>
+        <v>250.4</v>
       </c>
       <c r="D139" t="n">
-        <v>253.88</v>
+        <v>323.97</v>
       </c>
       <c r="E139" t="n">
-        <v>22.51</v>
+        <v>29.38</v>
       </c>
       <c r="F139" t="n">
-        <v>-2.67569</v>
+        <v>-3.61611</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>15.03</v>
+        <v>43.3</v>
       </c>
       <c r="D140" t="n">
-        <v>18.6</v>
+        <v>72.34</v>
       </c>
       <c r="E140" t="n">
-        <v>23.75</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F140" t="n">
-        <v>0.08944000000000001</v>
+        <v>0.008569999999999999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>72.55</v>
+        <v>161.91</v>
       </c>
       <c r="D141" t="n">
-        <v>76.29000000000001</v>
+        <v>209.36</v>
       </c>
       <c r="E141" t="n">
-        <v>5.16</v>
+        <v>29.31</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.36496</v>
+        <v>-1.52751</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>275.99</v>
+        <v>73.42</v>
       </c>
       <c r="D142" t="n">
-        <v>322.99</v>
+        <v>89.72</v>
       </c>
       <c r="E142" t="n">
-        <v>17.03</v>
+        <v>22.2</v>
       </c>
       <c r="F142" t="n">
-        <v>1.92883</v>
+        <v>0.70402</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>277.69</v>
+        <v>163.43</v>
       </c>
       <c r="D143" t="n">
-        <v>330.62</v>
+        <v>198.63</v>
       </c>
       <c r="E143" t="n">
-        <v>19.06</v>
+        <v>21.54</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.14398</v>
+        <v>1.4774</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>73.75</v>
+        <v>55.52</v>
       </c>
       <c r="D144" t="n">
-        <v>93.8</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="E144" t="n">
-        <v>27.19</v>
+        <v>67.94</v>
       </c>
       <c r="F144" t="n">
-        <v>0.31456</v>
+        <v>1.96119</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>121.13</v>
+        <v>99.3</v>
       </c>
       <c r="D145" t="n">
-        <v>138.92</v>
+        <v>153.74</v>
       </c>
       <c r="E145" t="n">
-        <v>14.69</v>
+        <v>54.82</v>
       </c>
       <c r="F145" t="n">
-        <v>0.41111</v>
+        <v>2.14918</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>132.79</v>
+        <v>197.73</v>
       </c>
       <c r="D146" t="n">
-        <v>163.39</v>
+        <v>223.04</v>
       </c>
       <c r="E146" t="n">
-        <v>23.04</v>
+        <v>12.8</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.12699</v>
+        <v>0.94077</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>309.78</v>
+        <v>725.17</v>
       </c>
       <c r="D147" t="n">
-        <v>341.85</v>
+        <v>899.5599999999999</v>
       </c>
       <c r="E147" t="n">
-        <v>10.35</v>
+        <v>24.05</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.13236</v>
+        <v>2.47985</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>36.25</v>
+        <v>79.58</v>
       </c>
       <c r="D148" t="n">
-        <v>41.61</v>
+        <v>98.41</v>
       </c>
       <c r="E148" t="n">
-        <v>14.79</v>
+        <v>23.66</v>
       </c>
       <c r="F148" t="n">
-        <v>0.22556</v>
+        <v>-0.83257</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>9.85</v>
+        <v>12.64</v>
       </c>
       <c r="D149" t="n">
-        <v>13.75</v>
+        <v>18.26</v>
       </c>
       <c r="E149" t="n">
-        <v>39.59</v>
+        <v>44.46</v>
       </c>
       <c r="F149" t="n">
-        <v>0.51236</v>
+        <v>0.26064</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>33.54</v>
+        <v>417.83</v>
       </c>
       <c r="D150" t="n">
-        <v>42.61</v>
+        <v>558.26</v>
       </c>
       <c r="E150" t="n">
-        <v>27.04</v>
+        <v>33.61</v>
       </c>
       <c r="F150" t="n">
-        <v>0.13446</v>
+        <v>3.75502</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>190.4</v>
+        <v>255.54</v>
       </c>
       <c r="D151" t="n">
-        <v>221.02</v>
+        <v>365.08</v>
       </c>
       <c r="E151" t="n">
-        <v>16.08</v>
+        <v>42.87</v>
       </c>
       <c r="F151" t="n">
-        <v>0.04179</v>
+        <v>2.95635</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>63.54</v>
+        <v>32.32</v>
       </c>
       <c r="D152" t="n">
-        <v>70.87</v>
+        <v>37.81</v>
       </c>
       <c r="E152" t="n">
-        <v>11.54</v>
+        <v>16.99</v>
       </c>
       <c r="F152" t="n">
-        <v>0.26916</v>
+        <v>0.07455000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>250.75</v>
+        <v>699965</v>
       </c>
       <c r="D153" t="n">
-        <v>340.38</v>
+        <v>773825</v>
       </c>
       <c r="E153" t="n">
-        <v>35.74</v>
+        <v>10.55</v>
       </c>
       <c r="F153" t="n">
-        <v>3.87926</v>
+        <v>3681.50215</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FMS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>529.12</v>
+        <v>20.19</v>
       </c>
       <c r="D154" t="n">
-        <v>681.46</v>
+        <v>22.96</v>
       </c>
       <c r="E154" t="n">
-        <v>28.79</v>
+        <v>13.72</v>
       </c>
       <c r="F154" t="n">
-        <v>9.785550000000001</v>
+        <v>-0.15989</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>57.4</v>
+        <v>139.71</v>
       </c>
       <c r="D155" t="n">
-        <v>104.79</v>
+        <v>193.9</v>
       </c>
       <c r="E155" t="n">
-        <v>82.56</v>
+        <v>38.79</v>
       </c>
       <c r="F155" t="n">
-        <v>0.21284</v>
+        <v>2.09242</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SGI</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>61.49</v>
+        <v>45.37</v>
       </c>
       <c r="D156" t="n">
-        <v>68.12</v>
+        <v>143.77</v>
       </c>
       <c r="E156" t="n">
-        <v>10.78</v>
+        <v>216.88</v>
       </c>
       <c r="F156" t="n">
-        <v>0.25125</v>
+        <v>5.51342</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BMRN</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>49.67</v>
+        <v>112.47</v>
       </c>
       <c r="D157" t="n">
-        <v>66.41</v>
+        <v>137.79</v>
       </c>
       <c r="E157" t="n">
-        <v>33.7</v>
+        <v>22.51</v>
       </c>
       <c r="F157" t="n">
-        <v>0.03841</v>
+        <v>0.54053</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>438.34</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D158" t="n">
-        <v>613.62</v>
+        <v>140.19</v>
       </c>
       <c r="E158" t="n">
-        <v>39.99</v>
+        <v>70.42</v>
       </c>
       <c r="F158" t="n">
-        <v>0.49995</v>
+        <v>1.63417</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>43.3</v>
+        <v>156.66</v>
       </c>
       <c r="D159" t="n">
-        <v>72.27</v>
+        <v>269.67</v>
       </c>
       <c r="E159" t="n">
-        <v>66.91</v>
+        <v>72.14</v>
       </c>
       <c r="F159" t="n">
-        <v>-0</v>
+        <v>3.05682</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>73.42</v>
+        <v>40.41</v>
       </c>
       <c r="D160" t="n">
-        <v>88.70999999999999</v>
+        <v>52.93</v>
       </c>
       <c r="E160" t="n">
-        <v>20.83</v>
+        <v>30.98</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7728699999999999</v>
+        <v>0.06672</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>63.16</v>
+        <v>197.38</v>
       </c>
       <c r="D161" t="n">
-        <v>101.84</v>
+        <v>263.04</v>
       </c>
       <c r="E161" t="n">
-        <v>61.24</v>
+        <v>33.27</v>
       </c>
       <c r="F161" t="n">
-        <v>1.43086</v>
+        <v>1.10836</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5563.62</v>
+        <v>393.42</v>
       </c>
       <c r="D162" t="n">
-        <v>6299.56</v>
+        <v>620.48</v>
       </c>
       <c r="E162" t="n">
-        <v>13.23</v>
+        <v>57.71</v>
       </c>
       <c r="F162" t="n">
-        <v>-44.26965</v>
+        <v>1.40198</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>26.18</v>
+        <v>74.63</v>
       </c>
       <c r="D163" t="n">
-        <v>36.71</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E163" t="n">
-        <v>40.22</v>
+        <v>18.87</v>
       </c>
       <c r="F163" t="n">
-        <v>0.135</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>186.61</v>
+        <v>465.4</v>
       </c>
       <c r="D164" t="n">
-        <v>237.89</v>
+        <v>516.76</v>
       </c>
       <c r="E164" t="n">
-        <v>27.48</v>
+        <v>11.04</v>
       </c>
       <c r="F164" t="n">
-        <v>-1.00997</v>
+        <v>2.46605</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>92.38</v>
+        <v>153.25</v>
       </c>
       <c r="D165" t="n">
-        <v>100.65</v>
+        <v>194.11</v>
       </c>
       <c r="E165" t="n">
-        <v>8.949999999999999</v>
+        <v>26.66</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.07876</v>
+        <v>1.57503</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>163.43</v>
+        <v>155.75</v>
       </c>
       <c r="D166" t="n">
-        <v>200.67</v>
+        <v>264.93</v>
       </c>
       <c r="E166" t="n">
-        <v>22.79</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F166" t="n">
-        <v>0.62133</v>
+        <v>5.58905</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>156.84</v>
+        <v>20.96</v>
       </c>
       <c r="D167" t="n">
-        <v>187.03</v>
+        <v>25.77</v>
       </c>
       <c r="E167" t="n">
-        <v>19.25</v>
+        <v>22.95</v>
       </c>
       <c r="F167" t="n">
-        <v>-2.68499</v>
+        <v>0.24889</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>101.75</v>
+        <v>40.59</v>
       </c>
       <c r="D168" t="n">
-        <v>129.17</v>
+        <v>57.61</v>
       </c>
       <c r="E168" t="n">
-        <v>26.95</v>
+        <v>41.93</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.25082</v>
+        <v>1.55685</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>55.52</v>
+        <v>128.43</v>
       </c>
       <c r="D169" t="n">
-        <v>94.83</v>
+        <v>153.74</v>
       </c>
       <c r="E169" t="n">
-        <v>70.8</v>
+        <v>19.71</v>
       </c>
       <c r="F169" t="n">
-        <v>1.61921</v>
+        <v>1.24056</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>99.3</v>
+        <v>213.69</v>
       </c>
       <c r="D170" t="n">
-        <v>151.7</v>
+        <v>410.84</v>
       </c>
       <c r="E170" t="n">
-        <v>52.77</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F170" t="n">
-        <v>1.17857</v>
+        <v>10.41305</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>68.98999999999999</v>
+        <v>223.65</v>
       </c>
       <c r="D171" t="n">
-        <v>88.93000000000001</v>
+        <v>397.04</v>
       </c>
       <c r="E171" t="n">
-        <v>28.9</v>
+        <v>77.53</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.34243</v>
+        <v>11.66693</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>725.17</v>
+        <v>66.95</v>
       </c>
       <c r="D172" t="n">
-        <v>910.95</v>
+        <v>86.61</v>
       </c>
       <c r="E172" t="n">
-        <v>25.62</v>
+        <v>29.37</v>
       </c>
       <c r="F172" t="n">
-        <v>1.91142</v>
+        <v>1.36817</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>197.73</v>
+        <v>18.71</v>
       </c>
       <c r="D173" t="n">
-        <v>225.85</v>
+        <v>21.33</v>
       </c>
       <c r="E173" t="n">
-        <v>14.22</v>
+        <v>14</v>
       </c>
       <c r="F173" t="n">
-        <v>0.9798</v>
+        <v>0.09087000000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>255.54</v>
+        <v>32.36</v>
       </c>
       <c r="D174" t="n">
-        <v>365.08</v>
+        <v>55.17</v>
       </c>
       <c r="E174" t="n">
-        <v>42.87</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="F174" t="n">
-        <v>3.26755</v>
+        <v>0.76689</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>12.64</v>
+        <v>43.81</v>
       </c>
       <c r="D175" t="n">
-        <v>17.74</v>
+        <v>103.55</v>
       </c>
       <c r="E175" t="n">
-        <v>40.35</v>
+        <v>136.36</v>
       </c>
       <c r="F175" t="n">
-        <v>0.24281</v>
+        <v>1.02235</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>417.83</v>
+        <v>62.93</v>
       </c>
       <c r="D176" t="n">
-        <v>556.3099999999999</v>
+        <v>190.45</v>
       </c>
       <c r="E176" t="n">
-        <v>33.14</v>
+        <v>202.64</v>
       </c>
       <c r="F176" t="n">
-        <v>0.43871</v>
+        <v>7.34012</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>383.99</v>
+        <v>120.88</v>
       </c>
       <c r="D177" t="n">
-        <v>474.13</v>
+        <v>209.62</v>
       </c>
       <c r="E177" t="n">
-        <v>23.47</v>
+        <v>73.41</v>
       </c>
       <c r="F177" t="n">
-        <v>-1.53084</v>
+        <v>-0.40223</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>32.32</v>
+        <v>83</v>
       </c>
       <c r="D178" t="n">
-        <v>37.72</v>
+        <v>141.9</v>
       </c>
       <c r="E178" t="n">
-        <v>16.71</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F178" t="n">
-        <v>0.15923</v>
+        <v>1.71804</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>252.74</v>
+        <v>105.37</v>
       </c>
       <c r="D179" t="n">
-        <v>326.23</v>
+        <v>230.27</v>
       </c>
       <c r="E179" t="n">
-        <v>29.08</v>
+        <v>118.53</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.21978</v>
+        <v>-1.24495</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BRK-A</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>699965</v>
+        <v>188.79</v>
       </c>
       <c r="D180" t="n">
-        <v>773825</v>
+        <v>276.53</v>
       </c>
       <c r="E180" t="n">
-        <v>10.55</v>
+        <v>46.47</v>
       </c>
       <c r="F180" t="n">
-        <v>3681.50215</v>
+        <v>-0.99091</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>139.71</v>
+        <v>112.5</v>
       </c>
       <c r="D181" t="n">
-        <v>193.61</v>
+        <v>190.67</v>
       </c>
       <c r="E181" t="n">
-        <v>38.58</v>
+        <v>69.48</v>
       </c>
       <c r="F181" t="n">
-        <v>1.72426</v>
+        <v>-0.51289</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>45.37</v>
+        <v>34.41</v>
       </c>
       <c r="D182" t="n">
-        <v>146.69</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E182" t="n">
-        <v>223.32</v>
+        <v>97.59</v>
       </c>
       <c r="F182" t="n">
-        <v>5.23484</v>
+        <v>0.22691</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>112.47</v>
+        <v>117.65</v>
       </c>
       <c r="D183" t="n">
-        <v>138.5</v>
+        <v>242.16</v>
       </c>
       <c r="E183" t="n">
-        <v>23.14</v>
+        <v>105.83</v>
       </c>
       <c r="F183" t="n">
-        <v>0.31006</v>
+        <v>1.79379</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>156.66</v>
+        <v>57.15</v>
       </c>
       <c r="D184" t="n">
-        <v>265.67</v>
+        <v>189.81</v>
       </c>
       <c r="E184" t="n">
-        <v>69.58</v>
+        <v>232.13</v>
       </c>
       <c r="F184" t="n">
-        <v>2.0428</v>
+        <v>4.93853</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>82.26000000000001</v>
+        <v>118.05</v>
       </c>
       <c r="D185" t="n">
-        <v>128.49</v>
+        <v>193.89</v>
       </c>
       <c r="E185" t="n">
-        <v>56.2</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="F185" t="n">
-        <v>0.08618000000000001</v>
+        <v>2.28457</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>13.06</v>
+        <v>18.26</v>
       </c>
       <c r="D186" t="n">
-        <v>19.91</v>
+        <v>33.82</v>
       </c>
       <c r="E186" t="n">
-        <v>52.45</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.009140000000000001</v>
+        <v>1.18337</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>40.41</v>
+        <v>25.85</v>
       </c>
       <c r="D187" t="n">
-        <v>51.96</v>
+        <v>41.65</v>
       </c>
       <c r="E187" t="n">
-        <v>28.58</v>
+        <v>61.12</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.19889</v>
+        <v>0.40151</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>197.38</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D188" t="n">
-        <v>261.77</v>
+        <v>175.65</v>
       </c>
       <c r="E188" t="n">
-        <v>32.62</v>
+        <v>123.47</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.05181</v>
+        <v>1.12337</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>393.42</v>
+        <v>10.49</v>
       </c>
       <c r="D189" t="n">
-        <v>595.41</v>
+        <v>19.98</v>
       </c>
       <c r="E189" t="n">
-        <v>51.34</v>
+        <v>90.47</v>
       </c>
       <c r="F189" t="n">
-        <v>-2.04834</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>56.06</v>
+        <v>76.7</v>
       </c>
       <c r="D190" t="n">
-        <v>62.39</v>
+        <v>172.37</v>
       </c>
       <c r="E190" t="n">
-        <v>11.29</v>
+        <v>124.73</v>
       </c>
       <c r="F190" t="n">
-        <v>0.03839</v>
+        <v>2.05425</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>74.63</v>
+        <v>166.99</v>
       </c>
       <c r="D191" t="n">
-        <v>89.34999999999999</v>
+        <v>327.23</v>
       </c>
       <c r="E191" t="n">
-        <v>19.72</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.05535</v>
+        <v>9.443759999999999</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>465.4</v>
+        <v>151.43</v>
       </c>
       <c r="D192" t="n">
-        <v>514.95</v>
+        <v>266.62</v>
       </c>
       <c r="E192" t="n">
-        <v>10.65</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F192" t="n">
-        <v>1.66879</v>
+        <v>1.96202</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>153.25</v>
+        <v>17.89</v>
       </c>
       <c r="D193" t="n">
-        <v>194.86</v>
+        <v>31.23</v>
       </c>
       <c r="E193" t="n">
-        <v>27.15</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="F193" t="n">
-        <v>0.85662</v>
+        <v>0.39427</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>20.96</v>
+        <v>56.43</v>
       </c>
       <c r="D194" t="n">
-        <v>25.85</v>
+        <v>112.25</v>
       </c>
       <c r="E194" t="n">
-        <v>23.33</v>
+        <v>98.92</v>
       </c>
       <c r="F194" t="n">
-        <v>0.28351</v>
+        <v>3.11717</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>155.75</v>
+        <v>95.67</v>
       </c>
       <c r="D195" t="n">
-        <v>257.06</v>
+        <v>189.93</v>
       </c>
       <c r="E195" t="n">
-        <v>65.05</v>
+        <v>98.53</v>
       </c>
       <c r="F195" t="n">
-        <v>5.74053</v>
+        <v>0.92719</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>83.51000000000001</v>
+        <v>23.63</v>
       </c>
       <c r="D196" t="n">
-        <v>96.97</v>
+        <v>25.4</v>
       </c>
       <c r="E196" t="n">
-        <v>16.12</v>
+        <v>7.49</v>
       </c>
       <c r="F196" t="n">
-        <v>0.63437</v>
+        <v>0.05914</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>40.59</v>
+        <v>62.49</v>
       </c>
       <c r="D197" t="n">
-        <v>56.33</v>
+        <v>90.06</v>
       </c>
       <c r="E197" t="n">
-        <v>38.78</v>
+        <v>44.12</v>
       </c>
       <c r="F197" t="n">
-        <v>1.40494</v>
+        <v>-0.21073</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>213.69</v>
+        <v>23.49</v>
       </c>
       <c r="D198" t="n">
-        <v>396.45</v>
+        <v>32.21</v>
       </c>
       <c r="E198" t="n">
-        <v>85.53</v>
+        <v>37.12</v>
       </c>
       <c r="F198" t="n">
-        <v>10.30916</v>
+        <v>0.17481</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>128.43</v>
+        <v>124.07</v>
       </c>
       <c r="D199" t="n">
-        <v>148.54</v>
+        <v>187.8</v>
       </c>
       <c r="E199" t="n">
-        <v>15.66</v>
+        <v>51.37</v>
       </c>
       <c r="F199" t="n">
-        <v>0.66273</v>
+        <v>4.85902</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>223.65</v>
+        <v>430.4</v>
       </c>
       <c r="D200" t="n">
-        <v>382.95</v>
+        <v>559.34</v>
       </c>
       <c r="E200" t="n">
-        <v>71.23</v>
+        <v>29.96</v>
       </c>
       <c r="F200" t="n">
-        <v>12.04345</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>18.71</v>
+        <v>172.34</v>
       </c>
       <c r="D201" t="n">
-        <v>21.49</v>
+        <v>216.17</v>
       </c>
       <c r="E201" t="n">
-        <v>14.86</v>
+        <v>25.43</v>
       </c>
       <c r="F201" t="n">
-        <v>0.13728</v>
+        <v>0.34426</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>66.95</v>
+        <v>96.73</v>
       </c>
       <c r="D202" t="n">
-        <v>86.44</v>
+        <v>122</v>
       </c>
       <c r="E202" t="n">
-        <v>29.11</v>
+        <v>26.12</v>
       </c>
       <c r="F202" t="n">
-        <v>1.50588</v>
+        <v>0.43594</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>126.32</v>
+        <v>164.13</v>
       </c>
       <c r="D203" t="n">
-        <v>157.22</v>
+        <v>543.51</v>
       </c>
       <c r="E203" t="n">
-        <v>24.46</v>
+        <v>231.15</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.32127</v>
+        <v>20.08884</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>25.85</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D204" t="n">
-        <v>42.91</v>
+        <v>101.14</v>
       </c>
       <c r="E204" t="n">
-        <v>66</v>
+        <v>12.37</v>
       </c>
       <c r="F204" t="n">
-        <v>0.12798</v>
+        <v>0.33492</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>188.79</v>
+        <v>3.88</v>
       </c>
       <c r="D205" t="n">
-        <v>276.63</v>
+        <v>6.44</v>
       </c>
       <c r="E205" t="n">
-        <v>46.53</v>
+        <v>65.98</v>
       </c>
       <c r="F205" t="n">
-        <v>-2.28574</v>
+        <v>0.07534</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>76.7</v>
+        <v>131.47</v>
       </c>
       <c r="D206" t="n">
-        <v>170.18</v>
+        <v>206.99</v>
       </c>
       <c r="E206" t="n">
-        <v>121.88</v>
+        <v>57.44</v>
       </c>
       <c r="F206" t="n">
-        <v>0.67575</v>
+        <v>2.05473</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>43.81</v>
+        <v>73.13</v>
       </c>
       <c r="D207" t="n">
-        <v>100.2</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E207" t="n">
-        <v>128.71</v>
+        <v>31.03</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.42056</v>
+        <v>0.60843</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>166.99</v>
+        <v>52.5</v>
       </c>
       <c r="D208" t="n">
-        <v>330.36</v>
+        <v>90</v>
       </c>
       <c r="E208" t="n">
-        <v>97.83</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>9.064159999999999</v>
+        <v>5.23697</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>32.36</v>
+        <v>273.5</v>
       </c>
       <c r="D209" t="n">
-        <v>53.34</v>
+        <v>344.98</v>
       </c>
       <c r="E209" t="n">
-        <v>64.83</v>
+        <v>26.14</v>
       </c>
       <c r="F209" t="n">
-        <v>0.36656</v>
+        <v>0.07092</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>112.5</v>
+        <v>28.35</v>
       </c>
       <c r="D210" t="n">
-        <v>194.21</v>
+        <v>39.25</v>
       </c>
       <c r="E210" t="n">
-        <v>72.63</v>
+        <v>38.45</v>
       </c>
       <c r="F210" t="n">
-        <v>-1.0532</v>
+        <v>0.49418</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>105.37</v>
+        <v>19.02</v>
       </c>
       <c r="D211" t="n">
-        <v>230.05</v>
+        <v>26.78</v>
       </c>
       <c r="E211" t="n">
-        <v>118.33</v>
+        <v>40.8</v>
       </c>
       <c r="F211" t="n">
-        <v>-1.90231</v>
+        <v>0.29688</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>121.11</v>
+        <v>258.08</v>
       </c>
       <c r="D212" t="n">
-        <v>332.35</v>
+        <v>288.9</v>
       </c>
       <c r="E212" t="n">
-        <v>174.42</v>
+        <v>11.94</v>
       </c>
       <c r="F212" t="n">
-        <v>2.08531</v>
+        <v>1.81284</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>78.59999999999999</v>
+        <v>24.77</v>
       </c>
       <c r="D213" t="n">
-        <v>167.84</v>
+        <v>36.78</v>
       </c>
       <c r="E213" t="n">
-        <v>113.54</v>
+        <v>48.49</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.11311</v>
+        <v>0.38487</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>117.65</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D214" t="n">
-        <v>231.88</v>
+        <v>21.61</v>
       </c>
       <c r="E214" t="n">
-        <v>97.09</v>
+        <v>150.99</v>
       </c>
       <c r="F214" t="n">
-        <v>0.40682</v>
+        <v>0.62903</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>34.41</v>
+        <v>22.61</v>
       </c>
       <c r="D215" t="n">
-        <v>67.69</v>
+        <v>55.88</v>
       </c>
       <c r="E215" t="n">
-        <v>96.72</v>
+        <v>147.15</v>
       </c>
       <c r="F215" t="n">
-        <v>0.14027</v>
+        <v>1.10062</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>17.89</v>
+        <v>59.66</v>
       </c>
       <c r="D216" t="n">
-        <v>31.41</v>
+        <v>82.63</v>
       </c>
       <c r="E216" t="n">
-        <v>75.56999999999999</v>
+        <v>38.5</v>
       </c>
       <c r="F216" t="n">
-        <v>0.28103</v>
+        <v>1.52417</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>120.88</v>
+        <v>284.79</v>
       </c>
       <c r="D217" t="n">
-        <v>211.54</v>
+        <v>417.54</v>
       </c>
       <c r="E217" t="n">
-        <v>75</v>
+        <v>46.61</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.8151</v>
+        <v>6.50222</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>151.43</v>
+        <v>273.14</v>
       </c>
       <c r="D218" t="n">
-        <v>265.67</v>
+        <v>341.43</v>
       </c>
       <c r="E218" t="n">
-        <v>75.44</v>
+        <v>25</v>
       </c>
       <c r="F218" t="n">
-        <v>1.55591</v>
+        <v>-0.05953</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>83</v>
+        <v>67.39</v>
       </c>
       <c r="D219" t="n">
-        <v>142.35</v>
+        <v>93.28</v>
       </c>
       <c r="E219" t="n">
-        <v>71.51000000000001</v>
+        <v>38.42</v>
       </c>
       <c r="F219" t="n">
-        <v>0.76309</v>
+        <v>0.61522</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>62.93</v>
+        <v>65.16</v>
       </c>
       <c r="D220" t="n">
-        <v>186.45</v>
+        <v>110.45</v>
       </c>
       <c r="E220" t="n">
-        <v>196.28</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="F220" t="n">
-        <v>6.24855</v>
+        <v>1.57155</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>118.05</v>
+        <v>29.16</v>
       </c>
       <c r="D221" t="n">
-        <v>191.73</v>
+        <v>39.69</v>
       </c>
       <c r="E221" t="n">
-        <v>62.41</v>
+        <v>36.11</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.40022</v>
+        <v>0.07466</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>18.26</v>
+        <v>31.8</v>
       </c>
       <c r="D222" t="n">
-        <v>34.02</v>
+        <v>67.66</v>
       </c>
       <c r="E222" t="n">
-        <v>86.31</v>
+        <v>112.77</v>
       </c>
       <c r="F222" t="n">
-        <v>1.1574</v>
+        <v>0.62832</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>10.49</v>
+        <v>97.52</v>
       </c>
       <c r="D223" t="n">
-        <v>19.88</v>
+        <v>129.59</v>
       </c>
       <c r="E223" t="n">
-        <v>89.51000000000001</v>
+        <v>32.89</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.15382</v>
+        <v>2.24577</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>57.15</v>
+        <v>119.51</v>
       </c>
       <c r="D224" t="n">
-        <v>192.77</v>
+        <v>259.35</v>
       </c>
       <c r="E224" t="n">
-        <v>237.31</v>
+        <v>117.01</v>
       </c>
       <c r="F224" t="n">
-        <v>4.18785</v>
+        <v>10.66539</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>56.43</v>
+        <v>204.77</v>
       </c>
       <c r="D225" t="n">
-        <v>106.91</v>
+        <v>273.05</v>
       </c>
       <c r="E225" t="n">
-        <v>89.45999999999999</v>
+        <v>33.34</v>
       </c>
       <c r="F225" t="n">
-        <v>3.01266</v>
+        <v>0.99791</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>124.07</v>
+        <v>12.96</v>
       </c>
       <c r="D226" t="n">
-        <v>180.15</v>
+        <v>16.65</v>
       </c>
       <c r="E226" t="n">
-        <v>45.2</v>
+        <v>28.47</v>
       </c>
       <c r="F226" t="n">
-        <v>4.1705</v>
+        <v>-0.03231</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>62.49</v>
+        <v>116.13</v>
       </c>
       <c r="D227" t="n">
-        <v>89.81999999999999</v>
+        <v>192.84</v>
       </c>
       <c r="E227" t="n">
-        <v>43.73</v>
+        <v>66.06</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.23607</v>
+        <v>0.13947</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>23.63</v>
+        <v>16.32</v>
       </c>
       <c r="D228" t="n">
-        <v>25.41</v>
+        <v>23.71</v>
       </c>
       <c r="E228" t="n">
-        <v>7.53</v>
+        <v>45.28</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0601</v>
+        <v>0.26691</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>190.63</v>
+        <v>41.19</v>
       </c>
       <c r="D229" t="n">
-        <v>218.57</v>
+        <v>97.14</v>
       </c>
       <c r="E229" t="n">
-        <v>14.66</v>
+        <v>135.83</v>
       </c>
       <c r="F229" t="n">
-        <v>-1.51875</v>
+        <v>1.2311</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>23.49</v>
+        <v>107.27</v>
       </c>
       <c r="D230" t="n">
-        <v>32.49</v>
+        <v>136.17</v>
       </c>
       <c r="E230" t="n">
-        <v>38.31</v>
+        <v>26.94</v>
       </c>
       <c r="F230" t="n">
-        <v>0.09743</v>
+        <v>0.75183</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>172.34</v>
+        <v>26.41</v>
       </c>
       <c r="D231" t="n">
-        <v>217.36</v>
+        <v>39.5</v>
       </c>
       <c r="E231" t="n">
-        <v>26.12</v>
+        <v>49.56</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.19213</v>
+        <v>1.30846</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>430.4</v>
+        <v>196.04</v>
       </c>
       <c r="D232" t="n">
-        <v>558.54</v>
+        <v>504.2</v>
       </c>
       <c r="E232" t="n">
-        <v>29.77</v>
+        <v>157.19</v>
       </c>
       <c r="F232" t="n">
-        <v>0.26252</v>
+        <v>7.29423</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>72.54000000000001</v>
+        <v>279.73</v>
       </c>
       <c r="D233" t="n">
-        <v>87.16</v>
+        <v>430.88</v>
       </c>
       <c r="E233" t="n">
-        <v>20.15</v>
+        <v>54.03</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.10751</v>
+        <v>5.88329</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>164.13</v>
+        <v>246.63</v>
       </c>
       <c r="D234" t="n">
-        <v>534.28</v>
+        <v>331.34</v>
       </c>
       <c r="E234" t="n">
-        <v>225.52</v>
+        <v>34.35</v>
       </c>
       <c r="F234" t="n">
-        <v>21.33398</v>
+        <v>4.71551</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>96.73</v>
+        <v>166</v>
       </c>
       <c r="D235" t="n">
-        <v>122.53</v>
+        <v>396.62</v>
       </c>
       <c r="E235" t="n">
-        <v>26.67</v>
+        <v>138.93</v>
       </c>
       <c r="F235" t="n">
-        <v>0.4313</v>
+        <v>3.79223</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>BML-PJ</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>19.05</v>
+        <v>33.63</v>
       </c>
       <c r="D236" t="n">
-        <v>19.64</v>
+        <v>43.87</v>
       </c>
       <c r="E236" t="n">
-        <v>3.1</v>
+        <v>30.45</v>
       </c>
       <c r="F236" t="n">
-        <v>0.02454</v>
+        <v>0.08643000000000001</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>20.33</v>
+        <v>39.84</v>
       </c>
       <c r="D237" t="n">
-        <v>29.1</v>
+        <v>58.28</v>
       </c>
       <c r="E237" t="n">
-        <v>43.14</v>
+        <v>46.29</v>
       </c>
       <c r="F237" t="n">
-        <v>0.12624</v>
+        <v>0.05681</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3.88</v>
+        <v>285.27</v>
       </c>
       <c r="D238" t="n">
-        <v>6.46</v>
+        <v>377.97</v>
       </c>
       <c r="E238" t="n">
-        <v>66.48999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="F238" t="n">
-        <v>0.08959</v>
+        <v>2.23594</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>246.63</v>
+        <v>106.41</v>
       </c>
       <c r="D239" t="n">
-        <v>333.08</v>
+        <v>117.55</v>
       </c>
       <c r="E239" t="n">
-        <v>35.05</v>
+        <v>10.47</v>
       </c>
       <c r="F239" t="n">
-        <v>3.52767</v>
+        <v>-0.56235</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>199.3</v>
+        <v>67.7</v>
       </c>
       <c r="D240" t="n">
-        <v>351.81</v>
+        <v>98.22</v>
       </c>
       <c r="E240" t="n">
-        <v>76.52</v>
+        <v>45.08</v>
       </c>
       <c r="F240" t="n">
-        <v>-1.44191</v>
+        <v>0.47423</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>73.13</v>
+        <v>14</v>
       </c>
       <c r="D241" t="n">
-        <v>95.43000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="E241" t="n">
-        <v>30.49</v>
+        <v>5.71</v>
       </c>
       <c r="F241" t="n">
-        <v>0.43563</v>
+        <v>0.00993</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>52.5</v>
+        <v>7.63</v>
       </c>
       <c r="D242" t="n">
-        <v>79.26000000000001</v>
+        <v>11.15</v>
       </c>
       <c r="E242" t="n">
-        <v>50.97</v>
+        <v>46.13</v>
       </c>
       <c r="F242" t="n">
-        <v>4.37139</v>
+        <v>0.16553</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>131.47</v>
+        <v>87.98</v>
       </c>
       <c r="D243" t="n">
-        <v>214.07</v>
+        <v>108.03</v>
       </c>
       <c r="E243" t="n">
-        <v>62.83</v>
+        <v>22.79</v>
       </c>
       <c r="F243" t="n">
-        <v>0.91734</v>
+        <v>0.75809</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>41.19</v>
+        <v>92.39</v>
       </c>
       <c r="D244" t="n">
-        <v>97.19</v>
+        <v>242.49</v>
       </c>
       <c r="E244" t="n">
-        <v>135.96</v>
+        <v>162.45</v>
       </c>
       <c r="F244" t="n">
-        <v>2.31858</v>
+        <v>5.44723</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>258.08</v>
+        <v>147.02</v>
       </c>
       <c r="D245" t="n">
-        <v>290.05</v>
+        <v>375.09</v>
       </c>
       <c r="E245" t="n">
-        <v>12.39</v>
+        <v>155.13</v>
       </c>
       <c r="F245" t="n">
-        <v>0.8742</v>
+        <v>1.92246</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>196.04</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D246" t="n">
-        <v>493.41</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="E246" t="n">
-        <v>151.69</v>
+        <v>17.6</v>
       </c>
       <c r="F246" t="n">
-        <v>9.84099</v>
+        <v>-0.25539</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>19.02</v>
+        <v>91.37</v>
       </c>
       <c r="D247" t="n">
-        <v>27.24</v>
+        <v>121.47</v>
       </c>
       <c r="E247" t="n">
-        <v>43.22</v>
+        <v>32.94</v>
       </c>
       <c r="F247" t="n">
-        <v>0.27865</v>
+        <v>0.12704</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>16.32</v>
+        <v>92.42</v>
       </c>
       <c r="D248" t="n">
-        <v>23.89</v>
+        <v>106.42</v>
       </c>
       <c r="E248" t="n">
-        <v>46.38</v>
+        <v>15.15</v>
       </c>
       <c r="F248" t="n">
-        <v>0.235</v>
+        <v>0.38316</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>284.79</v>
+        <v>295.52</v>
       </c>
       <c r="D249" t="n">
-        <v>424.24</v>
+        <v>375.62</v>
       </c>
       <c r="E249" t="n">
-        <v>48.97</v>
+        <v>27.1</v>
       </c>
       <c r="F249" t="n">
-        <v>5.01403</v>
+        <v>0.11189</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>107.27</v>
+        <v>525.72</v>
       </c>
       <c r="D250" t="n">
-        <v>136.18</v>
+        <v>670.24</v>
       </c>
       <c r="E250" t="n">
-        <v>26.95</v>
+        <v>27.49</v>
       </c>
       <c r="F250" t="n">
-        <v>1.00255</v>
+        <v>21.58203</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>67.39</v>
+        <v>3.42</v>
       </c>
       <c r="D251" t="n">
-        <v>93.43000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="E251" t="n">
-        <v>38.64</v>
+        <v>47.95</v>
       </c>
       <c r="F251" t="n">
-        <v>0.55682</v>
+        <v>0.09043</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>65.16</v>
+        <v>52.49</v>
       </c>
       <c r="D252" t="n">
-        <v>114.33</v>
+        <v>55.78</v>
       </c>
       <c r="E252" t="n">
-        <v>75.45999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="F252" t="n">
-        <v>2.2454</v>
+        <v>-0.04614</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>24.77</v>
+        <v>153.68</v>
       </c>
       <c r="D253" t="n">
-        <v>36.96</v>
+        <v>171.67</v>
       </c>
       <c r="E253" t="n">
-        <v>49.21</v>
+        <v>11.71</v>
       </c>
       <c r="F253" t="n">
-        <v>0.4117</v>
+        <v>-0.33974</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>273.5</v>
+        <v>125.78</v>
       </c>
       <c r="D254" t="n">
-        <v>349.39</v>
+        <v>143.79</v>
       </c>
       <c r="E254" t="n">
-        <v>27.75</v>
+        <v>14.32</v>
       </c>
       <c r="F254" t="n">
-        <v>-1.43004</v>
+        <v>-0.04365</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>204.77</v>
+        <v>24.24</v>
       </c>
       <c r="D255" t="n">
-        <v>274.99</v>
+        <v>30.44</v>
       </c>
       <c r="E255" t="n">
-        <v>34.29</v>
+        <v>25.58</v>
       </c>
       <c r="F255" t="n">
-        <v>0.55032</v>
+        <v>0.00578</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>273.14</v>
+        <v>23.77</v>
       </c>
       <c r="D256" t="n">
-        <v>345.71</v>
+        <v>29.05</v>
       </c>
       <c r="E256" t="n">
-        <v>26.57</v>
+        <v>22.21</v>
       </c>
       <c r="F256" t="n">
-        <v>-1.43948</v>
+        <v>0.28593</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>29.16</v>
+        <v>22.3</v>
       </c>
       <c r="D257" t="n">
-        <v>39.94</v>
+        <v>35.02</v>
       </c>
       <c r="E257" t="n">
-        <v>36.97</v>
+        <v>57.04</v>
       </c>
       <c r="F257" t="n">
-        <v>0.01199</v>
+        <v>0.52819</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>119.51</v>
+        <v>243.35</v>
       </c>
       <c r="D258" t="n">
-        <v>257.05</v>
+        <v>365</v>
       </c>
       <c r="E258" t="n">
-        <v>115.09</v>
+        <v>49.99</v>
       </c>
       <c r="F258" t="n">
-        <v>12.83332</v>
+        <v>3.17586</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>166</v>
+        <v>317.93</v>
       </c>
       <c r="D259" t="n">
-        <v>407.02</v>
+        <v>379.55</v>
       </c>
       <c r="E259" t="n">
-        <v>145.19</v>
+        <v>19.38</v>
       </c>
       <c r="F259" t="n">
-        <v>4.5493</v>
+        <v>0.46956</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>12.96</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D260" t="n">
-        <v>16.66</v>
+        <v>95.88</v>
       </c>
       <c r="E260" t="n">
-        <v>28.55</v>
+        <v>31.52</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.0515</v>
+        <v>0.94208</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>26.41</v>
+        <v>3.93</v>
       </c>
       <c r="D261" t="n">
-        <v>41.02</v>
+        <v>5.83</v>
       </c>
       <c r="E261" t="n">
-        <v>55.32</v>
+        <v>48.35</v>
       </c>
       <c r="F261" t="n">
-        <v>1.68935</v>
+        <v>0.11582</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>8.609999999999999</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D262" t="n">
-        <v>21.9</v>
+        <v>118.37</v>
       </c>
       <c r="E262" t="n">
-        <v>154.36</v>
+        <v>36.04</v>
       </c>
       <c r="F262" t="n">
-        <v>0.80893</v>
+        <v>1.18624</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>22.61</v>
+        <v>163.37</v>
       </c>
       <c r="D263" t="n">
-        <v>55.41</v>
+        <v>258.82</v>
       </c>
       <c r="E263" t="n">
-        <v>145.07</v>
+        <v>58.43</v>
       </c>
       <c r="F263" t="n">
-        <v>1.53437</v>
+        <v>0.25232</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>97.52</v>
+        <v>284.93</v>
       </c>
       <c r="D264" t="n">
-        <v>132.88</v>
+        <v>407.75</v>
       </c>
       <c r="E264" t="n">
-        <v>36.26</v>
+        <v>43.11</v>
       </c>
       <c r="F264" t="n">
-        <v>2.17585</v>
+        <v>0.7672099999999999</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>59.66</v>
+        <v>35.34</v>
       </c>
       <c r="D265" t="n">
-        <v>84.11</v>
+        <v>53.97</v>
       </c>
       <c r="E265" t="n">
-        <v>40.98</v>
+        <v>52.72</v>
       </c>
       <c r="F265" t="n">
-        <v>1.58777</v>
+        <v>0.84994</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>57.45</v>
+        <v>289.16</v>
       </c>
       <c r="D266" t="n">
-        <v>70.54000000000001</v>
+        <v>417.09</v>
       </c>
       <c r="E266" t="n">
-        <v>22.79</v>
+        <v>44.24</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.19886</v>
+        <v>0.82443</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>90.01000000000001</v>
+        <v>157.12</v>
       </c>
       <c r="D267" t="n">
-        <v>100.36</v>
+        <v>262.48</v>
       </c>
       <c r="E267" t="n">
-        <v>11.5</v>
+        <v>67.06</v>
       </c>
       <c r="F267" t="n">
-        <v>0.11228</v>
+        <v>2.10792</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>69.3</v>
+        <v>117.67</v>
       </c>
       <c r="D268" t="n">
-        <v>83.54000000000001</v>
+        <v>222.29</v>
       </c>
       <c r="E268" t="n">
-        <v>20.55</v>
+        <v>88.91</v>
       </c>
       <c r="F268" t="n">
-        <v>0.20672</v>
+        <v>0.07779</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>28.35</v>
+        <v>7.58</v>
       </c>
       <c r="D269" t="n">
-        <v>38.72</v>
+        <v>10.61</v>
       </c>
       <c r="E269" t="n">
-        <v>36.58</v>
+        <v>39.97</v>
       </c>
       <c r="F269" t="n">
-        <v>0.29357</v>
+        <v>0.17809</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>31.8</v>
+        <v>213.28</v>
       </c>
       <c r="D270" t="n">
-        <v>69.41</v>
+        <v>286.11</v>
       </c>
       <c r="E270" t="n">
-        <v>118.27</v>
+        <v>34.15</v>
       </c>
       <c r="F270" t="n">
-        <v>0.31551</v>
+        <v>0.03034</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>279.73</v>
+        <v>41.53</v>
       </c>
       <c r="D271" t="n">
-        <v>411.49</v>
+        <v>56.9</v>
       </c>
       <c r="E271" t="n">
-        <v>47.1</v>
+        <v>37.01</v>
       </c>
       <c r="F271" t="n">
-        <v>3.73943</v>
+        <v>0.18075</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>92.42</v>
+        <v>182.65</v>
       </c>
       <c r="D272" t="n">
-        <v>108.59</v>
+        <v>350.78</v>
       </c>
       <c r="E272" t="n">
-        <v>17.5</v>
+        <v>92.05</v>
       </c>
       <c r="F272" t="n">
-        <v>0.1877</v>
+        <v>5.93408</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,22 +6964,22 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>91.37</v>
+        <v>61.37</v>
       </c>
       <c r="D273" t="n">
-        <v>120.93</v>
+        <v>80.53</v>
       </c>
       <c r="E273" t="n">
-        <v>32.35</v>
+        <v>31.22</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.10485</v>
+        <v>0.10797</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>243.35</v>
+        <v>20.72</v>
       </c>
       <c r="D274" t="n">
-        <v>355.2</v>
+        <v>24.64</v>
       </c>
       <c r="E274" t="n">
-        <v>45.96</v>
+        <v>18.92</v>
       </c>
       <c r="F274" t="n">
-        <v>0.55648</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>182.65</v>
+        <v>110.24</v>
       </c>
       <c r="D275" t="n">
-        <v>341.79</v>
+        <v>150.27</v>
       </c>
       <c r="E275" t="n">
-        <v>87.13</v>
+        <v>36.31</v>
       </c>
       <c r="F275" t="n">
-        <v>4.40399</v>
+        <v>-0.85395</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>10.65</v>
+        <v>121.84</v>
       </c>
       <c r="D276" t="n">
-        <v>14.74</v>
+        <v>159.63</v>
       </c>
       <c r="E276" t="n">
-        <v>38.4</v>
+        <v>31.02</v>
       </c>
       <c r="F276" t="n">
-        <v>0.05009</v>
+        <v>1.3023</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,1192 +7060,160 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>39.84</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D277" t="n">
-        <v>58.53</v>
+        <v>156.62</v>
       </c>
       <c r="E277" t="n">
-        <v>46.91</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="F277" t="n">
-        <v>-0.08142000000000001</v>
+        <v>0.27415</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>61.37</v>
+        <v>95.48</v>
       </c>
       <c r="D278" t="n">
-        <v>80.23</v>
+        <v>111.5</v>
       </c>
       <c r="E278" t="n">
-        <v>30.73</v>
+        <v>16.78</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.09644999999999999</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>284.93</v>
+        <v>27.55</v>
       </c>
       <c r="D279" t="n">
-        <v>412.56</v>
+        <v>33.78</v>
       </c>
       <c r="E279" t="n">
-        <v>44.79</v>
+        <v>22.61</v>
       </c>
       <c r="F279" t="n">
-        <v>0.67323</v>
+        <v>-0.15662</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>33.63</v>
+        <v>17.13</v>
       </c>
       <c r="D280" t="n">
-        <v>43.55</v>
+        <v>43.01</v>
       </c>
       <c r="E280" t="n">
-        <v>29.5</v>
+        <v>151.08</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.00236</v>
+        <v>0.30712</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>AXSM</t>
+          <t>FMX</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>156.35</v>
+        <v>106.96</v>
       </c>
       <c r="D281" t="n">
-        <v>216.58</v>
+        <v>121.6</v>
       </c>
       <c r="E281" t="n">
-        <v>38.52</v>
+        <v>13.69</v>
       </c>
       <c r="F281" t="n">
-        <v>1.76572</v>
+        <v>-0.38552</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>71.42</v>
+        <v>63.78</v>
       </c>
       <c r="D282" t="n">
-        <v>78.89</v>
+        <v>69.81</v>
       </c>
       <c r="E282" t="n">
-        <v>10.46</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.24064</v>
+        <v>0.43847</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>87.01000000000001</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D283" t="n">
-        <v>116.9</v>
+        <v>172.45</v>
       </c>
       <c r="E283" t="n">
-        <v>34.35</v>
+        <v>72.47</v>
       </c>
       <c r="F283" t="n">
-        <v>0.85321</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="D284" t="n">
-        <v>375.28</v>
-      </c>
-      <c r="E284" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="F284" t="n">
-        <v>-0.74265</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>NMR</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="D285" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="E285" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="F285" t="n">
-        <v>0.17999</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>ZION</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="D286" t="n">
-        <v>69.18000000000001</v>
-      </c>
-      <c r="E286" t="n">
-        <v>24.87</v>
-      </c>
-      <c r="F286" t="n">
-        <v>-0.03903</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>525.72</v>
-      </c>
-      <c r="D287" t="n">
-        <v>665.6</v>
-      </c>
-      <c r="E287" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="F287" t="n">
-        <v>22.11172</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>CINF</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>153.68</v>
-      </c>
-      <c r="D288" t="n">
-        <v>172.02</v>
-      </c>
-      <c r="E288" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="F288" t="n">
-        <v>-0.63445</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>GGB</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="D289" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="E289" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="F289" t="n">
-        <v>0.09469</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>BUD</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>67.56999999999999</v>
-      </c>
-      <c r="D290" t="n">
-        <v>79.81999999999999</v>
-      </c>
-      <c r="E290" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="F290" t="n">
-        <v>-0.43807</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>AES</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
-        <v>14</v>
-      </c>
-      <c r="D291" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="E291" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="F291" t="n">
-        <v>0.01308</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>147.02</v>
-      </c>
-      <c r="D292" t="n">
-        <v>373.94</v>
-      </c>
-      <c r="E292" t="n">
-        <v>154.35</v>
-      </c>
-      <c r="F292" t="n">
-        <v>-2.08465</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>RDDT</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>121.84</v>
-      </c>
-      <c r="D293" t="n">
-        <v>162.38</v>
-      </c>
-      <c r="E293" t="n">
-        <v>33.27</v>
-      </c>
-      <c r="F293" t="n">
-        <v>0.05096</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>UNM</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="D294" t="n">
-        <v>94.92</v>
-      </c>
-      <c r="E294" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="F294" t="n">
-        <v>0.7454499999999999</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>SNAP</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="D295" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E295" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="F295" t="n">
-        <v>0.07327</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>285.27</v>
-      </c>
-      <c r="D296" t="n">
-        <v>378.05</v>
-      </c>
-      <c r="E296" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="F296" t="n">
-        <v>1.30077</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>202.71</v>
-      </c>
-      <c r="D297" t="n">
-        <v>258.48</v>
-      </c>
-      <c r="E297" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="F297" t="n">
-        <v>-1.41316</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>317.93</v>
-      </c>
-      <c r="D298" t="n">
-        <v>379.54</v>
-      </c>
-      <c r="E298" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="F298" t="n">
-        <v>-0.71048</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>EQH</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="D299" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="E299" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="F299" t="n">
-        <v>0.74151</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>SNX</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>157.12</v>
-      </c>
-      <c r="D300" t="n">
-        <v>261.12</v>
-      </c>
-      <c r="E300" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="F300" t="n">
-        <v>1.88244</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="D301" t="n">
-        <v>97.75</v>
-      </c>
-      <c r="E301" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="F301" t="n">
-        <v>0.25783</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>SPG-PJ</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="D302" t="n">
-        <v>56.12</v>
-      </c>
-      <c r="E302" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="F302" t="n">
-        <v>0.0173</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>ARCC</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="D303" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="E303" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="F303" t="n">
-        <v>-0.03105</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>EBAY</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>87.98</v>
-      </c>
-      <c r="D304" t="n">
-        <v>108.99</v>
-      </c>
-      <c r="E304" t="n">
-        <v>23.88</v>
-      </c>
-      <c r="F304" t="n">
-        <v>0.3621</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="D305" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="E305" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="F305" t="n">
-        <v>-0.14265</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>92.39</v>
-      </c>
-      <c r="D306" t="n">
-        <v>235.38</v>
-      </c>
-      <c r="E306" t="n">
-        <v>154.75</v>
-      </c>
-      <c r="F306" t="n">
-        <v>2.36905</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>AIZ</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>213.28</v>
-      </c>
-      <c r="D307" t="n">
-        <v>283.27</v>
-      </c>
-      <c r="E307" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="F307" t="n">
-        <v>-0.5633</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>WAT</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>289.16</v>
-      </c>
-      <c r="D308" t="n">
-        <v>410.01</v>
-      </c>
-      <c r="E308" t="n">
-        <v>41.79</v>
-      </c>
-      <c r="F308" t="n">
-        <v>-0.38142</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>CRBG</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="D309" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E309" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="F309" t="n">
-        <v>0.45747</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>MFG</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="D310" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="E310" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="F310" t="n">
-        <v>0.16084</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>87.15000000000001</v>
-      </c>
-      <c r="D311" t="n">
-        <v>157.45</v>
-      </c>
-      <c r="E311" t="n">
-        <v>80.67</v>
-      </c>
-      <c r="F311" t="n">
-        <v>-0.08858000000000001</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>DKNG</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="D312" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="E312" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="F312" t="n">
-        <v>-0.07012</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>CART</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>35.72</v>
-      </c>
-      <c r="D313" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="E313" t="n">
-        <v>38.52</v>
-      </c>
-      <c r="F313" t="n">
-        <v>-0.54794</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>AFG</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>125.78</v>
-      </c>
-      <c r="D314" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="E314" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="F314" t="n">
-        <v>-0.39666</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="D315" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="E315" t="n">
-        <v>153.65</v>
-      </c>
-      <c r="F315" t="n">
-        <v>0.28998</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>ICLR</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="D316" t="n">
-        <v>168.93</v>
-      </c>
-      <c r="E316" t="n">
-        <v>68.95</v>
-      </c>
-      <c r="F316" t="n">
-        <v>0.20101</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="D317" t="n">
-        <v>70.61</v>
-      </c>
-      <c r="E317" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="F317" t="n">
-        <v>0.28252</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>NWS</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>27.17</v>
-      </c>
-      <c r="D318" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="E318" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="F318" t="n">
-        <v>-0.24679</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>PAG</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>146.17</v>
-      </c>
-      <c r="D319" t="n">
-        <v>217.15</v>
-      </c>
-      <c r="E319" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="F319" t="n">
-        <v>0.01127</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>VRSN</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>241.14</v>
-      </c>
-      <c r="D320" t="n">
-        <v>298.6</v>
-      </c>
-      <c r="E320" t="n">
-        <v>23.83</v>
-      </c>
-      <c r="F320" t="n">
-        <v>1.64228</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>MDGL</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>445.04</v>
-      </c>
-      <c r="D321" t="n">
-        <v>540.0599999999999</v>
-      </c>
-      <c r="E321" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F321" t="n">
-        <v>2.20142</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>FMX</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>105.8</v>
-      </c>
-      <c r="D322" t="n">
-        <v>121.26</v>
-      </c>
-      <c r="E322" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="F322" t="n">
-        <v>-0.80715</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>KOF</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>94.23999999999999</v>
-      </c>
-      <c r="D323" t="n">
-        <v>112.01</v>
-      </c>
-      <c r="E323" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="F323" t="n">
-        <v>-0.19592</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>ABEV</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="D324" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E324" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="F324" t="n">
-        <v>0.02721</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>NWSA</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>23.97</v>
-      </c>
-      <c r="D325" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="E325" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="F325" t="n">
-        <v>-0.08098</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>WMG</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C326" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="D326" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E326" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="F326" t="n">
-        <v>0.22235</v>
+        <v>1.41425</v>
       </c>
     </row>
   </sheetData>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F283"/>
+  <dimension ref="A1:F284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -628,22 +628,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>298.59</v>
+        <v>5.67</v>
       </c>
       <c r="D9" t="n">
-        <v>331.46</v>
+        <v>6.83</v>
       </c>
       <c r="E9" t="n">
-        <v>11.01</v>
+        <v>20.46</v>
       </c>
       <c r="F9" t="n">
-        <v>1.09993</v>
+        <v>0.15101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.67</v>
+        <v>298.59</v>
       </c>
       <c r="D10" t="n">
-        <v>6.83</v>
+        <v>331.46</v>
       </c>
       <c r="E10" t="n">
-        <v>20.46</v>
+        <v>11.01</v>
       </c>
       <c r="F10" t="n">
-        <v>0.15101</v>
+        <v>1.09993</v>
       </c>
     </row>
     <row r="11">
@@ -691,7 +691,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.17</v>
+        <v>12.43</v>
       </c>
       <c r="D12" t="n">
-        <v>8.26</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="n">
-        <v>15.2</v>
+        <v>39.98</v>
       </c>
       <c r="F12" t="n">
-        <v>0.13953</v>
+        <v>0.8716699999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SBS</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.46</v>
+        <v>11.23</v>
       </c>
       <c r="D13" t="n">
-        <v>5.24</v>
+        <v>11.89</v>
       </c>
       <c r="E13" t="n">
-        <v>17.49</v>
+        <v>5.88</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08273999999999999</v>
+        <v>0.03859</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.23</v>
+        <v>7.17</v>
       </c>
       <c r="D15" t="n">
-        <v>11.89</v>
+        <v>8.26</v>
       </c>
       <c r="E15" t="n">
-        <v>5.88</v>
+        <v>15.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03859</v>
+        <v>0.13953</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>SBS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12.43</v>
+        <v>4.46</v>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>5.24</v>
       </c>
       <c r="E16" t="n">
-        <v>39.98</v>
+        <v>17.49</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8716699999999999</v>
+        <v>0.08273999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1099,7 +1099,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>146.38</v>
+        <v>332.02</v>
       </c>
       <c r="D29" t="n">
-        <v>215.67</v>
+        <v>377.16</v>
       </c>
       <c r="E29" t="n">
-        <v>47.34</v>
+        <v>13.6</v>
       </c>
       <c r="F29" t="n">
-        <v>0.62778</v>
+        <v>0.27114</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1132,22 +1132,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>332.02</v>
+        <v>27.14</v>
       </c>
       <c r="D30" t="n">
-        <v>377.16</v>
+        <v>31.56</v>
       </c>
       <c r="E30" t="n">
-        <v>13.6</v>
+        <v>16.29</v>
       </c>
       <c r="F30" t="n">
-        <v>0.27114</v>
+        <v>-0.13487</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>179.43</v>
+        <v>146.38</v>
       </c>
       <c r="D31" t="n">
-        <v>190.13</v>
+        <v>215.67</v>
       </c>
       <c r="E31" t="n">
-        <v>5.96</v>
+        <v>47.34</v>
       </c>
       <c r="F31" t="n">
-        <v>0.43388</v>
+        <v>0.62778</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1180,22 +1180,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.14</v>
+        <v>179.43</v>
       </c>
       <c r="D32" t="n">
-        <v>31.56</v>
+        <v>190.13</v>
       </c>
       <c r="E32" t="n">
-        <v>16.29</v>
+        <v>5.96</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.13487</v>
+        <v>0.43388</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1204,22 +1204,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>205.77</v>
+        <v>25.99</v>
       </c>
       <c r="D33" t="n">
-        <v>248.37</v>
+        <v>37.63</v>
       </c>
       <c r="E33" t="n">
-        <v>20.7</v>
+        <v>44.79</v>
       </c>
       <c r="F33" t="n">
-        <v>3.26641</v>
+        <v>0.74041</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.99</v>
+        <v>205.77</v>
       </c>
       <c r="D34" t="n">
-        <v>37.63</v>
+        <v>248.37</v>
       </c>
       <c r="E34" t="n">
-        <v>44.79</v>
+        <v>20.7</v>
       </c>
       <c r="F34" t="n">
-        <v>0.74041</v>
+        <v>3.26641</v>
       </c>
     </row>
     <row r="35">
@@ -1531,7 +1531,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1540,22 +1540,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>53.57</v>
+        <v>165.69</v>
       </c>
       <c r="D47" t="n">
-        <v>71.87</v>
+        <v>217.77</v>
       </c>
       <c r="E47" t="n">
-        <v>34.16</v>
+        <v>31.43</v>
       </c>
       <c r="F47" t="n">
-        <v>0.94957</v>
+        <v>3.21866</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1564,22 +1564,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>45.57</v>
+        <v>15.99</v>
       </c>
       <c r="D48" t="n">
-        <v>56.66</v>
+        <v>21.77</v>
       </c>
       <c r="E48" t="n">
-        <v>24.34</v>
+        <v>36.15</v>
       </c>
       <c r="F48" t="n">
-        <v>0.49648</v>
+        <v>0.6551900000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1588,22 +1588,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>41.99</v>
+        <v>51.98</v>
       </c>
       <c r="D49" t="n">
-        <v>51.45</v>
+        <v>66.97</v>
       </c>
       <c r="E49" t="n">
-        <v>22.53</v>
+        <v>28.84</v>
       </c>
       <c r="F49" t="n">
-        <v>0.50723</v>
+        <v>0.22746</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PBR-A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>40.25</v>
+        <v>14.49</v>
       </c>
       <c r="D50" t="n">
-        <v>51.33</v>
+        <v>19.57</v>
       </c>
       <c r="E50" t="n">
-        <v>27.53</v>
+        <v>35.06</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9265099999999999</v>
+        <v>0.58352</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>171.96</v>
+        <v>38.92</v>
       </c>
       <c r="D51" t="n">
-        <v>211.53</v>
+        <v>51.55</v>
       </c>
       <c r="E51" t="n">
-        <v>23.01</v>
+        <v>32.45</v>
       </c>
       <c r="F51" t="n">
-        <v>1.93053</v>
+        <v>0.30504</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>104.89</v>
+        <v>47.94</v>
       </c>
       <c r="D52" t="n">
-        <v>121.76</v>
+        <v>63.52</v>
       </c>
       <c r="E52" t="n">
-        <v>16.08</v>
+        <v>32.5</v>
       </c>
       <c r="F52" t="n">
-        <v>1.74063</v>
+        <v>0.82646</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,22 +1684,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>47.94</v>
+        <v>53.57</v>
       </c>
       <c r="D53" t="n">
-        <v>63.52</v>
+        <v>71.87</v>
       </c>
       <c r="E53" t="n">
-        <v>32.5</v>
+        <v>34.16</v>
       </c>
       <c r="F53" t="n">
-        <v>0.82646</v>
+        <v>0.94957</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1708,22 +1708,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38.92</v>
+        <v>45.57</v>
       </c>
       <c r="D54" t="n">
-        <v>51.55</v>
+        <v>56.66</v>
       </c>
       <c r="E54" t="n">
-        <v>32.45</v>
+        <v>24.34</v>
       </c>
       <c r="F54" t="n">
-        <v>0.30504</v>
+        <v>0.49648</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>110.99</v>
+        <v>171.96</v>
       </c>
       <c r="D55" t="n">
-        <v>135.35</v>
+        <v>211.53</v>
       </c>
       <c r="E55" t="n">
-        <v>21.95</v>
+        <v>23.01</v>
       </c>
       <c r="F55" t="n">
-        <v>0.19167</v>
+        <v>1.93053</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>31.87</v>
+        <v>17.93</v>
       </c>
       <c r="D56" t="n">
-        <v>47.41</v>
+        <v>24.49</v>
       </c>
       <c r="E56" t="n">
-        <v>48.76</v>
+        <v>36.59</v>
       </c>
       <c r="F56" t="n">
-        <v>1.0579</v>
+        <v>0.34403</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>14.49</v>
+        <v>36.15</v>
       </c>
       <c r="D57" t="n">
-        <v>19.57</v>
+        <v>46.96</v>
       </c>
       <c r="E57" t="n">
-        <v>35.06</v>
+        <v>29.9</v>
       </c>
       <c r="F57" t="n">
-        <v>0.58352</v>
+        <v>0.88425</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>165.69</v>
+        <v>110.99</v>
       </c>
       <c r="D58" t="n">
-        <v>217.77</v>
+        <v>135.35</v>
       </c>
       <c r="E58" t="n">
-        <v>31.43</v>
+        <v>21.95</v>
       </c>
       <c r="F58" t="n">
-        <v>3.21866</v>
+        <v>0.19167</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>51.98</v>
+        <v>104.89</v>
       </c>
       <c r="D59" t="n">
-        <v>66.97</v>
+        <v>121.76</v>
       </c>
       <c r="E59" t="n">
-        <v>28.84</v>
+        <v>16.08</v>
       </c>
       <c r="F59" t="n">
-        <v>0.22746</v>
+        <v>1.74063</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1852,22 +1852,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15.99</v>
+        <v>13.01</v>
       </c>
       <c r="D60" t="n">
-        <v>21.77</v>
+        <v>17.68</v>
       </c>
       <c r="E60" t="n">
-        <v>36.15</v>
+        <v>35.9</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6551900000000001</v>
+        <v>0.39546</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36.15</v>
+        <v>52.58</v>
       </c>
       <c r="D61" t="n">
-        <v>46.96</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>29.9</v>
+        <v>24.44</v>
       </c>
       <c r="F61" t="n">
-        <v>0.88425</v>
+        <v>0.00565</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>17.93</v>
+        <v>103.22</v>
       </c>
       <c r="D62" t="n">
-        <v>24.49</v>
+        <v>141.22</v>
       </c>
       <c r="E62" t="n">
-        <v>36.59</v>
+        <v>36.81</v>
       </c>
       <c r="F62" t="n">
-        <v>0.34403</v>
+        <v>2.28322</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>74.8</v>
+        <v>31.87</v>
       </c>
       <c r="D63" t="n">
-        <v>93.12</v>
+        <v>47.41</v>
       </c>
       <c r="E63" t="n">
-        <v>24.49</v>
+        <v>48.76</v>
       </c>
       <c r="F63" t="n">
-        <v>1.07146</v>
+        <v>1.0579</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>13.01</v>
+        <v>17.26</v>
       </c>
       <c r="D64" t="n">
-        <v>17.68</v>
+        <v>19.84</v>
       </c>
       <c r="E64" t="n">
-        <v>35.9</v>
+        <v>14.95</v>
       </c>
       <c r="F64" t="n">
-        <v>0.39546</v>
+        <v>0.16265</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>52.58</v>
+        <v>40.25</v>
       </c>
       <c r="D65" t="n">
-        <v>65.43000000000001</v>
+        <v>51.33</v>
       </c>
       <c r="E65" t="n">
-        <v>24.44</v>
+        <v>27.53</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00565</v>
+        <v>0.9265099999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>103.22</v>
+        <v>74.8</v>
       </c>
       <c r="D66" t="n">
-        <v>141.22</v>
+        <v>93.12</v>
       </c>
       <c r="E66" t="n">
-        <v>36.81</v>
+        <v>24.49</v>
       </c>
       <c r="F66" t="n">
-        <v>2.28322</v>
+        <v>1.07146</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2020,16 +2020,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>17.26</v>
+        <v>41.99</v>
       </c>
       <c r="D67" t="n">
-        <v>19.84</v>
+        <v>51.45</v>
       </c>
       <c r="E67" t="n">
-        <v>14.95</v>
+        <v>22.53</v>
       </c>
       <c r="F67" t="n">
-        <v>0.16265</v>
+        <v>0.50723</v>
       </c>
     </row>
     <row r="68">
@@ -2059,7 +2059,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2068,16 +2068,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>124.44</v>
+        <v>38.73</v>
       </c>
       <c r="D69" t="n">
-        <v>193.4</v>
+        <v>63.28</v>
       </c>
       <c r="E69" t="n">
-        <v>55.42</v>
+        <v>63.39</v>
       </c>
       <c r="F69" t="n">
-        <v>2.33628</v>
+        <v>0.3855</v>
       </c>
     </row>
     <row r="70">
@@ -2107,7 +2107,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2116,22 +2116,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38.73</v>
+        <v>124.44</v>
       </c>
       <c r="D71" t="n">
-        <v>63.28</v>
+        <v>193.4</v>
       </c>
       <c r="E71" t="n">
-        <v>63.39</v>
+        <v>55.42</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3855</v>
+        <v>2.33628</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>13.31</v>
+        <v>55.53</v>
       </c>
       <c r="D72" t="n">
-        <v>23.6</v>
+        <v>62.25</v>
       </c>
       <c r="E72" t="n">
-        <v>77.31</v>
+        <v>12.1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.58601</v>
+        <v>0.75354</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>55.53</v>
+        <v>13.31</v>
       </c>
       <c r="D73" t="n">
-        <v>62.25</v>
+        <v>23.6</v>
       </c>
       <c r="E73" t="n">
-        <v>12.1</v>
+        <v>77.31</v>
       </c>
       <c r="F73" t="n">
-        <v>0.75354</v>
+        <v>0.58601</v>
       </c>
     </row>
     <row r="74">
@@ -2203,7 +2203,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2212,22 +2212,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7.67</v>
+        <v>136.06</v>
       </c>
       <c r="D75" t="n">
-        <v>9.23</v>
+        <v>169.32</v>
       </c>
       <c r="E75" t="n">
-        <v>20.34</v>
+        <v>24.45</v>
       </c>
       <c r="F75" t="n">
-        <v>0.15642</v>
+        <v>1.98435</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2236,22 +2236,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>136.06</v>
+        <v>7.67</v>
       </c>
       <c r="D76" t="n">
-        <v>169.32</v>
+        <v>9.23</v>
       </c>
       <c r="E76" t="n">
-        <v>24.45</v>
+        <v>20.34</v>
       </c>
       <c r="F76" t="n">
-        <v>1.98435</v>
+        <v>0.15642</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2260,22 +2260,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>76.53</v>
+        <v>31.03</v>
       </c>
       <c r="D77" t="n">
-        <v>98.95</v>
+        <v>45.75</v>
       </c>
       <c r="E77" t="n">
-        <v>29.3</v>
+        <v>47.44</v>
       </c>
       <c r="F77" t="n">
-        <v>1.63317</v>
+        <v>0.94193</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2284,22 +2284,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>31.03</v>
+        <v>56.4</v>
       </c>
       <c r="D78" t="n">
-        <v>45.75</v>
+        <v>79.48</v>
       </c>
       <c r="E78" t="n">
-        <v>47.44</v>
+        <v>40.92</v>
       </c>
       <c r="F78" t="n">
-        <v>0.94193</v>
+        <v>2.00392</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2308,22 +2308,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>18.94</v>
+        <v>76.53</v>
       </c>
       <c r="D79" t="n">
-        <v>23.98</v>
+        <v>98.95</v>
       </c>
       <c r="E79" t="n">
-        <v>26.61</v>
+        <v>29.3</v>
       </c>
       <c r="F79" t="n">
-        <v>0.15742</v>
+        <v>1.63317</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2332,22 +2332,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>56.4</v>
+        <v>82.31</v>
       </c>
       <c r="D80" t="n">
-        <v>79.48</v>
+        <v>129.6</v>
       </c>
       <c r="E80" t="n">
-        <v>40.92</v>
+        <v>57.45</v>
       </c>
       <c r="F80" t="n">
-        <v>2.00392</v>
+        <v>2.83088</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>WDS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2356,22 +2356,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>82.31</v>
+        <v>18.94</v>
       </c>
       <c r="D81" t="n">
-        <v>129.6</v>
+        <v>23.98</v>
       </c>
       <c r="E81" t="n">
-        <v>57.45</v>
+        <v>26.61</v>
       </c>
       <c r="F81" t="n">
-        <v>2.83088</v>
+        <v>0.15742</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2380,22 +2380,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>44.39</v>
+        <v>107.27</v>
       </c>
       <c r="D82" t="n">
-        <v>60.34</v>
+        <v>172.56</v>
       </c>
       <c r="E82" t="n">
-        <v>35.93</v>
+        <v>60.87</v>
       </c>
       <c r="F82" t="n">
-        <v>0.25495</v>
+        <v>-0.66867</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2404,22 +2404,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>42.46</v>
+        <v>59.71</v>
       </c>
       <c r="D83" t="n">
-        <v>71.84999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="E83" t="n">
-        <v>69.22</v>
+        <v>34.08</v>
       </c>
       <c r="F83" t="n">
-        <v>1.88023</v>
+        <v>1.2886</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>59.71</v>
+        <v>42.46</v>
       </c>
       <c r="D84" t="n">
-        <v>80.06</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E84" t="n">
-        <v>34.08</v>
+        <v>69.22</v>
       </c>
       <c r="F84" t="n">
-        <v>1.2886</v>
+        <v>1.88023</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2452,22 +2452,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>166.5</v>
+        <v>352.83</v>
       </c>
       <c r="D85" t="n">
-        <v>195.47</v>
+        <v>497.12</v>
       </c>
       <c r="E85" t="n">
-        <v>17.4</v>
+        <v>40.9</v>
       </c>
       <c r="F85" t="n">
-        <v>1.03418</v>
+        <v>2.41856</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2476,22 +2476,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>107.27</v>
+        <v>44.39</v>
       </c>
       <c r="D86" t="n">
-        <v>172.56</v>
+        <v>60.34</v>
       </c>
       <c r="E86" t="n">
-        <v>60.87</v>
+        <v>35.93</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.66867</v>
+        <v>0.25495</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2500,22 +2500,22 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>136.68</v>
+        <v>170.28</v>
       </c>
       <c r="D87" t="n">
-        <v>156.99</v>
+        <v>241.96</v>
       </c>
       <c r="E87" t="n">
-        <v>14.86</v>
+        <v>42.1</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.72946</v>
+        <v>-1.37415</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2524,16 +2524,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>352.83</v>
+        <v>136.68</v>
       </c>
       <c r="D88" t="n">
-        <v>497.12</v>
+        <v>156.99</v>
       </c>
       <c r="E88" t="n">
-        <v>40.9</v>
+        <v>14.86</v>
       </c>
       <c r="F88" t="n">
-        <v>2.41856</v>
+        <v>-0.72946</v>
       </c>
     </row>
     <row r="89">
@@ -2563,7 +2563,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2572,16 +2572,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>170.28</v>
+        <v>166.5</v>
       </c>
       <c r="D90" t="n">
-        <v>241.96</v>
+        <v>195.47</v>
       </c>
       <c r="E90" t="n">
-        <v>42.1</v>
+        <v>17.4</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.37415</v>
+        <v>1.03418</v>
       </c>
     </row>
     <row r="91">
@@ -2611,7 +2611,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2620,22 +2620,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>62.12</v>
+        <v>10.51</v>
       </c>
       <c r="D92" t="n">
-        <v>79.97</v>
+        <v>15.29</v>
       </c>
       <c r="E92" t="n">
-        <v>28.73</v>
+        <v>45.48</v>
       </c>
       <c r="F92" t="n">
-        <v>0.93677</v>
+        <v>0.36599</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2644,22 +2644,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10.51</v>
+        <v>62.12</v>
       </c>
       <c r="D93" t="n">
-        <v>15.29</v>
+        <v>79.97</v>
       </c>
       <c r="E93" t="n">
-        <v>45.48</v>
+        <v>28.73</v>
       </c>
       <c r="F93" t="n">
-        <v>0.36599</v>
+        <v>0.93677</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>102.17</v>
+        <v>48.79</v>
       </c>
       <c r="D94" t="n">
-        <v>135.54</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>32.66</v>
+        <v>38.49</v>
       </c>
       <c r="F94" t="n">
-        <v>1.43815</v>
+        <v>0.33897</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2692,22 +2692,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>48.79</v>
+        <v>247.22</v>
       </c>
       <c r="D95" t="n">
-        <v>67.56999999999999</v>
+        <v>297.26</v>
       </c>
       <c r="E95" t="n">
-        <v>38.49</v>
+        <v>20.24</v>
       </c>
       <c r="F95" t="n">
-        <v>0.33897</v>
+        <v>2.46873</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2716,16 +2716,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>247.22</v>
+        <v>102.17</v>
       </c>
       <c r="D96" t="n">
-        <v>297.26</v>
+        <v>135.54</v>
       </c>
       <c r="E96" t="n">
-        <v>20.24</v>
+        <v>32.66</v>
       </c>
       <c r="F96" t="n">
-        <v>2.46873</v>
+        <v>1.43815</v>
       </c>
     </row>
     <row r="97">
@@ -2803,7 +2803,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2812,22 +2812,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>76.55</v>
+        <v>275.27</v>
       </c>
       <c r="D100" t="n">
-        <v>102.61</v>
+        <v>353.13</v>
       </c>
       <c r="E100" t="n">
-        <v>34.04</v>
+        <v>28.28</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.89647</v>
+        <v>-1.49134</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2836,22 +2836,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>74.98999999999999</v>
+        <v>140.71</v>
       </c>
       <c r="D101" t="n">
-        <v>102.38</v>
+        <v>185.92</v>
       </c>
       <c r="E101" t="n">
-        <v>36.52</v>
+        <v>32.13</v>
       </c>
       <c r="F101" t="n">
-        <v>1.20454</v>
+        <v>-0.65188</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2860,22 +2860,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>83.81999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>95.06</v>
+        <v>102.38</v>
       </c>
       <c r="E102" t="n">
-        <v>13.41</v>
+        <v>36.52</v>
       </c>
       <c r="F102" t="n">
-        <v>0.23447</v>
+        <v>1.20454</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2884,22 +2884,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>275.27</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D103" t="n">
-        <v>353.13</v>
+        <v>95.06</v>
       </c>
       <c r="E103" t="n">
-        <v>28.28</v>
+        <v>13.41</v>
       </c>
       <c r="F103" t="n">
-        <v>-1.49134</v>
+        <v>0.23447</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2908,16 +2908,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>140.71</v>
+        <v>76.55</v>
       </c>
       <c r="D104" t="n">
-        <v>185.92</v>
+        <v>102.61</v>
       </c>
       <c r="E104" t="n">
-        <v>32.13</v>
+        <v>34.04</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.65188</v>
+        <v>-0.89647</v>
       </c>
     </row>
     <row r="105">
@@ -2971,7 +2971,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2980,22 +2980,22 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>32.47</v>
+        <v>450.75</v>
       </c>
       <c r="D107" t="n">
-        <v>38.62</v>
+        <v>544.3200000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>18.94</v>
+        <v>20.76</v>
       </c>
       <c r="F107" t="n">
-        <v>0.35367</v>
+        <v>2.42297</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3004,22 +3004,22 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>450.75</v>
+        <v>48.87</v>
       </c>
       <c r="D108" t="n">
-        <v>544.3200000000001</v>
+        <v>58.8</v>
       </c>
       <c r="E108" t="n">
-        <v>20.76</v>
+        <v>20.32</v>
       </c>
       <c r="F108" t="n">
-        <v>2.42297</v>
+        <v>-0.23533</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3028,22 +3028,22 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>48.87</v>
+        <v>32.47</v>
       </c>
       <c r="D109" t="n">
-        <v>58.8</v>
+        <v>38.62</v>
       </c>
       <c r="E109" t="n">
-        <v>20.32</v>
+        <v>18.94</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.23533</v>
+        <v>0.35367</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>53.82</v>
+        <v>2.86</v>
       </c>
       <c r="D110" t="n">
-        <v>74.08</v>
+        <v>3.16</v>
       </c>
       <c r="E110" t="n">
-        <v>37.64</v>
+        <v>10.49</v>
       </c>
       <c r="F110" t="n">
-        <v>0.46228</v>
+        <v>0.02491</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3076,22 +3076,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>121.48</v>
+        <v>16.44</v>
       </c>
       <c r="D111" t="n">
-        <v>146.3</v>
+        <v>33.61</v>
       </c>
       <c r="E111" t="n">
-        <v>20.43</v>
+        <v>104.44</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1059</v>
+        <v>0.45364</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3100,22 +3100,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2.86</v>
+        <v>14.94</v>
       </c>
       <c r="D112" t="n">
-        <v>3.16</v>
+        <v>19.53</v>
       </c>
       <c r="E112" t="n">
-        <v>10.49</v>
+        <v>30.72</v>
       </c>
       <c r="F112" t="n">
-        <v>0.02491</v>
+        <v>0.51817</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3124,22 +3124,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>14.94</v>
+        <v>121.48</v>
       </c>
       <c r="D113" t="n">
-        <v>19.53</v>
+        <v>146.3</v>
       </c>
       <c r="E113" t="n">
-        <v>30.72</v>
+        <v>20.43</v>
       </c>
       <c r="F113" t="n">
-        <v>0.51817</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3148,22 +3148,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>19.82</v>
+        <v>53.82</v>
       </c>
       <c r="D114" t="n">
-        <v>25.46</v>
+        <v>74.08</v>
       </c>
       <c r="E114" t="n">
-        <v>28.46</v>
+        <v>37.64</v>
       </c>
       <c r="F114" t="n">
-        <v>0.29096</v>
+        <v>0.46228</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3172,16 +3172,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>16.44</v>
+        <v>19.82</v>
       </c>
       <c r="D115" t="n">
-        <v>33.61</v>
+        <v>25.46</v>
       </c>
       <c r="E115" t="n">
-        <v>104.44</v>
+        <v>28.46</v>
       </c>
       <c r="F115" t="n">
-        <v>0.45364</v>
+        <v>0.29096</v>
       </c>
     </row>
     <row r="116">
@@ -3235,7 +3235,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3244,22 +3244,22 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>195.11</v>
+        <v>15.03</v>
       </c>
       <c r="D118" t="n">
-        <v>248.36</v>
+        <v>18.7</v>
       </c>
       <c r="E118" t="n">
-        <v>27.29</v>
+        <v>24.42</v>
       </c>
       <c r="F118" t="n">
-        <v>0.6946099999999999</v>
+        <v>0.12759</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3268,22 +3268,22 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>15.03</v>
+        <v>140.19</v>
       </c>
       <c r="D119" t="n">
-        <v>18.7</v>
+        <v>146.67</v>
       </c>
       <c r="E119" t="n">
-        <v>24.42</v>
+        <v>4.62</v>
       </c>
       <c r="F119" t="n">
-        <v>0.12759</v>
+        <v>0.02814</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3292,22 +3292,22 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>140.19</v>
+        <v>195.11</v>
       </c>
       <c r="D120" t="n">
-        <v>146.67</v>
+        <v>248.36</v>
       </c>
       <c r="E120" t="n">
-        <v>4.62</v>
+        <v>27.29</v>
       </c>
       <c r="F120" t="n">
-        <v>0.02814</v>
+        <v>0.6946099999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3316,22 +3316,22 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>182.82</v>
+        <v>275.99</v>
       </c>
       <c r="D121" t="n">
-        <v>229.44</v>
+        <v>318.2</v>
       </c>
       <c r="E121" t="n">
-        <v>25.5</v>
+        <v>15.29</v>
       </c>
       <c r="F121" t="n">
-        <v>-1.30339</v>
+        <v>1.98323</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3340,22 +3340,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>275.99</v>
+        <v>23.85</v>
       </c>
       <c r="D122" t="n">
-        <v>318.2</v>
+        <v>34.15</v>
       </c>
       <c r="E122" t="n">
-        <v>15.29</v>
+        <v>43.19</v>
       </c>
       <c r="F122" t="n">
-        <v>1.98323</v>
+        <v>0.01267</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>23.85</v>
+        <v>277.69</v>
       </c>
       <c r="D123" t="n">
-        <v>34.15</v>
+        <v>328.7</v>
       </c>
       <c r="E123" t="n">
-        <v>43.19</v>
+        <v>18.37</v>
       </c>
       <c r="F123" t="n">
-        <v>0.01267</v>
+        <v>0.45735</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3388,22 +3388,22 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>73.75</v>
+        <v>182.82</v>
       </c>
       <c r="D124" t="n">
-        <v>93.75</v>
+        <v>229.44</v>
       </c>
       <c r="E124" t="n">
-        <v>27.12</v>
+        <v>25.5</v>
       </c>
       <c r="F124" t="n">
-        <v>0.46174</v>
+        <v>-1.30339</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>277.69</v>
+        <v>73.75</v>
       </c>
       <c r="D125" t="n">
-        <v>328.7</v>
+        <v>93.75</v>
       </c>
       <c r="E125" t="n">
-        <v>18.37</v>
+        <v>27.12</v>
       </c>
       <c r="F125" t="n">
-        <v>0.45735</v>
+        <v>0.46174</v>
       </c>
     </row>
     <row r="126">
@@ -3451,7 +3451,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3460,22 +3460,22 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>36.25</v>
+        <v>309.78</v>
       </c>
       <c r="D127" t="n">
-        <v>41.48</v>
+        <v>341.86</v>
       </c>
       <c r="E127" t="n">
-        <v>14.43</v>
+        <v>10.36</v>
       </c>
       <c r="F127" t="n">
-        <v>0.15456</v>
+        <v>-0.62071</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3484,22 +3484,22 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>309.78</v>
+        <v>36.25</v>
       </c>
       <c r="D128" t="n">
-        <v>341.86</v>
+        <v>41.48</v>
       </c>
       <c r="E128" t="n">
-        <v>10.36</v>
+        <v>14.43</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.62071</v>
+        <v>0.15456</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3508,22 +3508,22 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>63.54</v>
+        <v>190.4</v>
       </c>
       <c r="D129" t="n">
-        <v>71.28</v>
+        <v>221.31</v>
       </c>
       <c r="E129" t="n">
-        <v>12.18</v>
+        <v>16.23</v>
       </c>
       <c r="F129" t="n">
-        <v>0.374</v>
+        <v>0.59114</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>190.4</v>
+        <v>63.54</v>
       </c>
       <c r="D130" t="n">
-        <v>221.31</v>
+        <v>71.28</v>
       </c>
       <c r="E130" t="n">
-        <v>16.23</v>
+        <v>12.18</v>
       </c>
       <c r="F130" t="n">
-        <v>0.59114</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="131">
@@ -3619,7 +3619,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3628,22 +3628,22 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>438.34</v>
+        <v>161.91</v>
       </c>
       <c r="D134" t="n">
-        <v>641.39</v>
+        <v>209.36</v>
       </c>
       <c r="E134" t="n">
-        <v>46.32</v>
+        <v>29.31</v>
       </c>
       <c r="F134" t="n">
-        <v>3.85233</v>
+        <v>-1.52751</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3652,22 +3652,22 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>102.87</v>
+        <v>63.16</v>
       </c>
       <c r="D135" t="n">
-        <v>174.73</v>
+        <v>100.67</v>
       </c>
       <c r="E135" t="n">
-        <v>69.86</v>
+        <v>59.39</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.36801</v>
+        <v>1.35459</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3676,22 +3676,22 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>26.18</v>
+        <v>250.4</v>
       </c>
       <c r="D136" t="n">
-        <v>36.72</v>
+        <v>323.97</v>
       </c>
       <c r="E136" t="n">
-        <v>40.26</v>
+        <v>29.38</v>
       </c>
       <c r="F136" t="n">
-        <v>0.23738</v>
+        <v>-3.61611</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3700,22 +3700,22 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>186.61</v>
+        <v>102.87</v>
       </c>
       <c r="D137" t="n">
-        <v>247.08</v>
+        <v>174.73</v>
       </c>
       <c r="E137" t="n">
-        <v>32.4</v>
+        <v>69.86</v>
       </c>
       <c r="F137" t="n">
-        <v>0.19288</v>
+        <v>-0.36801</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3724,22 +3724,22 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>63.16</v>
+        <v>186.61</v>
       </c>
       <c r="D138" t="n">
-        <v>100.67</v>
+        <v>247.08</v>
       </c>
       <c r="E138" t="n">
-        <v>59.39</v>
+        <v>32.4</v>
       </c>
       <c r="F138" t="n">
-        <v>1.35459</v>
+        <v>0.19288</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3748,16 +3748,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>250.4</v>
+        <v>26.18</v>
       </c>
       <c r="D139" t="n">
-        <v>323.97</v>
+        <v>36.72</v>
       </c>
       <c r="E139" t="n">
-        <v>29.38</v>
+        <v>40.26</v>
       </c>
       <c r="F139" t="n">
-        <v>-3.61611</v>
+        <v>0.23738</v>
       </c>
     </row>
     <row r="140">
@@ -3787,7 +3787,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3796,22 +3796,22 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>161.91</v>
+        <v>73.42</v>
       </c>
       <c r="D141" t="n">
-        <v>209.36</v>
+        <v>89.72</v>
       </c>
       <c r="E141" t="n">
-        <v>29.31</v>
+        <v>22.2</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.52751</v>
+        <v>0.70402</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3820,16 +3820,16 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>73.42</v>
+        <v>438.34</v>
       </c>
       <c r="D142" t="n">
-        <v>89.72</v>
+        <v>641.39</v>
       </c>
       <c r="E142" t="n">
-        <v>22.2</v>
+        <v>46.32</v>
       </c>
       <c r="F142" t="n">
-        <v>0.70402</v>
+        <v>3.85233</v>
       </c>
     </row>
     <row r="143">
@@ -3979,7 +3979,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3988,16 +3988,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>12.64</v>
+        <v>255.54</v>
       </c>
       <c r="D149" t="n">
-        <v>18.26</v>
+        <v>365.08</v>
       </c>
       <c r="E149" t="n">
-        <v>44.46</v>
+        <v>42.87</v>
       </c>
       <c r="F149" t="n">
-        <v>0.26064</v>
+        <v>2.95635</v>
       </c>
     </row>
     <row r="150">
@@ -4027,7 +4027,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BIO-B</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4036,16 +4036,16 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>255.54</v>
+        <v>12.64</v>
       </c>
       <c r="D151" t="n">
-        <v>365.08</v>
+        <v>18.26</v>
       </c>
       <c r="E151" t="n">
-        <v>42.87</v>
+        <v>44.46</v>
       </c>
       <c r="F151" t="n">
-        <v>2.95635</v>
+        <v>0.26064</v>
       </c>
     </row>
     <row r="152">
@@ -4195,7 +4195,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4204,22 +4204,22 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>82.26000000000001</v>
+        <v>156.66</v>
       </c>
       <c r="D158" t="n">
-        <v>140.19</v>
+        <v>269.67</v>
       </c>
       <c r="E158" t="n">
-        <v>70.42</v>
+        <v>72.14</v>
       </c>
       <c r="F158" t="n">
-        <v>1.63417</v>
+        <v>3.05682</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4228,16 +4228,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>156.66</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="D159" t="n">
-        <v>269.67</v>
+        <v>140.19</v>
       </c>
       <c r="E159" t="n">
-        <v>72.14</v>
+        <v>70.42</v>
       </c>
       <c r="F159" t="n">
-        <v>3.05682</v>
+        <v>1.63417</v>
       </c>
     </row>
     <row r="160">
@@ -4387,7 +4387,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4396,22 +4396,22 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>155.75</v>
+        <v>20.96</v>
       </c>
       <c r="D166" t="n">
-        <v>264.93</v>
+        <v>25.77</v>
       </c>
       <c r="E166" t="n">
-        <v>70.09999999999999</v>
+        <v>22.95</v>
       </c>
       <c r="F166" t="n">
-        <v>5.58905</v>
+        <v>0.24889</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4420,16 +4420,16 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>20.96</v>
+        <v>155.75</v>
       </c>
       <c r="D167" t="n">
-        <v>25.77</v>
+        <v>264.93</v>
       </c>
       <c r="E167" t="n">
-        <v>22.95</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F167" t="n">
-        <v>0.24889</v>
+        <v>5.58905</v>
       </c>
     </row>
     <row r="168">
@@ -4459,7 +4459,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4468,22 +4468,22 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>128.43</v>
+        <v>213.69</v>
       </c>
       <c r="D169" t="n">
-        <v>153.74</v>
+        <v>410.84</v>
       </c>
       <c r="E169" t="n">
-        <v>19.71</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F169" t="n">
-        <v>1.24056</v>
+        <v>10.41305</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4492,22 +4492,22 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>213.69</v>
+        <v>223.65</v>
       </c>
       <c r="D170" t="n">
-        <v>410.84</v>
+        <v>397.04</v>
       </c>
       <c r="E170" t="n">
-        <v>92.26000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="F170" t="n">
-        <v>10.41305</v>
+        <v>11.66693</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4516,22 +4516,22 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>223.65</v>
+        <v>128.43</v>
       </c>
       <c r="D171" t="n">
-        <v>397.04</v>
+        <v>153.74</v>
       </c>
       <c r="E171" t="n">
-        <v>77.53</v>
+        <v>19.71</v>
       </c>
       <c r="F171" t="n">
-        <v>11.66693</v>
+        <v>1.24056</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4540,22 +4540,22 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>66.95</v>
+        <v>18.71</v>
       </c>
       <c r="D172" t="n">
-        <v>86.61</v>
+        <v>21.33</v>
       </c>
       <c r="E172" t="n">
-        <v>29.37</v>
+        <v>14</v>
       </c>
       <c r="F172" t="n">
-        <v>1.36817</v>
+        <v>0.09087000000000001</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4564,22 +4564,22 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>18.71</v>
+        <v>66.95</v>
       </c>
       <c r="D173" t="n">
-        <v>21.33</v>
+        <v>86.61</v>
       </c>
       <c r="E173" t="n">
-        <v>14</v>
+        <v>29.37</v>
       </c>
       <c r="F173" t="n">
-        <v>0.09087000000000001</v>
+        <v>1.36817</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4588,22 +4588,22 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>32.36</v>
+        <v>151.43</v>
       </c>
       <c r="D174" t="n">
-        <v>55.17</v>
+        <v>266.62</v>
       </c>
       <c r="E174" t="n">
-        <v>70.48999999999999</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F174" t="n">
-        <v>0.76689</v>
+        <v>1.96202</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4612,22 +4612,22 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>43.81</v>
+        <v>105.37</v>
       </c>
       <c r="D175" t="n">
-        <v>103.55</v>
+        <v>230.27</v>
       </c>
       <c r="E175" t="n">
-        <v>136.36</v>
+        <v>118.53</v>
       </c>
       <c r="F175" t="n">
-        <v>1.02235</v>
+        <v>-1.24495</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4636,22 +4636,22 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>62.93</v>
+        <v>120.88</v>
       </c>
       <c r="D176" t="n">
-        <v>190.45</v>
+        <v>209.62</v>
       </c>
       <c r="E176" t="n">
-        <v>202.64</v>
+        <v>73.41</v>
       </c>
       <c r="F176" t="n">
-        <v>7.34012</v>
+        <v>-0.40223</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4660,22 +4660,22 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>120.88</v>
+        <v>62.93</v>
       </c>
       <c r="D177" t="n">
-        <v>209.62</v>
+        <v>190.45</v>
       </c>
       <c r="E177" t="n">
-        <v>73.41</v>
+        <v>202.64</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.40223</v>
+        <v>7.34012</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4684,22 +4684,22 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>83</v>
+        <v>76.7</v>
       </c>
       <c r="D178" t="n">
-        <v>141.9</v>
+        <v>172.37</v>
       </c>
       <c r="E178" t="n">
-        <v>70.95999999999999</v>
+        <v>124.73</v>
       </c>
       <c r="F178" t="n">
-        <v>1.71804</v>
+        <v>2.05425</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4708,22 +4708,22 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>105.37</v>
+        <v>166.99</v>
       </c>
       <c r="D179" t="n">
-        <v>230.27</v>
+        <v>327.23</v>
       </c>
       <c r="E179" t="n">
-        <v>118.53</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="F179" t="n">
-        <v>-1.24495</v>
+        <v>9.443759999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4732,22 +4732,22 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>188.79</v>
+        <v>34.41</v>
       </c>
       <c r="D180" t="n">
-        <v>276.53</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E180" t="n">
-        <v>46.47</v>
+        <v>97.59</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.99091</v>
+        <v>0.22691</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4756,22 +4756,22 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>112.5</v>
+        <v>10.49</v>
       </c>
       <c r="D181" t="n">
-        <v>190.67</v>
+        <v>19.98</v>
       </c>
       <c r="E181" t="n">
-        <v>69.48</v>
+        <v>90.47</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.51289</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4780,22 +4780,22 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>34.41</v>
+        <v>57.15</v>
       </c>
       <c r="D182" t="n">
-        <v>67.98999999999999</v>
+        <v>189.81</v>
       </c>
       <c r="E182" t="n">
-        <v>97.59</v>
+        <v>232.13</v>
       </c>
       <c r="F182" t="n">
-        <v>0.22691</v>
+        <v>4.93853</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4804,22 +4804,22 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>117.65</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D183" t="n">
-        <v>242.16</v>
+        <v>175.65</v>
       </c>
       <c r="E183" t="n">
-        <v>105.83</v>
+        <v>123.47</v>
       </c>
       <c r="F183" t="n">
-        <v>1.79379</v>
+        <v>1.12337</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4828,22 +4828,22 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>57.15</v>
+        <v>118.05</v>
       </c>
       <c r="D184" t="n">
-        <v>189.81</v>
+        <v>193.89</v>
       </c>
       <c r="E184" t="n">
-        <v>232.13</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="F184" t="n">
-        <v>4.93853</v>
+        <v>2.28457</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4852,22 +4852,22 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>118.05</v>
+        <v>188.79</v>
       </c>
       <c r="D185" t="n">
-        <v>193.89</v>
+        <v>276.53</v>
       </c>
       <c r="E185" t="n">
-        <v>64.23999999999999</v>
+        <v>46.47</v>
       </c>
       <c r="F185" t="n">
-        <v>2.28457</v>
+        <v>-0.99091</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4876,22 +4876,22 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>18.26</v>
+        <v>32.36</v>
       </c>
       <c r="D186" t="n">
-        <v>33.82</v>
+        <v>55.17</v>
       </c>
       <c r="E186" t="n">
-        <v>85.20999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="F186" t="n">
-        <v>1.18337</v>
+        <v>0.76689</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4900,22 +4900,22 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>25.85</v>
+        <v>83</v>
       </c>
       <c r="D187" t="n">
-        <v>41.65</v>
+        <v>141.9</v>
       </c>
       <c r="E187" t="n">
-        <v>61.12</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F187" t="n">
-        <v>0.40151</v>
+        <v>1.71804</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4924,22 +4924,22 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>78.59999999999999</v>
+        <v>18.26</v>
       </c>
       <c r="D188" t="n">
-        <v>175.65</v>
+        <v>33.82</v>
       </c>
       <c r="E188" t="n">
-        <v>123.47</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="F188" t="n">
-        <v>1.12337</v>
+        <v>1.18337</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4948,22 +4948,22 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>10.49</v>
+        <v>112.5</v>
       </c>
       <c r="D189" t="n">
-        <v>19.98</v>
+        <v>190.67</v>
       </c>
       <c r="E189" t="n">
-        <v>90.47</v>
+        <v>69.48</v>
       </c>
       <c r="F189" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.51289</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4972,22 +4972,22 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>76.7</v>
+        <v>25.85</v>
       </c>
       <c r="D190" t="n">
-        <v>172.37</v>
+        <v>41.65</v>
       </c>
       <c r="E190" t="n">
-        <v>124.73</v>
+        <v>61.12</v>
       </c>
       <c r="F190" t="n">
-        <v>2.05425</v>
+        <v>0.40151</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4996,22 +4996,22 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>166.99</v>
+        <v>43.81</v>
       </c>
       <c r="D191" t="n">
-        <v>327.23</v>
+        <v>103.55</v>
       </c>
       <c r="E191" t="n">
-        <v>95.95999999999999</v>
+        <v>136.36</v>
       </c>
       <c r="F191" t="n">
-        <v>9.443759999999999</v>
+        <v>1.02235</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5020,16 +5020,16 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>151.43</v>
+        <v>117.65</v>
       </c>
       <c r="D192" t="n">
-        <v>266.62</v>
+        <v>242.16</v>
       </c>
       <c r="E192" t="n">
-        <v>76.06999999999999</v>
+        <v>105.83</v>
       </c>
       <c r="F192" t="n">
-        <v>1.96202</v>
+        <v>1.79379</v>
       </c>
     </row>
     <row r="193">
@@ -5059,7 +5059,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5068,22 +5068,22 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>56.43</v>
+        <v>95.67</v>
       </c>
       <c r="D194" t="n">
-        <v>112.25</v>
+        <v>189.93</v>
       </c>
       <c r="E194" t="n">
-        <v>98.92</v>
+        <v>98.53</v>
       </c>
       <c r="F194" t="n">
-        <v>3.11717</v>
+        <v>0.92719</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5092,22 +5092,22 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>95.67</v>
+        <v>56.43</v>
       </c>
       <c r="D195" t="n">
-        <v>189.93</v>
+        <v>112.25</v>
       </c>
       <c r="E195" t="n">
-        <v>98.53</v>
+        <v>98.92</v>
       </c>
       <c r="F195" t="n">
-        <v>0.92719</v>
+        <v>3.11717</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AGNCM</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5116,22 +5116,22 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>23.63</v>
+        <v>62.49</v>
       </c>
       <c r="D196" t="n">
-        <v>25.4</v>
+        <v>90.06</v>
       </c>
       <c r="E196" t="n">
-        <v>7.49</v>
+        <v>44.12</v>
       </c>
       <c r="F196" t="n">
-        <v>0.05914</v>
+        <v>-0.21073</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>AGNCM</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5140,22 +5140,22 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>62.49</v>
+        <v>23.63</v>
       </c>
       <c r="D197" t="n">
-        <v>90.06</v>
+        <v>25.4</v>
       </c>
       <c r="E197" t="n">
-        <v>44.12</v>
+        <v>7.49</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.21073</v>
+        <v>0.05914</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5164,22 +5164,22 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>23.49</v>
+        <v>124.07</v>
       </c>
       <c r="D198" t="n">
-        <v>32.21</v>
+        <v>187.8</v>
       </c>
       <c r="E198" t="n">
-        <v>37.12</v>
+        <v>51.37</v>
       </c>
       <c r="F198" t="n">
-        <v>0.17481</v>
+        <v>4.85902</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5188,22 +5188,22 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>124.07</v>
+        <v>23.49</v>
       </c>
       <c r="D199" t="n">
-        <v>187.8</v>
+        <v>32.21</v>
       </c>
       <c r="E199" t="n">
-        <v>51.37</v>
+        <v>37.12</v>
       </c>
       <c r="F199" t="n">
-        <v>4.85902</v>
+        <v>0.17481</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5212,22 +5212,22 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>430.4</v>
+        <v>172.34</v>
       </c>
       <c r="D200" t="n">
-        <v>559.34</v>
+        <v>216.17</v>
       </c>
       <c r="E200" t="n">
-        <v>29.96</v>
+        <v>25.43</v>
       </c>
       <c r="F200" t="n">
-        <v>0.948</v>
+        <v>0.34426</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5236,22 +5236,22 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>172.34</v>
+        <v>430.4</v>
       </c>
       <c r="D201" t="n">
-        <v>216.17</v>
+        <v>559.34</v>
       </c>
       <c r="E201" t="n">
-        <v>25.43</v>
+        <v>29.96</v>
       </c>
       <c r="F201" t="n">
-        <v>0.34426</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>EHC</t>
+          <t>BML-PJ</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5260,16 +5260,16 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>96.73</v>
+        <v>19.05</v>
       </c>
       <c r="D202" t="n">
-        <v>122</v>
+        <v>19.64</v>
       </c>
       <c r="E202" t="n">
-        <v>26.12</v>
+        <v>3.1</v>
       </c>
       <c r="F202" t="n">
-        <v>0.43594</v>
+        <v>0.02454</v>
       </c>
     </row>
     <row r="203">
@@ -5299,31 +5299,31 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>EHC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>90.01000000000001</v>
+        <v>96.73</v>
       </c>
       <c r="D204" t="n">
-        <v>101.14</v>
+        <v>122</v>
       </c>
       <c r="E204" t="n">
-        <v>12.37</v>
+        <v>26.12</v>
       </c>
       <c r="F204" t="n">
-        <v>0.33492</v>
+        <v>0.43594</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5332,22 +5332,22 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3.88</v>
+        <v>12.96</v>
       </c>
       <c r="D205" t="n">
-        <v>6.44</v>
+        <v>16.65</v>
       </c>
       <c r="E205" t="n">
-        <v>65.98</v>
+        <v>28.47</v>
       </c>
       <c r="F205" t="n">
-        <v>0.07534</v>
+        <v>-0.03231</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5356,22 +5356,22 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>131.47</v>
+        <v>284.79</v>
       </c>
       <c r="D206" t="n">
-        <v>206.99</v>
+        <v>417.54</v>
       </c>
       <c r="E206" t="n">
-        <v>57.44</v>
+        <v>46.61</v>
       </c>
       <c r="F206" t="n">
-        <v>2.05473</v>
+        <v>6.50222</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TIGO</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5380,22 +5380,22 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>73.13</v>
+        <v>166</v>
       </c>
       <c r="D207" t="n">
-        <v>95.81999999999999</v>
+        <v>396.62</v>
       </c>
       <c r="E207" t="n">
-        <v>31.03</v>
+        <v>138.93</v>
       </c>
       <c r="F207" t="n">
-        <v>0.60843</v>
+        <v>3.79223</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5404,22 +5404,22 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>52.5</v>
+        <v>119.51</v>
       </c>
       <c r="D208" t="n">
-        <v>90</v>
+        <v>259.35</v>
       </c>
       <c r="E208" t="n">
-        <v>71.43000000000001</v>
+        <v>117.01</v>
       </c>
       <c r="F208" t="n">
-        <v>5.23697</v>
+        <v>10.66539</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5428,22 +5428,22 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>273.5</v>
+        <v>29.16</v>
       </c>
       <c r="D209" t="n">
-        <v>344.98</v>
+        <v>39.69</v>
       </c>
       <c r="E209" t="n">
-        <v>26.14</v>
+        <v>36.11</v>
       </c>
       <c r="F209" t="n">
-        <v>0.07092</v>
+        <v>0.07466</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5452,22 +5452,22 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>28.35</v>
+        <v>97.52</v>
       </c>
       <c r="D210" t="n">
-        <v>39.25</v>
+        <v>129.59</v>
       </c>
       <c r="E210" t="n">
-        <v>38.45</v>
+        <v>32.89</v>
       </c>
       <c r="F210" t="n">
-        <v>0.49418</v>
+        <v>2.24577</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>TEVA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5476,22 +5476,22 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>19.02</v>
+        <v>28.35</v>
       </c>
       <c r="D211" t="n">
-        <v>26.78</v>
+        <v>39.25</v>
       </c>
       <c r="E211" t="n">
-        <v>40.8</v>
+        <v>38.45</v>
       </c>
       <c r="F211" t="n">
-        <v>0.29688</v>
+        <v>0.49418</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5500,22 +5500,22 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>258.08</v>
+        <v>131.47</v>
       </c>
       <c r="D212" t="n">
-        <v>288.9</v>
+        <v>206.99</v>
       </c>
       <c r="E212" t="n">
-        <v>11.94</v>
+        <v>57.44</v>
       </c>
       <c r="F212" t="n">
-        <v>1.81284</v>
+        <v>2.05473</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5524,22 +5524,22 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>24.77</v>
+        <v>258.08</v>
       </c>
       <c r="D213" t="n">
-        <v>36.78</v>
+        <v>288.9</v>
       </c>
       <c r="E213" t="n">
-        <v>48.49</v>
+        <v>11.94</v>
       </c>
       <c r="F213" t="n">
-        <v>0.38487</v>
+        <v>1.81284</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>8.609999999999999</v>
+        <v>24.77</v>
       </c>
       <c r="D214" t="n">
-        <v>21.61</v>
+        <v>36.78</v>
       </c>
       <c r="E214" t="n">
-        <v>150.99</v>
+        <v>48.49</v>
       </c>
       <c r="F214" t="n">
-        <v>0.62903</v>
+        <v>0.38487</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5572,22 +5572,22 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>22.61</v>
+        <v>73.13</v>
       </c>
       <c r="D215" t="n">
-        <v>55.88</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="E215" t="n">
-        <v>147.15</v>
+        <v>31.03</v>
       </c>
       <c r="F215" t="n">
-        <v>1.10062</v>
+        <v>0.60843</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SHG</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5596,22 +5596,22 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>59.66</v>
+        <v>67.39</v>
       </c>
       <c r="D216" t="n">
-        <v>82.63</v>
+        <v>93.28</v>
       </c>
       <c r="E216" t="n">
-        <v>38.5</v>
+        <v>38.42</v>
       </c>
       <c r="F216" t="n">
-        <v>1.52417</v>
+        <v>0.61522</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5620,22 +5620,22 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>284.79</v>
+        <v>22.61</v>
       </c>
       <c r="D217" t="n">
-        <v>417.54</v>
+        <v>55.88</v>
       </c>
       <c r="E217" t="n">
-        <v>46.61</v>
+        <v>147.15</v>
       </c>
       <c r="F217" t="n">
-        <v>6.50222</v>
+        <v>1.10062</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5644,22 +5644,22 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>273.14</v>
+        <v>65.16</v>
       </c>
       <c r="D218" t="n">
-        <v>341.43</v>
+        <v>110.45</v>
       </c>
       <c r="E218" t="n">
-        <v>25</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.05953</v>
+        <v>1.57155</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5668,22 +5668,22 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>67.39</v>
+        <v>19.02</v>
       </c>
       <c r="D219" t="n">
-        <v>93.28</v>
+        <v>26.78</v>
       </c>
       <c r="E219" t="n">
-        <v>38.42</v>
+        <v>40.8</v>
       </c>
       <c r="F219" t="n">
-        <v>0.61522</v>
+        <v>0.29688</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5692,22 +5692,22 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>65.16</v>
+        <v>116.13</v>
       </c>
       <c r="D220" t="n">
-        <v>110.45</v>
+        <v>192.84</v>
       </c>
       <c r="E220" t="n">
-        <v>69.51000000000001</v>
+        <v>66.06</v>
       </c>
       <c r="F220" t="n">
-        <v>1.57155</v>
+        <v>0.13947</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5716,22 +5716,22 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>29.16</v>
+        <v>16.32</v>
       </c>
       <c r="D221" t="n">
-        <v>39.69</v>
+        <v>23.71</v>
       </c>
       <c r="E221" t="n">
-        <v>36.11</v>
+        <v>45.28</v>
       </c>
       <c r="F221" t="n">
-        <v>0.07466</v>
+        <v>0.26691</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5740,22 +5740,22 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>31.8</v>
+        <v>41.19</v>
       </c>
       <c r="D222" t="n">
-        <v>67.66</v>
+        <v>97.14</v>
       </c>
       <c r="E222" t="n">
-        <v>112.77</v>
+        <v>135.83</v>
       </c>
       <c r="F222" t="n">
-        <v>0.62832</v>
+        <v>1.2311</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5764,22 +5764,22 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>97.52</v>
+        <v>52.5</v>
       </c>
       <c r="D223" t="n">
-        <v>129.59</v>
+        <v>90</v>
       </c>
       <c r="E223" t="n">
-        <v>32.89</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F223" t="n">
-        <v>2.24577</v>
+        <v>5.23697</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5788,22 +5788,22 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>119.51</v>
+        <v>107.27</v>
       </c>
       <c r="D224" t="n">
-        <v>259.35</v>
+        <v>136.17</v>
       </c>
       <c r="E224" t="n">
-        <v>117.01</v>
+        <v>26.94</v>
       </c>
       <c r="F224" t="n">
-        <v>10.66539</v>
+        <v>0.75183</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5812,22 +5812,22 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>204.77</v>
+        <v>196.04</v>
       </c>
       <c r="D225" t="n">
-        <v>273.05</v>
+        <v>504.2</v>
       </c>
       <c r="E225" t="n">
-        <v>33.34</v>
+        <v>157.19</v>
       </c>
       <c r="F225" t="n">
-        <v>0.99791</v>
+        <v>7.29423</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>AUR</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5836,22 +5836,22 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>12.96</v>
+        <v>3.88</v>
       </c>
       <c r="D226" t="n">
-        <v>16.65</v>
+        <v>6.44</v>
       </c>
       <c r="E226" t="n">
-        <v>28.47</v>
+        <v>65.98</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.03231</v>
+        <v>0.07534</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5860,22 +5860,22 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>116.13</v>
+        <v>246.63</v>
       </c>
       <c r="D227" t="n">
-        <v>192.84</v>
+        <v>331.34</v>
       </c>
       <c r="E227" t="n">
-        <v>66.06</v>
+        <v>34.35</v>
       </c>
       <c r="F227" t="n">
-        <v>0.13947</v>
+        <v>4.71551</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5884,22 +5884,22 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>16.32</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D228" t="n">
-        <v>23.71</v>
+        <v>21.61</v>
       </c>
       <c r="E228" t="n">
-        <v>45.28</v>
+        <v>150.99</v>
       </c>
       <c r="F228" t="n">
-        <v>0.26691</v>
+        <v>0.62903</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5908,22 +5908,22 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>41.19</v>
+        <v>273.5</v>
       </c>
       <c r="D229" t="n">
-        <v>97.14</v>
+        <v>344.98</v>
       </c>
       <c r="E229" t="n">
-        <v>135.83</v>
+        <v>26.14</v>
       </c>
       <c r="F229" t="n">
-        <v>1.2311</v>
+        <v>0.07092</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SHG</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>107.27</v>
+        <v>59.66</v>
       </c>
       <c r="D230" t="n">
-        <v>136.17</v>
+        <v>82.63</v>
       </c>
       <c r="E230" t="n">
-        <v>26.94</v>
+        <v>38.5</v>
       </c>
       <c r="F230" t="n">
-        <v>0.75183</v>
+        <v>1.52417</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>26.41</v>
+        <v>273.14</v>
       </c>
       <c r="D231" t="n">
-        <v>39.5</v>
+        <v>341.43</v>
       </c>
       <c r="E231" t="n">
-        <v>49.56</v>
+        <v>25</v>
       </c>
       <c r="F231" t="n">
-        <v>1.30846</v>
+        <v>-0.05953</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5980,22 +5980,22 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>196.04</v>
+        <v>204.77</v>
       </c>
       <c r="D232" t="n">
-        <v>504.2</v>
+        <v>273.05</v>
       </c>
       <c r="E232" t="n">
-        <v>157.19</v>
+        <v>33.34</v>
       </c>
       <c r="F232" t="n">
-        <v>7.29423</v>
+        <v>0.99791</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6004,22 +6004,22 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>279.73</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D233" t="n">
-        <v>430.88</v>
+        <v>101.14</v>
       </c>
       <c r="E233" t="n">
-        <v>54.03</v>
+        <v>12.37</v>
       </c>
       <c r="F233" t="n">
-        <v>5.88329</v>
+        <v>0.33492</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6028,22 +6028,22 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>246.63</v>
+        <v>26.41</v>
       </c>
       <c r="D234" t="n">
-        <v>331.34</v>
+        <v>39.5</v>
       </c>
       <c r="E234" t="n">
-        <v>34.35</v>
+        <v>49.56</v>
       </c>
       <c r="F234" t="n">
-        <v>4.71551</v>
+        <v>1.30846</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6052,46 +6052,46 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>166</v>
+        <v>31.8</v>
       </c>
       <c r="D235" t="n">
-        <v>396.62</v>
+        <v>67.66</v>
       </c>
       <c r="E235" t="n">
-        <v>138.93</v>
+        <v>112.77</v>
       </c>
       <c r="F235" t="n">
-        <v>3.79223</v>
+        <v>0.62832</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>33.63</v>
+        <v>279.73</v>
       </c>
       <c r="D236" t="n">
-        <v>43.87</v>
+        <v>430.88</v>
       </c>
       <c r="E236" t="n">
-        <v>30.45</v>
+        <v>54.03</v>
       </c>
       <c r="F236" t="n">
-        <v>0.08643000000000001</v>
+        <v>5.88329</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6100,22 +6100,22 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>39.84</v>
+        <v>525.72</v>
       </c>
       <c r="D237" t="n">
-        <v>58.28</v>
+        <v>670.24</v>
       </c>
       <c r="E237" t="n">
-        <v>46.29</v>
+        <v>27.49</v>
       </c>
       <c r="F237" t="n">
-        <v>0.05681</v>
+        <v>21.58203</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6124,22 +6124,22 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>285.27</v>
+        <v>92.39</v>
       </c>
       <c r="D238" t="n">
-        <v>377.97</v>
+        <v>242.49</v>
       </c>
       <c r="E238" t="n">
-        <v>32.5</v>
+        <v>162.45</v>
       </c>
       <c r="F238" t="n">
-        <v>2.23594</v>
+        <v>5.44723</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>106.41</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D239" t="n">
-        <v>117.55</v>
+        <v>118.37</v>
       </c>
       <c r="E239" t="n">
-        <v>10.47</v>
+        <v>36.04</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.56235</v>
+        <v>1.18624</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>ARMK</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6172,22 +6172,22 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>67.7</v>
+        <v>39.84</v>
       </c>
       <c r="D240" t="n">
-        <v>98.22</v>
+        <v>58.28</v>
       </c>
       <c r="E240" t="n">
-        <v>45.08</v>
+        <v>46.29</v>
       </c>
       <c r="F240" t="n">
-        <v>0.47423</v>
+        <v>0.05681</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>CRBG</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6196,22 +6196,22 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>14</v>
+        <v>22.3</v>
       </c>
       <c r="D241" t="n">
-        <v>14.8</v>
+        <v>35.02</v>
       </c>
       <c r="E241" t="n">
-        <v>5.71</v>
+        <v>57.04</v>
       </c>
       <c r="F241" t="n">
-        <v>0.00993</v>
+        <v>0.52819</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6220,22 +6220,22 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>7.63</v>
+        <v>317.93</v>
       </c>
       <c r="D242" t="n">
-        <v>11.15</v>
+        <v>379.55</v>
       </c>
       <c r="E242" t="n">
-        <v>46.13</v>
+        <v>19.38</v>
       </c>
       <c r="F242" t="n">
-        <v>0.16553</v>
+        <v>0.46956</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>EQH</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6244,22 +6244,22 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>87.98</v>
+        <v>35.34</v>
       </c>
       <c r="D243" t="n">
-        <v>108.03</v>
+        <v>53.97</v>
       </c>
       <c r="E243" t="n">
-        <v>22.79</v>
+        <v>52.72</v>
       </c>
       <c r="F243" t="n">
-        <v>0.75809</v>
+        <v>0.84994</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6268,22 +6268,22 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>92.39</v>
+        <v>7.63</v>
       </c>
       <c r="D244" t="n">
-        <v>242.49</v>
+        <v>11.15</v>
       </c>
       <c r="E244" t="n">
-        <v>162.45</v>
+        <v>46.13</v>
       </c>
       <c r="F244" t="n">
-        <v>5.44723</v>
+        <v>0.16553</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6292,22 +6292,22 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>147.02</v>
+        <v>3.42</v>
       </c>
       <c r="D245" t="n">
-        <v>375.09</v>
+        <v>5.06</v>
       </c>
       <c r="E245" t="n">
-        <v>155.13</v>
+        <v>47.95</v>
       </c>
       <c r="F245" t="n">
-        <v>1.92246</v>
+        <v>0.09043</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6316,22 +6316,22 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>67.56999999999999</v>
+        <v>147.02</v>
       </c>
       <c r="D246" t="n">
-        <v>79.45999999999999</v>
+        <v>375.09</v>
       </c>
       <c r="E246" t="n">
-        <v>17.6</v>
+        <v>155.13</v>
       </c>
       <c r="F246" t="n">
-        <v>-0.25539</v>
+        <v>1.92246</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>91.37</v>
+        <v>295.52</v>
       </c>
       <c r="D247" t="n">
-        <v>121.47</v>
+        <v>375.62</v>
       </c>
       <c r="E247" t="n">
-        <v>32.94</v>
+        <v>27.1</v>
       </c>
       <c r="F247" t="n">
-        <v>0.12704</v>
+        <v>0.11189</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6364,22 +6364,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>92.42</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D248" t="n">
-        <v>106.42</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="E248" t="n">
-        <v>15.15</v>
+        <v>17.6</v>
       </c>
       <c r="F248" t="n">
-        <v>0.38316</v>
+        <v>-0.25539</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6388,22 +6388,22 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>295.52</v>
+        <v>91.37</v>
       </c>
       <c r="D249" t="n">
-        <v>375.62</v>
+        <v>121.47</v>
       </c>
       <c r="E249" t="n">
-        <v>27.1</v>
+        <v>32.94</v>
       </c>
       <c r="F249" t="n">
-        <v>0.11189</v>
+        <v>0.12704</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>NMR</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>525.72</v>
+        <v>7.58</v>
       </c>
       <c r="D250" t="n">
-        <v>670.24</v>
+        <v>10.61</v>
       </c>
       <c r="E250" t="n">
-        <v>27.49</v>
+        <v>39.97</v>
       </c>
       <c r="F250" t="n">
-        <v>21.58203</v>
+        <v>0.17809</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3.42</v>
+        <v>92.42</v>
       </c>
       <c r="D251" t="n">
-        <v>5.06</v>
+        <v>106.42</v>
       </c>
       <c r="E251" t="n">
-        <v>47.95</v>
+        <v>15.15</v>
       </c>
       <c r="F251" t="n">
-        <v>0.09043</v>
+        <v>0.38316</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SPG-PJ</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>52.49</v>
+        <v>23.77</v>
       </c>
       <c r="D252" t="n">
-        <v>55.78</v>
+        <v>29.05</v>
       </c>
       <c r="E252" t="n">
-        <v>6.27</v>
+        <v>22.21</v>
       </c>
       <c r="F252" t="n">
-        <v>-0.04614</v>
+        <v>0.28593</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>153.68</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D253" t="n">
-        <v>171.67</v>
+        <v>156.62</v>
       </c>
       <c r="E253" t="n">
-        <v>11.71</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.33974</v>
+        <v>0.27415</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6508,22 +6508,22 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>125.78</v>
+        <v>24.24</v>
       </c>
       <c r="D254" t="n">
-        <v>143.79</v>
+        <v>30.44</v>
       </c>
       <c r="E254" t="n">
-        <v>14.32</v>
+        <v>25.58</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.04365</v>
+        <v>0.00578</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>24.24</v>
+        <v>243.35</v>
       </c>
       <c r="D255" t="n">
-        <v>30.44</v>
+        <v>365</v>
       </c>
       <c r="E255" t="n">
-        <v>25.58</v>
+        <v>49.99</v>
       </c>
       <c r="F255" t="n">
-        <v>0.00578</v>
+        <v>3.17586</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6556,22 +6556,22 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>23.77</v>
+        <v>121.84</v>
       </c>
       <c r="D256" t="n">
-        <v>29.05</v>
+        <v>159.63</v>
       </c>
       <c r="E256" t="n">
-        <v>22.21</v>
+        <v>31.02</v>
       </c>
       <c r="F256" t="n">
-        <v>0.28593</v>
+        <v>1.3023</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>22.3</v>
+        <v>14</v>
       </c>
       <c r="D257" t="n">
-        <v>35.02</v>
+        <v>14.8</v>
       </c>
       <c r="E257" t="n">
-        <v>57.04</v>
+        <v>5.71</v>
       </c>
       <c r="F257" t="n">
-        <v>0.52819</v>
+        <v>0.00993</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>243.35</v>
+        <v>163.37</v>
       </c>
       <c r="D258" t="n">
-        <v>365</v>
+        <v>258.82</v>
       </c>
       <c r="E258" t="n">
-        <v>49.99</v>
+        <v>58.43</v>
       </c>
       <c r="F258" t="n">
-        <v>3.17586</v>
+        <v>0.25232</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6628,22 +6628,22 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>317.93</v>
+        <v>3.93</v>
       </c>
       <c r="D259" t="n">
-        <v>379.55</v>
+        <v>5.83</v>
       </c>
       <c r="E259" t="n">
-        <v>19.38</v>
+        <v>48.35</v>
       </c>
       <c r="F259" t="n">
-        <v>0.46956</v>
+        <v>0.11582</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>SNX</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6652,22 +6652,22 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>72.90000000000001</v>
+        <v>157.12</v>
       </c>
       <c r="D260" t="n">
-        <v>95.88</v>
+        <v>262.48</v>
       </c>
       <c r="E260" t="n">
-        <v>31.52</v>
+        <v>67.06</v>
       </c>
       <c r="F260" t="n">
-        <v>0.94208</v>
+        <v>2.10792</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6676,22 +6676,22 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3.93</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D261" t="n">
-        <v>5.83</v>
+        <v>95.88</v>
       </c>
       <c r="E261" t="n">
-        <v>48.35</v>
+        <v>31.52</v>
       </c>
       <c r="F261" t="n">
-        <v>0.11582</v>
+        <v>0.94208</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6700,22 +6700,22 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>87.01000000000001</v>
+        <v>182.65</v>
       </c>
       <c r="D262" t="n">
-        <v>118.37</v>
+        <v>350.78</v>
       </c>
       <c r="E262" t="n">
-        <v>36.04</v>
+        <v>92.05</v>
       </c>
       <c r="F262" t="n">
-        <v>1.18624</v>
+        <v>5.93408</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>163.37</v>
+        <v>61.37</v>
       </c>
       <c r="D263" t="n">
-        <v>258.82</v>
+        <v>80.53</v>
       </c>
       <c r="E263" t="n">
-        <v>58.43</v>
+        <v>31.22</v>
       </c>
       <c r="F263" t="n">
-        <v>0.25232</v>
+        <v>0.10797</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6748,22 +6748,22 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>284.93</v>
+        <v>153.68</v>
       </c>
       <c r="D264" t="n">
-        <v>407.75</v>
+        <v>171.67</v>
       </c>
       <c r="E264" t="n">
-        <v>43.11</v>
+        <v>11.71</v>
       </c>
       <c r="F264" t="n">
-        <v>0.7672099999999999</v>
+        <v>-0.33974</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>EQH</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6772,22 +6772,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>35.34</v>
+        <v>213.28</v>
       </c>
       <c r="D265" t="n">
-        <v>53.97</v>
+        <v>286.11</v>
       </c>
       <c r="E265" t="n">
-        <v>52.72</v>
+        <v>34.15</v>
       </c>
       <c r="F265" t="n">
-        <v>0.84994</v>
+        <v>0.03034</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6796,22 +6796,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>289.16</v>
+        <v>41.53</v>
       </c>
       <c r="D266" t="n">
-        <v>417.09</v>
+        <v>56.9</v>
       </c>
       <c r="E266" t="n">
-        <v>44.24</v>
+        <v>37.01</v>
       </c>
       <c r="F266" t="n">
-        <v>0.82443</v>
+        <v>0.18075</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SNX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6820,22 +6820,22 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>157.12</v>
+        <v>110.24</v>
       </c>
       <c r="D267" t="n">
-        <v>262.48</v>
+        <v>150.27</v>
       </c>
       <c r="E267" t="n">
-        <v>67.06</v>
+        <v>36.31</v>
       </c>
       <c r="F267" t="n">
-        <v>2.10792</v>
+        <v>-0.85395</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>117.67</v>
+        <v>284.93</v>
       </c>
       <c r="D268" t="n">
-        <v>222.29</v>
+        <v>407.75</v>
       </c>
       <c r="E268" t="n">
-        <v>88.91</v>
+        <v>43.11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.07779</v>
+        <v>0.7672099999999999</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>NMR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>7.58</v>
+        <v>20.72</v>
       </c>
       <c r="D269" t="n">
-        <v>10.61</v>
+        <v>24.64</v>
       </c>
       <c r="E269" t="n">
-        <v>39.97</v>
+        <v>18.92</v>
       </c>
       <c r="F269" t="n">
-        <v>0.17809</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6892,22 +6892,22 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>213.28</v>
+        <v>87.98</v>
       </c>
       <c r="D270" t="n">
-        <v>286.11</v>
+        <v>108.03</v>
       </c>
       <c r="E270" t="n">
-        <v>34.15</v>
+        <v>22.79</v>
       </c>
       <c r="F270" t="n">
-        <v>0.03034</v>
+        <v>0.75809</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>SPG-PJ</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6916,22 +6916,22 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>41.53</v>
+        <v>52.49</v>
       </c>
       <c r="D271" t="n">
-        <v>56.9</v>
+        <v>56.12</v>
       </c>
       <c r="E271" t="n">
-        <v>37.01</v>
+        <v>6.92</v>
       </c>
       <c r="F271" t="n">
-        <v>0.18075</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6940,22 +6940,22 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>182.65</v>
+        <v>117.67</v>
       </c>
       <c r="D272" t="n">
-        <v>350.78</v>
+        <v>222.29</v>
       </c>
       <c r="E272" t="n">
-        <v>92.05</v>
+        <v>88.91</v>
       </c>
       <c r="F272" t="n">
-        <v>5.93408</v>
+        <v>0.07779</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6964,22 +6964,22 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>61.37</v>
+        <v>67.7</v>
       </c>
       <c r="D273" t="n">
-        <v>80.53</v>
+        <v>98.22</v>
       </c>
       <c r="E273" t="n">
-        <v>31.22</v>
+        <v>45.08</v>
       </c>
       <c r="F273" t="n">
-        <v>0.10797</v>
+        <v>0.47423</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6988,22 +6988,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>20.72</v>
+        <v>289.16</v>
       </c>
       <c r="D274" t="n">
-        <v>24.64</v>
+        <v>417.09</v>
       </c>
       <c r="E274" t="n">
-        <v>18.92</v>
+        <v>44.24</v>
       </c>
       <c r="F274" t="n">
-        <v>0.0299</v>
+        <v>0.82443</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7012,22 +7012,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>110.24</v>
+        <v>106.41</v>
       </c>
       <c r="D275" t="n">
-        <v>150.27</v>
+        <v>117.55</v>
       </c>
       <c r="E275" t="n">
-        <v>36.31</v>
+        <v>10.47</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.85395</v>
+        <v>-0.56235</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7036,22 +7036,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>121.84</v>
+        <v>33.63</v>
       </c>
       <c r="D276" t="n">
-        <v>159.63</v>
+        <v>43.87</v>
       </c>
       <c r="E276" t="n">
-        <v>31.02</v>
+        <v>30.45</v>
       </c>
       <c r="F276" t="n">
-        <v>1.3023</v>
+        <v>0.08643000000000001</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7060,46 +7060,46 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>87.15000000000001</v>
+        <v>285.27</v>
       </c>
       <c r="D277" t="n">
-        <v>156.62</v>
+        <v>377.97</v>
       </c>
       <c r="E277" t="n">
-        <v>79.70999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="F277" t="n">
-        <v>0.27415</v>
+        <v>2.23594</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>95.48</v>
+        <v>125.78</v>
       </c>
       <c r="D278" t="n">
-        <v>111.5</v>
+        <v>143.79</v>
       </c>
       <c r="E278" t="n">
-        <v>16.78</v>
+        <v>14.32</v>
       </c>
       <c r="F278" t="n">
-        <v>0.0456</v>
+        <v>-0.04365</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7108,22 +7108,22 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>27.55</v>
+        <v>17.13</v>
       </c>
       <c r="D279" t="n">
-        <v>33.78</v>
+        <v>43.01</v>
       </c>
       <c r="E279" t="n">
-        <v>22.61</v>
+        <v>151.08</v>
       </c>
       <c r="F279" t="n">
-        <v>-0.15662</v>
+        <v>0.30712</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7132,16 +7132,16 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>17.13</v>
+        <v>27.55</v>
       </c>
       <c r="D280" t="n">
-        <v>43.01</v>
+        <v>33.78</v>
       </c>
       <c r="E280" t="n">
-        <v>151.08</v>
+        <v>22.61</v>
       </c>
       <c r="F280" t="n">
-        <v>0.30712</v>
+        <v>-0.15662</v>
       </c>
     </row>
     <row r="281">
@@ -7171,48 +7171,72 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>63.78</v>
+        <v>95.48</v>
       </c>
       <c r="D282" t="n">
-        <v>69.81</v>
+        <v>111.5</v>
       </c>
       <c r="E282" t="n">
-        <v>9.449999999999999</v>
+        <v>16.78</v>
       </c>
       <c r="F282" t="n">
-        <v>0.43847</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="D283" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="E283" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.43847</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
           <t>ICLR</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C283" t="n">
+      <c r="C284" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="D283" t="n">
+      <c r="D284" t="n">
         <v>172.45</v>
       </c>
-      <c r="E283" t="n">
+      <c r="E284" t="n">
         <v>72.47</v>
       </c>
-      <c r="F283" t="n">
+      <c r="F284" t="n">
         <v>1.41425</v>
       </c>
     </row>

--- a/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
+++ b/dip_yakalama_daily_120dip_rebound_sonuclar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F284"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,16 +460,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.54000000000001</v>
+        <v>48.12</v>
       </c>
       <c r="D2" t="n">
-        <v>86.11</v>
+        <v>50.33</v>
       </c>
       <c r="E2" t="n">
-        <v>6.92</v>
+        <v>4.59</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.96334</v>
+        <v>-0.21121</v>
       </c>
     </row>
     <row r="3">
@@ -487,13 +487,13 @@
         <v>54.33</v>
       </c>
       <c r="D3" t="n">
-        <v>56.52</v>
+        <v>56.41</v>
       </c>
       <c r="E3" t="n">
-        <v>4.03</v>
+        <v>3.83</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09851</v>
+        <v>0.05849</v>
       </c>
     </row>
     <row r="4">
@@ -511,13 +511,13 @@
         <v>38.22</v>
       </c>
       <c r="D4" t="n">
-        <v>42.77</v>
+        <v>42.5</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1714</v>
+        <v>0.28841</v>
       </c>
     </row>
     <row r="5">
@@ -535,13 +535,13 @@
         <v>700.51</v>
       </c>
       <c r="D5" t="n">
-        <v>731.75</v>
+        <v>732.51</v>
       </c>
       <c r="E5" t="n">
-        <v>4.46</v>
+        <v>4.57</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9792</v>
+        <v>-0.97165</v>
       </c>
     </row>
     <row r="6">
@@ -559,13 +559,13 @@
         <v>17.87</v>
       </c>
       <c r="D6" t="n">
-        <v>21.44</v>
+        <v>21.75</v>
       </c>
       <c r="E6" t="n">
-        <v>19.98</v>
+        <v>21.71</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7442</v>
+        <v>0.80284</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>102.63</v>
       </c>
       <c r="D7" t="n">
-        <v>108.09</v>
+        <v>108.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5.32</v>
+        <v>5.72</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01302</v>
+        <v>0.27559</v>
       </c>
     </row>
     <row r="8">
@@ -607,19 +607,19 @@
         <v>13.03</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>14.87</v>
       </c>
       <c r="E8" t="n">
-        <v>15.12</v>
+        <v>14.12</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09046</v>
+        <v>0.16756</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -628,22 +628,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.67</v>
+        <v>298.59</v>
       </c>
       <c r="D9" t="n">
-        <v>6.83</v>
+        <v>329.02</v>
       </c>
       <c r="E9" t="n">
-        <v>20.46</v>
+        <v>10.19</v>
       </c>
       <c r="F9" t="n">
-        <v>0.15101</v>
+        <v>2.37851</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>298.59</v>
+        <v>5.67</v>
       </c>
       <c r="D10" t="n">
-        <v>331.46</v>
+        <v>6.89</v>
       </c>
       <c r="E10" t="n">
-        <v>11.01</v>
+        <v>21.43</v>
       </c>
       <c r="F10" t="n">
-        <v>1.09993</v>
+        <v>0.14377</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +679,19 @@
         <v>141.63</v>
       </c>
       <c r="D11" t="n">
-        <v>157.63</v>
+        <v>152.84</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3</v>
+        <v>7.91</v>
       </c>
       <c r="F11" t="n">
-        <v>1.69159</v>
+        <v>1.57049</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>BBD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12.43</v>
+        <v>2.98</v>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>3.47</v>
       </c>
       <c r="E12" t="n">
-        <v>39.98</v>
+        <v>16.61</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8716699999999999</v>
+        <v>0.05183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.23</v>
+        <v>12.43</v>
       </c>
       <c r="D13" t="n">
-        <v>11.89</v>
+        <v>17.6</v>
       </c>
       <c r="E13" t="n">
-        <v>5.88</v>
+        <v>41.63</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03859</v>
+        <v>0.84628</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BBD</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.98</v>
+        <v>11.23</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5</v>
+        <v>11.89</v>
       </c>
       <c r="E14" t="n">
-        <v>17.45</v>
+        <v>5.88</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06834</v>
+        <v>0.03206</v>
       </c>
     </row>
     <row r="15">
@@ -775,13 +775,13 @@
         <v>7.17</v>
       </c>
       <c r="D15" t="n">
-        <v>8.26</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.13953</v>
+        <v>0.11767</v>
       </c>
     </row>
     <row r="16">
@@ -799,19 +799,19 @@
         <v>4.46</v>
       </c>
       <c r="D16" t="n">
-        <v>5.24</v>
+        <v>5.26</v>
       </c>
       <c r="E16" t="n">
-        <v>17.49</v>
+        <v>17.96</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08273999999999999</v>
+        <v>0.06924</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TIMB</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.28</v>
+        <v>98.45</v>
       </c>
       <c r="D17" t="n">
-        <v>19.03</v>
+        <v>119.98</v>
       </c>
       <c r="E17" t="n">
-        <v>10.13</v>
+        <v>21.87</v>
       </c>
       <c r="F17" t="n">
-        <v>0.20851</v>
+        <v>1.42021</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>TIMB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -844,22 +844,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>98.45</v>
+        <v>17.28</v>
       </c>
       <c r="D18" t="n">
-        <v>123.79</v>
+        <v>19.07</v>
       </c>
       <c r="E18" t="n">
-        <v>25.74</v>
+        <v>10.36</v>
       </c>
       <c r="F18" t="n">
-        <v>1.77497</v>
+        <v>0.17818</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ABEV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -868,118 +868,118 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.78</v>
+        <v>63.96</v>
       </c>
       <c r="D19" t="n">
-        <v>3.02</v>
+        <v>70.44</v>
       </c>
       <c r="E19" t="n">
-        <v>8.630000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02557</v>
+        <v>0.5539500000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>BML-PL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>52.62</v>
+        <v>18.84</v>
       </c>
       <c r="D20" t="n">
-        <v>56.64</v>
+        <v>19.47</v>
       </c>
       <c r="E20" t="n">
-        <v>7.64</v>
+        <v>3.34</v>
       </c>
       <c r="F20" t="n">
-        <v>0.35581</v>
+        <v>0.04797</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>ABEV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.54</v>
+        <v>2.78</v>
       </c>
       <c r="D21" t="n">
-        <v>50.24</v>
+        <v>2.98</v>
       </c>
       <c r="E21" t="n">
-        <v>41.36</v>
+        <v>7.37</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3384</v>
+        <v>0.01789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>123.39</v>
+        <v>52.62</v>
       </c>
       <c r="D22" t="n">
-        <v>133.73</v>
+        <v>57.14</v>
       </c>
       <c r="E22" t="n">
-        <v>8.380000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="F22" t="n">
-        <v>1.10452</v>
+        <v>0.34288</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.54</v>
+        <v>35.54</v>
       </c>
       <c r="D23" t="n">
-        <v>71.70999999999999</v>
+        <v>48.25</v>
       </c>
       <c r="E23" t="n">
-        <v>12.86</v>
+        <v>35.76</v>
       </c>
       <c r="F23" t="n">
-        <v>0.51027</v>
+        <v>2.43665</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -988,70 +988,70 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>340.65</v>
+        <v>63.54</v>
       </c>
       <c r="D24" t="n">
-        <v>371.63</v>
+        <v>72.89</v>
       </c>
       <c r="E24" t="n">
-        <v>9.09</v>
+        <v>14.72</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.20992</v>
+        <v>1.06357</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.81</v>
+        <v>155.62</v>
       </c>
       <c r="D25" t="n">
-        <v>11.01</v>
+        <v>163.28</v>
       </c>
       <c r="E25" t="n">
-        <v>40.97</v>
+        <v>4.92</v>
       </c>
       <c r="F25" t="n">
-        <v>0.11474</v>
+        <v>-0.05146</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41.55</v>
+        <v>7.81</v>
       </c>
       <c r="D26" t="n">
-        <v>68.84999999999999</v>
+        <v>11.16</v>
       </c>
       <c r="E26" t="n">
-        <v>65.7</v>
+        <v>42.96</v>
       </c>
       <c r="F26" t="n">
-        <v>0.36109</v>
+        <v>0.17858</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1060,118 +1060,118 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>48.68</v>
+        <v>41.55</v>
       </c>
       <c r="D27" t="n">
-        <v>61.1</v>
+        <v>71.3</v>
       </c>
       <c r="E27" t="n">
-        <v>25.51</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.47155</v>
+        <v>1.52289</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11.03</v>
+        <v>602.35</v>
       </c>
       <c r="D28" t="n">
-        <v>12.84</v>
+        <v>920.85</v>
       </c>
       <c r="E28" t="n">
-        <v>16.41</v>
+        <v>52.88</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01194</v>
+        <v>-5.02158</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>332.02</v>
+        <v>298.32</v>
       </c>
       <c r="D29" t="n">
-        <v>377.16</v>
+        <v>360.72</v>
       </c>
       <c r="E29" t="n">
-        <v>13.6</v>
+        <v>20.92</v>
       </c>
       <c r="F29" t="n">
-        <v>0.27114</v>
+        <v>1.53006</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.14</v>
+        <v>29.31</v>
       </c>
       <c r="D30" t="n">
-        <v>31.56</v>
+        <v>43.35</v>
       </c>
       <c r="E30" t="n">
-        <v>16.29</v>
+        <v>47.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.13487</v>
+        <v>0.40036</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>146.38</v>
+        <v>11.03</v>
       </c>
       <c r="D31" t="n">
-        <v>215.67</v>
+        <v>12.76</v>
       </c>
       <c r="E31" t="n">
-        <v>47.34</v>
+        <v>15.68</v>
       </c>
       <c r="F31" t="n">
-        <v>0.62778</v>
+        <v>0.11176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1180,184 +1180,184 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>179.43</v>
+        <v>146.38</v>
       </c>
       <c r="D32" t="n">
-        <v>190.13</v>
+        <v>215.05</v>
       </c>
       <c r="E32" t="n">
-        <v>5.96</v>
+        <v>46.91</v>
       </c>
       <c r="F32" t="n">
-        <v>0.43388</v>
+        <v>1.43466</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.99</v>
+        <v>332.02</v>
       </c>
       <c r="D33" t="n">
-        <v>37.63</v>
+        <v>382.62</v>
       </c>
       <c r="E33" t="n">
-        <v>44.79</v>
+        <v>15.24</v>
       </c>
       <c r="F33" t="n">
-        <v>0.74041</v>
+        <v>2.35615</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>205.77</v>
+        <v>179.43</v>
       </c>
       <c r="D34" t="n">
-        <v>248.37</v>
+        <v>194.41</v>
       </c>
       <c r="E34" t="n">
-        <v>20.7</v>
+        <v>8.35</v>
       </c>
       <c r="F34" t="n">
-        <v>3.26641</v>
+        <v>0.84732</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CACI</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>440.76</v>
+        <v>25.99</v>
       </c>
       <c r="D35" t="n">
-        <v>636.4</v>
+        <v>37.54</v>
       </c>
       <c r="E35" t="n">
-        <v>44.39</v>
+        <v>44.44</v>
       </c>
       <c r="F35" t="n">
-        <v>4.10788</v>
+        <v>0.84323</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>89.2</v>
+        <v>205.77</v>
       </c>
       <c r="D36" t="n">
-        <v>124.19</v>
+        <v>239.64</v>
       </c>
       <c r="E36" t="n">
-        <v>39.23</v>
+        <v>16.46</v>
       </c>
       <c r="F36" t="n">
-        <v>0.38279</v>
+        <v>3.49087</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>103.45</v>
+        <v>440.76</v>
       </c>
       <c r="D37" t="n">
-        <v>150.02</v>
+        <v>633.46</v>
       </c>
       <c r="E37" t="n">
-        <v>45.02</v>
+        <v>43.72</v>
       </c>
       <c r="F37" t="n">
-        <v>1.07197</v>
+        <v>4.61666</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>198.14</v>
+        <v>136.34</v>
       </c>
       <c r="D38" t="n">
-        <v>263.09</v>
+        <v>199.35</v>
       </c>
       <c r="E38" t="n">
-        <v>32.78</v>
+        <v>46.22</v>
       </c>
       <c r="F38" t="n">
-        <v>2.17265</v>
+        <v>0.24568</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RRC</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35.49</v>
+        <v>198.14</v>
       </c>
       <c r="D39" t="n">
-        <v>41.9</v>
+        <v>259.31</v>
       </c>
       <c r="E39" t="n">
-        <v>18.06</v>
+        <v>30.87</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08939999999999999</v>
+        <v>1.83716</v>
       </c>
     </row>
     <row r="40">
@@ -1375,13 +1375,13 @@
         <v>41.44</v>
       </c>
       <c r="D40" t="n">
-        <v>45.37</v>
+        <v>45.43</v>
       </c>
       <c r="E40" t="n">
-        <v>9.48</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.55671</v>
+        <v>0.5894</v>
       </c>
     </row>
     <row r="41">
@@ -1399,13 +1399,13 @@
         <v>510.39</v>
       </c>
       <c r="D41" t="n">
-        <v>643.33</v>
+        <v>656.95</v>
       </c>
       <c r="E41" t="n">
-        <v>26.05</v>
+        <v>28.72</v>
       </c>
       <c r="F41" t="n">
-        <v>5.93092</v>
+        <v>8.47274</v>
       </c>
     </row>
     <row r="42">
@@ -1429,7 +1429,7 @@
         <v>16.27</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04462</v>
+        <v>0.03846</v>
       </c>
     </row>
     <row r="43">
@@ -1447,19 +1447,19 @@
         <v>2.2</v>
       </c>
       <c r="D43" t="n">
-        <v>4.68</v>
+        <v>4.34</v>
       </c>
       <c r="E43" t="n">
-        <v>112.73</v>
+        <v>97.27</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.01815</v>
+        <v>0.00263</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>162.11</v>
+        <v>24.36</v>
       </c>
       <c r="D44" t="n">
-        <v>177.71</v>
+        <v>32.99</v>
       </c>
       <c r="E44" t="n">
-        <v>9.619999999999999</v>
+        <v>35.43</v>
       </c>
       <c r="F44" t="n">
-        <v>0.54084</v>
+        <v>0.42641</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1492,46 +1492,46 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>24.36</v>
+        <v>162.11</v>
       </c>
       <c r="D45" t="n">
-        <v>33.92</v>
+        <v>178.99</v>
       </c>
       <c r="E45" t="n">
-        <v>39.24</v>
+        <v>10.41</v>
       </c>
       <c r="F45" t="n">
-        <v>0.50814</v>
+        <v>1.06123</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>40.48</v>
+        <v>15.99</v>
       </c>
       <c r="D46" t="n">
-        <v>45.96</v>
+        <v>21.13</v>
       </c>
       <c r="E46" t="n">
-        <v>13.54</v>
+        <v>32.15</v>
       </c>
       <c r="F46" t="n">
-        <v>0.24459</v>
+        <v>0.56898</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1540,22 +1540,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>165.69</v>
+        <v>13.01</v>
       </c>
       <c r="D47" t="n">
-        <v>217.77</v>
+        <v>17.53</v>
       </c>
       <c r="E47" t="n">
-        <v>31.43</v>
+        <v>34.78</v>
       </c>
       <c r="F47" t="n">
-        <v>3.21866</v>
+        <v>0.37732</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1564,22 +1564,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.99</v>
+        <v>17.26</v>
       </c>
       <c r="D48" t="n">
-        <v>21.77</v>
+        <v>19.6</v>
       </c>
       <c r="E48" t="n">
-        <v>36.15</v>
+        <v>13.59</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6551900000000001</v>
+        <v>0.14763</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>51.98</v>
+        <v>104.89</v>
       </c>
       <c r="D49" t="n">
-        <v>66.97</v>
+        <v>119.54</v>
       </c>
       <c r="E49" t="n">
-        <v>28.84</v>
+        <v>13.97</v>
       </c>
       <c r="F49" t="n">
-        <v>0.22746</v>
+        <v>1.0939</v>
       </c>
     </row>
     <row r="50">
@@ -1615,13 +1615,13 @@
         <v>14.49</v>
       </c>
       <c r="D50" t="n">
-        <v>19.57</v>
+        <v>19.1</v>
       </c>
       <c r="E50" t="n">
-        <v>35.06</v>
+        <v>31.82</v>
       </c>
       <c r="F50" t="n">
-        <v>0.58352</v>
+        <v>0.51652</v>
       </c>
     </row>
     <row r="51">
@@ -1639,19 +1639,19 @@
         <v>38.92</v>
       </c>
       <c r="D51" t="n">
-        <v>51.55</v>
+        <v>50.38</v>
       </c>
       <c r="E51" t="n">
-        <v>32.45</v>
+        <v>29.43</v>
       </c>
       <c r="F51" t="n">
-        <v>0.30504</v>
+        <v>0.23551</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>47.94</v>
+        <v>53.57</v>
       </c>
       <c r="D52" t="n">
-        <v>63.52</v>
+        <v>69.8</v>
       </c>
       <c r="E52" t="n">
-        <v>32.5</v>
+        <v>30.3</v>
       </c>
       <c r="F52" t="n">
-        <v>0.82646</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53.57</v>
+        <v>40.25</v>
       </c>
       <c r="D53" t="n">
-        <v>71.87</v>
+        <v>49.14</v>
       </c>
       <c r="E53" t="n">
-        <v>34.16</v>
+        <v>22.09</v>
       </c>
       <c r="F53" t="n">
-        <v>0.94957</v>
+        <v>0.75446</v>
       </c>
     </row>
     <row r="54">
@@ -1711,19 +1711,19 @@
         <v>45.57</v>
       </c>
       <c r="D54" t="n">
-        <v>56.66</v>
+        <v>55.83</v>
       </c>
       <c r="E54" t="n">
-        <v>24.34</v>
+        <v>22.53</v>
       </c>
       <c r="F54" t="n">
-        <v>0.49648</v>
+        <v>0.39348</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1732,22 +1732,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>171.96</v>
+        <v>36.15</v>
       </c>
       <c r="D55" t="n">
-        <v>211.53</v>
+        <v>45.88</v>
       </c>
       <c r="E55" t="n">
-        <v>23.01</v>
+        <v>26.9</v>
       </c>
       <c r="F55" t="n">
-        <v>1.93053</v>
+        <v>0.78052</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.93</v>
+        <v>74.8</v>
       </c>
       <c r="D56" t="n">
-        <v>24.49</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>36.59</v>
+        <v>23.46</v>
       </c>
       <c r="F56" t="n">
-        <v>0.34403</v>
+        <v>1.07608</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1780,22 +1780,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>36.15</v>
+        <v>31.87</v>
       </c>
       <c r="D57" t="n">
-        <v>46.96</v>
+        <v>45.31</v>
       </c>
       <c r="E57" t="n">
-        <v>29.9</v>
+        <v>42.16</v>
       </c>
       <c r="F57" t="n">
-        <v>0.88425</v>
+        <v>1.03096</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1804,22 +1804,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>110.99</v>
+        <v>165.69</v>
       </c>
       <c r="D58" t="n">
-        <v>135.35</v>
+        <v>213.04</v>
       </c>
       <c r="E58" t="n">
-        <v>21.95</v>
+        <v>28.58</v>
       </c>
       <c r="F58" t="n">
-        <v>0.19167</v>
+        <v>2.93926</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>104.89</v>
+        <v>20.48</v>
       </c>
       <c r="D59" t="n">
-        <v>121.76</v>
+        <v>26.18</v>
       </c>
       <c r="E59" t="n">
-        <v>16.08</v>
+        <v>27.81</v>
       </c>
       <c r="F59" t="n">
-        <v>1.74063</v>
+        <v>0.35228</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.01</v>
+        <v>41.99</v>
       </c>
       <c r="D60" t="n">
-        <v>17.68</v>
+        <v>50.4</v>
       </c>
       <c r="E60" t="n">
-        <v>35.9</v>
+        <v>20.02</v>
       </c>
       <c r="F60" t="n">
-        <v>0.39546</v>
+        <v>0.4994</v>
       </c>
     </row>
     <row r="61">
@@ -1879,13 +1879,13 @@
         <v>52.58</v>
       </c>
       <c r="D61" t="n">
-        <v>65.43000000000001</v>
+        <v>64.75</v>
       </c>
       <c r="E61" t="n">
-        <v>24.44</v>
+        <v>23.16</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00565</v>
+        <v>0.04845</v>
       </c>
     </row>
     <row r="62">
@@ -1903,19 +1903,19 @@
         <v>103.22</v>
       </c>
       <c r="D62" t="n">
-        <v>141.22</v>
+        <v>134.41</v>
       </c>
       <c r="E62" t="n">
-        <v>36.81</v>
+        <v>30.22</v>
       </c>
       <c r="F62" t="n">
-        <v>2.28322</v>
+        <v>1.81577</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1924,2662 +1924,2662 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>31.87</v>
+        <v>27.02</v>
       </c>
       <c r="D63" t="n">
-        <v>47.41</v>
+        <v>30.14</v>
       </c>
       <c r="E63" t="n">
-        <v>48.76</v>
+        <v>11.55</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0579</v>
+        <v>-0.26502</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>17.26</v>
+        <v>124.44</v>
       </c>
       <c r="D64" t="n">
-        <v>19.84</v>
+        <v>190.79</v>
       </c>
       <c r="E64" t="n">
-        <v>14.95</v>
+        <v>53.31</v>
       </c>
       <c r="F64" t="n">
-        <v>0.16265</v>
+        <v>3.33997</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>40.25</v>
+        <v>55.53</v>
       </c>
       <c r="D65" t="n">
-        <v>51.33</v>
+        <v>61.42</v>
       </c>
       <c r="E65" t="n">
-        <v>27.53</v>
+        <v>10.6</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9265099999999999</v>
+        <v>1.10701</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>74.8</v>
+        <v>38.73</v>
       </c>
       <c r="D66" t="n">
-        <v>93.12</v>
+        <v>62.23</v>
       </c>
       <c r="E66" t="n">
-        <v>24.49</v>
+        <v>60.68</v>
       </c>
       <c r="F66" t="n">
-        <v>1.07146</v>
+        <v>0.72117</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SUZ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>41.99</v>
+        <v>7.67</v>
       </c>
       <c r="D67" t="n">
-        <v>51.45</v>
+        <v>9.18</v>
       </c>
       <c r="E67" t="n">
-        <v>22.53</v>
+        <v>19.69</v>
       </c>
       <c r="F67" t="n">
-        <v>0.50723</v>
+        <v>0.11771</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>20.48</v>
+        <v>136.06</v>
       </c>
       <c r="D68" t="n">
-        <v>26.72</v>
+        <v>164.75</v>
       </c>
       <c r="E68" t="n">
-        <v>30.47</v>
+        <v>21.09</v>
       </c>
       <c r="F68" t="n">
-        <v>0.32346</v>
+        <v>1.74965</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>38.73</v>
+        <v>56.4</v>
       </c>
       <c r="D69" t="n">
-        <v>63.28</v>
+        <v>79.33</v>
       </c>
       <c r="E69" t="n">
-        <v>63.39</v>
+        <v>40.66</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3855</v>
+        <v>2.26784</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>62.05</v>
+        <v>76.53</v>
       </c>
       <c r="D70" t="n">
-        <v>81.29000000000001</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>31.01</v>
+        <v>26.36</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.26747</v>
+        <v>1.54858</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>124.44</v>
+        <v>31.03</v>
       </c>
       <c r="D71" t="n">
-        <v>193.4</v>
+        <v>44.79</v>
       </c>
       <c r="E71" t="n">
-        <v>55.42</v>
+        <v>44.34</v>
       </c>
       <c r="F71" t="n">
-        <v>2.33628</v>
+        <v>0.82175</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>55.53</v>
+        <v>44.39</v>
       </c>
       <c r="D72" t="n">
-        <v>62.25</v>
+        <v>59.46</v>
       </c>
       <c r="E72" t="n">
-        <v>12.1</v>
+        <v>33.95</v>
       </c>
       <c r="F72" t="n">
-        <v>0.75354</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13.31</v>
+        <v>166.5</v>
       </c>
       <c r="D73" t="n">
-        <v>23.6</v>
+        <v>194.63</v>
       </c>
       <c r="E73" t="n">
-        <v>77.31</v>
+        <v>16.89</v>
       </c>
       <c r="F73" t="n">
-        <v>0.58601</v>
+        <v>1.14045</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13.43</v>
+        <v>59.71</v>
       </c>
       <c r="D74" t="n">
-        <v>15.03</v>
+        <v>78.61</v>
       </c>
       <c r="E74" t="n">
-        <v>11.91</v>
+        <v>31.65</v>
       </c>
       <c r="F74" t="n">
-        <v>0.08283</v>
+        <v>1.44492</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>136.06</v>
+        <v>136.68</v>
       </c>
       <c r="D75" t="n">
-        <v>169.32</v>
+        <v>154.81</v>
       </c>
       <c r="E75" t="n">
-        <v>24.45</v>
+        <v>13.26</v>
       </c>
       <c r="F75" t="n">
-        <v>1.98435</v>
+        <v>0.07715</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SUZ</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7.67</v>
+        <v>352.83</v>
       </c>
       <c r="D76" t="n">
-        <v>9.23</v>
+        <v>493.45</v>
       </c>
       <c r="E76" t="n">
-        <v>20.34</v>
+        <v>39.85</v>
       </c>
       <c r="F76" t="n">
-        <v>0.15642</v>
+        <v>2.28393</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>31.03</v>
+        <v>42.46</v>
       </c>
       <c r="D77" t="n">
-        <v>45.75</v>
+        <v>70.94</v>
       </c>
       <c r="E77" t="n">
-        <v>47.44</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>0.94193</v>
+        <v>2.19068</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>56.4</v>
+        <v>107.27</v>
       </c>
       <c r="D78" t="n">
-        <v>79.48</v>
+        <v>172.82</v>
       </c>
       <c r="E78" t="n">
-        <v>40.92</v>
+        <v>61.11</v>
       </c>
       <c r="F78" t="n">
-        <v>2.00392</v>
+        <v>0.05787</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>76.53</v>
+        <v>49.87</v>
       </c>
       <c r="D79" t="n">
-        <v>98.95</v>
+        <v>61.87</v>
       </c>
       <c r="E79" t="n">
-        <v>29.3</v>
+        <v>24.06</v>
       </c>
       <c r="F79" t="n">
-        <v>1.63317</v>
+        <v>0.5321900000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>82.31</v>
+        <v>60.37</v>
       </c>
       <c r="D80" t="n">
-        <v>129.6</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>57.45</v>
+        <v>29.32</v>
       </c>
       <c r="F80" t="n">
-        <v>2.83088</v>
+        <v>0.83774</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WDS</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>18.94</v>
+        <v>10.51</v>
       </c>
       <c r="D81" t="n">
-        <v>23.98</v>
+        <v>14.89</v>
       </c>
       <c r="E81" t="n">
-        <v>26.61</v>
+        <v>41.69</v>
       </c>
       <c r="F81" t="n">
-        <v>0.15742</v>
+        <v>0.27314</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>107.27</v>
+        <v>62.12</v>
       </c>
       <c r="D82" t="n">
-        <v>172.56</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E82" t="n">
-        <v>60.87</v>
+        <v>26.93</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.66867</v>
+        <v>1.0866</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>59.71</v>
+        <v>247.22</v>
       </c>
       <c r="D83" t="n">
-        <v>80.06</v>
+        <v>300.91</v>
       </c>
       <c r="E83" t="n">
-        <v>34.08</v>
+        <v>21.72</v>
       </c>
       <c r="F83" t="n">
-        <v>1.2886</v>
+        <v>3.38218</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>42.46</v>
+        <v>102.17</v>
       </c>
       <c r="D84" t="n">
-        <v>71.84999999999999</v>
+        <v>133.37</v>
       </c>
       <c r="E84" t="n">
-        <v>69.22</v>
+        <v>30.54</v>
       </c>
       <c r="F84" t="n">
-        <v>1.88023</v>
+        <v>1.13546</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>352.83</v>
+        <v>48.79</v>
       </c>
       <c r="D85" t="n">
-        <v>497.12</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>40.9</v>
+        <v>36.5</v>
       </c>
       <c r="F85" t="n">
-        <v>2.41856</v>
+        <v>0.44193</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>44.39</v>
+        <v>150.12</v>
       </c>
       <c r="D86" t="n">
-        <v>60.34</v>
+        <v>251.63</v>
       </c>
       <c r="E86" t="n">
-        <v>35.93</v>
+        <v>67.62</v>
       </c>
       <c r="F86" t="n">
-        <v>0.25495</v>
+        <v>7.11738</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>170.28</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="D87" t="n">
-        <v>241.96</v>
+        <v>100.54</v>
       </c>
       <c r="E87" t="n">
-        <v>42.1</v>
+        <v>34.07</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.37415</v>
+        <v>1.48697</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>136.68</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="D88" t="n">
-        <v>156.99</v>
+        <v>118.66</v>
       </c>
       <c r="E88" t="n">
-        <v>14.86</v>
+        <v>56.05</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.72946</v>
+        <v>3.13077</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>49.87</v>
+        <v>140.71</v>
       </c>
       <c r="D89" t="n">
-        <v>62.3</v>
+        <v>183.93</v>
       </c>
       <c r="E89" t="n">
-        <v>24.92</v>
+        <v>30.71</v>
       </c>
       <c r="F89" t="n">
-        <v>0.41873</v>
+        <v>0.12496</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>166.5</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>195.47</v>
+        <v>93.47</v>
       </c>
       <c r="E90" t="n">
-        <v>17.4</v>
+        <v>11.51</v>
       </c>
       <c r="F90" t="n">
-        <v>1.03418</v>
+        <v>0.57595</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>60.37</v>
+        <v>125.73</v>
       </c>
       <c r="D91" t="n">
-        <v>78.72</v>
+        <v>191.89</v>
       </c>
       <c r="E91" t="n">
-        <v>30.4</v>
+        <v>52.62</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9964499999999999</v>
+        <v>2.78395</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VG</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10.51</v>
+        <v>141.17</v>
       </c>
       <c r="D92" t="n">
-        <v>15.29</v>
+        <v>180.05</v>
       </c>
       <c r="E92" t="n">
-        <v>45.48</v>
+        <v>27.54</v>
       </c>
       <c r="F92" t="n">
-        <v>0.36599</v>
+        <v>1.73057</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>62.12</v>
+        <v>32.47</v>
       </c>
       <c r="D93" t="n">
-        <v>79.97</v>
+        <v>38.88</v>
       </c>
       <c r="E93" t="n">
-        <v>28.73</v>
+        <v>19.74</v>
       </c>
       <c r="F93" t="n">
-        <v>0.93677</v>
+        <v>0.49904</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>ENSG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>48.79</v>
+        <v>147.13</v>
       </c>
       <c r="D94" t="n">
-        <v>67.56999999999999</v>
+        <v>177.18</v>
       </c>
       <c r="E94" t="n">
-        <v>38.49</v>
+        <v>20.42</v>
       </c>
       <c r="F94" t="n">
-        <v>0.33897</v>
+        <v>0.01231</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>247.22</v>
+        <v>53.82</v>
       </c>
       <c r="D95" t="n">
-        <v>297.26</v>
+        <v>75.13</v>
       </c>
       <c r="E95" t="n">
-        <v>20.24</v>
+        <v>39.59</v>
       </c>
       <c r="F95" t="n">
-        <v>2.46873</v>
+        <v>0.45444</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>102.17</v>
+        <v>19.82</v>
       </c>
       <c r="D96" t="n">
-        <v>135.54</v>
+        <v>25.03</v>
       </c>
       <c r="E96" t="n">
-        <v>32.66</v>
+        <v>26.29</v>
       </c>
       <c r="F96" t="n">
-        <v>1.43815</v>
+        <v>0.22801</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>76.04000000000001</v>
+        <v>121.48</v>
       </c>
       <c r="D97" t="n">
-        <v>123.51</v>
+        <v>148.49</v>
       </c>
       <c r="E97" t="n">
-        <v>62.43</v>
+        <v>22.23</v>
       </c>
       <c r="F97" t="n">
-        <v>3.02454</v>
+        <v>0.4463</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BBDO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>125.73</v>
+        <v>2.86</v>
       </c>
       <c r="D98" t="n">
-        <v>195.62</v>
+        <v>3.17</v>
       </c>
       <c r="E98" t="n">
-        <v>55.59</v>
+        <v>10.84</v>
       </c>
       <c r="F98" t="n">
-        <v>0.83805</v>
+        <v>0.02063</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>150.12</v>
+        <v>14.94</v>
       </c>
       <c r="D99" t="n">
-        <v>255.65</v>
+        <v>19.82</v>
       </c>
       <c r="E99" t="n">
-        <v>70.3</v>
+        <v>32.63</v>
       </c>
       <c r="F99" t="n">
-        <v>6.95816</v>
+        <v>0.45406</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>275.27</v>
+        <v>361.32</v>
       </c>
       <c r="D100" t="n">
-        <v>353.13</v>
+        <v>432.02</v>
       </c>
       <c r="E100" t="n">
-        <v>28.28</v>
+        <v>19.57</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.49134</v>
+        <v>4.82436</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>140.71</v>
+        <v>161.37</v>
       </c>
       <c r="D101" t="n">
-        <v>185.92</v>
+        <v>266.56</v>
       </c>
       <c r="E101" t="n">
-        <v>32.13</v>
+        <v>65.19</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.65188</v>
+        <v>0.26188</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>74.98999999999999</v>
+        <v>15.03</v>
       </c>
       <c r="D102" t="n">
-        <v>102.38</v>
+        <v>18.77</v>
       </c>
       <c r="E102" t="n">
-        <v>36.52</v>
+        <v>24.92</v>
       </c>
       <c r="F102" t="n">
-        <v>1.20454</v>
+        <v>0.17877</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>83.81999999999999</v>
+        <v>140.19</v>
       </c>
       <c r="D103" t="n">
-        <v>95.06</v>
+        <v>148.12</v>
       </c>
       <c r="E103" t="n">
-        <v>13.41</v>
+        <v>5.65</v>
       </c>
       <c r="F103" t="n">
-        <v>0.23447</v>
+        <v>0.51546</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>76.55</v>
+        <v>195.11</v>
       </c>
       <c r="D104" t="n">
-        <v>102.61</v>
+        <v>249.95</v>
       </c>
       <c r="E104" t="n">
-        <v>34.04</v>
+        <v>28.11</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.89647</v>
+        <v>0.8667899999999999</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>141.17</v>
+        <v>72.55</v>
       </c>
       <c r="D105" t="n">
-        <v>176.85</v>
+        <v>76.23</v>
       </c>
       <c r="E105" t="n">
-        <v>25.27</v>
+        <v>5.07</v>
       </c>
       <c r="F105" t="n">
-        <v>1.14115</v>
+        <v>-0.10261</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>33.22</v>
+        <v>277.69</v>
       </c>
       <c r="D106" t="n">
-        <v>38.83</v>
+        <v>329.91</v>
       </c>
       <c r="E106" t="n">
-        <v>16.89</v>
+        <v>18.81</v>
       </c>
       <c r="F106" t="n">
-        <v>0.12529</v>
+        <v>0.7357</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>450.75</v>
+        <v>73.75</v>
       </c>
       <c r="D107" t="n">
-        <v>544.3200000000001</v>
+        <v>93.45</v>
       </c>
       <c r="E107" t="n">
-        <v>20.76</v>
+        <v>26.71</v>
       </c>
       <c r="F107" t="n">
-        <v>2.42297</v>
+        <v>0.59205</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>48.87</v>
+        <v>182.82</v>
       </c>
       <c r="D108" t="n">
-        <v>58.8</v>
+        <v>228.01</v>
       </c>
       <c r="E108" t="n">
-        <v>20.32</v>
+        <v>24.72</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.23533</v>
+        <v>-0.3764</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>32.47</v>
+        <v>23.85</v>
       </c>
       <c r="D109" t="n">
-        <v>38.62</v>
+        <v>34.6</v>
       </c>
       <c r="E109" t="n">
-        <v>18.94</v>
+        <v>45.07</v>
       </c>
       <c r="F109" t="n">
-        <v>0.35367</v>
+        <v>0.23718</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BBDO</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2.86</v>
+        <v>275.99</v>
       </c>
       <c r="D110" t="n">
-        <v>3.16</v>
+        <v>322.4</v>
       </c>
       <c r="E110" t="n">
-        <v>10.49</v>
+        <v>16.82</v>
       </c>
       <c r="F110" t="n">
-        <v>0.02491</v>
+        <v>1.9334</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>WTRG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>16.44</v>
+        <v>36.25</v>
       </c>
       <c r="D111" t="n">
-        <v>33.61</v>
+        <v>41.44</v>
       </c>
       <c r="E111" t="n">
-        <v>104.44</v>
+        <v>14.31</v>
       </c>
       <c r="F111" t="n">
-        <v>0.45364</v>
+        <v>0.10546</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>14.94</v>
+        <v>9.85</v>
       </c>
       <c r="D112" t="n">
-        <v>19.53</v>
+        <v>13.6</v>
       </c>
       <c r="E112" t="n">
-        <v>30.72</v>
+        <v>38.02</v>
       </c>
       <c r="F112" t="n">
-        <v>0.51817</v>
+        <v>0.43708</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>121.48</v>
+        <v>309.78</v>
       </c>
       <c r="D113" t="n">
-        <v>146.3</v>
+        <v>343.3</v>
       </c>
       <c r="E113" t="n">
-        <v>20.43</v>
+        <v>10.82</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1059</v>
+        <v>-0.12017</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>53.82</v>
+        <v>63.54</v>
       </c>
       <c r="D114" t="n">
-        <v>74.08</v>
+        <v>70.53</v>
       </c>
       <c r="E114" t="n">
-        <v>37.64</v>
+        <v>11</v>
       </c>
       <c r="F114" t="n">
-        <v>0.46228</v>
+        <v>0.3841</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>19.82</v>
+        <v>190.4</v>
       </c>
       <c r="D115" t="n">
-        <v>25.46</v>
+        <v>218.92</v>
       </c>
       <c r="E115" t="n">
-        <v>28.46</v>
+        <v>14.98</v>
       </c>
       <c r="F115" t="n">
-        <v>0.29096</v>
+        <v>0.79484</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>361.32</v>
+        <v>529.12</v>
       </c>
       <c r="D116" t="n">
-        <v>423.82</v>
+        <v>673.59</v>
       </c>
       <c r="E116" t="n">
-        <v>17.3</v>
+        <v>27.3</v>
       </c>
       <c r="F116" t="n">
-        <v>4.19429</v>
+        <v>8.185090000000001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OHI</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>43.67</v>
+        <v>57.4</v>
       </c>
       <c r="D117" t="n">
-        <v>47.13</v>
+        <v>105.45</v>
       </c>
       <c r="E117" t="n">
-        <v>7.92</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="F117" t="n">
-        <v>0.04408</v>
+        <v>1.24375</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>15.03</v>
+        <v>303.86</v>
       </c>
       <c r="D118" t="n">
-        <v>18.7</v>
+        <v>381.15</v>
       </c>
       <c r="E118" t="n">
-        <v>24.42</v>
+        <v>25.44</v>
       </c>
       <c r="F118" t="n">
-        <v>0.12759</v>
+        <v>-0.42143</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>140.19</v>
+        <v>149.93</v>
       </c>
       <c r="D119" t="n">
-        <v>146.67</v>
+        <v>281.58</v>
       </c>
       <c r="E119" t="n">
-        <v>4.62</v>
+        <v>87.8</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02814</v>
+        <v>-1.57099</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>195.11</v>
+        <v>186.61</v>
       </c>
       <c r="D120" t="n">
-        <v>248.36</v>
+        <v>246.95</v>
       </c>
       <c r="E120" t="n">
-        <v>27.29</v>
+        <v>32.33</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6946099999999999</v>
+        <v>1.68022</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>275.99</v>
+        <v>250.4</v>
       </c>
       <c r="D121" t="n">
-        <v>318.2</v>
+        <v>323.3</v>
       </c>
       <c r="E121" t="n">
-        <v>15.29</v>
+        <v>29.11</v>
       </c>
       <c r="F121" t="n">
-        <v>1.98323</v>
+        <v>-1.716</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>23.85</v>
+        <v>43.3</v>
       </c>
       <c r="D122" t="n">
-        <v>34.15</v>
+        <v>72.31</v>
       </c>
       <c r="E122" t="n">
-        <v>43.19</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01267</v>
+        <v>0.02918</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>277.69</v>
+        <v>438.34</v>
       </c>
       <c r="D123" t="n">
-        <v>328.7</v>
+        <v>649.9299999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>18.37</v>
+        <v>48.27</v>
       </c>
       <c r="F123" t="n">
-        <v>0.45735</v>
+        <v>7.93783</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>182.82</v>
+        <v>26.18</v>
       </c>
       <c r="D124" t="n">
-        <v>229.44</v>
+        <v>36.74</v>
       </c>
       <c r="E124" t="n">
-        <v>25.5</v>
+        <v>40.34</v>
       </c>
       <c r="F124" t="n">
-        <v>-1.30339</v>
+        <v>0.31287</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>73.75</v>
+        <v>73.42</v>
       </c>
       <c r="D125" t="n">
-        <v>93.75</v>
+        <v>88.61</v>
       </c>
       <c r="E125" t="n">
-        <v>27.12</v>
+        <v>20.69</v>
       </c>
       <c r="F125" t="n">
-        <v>0.46174</v>
+        <v>0.55697</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9.85</v>
+        <v>161.91</v>
       </c>
       <c r="D126" t="n">
-        <v>14</v>
+        <v>209.88</v>
       </c>
       <c r="E126" t="n">
-        <v>42.13</v>
+        <v>29.62</v>
       </c>
       <c r="F126" t="n">
-        <v>0.47309</v>
+        <v>-0.49204</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>309.78</v>
+        <v>102.87</v>
       </c>
       <c r="D127" t="n">
-        <v>341.86</v>
+        <v>175.15</v>
       </c>
       <c r="E127" t="n">
-        <v>10.36</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.62071</v>
+        <v>0.66394</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>WTRG</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>36.25</v>
+        <v>163.43</v>
       </c>
       <c r="D128" t="n">
-        <v>41.48</v>
+        <v>200.78</v>
       </c>
       <c r="E128" t="n">
-        <v>14.43</v>
+        <v>22.85</v>
       </c>
       <c r="F128" t="n">
-        <v>0.15456</v>
+        <v>2.47764</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>190.4</v>
+        <v>55.52</v>
       </c>
       <c r="D129" t="n">
-        <v>221.31</v>
+        <v>92.75</v>
       </c>
       <c r="E129" t="n">
-        <v>16.23</v>
+        <v>67.06</v>
       </c>
       <c r="F129" t="n">
-        <v>0.59114</v>
+        <v>2.21822</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>63.54</v>
+        <v>1025.53</v>
       </c>
       <c r="D130" t="n">
-        <v>71.28</v>
+        <v>1382.75</v>
       </c>
       <c r="E130" t="n">
-        <v>12.18</v>
+        <v>34.83</v>
       </c>
       <c r="F130" t="n">
-        <v>0.374</v>
+        <v>-11.89064</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GFL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>33.54</v>
+        <v>99.3</v>
       </c>
       <c r="D131" t="n">
-        <v>42.18</v>
+        <v>150.62</v>
       </c>
       <c r="E131" t="n">
-        <v>25.76</v>
+        <v>51.68</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1388</v>
+        <v>2.70831</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>QGEN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>529.12</v>
+        <v>32.63</v>
       </c>
       <c r="D132" t="n">
-        <v>684.04</v>
+        <v>43.3</v>
       </c>
       <c r="E132" t="n">
-        <v>29.28</v>
+        <v>32.7</v>
       </c>
       <c r="F132" t="n">
-        <v>9.50407</v>
+        <v>-0.12919</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>57.4</v>
+        <v>725.17</v>
       </c>
       <c r="D133" t="n">
-        <v>103.69</v>
+        <v>892</v>
       </c>
       <c r="E133" t="n">
-        <v>80.64</v>
+        <v>23.01</v>
       </c>
       <c r="F133" t="n">
-        <v>0.53257</v>
+        <v>3.30463</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>161.91</v>
+        <v>77.17</v>
       </c>
       <c r="D134" t="n">
-        <v>209.36</v>
+        <v>88.89</v>
       </c>
       <c r="E134" t="n">
-        <v>29.31</v>
+        <v>15.19</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.52751</v>
+        <v>-0.98344</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>63.16</v>
+        <v>197.73</v>
       </c>
       <c r="D135" t="n">
-        <v>100.67</v>
+        <v>222.26</v>
       </c>
       <c r="E135" t="n">
-        <v>59.39</v>
+        <v>12.41</v>
       </c>
       <c r="F135" t="n">
-        <v>1.35459</v>
+        <v>0.96355</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>250.4</v>
+        <v>79.58</v>
       </c>
       <c r="D136" t="n">
-        <v>323.97</v>
+        <v>97.39</v>
       </c>
       <c r="E136" t="n">
-        <v>29.38</v>
+        <v>22.38</v>
       </c>
       <c r="F136" t="n">
-        <v>-3.61611</v>
+        <v>-0.28185</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>102.87</v>
+        <v>417.83</v>
       </c>
       <c r="D137" t="n">
-        <v>174.73</v>
+        <v>553.22</v>
       </c>
       <c r="E137" t="n">
-        <v>69.86</v>
+        <v>32.4</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.36801</v>
+        <v>6.39645</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BIO-B</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>186.61</v>
+        <v>255.54</v>
       </c>
       <c r="D138" t="n">
-        <v>247.08</v>
+        <v>365.08</v>
       </c>
       <c r="E138" t="n">
-        <v>32.4</v>
+        <v>42.87</v>
       </c>
       <c r="F138" t="n">
-        <v>0.19288</v>
+        <v>2.95635</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>26.18</v>
+        <v>12.64</v>
       </c>
       <c r="D139" t="n">
-        <v>36.72</v>
+        <v>17.67</v>
       </c>
       <c r="E139" t="n">
-        <v>40.26</v>
+        <v>39.75</v>
       </c>
       <c r="F139" t="n">
-        <v>0.23738</v>
+        <v>0.19725</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>43.3</v>
+        <v>32.32</v>
       </c>
       <c r="D140" t="n">
-        <v>72.34</v>
+        <v>38.5</v>
       </c>
       <c r="E140" t="n">
-        <v>67.06999999999999</v>
+        <v>19.12</v>
       </c>
       <c r="F140" t="n">
-        <v>0.008569999999999999</v>
+        <v>0.11506</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>BRK-A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>73.42</v>
+        <v>699965</v>
       </c>
       <c r="D141" t="n">
-        <v>89.72</v>
+        <v>781466.0600000001</v>
       </c>
       <c r="E141" t="n">
-        <v>22.2</v>
+        <v>11.64</v>
       </c>
       <c r="F141" t="n">
-        <v>0.70402</v>
+        <v>5256.69837</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>FMS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-         